--- a/Objets_parlementaires_Jura.xlsx
+++ b/Objets_parlementaires_Jura.xlsx
@@ -80,6 +80,66 @@
     <t xml:space="preserve">Statut_Change_Date</t>
   </si>
   <si>
+    <t xml:space="preserve">26.3597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Po.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Juillard Charles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le Centre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EJPD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Für eine Harmonisierung der Definition des Konkubinats im Bundesrecht</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pour une harmonisation de la définition du concubinage dans la législation fédérale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armonizzare la definizione di concubinato nella legislazione federale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Procéder à un examen de la législation pour recenser les textes qui font référence directement ou indirectement à la notion de concubinage et de ses effets concrets pour les citoyens (fiscalité, assurances sociales, droits réels, droit de la famille, etc.),&lt;/li&gt;&lt;li&gt;Établir une comparaison de ces notions différentes et de leurs effets,&lt;/li&gt;&lt;li&gt;Dresser un rapport à l’attention du Parlement,&lt;/li&gt;&lt;li&gt;Proposer l’uniformisation ou l’harmonisation des dispositions légales concernées,&lt;/li&gt;&lt;li&gt;Si de tels projets sont déjà menés, en indiquer l'état de situation et le calendrier de mise en œuvre.&lt;/li&gt;&lt;/ul&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;das geltende Recht zu überprüfen, um die Bestimmungen zu ermitteln, die sich direkt oder indirekt auf den Begriff des Konkubinats beziehen, und die jeweiligen konkreten Auswirkungen auf die Bürgerinnen und Bürger zu erfassen&amp;nbsp;(Steuerrecht, Sozialversicherungsrecht, Sachenrecht, Familienrecht usw.);&lt;/li&gt;&lt;li&gt;die unterschiedlichen Begriffe und ihre Auswirkungen zu vergleichen;&lt;/li&gt;&lt;li&gt;einen Bericht zuhanden des Parlaments auszuarbeiten;&lt;/li&gt;&lt;li&gt;eine Vereinheitlichung oder Harmonisierung der entsprechenden gesetzlichen Bestimmungen vorzuschlagen;&lt;/li&gt;&lt;li&gt;für den Fall, dass solche Projekte bereits durchgeführt werden, deren aktuellen Stand und den Umsetzungszeitplan anzugeben.&lt;/li&gt;&lt;/ul&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Erledigt / Liquidé</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Titre uniquement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soziale Fragen|Zivilrecht|Sozialer Schutz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Questions sociales|Droit civil|Protection sociale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Questioni sociali|Diritto civile|Protezione sociale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-07</t>
+  </si>
+  <si>
     <t xml:space="preserve">26.3564</t>
   </si>
   <si>
@@ -125,9 +185,6 @@
     <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263564</t>
   </si>
   <si>
-    <t xml:space="preserve">Titre uniquement</t>
-  </si>
-  <si>
     <t xml:space="preserve">Beschäftigung und Arbeit|Zivilrecht|Gesundheit</t>
   </si>
   <si>
@@ -200,18 +257,9 @@
     <t xml:space="preserve">26.3891</t>
   </si>
   <si>
-    <t xml:space="preserve">Juillard Charles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Le Centre</t>
-  </si>
-  <si>
     <t xml:space="preserve">2026-06-19</t>
   </si>
   <si>
-    <t xml:space="preserve">SR</t>
-  </si>
-  <si>
     <t xml:space="preserve">Für eine neue Finanzierungsquelle für grosse öffentliche Ausgabenposten. Eine befristete Solidaritätsabgabe auf den Zahlungsverkehr</t>
   </si>
   <si>
@@ -351,54 +399,6 @@
   </si>
   <si>
     <t xml:space="preserve">Politica di sicurezza|Media e comunicazione</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Po.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EJPD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Für eine Harmonisierung der Definition des Konkubinats im Bundesrecht</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pour une harmonisation de la définition du concubinage dans la législation fédérale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Armonizzare la definizione di concubinato nella legislazione federale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Procéder à un examen de la législation pour recenser les textes qui font référence directement ou indirectement à la notion de concubinage et de ses effets concrets pour les citoyens (fiscalité, assurances sociales, droits réels, droit de la famille, etc.),&lt;/li&gt;&lt;li&gt;Établir une comparaison de ces notions différentes et de leurs effets,&lt;/li&gt;&lt;li&gt;Dresser un rapport à l’attention du Parlement,&lt;/li&gt;&lt;li&gt;Proposer l’uniformisation ou l’harmonisation des dispositions légales concernées,&lt;/li&gt;&lt;li&gt;Si de tels projets sont déjà menés, en indiquer l'état de situation et le calendrier de mise en œuvre.&lt;/li&gt;&lt;/ul&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;das geltende Recht zu überprüfen, um die Bestimmungen zu ermitteln, die sich direkt oder indirekt auf den Begriff des Konkubinats beziehen, und die jeweiligen konkreten Auswirkungen auf die Bürgerinnen und Bürger zu erfassen&amp;nbsp;(Steuerrecht, Sozialversicherungsrecht, Sachenrecht, Familienrecht usw.);&lt;/li&gt;&lt;li&gt;die unterschiedlichen Begriffe und ihre Auswirkungen zu vergleichen;&lt;/li&gt;&lt;li&gt;einen Bericht zuhanden des Parlaments auszuarbeiten;&lt;/li&gt;&lt;li&gt;eine Vereinheitlichung oder Harmonisierung der entsprechenden gesetzlichen Bestimmungen vorzuschlagen;&lt;/li&gt;&lt;li&gt;für den Fall, dass solche Projekte bereits durchgeführt werden, deren aktuellen Stand und den Umsetzungszeitplan anzugeben.&lt;/li&gt;&lt;/ul&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Erledigt / Liquidé</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Soziale Fragen|Zivilrecht|Sozialer Schutz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Questions sociales|Droit civil|Protection sociale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Questioni sociali|Diritto civile|Protezione sociale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-07</t>
   </si>
   <si>
     <t xml:space="preserve">26.3571</t>
@@ -5613,7 +5613,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>20263564</v>
+        <v>20263597</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
@@ -5679,7 +5679,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>20263518</v>
+        <v>20263564</v>
       </c>
       <c r="B3" t="s">
         <v>42</v>
@@ -5697,37 +5697,37 @@
         <v>46</v>
       </c>
       <c r="G3" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q3" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="R3" t="s">
         <v>57</v>
@@ -5745,121 +5745,121 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>20263891</v>
+        <v>20263518</v>
       </c>
       <c r="B4" t="s">
         <v>61</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="D4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G4" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="H4" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="I4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="L4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="M4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="N4" t="s">
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="O4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="P4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Q4" t="s">
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="R4" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="S4" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="T4" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="U4" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="V4"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>20263936</v>
+        <v>20263891</v>
       </c>
       <c r="B5" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D5" t="s">
-        <v>78</v>
+        <v>24</v>
       </c>
       <c r="E5" t="s">
-        <v>79</v>
+        <v>25</v>
       </c>
       <c r="F5" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="G5" t="s">
         <v>27</v>
       </c>
       <c r="H5" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="I5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="N5" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="O5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="P5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Q5" t="s">
-        <v>88</v>
+        <v>37</v>
       </c>
       <c r="R5" t="s">
         <v>89</v>
@@ -5871,209 +5871,207 @@
         <v>91</v>
       </c>
       <c r="U5" t="s">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="V5"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>20263949</v>
+        <v>20263936</v>
       </c>
       <c r="B6" t="s">
+        <v>93</v>
+      </c>
+      <c r="C6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D6" t="s">
+        <v>94</v>
+      </c>
+      <c r="E6" t="s">
+        <v>95</v>
+      </c>
+      <c r="F6" t="s">
+        <v>81</v>
+      </c>
+      <c r="G6" t="s">
+        <v>47</v>
+      </c>
+      <c r="H6" t="s">
+        <v>96</v>
+      </c>
+      <c r="I6" t="s">
+        <v>97</v>
+      </c>
+      <c r="J6" t="s">
+        <v>98</v>
+      </c>
+      <c r="K6" t="s">
+        <v>99</v>
+      </c>
+      <c r="L6" t="s">
+        <v>100</v>
+      </c>
+      <c r="M6" t="s">
+        <v>101</v>
+      </c>
+      <c r="N6" t="s">
+        <v>54</v>
+      </c>
+      <c r="O6" t="s">
+        <v>102</v>
+      </c>
+      <c r="P6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>104</v>
+      </c>
+      <c r="R6" t="s">
+        <v>105</v>
+      </c>
+      <c r="S6" t="s">
+        <v>106</v>
+      </c>
+      <c r="T6" t="s">
+        <v>107</v>
+      </c>
+      <c r="U6" t="s">
         <v>92</v>
-      </c>
-      <c r="C6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" t="s">
-        <v>78</v>
-      </c>
-      <c r="E6" t="s">
-        <v>79</v>
-      </c>
-      <c r="F6" t="s">
-        <v>64</v>
-      </c>
-      <c r="G6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H6" t="s">
-        <v>80</v>
-      </c>
-      <c r="I6" t="s">
-        <v>93</v>
-      </c>
-      <c r="J6" t="s">
-        <v>94</v>
-      </c>
-      <c r="K6" t="s">
-        <v>95</v>
-      </c>
-      <c r="L6" t="s">
-        <v>96</v>
-      </c>
-      <c r="M6" t="s">
-        <v>97</v>
-      </c>
-      <c r="N6" t="s">
-        <v>34</v>
-      </c>
-      <c r="O6" t="s">
-        <v>98</v>
-      </c>
-      <c r="P6" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>88</v>
-      </c>
-      <c r="R6" t="s">
-        <v>89</v>
-      </c>
-      <c r="S6" t="s">
-        <v>90</v>
-      </c>
-      <c r="T6" t="s">
-        <v>91</v>
-      </c>
-      <c r="U6" t="s">
-        <v>76</v>
       </c>
       <c r="V6"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>20263628</v>
+        <v>20263949</v>
       </c>
       <c r="B7" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="C7" t="s">
         <v>43</v>
       </c>
       <c r="D7" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="E7" t="s">
-        <v>63</v>
+        <v>95</v>
       </c>
       <c r="F7" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="G7" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="H7" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="I7" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="J7" t="s">
+        <v>110</v>
+      </c>
+      <c r="K7" t="s">
+        <v>111</v>
+      </c>
+      <c r="L7" t="s">
+        <v>112</v>
+      </c>
+      <c r="M7" t="s">
+        <v>113</v>
+      </c>
+      <c r="N7" t="s">
+        <v>54</v>
+      </c>
+      <c r="O7" t="s">
+        <v>114</v>
+      </c>
+      <c r="P7" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q7" t="s">
         <v>104</v>
       </c>
-      <c r="K7" t="s">
+      <c r="R7" t="s">
         <v>105</v>
       </c>
-      <c r="L7" t="s">
+      <c r="S7" t="s">
         <v>106</v>
       </c>
-      <c r="M7" t="s">
+      <c r="T7" t="s">
         <v>107</v>
       </c>
-      <c r="N7" t="s">
-        <v>34</v>
-      </c>
-      <c r="O7" t="s">
-        <v>108</v>
-      </c>
-      <c r="P7" t="s">
-        <v>109</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>37</v>
-      </c>
-      <c r="R7" t="s">
-        <v>110</v>
-      </c>
-      <c r="S7" t="s">
-        <v>111</v>
-      </c>
-      <c r="T7" t="s">
-        <v>112</v>
-      </c>
       <c r="U7" t="s">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="V7"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>20263597</v>
+        <v>20263628</v>
       </c>
       <c r="B8" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C8" t="s">
-        <v>114</v>
+        <v>62</v>
       </c>
       <c r="D8" t="s">
-        <v>62</v>
+        <v>24</v>
       </c>
       <c r="E8" t="s">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="F8" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G8" t="s">
-        <v>65</v>
+        <v>27</v>
       </c>
       <c r="H8" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="I8" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="J8" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="K8" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="L8" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="M8" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="N8" t="s">
-        <v>122</v>
+        <v>54</v>
       </c>
       <c r="O8" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="P8" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="Q8" t="s">
         <v>37</v>
       </c>
       <c r="R8" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="S8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="T8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="U8" t="s">
-        <v>128</v>
-      </c>
-      <c r="V8" t="s">
-        <v>128</v>
-      </c>
+        <v>92</v>
+      </c>
+      <c r="V8"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -6083,7 +6081,7 @@
         <v>129</v>
       </c>
       <c r="C9" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="D9" t="s">
         <v>130</v>
@@ -6092,13 +6090,13 @@
         <v>131</v>
       </c>
       <c r="F9" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="G9" t="s">
-        <v>65</v>
+        <v>27</v>
       </c>
       <c r="H9" t="s">
-        <v>116</v>
+        <v>28</v>
       </c>
       <c r="I9" t="s">
         <v>132</v>
@@ -6116,7 +6114,7 @@
         <v>136</v>
       </c>
       <c r="N9" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="O9" t="s">
         <v>137</v>
@@ -6149,19 +6147,19 @@
         <v>144</v>
       </c>
       <c r="C10" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D10" t="s">
         <v>145</v>
       </c>
       <c r="E10" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="F10" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="G10" t="s">
-        <v>65</v>
+        <v>27</v>
       </c>
       <c r="H10" t="s">
         <v>146</v>
@@ -6182,7 +6180,7 @@
         <v>151</v>
       </c>
       <c r="N10" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="O10" t="s">
         <v>152</v>
@@ -6215,19 +6213,19 @@
         <v>158</v>
       </c>
       <c r="C11" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D11" t="s">
         <v>159</v>
       </c>
       <c r="E11" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="F11" t="s">
         <v>160</v>
       </c>
       <c r="G11" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H11" t="s">
         <v>146</v>
@@ -6248,7 +6246,7 @@
         <v>165</v>
       </c>
       <c r="N11" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="O11" t="s">
         <v>166</v>
@@ -6257,7 +6255,7 @@
         <v>167</v>
       </c>
       <c r="Q11" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="R11" t="s">
         <v>168</v>
@@ -6281,19 +6279,19 @@
         <v>171</v>
       </c>
       <c r="C12" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D12" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="E12" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="F12" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="G12" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H12" t="s">
         <v>146</v>
@@ -6314,7 +6312,7 @@
         <v>176</v>
       </c>
       <c r="N12" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="O12" t="s">
         <v>177</v>
@@ -6347,22 +6345,22 @@
         <v>182</v>
       </c>
       <c r="C13" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="D13" t="s">
         <v>145</v>
       </c>
       <c r="E13" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="F13" t="s">
         <v>183</v>
       </c>
       <c r="G13" t="s">
-        <v>65</v>
+        <v>27</v>
       </c>
       <c r="H13" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="I13" t="s">
         <v>184</v>
@@ -6413,22 +6411,22 @@
         <v>196</v>
       </c>
       <c r="C14" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D14" t="s">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="E14" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="F14" t="s">
         <v>197</v>
       </c>
       <c r="G14" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H14" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="I14" t="s">
         <v>198</v>
@@ -6446,7 +6444,7 @@
         <v>202</v>
       </c>
       <c r="N14" t="s">
-        <v>122</v>
+        <v>34</v>
       </c>
       <c r="O14" t="s">
         <v>203</v>
@@ -6455,19 +6453,19 @@
         <v>204</v>
       </c>
       <c r="Q14" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="R14" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="S14" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="T14" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="U14" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="V14"/>
     </row>
@@ -6479,22 +6477,22 @@
         <v>205</v>
       </c>
       <c r="C15" t="s">
-        <v>114</v>
+        <v>23</v>
       </c>
       <c r="D15" t="s">
-        <v>62</v>
+        <v>24</v>
       </c>
       <c r="E15" t="s">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="F15" t="s">
         <v>206</v>
       </c>
       <c r="G15" t="s">
-        <v>65</v>
+        <v>27</v>
       </c>
       <c r="H15" t="s">
-        <v>116</v>
+        <v>28</v>
       </c>
       <c r="I15" t="s">
         <v>207</v>
@@ -6548,19 +6546,19 @@
         <v>220</v>
       </c>
       <c r="D16" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="E16" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="F16" t="s">
         <v>221</v>
       </c>
       <c r="G16" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H16" t="s">
-        <v>116</v>
+        <v>28</v>
       </c>
       <c r="I16" t="s">
         <v>222</v>
@@ -6576,7 +6574,7 @@
         <v>225</v>
       </c>
       <c r="N16" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="O16" t="s">
         <v>226</v>
@@ -6612,19 +6610,19 @@
         <v>220</v>
       </c>
       <c r="D17" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="E17" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="F17" t="s">
         <v>233</v>
       </c>
       <c r="G17" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H17" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="I17" t="s">
         <v>234</v>
@@ -6640,7 +6638,7 @@
         <v>237</v>
       </c>
       <c r="N17" t="s">
-        <v>122</v>
+        <v>34</v>
       </c>
       <c r="O17" t="s">
         <v>238</v>
@@ -6685,10 +6683,10 @@
         <v>233</v>
       </c>
       <c r="G18" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H18" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="I18" t="s">
         <v>245</v>
@@ -6704,7 +6702,7 @@
         <v>248</v>
       </c>
       <c r="N18" t="s">
-        <v>122</v>
+        <v>34</v>
       </c>
       <c r="O18" t="s">
         <v>249</v>
@@ -6737,22 +6735,22 @@
         <v>254</v>
       </c>
       <c r="C19" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D19" t="s">
         <v>255</v>
       </c>
       <c r="E19" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="F19" t="s">
         <v>256</v>
       </c>
       <c r="G19" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H19" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="I19" t="s">
         <v>257</v>
@@ -6770,7 +6768,7 @@
         <v>261</v>
       </c>
       <c r="N19" t="s">
-        <v>122</v>
+        <v>34</v>
       </c>
       <c r="O19" t="s">
         <v>262</v>
@@ -6803,19 +6801,19 @@
         <v>268</v>
       </c>
       <c r="C20" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D20" t="s">
-        <v>62</v>
+        <v>24</v>
       </c>
       <c r="E20" t="s">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="F20" t="s">
         <v>269</v>
       </c>
       <c r="G20" t="s">
-        <v>65</v>
+        <v>27</v>
       </c>
       <c r="H20" t="s">
         <v>146</v>
@@ -6836,7 +6834,7 @@
         <v>274</v>
       </c>
       <c r="N20" t="s">
-        <v>122</v>
+        <v>34</v>
       </c>
       <c r="O20" t="s">
         <v>275</v>
@@ -6869,22 +6867,22 @@
         <v>280</v>
       </c>
       <c r="C21" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="D21" t="s">
         <v>281</v>
       </c>
       <c r="E21" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="F21" t="s">
         <v>183</v>
       </c>
       <c r="G21" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H21" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="I21" t="s">
         <v>282</v>
@@ -6902,7 +6900,7 @@
         <v>286</v>
       </c>
       <c r="N21" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="O21" t="s">
         <v>287</v>
@@ -6911,7 +6909,7 @@
         <v>288</v>
       </c>
       <c r="Q21" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="R21" t="s">
         <v>289</v>
@@ -6935,19 +6933,19 @@
         <v>293</v>
       </c>
       <c r="C22" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D22" t="s">
         <v>294</v>
       </c>
       <c r="E22" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="F22" t="s">
         <v>197</v>
       </c>
       <c r="G22" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H22" t="s">
         <v>146</v>
@@ -6968,7 +6966,7 @@
         <v>299</v>
       </c>
       <c r="N22" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="O22" t="s">
         <v>300</v>
@@ -6977,7 +6975,7 @@
         <v>301</v>
       </c>
       <c r="Q22" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="R22" t="s">
         <v>277</v>
@@ -7001,7 +6999,7 @@
         <v>302</v>
       </c>
       <c r="C23" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="D23" t="s">
         <v>303</v>
@@ -7011,10 +7009,10 @@
         <v>269</v>
       </c>
       <c r="G23" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H23" t="s">
-        <v>116</v>
+        <v>28</v>
       </c>
       <c r="I23" t="s">
         <v>132</v>
@@ -7032,7 +7030,7 @@
         <v>136</v>
       </c>
       <c r="N23" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="O23" t="s">
         <v>306</v>
@@ -7065,7 +7063,7 @@
         <v>308</v>
       </c>
       <c r="C24" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="D24" t="s">
         <v>309</v>
@@ -7075,10 +7073,10 @@
         <v>183</v>
       </c>
       <c r="G24" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H24" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="I24" t="s">
         <v>310</v>
@@ -7096,7 +7094,7 @@
         <v>314</v>
       </c>
       <c r="N24" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="O24" t="s">
         <v>315</v>
@@ -7105,7 +7103,7 @@
         <v>316</v>
       </c>
       <c r="Q24" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="R24" t="s">
         <v>317</v>
@@ -7129,7 +7127,7 @@
         <v>321</v>
       </c>
       <c r="C25" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D25" t="s">
         <v>244</v>
@@ -7141,7 +7139,7 @@
         <v>183</v>
       </c>
       <c r="G25" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H25" t="s">
         <v>146</v>
@@ -7162,7 +7160,7 @@
         <v>326</v>
       </c>
       <c r="N25" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="O25" t="s">
         <v>327</v>
@@ -7195,7 +7193,7 @@
         <v>332</v>
       </c>
       <c r="C26" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D26" t="s">
         <v>333</v>
@@ -7207,7 +7205,7 @@
         <v>334</v>
       </c>
       <c r="G26" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H26" t="s">
         <v>335</v>
@@ -7228,7 +7226,7 @@
         <v>340</v>
       </c>
       <c r="N26" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="O26" t="s">
         <v>341</v>
@@ -7237,7 +7235,7 @@
         <v>342</v>
       </c>
       <c r="Q26" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="R26" t="s">
         <v>343</v>
@@ -7261,7 +7259,7 @@
         <v>346</v>
       </c>
       <c r="C27" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="D27" t="s">
         <v>347</v>
@@ -7273,10 +7271,10 @@
         <v>269</v>
       </c>
       <c r="G27" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H27" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="I27" t="s">
         <v>348</v>
@@ -7294,7 +7292,7 @@
         <v>352</v>
       </c>
       <c r="N27" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="O27" t="s">
         <v>353</v>
@@ -7327,7 +7325,7 @@
         <v>359</v>
       </c>
       <c r="C28" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D28" t="s">
         <v>360</v>
@@ -7339,7 +7337,7 @@
         <v>361</v>
       </c>
       <c r="G28" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H28" t="s">
         <v>146</v>
@@ -7360,7 +7358,7 @@
         <v>366</v>
       </c>
       <c r="N28" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="O28" t="s">
         <v>367</v>
@@ -7369,7 +7367,7 @@
         <v>368</v>
       </c>
       <c r="Q28" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="R28" t="s">
         <v>329</v>
@@ -7393,22 +7391,22 @@
         <v>369</v>
       </c>
       <c r="C29" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="D29" t="s">
-        <v>62</v>
+        <v>24</v>
       </c>
       <c r="E29" t="s">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="F29" t="s">
         <v>370</v>
       </c>
       <c r="G29" t="s">
-        <v>65</v>
+        <v>27</v>
       </c>
       <c r="H29" t="s">
-        <v>116</v>
+        <v>28</v>
       </c>
       <c r="I29" t="s">
         <v>371</v>
@@ -7465,16 +7463,16 @@
         <v>255</v>
       </c>
       <c r="E30" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="F30" t="s">
         <v>384</v>
       </c>
       <c r="G30" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H30" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="I30" t="s">
         <v>385</v>
@@ -7490,7 +7488,7 @@
         <v>388</v>
       </c>
       <c r="N30" t="s">
-        <v>122</v>
+        <v>34</v>
       </c>
       <c r="O30" t="s">
         <v>389</v>
@@ -7535,10 +7533,10 @@
         <v>361</v>
       </c>
       <c r="G31" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H31" t="s">
-        <v>116</v>
+        <v>28</v>
       </c>
       <c r="I31" t="s">
         <v>398</v>
@@ -7554,7 +7552,7 @@
         <v>401</v>
       </c>
       <c r="N31" t="s">
-        <v>122</v>
+        <v>34</v>
       </c>
       <c r="O31" t="s">
         <v>402</v>
@@ -7563,7 +7561,7 @@
         <v>403</v>
       </c>
       <c r="Q31" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="R31" t="s">
         <v>404</v>
@@ -7591,14 +7589,14 @@
       </c>
       <c r="D32"/>
       <c r="E32" t="s">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="F32" t="s">
         <v>409</v>
       </c>
       <c r="G32"/>
       <c r="H32" t="s">
-        <v>116</v>
+        <v>28</v>
       </c>
       <c r="I32" t="s">
         <v>410</v>
@@ -7612,7 +7610,7 @@
       <c r="L32"/>
       <c r="M32"/>
       <c r="N32" t="s">
-        <v>122</v>
+        <v>34</v>
       </c>
       <c r="O32" t="s">
         <v>413</v>
@@ -7651,16 +7649,16 @@
         <v>281</v>
       </c>
       <c r="E33" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="F33" t="s">
         <v>416</v>
       </c>
       <c r="G33" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H33" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="I33" t="s">
         <v>417</v>
@@ -7676,7 +7674,7 @@
         <v>420</v>
       </c>
       <c r="N33" t="s">
-        <v>122</v>
+        <v>34</v>
       </c>
       <c r="O33" t="s">
         <v>421</v>
@@ -7709,22 +7707,22 @@
         <v>426</v>
       </c>
       <c r="C34" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="D34" t="s">
         <v>427</v>
       </c>
       <c r="E34" t="s">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="F34" t="s">
         <v>428</v>
       </c>
       <c r="G34" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H34" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="I34" t="s">
         <v>429</v>
@@ -7742,7 +7740,7 @@
         <v>433</v>
       </c>
       <c r="N34" t="s">
-        <v>122</v>
+        <v>34</v>
       </c>
       <c r="O34" t="s">
         <v>434</v>
@@ -7754,13 +7752,13 @@
         <v>139</v>
       </c>
       <c r="R34" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="S34" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="T34" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="U34" t="s">
         <v>394</v>
@@ -7775,7 +7773,7 @@
         <v>436</v>
       </c>
       <c r="C35" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D35" t="s">
         <v>437</v>
@@ -7787,10 +7785,10 @@
         <v>370</v>
       </c>
       <c r="G35" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H35" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="I35" t="s">
         <v>439</v>
@@ -7808,7 +7806,7 @@
         <v>443</v>
       </c>
       <c r="N35" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="O35" t="s">
         <v>444</v>
@@ -7817,7 +7815,7 @@
         <v>445</v>
       </c>
       <c r="Q35" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="R35" t="s">
         <v>446</v>
@@ -7841,7 +7839,7 @@
         <v>449</v>
       </c>
       <c r="C36" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D36" t="s">
         <v>450</v>
@@ -7853,7 +7851,7 @@
         <v>370</v>
       </c>
       <c r="G36" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H36" t="s">
         <v>146</v>
@@ -7874,7 +7872,7 @@
         <v>455</v>
       </c>
       <c r="N36" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="O36" t="s">
         <v>456</v>
@@ -7883,7 +7881,7 @@
         <v>457</v>
       </c>
       <c r="Q36" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="R36" t="s">
         <v>458</v>
@@ -7907,22 +7905,22 @@
         <v>461</v>
       </c>
       <c r="C37" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="D37" t="s">
-        <v>62</v>
+        <v>24</v>
       </c>
       <c r="E37" t="s">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="F37" t="s">
         <v>462</v>
       </c>
       <c r="G37" t="s">
-        <v>65</v>
+        <v>27</v>
       </c>
       <c r="H37" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="I37" t="s">
         <v>463</v>
@@ -7973,22 +7971,22 @@
         <v>473</v>
       </c>
       <c r="C38" t="s">
-        <v>114</v>
+        <v>23</v>
       </c>
       <c r="D38" t="s">
-        <v>62</v>
+        <v>24</v>
       </c>
       <c r="E38" t="s">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="F38" t="s">
         <v>462</v>
       </c>
       <c r="G38" t="s">
-        <v>65</v>
+        <v>27</v>
       </c>
       <c r="H38" t="s">
-        <v>116</v>
+        <v>28</v>
       </c>
       <c r="I38" t="s">
         <v>474</v>
@@ -8039,22 +8037,22 @@
         <v>484</v>
       </c>
       <c r="C39" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D39" t="s">
         <v>485</v>
       </c>
       <c r="E39" t="s">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="F39" t="s">
         <v>486</v>
       </c>
       <c r="G39" t="s">
-        <v>65</v>
+        <v>27</v>
       </c>
       <c r="H39" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="I39" t="s">
         <v>487</v>
@@ -8072,7 +8070,7 @@
         <v>491</v>
       </c>
       <c r="N39" t="s">
-        <v>122</v>
+        <v>34</v>
       </c>
       <c r="O39" t="s">
         <v>492</v>
@@ -8081,7 +8079,7 @@
         <v>493</v>
       </c>
       <c r="Q39" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="R39" t="s">
         <v>494</v>
@@ -8105,7 +8103,7 @@
         <v>497</v>
       </c>
       <c r="C40" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="D40" t="s">
         <v>347</v>
@@ -8117,10 +8115,10 @@
         <v>256</v>
       </c>
       <c r="G40" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H40" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="I40" t="s">
         <v>498</v>
@@ -8138,7 +8136,7 @@
         <v>502</v>
       </c>
       <c r="N40" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="O40" t="s">
         <v>503</v>
@@ -8147,16 +8145,16 @@
         <v>504</v>
       </c>
       <c r="Q40" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="R40" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="S40" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="T40" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="U40" t="s">
         <v>394</v>
@@ -8177,16 +8175,16 @@
         <v>506</v>
       </c>
       <c r="E41" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="F41" t="s">
         <v>507</v>
       </c>
       <c r="G41" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H41" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="I41" t="s">
         <v>508</v>
@@ -8202,7 +8200,7 @@
         <v>511</v>
       </c>
       <c r="N41" t="s">
-        <v>122</v>
+        <v>34</v>
       </c>
       <c r="O41" t="s">
         <v>512</v>
@@ -8247,10 +8245,10 @@
         <v>507</v>
       </c>
       <c r="G42" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H42" t="s">
-        <v>116</v>
+        <v>28</v>
       </c>
       <c r="I42" t="s">
         <v>518</v>
@@ -8266,7 +8264,7 @@
         <v>521</v>
       </c>
       <c r="N42" t="s">
-        <v>122</v>
+        <v>34</v>
       </c>
       <c r="O42" t="s">
         <v>522</v>
@@ -8299,7 +8297,7 @@
         <v>524</v>
       </c>
       <c r="C43" t="s">
-        <v>114</v>
+        <v>23</v>
       </c>
       <c r="D43" t="s">
         <v>525</v>
@@ -8309,10 +8307,10 @@
         <v>526</v>
       </c>
       <c r="G43" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H43" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="I43" t="s">
         <v>527</v>
@@ -8363,7 +8361,7 @@
         <v>537</v>
       </c>
       <c r="C44" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="D44" t="s">
         <v>538</v>
@@ -8375,10 +8373,10 @@
         <v>539</v>
       </c>
       <c r="G44" t="s">
-        <v>65</v>
+        <v>27</v>
       </c>
       <c r="H44" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="I44" t="s">
         <v>540</v>
@@ -8396,7 +8394,7 @@
         <v>544</v>
       </c>
       <c r="N44" t="s">
-        <v>122</v>
+        <v>34</v>
       </c>
       <c r="O44" t="s">
         <v>545</v>
@@ -8429,22 +8427,22 @@
         <v>550</v>
       </c>
       <c r="C45" t="s">
-        <v>114</v>
+        <v>23</v>
       </c>
       <c r="D45" t="s">
         <v>551</v>
       </c>
       <c r="E45" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="F45" t="s">
         <v>539</v>
       </c>
       <c r="G45" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H45" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="I45" t="s">
         <v>552</v>
@@ -8462,7 +8460,7 @@
         <v>556</v>
       </c>
       <c r="N45" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="O45" t="s">
         <v>557</v>
@@ -8495,19 +8493,19 @@
         <v>559</v>
       </c>
       <c r="C46" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D46" t="s">
         <v>294</v>
       </c>
       <c r="E46" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="F46" t="s">
         <v>539</v>
       </c>
       <c r="G46" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H46" t="s">
         <v>146</v>
@@ -8528,7 +8526,7 @@
         <v>564</v>
       </c>
       <c r="N46" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="O46" t="s">
         <v>565</v>
@@ -8537,7 +8535,7 @@
         <v>566</v>
       </c>
       <c r="Q46" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="R46" t="s">
         <v>329</v>
@@ -8561,22 +8559,22 @@
         <v>567</v>
       </c>
       <c r="C47" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="D47" t="s">
         <v>145</v>
       </c>
       <c r="E47" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="F47" t="s">
         <v>539</v>
       </c>
       <c r="G47" t="s">
-        <v>65</v>
+        <v>27</v>
       </c>
       <c r="H47" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="I47" t="s">
         <v>568</v>
@@ -8627,22 +8625,22 @@
         <v>578</v>
       </c>
       <c r="C48" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D48" t="s">
         <v>579</v>
       </c>
       <c r="E48" t="s">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="F48" t="s">
         <v>580</v>
       </c>
       <c r="G48" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H48" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="I48" t="s">
         <v>581</v>
@@ -8660,7 +8658,7 @@
         <v>585</v>
       </c>
       <c r="N48" t="s">
-        <v>122</v>
+        <v>34</v>
       </c>
       <c r="O48" t="s">
         <v>586</v>
@@ -8669,7 +8667,7 @@
         <v>587</v>
       </c>
       <c r="Q48" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="R48" t="s">
         <v>446</v>
@@ -8693,22 +8691,22 @@
         <v>588</v>
       </c>
       <c r="C49" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D49" t="s">
-        <v>62</v>
+        <v>24</v>
       </c>
       <c r="E49" t="s">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="F49" t="s">
         <v>589</v>
       </c>
       <c r="G49" t="s">
-        <v>65</v>
+        <v>27</v>
       </c>
       <c r="H49" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="I49" t="s">
         <v>590</v>
@@ -8726,7 +8724,7 @@
         <v>594</v>
       </c>
       <c r="N49" t="s">
-        <v>122</v>
+        <v>34</v>
       </c>
       <c r="O49" t="s">
         <v>595</v>
@@ -8735,7 +8733,7 @@
         <v>596</v>
       </c>
       <c r="Q49" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="R49" t="s">
         <v>597</v>
@@ -8759,7 +8757,7 @@
         <v>600</v>
       </c>
       <c r="C50" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D50" t="s">
         <v>601</v>
@@ -8771,10 +8769,10 @@
         <v>589</v>
       </c>
       <c r="G50" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H50" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="I50" t="s">
         <v>602</v>
@@ -8792,7 +8790,7 @@
         <v>606</v>
       </c>
       <c r="N50" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="O50" t="s">
         <v>607</v>
@@ -8801,7 +8799,7 @@
         <v>608</v>
       </c>
       <c r="Q50" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="R50" t="s">
         <v>609</v>
@@ -8825,22 +8823,22 @@
         <v>612</v>
       </c>
       <c r="C51" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D51" t="s">
         <v>613</v>
       </c>
       <c r="E51" t="s">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="F51" t="s">
         <v>614</v>
       </c>
       <c r="G51" t="s">
-        <v>65</v>
+        <v>27</v>
       </c>
       <c r="H51" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="I51" t="s">
         <v>615</v>
@@ -8858,7 +8856,7 @@
         <v>619</v>
       </c>
       <c r="N51" t="s">
-        <v>122</v>
+        <v>34</v>
       </c>
       <c r="O51" t="s">
         <v>620</v>
@@ -8867,7 +8865,7 @@
         <v>621</v>
       </c>
       <c r="Q51" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="R51" t="s">
         <v>622</v>
@@ -8903,10 +8901,10 @@
         <v>627</v>
       </c>
       <c r="G52" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H52" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="I52" t="s">
         <v>628</v>
@@ -8957,7 +8955,7 @@
         <v>639</v>
       </c>
       <c r="C53" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="D53" t="s">
         <v>640</v>
@@ -8969,7 +8967,7 @@
         <v>641</v>
       </c>
       <c r="G53" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H53" t="s">
         <v>146</v>
@@ -8990,7 +8988,7 @@
         <v>646</v>
       </c>
       <c r="N53" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="O53" t="s">
         <v>647</v>
@@ -9035,10 +9033,10 @@
         <v>641</v>
       </c>
       <c r="G54" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H54" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="I54" t="s">
         <v>655</v>
@@ -9054,7 +9052,7 @@
         <v>658</v>
       </c>
       <c r="N54" t="s">
-        <v>122</v>
+        <v>34</v>
       </c>
       <c r="O54" t="s">
         <v>659</v>
@@ -9063,7 +9061,7 @@
         <v>660</v>
       </c>
       <c r="Q54" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="R54" t="s">
         <v>446</v>
@@ -9093,16 +9091,16 @@
         <v>662</v>
       </c>
       <c r="E55" t="s">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="F55" t="s">
         <v>641</v>
       </c>
       <c r="G55" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H55" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="I55" t="s">
         <v>663</v>
@@ -9118,7 +9116,7 @@
         <v>666</v>
       </c>
       <c r="N55" t="s">
-        <v>122</v>
+        <v>34</v>
       </c>
       <c r="O55" t="s">
         <v>667</v>
@@ -9127,7 +9125,7 @@
         <v>668</v>
       </c>
       <c r="Q55" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="R55" t="s">
         <v>669</v>
@@ -9163,10 +9161,10 @@
         <v>673</v>
       </c>
       <c r="G56" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H56" t="s">
-        <v>116</v>
+        <v>28</v>
       </c>
       <c r="I56" t="s">
         <v>674</v>
@@ -9182,7 +9180,7 @@
         <v>677</v>
       </c>
       <c r="N56" t="s">
-        <v>122</v>
+        <v>34</v>
       </c>
       <c r="O56" t="s">
         <v>678</v>
@@ -9191,7 +9189,7 @@
         <v>679</v>
       </c>
       <c r="Q56" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="R56" t="s">
         <v>680</v>
@@ -9215,7 +9213,7 @@
         <v>683</v>
       </c>
       <c r="C57" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D57" t="s">
         <v>684</v>
@@ -9227,10 +9225,10 @@
         <v>685</v>
       </c>
       <c r="G57" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H57" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="I57" t="s">
         <v>686</v>
@@ -9248,7 +9246,7 @@
         <v>690</v>
       </c>
       <c r="N57" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="O57" t="s">
         <v>691</v>
@@ -9293,10 +9291,10 @@
         <v>685</v>
       </c>
       <c r="G58" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H58" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="I58" t="s">
         <v>697</v>
@@ -9312,7 +9310,7 @@
         <v>700</v>
       </c>
       <c r="N58" t="s">
-        <v>122</v>
+        <v>34</v>
       </c>
       <c r="O58" t="s">
         <v>701</v>
@@ -9356,7 +9354,7 @@
       </c>
       <c r="G59"/>
       <c r="H59" t="s">
-        <v>116</v>
+        <v>28</v>
       </c>
       <c r="I59" t="s">
         <v>710</v>
@@ -9374,7 +9372,7 @@
         <v>714</v>
       </c>
       <c r="N59" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="O59" t="s">
         <v>715</v>
@@ -9401,19 +9399,19 @@
         <v>717</v>
       </c>
       <c r="C60" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D60" t="s">
         <v>718</v>
       </c>
       <c r="E60" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="F60" t="s">
         <v>719</v>
       </c>
       <c r="G60" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H60" t="s">
         <v>146</v>
@@ -9434,7 +9432,7 @@
         <v>724</v>
       </c>
       <c r="N60" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="O60" t="s">
         <v>725</v>
@@ -9443,7 +9441,7 @@
         <v>726</v>
       </c>
       <c r="Q60" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="R60" t="s">
         <v>727</v>
@@ -9467,19 +9465,19 @@
         <v>730</v>
       </c>
       <c r="C61" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D61" t="s">
         <v>731</v>
       </c>
       <c r="E61" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="F61" t="s">
         <v>719</v>
       </c>
       <c r="G61" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H61" t="s">
         <v>146</v>
@@ -9500,7 +9498,7 @@
         <v>736</v>
       </c>
       <c r="N61" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="O61" t="s">
         <v>737</v>
@@ -9533,22 +9531,22 @@
         <v>742</v>
       </c>
       <c r="C62" t="s">
-        <v>114</v>
+        <v>23</v>
       </c>
       <c r="D62" t="s">
         <v>743</v>
       </c>
       <c r="E62" t="s">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="F62" t="s">
         <v>719</v>
       </c>
       <c r="G62" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H62" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="I62" t="s">
         <v>744</v>
@@ -9599,7 +9597,7 @@
         <v>755</v>
       </c>
       <c r="C63" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="D63" t="s">
         <v>309</v>
@@ -9609,10 +9607,10 @@
         <v>756</v>
       </c>
       <c r="G63" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H63" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="I63" t="s">
         <v>757</v>
@@ -9630,7 +9628,7 @@
         <v>761</v>
       </c>
       <c r="N63" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="O63" t="s">
         <v>762</v>
@@ -9639,7 +9637,7 @@
         <v>763</v>
       </c>
       <c r="Q63" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="R63" t="s">
         <v>764</v>
@@ -9663,22 +9661,22 @@
         <v>767</v>
       </c>
       <c r="C64" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D64" t="s">
         <v>768</v>
       </c>
       <c r="E64" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="F64" t="s">
         <v>756</v>
       </c>
       <c r="G64" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H64" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="I64" t="s">
         <v>769</v>
@@ -9696,7 +9694,7 @@
         <v>773</v>
       </c>
       <c r="N64" t="s">
-        <v>122</v>
+        <v>34</v>
       </c>
       <c r="O64" t="s">
         <v>774</v>
@@ -9705,7 +9703,7 @@
         <v>775</v>
       </c>
       <c r="Q64" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="R64" t="s">
         <v>776</v>
@@ -9729,19 +9727,19 @@
         <v>779</v>
       </c>
       <c r="C65" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D65" t="s">
         <v>780</v>
       </c>
       <c r="E65" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="F65" t="s">
         <v>781</v>
       </c>
       <c r="G65" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H65" t="s">
         <v>146</v>
@@ -9762,7 +9760,7 @@
         <v>786</v>
       </c>
       <c r="N65" t="s">
-        <v>122</v>
+        <v>34</v>
       </c>
       <c r="O65" t="s">
         <v>787</v>
@@ -9771,7 +9769,7 @@
         <v>788</v>
       </c>
       <c r="Q65" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="R65" t="s">
         <v>329</v>
@@ -9795,7 +9793,7 @@
         <v>789</v>
       </c>
       <c r="C66" t="s">
-        <v>114</v>
+        <v>23</v>
       </c>
       <c r="D66" t="s">
         <v>790</v>
@@ -9805,7 +9803,7 @@
         <v>781</v>
       </c>
       <c r="G66" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H66" t="s">
         <v>146</v>
@@ -9859,19 +9857,19 @@
         <v>801</v>
       </c>
       <c r="C67" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D67" t="s">
         <v>551</v>
       </c>
       <c r="E67" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="F67" t="s">
         <v>781</v>
       </c>
       <c r="G67" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H67" t="s">
         <v>146</v>
@@ -9892,7 +9890,7 @@
         <v>806</v>
       </c>
       <c r="N67" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="O67" t="s">
         <v>807</v>
@@ -9901,7 +9899,7 @@
         <v>808</v>
       </c>
       <c r="Q67" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="R67" t="s">
         <v>809</v>
@@ -9925,7 +9923,7 @@
         <v>812</v>
       </c>
       <c r="C68" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D68" t="s">
         <v>813</v>
@@ -9937,7 +9935,7 @@
         <v>814</v>
       </c>
       <c r="G68" t="s">
-        <v>65</v>
+        <v>27</v>
       </c>
       <c r="H68" t="s">
         <v>146</v>
@@ -9958,7 +9956,7 @@
         <v>819</v>
       </c>
       <c r="N68" t="s">
-        <v>122</v>
+        <v>34</v>
       </c>
       <c r="O68" t="s">
         <v>820</v>
@@ -9991,7 +9989,7 @@
         <v>822</v>
       </c>
       <c r="C69" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="D69" t="s">
         <v>823</v>
@@ -10003,7 +10001,7 @@
         <v>824</v>
       </c>
       <c r="G69" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H69" t="s">
         <v>146</v>
@@ -10024,7 +10022,7 @@
         <v>829</v>
       </c>
       <c r="N69" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="O69" t="s">
         <v>830</v>
@@ -10057,7 +10055,7 @@
         <v>832</v>
       </c>
       <c r="C70" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="D70" t="s">
         <v>833</v>
@@ -10069,10 +10067,10 @@
         <v>835</v>
       </c>
       <c r="G70" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H70" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="I70" t="s">
         <v>836</v>
@@ -10090,7 +10088,7 @@
         <v>840</v>
       </c>
       <c r="N70" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="O70" t="s">
         <v>841</v>
@@ -10099,7 +10097,7 @@
         <v>842</v>
       </c>
       <c r="Q70" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="R70" t="s">
         <v>843</v>
@@ -10123,7 +10121,7 @@
         <v>846</v>
       </c>
       <c r="C71" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="D71" t="s">
         <v>601</v>
@@ -10135,10 +10133,10 @@
         <v>835</v>
       </c>
       <c r="G71" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H71" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="I71" t="s">
         <v>847</v>
@@ -10156,7 +10154,7 @@
         <v>851</v>
       </c>
       <c r="N71" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="O71" t="s">
         <v>852</v>
@@ -10165,7 +10163,7 @@
         <v>853</v>
       </c>
       <c r="Q71" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="R71" t="s">
         <v>854</v>
@@ -10189,7 +10187,7 @@
         <v>857</v>
       </c>
       <c r="C72" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="D72" t="s">
         <v>858</v>
@@ -10199,10 +10197,10 @@
         <v>859</v>
       </c>
       <c r="G72" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H72" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="I72" t="s">
         <v>860</v>
@@ -10229,7 +10227,7 @@
         <v>866</v>
       </c>
       <c r="Q72" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="R72" t="s">
         <v>854</v>
@@ -10253,19 +10251,19 @@
         <v>867</v>
       </c>
       <c r="C73" t="s">
-        <v>114</v>
+        <v>23</v>
       </c>
       <c r="D73" t="s">
         <v>868</v>
       </c>
       <c r="E73" t="s">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="F73" t="s">
         <v>869</v>
       </c>
       <c r="G73" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H73" t="s">
         <v>870</v>
@@ -10319,22 +10317,22 @@
         <v>881</v>
       </c>
       <c r="C74" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D74" t="s">
         <v>882</v>
       </c>
       <c r="E74" t="s">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="F74" t="s">
         <v>869</v>
       </c>
       <c r="G74" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H74" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="I74" t="s">
         <v>883</v>
@@ -10352,7 +10350,7 @@
         <v>887</v>
       </c>
       <c r="N74" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="O74" t="s">
         <v>888</v>
@@ -10385,19 +10383,19 @@
         <v>893</v>
       </c>
       <c r="C75" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D75" t="s">
         <v>894</v>
       </c>
       <c r="E75" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="F75" t="s">
         <v>869</v>
       </c>
       <c r="G75" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H75" t="s">
         <v>146</v>
@@ -10418,7 +10416,7 @@
         <v>899</v>
       </c>
       <c r="N75" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="O75" t="s">
         <v>900</v>
@@ -10427,7 +10425,7 @@
         <v>901</v>
       </c>
       <c r="Q75" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="R75" t="s">
         <v>649</v>
@@ -10451,22 +10449,22 @@
         <v>902</v>
       </c>
       <c r="C76" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="D76" t="s">
         <v>903</v>
       </c>
       <c r="E76" t="s">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="F76" t="s">
         <v>904</v>
       </c>
       <c r="G76" t="s">
-        <v>65</v>
+        <v>27</v>
       </c>
       <c r="H76" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="I76" t="s">
         <v>905</v>
@@ -10484,7 +10482,7 @@
         <v>909</v>
       </c>
       <c r="N76" t="s">
-        <v>122</v>
+        <v>34</v>
       </c>
       <c r="O76" t="s">
         <v>910</v>
@@ -10493,7 +10491,7 @@
         <v>911</v>
       </c>
       <c r="Q76" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="R76" t="s">
         <v>912</v>
@@ -10517,22 +10515,22 @@
         <v>915</v>
       </c>
       <c r="C77" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="D77" t="s">
-        <v>62</v>
+        <v>24</v>
       </c>
       <c r="E77" t="s">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="F77" t="s">
         <v>904</v>
       </c>
       <c r="G77" t="s">
-        <v>65</v>
+        <v>27</v>
       </c>
       <c r="H77" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="I77" t="s">
         <v>916</v>
@@ -10559,7 +10557,7 @@
         <v>922</v>
       </c>
       <c r="Q77" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="R77" t="s">
         <v>854</v>
@@ -10583,19 +10581,19 @@
         <v>923</v>
       </c>
       <c r="C78" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D78" t="s">
         <v>485</v>
       </c>
       <c r="E78" t="s">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="F78" t="s">
         <v>924</v>
       </c>
       <c r="G78" t="s">
-        <v>65</v>
+        <v>27</v>
       </c>
       <c r="H78" t="s">
         <v>146</v>
@@ -10616,7 +10614,7 @@
         <v>929</v>
       </c>
       <c r="N78" t="s">
-        <v>122</v>
+        <v>34</v>
       </c>
       <c r="O78" t="s">
         <v>930</v>
@@ -10625,7 +10623,7 @@
         <v>931</v>
       </c>
       <c r="Q78" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="R78" t="s">
         <v>932</v>
@@ -10649,22 +10647,22 @@
         <v>935</v>
       </c>
       <c r="C79" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D79" t="s">
         <v>768</v>
       </c>
       <c r="E79" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="F79" t="s">
         <v>936</v>
       </c>
       <c r="G79" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H79" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="I79" t="s">
         <v>937</v>
@@ -10682,7 +10680,7 @@
         <v>941</v>
       </c>
       <c r="N79" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="O79" t="s">
         <v>942</v>
@@ -10782,7 +10780,7 @@
       </c>
       <c r="G81"/>
       <c r="H81" t="s">
-        <v>116</v>
+        <v>28</v>
       </c>
       <c r="I81" t="s">
         <v>710</v>
@@ -10800,7 +10798,7 @@
         <v>961</v>
       </c>
       <c r="N81" t="s">
-        <v>122</v>
+        <v>34</v>
       </c>
       <c r="O81" t="s">
         <v>962</v>
@@ -10837,10 +10835,10 @@
         <v>966</v>
       </c>
       <c r="G82" t="s">
-        <v>65</v>
+        <v>27</v>
       </c>
       <c r="H82" t="s">
-        <v>116</v>
+        <v>28</v>
       </c>
       <c r="I82" t="s">
         <v>967</v>
@@ -10897,13 +10895,13 @@
         <v>731</v>
       </c>
       <c r="E83" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="F83" t="s">
         <v>978</v>
       </c>
       <c r="G83" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H83" t="s">
         <v>146</v>
@@ -10924,7 +10922,7 @@
         <v>983</v>
       </c>
       <c r="N83" t="s">
-        <v>122</v>
+        <v>34</v>
       </c>
       <c r="O83" t="s">
         <v>984</v>
@@ -10957,7 +10955,7 @@
         <v>989</v>
       </c>
       <c r="C84" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D84" t="s">
         <v>833</v>
@@ -10969,10 +10967,10 @@
         <v>978</v>
       </c>
       <c r="G84" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H84" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="I84" t="s">
         <v>990</v>
@@ -10990,7 +10988,7 @@
         <v>994</v>
       </c>
       <c r="N84" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="O84" t="s">
         <v>995</v>
@@ -10999,7 +10997,7 @@
         <v>996</v>
       </c>
       <c r="Q84" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="R84" t="s">
         <v>997</v>
@@ -11023,19 +11021,19 @@
         <v>1000</v>
       </c>
       <c r="C85" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D85" t="s">
         <v>1001</v>
       </c>
       <c r="E85" t="s">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="F85" t="s">
         <v>978</v>
       </c>
       <c r="G85" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H85" t="s">
         <v>335</v>
@@ -11056,7 +11054,7 @@
         <v>1006</v>
       </c>
       <c r="N85" t="s">
-        <v>122</v>
+        <v>34</v>
       </c>
       <c r="O85" t="s">
         <v>1007</v>
@@ -11065,7 +11063,7 @@
         <v>1008</v>
       </c>
       <c r="Q85" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="R85" t="s">
         <v>1009</v>
@@ -11089,22 +11087,22 @@
         <v>1012</v>
       </c>
       <c r="C86" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="D86" t="s">
         <v>551</v>
       </c>
       <c r="E86" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="F86" t="s">
         <v>978</v>
       </c>
       <c r="G86" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H86" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="I86" t="s">
         <v>1013</v>
@@ -11131,7 +11129,7 @@
         <v>1019</v>
       </c>
       <c r="Q86" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="R86" t="s">
         <v>1020</v>
@@ -11155,22 +11153,22 @@
         <v>1023</v>
       </c>
       <c r="C87" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="D87" t="s">
         <v>1024</v>
       </c>
       <c r="E87" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="F87" t="s">
         <v>978</v>
       </c>
       <c r="G87" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H87" t="s">
-        <v>116</v>
+        <v>28</v>
       </c>
       <c r="I87" t="s">
         <v>1025</v>
@@ -11188,7 +11186,7 @@
         <v>1029</v>
       </c>
       <c r="N87" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="O87" t="s">
         <v>1030</v>
@@ -11197,7 +11195,7 @@
         <v>1031</v>
       </c>
       <c r="Q87" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="R87" t="s">
         <v>1032</v>
@@ -11221,22 +11219,22 @@
         <v>1035</v>
       </c>
       <c r="C88" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D88" t="s">
         <v>1036</v>
       </c>
       <c r="E88" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="F88" t="s">
         <v>978</v>
       </c>
       <c r="G88" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H88" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="I88" t="s">
         <v>1037</v>
@@ -11254,7 +11252,7 @@
         <v>1041</v>
       </c>
       <c r="N88" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="O88" t="s">
         <v>1042</v>
@@ -11263,7 +11261,7 @@
         <v>1043</v>
       </c>
       <c r="Q88" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="R88" t="s">
         <v>1044</v>
@@ -11293,13 +11291,13 @@
         <v>662</v>
       </c>
       <c r="E89" t="s">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="F89" t="s">
         <v>1048</v>
       </c>
       <c r="G89" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H89" t="s">
         <v>146</v>
@@ -11320,7 +11318,7 @@
         <v>1053</v>
       </c>
       <c r="N89" t="s">
-        <v>122</v>
+        <v>34</v>
       </c>
       <c r="O89" t="s">
         <v>1054</v>
@@ -11353,19 +11351,19 @@
         <v>1059</v>
       </c>
       <c r="C90" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D90" t="s">
         <v>1060</v>
       </c>
       <c r="E90" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="F90" t="s">
         <v>1048</v>
       </c>
       <c r="G90" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H90" t="s">
         <v>146</v>
@@ -11386,7 +11384,7 @@
         <v>1065</v>
       </c>
       <c r="N90" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="O90" t="s">
         <v>1066</v>
@@ -11395,7 +11393,7 @@
         <v>1067</v>
       </c>
       <c r="Q90" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="R90" t="s">
         <v>1068</v>
@@ -11448,7 +11446,7 @@
         <v>1077</v>
       </c>
       <c r="N91" t="s">
-        <v>122</v>
+        <v>34</v>
       </c>
       <c r="O91" t="s">
         <v>1078</v>
@@ -11475,7 +11473,7 @@
         <v>1080</v>
       </c>
       <c r="C92" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="D92" t="s">
         <v>244</v>
@@ -11487,10 +11485,10 @@
         <v>1081</v>
       </c>
       <c r="G92" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H92" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="I92" t="s">
         <v>540</v>
@@ -11508,7 +11506,7 @@
         <v>1085</v>
       </c>
       <c r="N92" t="s">
-        <v>122</v>
+        <v>34</v>
       </c>
       <c r="O92" t="s">
         <v>1086</v>
@@ -11553,10 +11551,10 @@
         <v>1090</v>
       </c>
       <c r="G93" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H93" t="s">
-        <v>116</v>
+        <v>28</v>
       </c>
       <c r="I93" t="s">
         <v>1091</v>
@@ -11572,7 +11570,7 @@
         <v>1094</v>
       </c>
       <c r="N93" t="s">
-        <v>122</v>
+        <v>34</v>
       </c>
       <c r="O93" t="s">
         <v>1095</v>
@@ -11611,13 +11609,13 @@
         <v>1101</v>
       </c>
       <c r="E94" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="F94" t="s">
         <v>1102</v>
       </c>
       <c r="G94" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H94" t="s">
         <v>146</v>
@@ -11636,7 +11634,7 @@
         <v>1106</v>
       </c>
       <c r="N94" t="s">
-        <v>122</v>
+        <v>34</v>
       </c>
       <c r="O94" t="s">
         <v>1107</v>
@@ -11673,14 +11671,14 @@
       </c>
       <c r="D95"/>
       <c r="E95" t="s">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="F95" t="s">
         <v>1110</v>
       </c>
       <c r="G95"/>
       <c r="H95" t="s">
-        <v>116</v>
+        <v>28</v>
       </c>
       <c r="I95" t="s">
         <v>1111</v>
@@ -11694,7 +11692,7 @@
       <c r="L95"/>
       <c r="M95"/>
       <c r="N95" t="s">
-        <v>122</v>
+        <v>34</v>
       </c>
       <c r="O95" t="s">
         <v>1114</v>
@@ -11738,7 +11736,7 @@
       </c>
       <c r="G96"/>
       <c r="H96" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="I96" t="s">
         <v>1121</v>
@@ -11851,7 +11849,7 @@
         <v>1143</v>
       </c>
       <c r="C98" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="D98" t="s">
         <v>833</v>
@@ -11863,10 +11861,10 @@
         <v>1144</v>
       </c>
       <c r="G98" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H98" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="I98" t="s">
         <v>1145</v>
@@ -11884,7 +11882,7 @@
         <v>1149</v>
       </c>
       <c r="N98" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="O98" t="s">
         <v>1150</v>
@@ -11893,7 +11891,7 @@
         <v>1151</v>
       </c>
       <c r="Q98" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="R98" t="s">
         <v>1152</v>
@@ -11917,22 +11915,22 @@
         <v>1155</v>
       </c>
       <c r="C99" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="D99" t="s">
         <v>1156</v>
       </c>
       <c r="E99" t="s">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="F99" t="s">
         <v>1157</v>
       </c>
       <c r="G99" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H99" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="I99" t="s">
         <v>1158</v>
@@ -11950,7 +11948,7 @@
         <v>1162</v>
       </c>
       <c r="N99" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="O99" t="s">
         <v>1163</v>
@@ -11959,7 +11957,7 @@
         <v>1164</v>
       </c>
       <c r="Q99" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="R99" t="s">
         <v>1165</v>
@@ -11983,7 +11981,7 @@
         <v>1168</v>
       </c>
       <c r="C100" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D100" t="s">
         <v>1169</v>
@@ -11995,7 +11993,7 @@
         <v>1157</v>
       </c>
       <c r="G100" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H100" t="s">
         <v>146</v>
@@ -12016,7 +12014,7 @@
         <v>1174</v>
       </c>
       <c r="N100" t="s">
-        <v>122</v>
+        <v>34</v>
       </c>
       <c r="O100" t="s">
         <v>1175</v>
@@ -12049,22 +12047,22 @@
         <v>1177</v>
       </c>
       <c r="C101" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="D101" t="s">
         <v>1178</v>
       </c>
       <c r="E101" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="F101" t="s">
         <v>1157</v>
       </c>
       <c r="G101" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H101" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="I101" t="s">
         <v>1179</v>
@@ -12082,7 +12080,7 @@
         <v>1183</v>
       </c>
       <c r="N101" t="s">
-        <v>122</v>
+        <v>34</v>
       </c>
       <c r="O101" t="s">
         <v>1184</v>
@@ -12091,7 +12089,7 @@
         <v>1185</v>
       </c>
       <c r="Q101" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="R101" t="s">
         <v>1186</v>
@@ -12115,22 +12113,22 @@
         <v>1189</v>
       </c>
       <c r="C102" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D102" t="s">
         <v>1190</v>
       </c>
       <c r="E102" t="s">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="F102" t="s">
         <v>1157</v>
       </c>
       <c r="G102" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H102" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="I102" t="s">
         <v>1191</v>
@@ -12148,7 +12146,7 @@
         <v>1195</v>
       </c>
       <c r="N102" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="O102" t="s">
         <v>1196</v>
@@ -12157,7 +12155,7 @@
         <v>1197</v>
       </c>
       <c r="Q102" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="R102" t="s">
         <v>727</v>
@@ -12181,22 +12179,22 @@
         <v>1198</v>
       </c>
       <c r="C103" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="D103" t="s">
         <v>1199</v>
       </c>
       <c r="E103" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="F103" t="s">
         <v>1200</v>
       </c>
       <c r="G103" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H103" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="I103" t="s">
         <v>1201</v>
@@ -12214,7 +12212,7 @@
         <v>1205</v>
       </c>
       <c r="N103" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="O103" t="s">
         <v>1206</v>
@@ -12223,7 +12221,7 @@
         <v>1207</v>
       </c>
       <c r="Q103" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="R103" t="s">
         <v>514</v>
@@ -12259,10 +12257,10 @@
         <v>1209</v>
       </c>
       <c r="G104" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H104" t="s">
-        <v>116</v>
+        <v>28</v>
       </c>
       <c r="I104" t="s">
         <v>1210</v>
@@ -12278,7 +12276,7 @@
         <v>1213</v>
       </c>
       <c r="N104" t="s">
-        <v>122</v>
+        <v>34</v>
       </c>
       <c r="O104" t="s">
         <v>1214</v>
@@ -12287,7 +12285,7 @@
         <v>1215</v>
       </c>
       <c r="Q104" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="R104" t="s">
         <v>343</v>
@@ -12311,19 +12309,19 @@
         <v>1216</v>
       </c>
       <c r="C105" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D105" t="s">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="E105" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="F105" t="s">
         <v>1217</v>
       </c>
       <c r="G105" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H105" t="s">
         <v>146</v>
@@ -12344,7 +12342,7 @@
         <v>1222</v>
       </c>
       <c r="N105" t="s">
-        <v>122</v>
+        <v>34</v>
       </c>
       <c r="O105" t="s">
         <v>1223</v>
@@ -12353,7 +12351,7 @@
         <v>1224</v>
       </c>
       <c r="Q105" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="R105" t="s">
         <v>329</v>
@@ -12383,13 +12381,13 @@
         <v>1190</v>
       </c>
       <c r="E106" t="s">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="F106" t="s">
         <v>1226</v>
       </c>
       <c r="G106" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H106" t="s">
         <v>146</v>
@@ -12408,7 +12406,7 @@
         <v>1230</v>
       </c>
       <c r="N106" t="s">
-        <v>122</v>
+        <v>34</v>
       </c>
       <c r="O106" t="s">
         <v>1231</v>
@@ -12453,10 +12451,10 @@
         <v>1226</v>
       </c>
       <c r="G107" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H107" t="s">
-        <v>116</v>
+        <v>28</v>
       </c>
       <c r="I107" t="s">
         <v>1234</v>
@@ -12472,7 +12470,7 @@
         <v>1237</v>
       </c>
       <c r="N107" t="s">
-        <v>122</v>
+        <v>34</v>
       </c>
       <c r="O107" t="s">
         <v>1238</v>
@@ -12481,7 +12479,7 @@
         <v>1239</v>
       </c>
       <c r="Q107" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="R107" t="s">
         <v>343</v>
@@ -12517,10 +12515,10 @@
         <v>1226</v>
       </c>
       <c r="G108" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H108" t="s">
-        <v>116</v>
+        <v>28</v>
       </c>
       <c r="I108" t="s">
         <v>1234</v>
@@ -12536,7 +12534,7 @@
         <v>1242</v>
       </c>
       <c r="N108" t="s">
-        <v>122</v>
+        <v>34</v>
       </c>
       <c r="O108" t="s">
         <v>1243</v>
@@ -12545,7 +12543,7 @@
         <v>1244</v>
       </c>
       <c r="Q108" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="R108" t="s">
         <v>343</v>
@@ -12581,10 +12579,10 @@
         <v>1226</v>
       </c>
       <c r="G109" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H109" t="s">
-        <v>116</v>
+        <v>28</v>
       </c>
       <c r="I109" t="s">
         <v>1234</v>
@@ -12600,7 +12598,7 @@
         <v>1247</v>
       </c>
       <c r="N109" t="s">
-        <v>122</v>
+        <v>34</v>
       </c>
       <c r="O109" t="s">
         <v>1248</v>
@@ -12609,7 +12607,7 @@
         <v>1249</v>
       </c>
       <c r="Q109" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="R109" t="s">
         <v>343</v>
@@ -12633,7 +12631,7 @@
         <v>1250</v>
       </c>
       <c r="C110" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D110" t="s">
         <v>684</v>
@@ -12645,10 +12643,10 @@
         <v>1251</v>
       </c>
       <c r="G110" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H110" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="I110" t="s">
         <v>1252</v>
@@ -12666,7 +12664,7 @@
         <v>1256</v>
       </c>
       <c r="N110" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="O110" t="s">
         <v>1257</v>
@@ -12699,22 +12697,22 @@
         <v>1262</v>
       </c>
       <c r="C111" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D111" t="s">
         <v>743</v>
       </c>
       <c r="E111" t="s">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="F111" t="s">
         <v>1263</v>
       </c>
       <c r="G111" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H111" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="I111" t="s">
         <v>1264</v>
@@ -12732,7 +12730,7 @@
         <v>1268</v>
       </c>
       <c r="N111" t="s">
-        <v>122</v>
+        <v>34</v>
       </c>
       <c r="O111" t="s">
         <v>1269</v>
@@ -12765,7 +12763,7 @@
         <v>1271</v>
       </c>
       <c r="C112" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D112" t="s">
         <v>1272</v>
@@ -12777,7 +12775,7 @@
         <v>1263</v>
       </c>
       <c r="G112" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H112" t="s">
         <v>146</v>
@@ -12798,7 +12796,7 @@
         <v>1277</v>
       </c>
       <c r="N112" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="O112" t="s">
         <v>1278</v>
@@ -12831,22 +12829,22 @@
         <v>1283</v>
       </c>
       <c r="C113" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D113" t="s">
         <v>1284</v>
       </c>
       <c r="E113" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="F113" t="s">
         <v>1263</v>
       </c>
       <c r="G113" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H113" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="I113" t="s">
         <v>1285</v>
@@ -12864,7 +12862,7 @@
         <v>1289</v>
       </c>
       <c r="N113" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="O113" t="s">
         <v>1290</v>
@@ -12873,7 +12871,7 @@
         <v>1291</v>
       </c>
       <c r="Q113" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="R113" t="s">
         <v>1292</v>
@@ -12959,22 +12957,22 @@
         <v>1308</v>
       </c>
       <c r="C115" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="D115" t="s">
         <v>579</v>
       </c>
       <c r="E115" t="s">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="F115" t="s">
         <v>1296</v>
       </c>
       <c r="G115" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H115" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="I115" t="s">
         <v>1309</v>
@@ -12992,7 +12990,7 @@
         <v>1313</v>
       </c>
       <c r="N115" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="O115" t="s">
         <v>1314</v>
@@ -13001,7 +12999,7 @@
         <v>1315</v>
       </c>
       <c r="Q115" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="R115" t="s">
         <v>1316</v>
@@ -13025,22 +13023,22 @@
         <v>1319</v>
       </c>
       <c r="C116" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="D116" t="s">
         <v>1320</v>
       </c>
       <c r="E116" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="F116" t="s">
         <v>1296</v>
       </c>
       <c r="G116" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H116" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="I116" t="s">
         <v>1321</v>
@@ -13058,7 +13056,7 @@
         <v>1325</v>
       </c>
       <c r="N116" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="O116" t="s">
         <v>1326</v>
@@ -13067,7 +13065,7 @@
         <v>1327</v>
       </c>
       <c r="Q116" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="R116" t="s">
         <v>1328</v>
@@ -13091,22 +13089,22 @@
         <v>1331</v>
       </c>
       <c r="C117" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D117" t="s">
         <v>1332</v>
       </c>
       <c r="E117" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="F117" t="s">
         <v>1296</v>
       </c>
       <c r="G117" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H117" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="I117" t="s">
         <v>1333</v>
@@ -13124,7 +13122,7 @@
         <v>1337</v>
       </c>
       <c r="N117" t="s">
-        <v>122</v>
+        <v>34</v>
       </c>
       <c r="O117" t="s">
         <v>1338</v>
@@ -13133,7 +13131,7 @@
         <v>1339</v>
       </c>
       <c r="Q117" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="R117" t="s">
         <v>997</v>
@@ -13157,19 +13155,19 @@
         <v>1340</v>
       </c>
       <c r="C118" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="D118" t="s">
         <v>731</v>
       </c>
       <c r="E118" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="F118" t="s">
         <v>1296</v>
       </c>
       <c r="G118" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H118" t="s">
         <v>146</v>
@@ -13190,7 +13188,7 @@
         <v>1345</v>
       </c>
       <c r="N118" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="O118" t="s">
         <v>1346</v>
@@ -13199,7 +13197,7 @@
         <v>1347</v>
       </c>
       <c r="Q118" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="R118" t="s">
         <v>1348</v>
@@ -13223,7 +13221,7 @@
         <v>1351</v>
       </c>
       <c r="C119" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="D119" t="s">
         <v>684</v>
@@ -13235,10 +13233,10 @@
         <v>1296</v>
       </c>
       <c r="G119" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H119" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="I119" t="s">
         <v>1352</v>
@@ -13289,7 +13287,7 @@
         <v>1363</v>
       </c>
       <c r="C120" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D120" t="s">
         <v>244</v>
@@ -13301,7 +13299,7 @@
         <v>1364</v>
       </c>
       <c r="G120" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H120" t="s">
         <v>146</v>
@@ -13322,7 +13320,7 @@
         <v>1369</v>
       </c>
       <c r="N120" t="s">
-        <v>122</v>
+        <v>34</v>
       </c>
       <c r="O120" t="s">
         <v>1370</v>
@@ -13355,22 +13353,22 @@
         <v>1372</v>
       </c>
       <c r="C121" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="D121" t="s">
         <v>551</v>
       </c>
       <c r="E121" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="F121" t="s">
         <v>1373</v>
       </c>
       <c r="G121" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H121" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="I121" t="s">
         <v>1374</v>
@@ -13388,7 +13386,7 @@
         <v>1378</v>
       </c>
       <c r="N121" t="s">
-        <v>122</v>
+        <v>34</v>
       </c>
       <c r="O121" t="s">
         <v>1379</v>
@@ -13397,7 +13395,7 @@
         <v>1380</v>
       </c>
       <c r="Q121" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="R121" t="s">
         <v>854</v>
@@ -13433,10 +13431,10 @@
         <v>1383</v>
       </c>
       <c r="G122" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H122" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="I122" t="s">
         <v>1384</v>
@@ -13452,7 +13450,7 @@
         <v>1387</v>
       </c>
       <c r="N122" t="s">
-        <v>122</v>
+        <v>34</v>
       </c>
       <c r="O122" t="s">
         <v>1388</v>
@@ -13491,13 +13489,13 @@
         <v>1391</v>
       </c>
       <c r="E123" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="F123" t="s">
         <v>1383</v>
       </c>
       <c r="G123" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H123" t="s">
         <v>146</v>
@@ -13516,7 +13514,7 @@
         <v>1395</v>
       </c>
       <c r="N123" t="s">
-        <v>122</v>
+        <v>34</v>
       </c>
       <c r="O123" t="s">
         <v>1396</v>
@@ -13549,19 +13547,19 @@
         <v>1401</v>
       </c>
       <c r="C124" t="s">
-        <v>114</v>
+        <v>23</v>
       </c>
       <c r="D124" t="s">
         <v>294</v>
       </c>
       <c r="E124" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="F124" t="s">
         <v>1402</v>
       </c>
       <c r="G124" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H124" t="s">
         <v>146</v>
@@ -13582,7 +13580,7 @@
         <v>1407</v>
       </c>
       <c r="N124" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="O124" t="s">
         <v>1408</v>
@@ -13591,7 +13589,7 @@
         <v>1409</v>
       </c>
       <c r="Q124" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="R124" t="s">
         <v>932</v>
@@ -13619,14 +13617,14 @@
       </c>
       <c r="D125"/>
       <c r="E125" t="s">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="F125" t="s">
         <v>1411</v>
       </c>
       <c r="G125"/>
       <c r="H125" t="s">
-        <v>116</v>
+        <v>28</v>
       </c>
       <c r="I125" t="s">
         <v>1412</v>
@@ -13684,7 +13682,7 @@
       </c>
       <c r="G126"/>
       <c r="H126" t="s">
-        <v>116</v>
+        <v>28</v>
       </c>
       <c r="I126" t="s">
         <v>1423</v>
@@ -13735,19 +13733,19 @@
         <v>1433</v>
       </c>
       <c r="C127" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D127" t="s">
         <v>1434</v>
       </c>
       <c r="E127" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="F127" t="s">
         <v>1435</v>
       </c>
       <c r="G127" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H127" t="s">
         <v>146</v>
@@ -13768,7 +13766,7 @@
         <v>1440</v>
       </c>
       <c r="N127" t="s">
-        <v>122</v>
+        <v>34</v>
       </c>
       <c r="O127" t="s">
         <v>1441</v>
@@ -13777,7 +13775,7 @@
         <v>1442</v>
       </c>
       <c r="Q127" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="R127" t="s">
         <v>1443</v>
@@ -13801,22 +13799,22 @@
         <v>1446</v>
       </c>
       <c r="C128" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D128" t="s">
         <v>1447</v>
       </c>
       <c r="E128" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="F128" t="s">
         <v>1448</v>
       </c>
       <c r="G128" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H128" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="I128" t="s">
         <v>1449</v>
@@ -13834,7 +13832,7 @@
         <v>1453</v>
       </c>
       <c r="N128" t="s">
-        <v>122</v>
+        <v>34</v>
       </c>
       <c r="O128" t="s">
         <v>1454</v>
@@ -13843,7 +13841,7 @@
         <v>1455</v>
       </c>
       <c r="Q128" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="R128" t="s">
         <v>1456</v>
@@ -13867,19 +13865,19 @@
         <v>1459</v>
       </c>
       <c r="C129" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D129" t="s">
         <v>145</v>
       </c>
       <c r="E129" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="F129" t="s">
         <v>1448</v>
       </c>
       <c r="G129" t="s">
-        <v>65</v>
+        <v>27</v>
       </c>
       <c r="H129" t="s">
         <v>146</v>
@@ -13900,7 +13898,7 @@
         <v>1464</v>
       </c>
       <c r="N129" t="s">
-        <v>122</v>
+        <v>34</v>
       </c>
       <c r="O129" t="s">
         <v>1465</v>
@@ -13933,22 +13931,22 @@
         <v>1467</v>
       </c>
       <c r="C130" t="s">
-        <v>114</v>
+        <v>23</v>
       </c>
       <c r="D130" t="s">
         <v>485</v>
       </c>
       <c r="E130" t="s">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="F130" t="s">
         <v>1468</v>
       </c>
       <c r="G130" t="s">
-        <v>65</v>
+        <v>27</v>
       </c>
       <c r="H130" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="I130" t="s">
         <v>1469</v>
@@ -13975,7 +13973,7 @@
         <v>1475</v>
       </c>
       <c r="Q130" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="R130" t="s">
         <v>1305</v>
@@ -13999,19 +13997,19 @@
         <v>1476</v>
       </c>
       <c r="C131" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="D131" t="s">
         <v>1477</v>
       </c>
       <c r="E131" t="s">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="F131" t="s">
         <v>1468</v>
       </c>
       <c r="G131" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H131" t="s">
         <v>146</v>
@@ -14041,7 +14039,7 @@
         <v>1484</v>
       </c>
       <c r="Q131" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="R131" t="s">
         <v>1485</v>
@@ -14065,7 +14063,7 @@
         <v>1488</v>
       </c>
       <c r="C132" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="D132" t="s">
         <v>1489</v>
@@ -14077,10 +14075,10 @@
         <v>1468</v>
       </c>
       <c r="G132" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H132" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="I132" t="s">
         <v>1491</v>
@@ -14098,7 +14096,7 @@
         <v>1495</v>
       </c>
       <c r="N132" t="s">
-        <v>122</v>
+        <v>34</v>
       </c>
       <c r="O132" t="s">
         <v>1496</v>
@@ -14107,7 +14105,7 @@
         <v>1497</v>
       </c>
       <c r="Q132" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="R132" t="s">
         <v>1498</v>
@@ -14131,7 +14129,7 @@
         <v>1501</v>
       </c>
       <c r="C133" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D133" t="s">
         <v>450</v>
@@ -14143,7 +14141,7 @@
         <v>1468</v>
       </c>
       <c r="G133" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H133" t="s">
         <v>146</v>
@@ -14164,7 +14162,7 @@
         <v>1506</v>
       </c>
       <c r="N133" t="s">
-        <v>122</v>
+        <v>34</v>
       </c>
       <c r="O133" t="s">
         <v>1507</v>
@@ -14197,22 +14195,22 @@
         <v>1512</v>
       </c>
       <c r="C134" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D134" t="s">
         <v>1477</v>
       </c>
       <c r="E134" t="s">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="F134" t="s">
         <v>1468</v>
       </c>
       <c r="G134" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H134" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="I134" t="s">
         <v>1513</v>
@@ -14230,7 +14228,7 @@
         <v>1517</v>
       </c>
       <c r="N134" t="s">
-        <v>122</v>
+        <v>34</v>
       </c>
       <c r="O134" t="s">
         <v>1518</v>
@@ -14263,22 +14261,22 @@
         <v>1523</v>
       </c>
       <c r="C135" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D135" t="s">
         <v>1178</v>
       </c>
       <c r="E135" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="F135" t="s">
         <v>1468</v>
       </c>
       <c r="G135" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H135" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="I135" t="s">
         <v>1524</v>
@@ -14296,7 +14294,7 @@
         <v>1528</v>
       </c>
       <c r="N135" t="s">
-        <v>122</v>
+        <v>34</v>
       </c>
       <c r="O135" t="s">
         <v>1529</v>
@@ -14305,7 +14303,7 @@
         <v>1530</v>
       </c>
       <c r="Q135" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="R135" t="s">
         <v>1531</v>
@@ -14329,22 +14327,22 @@
         <v>1534</v>
       </c>
       <c r="C136" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D136" t="s">
         <v>1535</v>
       </c>
       <c r="E136" t="s">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="F136" t="s">
         <v>1536</v>
       </c>
       <c r="G136" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H136" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="I136" t="s">
         <v>1537</v>
@@ -14362,7 +14360,7 @@
         <v>1541</v>
       </c>
       <c r="N136" t="s">
-        <v>122</v>
+        <v>34</v>
       </c>
       <c r="O136" t="s">
         <v>1542</v>
@@ -14371,7 +14369,7 @@
         <v>1543</v>
       </c>
       <c r="Q136" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="R136" t="s">
         <v>854</v>
@@ -14395,7 +14393,7 @@
         <v>1544</v>
       </c>
       <c r="C137" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D137" t="s">
         <v>347</v>
@@ -14407,10 +14405,10 @@
         <v>1545</v>
       </c>
       <c r="G137" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H137" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="I137" t="s">
         <v>1546</v>
@@ -14428,7 +14426,7 @@
         <v>1550</v>
       </c>
       <c r="N137" t="s">
-        <v>122</v>
+        <v>34</v>
       </c>
       <c r="O137" t="s">
         <v>1551</v>
@@ -14461,22 +14459,22 @@
         <v>1553</v>
       </c>
       <c r="C138" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D138" t="s">
         <v>1554</v>
       </c>
       <c r="E138" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="F138" t="s">
         <v>1555</v>
       </c>
       <c r="G138" t="s">
-        <v>65</v>
+        <v>27</v>
       </c>
       <c r="H138" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="I138" t="s">
         <v>1556</v>
@@ -14494,7 +14492,7 @@
         <v>1560</v>
       </c>
       <c r="N138" t="s">
-        <v>122</v>
+        <v>34</v>
       </c>
       <c r="O138" t="s">
         <v>1561</v>
@@ -14527,22 +14525,22 @@
         <v>1563</v>
       </c>
       <c r="C139" t="s">
-        <v>114</v>
+        <v>23</v>
       </c>
       <c r="D139" t="s">
         <v>1564</v>
       </c>
       <c r="E139" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="F139" t="s">
         <v>1565</v>
       </c>
       <c r="G139" t="s">
-        <v>65</v>
+        <v>27</v>
       </c>
       <c r="H139" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="I139" t="s">
         <v>1566</v>
@@ -14605,7 +14603,7 @@
         <v>1565</v>
       </c>
       <c r="G140" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H140" t="s">
         <v>146</v>
@@ -14624,7 +14622,7 @@
         <v>1577</v>
       </c>
       <c r="N140" t="s">
-        <v>122</v>
+        <v>34</v>
       </c>
       <c r="O140" t="s">
         <v>1578</v>
@@ -14633,7 +14631,7 @@
         <v>1579</v>
       </c>
       <c r="Q140" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="R140" t="s">
         <v>329</v>
@@ -14663,13 +14661,13 @@
         <v>294</v>
       </c>
       <c r="E141" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="F141" t="s">
         <v>1581</v>
       </c>
       <c r="G141" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H141" t="s">
         <v>146</v>
@@ -14688,7 +14686,7 @@
         <v>1585</v>
       </c>
       <c r="N141" t="s">
-        <v>122</v>
+        <v>34</v>
       </c>
       <c r="O141" t="s">
         <v>1586</v>
@@ -14721,7 +14719,7 @@
         <v>1588</v>
       </c>
       <c r="C142" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="D142" t="s">
         <v>1589</v>
@@ -14731,10 +14729,10 @@
         <v>1590</v>
       </c>
       <c r="G142" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H142" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="I142" t="s">
         <v>1591</v>
@@ -14761,7 +14759,7 @@
         <v>1597</v>
       </c>
       <c r="Q142" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="R142" t="s">
         <v>1598</v>
@@ -14785,19 +14783,19 @@
         <v>1601</v>
       </c>
       <c r="C143" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D143" t="s">
         <v>894</v>
       </c>
       <c r="E143" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="F143" t="s">
         <v>1602</v>
       </c>
       <c r="G143" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H143" t="s">
         <v>146</v>
@@ -14818,7 +14816,7 @@
         <v>1607</v>
       </c>
       <c r="N143" t="s">
-        <v>122</v>
+        <v>34</v>
       </c>
       <c r="O143" t="s">
         <v>1608</v>
@@ -14827,7 +14825,7 @@
         <v>1609</v>
       </c>
       <c r="Q143" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="R143" t="s">
         <v>1610</v>
@@ -14851,22 +14849,22 @@
         <v>1613</v>
       </c>
       <c r="C144" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="D144" t="s">
         <v>718</v>
       </c>
       <c r="E144" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="F144" t="s">
         <v>1602</v>
       </c>
       <c r="G144" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H144" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="I144" t="s">
         <v>1614</v>
@@ -14884,7 +14882,7 @@
         <v>1618</v>
       </c>
       <c r="N144" t="s">
-        <v>122</v>
+        <v>34</v>
       </c>
       <c r="O144" t="s">
         <v>1619</v>
@@ -14893,7 +14891,7 @@
         <v>1620</v>
       </c>
       <c r="Q144" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="R144" t="s">
         <v>1621</v>
@@ -14917,19 +14915,19 @@
         <v>1624</v>
       </c>
       <c r="C145" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="D145" t="s">
         <v>1625</v>
       </c>
       <c r="E145" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="F145" t="s">
         <v>1626</v>
       </c>
       <c r="G145" t="s">
-        <v>65</v>
+        <v>27</v>
       </c>
       <c r="H145" t="s">
         <v>870</v>
@@ -14950,7 +14948,7 @@
         <v>1631</v>
       </c>
       <c r="N145" t="s">
-        <v>122</v>
+        <v>34</v>
       </c>
       <c r="O145" t="s">
         <v>1632</v>
@@ -14959,7 +14957,7 @@
         <v>1633</v>
       </c>
       <c r="Q145" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="R145" t="s">
         <v>1634</v>
@@ -14983,19 +14981,19 @@
         <v>1637</v>
       </c>
       <c r="C146" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="D146" t="s">
         <v>1024</v>
       </c>
       <c r="E146" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="F146" t="s">
         <v>1626</v>
       </c>
       <c r="G146" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H146" t="s">
         <v>870</v>
@@ -15016,7 +15014,7 @@
         <v>1631</v>
       </c>
       <c r="N146" t="s">
-        <v>122</v>
+        <v>34</v>
       </c>
       <c r="O146" t="s">
         <v>1638</v>
@@ -15025,7 +15023,7 @@
         <v>1639</v>
       </c>
       <c r="Q146" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="R146" t="s">
         <v>1640</v>
@@ -15049,7 +15047,7 @@
         <v>1643</v>
       </c>
       <c r="C147" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D147" t="s">
         <v>1644</v>
@@ -15061,10 +15059,10 @@
         <v>1645</v>
       </c>
       <c r="G147" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H147" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="I147" t="s">
         <v>1646</v>
@@ -15082,7 +15080,7 @@
         <v>1650</v>
       </c>
       <c r="N147" t="s">
-        <v>122</v>
+        <v>34</v>
       </c>
       <c r="O147" t="s">
         <v>1651</v>
@@ -15091,7 +15089,7 @@
         <v>1652</v>
       </c>
       <c r="Q147" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="R147" t="s">
         <v>649</v>
@@ -15115,19 +15113,19 @@
         <v>1653</v>
       </c>
       <c r="C148" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D148" t="s">
-        <v>62</v>
+        <v>24</v>
       </c>
       <c r="E148" t="s">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="F148" t="s">
         <v>1654</v>
       </c>
       <c r="G148" t="s">
-        <v>65</v>
+        <v>27</v>
       </c>
       <c r="H148" t="s">
         <v>146</v>
@@ -15148,7 +15146,7 @@
         <v>1659</v>
       </c>
       <c r="N148" t="s">
-        <v>122</v>
+        <v>34</v>
       </c>
       <c r="O148" t="s">
         <v>1660</v>
@@ -15181,7 +15179,7 @@
         <v>1665</v>
       </c>
       <c r="C149" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D149" t="s">
         <v>684</v>
@@ -15193,7 +15191,7 @@
         <v>1666</v>
       </c>
       <c r="G149" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H149" t="s">
         <v>146</v>
@@ -15214,7 +15212,7 @@
         <v>1671</v>
       </c>
       <c r="N149" t="s">
-        <v>122</v>
+        <v>34</v>
       </c>
       <c r="O149" t="s">
         <v>1672</v>
@@ -15253,13 +15251,13 @@
         <v>1678</v>
       </c>
       <c r="E150" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="F150" t="s">
         <v>1666</v>
       </c>
       <c r="G150" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H150" t="s">
         <v>146</v>
@@ -15278,7 +15276,7 @@
         <v>1682</v>
       </c>
       <c r="N150" t="s">
-        <v>122</v>
+        <v>34</v>
       </c>
       <c r="O150" t="s">
         <v>1683</v>
@@ -15287,7 +15285,7 @@
         <v>1684</v>
       </c>
       <c r="Q150" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="R150" t="s">
         <v>1674</v>
@@ -15317,13 +15315,13 @@
         <v>1678</v>
       </c>
       <c r="E151" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="F151" t="s">
         <v>1666</v>
       </c>
       <c r="G151" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H151" t="s">
         <v>146</v>
@@ -15342,7 +15340,7 @@
         <v>1689</v>
       </c>
       <c r="N151" t="s">
-        <v>122</v>
+        <v>34</v>
       </c>
       <c r="O151" t="s">
         <v>1690</v>
@@ -15351,7 +15349,7 @@
         <v>1691</v>
       </c>
       <c r="Q151" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="R151" t="s">
         <v>1674</v>
@@ -15387,7 +15385,7 @@
         <v>1694</v>
       </c>
       <c r="G152" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H152" t="s">
         <v>146</v>
@@ -15406,7 +15404,7 @@
         <v>1698</v>
       </c>
       <c r="N152" t="s">
-        <v>122</v>
+        <v>34</v>
       </c>
       <c r="O152" t="s">
         <v>1699</v>
@@ -15415,7 +15413,7 @@
         <v>1700</v>
       </c>
       <c r="Q152" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="R152" t="s">
         <v>649</v>
@@ -15445,16 +15443,16 @@
         <v>1477</v>
       </c>
       <c r="E153" t="s">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="F153" t="s">
         <v>1702</v>
       </c>
       <c r="G153" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H153" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="I153" t="s">
         <v>1703</v>
@@ -15470,7 +15468,7 @@
         <v>1706</v>
       </c>
       <c r="N153" t="s">
-        <v>122</v>
+        <v>34</v>
       </c>
       <c r="O153" t="s">
         <v>1707</v>
@@ -15479,7 +15477,7 @@
         <v>1708</v>
       </c>
       <c r="Q153" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="R153" t="s">
         <v>1709</v>
@@ -15514,7 +15512,7 @@
       </c>
       <c r="G154"/>
       <c r="H154" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="I154" t="s">
         <v>1714</v>
@@ -15532,7 +15530,7 @@
         <v>1718</v>
       </c>
       <c r="N154" t="s">
-        <v>122</v>
+        <v>34</v>
       </c>
       <c r="O154" t="s">
         <v>1719</v>

--- a/Objets_parlementaires_Jura.xlsx
+++ b/Objets_parlementaires_Jura.xlsx
@@ -80,27 +80,120 @@
     <t xml:space="preserve">Statut_Change_Date</t>
   </si>
   <si>
+    <t xml:space="preserve">26.3891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ip.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Juillard Charles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le Centre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Für eine neue Finanzierungsquelle für grosse öffentliche Ausgabenposten. Eine befristete Solidaritätsabgabe auf den Zahlungsverkehr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pour une nouvelle source de financement des grands dossiers en charge des collectivités publiques. Une contribution de solidarité temporaire prélevée sur les mouvements financiers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Una nuova fonte di finanziamento per i grandi progetti a carico delle collettività pubbliche. Un contributo di solidarietà temporaneo prelevato sui movimenti finanziari</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;La Confédération doit faire face à des défis financiers importants que les sources de financements actuelles n'arriveront sans doute pas à financer. Il y a les impôts, les taxes, la TVA notamment; mais celles-ci ne suffisent plus à financer des grands projets dont le pays a besoin. Il s'agit notamment de l'AVS, des infrastructures de transport, de la sécurité du pays (armée notamment), la prévention des dangers naturels liés au changement climatique (tâche partagée avec les cantons et les communes). Mes questions portent sur la création temporaire (10 ans) d'une forme de contribution de solidarité pour les "grands travaux" des 3 niveaux politiques suisses.&amp;nbsp;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Je demande au Conseil fédéral de bien vouloir répondre aux questions suivantes:&lt;/p&gt;&lt;p&gt;1. Le Conseil fédéral a-t-il déjà mené des réflexions quant à la mise en œuvre de nouvelles sources de financement, si oui lesquelles?&lt;/p&gt;&lt;p&gt;2. Sachant que le nombre annuel des mouvements financiers ( et non les transactions financières) s'élève à environ 5560 mio pour un volume financier d'environ CHF 17'530 milliards ( pour 2025), le prélèvement de 1 pour-mille sur ces transactions pourrait rapporter environ CHF 17,5 milliards/an, que ces montants pourraient être versés dans 3 fonds spécifiques (prévoyance sociale, sécurité, dangers naturels) gérés par la Confédération ou la BNS, le Conseil fédéral est-il prêt à examiner rapidement cette nouvelle source de financement et, cas échéant de proposer un projet au Parlement?&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Der Bund steht vor erheblichen finanziellen Herausforderungen, für welche die heutigen Finanzierungsquellen offenkundig nicht ausreichen. Zu diesen Finanzierungsquellen gehören insbesondere Steuern, Abgaben und die Mehrwertsteuer. Diese reichen jedoch nicht mehr aus, um die Finanzierung grosser Ausgabenposten von nationaler Bedeutung sicherzustellen. Hierzu zählen insbesondere die AHV, die Verkehrsinfrastruktur, die Sicherheit des Landes (insbesondere die Armee) sowie die Prävention von Naturgefahren im Zusammenhang mit dem Klimawandel (eine gemeinsam mit den Kantonen und Gemeinden wahrgenommene Aufgabe). Meine Fragen betreffen die Einführung eines (auf zehn Jahre) befristeten Solidaritätsbeitrags für die «grossen Ausgabenposten» der drei politischen Ebenen der Schweiz.&amp;nbsp;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Ich bitte den Bundesrat, die folgenden Fragen zu beantworten:&lt;/p&gt;&lt;p&gt;1. Hat der Bundesrat bereits Überlegungen zu neuen Finanzierungsquellen angestellt, und wenn ja, welche?&lt;/p&gt;&lt;p&gt;2. Ausgehend davon, dass jährlich rund 5560&amp;nbsp;Millionen Finanzströme (und nicht Finanztransaktionen) mit einem Gesamtvolumen von rund 17&amp;nbsp;530&amp;nbsp;Milliarden Franken (2025) abgewickelt werden, könnte eine Abgabe von 1&amp;nbsp;Promille auf diesen Finanzströmen jährliche Einnahmen von rund 17,5&amp;nbsp;Milliarden Franken generieren. Diese Mittel könnten drei Fonds (für die soziale Wohlfahrt, die Sicherheit sowie die Prävention von Naturgefahren) zufliessen, die vom Bund oder von der Schweizerischen Nationalbank verwaltet würden. Ist der Bundesrat bereit, diese neue Finanzierungsquelle rasch zu prüfen und gegebenenfalls dem Parlament eine entsprechende Vorlage zu unterbreiten?&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In Ständerat geplant / Planifié au Conseil des Etats</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Titre uniquement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finanzwesen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finances</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finanze</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crevoisier Crelier Mathilde</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVEK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gewährleistung des Betriebs der Opferhilfe-Nummer 142 in der ganzen Schweiz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Garantir le fonctionnement de la ligne d'aide aux victimes 142 sur l'ensemble du territoire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Garantire il funzionamento della linea di assistenza alle vittime 142 su tutto il territorio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;La Suisse possède plusieurs numéros courts pour les situations d’urgence&amp;nbsp;: le service d'urgence européen (112), l’appel d'urgence de la police (117), la centrale d’alarme feu (118), l’appel d'urgence sanitaire (144), l’appel d’urgence en cas d’intoxication (145), la main tendue (143), le secours téléphonique pour les enfants et les jeunes (147). Depuis le 1&lt;sup&gt;er&lt;/sup&gt;&amp;nbsp;mai 2026, une ligne de secours téléphonique pour les victimes de violence domestique, le 142, est également en service. Ces différents numéros permettent à la population d’atteindre gratuitement le service d’urgence ou de conseil nécessaire.&lt;/p&gt;&lt;p&gt;L’introduction de la ligne pour l’aide aux victimes 142 s’est accompagnée d’une révision des ordonnances correspondantes, l’ordonnance sur les services de télécommunication (OST, RS&amp;nbsp;784.101.1) et l’ordonnance sur les ressources d'adressage dans le domaine des télécommunications (ORAT&amp;nbsp;; RS&amp;nbsp;784.104), qui distinguent clairement les services d’urgence et les services d’aide et de conseil, dont relève le numéro 142 (art.&amp;nbsp;28 et 28a ORAT). Les deux ordonnances révisées entrent en vigueur le 1&lt;sup&gt;er&lt;/sup&gt;&amp;nbsp;juillet 2026.&lt;/p&gt;&lt;p&gt;Or dans les zones frontalières, le fonctionnement des numéros courts présente des défis techniques liés à l'interconnexion automatique avec les réseaux étrangers. Le cas échéant, si l'acheminement est garanti pour les numéros d'urgence au sens strict, il subsiste des incertitudes pour les 142, qui relève d'un service d'aide et de conseil.&lt;/p&gt;&lt;p&gt;Dès lors, le Conseil fédéral est prié de répondre à la question suivante: quelles sont les mesures prévues pour garantir l'acheminement des appels téléphoniques sur la ligne d'aide aux victimes 142, indépendamment du réseau capté et y compris dans les zones frontalières?&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;In der Schweiz stehen mehrere Kurznummern für Notfälle zur Verfügung: europäischer Notruf&amp;nbsp;(112), Polizei&amp;nbsp;(117), Feuerwehr&amp;nbsp;(118), Sanität&amp;nbsp;(144), Tox-Zentrum&amp;nbsp;(145), dargebotene Hand&amp;nbsp;(143) sowie die Telefonhilfe für Kinder und Jugendliche&amp;nbsp;(147). Seit dem 1.&amp;nbsp;Mai&amp;nbsp;2026 ist zudem die Opferhilfe-Nummer&amp;nbsp;142 für Opfer häuslicher Gewalt in Betrieb.&lt;sup&gt;&lt;/sup&gt; Über diese verschiedenen Nummern kann die Bevölkerung kostenlos den jeweils erforderlichen Notruf- oder Beratungsdienst erreichen.&lt;/p&gt;&lt;p&gt;Die Einführung der Opferhilfe-Nummer&amp;nbsp;142 ging mit einer Revision der entsprechenden Verordnungen einher, nämlich der Verordnung über Fernmeldedienste (FDV; SR 784.101.1) und der Verordnung über die Adressierungselemente im Fernmeldebereich (AEFV; SR 784.104). Diese unterscheiden klar zwischen Notdiensten sowie Hilfs- und Beratungsdiensten, denen die Nummer&amp;nbsp;142 zugeordnet ist (Artikel 28 und 28a AEFV). Die beiden revidierten Verordnungen treten am 1.&amp;nbsp;Juli&amp;nbsp;2026 in Kraft.&lt;sup&gt;&lt;/sup&gt;&lt;/p&gt;&lt;p&gt;In Grenzgebieten ergeben sich beim Betrieb von Kurznummern jedoch technische Herausforderungen im Zusammenhang mit der automatischen Verbindung mit ausländischen Netzen. Während die Weiterleitung von Anrufen an Notrufnummern im engeren Sinne gewährleistet ist, bestehen hinsichtlich der Nummer&amp;nbsp;142, die einem Hilfs- und Beratungsdienst zugeordnet ist, weiterhin Unsicherheiten.&lt;/p&gt;&lt;p&gt;Welche Massnahmen sind vorgesehen, um die Weiterleitung von Anrufen an die Opferhilfe-Nummer&amp;nbsp;142 unabhängig vom jeweils genutzten Netz auch in Grenzgebieten sicherzustellen?&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Internationale Politik|Medien und Kommunikation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politique internationale|Médias et communication</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politica internazionale|Media e comunicazione</t>
+  </si>
+  <si>
     <t xml:space="preserve">26.3968</t>
   </si>
   <si>
-    <t xml:space="preserve">Ip.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Chollet Clarence</t>
   </si>
   <si>
     <t xml:space="preserve">VERT-E-S</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-06-19</t>
-  </si>
-  <si>
     <t xml:space="preserve">NR</t>
   </si>
   <si>
-    <t xml:space="preserve">UVEK</t>
-  </si>
-  <si>
     <t xml:space="preserve">Der "Roi du Doubs" muss gerettet werden, bevor es zu spät ist</t>
   </si>
   <si>
@@ -137,9 +230,6 @@
     <t xml:space="preserve">Ambiente</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10</t>
-  </si>
-  <si>
     <t xml:space="preserve">26.3997</t>
   </si>
   <si>
@@ -182,27 +272,171 @@
     <t xml:space="preserve">Economia|Scienza e ricerca|Imposte|Salute</t>
   </si>
   <si>
+    <t xml:space="preserve">26.3628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VBS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cybersicherheit und digitale Souveränität. Eine nationale Roadmap für den Übergang zur Post-Quanten-Kryptografie in der Schweiz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cybersécurité et souveraineté numérique. Doter la Suisse d'une feuille de route nationale de transition vers la cryptographie post-quantique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cibersicurezza e sovranità digitale. Dotare la Svizzera di una tabella di marcia nazionale per la transizione verso la crittografia post-quantistica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé d’élaborer, en collaboration avec les cantons, les hautes écoles, les instituts de recherche, les autorités de surveillance sectorielles et le secteur privé, une feuille de route nationale pour la transition de la Suisse vers la cryptographie post-quantique. Cette feuille de route doit garantir la protection durable des données et des communications sensibles, la résilience des infrastructures critiques, la validité à long terme des signatures et des documents électroniques, l’interopérabilité internationale des systèmes suisses et la compétitivité des entreprises actives sur les marchés internationaux. Elle doit en particulier :&lt;/p&gt;&lt;ol style="list-style-type:lower-alpha;"&gt;&lt;li&gt;&lt;strong&gt;établir, d’ici à fin 2027 au plus tard, une stratégie nationale de migration — c’est-à-dire de remplacement progressif des algorithmes vulnérables — fondée sur les risques,&amp;nbsp;&lt;/strong&gt;comprenant un inventaire des usages cryptographiques critiques, une cartographie des dépendances, y compris à l’égard des fournisseurs étrangers, et le lancement de projets pilotes pour les cas d’usage présentant un risque élevé ou une longue durée de confidentialité ;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;fixer des jalons coordonnés avec les calendriers internationaux pertinents,&amp;nbsp;&lt;/strong&gt;notamment la migration prioritaire des cas d’usage à haut risque d’ici à fin 2030 et la transition progressive des autres systèmes critiques ou sensibles d’ici à fin 2035, sous réserve de la maturité des standards, de l’interopérabilité et de la proportionnalité des mesures ;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;désigner les responsabilités de pilotage et de coordination au sein de l’administration fédérale,&amp;nbsp;&lt;/strong&gt;en s’appuyant en particulier sur l’Office fédéral de la cybersécurité (OFCS, anciennement NCSC), l’Office fédéral de l’informatique et de la télécommunication (OFIT) et les autorités sectorielles compétentes, sans créer de structures redondantes, et présenter au Parlement un rapport biennal sur l’état d’avancement ;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;définir les exigences minimales applicables aux infrastructures critiques, aux systèmes d’information de la Confédération et aux fournisseurs de prestations numériques critiques,&amp;nbsp;&lt;/strong&gt;notamment en matière d’inventaire cryptographique standardisé et interopérable — fondé, lorsque cela est approprié, sur des formats reconnus tels que le Cryptographic Bill of Materials (CBOM) —, de crypto-agilité, de capacité de mise à jour et de gestion sécurisée des dépendances fournisseurs, ces inventaires étant traités comme des informations sensibles de sécurité à accès restreint et non destinées à publication détaillée ;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;intégrer des exigences de préparation à la cryptographie post-quantique dans les marchés publics fédéraux et dans les contrats fournisseurs&amp;nbsp;&lt;/strong&gt;pour les produits et services numériques dont la durée de vie, la criticité ou la durée de confidentialité attendue dépasse 2030 ;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;garantir la résilience quantique de la signature électronique et de l’archivage à long terme,&amp;nbsp;&lt;/strong&gt;afin de préserver la validité durable des signatures, certificats, horodatages, actes authentiques, dossiers médicaux, registres publics et archives, en cohérence avec les travaux de la Swiss Government PKI ;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;assurer la cohérence avec les cadres internationaux applicables,&amp;nbsp;&lt;/strong&gt;en particulier la feuille de route coordonnée adoptée par le NIS Cooperation Group de l’Union européenne le 11 juin 2025, ainsi que les exigences du Cyber Resilience Act applicables dès le 11 décembre 2027 aux produits placés sur le marché européen ;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;examiner les adaptations légales ou réglementaires nécessaires,&amp;nbsp;&lt;/strong&gt;notamment dans le cadre de la législation sur la sécurité de l’information, de l’ordonnance sur la cybersécurité, des prescriptions de marchés publics et des réglementations sectorielles applicables ;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;prévoir des mesures de soutien proportionnées pour les cantons, les PME, les hautes écoles et les entreprises suisses,&amp;nbsp;&lt;/strong&gt;notamment par des lignes directrices, des modèles d’inventaire, des projets pilotes, des tests d’interopérabilité et la mobilisation des compétences nationales, dans une logique de souveraineté technologique cohérente avec l’objectif de la motion 24.3209.&lt;/li&gt;&lt;/ol&gt;&lt;p&gt;La feuille de route respecte les principes de neutralité technologique, d’ouverture des standards, de sécurité par conception et de proportionnalité économique — les obligations étant graduées selon le risque, la criticité, la durée de confidentialité des données et la durée de vie des systèmes. Conformément à la tradition suisse de conditions-cadres favorables plutôt que de politique industrielle sélective, elle ne vise pas à privilégier un fournisseur ou une technologie, mais à fixer les exigences de sécurité applicables aux infrastructures de l’État. Les informations sensibles contenues dans les inventaires cryptographiques sont protégées.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, in Zusammenarbeit mit den Kantonen, den Hochschulen, den Forschungsinstituten, den branchenspezifischen Aufsichtsbehörden und der Privatwirtschaft eine nationale Roadmap für den Übergang der Schweiz zur Post-Quanten-Kryptografie auszuarbeiten. Diese Roadmap soll den nachhaltigen Schutz besonders schützenswerter Daten und sensitiver Kommunikation, die Widerstandsfähigkeit kritischer Infrastrukturen, die langfristige Gültigkeit elektronischer Signaturen und Dokumente, die internationale Interoperabilität der Schweizer Systeme und die Wettbewerbsfähigkeit der im internationalen Markt tätigen Unternehmen gewährleisten. Insbesondere ist Folgendes vorzusehen:&lt;/p&gt;&lt;ol style="list-style-type:lower-alpha;"&gt;&lt;li&gt;&lt;strong&gt;Spätestens bis Ende 2027 muss eine nationale Migrationsstrategie – d. h. eine Strategie zur schrittweisen Ablösung anfälliger Algorithmen – auf der Grundlage einer Risikobewertung erarbeitet werden,&amp;nbsp;&lt;/strong&gt;einschliesslich einer Bestandsaufnahme kritischer kryptografischer Anwendungen, einer Kartografie der Abhängigkeiten, auch gegenüber ausländischen Anbietern, sowie der Lancierung von Pilotprojekten für Anwendungsfälle mit hohem Risiko oder langer Vertraulichkeitsdauer.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Es müssen Meilensteine festgelegt werden, die auf die einschlägigen internationalen Zeitpläne abgestimmt sind,&amp;nbsp;&lt;/strong&gt;insbesondere die vorrangige Umstellung für Anwendungsfälle mit hohem Risiko bis Ende 2030 und die schrittweise Umstellung der übrigen kritischen oder sensitiven Systeme bis Ende 2035; dies unter Berücksichtigung der Ausgereiftheit der Standards, der Interoperabilität und der Verhältnismässigkeit der Massnahmen.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Es müssen die Zuständigkeiten für die Steuerung und Koordination innerhalb der Bundesverwaltung festgelegt werden,&lt;/strong&gt; insbesondere unter Einbezug des Bundesamts für Cybersicherheit (BACS, ehemals NCSC), des Bundesamts für Informatik und Telekommunikation (BIT) sowie der spezifisch zuständigen Behörden. Redundante Strukturen müssen vermieden werden. Dem Parlament ist alle zwei Jahre ein Bericht über den Stand der Umsetzung vorzulegen.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Es müssen Mindestanforderungen für kritische Infrastrukturen, Informationssysteme des Bundes und Anbieter kritischer digitaler Dienste festgelegt werden,&amp;nbsp;&lt;/strong&gt;insbesondere betreffend ein standardisiertes und interoperables kryptografisches Inventar – das, soweit angemessen, auf anerkannten Formaten wie der Cryptographic Bill of Materials (CBOM) basiert –, Krypto-Agilität, Aktualisierbarkeit sowie die gesicherte Verwaltung von Lieferantenabhängigkeiten. Diese Inventare müssen als sensitive Sicherheitsinformationen mit eingeschränktem Zugriff behandelt werden und dürfen nicht detailliert veröffentlicht werden.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Anforderungen zur Vorbereitung auf die Post-Quanten-Kryptografie müssen in öffentliche Ausschreibungen des Bundes und in Lieferantenverträgen&lt;/strong&gt;für digitale Produkte und Dienstleistungen, deren Lebensdauer, Kritikalität oder erwartete Vertraulichkeitsdauer über das Jahr 2030 hinausgeht, aufgenommen werden.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Die Quantenresilienz der elektronischen Signatur und der Langzeitarchivierung ist zu gewährleisten,&lt;/strong&gt; um die dauerhafte Gültigkeit von Signaturen, Zertifikaten, Zeitstempeln, öffentlichen Urkunden, Patientendossier, öffentlichen Registern und Archiven in Übereinstimmung mit den Arbeiten der Swiss Government PKI sicherzustellen.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Die Übereinstimmung mit den geltenden internationalen Rahmenwerken ist sicherzustellen,&amp;nbsp;&lt;/strong&gt;insbesondere diejenige mit der koordinierten Roadmap, die am 11. Juni 2025 von der NIS-Kooperationsgruppe der Europäischen Union verabschiedet wurde, sowie diejenige mit den Anforderungen der Cyberresilienz-Verordnung, die ab dem 11. Dezember 2027 für Produkte gelten, die auf den europäischen Markt gebracht werden.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Der rechtlich und reglementarisch erforderliche Anpassungsbedarf ist zu prüfen,&lt;/strong&gt; insbesondere betreffend die Gesetzgebung zur Informationssicherheit, die Cybersicherheitsverordnung, die Vorschriften für das öffentliche Beschaffungswesen und die geltenden bereichsspezifischen Regelungen.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Für die Kantone, KMU, Hochschulen und Schweizer Unternehmen sind angemessene Unterstützungsmassnahmen vorzusehen,&lt;/strong&gt; insbesondere in Form von Leitlinien, Inventarvorlagen, Pilotprojekten, Interoperabilitätstests und durch die Mobilisierung nationaler Kompetenzen im Sinne einer technologischen Souveränität, die mit dem Ziel der Motion 24.3209 übereinstimmt.&lt;/li&gt;&lt;/ol&gt;&lt;p&gt;Die Roadmap berücksichtigt die Grundsätze der Technologieneutralität, der Offenheit der Standards, der Sicherheit durch Design und der wirtschaftlichen Verhältnismässigkeit – wobei die Verpflichtungen je nach Risiko, Kritikalität, Dauer der Vertraulichkeit der Daten und Lebensdauer der Systeme unterschiedlich ausgestaltet sind. Entsprechend der Schweizer Tradition, die eher auf günstige Rahmenbedingungen als auf eine selektive Industriepolitik setzt, zielt sie nicht darauf ab, einen bestimmten Anbieter oder eine bestimmte Technologie zu begünstigen, sondern die Sicherheitsanforderungen für staatliche Infrastrukturen festzulegen. Die in den kryptografischen Bestandesverzeichnissen enthaltenen sensitiven Informationen sind geschützt.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sicherheitspolitik|Medien und Kommunikation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politique de sécurité|Médias et communication</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politica di sicurezza|Media e comunicazione</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Friedli Esther</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UDC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EJPD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Von Dänemark lernen. Bei längerfristigen Freiheitsstrafen muss die obligatorische Landesverweisung obligatorisch sein</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S'inspirer du Danemark. En cas de peines privatives de liberté de longue durée, l'expulsion obligatoire doit être réellement obligatoire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Imparare dalla Danimarca. Espulsione obbligatoria in caso di pene detentive di lunga durata</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé de présenter les modifications législatives nécessaires afin que les étrangers criminels condamnés à une peine privative de liberté d’un an ou plus – qu'elle soit ferme ou assortie d’un sursis total ou partiel – fassent dans tous les cas l'objet d'une expulsion, qui devra obligatoirement être exécutée.&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, die erforderlichen Gesetzesanpassungen vorzulegen, so dass für kriminelle Ausländer bei einer längerfristigen Freiheitsstrafe ab einem Jahr – unabhängig davon, ob diese unbedingt, teilbedingt oder bedingt ausfällt – in jedem Fall zwingend eine Landesverweisung angeordnet und vollzogen werden muss.&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Élu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strafrecht|Migration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Droit pénal|Politique migratoire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diritto penale|Migrazione</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CSSS-N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commissions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13. AHV-Rente. Zuweisung der Steuermehreinnahmen der Kantone und Gemeinden an die AHV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13e rente AVS. Affectation des recettes fiscales supplémentaires des cantons et des communes à l'AVS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">13esima mensilità AVS. Destinare le entrate fiscali supplementari dei Cantoni e dei Comuni all'AVS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé de modifier les bases légales de sorte que les recettes fiscales supplémentaires générées par l’introduction de la 13&lt;sup&gt;e&lt;/sup&gt; rente AVS, pour les cantons et les communes, soient intégralement reversées à la Confédération&lt;u&gt;,&lt;/u&gt; qui les transfère directement à l'AVS.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Une minorité de la commission (Rechsteiner Thomas, Alijaj, Blunschy, Crottaz, Gysi Barbara, Hess Lorenz, Roduit, Piller Carrad, Porchet, Weichelt, Wyss, Zybach) propose de rejeter la motion.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, die gesetzlichen Grundlagen so anzupassen, dass die durch die Einführung der 13. AHV-Rente entstehenden Steuermehreinnahmen bei Kantonen und Gemeinden vollständig dem Bund zufliessen, der diese Mittel direkt an die AHV weiterleitet.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Eine Minderheit&amp;nbsp;der Kommission&amp;nbsp;(Rechsteiner Thomas, Alijaj, Blunschy, Crottaz, Gysi Barbara, Hess Lorenz, Roduit, Piller Carrad, Porchet, Weichelt, Wyss, Zybach) beantragt, die Motion abzulehnen.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finanzwesen|Steuer|Sozialer Schutz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finances|Fiscalité|Protection sociale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finanze|Imposte|Protezione sociale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fraktion der Schweizerischen Volkspartei</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inspirons-nous du Danemark. Rendons réellement obligatoire l'expulsion en cas de peine privative de liberté de longue durée</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé de présenter les modifications législatives nécessaires pour que lorsqu’un délinquant étranger est condamné à une peine privative de liberté de longue durée (un an au moins), que cette peine soit ferme ou assortie d’un sursis ou d’un sursis partiel, une expulsion soit obligatoirement ordonnée et exécutée.&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In Nationalrat geplant / Planifié au Conseil national</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263131</t>
+  </si>
+  <si>
     <t xml:space="preserve">26.3597</t>
   </si>
   <si>
     <t xml:space="preserve">Po.</t>
   </si>
   <si>
-    <t xml:space="preserve">Juillard Charles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Le Centre</t>
-  </si>
-  <si>
     <t xml:space="preserve">2026-06-09</t>
   </si>
   <si>
-    <t xml:space="preserve">SR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EJPD</t>
-  </si>
-  <si>
     <t xml:space="preserve">Für eine Harmonisierung der Definition des Konkubinats im Bundesrecht</t>
   </si>
   <si>
@@ -227,9 +461,6 @@
     <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263597</t>
   </si>
   <si>
-    <t xml:space="preserve">Titre uniquement</t>
-  </si>
-  <si>
     <t xml:space="preserve">Soziale Fragen|Zivilrecht|Sozialer Schutz</t>
   </si>
   <si>
@@ -248,12 +479,6 @@
     <t xml:space="preserve">Dobler Loïc</t>
   </si>
   <si>
-    <t xml:space="preserve">PS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-04</t>
-  </si>
-  <si>
     <t xml:space="preserve">Arztzeugnisse für Kurzabwesenheiten. Unnötige Kosten für die obligatorische Krankenversicherung?</t>
   </si>
   <si>
@@ -287,90 +512,6 @@
     <t xml:space="preserve">2026-09-03</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mo.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CSSS-N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Commissions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-04-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EFD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13. AHV-Rente. Zuweisung der Steuermehreinnahmen der Kantone und Gemeinden an die AHV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13e rente AVS. Affectation des recettes fiscales supplémentaires des cantons et des communes à l'AVS </t>
-  </si>
-  <si>
-    <t xml:space="preserve">13esima mensilità AVS. Destinare le entrate fiscali supplementari dei Cantoni e dei Comuni all'AVS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé de modifier les bases légales de sorte que les recettes fiscales supplémentaires générées par l’introduction de la 13&lt;sup&gt;e&lt;/sup&gt; rente AVS, pour les cantons et les communes, soient intégralement reversées à la Confédération&lt;u&gt;,&lt;/u&gt; qui les transfère directement à l'AVS.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Une minorité de la commission (Rechsteiner Thomas, Alijaj, Blunschy, Crottaz, Gysi Barbara, Hess Lorenz, Roduit, Piller Carrad, Porchet, Weichelt, Wyss, Zybach) propose de rejeter la motion.&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, die gesetzlichen Grundlagen so anzupassen, dass die durch die Einführung der 13. AHV-Rente entstehenden Steuermehreinnahmen bei Kantonen und Gemeinden vollständig dem Bund zufliessen, der diese Mittel direkt an die AHV weiterleitet.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Eine Minderheit&amp;nbsp;der Kommission&amp;nbsp;(Rechsteiner Thomas, Alijaj, Blunschy, Crottaz, Gysi Barbara, Hess Lorenz, Roduit, Piller Carrad, Porchet, Weichelt, Wyss, Zybach) beantragt, die Motion abzulehnen.&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">In Ständerat geplant / Planifié au Conseil des Etats</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finanzwesen|Steuer|Sozialer Schutz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finances|Fiscalité|Protection sociale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finanze|Imposte|Protezione sociale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Für eine neue Finanzierungsquelle für grosse öffentliche Ausgabenposten. Eine befristete Solidaritätsabgabe auf den Zahlungsverkehr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pour une nouvelle source de financement des grands dossiers en charge des collectivités publiques. Une contribution de solidarité temporaire prélevée sur les mouvements financiers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Una nuova fonte di finanziamento per i grandi progetti a carico delle collettività pubbliche. Un contributo di solidarietà temporaneo prelevato sui movimenti finanziari</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;La Confédération doit faire face à des défis financiers importants que les sources de financements actuelles n'arriveront sans doute pas à financer. Il y a les impôts, les taxes, la TVA notamment; mais celles-ci ne suffisent plus à financer des grands projets dont le pays a besoin. Il s'agit notamment de l'AVS, des infrastructures de transport, de la sécurité du pays (armée notamment), la prévention des dangers naturels liés au changement climatique (tâche partagée avec les cantons et les communes). Mes questions portent sur la création temporaire (10 ans) d'une forme de contribution de solidarité pour les "grands travaux" des 3 niveaux politiques suisses.&amp;nbsp;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Je demande au Conseil fédéral de bien vouloir répondre aux questions suivantes:&lt;/p&gt;&lt;p&gt;1. Le Conseil fédéral a-t-il déjà mené des réflexions quant à la mise en œuvre de nouvelles sources de financement, si oui lesquelles?&lt;/p&gt;&lt;p&gt;2. Sachant que le nombre annuel des mouvements financiers ( et non les transactions financières) s'élève à environ 5560 mio pour un volume financier d'environ CHF 17'530 milliards ( pour 2025), le prélèvement de 1 pour-mille sur ces transactions pourrait rapporter environ CHF 17,5 milliards/an, que ces montants pourraient être versés dans 3 fonds spécifiques (prévoyance sociale, sécurité, dangers naturels) gérés par la Confédération ou la BNS, le Conseil fédéral est-il prêt à examiner rapidement cette nouvelle source de financement et, cas échéant de proposer un projet au Parlement?&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Der Bund steht vor erheblichen finanziellen Herausforderungen, für welche die heutigen Finanzierungsquellen offenkundig nicht ausreichen. Zu diesen Finanzierungsquellen gehören insbesondere Steuern, Abgaben und die Mehrwertsteuer. Diese reichen jedoch nicht mehr aus, um die Finanzierung grosser Ausgabenposten von nationaler Bedeutung sicherzustellen. Hierzu zählen insbesondere die AHV, die Verkehrsinfrastruktur, die Sicherheit des Landes (insbesondere die Armee) sowie die Prävention von Naturgefahren im Zusammenhang mit dem Klimawandel (eine gemeinsam mit den Kantonen und Gemeinden wahrgenommene Aufgabe). Meine Fragen betreffen die Einführung eines (auf zehn Jahre) befristeten Solidaritätsbeitrags für die «grossen Ausgabenposten» der drei politischen Ebenen der Schweiz.&amp;nbsp;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Ich bitte den Bundesrat, die folgenden Fragen zu beantworten:&lt;/p&gt;&lt;p&gt;1. Hat der Bundesrat bereits Überlegungen zu neuen Finanzierungsquellen angestellt, und wenn ja, welche?&lt;/p&gt;&lt;p&gt;2. Ausgehend davon, dass jährlich rund 5560&amp;nbsp;Millionen Finanzströme (und nicht Finanztransaktionen) mit einem Gesamtvolumen von rund 17&amp;nbsp;530&amp;nbsp;Milliarden Franken (2025) abgewickelt werden, könnte eine Abgabe von 1&amp;nbsp;Promille auf diesen Finanzströmen jährliche Einnahmen von rund 17,5&amp;nbsp;Milliarden Franken generieren. Diese Mittel könnten drei Fonds (für die soziale Wohlfahrt, die Sicherheit sowie die Prävention von Naturgefahren) zufliessen, die vom Bund oder von der Schweizerischen Nationalbank verwaltet würden. Ist der Bundesrat bereit, diese neue Finanzierungsquelle rasch zu prüfen und gegebenenfalls dem Parlament eine entsprechende Vorlage zu unterbreiten?&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finanzwesen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finances</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finanze</t>
-  </si>
-  <si>
     <t xml:space="preserve">26.3936</t>
   </si>
   <si>
@@ -440,123 +581,6 @@
     <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263949</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VBS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cybersicherheit und digitale Souveränität. Eine nationale Roadmap für den Übergang zur Post-Quanten-Kryptografie in der Schweiz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cybersécurité et souveraineté numérique. Doter la Suisse d'une feuille de route nationale de transition vers la cryptographie post-quantique</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cibersicurezza e sovranità digitale. Dotare la Svizzera di una tabella di marcia nazionale per la transizione verso la crittografia post-quantistica</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé d’élaborer, en collaboration avec les cantons, les hautes écoles, les instituts de recherche, les autorités de surveillance sectorielles et le secteur privé, une feuille de route nationale pour la transition de la Suisse vers la cryptographie post-quantique. Cette feuille de route doit garantir la protection durable des données et des communications sensibles, la résilience des infrastructures critiques, la validité à long terme des signatures et des documents électroniques, l’interopérabilité internationale des systèmes suisses et la compétitivité des entreprises actives sur les marchés internationaux. Elle doit en particulier :&lt;/p&gt;&lt;ol style="list-style-type:lower-alpha;"&gt;&lt;li&gt;&lt;strong&gt;établir, d’ici à fin 2027 au plus tard, une stratégie nationale de migration — c’est-à-dire de remplacement progressif des algorithmes vulnérables — fondée sur les risques,&amp;nbsp;&lt;/strong&gt;comprenant un inventaire des usages cryptographiques critiques, une cartographie des dépendances, y compris à l’égard des fournisseurs étrangers, et le lancement de projets pilotes pour les cas d’usage présentant un risque élevé ou une longue durée de confidentialité ;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;fixer des jalons coordonnés avec les calendriers internationaux pertinents,&amp;nbsp;&lt;/strong&gt;notamment la migration prioritaire des cas d’usage à haut risque d’ici à fin 2030 et la transition progressive des autres systèmes critiques ou sensibles d’ici à fin 2035, sous réserve de la maturité des standards, de l’interopérabilité et de la proportionnalité des mesures ;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;désigner les responsabilités de pilotage et de coordination au sein de l’administration fédérale,&amp;nbsp;&lt;/strong&gt;en s’appuyant en particulier sur l’Office fédéral de la cybersécurité (OFCS, anciennement NCSC), l’Office fédéral de l’informatique et de la télécommunication (OFIT) et les autorités sectorielles compétentes, sans créer de structures redondantes, et présenter au Parlement un rapport biennal sur l’état d’avancement ;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;définir les exigences minimales applicables aux infrastructures critiques, aux systèmes d’information de la Confédération et aux fournisseurs de prestations numériques critiques,&amp;nbsp;&lt;/strong&gt;notamment en matière d’inventaire cryptographique standardisé et interopérable — fondé, lorsque cela est approprié, sur des formats reconnus tels que le Cryptographic Bill of Materials (CBOM) —, de crypto-agilité, de capacité de mise à jour et de gestion sécurisée des dépendances fournisseurs, ces inventaires étant traités comme des informations sensibles de sécurité à accès restreint et non destinées à publication détaillée ;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;intégrer des exigences de préparation à la cryptographie post-quantique dans les marchés publics fédéraux et dans les contrats fournisseurs&amp;nbsp;&lt;/strong&gt;pour les produits et services numériques dont la durée de vie, la criticité ou la durée de confidentialité attendue dépasse 2030 ;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;garantir la résilience quantique de la signature électronique et de l’archivage à long terme,&amp;nbsp;&lt;/strong&gt;afin de préserver la validité durable des signatures, certificats, horodatages, actes authentiques, dossiers médicaux, registres publics et archives, en cohérence avec les travaux de la Swiss Government PKI ;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;assurer la cohérence avec les cadres internationaux applicables,&amp;nbsp;&lt;/strong&gt;en particulier la feuille de route coordonnée adoptée par le NIS Cooperation Group de l’Union européenne le 11 juin 2025, ainsi que les exigences du Cyber Resilience Act applicables dès le 11 décembre 2027 aux produits placés sur le marché européen ;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;examiner les adaptations légales ou réglementaires nécessaires,&amp;nbsp;&lt;/strong&gt;notamment dans le cadre de la législation sur la sécurité de l’information, de l’ordonnance sur la cybersécurité, des prescriptions de marchés publics et des réglementations sectorielles applicables ;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;prévoir des mesures de soutien proportionnées pour les cantons, les PME, les hautes écoles et les entreprises suisses,&amp;nbsp;&lt;/strong&gt;notamment par des lignes directrices, des modèles d’inventaire, des projets pilotes, des tests d’interopérabilité et la mobilisation des compétences nationales, dans une logique de souveraineté technologique cohérente avec l’objectif de la motion 24.3209.&lt;/li&gt;&lt;/ol&gt;&lt;p&gt;La feuille de route respecte les principes de neutralité technologique, d’ouverture des standards, de sécurité par conception et de proportionnalité économique — les obligations étant graduées selon le risque, la criticité, la durée de confidentialité des données et la durée de vie des systèmes. Conformément à la tradition suisse de conditions-cadres favorables plutôt que de politique industrielle sélective, elle ne vise pas à privilégier un fournisseur ou une technologie, mais à fixer les exigences de sécurité applicables aux infrastructures de l’État. Les informations sensibles contenues dans les inventaires cryptographiques sont protégées.&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, in Zusammenarbeit mit den Kantonen, den Hochschulen, den Forschungsinstituten, den branchenspezifischen Aufsichtsbehörden und der Privatwirtschaft eine nationale Roadmap für den Übergang der Schweiz zur Post-Quanten-Kryptografie auszuarbeiten. Diese Roadmap soll den nachhaltigen Schutz besonders schützenswerter Daten und sensitiver Kommunikation, die Widerstandsfähigkeit kritischer Infrastrukturen, die langfristige Gültigkeit elektronischer Signaturen und Dokumente, die internationale Interoperabilität der Schweizer Systeme und die Wettbewerbsfähigkeit der im internationalen Markt tätigen Unternehmen gewährleisten. Insbesondere ist Folgendes vorzusehen:&lt;/p&gt;&lt;ol style="list-style-type:lower-alpha;"&gt;&lt;li&gt;&lt;strong&gt;Spätestens bis Ende 2027 muss eine nationale Migrationsstrategie – d. h. eine Strategie zur schrittweisen Ablösung anfälliger Algorithmen – auf der Grundlage einer Risikobewertung erarbeitet werden,&amp;nbsp;&lt;/strong&gt;einschliesslich einer Bestandsaufnahme kritischer kryptografischer Anwendungen, einer Kartografie der Abhängigkeiten, auch gegenüber ausländischen Anbietern, sowie der Lancierung von Pilotprojekten für Anwendungsfälle mit hohem Risiko oder langer Vertraulichkeitsdauer.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Es müssen Meilensteine festgelegt werden, die auf die einschlägigen internationalen Zeitpläne abgestimmt sind,&amp;nbsp;&lt;/strong&gt;insbesondere die vorrangige Umstellung für Anwendungsfälle mit hohem Risiko bis Ende 2030 und die schrittweise Umstellung der übrigen kritischen oder sensitiven Systeme bis Ende 2035; dies unter Berücksichtigung der Ausgereiftheit der Standards, der Interoperabilität und der Verhältnismässigkeit der Massnahmen.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Es müssen die Zuständigkeiten für die Steuerung und Koordination innerhalb der Bundesverwaltung festgelegt werden,&lt;/strong&gt; insbesondere unter Einbezug des Bundesamts für Cybersicherheit (BACS, ehemals NCSC), des Bundesamts für Informatik und Telekommunikation (BIT) sowie der spezifisch zuständigen Behörden. Redundante Strukturen müssen vermieden werden. Dem Parlament ist alle zwei Jahre ein Bericht über den Stand der Umsetzung vorzulegen.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Es müssen Mindestanforderungen für kritische Infrastrukturen, Informationssysteme des Bundes und Anbieter kritischer digitaler Dienste festgelegt werden,&amp;nbsp;&lt;/strong&gt;insbesondere betreffend ein standardisiertes und interoperables kryptografisches Inventar – das, soweit angemessen, auf anerkannten Formaten wie der Cryptographic Bill of Materials (CBOM) basiert –, Krypto-Agilität, Aktualisierbarkeit sowie die gesicherte Verwaltung von Lieferantenabhängigkeiten. Diese Inventare müssen als sensitive Sicherheitsinformationen mit eingeschränktem Zugriff behandelt werden und dürfen nicht detailliert veröffentlicht werden.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Anforderungen zur Vorbereitung auf die Post-Quanten-Kryptografie müssen in öffentliche Ausschreibungen des Bundes und in Lieferantenverträgen&lt;/strong&gt;für digitale Produkte und Dienstleistungen, deren Lebensdauer, Kritikalität oder erwartete Vertraulichkeitsdauer über das Jahr 2030 hinausgeht, aufgenommen werden.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Die Quantenresilienz der elektronischen Signatur und der Langzeitarchivierung ist zu gewährleisten,&lt;/strong&gt; um die dauerhafte Gültigkeit von Signaturen, Zertifikaten, Zeitstempeln, öffentlichen Urkunden, Patientendossier, öffentlichen Registern und Archiven in Übereinstimmung mit den Arbeiten der Swiss Government PKI sicherzustellen.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Die Übereinstimmung mit den geltenden internationalen Rahmenwerken ist sicherzustellen,&amp;nbsp;&lt;/strong&gt;insbesondere diejenige mit der koordinierten Roadmap, die am 11. Juni 2025 von der NIS-Kooperationsgruppe der Europäischen Union verabschiedet wurde, sowie diejenige mit den Anforderungen der Cyberresilienz-Verordnung, die ab dem 11. Dezember 2027 für Produkte gelten, die auf den europäischen Markt gebracht werden.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Der rechtlich und reglementarisch erforderliche Anpassungsbedarf ist zu prüfen,&lt;/strong&gt; insbesondere betreffend die Gesetzgebung zur Informationssicherheit, die Cybersicherheitsverordnung, die Vorschriften für das öffentliche Beschaffungswesen und die geltenden bereichsspezifischen Regelungen.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Für die Kantone, KMU, Hochschulen und Schweizer Unternehmen sind angemessene Unterstützungsmassnahmen vorzusehen,&lt;/strong&gt; insbesondere in Form von Leitlinien, Inventarvorlagen, Pilotprojekten, Interoperabilitätstests und durch die Mobilisierung nationaler Kompetenzen im Sinne einer technologischen Souveränität, die mit dem Ziel der Motion 24.3209 übereinstimmt.&lt;/li&gt;&lt;/ol&gt;&lt;p&gt;Die Roadmap berücksichtigt die Grundsätze der Technologieneutralität, der Offenheit der Standards, der Sicherheit durch Design und der wirtschaftlichen Verhältnismässigkeit – wobei die Verpflichtungen je nach Risiko, Kritikalität, Dauer der Vertraulichkeit der Daten und Lebensdauer der Systeme unterschiedlich ausgestaltet sind. Entsprechend der Schweizer Tradition, die eher auf günstige Rahmenbedingungen als auf eine selektive Industriepolitik setzt, zielt sie nicht darauf ab, einen bestimmten Anbieter oder eine bestimmte Technologie zu begünstigen, sondern die Sicherheitsanforderungen für staatliche Infrastrukturen festzulegen. Die in den kryptografischen Bestandesverzeichnissen enthaltenen sensitiven Informationen sind geschützt.&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sicherheitspolitik|Medien und Kommunikation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politique de sécurité|Médias et communication</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politica di sicurezza|Media e comunicazione</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Friedli Esther</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UDC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Von Dänemark lernen. Bei längerfristigen Freiheitsstrafen muss die obligatorische Landesverweisung obligatorisch sein</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S'inspirer du Danemark. En cas de peines privatives de liberté de longue durée, l'expulsion obligatoire doit être réellement obligatoire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Imparare dalla Danimarca. Espulsione obbligatoria in caso di pene detentive di lunga durata</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé de présenter les modifications législatives nécessaires afin que les étrangers criminels condamnés à une peine privative de liberté d’un an ou plus – qu'elle soit ferme ou assortie d’un sursis total ou partiel – fassent dans tous les cas l'objet d'une expulsion, qui devra obligatoirement être exécutée.&amp;nbsp;&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, die erforderlichen Gesetzesanpassungen vorzulegen, so dass für kriminelle Ausländer bei einer längerfristigen Freiheitsstrafe ab einem Jahr – unabhängig davon, ob diese unbedingt, teilbedingt oder bedingt ausfällt – in jedem Fall zwingend eine Landesverweisung angeordnet und vollzogen werden muss.&amp;nbsp;&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Élu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strafrecht|Migration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Droit pénal|Politique migratoire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diritto penale|Migrazione</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Crevoisier Crelier Mathilde</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gewährleistung des Betriebs der Opferhilfe-Nummer 142 in der ganzen Schweiz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Garantir le fonctionnement de la ligne d'aide aux victimes 142 sur l'ensemble du territoire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Garantire il funzionamento della linea di assistenza alle vittime 142 su tutto il territorio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;La Suisse possède plusieurs numéros courts pour les situations d’urgence&amp;nbsp;: le service d'urgence européen (112), l’appel d'urgence de la police (117), la centrale d’alarme feu (118), l’appel d'urgence sanitaire (144), l’appel d’urgence en cas d’intoxication (145), la main tendue (143), le secours téléphonique pour les enfants et les jeunes (147). Depuis le 1&lt;sup&gt;er&lt;/sup&gt;&amp;nbsp;mai 2026, une ligne de secours téléphonique pour les victimes de violence domestique, le 142, est également en service. Ces différents numéros permettent à la population d’atteindre gratuitement le service d’urgence ou de conseil nécessaire.&lt;/p&gt;&lt;p&gt;L’introduction de la ligne pour l’aide aux victimes 142 s’est accompagnée d’une révision des ordonnances correspondantes, l’ordonnance sur les services de télécommunication (OST, RS&amp;nbsp;784.101.1) et l’ordonnance sur les ressources d'adressage dans le domaine des télécommunications (ORAT&amp;nbsp;; RS&amp;nbsp;784.104), qui distinguent clairement les services d’urgence et les services d’aide et de conseil, dont relève le numéro 142 (art.&amp;nbsp;28 et 28a ORAT). Les deux ordonnances révisées entrent en vigueur le 1&lt;sup&gt;er&lt;/sup&gt;&amp;nbsp;juillet 2026.&lt;/p&gt;&lt;p&gt;Or dans les zones frontalières, le fonctionnement des numéros courts présente des défis techniques liés à l'interconnexion automatique avec les réseaux étrangers. Le cas échéant, si l'acheminement est garanti pour les numéros d'urgence au sens strict, il subsiste des incertitudes pour les 142, qui relève d'un service d'aide et de conseil.&lt;/p&gt;&lt;p&gt;Dès lors, le Conseil fédéral est prié de répondre à la question suivante: quelles sont les mesures prévues pour garantir l'acheminement des appels téléphoniques sur la ligne d'aide aux victimes 142, indépendamment du réseau capté et y compris dans les zones frontalières?&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;In der Schweiz stehen mehrere Kurznummern für Notfälle zur Verfügung: europäischer Notruf&amp;nbsp;(112), Polizei&amp;nbsp;(117), Feuerwehr&amp;nbsp;(118), Sanität&amp;nbsp;(144), Tox-Zentrum&amp;nbsp;(145), dargebotene Hand&amp;nbsp;(143) sowie die Telefonhilfe für Kinder und Jugendliche&amp;nbsp;(147). Seit dem 1.&amp;nbsp;Mai&amp;nbsp;2026 ist zudem die Opferhilfe-Nummer&amp;nbsp;142 für Opfer häuslicher Gewalt in Betrieb.&lt;sup&gt;&lt;/sup&gt; Über diese verschiedenen Nummern kann die Bevölkerung kostenlos den jeweils erforderlichen Notruf- oder Beratungsdienst erreichen.&lt;/p&gt;&lt;p&gt;Die Einführung der Opferhilfe-Nummer&amp;nbsp;142 ging mit einer Revision der entsprechenden Verordnungen einher, nämlich der Verordnung über Fernmeldedienste (FDV; SR 784.101.1) und der Verordnung über die Adressierungselemente im Fernmeldebereich (AEFV; SR 784.104). Diese unterscheiden klar zwischen Notdiensten sowie Hilfs- und Beratungsdiensten, denen die Nummer&amp;nbsp;142 zugeordnet ist (Artikel 28 und 28a AEFV). Die beiden revidierten Verordnungen treten am 1.&amp;nbsp;Juli&amp;nbsp;2026 in Kraft.&lt;sup&gt;&lt;/sup&gt;&lt;/p&gt;&lt;p&gt;In Grenzgebieten ergeben sich beim Betrieb von Kurznummern jedoch technische Herausforderungen im Zusammenhang mit der automatischen Verbindung mit ausländischen Netzen. Während die Weiterleitung von Anrufen an Notrufnummern im engeren Sinne gewährleistet ist, bestehen hinsichtlich der Nummer&amp;nbsp;142, die einem Hilfs- und Beratungsdienst zugeordnet ist, weiterhin Unsicherheiten.&lt;/p&gt;&lt;p&gt;Welche Massnahmen sind vorgesehen, um die Weiterleitung von Anrufen an die Opferhilfe-Nummer&amp;nbsp;142 unabhängig vom jeweils genutzten Netz auch in Grenzgebieten sicherzustellen?&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Internationale Politik|Medien und Kommunikation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politique internationale|Médias et communication</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politica internazionale|Media e comunicazione</t>
-  </si>
-  <si>
     <t xml:space="preserve">26.3601</t>
   </si>
   <si>
@@ -893,9 +917,6 @@
     <t xml:space="preserve">26.3121</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-03-16</t>
-  </si>
-  <si>
     <t xml:space="preserve">Dank einer leistungsfähigen Nationalstrasse N18 Kultur- und Wirtschaftsräume effektiv miteinander verbinden</t>
   </si>
   <si>
@@ -990,27 +1011,6 @@
   </si>
   <si>
     <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fraktion der Schweizerischen Volkspartei</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Inspirons-nous du Danemark. Rendons réellement obligatoire l'expulsion en cas de peine privative de liberté de longue durée</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé de présenter les modifications législatives nécessaires pour que lorsqu’un délinquant étranger est condamné à une peine privative de liberté de longue durée (un an au moins), que cette peine soit ferme ou assortie d’un sursis ou d’un sursis partiel, une expulsion soit obligatoirement ordonnée et exécutée.&amp;nbsp;&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">In Nationalrat geplant / Planifié au Conseil national</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263131</t>
   </si>
   <si>
     <t xml:space="preserve">26.3374</t>
@@ -5670,7 +5670,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>20263968</v>
+        <v>20263891</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
@@ -5736,7 +5736,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>20263997</v>
+        <v>20263916</v>
       </c>
       <c r="B3" t="s">
         <v>42</v>
@@ -5802,611 +5802,599 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>20263597</v>
+        <v>20263968</v>
       </c>
       <c r="B4" t="s">
         <v>56</v>
       </c>
       <c r="C4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" t="s">
         <v>57</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>58</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" t="s">
         <v>59</v>
       </c>
-      <c r="F4" t="s">
+      <c r="H4" t="s">
+        <v>45</v>
+      </c>
+      <c r="I4" t="s">
         <v>60</v>
       </c>
-      <c r="G4" t="s">
+      <c r="J4" t="s">
         <v>61</v>
       </c>
-      <c r="H4" t="s">
+      <c r="K4" t="s">
         <v>62</v>
       </c>
-      <c r="I4" t="s">
+      <c r="L4" t="s">
         <v>63</v>
       </c>
-      <c r="J4" t="s">
+      <c r="M4" t="s">
         <v>64</v>
       </c>
-      <c r="K4" t="s">
+      <c r="N4" t="s">
         <v>65</v>
       </c>
-      <c r="L4" t="s">
+      <c r="O4" t="s">
         <v>66</v>
       </c>
-      <c r="M4" t="s">
+      <c r="P4" t="s">
         <v>67</v>
       </c>
-      <c r="N4" t="s">
+      <c r="Q4" t="s">
         <v>68</v>
       </c>
-      <c r="O4" t="s">
+      <c r="R4" t="s">
         <v>69</v>
       </c>
-      <c r="P4" t="s">
+      <c r="S4" t="s">
         <v>70</v>
       </c>
-      <c r="Q4" t="s">
+      <c r="T4" t="s">
         <v>71</v>
       </c>
-      <c r="R4" t="s">
-        <v>72</v>
-      </c>
-      <c r="S4" t="s">
-        <v>73</v>
-      </c>
-      <c r="T4" t="s">
-        <v>74</v>
-      </c>
       <c r="U4" t="s">
-        <v>75</v>
+        <v>41</v>
       </c>
       <c r="V4"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>20263564</v>
+        <v>20263997</v>
       </c>
       <c r="B5" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C5" t="s">
         <v>23</v>
       </c>
       <c r="D5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E5" t="s">
+        <v>74</v>
+      </c>
+      <c r="F5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H5" t="s">
+        <v>75</v>
+      </c>
+      <c r="I5" t="s">
+        <v>76</v>
+      </c>
+      <c r="J5" t="s">
         <v>77</v>
       </c>
-      <c r="E5" t="s">
+      <c r="K5" t="s">
         <v>78</v>
       </c>
-      <c r="F5" t="s">
+      <c r="L5" t="s">
         <v>79</v>
       </c>
-      <c r="G5" t="s">
-        <v>27</v>
-      </c>
-      <c r="H5" t="s">
-        <v>45</v>
-      </c>
-      <c r="I5" t="s">
+      <c r="M5" t="s">
         <v>80</v>
       </c>
-      <c r="J5" t="s">
+      <c r="N5" t="s">
+        <v>65</v>
+      </c>
+      <c r="O5" t="s">
         <v>81</v>
       </c>
-      <c r="K5" t="s">
+      <c r="P5" t="s">
         <v>82</v>
       </c>
-      <c r="L5" t="s">
+      <c r="Q5" t="s">
+        <v>68</v>
+      </c>
+      <c r="R5" t="s">
         <v>83</v>
       </c>
-      <c r="M5" t="s">
+      <c r="S5" t="s">
         <v>84</v>
       </c>
-      <c r="N5" t="s">
-        <v>34</v>
-      </c>
-      <c r="O5" t="s">
+      <c r="T5" t="s">
         <v>85</v>
       </c>
-      <c r="P5" t="s">
-        <v>86</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>71</v>
-      </c>
-      <c r="R5" t="s">
-        <v>87</v>
-      </c>
-      <c r="S5" t="s">
-        <v>88</v>
-      </c>
-      <c r="T5" t="s">
-        <v>89</v>
-      </c>
       <c r="U5" t="s">
-        <v>90</v>
+        <v>41</v>
       </c>
       <c r="V5"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>20263518</v>
+        <v>20263628</v>
       </c>
       <c r="B6" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C6" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D6" t="s">
-        <v>93</v>
+        <v>24</v>
       </c>
       <c r="E6" t="s">
-        <v>94</v>
+        <v>25</v>
       </c>
       <c r="F6" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="G6" t="s">
         <v>27</v>
       </c>
       <c r="H6" t="s">
+        <v>89</v>
+      </c>
+      <c r="I6" t="s">
+        <v>90</v>
+      </c>
+      <c r="J6" t="s">
+        <v>91</v>
+      </c>
+      <c r="K6" t="s">
+        <v>92</v>
+      </c>
+      <c r="L6" t="s">
+        <v>93</v>
+      </c>
+      <c r="M6" t="s">
+        <v>94</v>
+      </c>
+      <c r="N6" t="s">
+        <v>34</v>
+      </c>
+      <c r="O6" t="s">
+        <v>95</v>
+      </c>
+      <c r="P6" t="s">
         <v>96</v>
-      </c>
-      <c r="I6" t="s">
-        <v>97</v>
-      </c>
-      <c r="J6" t="s">
-        <v>98</v>
-      </c>
-      <c r="K6" t="s">
-        <v>99</v>
-      </c>
-      <c r="L6" t="s">
-        <v>100</v>
-      </c>
-      <c r="M6" t="s">
-        <v>101</v>
-      </c>
-      <c r="N6" t="s">
-        <v>102</v>
-      </c>
-      <c r="O6" t="s">
-        <v>103</v>
-      </c>
-      <c r="P6" t="s">
-        <v>104</v>
       </c>
       <c r="Q6" t="s">
         <v>37</v>
       </c>
       <c r="R6" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="S6" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="T6" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="U6" t="s">
         <v>41</v>
       </c>
-      <c r="V6" t="s">
-        <v>41</v>
-      </c>
+      <c r="V6"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>20263891</v>
+        <v>20263571</v>
       </c>
       <c r="B7" t="s">
+        <v>100</v>
+      </c>
+      <c r="C7" t="s">
+        <v>87</v>
+      </c>
+      <c r="D7" t="s">
+        <v>101</v>
+      </c>
+      <c r="E7" t="s">
+        <v>102</v>
+      </c>
+      <c r="F7" t="s">
+        <v>103</v>
+      </c>
+      <c r="G7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H7" t="s">
+        <v>104</v>
+      </c>
+      <c r="I7" t="s">
+        <v>105</v>
+      </c>
+      <c r="J7" t="s">
+        <v>106</v>
+      </c>
+      <c r="K7" t="s">
+        <v>107</v>
+      </c>
+      <c r="L7" t="s">
         <v>108</v>
       </c>
-      <c r="C7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" t="s">
-        <v>58</v>
-      </c>
-      <c r="E7" t="s">
-        <v>59</v>
-      </c>
-      <c r="F7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G7" t="s">
-        <v>61</v>
-      </c>
-      <c r="H7" t="s">
-        <v>96</v>
-      </c>
-      <c r="I7" t="s">
+      <c r="M7" t="s">
         <v>109</v>
       </c>
-      <c r="J7" t="s">
+      <c r="N7" t="s">
+        <v>34</v>
+      </c>
+      <c r="O7" t="s">
         <v>110</v>
       </c>
-      <c r="K7" t="s">
+      <c r="P7" t="s">
         <v>111</v>
       </c>
-      <c r="L7" t="s">
+      <c r="Q7" t="s">
         <v>112</v>
       </c>
-      <c r="M7" t="s">
+      <c r="R7" t="s">
         <v>113</v>
       </c>
-      <c r="N7" t="s">
-        <v>102</v>
-      </c>
-      <c r="O7" t="s">
+      <c r="S7" t="s">
         <v>114</v>
       </c>
-      <c r="P7" t="s">
+      <c r="T7" t="s">
         <v>115</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>71</v>
-      </c>
-      <c r="R7" t="s">
-        <v>116</v>
-      </c>
-      <c r="S7" t="s">
-        <v>117</v>
-      </c>
-      <c r="T7" t="s">
-        <v>118</v>
       </c>
       <c r="U7" t="s">
         <v>41</v>
       </c>
-      <c r="V7" t="s">
-        <v>41</v>
-      </c>
+      <c r="V7"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>20263936</v>
+        <v>20263518</v>
       </c>
       <c r="B8" t="s">
+        <v>116</v>
+      </c>
+      <c r="C8" t="s">
+        <v>87</v>
+      </c>
+      <c r="D8" t="s">
+        <v>117</v>
+      </c>
+      <c r="E8" t="s">
+        <v>118</v>
+      </c>
+      <c r="F8" t="s">
         <v>119</v>
       </c>
-      <c r="C8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D8" t="s">
+      <c r="G8" t="s">
+        <v>59</v>
+      </c>
+      <c r="H8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I8" t="s">
         <v>120</v>
       </c>
-      <c r="E8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F8" t="s">
-        <v>26</v>
-      </c>
-      <c r="G8" t="s">
-        <v>27</v>
-      </c>
-      <c r="H8" t="s">
+      <c r="J8" t="s">
         <v>121</v>
       </c>
-      <c r="I8" t="s">
+      <c r="K8" t="s">
         <v>122</v>
       </c>
-      <c r="J8" t="s">
+      <c r="L8" t="s">
         <v>123</v>
       </c>
-      <c r="K8" t="s">
+      <c r="M8" t="s">
         <v>124</v>
-      </c>
-      <c r="L8" t="s">
-        <v>125</v>
-      </c>
-      <c r="M8" t="s">
-        <v>126</v>
       </c>
       <c r="N8" t="s">
         <v>34</v>
       </c>
       <c r="O8" t="s">
+        <v>125</v>
+      </c>
+      <c r="P8" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>68</v>
+      </c>
+      <c r="R8" t="s">
         <v>127</v>
       </c>
-      <c r="P8" t="s">
+      <c r="S8" t="s">
         <v>128</v>
       </c>
-      <c r="Q8" t="s">
+      <c r="T8" t="s">
         <v>129</v>
       </c>
-      <c r="R8" t="s">
-        <v>130</v>
-      </c>
-      <c r="S8" t="s">
-        <v>131</v>
-      </c>
-      <c r="T8" t="s">
-        <v>132</v>
-      </c>
       <c r="U8" t="s">
-        <v>133</v>
+        <v>41</v>
       </c>
       <c r="V8"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>20263949</v>
+        <v>20263131</v>
       </c>
       <c r="B9" t="s">
+        <v>130</v>
+      </c>
+      <c r="C9" t="s">
+        <v>87</v>
+      </c>
+      <c r="D9" t="s">
+        <v>131</v>
+      </c>
+      <c r="E9"/>
+      <c r="F9" t="s">
+        <v>132</v>
+      </c>
+      <c r="G9" t="s">
+        <v>59</v>
+      </c>
+      <c r="H9" t="s">
+        <v>104</v>
+      </c>
+      <c r="I9" t="s">
+        <v>105</v>
+      </c>
+      <c r="J9" t="s">
+        <v>133</v>
+      </c>
+      <c r="K9" t="s">
+        <v>107</v>
+      </c>
+      <c r="L9" t="s">
         <v>134</v>
       </c>
-      <c r="C9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D9" t="s">
-        <v>120</v>
-      </c>
-      <c r="E9" t="s">
-        <v>25</v>
-      </c>
-      <c r="F9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G9" t="s">
-        <v>27</v>
-      </c>
-      <c r="H9" t="s">
-        <v>121</v>
-      </c>
-      <c r="I9" t="s">
+      <c r="M9" t="s">
+        <v>109</v>
+      </c>
+      <c r="N9" t="s">
         <v>135</v>
       </c>
-      <c r="J9" t="s">
+      <c r="O9" t="s">
         <v>136</v>
       </c>
-      <c r="K9" t="s">
+      <c r="P9" t="s">
         <v>137</v>
       </c>
-      <c r="L9" t="s">
-        <v>138</v>
-      </c>
-      <c r="M9" t="s">
-        <v>139</v>
-      </c>
-      <c r="N9" t="s">
-        <v>34</v>
-      </c>
-      <c r="O9" t="s">
-        <v>140</v>
-      </c>
-      <c r="P9" t="s">
-        <v>141</v>
-      </c>
       <c r="Q9" t="s">
-        <v>129</v>
+        <v>112</v>
       </c>
       <c r="R9" t="s">
-        <v>130</v>
+        <v>113</v>
       </c>
       <c r="S9" t="s">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="T9" t="s">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="U9" t="s">
-        <v>133</v>
+        <v>41</v>
       </c>
       <c r="V9"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>20263628</v>
+        <v>20263597</v>
       </c>
       <c r="B10" t="s">
+        <v>138</v>
+      </c>
+      <c r="C10" t="s">
+        <v>139</v>
+      </c>
+      <c r="D10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E10" t="s">
+        <v>25</v>
+      </c>
+      <c r="F10" t="s">
+        <v>140</v>
+      </c>
+      <c r="G10" t="s">
+        <v>27</v>
+      </c>
+      <c r="H10" t="s">
+        <v>104</v>
+      </c>
+      <c r="I10" t="s">
+        <v>141</v>
+      </c>
+      <c r="J10" t="s">
         <v>142</v>
       </c>
-      <c r="C10" t="s">
-        <v>92</v>
-      </c>
-      <c r="D10" t="s">
-        <v>58</v>
-      </c>
-      <c r="E10" t="s">
-        <v>59</v>
-      </c>
-      <c r="F10" t="s">
+      <c r="K10" t="s">
         <v>143</v>
       </c>
-      <c r="G10" t="s">
-        <v>61</v>
-      </c>
-      <c r="H10" t="s">
+      <c r="L10" t="s">
         <v>144</v>
       </c>
-      <c r="I10" t="s">
+      <c r="M10" t="s">
         <v>145</v>
       </c>
-      <c r="J10" t="s">
+      <c r="N10" t="s">
         <v>146</v>
       </c>
-      <c r="K10" t="s">
+      <c r="O10" t="s">
         <v>147</v>
       </c>
-      <c r="L10" t="s">
+      <c r="P10" t="s">
         <v>148</v>
       </c>
-      <c r="M10" t="s">
+      <c r="Q10" t="s">
+        <v>37</v>
+      </c>
+      <c r="R10" t="s">
         <v>149</v>
       </c>
-      <c r="N10" t="s">
-        <v>102</v>
-      </c>
-      <c r="O10" t="s">
+      <c r="S10" t="s">
         <v>150</v>
       </c>
-      <c r="P10" t="s">
+      <c r="T10" t="s">
         <v>151</v>
       </c>
-      <c r="Q10" t="s">
-        <v>71</v>
-      </c>
-      <c r="R10" t="s">
+      <c r="U10" t="s">
         <v>152</v>
       </c>
-      <c r="S10" t="s">
-        <v>153</v>
-      </c>
-      <c r="T10" t="s">
-        <v>154</v>
-      </c>
-      <c r="U10" t="s">
-        <v>41</v>
-      </c>
-      <c r="V10" t="s">
-        <v>41</v>
-      </c>
+      <c r="V10"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>20263571</v>
+        <v>20263564</v>
       </c>
       <c r="B11" t="s">
+        <v>153</v>
+      </c>
+      <c r="C11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" t="s">
+        <v>154</v>
+      </c>
+      <c r="E11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F11" t="s">
+        <v>103</v>
+      </c>
+      <c r="G11" t="s">
+        <v>59</v>
+      </c>
+      <c r="H11" t="s">
+        <v>75</v>
+      </c>
+      <c r="I11" t="s">
         <v>155</v>
       </c>
-      <c r="C11" t="s">
-        <v>92</v>
-      </c>
-      <c r="D11" t="s">
+      <c r="J11" t="s">
         <v>156</v>
       </c>
-      <c r="E11" t="s">
+      <c r="K11" t="s">
         <v>157</v>
       </c>
-      <c r="F11" t="s">
-        <v>79</v>
-      </c>
-      <c r="G11" t="s">
-        <v>61</v>
-      </c>
-      <c r="H11" t="s">
-        <v>62</v>
-      </c>
-      <c r="I11" t="s">
+      <c r="L11" t="s">
         <v>158</v>
       </c>
-      <c r="J11" t="s">
+      <c r="M11" t="s">
         <v>159</v>
       </c>
-      <c r="K11" t="s">
+      <c r="N11" t="s">
+        <v>65</v>
+      </c>
+      <c r="O11" t="s">
         <v>160</v>
       </c>
-      <c r="L11" t="s">
+      <c r="P11" t="s">
         <v>161</v>
       </c>
-      <c r="M11" t="s">
+      <c r="Q11" t="s">
+        <v>37</v>
+      </c>
+      <c r="R11" t="s">
         <v>162</v>
       </c>
-      <c r="N11" t="s">
-        <v>102</v>
-      </c>
-      <c r="O11" t="s">
+      <c r="S11" t="s">
         <v>163</v>
       </c>
-      <c r="P11" t="s">
+      <c r="T11" t="s">
         <v>164</v>
       </c>
-      <c r="Q11" t="s">
+      <c r="U11" t="s">
         <v>165</v>
       </c>
-      <c r="R11" t="s">
-        <v>166</v>
-      </c>
-      <c r="S11" t="s">
-        <v>167</v>
-      </c>
-      <c r="T11" t="s">
-        <v>168</v>
-      </c>
-      <c r="U11" t="s">
-        <v>41</v>
-      </c>
-      <c r="V11" t="s">
-        <v>41</v>
-      </c>
+      <c r="V11"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>20263916</v>
+        <v>20263936</v>
       </c>
       <c r="B12" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C12" t="s">
         <v>23</v>
       </c>
       <c r="D12" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="E12" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="F12" t="s">
         <v>26</v>
       </c>
       <c r="G12" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H12" t="s">
-        <v>28</v>
+        <v>168</v>
       </c>
       <c r="I12" t="s">
+        <v>169</v>
+      </c>
+      <c r="J12" t="s">
+        <v>170</v>
+      </c>
+      <c r="K12" t="s">
         <v>171</v>
       </c>
-      <c r="J12" t="s">
+      <c r="L12" t="s">
         <v>172</v>
       </c>
-      <c r="K12" t="s">
+      <c r="M12" t="s">
         <v>173</v>
       </c>
-      <c r="L12" t="s">
+      <c r="N12" t="s">
+        <v>65</v>
+      </c>
+      <c r="O12" t="s">
         <v>174</v>
       </c>
-      <c r="M12" t="s">
+      <c r="P12" t="s">
         <v>175</v>
       </c>
-      <c r="N12" t="s">
-        <v>102</v>
-      </c>
-      <c r="O12" t="s">
+      <c r="Q12" t="s">
         <v>176</v>
       </c>
-      <c r="P12" t="s">
+      <c r="R12" t="s">
         <v>177</v>
       </c>
-      <c r="Q12" t="s">
-        <v>71</v>
-      </c>
-      <c r="R12" t="s">
+      <c r="S12" t="s">
         <v>178</v>
       </c>
-      <c r="S12" t="s">
+      <c r="T12" t="s">
         <v>179</v>
       </c>
-      <c r="T12" t="s">
+      <c r="U12" t="s">
         <v>180</v>
       </c>
-      <c r="U12" t="s">
-        <v>41</v>
-      </c>
-      <c r="V12" t="s">
-        <v>41</v>
-      </c>
+      <c r="V12"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>20263601</v>
+        <v>20263949</v>
       </c>
       <c r="B13" t="s">
         <v>181</v>
@@ -6415,821 +6403,823 @@
         <v>23</v>
       </c>
       <c r="D13" t="s">
+        <v>167</v>
+      </c>
+      <c r="E13" t="s">
+        <v>58</v>
+      </c>
+      <c r="F13" t="s">
+        <v>26</v>
+      </c>
+      <c r="G13" t="s">
+        <v>59</v>
+      </c>
+      <c r="H13" t="s">
+        <v>168</v>
+      </c>
+      <c r="I13" t="s">
         <v>182</v>
       </c>
-      <c r="E13" t="s">
-        <v>25</v>
-      </c>
-      <c r="F13" t="s">
+      <c r="J13" t="s">
         <v>183</v>
       </c>
-      <c r="G13" t="s">
-        <v>27</v>
-      </c>
-      <c r="H13" t="s">
-        <v>28</v>
-      </c>
-      <c r="I13" t="s">
+      <c r="K13" t="s">
         <v>184</v>
       </c>
-      <c r="J13" t="s">
+      <c r="L13" t="s">
         <v>185</v>
       </c>
-      <c r="K13" t="s">
+      <c r="M13" t="s">
         <v>186</v>
       </c>
-      <c r="L13" t="s">
+      <c r="N13" t="s">
+        <v>65</v>
+      </c>
+      <c r="O13" t="s">
         <v>187</v>
       </c>
-      <c r="M13" t="s">
+      <c r="P13" t="s">
         <v>188</v>
       </c>
-      <c r="N13" t="s">
-        <v>34</v>
-      </c>
-      <c r="O13" t="s">
-        <v>189</v>
-      </c>
-      <c r="P13" t="s">
-        <v>190</v>
-      </c>
       <c r="Q13" t="s">
-        <v>37</v>
+        <v>176</v>
       </c>
       <c r="R13" t="s">
-        <v>191</v>
+        <v>177</v>
       </c>
       <c r="S13" t="s">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="T13" t="s">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="U13" t="s">
-        <v>194</v>
+        <v>180</v>
       </c>
       <c r="V13"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>20263563</v>
+        <v>20263601</v>
       </c>
       <c r="B14" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="C14" t="s">
         <v>23</v>
       </c>
       <c r="D14" t="s">
-        <v>77</v>
+        <v>190</v>
       </c>
       <c r="E14" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="F14" t="s">
-        <v>79</v>
+        <v>191</v>
       </c>
       <c r="G14" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H14" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="I14" t="s">
+        <v>192</v>
+      </c>
+      <c r="J14" t="s">
+        <v>193</v>
+      </c>
+      <c r="K14" t="s">
+        <v>194</v>
+      </c>
+      <c r="L14" t="s">
+        <v>195</v>
+      </c>
+      <c r="M14" t="s">
         <v>196</v>
       </c>
-      <c r="J14" t="s">
+      <c r="N14" t="s">
+        <v>65</v>
+      </c>
+      <c r="O14" t="s">
         <v>197</v>
       </c>
-      <c r="K14" t="s">
+      <c r="P14" t="s">
         <v>198</v>
       </c>
-      <c r="L14" t="s">
+      <c r="Q14" t="s">
+        <v>68</v>
+      </c>
+      <c r="R14" t="s">
         <v>199</v>
       </c>
-      <c r="M14" t="s">
+      <c r="S14" t="s">
         <v>200</v>
       </c>
-      <c r="N14" t="s">
-        <v>34</v>
-      </c>
-      <c r="O14" t="s">
+      <c r="T14" t="s">
         <v>201</v>
       </c>
-      <c r="P14" t="s">
+      <c r="U14" t="s">
         <v>202</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>71</v>
-      </c>
-      <c r="R14" t="s">
-        <v>203</v>
-      </c>
-      <c r="S14" t="s">
-        <v>204</v>
-      </c>
-      <c r="T14" t="s">
-        <v>205</v>
-      </c>
-      <c r="U14" t="s">
-        <v>194</v>
       </c>
       <c r="V14"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>20263411</v>
+        <v>20263563</v>
       </c>
       <c r="B15" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="C15" t="s">
-        <v>92</v>
+        <v>23</v>
       </c>
       <c r="D15" t="s">
-        <v>170</v>
+        <v>154</v>
       </c>
       <c r="E15" t="s">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="F15" t="s">
-        <v>207</v>
+        <v>103</v>
       </c>
       <c r="G15" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H15" t="s">
         <v>45</v>
       </c>
       <c r="I15" t="s">
+        <v>204</v>
+      </c>
+      <c r="J15" t="s">
+        <v>205</v>
+      </c>
+      <c r="K15" t="s">
+        <v>206</v>
+      </c>
+      <c r="L15" t="s">
+        <v>207</v>
+      </c>
+      <c r="M15" t="s">
         <v>208</v>
       </c>
-      <c r="J15" t="s">
+      <c r="N15" t="s">
+        <v>65</v>
+      </c>
+      <c r="O15" t="s">
         <v>209</v>
       </c>
-      <c r="K15" t="s">
+      <c r="P15" t="s">
         <v>210</v>
       </c>
-      <c r="L15" t="s">
+      <c r="Q15" t="s">
+        <v>37</v>
+      </c>
+      <c r="R15" t="s">
         <v>211</v>
       </c>
-      <c r="M15" t="s">
+      <c r="S15" t="s">
         <v>212</v>
       </c>
-      <c r="N15" t="s">
+      <c r="T15" t="s">
         <v>213</v>
       </c>
-      <c r="O15" t="s">
-        <v>214</v>
-      </c>
-      <c r="P15" t="s">
-        <v>215</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>71</v>
-      </c>
-      <c r="R15" t="s">
-        <v>216</v>
-      </c>
-      <c r="S15" t="s">
-        <v>217</v>
-      </c>
-      <c r="T15" t="s">
-        <v>218</v>
-      </c>
       <c r="U15" t="s">
-        <v>219</v>
+        <v>202</v>
       </c>
       <c r="V15"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>20263323</v>
+        <v>20263411</v>
       </c>
       <c r="B16" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="C16" t="s">
-        <v>23</v>
+        <v>87</v>
       </c>
       <c r="D16" t="s">
-        <v>120</v>
+        <v>43</v>
       </c>
       <c r="E16" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="F16" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="G16" t="s">
         <v>27</v>
       </c>
       <c r="H16" t="s">
-        <v>121</v>
+        <v>75</v>
       </c>
       <c r="I16" t="s">
+        <v>216</v>
+      </c>
+      <c r="J16" t="s">
+        <v>217</v>
+      </c>
+      <c r="K16" t="s">
+        <v>218</v>
+      </c>
+      <c r="L16" t="s">
+        <v>219</v>
+      </c>
+      <c r="M16" t="s">
+        <v>220</v>
+      </c>
+      <c r="N16" t="s">
+        <v>221</v>
+      </c>
+      <c r="O16" t="s">
         <v>222</v>
       </c>
-      <c r="J16" t="s">
+      <c r="P16" t="s">
         <v>223</v>
       </c>
-      <c r="K16" t="s">
+      <c r="Q16" t="s">
+        <v>37</v>
+      </c>
+      <c r="R16" t="s">
         <v>224</v>
       </c>
-      <c r="L16" t="s">
+      <c r="S16" t="s">
         <v>225</v>
       </c>
-      <c r="M16" t="s">
+      <c r="T16" t="s">
         <v>226</v>
       </c>
-      <c r="N16" t="s">
-        <v>68</v>
-      </c>
-      <c r="O16" t="s">
+      <c r="U16" t="s">
         <v>227</v>
-      </c>
-      <c r="P16" t="s">
-        <v>228</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>129</v>
-      </c>
-      <c r="R16" t="s">
-        <v>130</v>
-      </c>
-      <c r="S16" t="s">
-        <v>131</v>
-      </c>
-      <c r="T16" t="s">
-        <v>132</v>
-      </c>
-      <c r="U16" t="s">
-        <v>26</v>
       </c>
       <c r="V16"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>20263099</v>
+        <v>20263323</v>
       </c>
       <c r="B17" t="s">
+        <v>228</v>
+      </c>
+      <c r="C17" t="s">
+        <v>23</v>
+      </c>
+      <c r="D17" t="s">
+        <v>167</v>
+      </c>
+      <c r="E17" t="s">
+        <v>58</v>
+      </c>
+      <c r="F17" t="s">
         <v>229</v>
       </c>
-      <c r="C17" t="s">
-        <v>57</v>
-      </c>
-      <c r="D17" t="s">
-        <v>58</v>
-      </c>
-      <c r="E17" t="s">
+      <c r="G17" t="s">
         <v>59</v>
       </c>
-      <c r="F17" t="s">
+      <c r="H17" t="s">
+        <v>168</v>
+      </c>
+      <c r="I17" t="s">
         <v>230</v>
       </c>
-      <c r="G17" t="s">
-        <v>61</v>
-      </c>
-      <c r="H17" t="s">
-        <v>62</v>
-      </c>
-      <c r="I17" t="s">
+      <c r="J17" t="s">
         <v>231</v>
       </c>
-      <c r="J17" t="s">
+      <c r="K17" t="s">
         <v>232</v>
       </c>
-      <c r="K17" t="s">
+      <c r="L17" t="s">
         <v>233</v>
       </c>
-      <c r="L17" t="s">
+      <c r="M17" t="s">
         <v>234</v>
       </c>
-      <c r="M17" t="s">
+      <c r="N17" t="s">
+        <v>146</v>
+      </c>
+      <c r="O17" t="s">
         <v>235</v>
       </c>
-      <c r="N17" t="s">
+      <c r="P17" t="s">
         <v>236</v>
       </c>
-      <c r="O17" t="s">
-        <v>237</v>
-      </c>
-      <c r="P17" t="s">
-        <v>238</v>
-      </c>
       <c r="Q17" t="s">
-        <v>71</v>
+        <v>176</v>
       </c>
       <c r="R17" t="s">
-        <v>239</v>
+        <v>177</v>
       </c>
       <c r="S17" t="s">
-        <v>240</v>
+        <v>178</v>
       </c>
       <c r="T17" t="s">
-        <v>241</v>
+        <v>179</v>
       </c>
       <c r="U17" t="s">
-        <v>242</v>
+        <v>26</v>
       </c>
       <c r="V17"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>20267473</v>
+        <v>20263099</v>
       </c>
       <c r="B18" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="C18" t="s">
-        <v>244</v>
+        <v>139</v>
       </c>
       <c r="D18" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="E18" t="s">
-        <v>78</v>
+        <v>25</v>
       </c>
       <c r="F18" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="G18" t="s">
         <v>27</v>
       </c>
       <c r="H18" t="s">
-        <v>62</v>
+        <v>104</v>
       </c>
       <c r="I18" t="s">
+        <v>239</v>
+      </c>
+      <c r="J18" t="s">
+        <v>240</v>
+      </c>
+      <c r="K18" t="s">
+        <v>241</v>
+      </c>
+      <c r="L18" t="s">
+        <v>242</v>
+      </c>
+      <c r="M18" t="s">
+        <v>243</v>
+      </c>
+      <c r="N18" t="s">
+        <v>244</v>
+      </c>
+      <c r="O18" t="s">
+        <v>245</v>
+      </c>
+      <c r="P18" t="s">
         <v>246</v>
       </c>
-      <c r="J18" t="s">
+      <c r="Q18" t="s">
+        <v>37</v>
+      </c>
+      <c r="R18" t="s">
         <v>247</v>
       </c>
-      <c r="K18"/>
-      <c r="L18" t="s">
+      <c r="S18" t="s">
         <v>248</v>
       </c>
-      <c r="M18" t="s">
+      <c r="T18" t="s">
         <v>249</v>
       </c>
-      <c r="N18" t="s">
-        <v>34</v>
-      </c>
-      <c r="O18" t="s">
+      <c r="U18" t="s">
         <v>250</v>
-      </c>
-      <c r="P18" t="s">
-        <v>251</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>71</v>
-      </c>
-      <c r="R18" t="s">
-        <v>252</v>
-      </c>
-      <c r="S18" t="s">
-        <v>253</v>
-      </c>
-      <c r="T18" t="s">
-        <v>254</v>
-      </c>
-      <c r="U18" t="s">
-        <v>255</v>
       </c>
       <c r="V18"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>20267426</v>
+        <v>20267473</v>
       </c>
       <c r="B19" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="C19" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="D19" t="s">
-        <v>77</v>
+        <v>154</v>
       </c>
       <c r="E19" t="s">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="F19" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="G19" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H19" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="I19" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="J19" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="K19"/>
       <c r="L19" t="s">
+        <v>256</v>
+      </c>
+      <c r="M19" t="s">
+        <v>257</v>
+      </c>
+      <c r="N19" t="s">
+        <v>65</v>
+      </c>
+      <c r="O19" t="s">
+        <v>258</v>
+      </c>
+      <c r="P19" t="s">
+        <v>259</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>37</v>
+      </c>
+      <c r="R19" t="s">
         <v>260</v>
       </c>
-      <c r="M19" t="s">
+      <c r="S19" t="s">
         <v>261</v>
       </c>
-      <c r="N19" t="s">
-        <v>68</v>
-      </c>
-      <c r="O19" t="s">
+      <c r="T19" t="s">
         <v>262</v>
       </c>
-      <c r="P19" t="s">
+      <c r="U19" t="s">
         <v>263</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>71</v>
-      </c>
-      <c r="R19" t="s">
-        <v>264</v>
-      </c>
-      <c r="S19" t="s">
-        <v>265</v>
-      </c>
-      <c r="T19" t="s">
-        <v>266</v>
-      </c>
-      <c r="U19" t="s">
-        <v>245</v>
       </c>
       <c r="V19"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>20267446</v>
+        <v>20267426</v>
       </c>
       <c r="B20" t="s">
+        <v>264</v>
+      </c>
+      <c r="C20" t="s">
+        <v>252</v>
+      </c>
+      <c r="D20" t="s">
+        <v>154</v>
+      </c>
+      <c r="E20" t="s">
+        <v>44</v>
+      </c>
+      <c r="F20" t="s">
+        <v>265</v>
+      </c>
+      <c r="G20" t="s">
+        <v>59</v>
+      </c>
+      <c r="H20" t="s">
+        <v>168</v>
+      </c>
+      <c r="I20" t="s">
+        <v>266</v>
+      </c>
+      <c r="J20" t="s">
         <v>267</v>
-      </c>
-      <c r="C20" t="s">
-        <v>244</v>
-      </c>
-      <c r="D20" t="s">
-        <v>268</v>
-      </c>
-      <c r="E20" t="s">
-        <v>157</v>
-      </c>
-      <c r="F20" t="s">
-        <v>257</v>
-      </c>
-      <c r="G20" t="s">
-        <v>27</v>
-      </c>
-      <c r="H20" t="s">
-        <v>121</v>
-      </c>
-      <c r="I20" t="s">
-        <v>269</v>
-      </c>
-      <c r="J20" t="s">
-        <v>270</v>
       </c>
       <c r="K20"/>
       <c r="L20" t="s">
+        <v>268</v>
+      </c>
+      <c r="M20" t="s">
+        <v>269</v>
+      </c>
+      <c r="N20" t="s">
+        <v>146</v>
+      </c>
+      <c r="O20" t="s">
+        <v>270</v>
+      </c>
+      <c r="P20" t="s">
         <v>271</v>
       </c>
-      <c r="M20" t="s">
+      <c r="Q20" t="s">
+        <v>37</v>
+      </c>
+      <c r="R20" t="s">
         <v>272</v>
       </c>
-      <c r="N20" t="s">
-        <v>68</v>
-      </c>
-      <c r="O20" t="s">
+      <c r="S20" t="s">
         <v>273</v>
       </c>
-      <c r="P20" t="s">
+      <c r="T20" t="s">
         <v>274</v>
       </c>
-      <c r="Q20" t="s">
-        <v>71</v>
-      </c>
-      <c r="R20" t="s">
-        <v>275</v>
-      </c>
-      <c r="S20" t="s">
-        <v>276</v>
-      </c>
-      <c r="T20" t="s">
-        <v>277</v>
-      </c>
       <c r="U20" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="V20"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>20254531</v>
+        <v>20267446</v>
       </c>
       <c r="B21" t="s">
+        <v>275</v>
+      </c>
+      <c r="C21" t="s">
+        <v>252</v>
+      </c>
+      <c r="D21" t="s">
+        <v>276</v>
+      </c>
+      <c r="E21" t="s">
+        <v>102</v>
+      </c>
+      <c r="F21" t="s">
+        <v>265</v>
+      </c>
+      <c r="G21" t="s">
+        <v>59</v>
+      </c>
+      <c r="H21" t="s">
+        <v>168</v>
+      </c>
+      <c r="I21" t="s">
+        <v>277</v>
+      </c>
+      <c r="J21" t="s">
         <v>278</v>
       </c>
-      <c r="C21" t="s">
-        <v>23</v>
-      </c>
-      <c r="D21" t="s">
+      <c r="K21"/>
+      <c r="L21" t="s">
         <v>279</v>
       </c>
-      <c r="E21" t="s">
-        <v>78</v>
-      </c>
-      <c r="F21" t="s">
+      <c r="M21" t="s">
         <v>280</v>
       </c>
-      <c r="G21" t="s">
-        <v>27</v>
-      </c>
-      <c r="H21" t="s">
-        <v>45</v>
-      </c>
-      <c r="I21" t="s">
+      <c r="N21" t="s">
+        <v>146</v>
+      </c>
+      <c r="O21" t="s">
         <v>281</v>
       </c>
-      <c r="J21" t="s">
+      <c r="P21" t="s">
         <v>282</v>
       </c>
-      <c r="K21" t="s">
+      <c r="Q21" t="s">
+        <v>37</v>
+      </c>
+      <c r="R21" t="s">
         <v>283</v>
       </c>
-      <c r="L21" t="s">
+      <c r="S21" t="s">
         <v>284</v>
       </c>
-      <c r="M21" t="s">
+      <c r="T21" t="s">
         <v>285</v>
       </c>
-      <c r="N21" t="s">
-        <v>68</v>
-      </c>
-      <c r="O21" t="s">
-        <v>286</v>
-      </c>
-      <c r="P21" t="s">
-        <v>287</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>71</v>
-      </c>
-      <c r="R21" t="s">
-        <v>288</v>
-      </c>
-      <c r="S21" t="s">
-        <v>289</v>
-      </c>
-      <c r="T21" t="s">
-        <v>290</v>
-      </c>
       <c r="U21" t="s">
-        <v>291</v>
+        <v>253</v>
       </c>
       <c r="V21"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>20263121</v>
+        <v>20254531</v>
       </c>
       <c r="B22" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="C22" t="s">
         <v>23</v>
       </c>
       <c r="D22" t="s">
-        <v>58</v>
+        <v>287</v>
       </c>
       <c r="E22" t="s">
+        <v>44</v>
+      </c>
+      <c r="F22" t="s">
+        <v>288</v>
+      </c>
+      <c r="G22" t="s">
         <v>59</v>
       </c>
-      <c r="F22" t="s">
+      <c r="H22" t="s">
+        <v>75</v>
+      </c>
+      <c r="I22" t="s">
+        <v>289</v>
+      </c>
+      <c r="J22" t="s">
+        <v>290</v>
+      </c>
+      <c r="K22" t="s">
+        <v>291</v>
+      </c>
+      <c r="L22" t="s">
+        <v>292</v>
+      </c>
+      <c r="M22" t="s">
         <v>293</v>
       </c>
-      <c r="G22" t="s">
-        <v>61</v>
-      </c>
-      <c r="H22" t="s">
-        <v>28</v>
-      </c>
-      <c r="I22" t="s">
+      <c r="N22" t="s">
+        <v>146</v>
+      </c>
+      <c r="O22" t="s">
         <v>294</v>
       </c>
-      <c r="J22" t="s">
+      <c r="P22" t="s">
         <v>295</v>
       </c>
-      <c r="K22" t="s">
+      <c r="Q22" t="s">
+        <v>37</v>
+      </c>
+      <c r="R22" t="s">
         <v>296</v>
       </c>
-      <c r="L22" t="s">
+      <c r="S22" t="s">
         <v>297</v>
       </c>
-      <c r="M22" t="s">
+      <c r="T22" t="s">
         <v>298</v>
       </c>
-      <c r="N22" t="s">
-        <v>68</v>
-      </c>
-      <c r="O22" t="s">
+      <c r="U22" t="s">
         <v>299</v>
-      </c>
-      <c r="P22" t="s">
-        <v>300</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>71</v>
-      </c>
-      <c r="R22" t="s">
-        <v>301</v>
-      </c>
-      <c r="S22" t="s">
-        <v>302</v>
-      </c>
-      <c r="T22" t="s">
-        <v>303</v>
-      </c>
-      <c r="U22" t="s">
-        <v>257</v>
       </c>
       <c r="V22"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>20263497</v>
+        <v>20263121</v>
       </c>
       <c r="B23" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="C23" t="s">
-        <v>92</v>
+        <v>23</v>
       </c>
       <c r="D23" t="s">
-        <v>305</v>
+        <v>24</v>
       </c>
       <c r="E23" t="s">
         <v>25</v>
       </c>
       <c r="F23" t="s">
-        <v>207</v>
+        <v>132</v>
       </c>
       <c r="G23" t="s">
         <v>27</v>
       </c>
       <c r="H23" t="s">
-        <v>121</v>
+        <v>45</v>
       </c>
       <c r="I23" t="s">
+        <v>301</v>
+      </c>
+      <c r="J23" t="s">
+        <v>302</v>
+      </c>
+      <c r="K23" t="s">
+        <v>303</v>
+      </c>
+      <c r="L23" t="s">
+        <v>304</v>
+      </c>
+      <c r="M23" t="s">
+        <v>305</v>
+      </c>
+      <c r="N23" t="s">
+        <v>146</v>
+      </c>
+      <c r="O23" t="s">
         <v>306</v>
       </c>
-      <c r="J23" t="s">
+      <c r="P23" t="s">
         <v>307</v>
-      </c>
-      <c r="K23" t="s">
-        <v>308</v>
-      </c>
-      <c r="L23" t="s">
-        <v>309</v>
-      </c>
-      <c r="M23" t="s">
-        <v>310</v>
-      </c>
-      <c r="N23" t="s">
-        <v>34</v>
-      </c>
-      <c r="O23" t="s">
-        <v>311</v>
-      </c>
-      <c r="P23" t="s">
-        <v>312</v>
       </c>
       <c r="Q23" t="s">
         <v>37</v>
       </c>
       <c r="R23" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="S23" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="T23" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="U23" t="s">
-        <v>316</v>
+        <v>265</v>
       </c>
       <c r="V23"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>20263228</v>
+        <v>20263497</v>
       </c>
       <c r="B24" t="s">
+        <v>311</v>
+      </c>
+      <c r="C24" t="s">
+        <v>87</v>
+      </c>
+      <c r="D24" t="s">
+        <v>312</v>
+      </c>
+      <c r="E24" t="s">
+        <v>58</v>
+      </c>
+      <c r="F24" t="s">
+        <v>215</v>
+      </c>
+      <c r="G24" t="s">
+        <v>59</v>
+      </c>
+      <c r="H24" t="s">
+        <v>168</v>
+      </c>
+      <c r="I24" t="s">
+        <v>313</v>
+      </c>
+      <c r="J24" t="s">
+        <v>314</v>
+      </c>
+      <c r="K24" t="s">
+        <v>315</v>
+      </c>
+      <c r="L24" t="s">
+        <v>316</v>
+      </c>
+      <c r="M24" t="s">
         <v>317</v>
       </c>
-      <c r="C24" t="s">
-        <v>23</v>
-      </c>
-      <c r="D24" t="s">
+      <c r="N24" t="s">
+        <v>65</v>
+      </c>
+      <c r="O24" t="s">
         <v>318</v>
       </c>
-      <c r="E24" t="s">
-        <v>78</v>
-      </c>
-      <c r="F24" t="s">
-        <v>221</v>
-      </c>
-      <c r="G24" t="s">
-        <v>27</v>
-      </c>
-      <c r="H24" t="s">
-        <v>28</v>
-      </c>
-      <c r="I24" t="s">
+      <c r="P24" t="s">
         <v>319</v>
       </c>
-      <c r="J24" t="s">
+      <c r="Q24" t="s">
+        <v>68</v>
+      </c>
+      <c r="R24" t="s">
         <v>320</v>
       </c>
-      <c r="K24" t="s">
+      <c r="S24" t="s">
         <v>321</v>
       </c>
-      <c r="L24" t="s">
+      <c r="T24" t="s">
         <v>322</v>
       </c>
-      <c r="M24" t="s">
+      <c r="U24" t="s">
         <v>323</v>
-      </c>
-      <c r="N24" t="s">
-        <v>34</v>
-      </c>
-      <c r="O24" t="s">
-        <v>324</v>
-      </c>
-      <c r="P24" t="s">
-        <v>325</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>129</v>
-      </c>
-      <c r="R24" t="s">
-        <v>301</v>
-      </c>
-      <c r="S24" t="s">
-        <v>302</v>
-      </c>
-      <c r="T24" t="s">
-        <v>303</v>
-      </c>
-      <c r="U24" t="s">
-        <v>316</v>
       </c>
       <c r="V24"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>20263131</v>
+        <v>20263228</v>
       </c>
       <c r="B25" t="s">
+        <v>324</v>
+      </c>
+      <c r="C25" t="s">
+        <v>23</v>
+      </c>
+      <c r="D25" t="s">
+        <v>325</v>
+      </c>
+      <c r="E25" t="s">
+        <v>44</v>
+      </c>
+      <c r="F25" t="s">
+        <v>229</v>
+      </c>
+      <c r="G25" t="s">
+        <v>59</v>
+      </c>
+      <c r="H25" t="s">
+        <v>45</v>
+      </c>
+      <c r="I25" t="s">
         <v>326</v>
       </c>
-      <c r="C25" t="s">
-        <v>92</v>
-      </c>
-      <c r="D25" t="s">
+      <c r="J25" t="s">
         <v>327</v>
       </c>
-      <c r="E25"/>
-      <c r="F25" t="s">
-        <v>293</v>
-      </c>
-      <c r="G25" t="s">
-        <v>27</v>
-      </c>
-      <c r="H25" t="s">
-        <v>62</v>
-      </c>
-      <c r="I25" t="s">
-        <v>158</v>
-      </c>
-      <c r="J25" t="s">
+      <c r="K25" t="s">
         <v>328</v>
-      </c>
-      <c r="K25" t="s">
-        <v>160</v>
       </c>
       <c r="L25" t="s">
         <v>329</v>
       </c>
       <c r="M25" t="s">
-        <v>162</v>
+        <v>330</v>
       </c>
       <c r="N25" t="s">
-        <v>330</v>
+        <v>65</v>
       </c>
       <c r="O25" t="s">
         <v>331</v>
@@ -7238,23 +7228,21 @@
         <v>332</v>
       </c>
       <c r="Q25" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="R25" t="s">
-        <v>166</v>
+        <v>308</v>
       </c>
       <c r="S25" t="s">
-        <v>167</v>
+        <v>309</v>
       </c>
       <c r="T25" t="s">
-        <v>168</v>
+        <v>310</v>
       </c>
       <c r="U25" t="s">
-        <v>41</v>
-      </c>
-      <c r="V25" t="s">
-        <v>41</v>
-      </c>
+        <v>323</v>
+      </c>
+      <c r="V25"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -7264,20 +7252,20 @@
         <v>333</v>
       </c>
       <c r="C26" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D26" t="s">
         <v>334</v>
       </c>
       <c r="E26"/>
       <c r="F26" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="G26" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H26" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="I26" t="s">
         <v>335</v>
@@ -7295,7 +7283,7 @@
         <v>339</v>
       </c>
       <c r="N26" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="O26" t="s">
         <v>340</v>
@@ -7304,7 +7292,7 @@
         <v>341</v>
       </c>
       <c r="Q26" t="s">
-        <v>129</v>
+        <v>176</v>
       </c>
       <c r="R26" t="s">
         <v>342</v>
@@ -7331,19 +7319,19 @@
         <v>23</v>
       </c>
       <c r="D27" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E27" t="s">
-        <v>157</v>
+        <v>102</v>
       </c>
       <c r="F27" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="G27" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H27" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="I27" t="s">
         <v>347</v>
@@ -7361,7 +7349,7 @@
         <v>351</v>
       </c>
       <c r="N27" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="O27" t="s">
         <v>352</v>
@@ -7370,7 +7358,7 @@
         <v>353</v>
       </c>
       <c r="Q27" t="s">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="R27" t="s">
         <v>354</v>
@@ -7400,13 +7388,13 @@
         <v>358</v>
       </c>
       <c r="E28" t="s">
-        <v>157</v>
+        <v>102</v>
       </c>
       <c r="F28" t="s">
         <v>359</v>
       </c>
       <c r="G28" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H28" t="s">
         <v>360</v>
@@ -7427,7 +7415,7 @@
         <v>365</v>
       </c>
       <c r="N28" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="O28" t="s">
         <v>366</v>
@@ -7436,7 +7424,7 @@
         <v>367</v>
       </c>
       <c r="Q28" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="R28" t="s">
         <v>368</v>
@@ -7460,22 +7448,22 @@
         <v>371</v>
       </c>
       <c r="C29" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D29" t="s">
         <v>372</v>
       </c>
       <c r="E29" t="s">
-        <v>157</v>
+        <v>102</v>
       </c>
       <c r="F29" t="s">
-        <v>293</v>
+        <v>132</v>
       </c>
       <c r="G29" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H29" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="I29" t="s">
         <v>373</v>
@@ -7493,7 +7481,7 @@
         <v>377</v>
       </c>
       <c r="N29" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="O29" t="s">
         <v>378</v>
@@ -7502,7 +7490,7 @@
         <v>379</v>
       </c>
       <c r="Q29" t="s">
-        <v>165</v>
+        <v>112</v>
       </c>
       <c r="R29" t="s">
         <v>380</v>
@@ -7532,16 +7520,16 @@
         <v>385</v>
       </c>
       <c r="E30" t="s">
-        <v>157</v>
+        <v>102</v>
       </c>
       <c r="F30" t="s">
         <v>386</v>
       </c>
       <c r="G30" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H30" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="I30" t="s">
         <v>387</v>
@@ -7559,7 +7547,7 @@
         <v>391</v>
       </c>
       <c r="N30" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="O30" t="s">
         <v>392</v>
@@ -7568,7 +7556,7 @@
         <v>393</v>
       </c>
       <c r="Q30" t="s">
-        <v>129</v>
+        <v>176</v>
       </c>
       <c r="R30" t="s">
         <v>354</v>
@@ -7592,22 +7580,22 @@
         <v>394</v>
       </c>
       <c r="C31" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D31" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="E31" t="s">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="F31" t="s">
         <v>395</v>
       </c>
       <c r="G31" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="H31" t="s">
-        <v>62</v>
+        <v>104</v>
       </c>
       <c r="I31" t="s">
         <v>396</v>
@@ -7634,7 +7622,7 @@
         <v>403</v>
       </c>
       <c r="Q31" t="s">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="R31" t="s">
         <v>404</v>
@@ -7658,22 +7646,22 @@
         <v>408</v>
       </c>
       <c r="C32" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="D32" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="E32" t="s">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="F32" t="s">
         <v>409</v>
       </c>
       <c r="G32" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H32" t="s">
-        <v>121</v>
+        <v>168</v>
       </c>
       <c r="I32" t="s">
         <v>410</v>
@@ -7689,7 +7677,7 @@
         <v>413</v>
       </c>
       <c r="N32" t="s">
-        <v>68</v>
+        <v>146</v>
       </c>
       <c r="O32" t="s">
         <v>414</v>
@@ -7698,7 +7686,7 @@
         <v>415</v>
       </c>
       <c r="Q32" t="s">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="R32" t="s">
         <v>416</v>
@@ -7722,7 +7710,7 @@
         <v>420</v>
       </c>
       <c r="C33" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="D33" t="s">
         <v>421</v>
@@ -7734,10 +7722,10 @@
         <v>386</v>
       </c>
       <c r="G33" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H33" t="s">
-        <v>62</v>
+        <v>104</v>
       </c>
       <c r="I33" t="s">
         <v>423</v>
@@ -7753,7 +7741,7 @@
         <v>426</v>
       </c>
       <c r="N33" t="s">
-        <v>68</v>
+        <v>146</v>
       </c>
       <c r="O33" t="s">
         <v>427</v>
@@ -7762,7 +7750,7 @@
         <v>428</v>
       </c>
       <c r="Q33" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="R33" t="s">
         <v>429</v>
@@ -7790,14 +7778,14 @@
       </c>
       <c r="D34"/>
       <c r="E34" t="s">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="F34" t="s">
         <v>434</v>
       </c>
       <c r="G34"/>
       <c r="H34" t="s">
-        <v>62</v>
+        <v>104</v>
       </c>
       <c r="I34" t="s">
         <v>435</v>
@@ -7811,7 +7799,7 @@
       <c r="L34"/>
       <c r="M34"/>
       <c r="N34" t="s">
-        <v>68</v>
+        <v>146</v>
       </c>
       <c r="O34" t="s">
         <v>438</v>
@@ -7820,7 +7808,7 @@
         <v>439</v>
       </c>
       <c r="Q34" t="s">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="R34" t="s">
         <v>368</v>
@@ -7844,22 +7832,22 @@
         <v>440</v>
       </c>
       <c r="C35" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="D35" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="E35" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="F35" t="s">
         <v>441</v>
       </c>
       <c r="G35" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H35" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="I35" t="s">
         <v>442</v>
@@ -7875,7 +7863,7 @@
         <v>445</v>
       </c>
       <c r="N35" t="s">
-        <v>68</v>
+        <v>146</v>
       </c>
       <c r="O35" t="s">
         <v>446</v>
@@ -7884,7 +7872,7 @@
         <v>447</v>
       </c>
       <c r="Q35" t="s">
-        <v>165</v>
+        <v>112</v>
       </c>
       <c r="R35" t="s">
         <v>448</v>
@@ -7908,22 +7896,22 @@
         <v>451</v>
       </c>
       <c r="C36" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D36" t="s">
         <v>452</v>
       </c>
       <c r="E36" t="s">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="F36" t="s">
         <v>453</v>
       </c>
       <c r="G36" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H36" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="I36" t="s">
         <v>454</v>
@@ -7941,7 +7929,7 @@
         <v>458</v>
       </c>
       <c r="N36" t="s">
-        <v>68</v>
+        <v>146</v>
       </c>
       <c r="O36" t="s">
         <v>459</v>
@@ -7950,16 +7938,16 @@
         <v>460</v>
       </c>
       <c r="Q36" t="s">
-        <v>165</v>
+        <v>112</v>
       </c>
       <c r="R36" t="s">
-        <v>116</v>
+        <v>38</v>
       </c>
       <c r="S36" t="s">
-        <v>117</v>
+        <v>39</v>
       </c>
       <c r="T36" t="s">
-        <v>118</v>
+        <v>40</v>
       </c>
       <c r="U36" t="s">
         <v>419</v>
@@ -7986,10 +7974,10 @@
         <v>395</v>
       </c>
       <c r="G37" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H37" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="I37" t="s">
         <v>464</v>
@@ -8007,7 +7995,7 @@
         <v>468</v>
       </c>
       <c r="N37" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="O37" t="s">
         <v>469</v>
@@ -8016,7 +8004,7 @@
         <v>470</v>
       </c>
       <c r="Q37" t="s">
-        <v>129</v>
+        <v>176</v>
       </c>
       <c r="R37" t="s">
         <v>471</v>
@@ -8046,16 +8034,16 @@
         <v>475</v>
       </c>
       <c r="E38" t="s">
-        <v>157</v>
+        <v>102</v>
       </c>
       <c r="F38" t="s">
         <v>395</v>
       </c>
       <c r="G38" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H38" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="I38" t="s">
         <v>476</v>
@@ -8073,7 +8061,7 @@
         <v>480</v>
       </c>
       <c r="N38" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="O38" t="s">
         <v>481</v>
@@ -8082,7 +8070,7 @@
         <v>482</v>
       </c>
       <c r="Q38" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="R38" t="s">
         <v>483</v>
@@ -8106,22 +8094,22 @@
         <v>486</v>
       </c>
       <c r="C39" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D39" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="E39" t="s">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="F39" t="s">
         <v>487</v>
       </c>
       <c r="G39" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="H39" t="s">
-        <v>144</v>
+        <v>89</v>
       </c>
       <c r="I39" t="s">
         <v>488</v>
@@ -8139,7 +8127,7 @@
         <v>492</v>
       </c>
       <c r="N39" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="O39" t="s">
         <v>493</v>
@@ -8148,7 +8136,7 @@
         <v>494</v>
       </c>
       <c r="Q39" t="s">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="R39" t="s">
         <v>495</v>
@@ -8172,22 +8160,22 @@
         <v>498</v>
       </c>
       <c r="C40" t="s">
-        <v>57</v>
+        <v>139</v>
       </c>
       <c r="D40" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="E40" t="s">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="F40" t="s">
         <v>487</v>
       </c>
       <c r="G40" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="H40" t="s">
-        <v>62</v>
+        <v>104</v>
       </c>
       <c r="I40" t="s">
         <v>499</v>
@@ -8205,7 +8193,7 @@
         <v>503</v>
       </c>
       <c r="N40" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="O40" t="s">
         <v>504</v>
@@ -8214,7 +8202,7 @@
         <v>505</v>
       </c>
       <c r="Q40" t="s">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="R40" t="s">
         <v>506</v>
@@ -8244,16 +8232,16 @@
         <v>510</v>
       </c>
       <c r="E41" t="s">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="F41" t="s">
         <v>511</v>
       </c>
       <c r="G41" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="H41" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="I41" t="s">
         <v>512</v>
@@ -8271,7 +8259,7 @@
         <v>516</v>
       </c>
       <c r="N41" t="s">
-        <v>68</v>
+        <v>146</v>
       </c>
       <c r="O41" t="s">
         <v>517</v>
@@ -8280,7 +8268,7 @@
         <v>518</v>
       </c>
       <c r="Q41" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="R41" t="s">
         <v>519</v>
@@ -8304,22 +8292,22 @@
         <v>522</v>
       </c>
       <c r="C42" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D42" t="s">
         <v>372</v>
       </c>
       <c r="E42" t="s">
-        <v>157</v>
+        <v>102</v>
       </c>
       <c r="F42" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="G42" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H42" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="I42" t="s">
         <v>523</v>
@@ -8337,7 +8325,7 @@
         <v>527</v>
       </c>
       <c r="N42" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="O42" t="s">
         <v>528</v>
@@ -8346,16 +8334,16 @@
         <v>529</v>
       </c>
       <c r="Q42" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="R42" t="s">
-        <v>116</v>
+        <v>38</v>
       </c>
       <c r="S42" t="s">
-        <v>117</v>
+        <v>39</v>
       </c>
       <c r="T42" t="s">
-        <v>118</v>
+        <v>40</v>
       </c>
       <c r="U42" t="s">
         <v>419</v>
@@ -8370,22 +8358,22 @@
         <v>530</v>
       </c>
       <c r="C43" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="D43" t="s">
         <v>531</v>
       </c>
       <c r="E43" t="s">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="F43" t="s">
         <v>532</v>
       </c>
       <c r="G43" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H43" t="s">
-        <v>144</v>
+        <v>89</v>
       </c>
       <c r="I43" t="s">
         <v>533</v>
@@ -8401,7 +8389,7 @@
         <v>536</v>
       </c>
       <c r="N43" t="s">
-        <v>68</v>
+        <v>146</v>
       </c>
       <c r="O43" t="s">
         <v>537</v>
@@ -8410,7 +8398,7 @@
         <v>538</v>
       </c>
       <c r="Q43" t="s">
-        <v>165</v>
+        <v>112</v>
       </c>
       <c r="R43" t="s">
         <v>539</v>
@@ -8434,22 +8422,22 @@
         <v>542</v>
       </c>
       <c r="C44" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="D44" t="s">
         <v>358</v>
       </c>
       <c r="E44" t="s">
-        <v>157</v>
+        <v>102</v>
       </c>
       <c r="F44" t="s">
         <v>532</v>
       </c>
       <c r="G44" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H44" t="s">
-        <v>62</v>
+        <v>104</v>
       </c>
       <c r="I44" t="s">
         <v>543</v>
@@ -8465,7 +8453,7 @@
         <v>546</v>
       </c>
       <c r="N44" t="s">
-        <v>68</v>
+        <v>146</v>
       </c>
       <c r="O44" t="s">
         <v>547</v>
@@ -8474,16 +8462,16 @@
         <v>548</v>
       </c>
       <c r="Q44" t="s">
-        <v>165</v>
+        <v>112</v>
       </c>
       <c r="R44" t="s">
-        <v>166</v>
+        <v>113</v>
       </c>
       <c r="S44" t="s">
-        <v>167</v>
+        <v>114</v>
       </c>
       <c r="T44" t="s">
-        <v>168</v>
+        <v>115</v>
       </c>
       <c r="U44" t="s">
         <v>419</v>
@@ -8498,7 +8486,7 @@
         <v>549</v>
       </c>
       <c r="C45" t="s">
-        <v>57</v>
+        <v>139</v>
       </c>
       <c r="D45" t="s">
         <v>550</v>
@@ -8508,10 +8496,10 @@
         <v>551</v>
       </c>
       <c r="G45" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H45" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="I45" t="s">
         <v>552</v>
@@ -8529,7 +8517,7 @@
         <v>556</v>
       </c>
       <c r="N45" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="O45" t="s">
         <v>557</v>
@@ -8538,7 +8526,7 @@
         <v>558</v>
       </c>
       <c r="Q45" t="s">
-        <v>165</v>
+        <v>112</v>
       </c>
       <c r="R45" t="s">
         <v>559</v>
@@ -8562,22 +8550,22 @@
         <v>562</v>
       </c>
       <c r="C46" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D46" t="s">
         <v>563</v>
       </c>
       <c r="E46" t="s">
-        <v>157</v>
+        <v>102</v>
       </c>
       <c r="F46" t="s">
         <v>564</v>
       </c>
       <c r="G46" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="H46" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="I46" t="s">
         <v>565</v>
@@ -8595,7 +8583,7 @@
         <v>569</v>
       </c>
       <c r="N46" t="s">
-        <v>68</v>
+        <v>146</v>
       </c>
       <c r="O46" t="s">
         <v>570</v>
@@ -8604,7 +8592,7 @@
         <v>571</v>
       </c>
       <c r="Q46" t="s">
-        <v>165</v>
+        <v>112</v>
       </c>
       <c r="R46" t="s">
         <v>572</v>
@@ -8628,22 +8616,22 @@
         <v>575</v>
       </c>
       <c r="C47" t="s">
-        <v>57</v>
+        <v>139</v>
       </c>
       <c r="D47" t="s">
         <v>576</v>
       </c>
       <c r="E47" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="F47" t="s">
         <v>564</v>
       </c>
       <c r="G47" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H47" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="I47" t="s">
         <v>577</v>
@@ -8661,7 +8649,7 @@
         <v>581</v>
       </c>
       <c r="N47" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="O47" t="s">
         <v>582</v>
@@ -8670,7 +8658,7 @@
         <v>583</v>
       </c>
       <c r="Q47" t="s">
-        <v>165</v>
+        <v>112</v>
       </c>
       <c r="R47" t="s">
         <v>368</v>
@@ -8697,19 +8685,19 @@
         <v>23</v>
       </c>
       <c r="D48" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="E48" t="s">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="F48" t="s">
         <v>564</v>
       </c>
       <c r="G48" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H48" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="I48" t="s">
         <v>585</v>
@@ -8727,7 +8715,7 @@
         <v>589</v>
       </c>
       <c r="N48" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="O48" t="s">
         <v>590</v>
@@ -8736,7 +8724,7 @@
         <v>591</v>
       </c>
       <c r="Q48" t="s">
-        <v>129</v>
+        <v>176</v>
       </c>
       <c r="R48" t="s">
         <v>354</v>
@@ -8760,22 +8748,22 @@
         <v>592</v>
       </c>
       <c r="C49" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D49" t="s">
-        <v>170</v>
+        <v>43</v>
       </c>
       <c r="E49" t="s">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="F49" t="s">
         <v>564</v>
       </c>
       <c r="G49" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="H49" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="I49" t="s">
         <v>593</v>
@@ -8793,7 +8781,7 @@
         <v>597</v>
       </c>
       <c r="N49" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="O49" t="s">
         <v>598</v>
@@ -8802,7 +8790,7 @@
         <v>599</v>
       </c>
       <c r="Q49" t="s">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="R49" t="s">
         <v>600</v>
@@ -8832,16 +8820,16 @@
         <v>604</v>
       </c>
       <c r="E50" t="s">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="F50" t="s">
         <v>605</v>
       </c>
       <c r="G50" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H50" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="I50" t="s">
         <v>606</v>
@@ -8859,7 +8847,7 @@
         <v>610</v>
       </c>
       <c r="N50" t="s">
-        <v>68</v>
+        <v>146</v>
       </c>
       <c r="O50" t="s">
         <v>611</v>
@@ -8868,7 +8856,7 @@
         <v>612</v>
       </c>
       <c r="Q50" t="s">
-        <v>129</v>
+        <v>176</v>
       </c>
       <c r="R50" t="s">
         <v>471</v>
@@ -8895,19 +8883,19 @@
         <v>23</v>
       </c>
       <c r="D51" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="E51" t="s">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="F51" t="s">
         <v>614</v>
       </c>
       <c r="G51" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="H51" t="s">
-        <v>121</v>
+        <v>168</v>
       </c>
       <c r="I51" t="s">
         <v>615</v>
@@ -8925,7 +8913,7 @@
         <v>619</v>
       </c>
       <c r="N51" t="s">
-        <v>68</v>
+        <v>146</v>
       </c>
       <c r="O51" t="s">
         <v>620</v>
@@ -8934,7 +8922,7 @@
         <v>621</v>
       </c>
       <c r="Q51" t="s">
-        <v>129</v>
+        <v>176</v>
       </c>
       <c r="R51" t="s">
         <v>622</v>
@@ -8964,16 +8952,16 @@
         <v>626</v>
       </c>
       <c r="E52" t="s">
-        <v>157</v>
+        <v>102</v>
       </c>
       <c r="F52" t="s">
         <v>614</v>
       </c>
       <c r="G52" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H52" t="s">
-        <v>144</v>
+        <v>89</v>
       </c>
       <c r="I52" t="s">
         <v>627</v>
@@ -8991,7 +8979,7 @@
         <v>631</v>
       </c>
       <c r="N52" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="O52" t="s">
         <v>632</v>
@@ -9000,7 +8988,7 @@
         <v>633</v>
       </c>
       <c r="Q52" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="R52" t="s">
         <v>634</v>
@@ -9030,16 +9018,16 @@
         <v>638</v>
       </c>
       <c r="E53" t="s">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="F53" t="s">
         <v>639</v>
       </c>
       <c r="G53" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="H53" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="I53" t="s">
         <v>640</v>
@@ -9057,7 +9045,7 @@
         <v>644</v>
       </c>
       <c r="N53" t="s">
-        <v>68</v>
+        <v>146</v>
       </c>
       <c r="O53" t="s">
         <v>645</v>
@@ -9066,7 +9054,7 @@
         <v>646</v>
       </c>
       <c r="Q53" t="s">
-        <v>129</v>
+        <v>176</v>
       </c>
       <c r="R53" t="s">
         <v>647</v>
@@ -9093,19 +9081,19 @@
         <v>651</v>
       </c>
       <c r="D54" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E54" t="s">
-        <v>157</v>
+        <v>102</v>
       </c>
       <c r="F54" t="s">
         <v>652</v>
       </c>
       <c r="G54" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H54" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="I54" t="s">
         <v>653</v>
@@ -9132,7 +9120,7 @@
         <v>660</v>
       </c>
       <c r="Q54" t="s">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="R54" t="s">
         <v>661</v>
@@ -9156,7 +9144,7 @@
         <v>664</v>
       </c>
       <c r="C55" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D55" t="s">
         <v>665</v>
@@ -9168,10 +9156,10 @@
         <v>666</v>
       </c>
       <c r="G55" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H55" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="I55" t="s">
         <v>667</v>
@@ -9189,7 +9177,7 @@
         <v>671</v>
       </c>
       <c r="N55" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="O55" t="s">
         <v>672</v>
@@ -9198,7 +9186,7 @@
         <v>673</v>
       </c>
       <c r="Q55" t="s">
-        <v>165</v>
+        <v>112</v>
       </c>
       <c r="R55" t="s">
         <v>674</v>
@@ -9222,22 +9210,22 @@
         <v>677</v>
       </c>
       <c r="C56" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="D56" t="s">
-        <v>43</v>
+        <v>73</v>
       </c>
       <c r="E56" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="F56" t="s">
         <v>666</v>
       </c>
       <c r="G56" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H56" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="I56" t="s">
         <v>678</v>
@@ -9253,7 +9241,7 @@
         <v>681</v>
       </c>
       <c r="N56" t="s">
-        <v>68</v>
+        <v>146</v>
       </c>
       <c r="O56" t="s">
         <v>682</v>
@@ -9262,7 +9250,7 @@
         <v>683</v>
       </c>
       <c r="Q56" t="s">
-        <v>129</v>
+        <v>176</v>
       </c>
       <c r="R56" t="s">
         <v>471</v>
@@ -9286,22 +9274,22 @@
         <v>684</v>
       </c>
       <c r="C57" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="D57" t="s">
         <v>685</v>
       </c>
       <c r="E57" t="s">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="F57" t="s">
         <v>666</v>
       </c>
       <c r="G57" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H57" t="s">
-        <v>121</v>
+        <v>168</v>
       </c>
       <c r="I57" t="s">
         <v>686</v>
@@ -9317,7 +9305,7 @@
         <v>689</v>
       </c>
       <c r="N57" t="s">
-        <v>68</v>
+        <v>146</v>
       </c>
       <c r="O57" t="s">
         <v>690</v>
@@ -9326,7 +9314,7 @@
         <v>691</v>
       </c>
       <c r="Q57" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="R57" t="s">
         <v>692</v>
@@ -9350,22 +9338,22 @@
         <v>695</v>
       </c>
       <c r="C58" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="D58" t="s">
         <v>626</v>
       </c>
       <c r="E58" t="s">
-        <v>157</v>
+        <v>102</v>
       </c>
       <c r="F58" t="s">
         <v>696</v>
       </c>
       <c r="G58" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H58" t="s">
-        <v>62</v>
+        <v>104</v>
       </c>
       <c r="I58" t="s">
         <v>697</v>
@@ -9381,7 +9369,7 @@
         <v>700</v>
       </c>
       <c r="N58" t="s">
-        <v>68</v>
+        <v>146</v>
       </c>
       <c r="O58" t="s">
         <v>701</v>
@@ -9390,7 +9378,7 @@
         <v>702</v>
       </c>
       <c r="Q58" t="s">
-        <v>129</v>
+        <v>176</v>
       </c>
       <c r="R58" t="s">
         <v>703</v>
@@ -9420,16 +9408,16 @@
         <v>707</v>
       </c>
       <c r="E59" t="s">
-        <v>157</v>
+        <v>102</v>
       </c>
       <c r="F59" t="s">
         <v>708</v>
       </c>
       <c r="G59" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H59" t="s">
-        <v>144</v>
+        <v>89</v>
       </c>
       <c r="I59" t="s">
         <v>709</v>
@@ -9447,7 +9435,7 @@
         <v>713</v>
       </c>
       <c r="N59" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="O59" t="s">
         <v>714</v>
@@ -9456,7 +9444,7 @@
         <v>715</v>
       </c>
       <c r="Q59" t="s">
-        <v>165</v>
+        <v>112</v>
       </c>
       <c r="R59" t="s">
         <v>716</v>
@@ -9480,22 +9468,22 @@
         <v>719</v>
       </c>
       <c r="C60" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="D60" t="s">
         <v>707</v>
       </c>
       <c r="E60" t="s">
-        <v>157</v>
+        <v>102</v>
       </c>
       <c r="F60" t="s">
         <v>708</v>
       </c>
       <c r="G60" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H60" t="s">
-        <v>144</v>
+        <v>89</v>
       </c>
       <c r="I60" t="s">
         <v>720</v>
@@ -9511,7 +9499,7 @@
         <v>723</v>
       </c>
       <c r="N60" t="s">
-        <v>68</v>
+        <v>146</v>
       </c>
       <c r="O60" t="s">
         <v>724</v>
@@ -9520,7 +9508,7 @@
         <v>725</v>
       </c>
       <c r="Q60" t="s">
-        <v>165</v>
+        <v>112</v>
       </c>
       <c r="R60" t="s">
         <v>726</v>
@@ -9555,7 +9543,7 @@
       </c>
       <c r="G61"/>
       <c r="H61" t="s">
-        <v>62</v>
+        <v>104</v>
       </c>
       <c r="I61" t="s">
         <v>733</v>
@@ -9573,7 +9561,7 @@
         <v>737</v>
       </c>
       <c r="N61" t="s">
-        <v>102</v>
+        <v>34</v>
       </c>
       <c r="O61" t="s">
         <v>738</v>
@@ -9582,7 +9570,7 @@
         <v>739</v>
       </c>
       <c r="Q61" t="s">
-        <v>165</v>
+        <v>112</v>
       </c>
       <c r="R61"/>
       <c r="S61"/>
@@ -9606,16 +9594,16 @@
         <v>741</v>
       </c>
       <c r="E62" t="s">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="F62" t="s">
         <v>742</v>
       </c>
       <c r="G62" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H62" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="I62" t="s">
         <v>743</v>
@@ -9633,7 +9621,7 @@
         <v>747</v>
       </c>
       <c r="N62" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="O62" t="s">
         <v>748</v>
@@ -9642,7 +9630,7 @@
         <v>749</v>
       </c>
       <c r="Q62" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="R62" t="s">
         <v>750</v>
@@ -9672,16 +9660,16 @@
         <v>754</v>
       </c>
       <c r="E63" t="s">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="F63" t="s">
         <v>742</v>
       </c>
       <c r="G63" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H63" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="I63" t="s">
         <v>755</v>
@@ -9699,7 +9687,7 @@
         <v>759</v>
       </c>
       <c r="N63" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="O63" t="s">
         <v>760</v>
@@ -9708,7 +9696,7 @@
         <v>761</v>
       </c>
       <c r="Q63" t="s">
-        <v>165</v>
+        <v>112</v>
       </c>
       <c r="R63" t="s">
         <v>762</v>
@@ -9732,22 +9720,22 @@
         <v>765</v>
       </c>
       <c r="C64" t="s">
-        <v>57</v>
+        <v>139</v>
       </c>
       <c r="D64" t="s">
         <v>766</v>
       </c>
       <c r="E64" t="s">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="F64" t="s">
         <v>742</v>
       </c>
       <c r="G64" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H64" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="I64" t="s">
         <v>767</v>
@@ -9765,7 +9753,7 @@
         <v>771</v>
       </c>
       <c r="N64" t="s">
-        <v>330</v>
+        <v>135</v>
       </c>
       <c r="O64" t="s">
         <v>772</v>
@@ -9774,7 +9762,7 @@
         <v>773</v>
       </c>
       <c r="Q64" t="s">
-        <v>165</v>
+        <v>112</v>
       </c>
       <c r="R64" t="s">
         <v>774</v>
@@ -9798,7 +9786,7 @@
         <v>777</v>
       </c>
       <c r="C65" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D65" t="s">
         <v>334</v>
@@ -9808,10 +9796,10 @@
         <v>778</v>
       </c>
       <c r="G65" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H65" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="I65" t="s">
         <v>779</v>
@@ -9829,7 +9817,7 @@
         <v>783</v>
       </c>
       <c r="N65" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="O65" t="s">
         <v>784</v>
@@ -9838,7 +9826,7 @@
         <v>785</v>
       </c>
       <c r="Q65" t="s">
-        <v>129</v>
+        <v>176</v>
       </c>
       <c r="R65" t="s">
         <v>786</v>
@@ -9868,16 +9856,16 @@
         <v>790</v>
       </c>
       <c r="E66" t="s">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="F66" t="s">
         <v>778</v>
       </c>
       <c r="G66" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H66" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="I66" t="s">
         <v>791</v>
@@ -9895,7 +9883,7 @@
         <v>795</v>
       </c>
       <c r="N66" t="s">
-        <v>68</v>
+        <v>146</v>
       </c>
       <c r="O66" t="s">
         <v>796</v>
@@ -9904,7 +9892,7 @@
         <v>797</v>
       </c>
       <c r="Q66" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="R66" t="s">
         <v>798</v>
@@ -9934,16 +9922,16 @@
         <v>802</v>
       </c>
       <c r="E67" t="s">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="F67" t="s">
         <v>803</v>
       </c>
       <c r="G67" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H67" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="I67" t="s">
         <v>804</v>
@@ -9961,7 +9949,7 @@
         <v>808</v>
       </c>
       <c r="N67" t="s">
-        <v>68</v>
+        <v>146</v>
       </c>
       <c r="O67" t="s">
         <v>809</v>
@@ -9970,7 +9958,7 @@
         <v>810</v>
       </c>
       <c r="Q67" t="s">
-        <v>129</v>
+        <v>176</v>
       </c>
       <c r="R67" t="s">
         <v>354</v>
@@ -9994,7 +9982,7 @@
         <v>811</v>
       </c>
       <c r="C68" t="s">
-        <v>57</v>
+        <v>139</v>
       </c>
       <c r="D68" t="s">
         <v>812</v>
@@ -10004,10 +9992,10 @@
         <v>803</v>
       </c>
       <c r="G68" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H68" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="I68" t="s">
         <v>813</v>
@@ -10025,7 +10013,7 @@
         <v>817</v>
       </c>
       <c r="N68" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="O68" t="s">
         <v>818</v>
@@ -10034,7 +10022,7 @@
         <v>819</v>
       </c>
       <c r="Q68" t="s">
-        <v>165</v>
+        <v>112</v>
       </c>
       <c r="R68" t="s">
         <v>820</v>
@@ -10064,16 +10052,16 @@
         <v>576</v>
       </c>
       <c r="E69" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="F69" t="s">
         <v>803</v>
       </c>
       <c r="G69" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H69" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="I69" t="s">
         <v>824</v>
@@ -10091,7 +10079,7 @@
         <v>828</v>
       </c>
       <c r="N69" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="O69" t="s">
         <v>829</v>
@@ -10100,7 +10088,7 @@
         <v>830</v>
       </c>
       <c r="Q69" t="s">
-        <v>129</v>
+        <v>176</v>
       </c>
       <c r="R69" t="s">
         <v>831</v>
@@ -10136,10 +10124,10 @@
         <v>836</v>
       </c>
       <c r="G70" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="H70" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="I70" t="s">
         <v>837</v>
@@ -10157,7 +10145,7 @@
         <v>841</v>
       </c>
       <c r="N70" t="s">
-        <v>68</v>
+        <v>146</v>
       </c>
       <c r="O70" t="s">
         <v>842</v>
@@ -10166,7 +10154,7 @@
         <v>843</v>
       </c>
       <c r="Q70" t="s">
-        <v>165</v>
+        <v>112</v>
       </c>
       <c r="R70" t="s">
         <v>750</v>
@@ -10190,22 +10178,22 @@
         <v>844</v>
       </c>
       <c r="C71" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D71" t="s">
         <v>845</v>
       </c>
       <c r="E71" t="s">
-        <v>157</v>
+        <v>102</v>
       </c>
       <c r="F71" t="s">
         <v>846</v>
       </c>
       <c r="G71" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H71" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="I71" t="s">
         <v>847</v>
@@ -10223,7 +10211,7 @@
         <v>851</v>
       </c>
       <c r="N71" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="O71" t="s">
         <v>852</v>
@@ -10232,16 +10220,16 @@
         <v>853</v>
       </c>
       <c r="Q71" t="s">
-        <v>165</v>
+        <v>112</v>
       </c>
       <c r="R71" t="s">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="S71" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="T71" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="U71" t="s">
         <v>419</v>
@@ -10256,7 +10244,7 @@
         <v>854</v>
       </c>
       <c r="C72" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D72" t="s">
         <v>855</v>
@@ -10268,10 +10256,10 @@
         <v>857</v>
       </c>
       <c r="G72" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H72" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="I72" t="s">
         <v>858</v>
@@ -10289,7 +10277,7 @@
         <v>862</v>
       </c>
       <c r="N72" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="O72" t="s">
         <v>863</v>
@@ -10298,7 +10286,7 @@
         <v>864</v>
       </c>
       <c r="Q72" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="R72" t="s">
         <v>865</v>
@@ -10322,22 +10310,22 @@
         <v>868</v>
       </c>
       <c r="C73" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D73" t="s">
         <v>626</v>
       </c>
       <c r="E73" t="s">
-        <v>157</v>
+        <v>102</v>
       </c>
       <c r="F73" t="s">
         <v>857</v>
       </c>
       <c r="G73" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H73" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="I73" t="s">
         <v>869</v>
@@ -10355,7 +10343,7 @@
         <v>873</v>
       </c>
       <c r="N73" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="O73" t="s">
         <v>874</v>
@@ -10364,7 +10352,7 @@
         <v>875</v>
       </c>
       <c r="Q73" t="s">
-        <v>129</v>
+        <v>176</v>
       </c>
       <c r="R73" t="s">
         <v>876</v>
@@ -10388,7 +10376,7 @@
         <v>879</v>
       </c>
       <c r="C74" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D74" t="s">
         <v>880</v>
@@ -10398,10 +10386,10 @@
         <v>881</v>
       </c>
       <c r="G74" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H74" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="I74" t="s">
         <v>882</v>
@@ -10419,7 +10407,7 @@
         <v>886</v>
       </c>
       <c r="N74" t="s">
-        <v>330</v>
+        <v>135</v>
       </c>
       <c r="O74" t="s">
         <v>887</v>
@@ -10428,7 +10416,7 @@
         <v>888</v>
       </c>
       <c r="Q74" t="s">
-        <v>129</v>
+        <v>176</v>
       </c>
       <c r="R74" t="s">
         <v>876</v>
@@ -10452,19 +10440,19 @@
         <v>889</v>
       </c>
       <c r="C75" t="s">
-        <v>57</v>
+        <v>139</v>
       </c>
       <c r="D75" t="s">
         <v>890</v>
       </c>
       <c r="E75" t="s">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="F75" t="s">
         <v>891</v>
       </c>
       <c r="G75" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H75" t="s">
         <v>892</v>
@@ -10485,7 +10473,7 @@
         <v>897</v>
       </c>
       <c r="N75" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="O75" t="s">
         <v>898</v>
@@ -10494,7 +10482,7 @@
         <v>899</v>
       </c>
       <c r="Q75" t="s">
-        <v>165</v>
+        <v>112</v>
       </c>
       <c r="R75" t="s">
         <v>900</v>
@@ -10524,16 +10512,16 @@
         <v>904</v>
       </c>
       <c r="E76" t="s">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="F76" t="s">
         <v>891</v>
       </c>
       <c r="G76" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H76" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="I76" t="s">
         <v>905</v>
@@ -10551,7 +10539,7 @@
         <v>909</v>
       </c>
       <c r="N76" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="O76" t="s">
         <v>910</v>
@@ -10560,7 +10548,7 @@
         <v>911</v>
       </c>
       <c r="Q76" t="s">
-        <v>165</v>
+        <v>112</v>
       </c>
       <c r="R76" t="s">
         <v>912</v>
@@ -10590,16 +10578,16 @@
         <v>916</v>
       </c>
       <c r="E77" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="F77" t="s">
         <v>891</v>
       </c>
       <c r="G77" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H77" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="I77" t="s">
         <v>917</v>
@@ -10617,7 +10605,7 @@
         <v>921</v>
       </c>
       <c r="N77" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="O77" t="s">
         <v>922</v>
@@ -10626,7 +10614,7 @@
         <v>923</v>
       </c>
       <c r="Q77" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="R77" t="s">
         <v>674</v>
@@ -10650,22 +10638,22 @@
         <v>924</v>
       </c>
       <c r="C78" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D78" t="s">
         <v>925</v>
       </c>
       <c r="E78" t="s">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="F78" t="s">
         <v>926</v>
       </c>
       <c r="G78" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="H78" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="I78" t="s">
         <v>927</v>
@@ -10683,7 +10671,7 @@
         <v>931</v>
       </c>
       <c r="N78" t="s">
-        <v>68</v>
+        <v>146</v>
       </c>
       <c r="O78" t="s">
         <v>932</v>
@@ -10692,7 +10680,7 @@
         <v>933</v>
       </c>
       <c r="Q78" t="s">
-        <v>129</v>
+        <v>176</v>
       </c>
       <c r="R78" t="s">
         <v>934</v>
@@ -10716,22 +10704,22 @@
         <v>937</v>
       </c>
       <c r="C79" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D79" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="E79" t="s">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="F79" t="s">
         <v>926</v>
       </c>
       <c r="G79" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="H79" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="I79" t="s">
         <v>938</v>
@@ -10749,7 +10737,7 @@
         <v>942</v>
       </c>
       <c r="N79" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="O79" t="s">
         <v>943</v>
@@ -10758,7 +10746,7 @@
         <v>944</v>
       </c>
       <c r="Q79" t="s">
-        <v>129</v>
+        <v>176</v>
       </c>
       <c r="R79" t="s">
         <v>876</v>
@@ -10788,16 +10776,16 @@
         <v>510</v>
       </c>
       <c r="E80" t="s">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="F80" t="s">
         <v>946</v>
       </c>
       <c r="G80" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="H80" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="I80" t="s">
         <v>947</v>
@@ -10815,7 +10803,7 @@
         <v>951</v>
       </c>
       <c r="N80" t="s">
-        <v>68</v>
+        <v>146</v>
       </c>
       <c r="O80" t="s">
         <v>952</v>
@@ -10824,7 +10812,7 @@
         <v>953</v>
       </c>
       <c r="Q80" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="R80" t="s">
         <v>954</v>
@@ -10854,16 +10842,16 @@
         <v>790</v>
       </c>
       <c r="E81" t="s">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="F81" t="s">
         <v>958</v>
       </c>
       <c r="G81" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H81" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="I81" t="s">
         <v>959</v>
@@ -10881,7 +10869,7 @@
         <v>963</v>
       </c>
       <c r="N81" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="O81" t="s">
         <v>964</v>
@@ -10890,7 +10878,7 @@
         <v>965</v>
       </c>
       <c r="Q81" t="s">
-        <v>165</v>
+        <v>112</v>
       </c>
       <c r="R81" t="s">
         <v>966</v>
@@ -10925,7 +10913,7 @@
       </c>
       <c r="G82"/>
       <c r="H82" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="I82" t="s">
         <v>972</v>
@@ -10952,7 +10940,7 @@
         <v>978</v>
       </c>
       <c r="Q82" t="s">
-        <v>165</v>
+        <v>112</v>
       </c>
       <c r="R82"/>
       <c r="S82"/>
@@ -10981,7 +10969,7 @@
       </c>
       <c r="G83"/>
       <c r="H83" t="s">
-        <v>62</v>
+        <v>104</v>
       </c>
       <c r="I83" t="s">
         <v>733</v>
@@ -10999,7 +10987,7 @@
         <v>983</v>
       </c>
       <c r="N83" t="s">
-        <v>68</v>
+        <v>146</v>
       </c>
       <c r="O83" t="s">
         <v>984</v>
@@ -11008,7 +10996,7 @@
         <v>985</v>
       </c>
       <c r="Q83" t="s">
-        <v>165</v>
+        <v>112</v>
       </c>
       <c r="R83"/>
       <c r="S83"/>
@@ -11036,10 +11024,10 @@
         <v>988</v>
       </c>
       <c r="G84" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="H84" t="s">
-        <v>62</v>
+        <v>104</v>
       </c>
       <c r="I84" t="s">
         <v>989</v>
@@ -11066,7 +11054,7 @@
         <v>995</v>
       </c>
       <c r="Q84" t="s">
-        <v>165</v>
+        <v>112</v>
       </c>
       <c r="R84" t="s">
         <v>996</v>
@@ -11096,16 +11084,16 @@
         <v>754</v>
       </c>
       <c r="E85" t="s">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="F85" t="s">
         <v>1000</v>
       </c>
       <c r="G85" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H85" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="I85" t="s">
         <v>1001</v>
@@ -11123,7 +11111,7 @@
         <v>1005</v>
       </c>
       <c r="N85" t="s">
-        <v>68</v>
+        <v>146</v>
       </c>
       <c r="O85" t="s">
         <v>1006</v>
@@ -11132,7 +11120,7 @@
         <v>1007</v>
       </c>
       <c r="Q85" t="s">
-        <v>165</v>
+        <v>112</v>
       </c>
       <c r="R85" t="s">
         <v>1008</v>
@@ -11168,10 +11156,10 @@
         <v>1000</v>
       </c>
       <c r="G86" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H86" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="I86" t="s">
         <v>1012</v>
@@ -11189,7 +11177,7 @@
         <v>1016</v>
       </c>
       <c r="N86" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="O86" t="s">
         <v>1017</v>
@@ -11198,7 +11186,7 @@
         <v>1018</v>
       </c>
       <c r="Q86" t="s">
-        <v>129</v>
+        <v>176</v>
       </c>
       <c r="R86" t="s">
         <v>1019</v>
@@ -11228,13 +11216,13 @@
         <v>1023</v>
       </c>
       <c r="E87" t="s">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="F87" t="s">
         <v>1000</v>
       </c>
       <c r="G87" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H87" t="s">
         <v>360</v>
@@ -11255,7 +11243,7 @@
         <v>1028</v>
       </c>
       <c r="N87" t="s">
-        <v>68</v>
+        <v>146</v>
       </c>
       <c r="O87" t="s">
         <v>1029</v>
@@ -11264,7 +11252,7 @@
         <v>1030</v>
       </c>
       <c r="Q87" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="R87" t="s">
         <v>1031</v>
@@ -11288,22 +11276,22 @@
         <v>1034</v>
       </c>
       <c r="C88" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D88" t="s">
         <v>576</v>
       </c>
       <c r="E88" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="F88" t="s">
         <v>1000</v>
       </c>
       <c r="G88" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H88" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="I88" t="s">
         <v>1035</v>
@@ -11321,7 +11309,7 @@
         <v>1039</v>
       </c>
       <c r="N88" t="s">
-        <v>330</v>
+        <v>135</v>
       </c>
       <c r="O88" t="s">
         <v>1040</v>
@@ -11330,7 +11318,7 @@
         <v>1041</v>
       </c>
       <c r="Q88" t="s">
-        <v>129</v>
+        <v>176</v>
       </c>
       <c r="R88" t="s">
         <v>1042</v>
@@ -11354,22 +11342,22 @@
         <v>1045</v>
       </c>
       <c r="C89" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D89" t="s">
         <v>1046</v>
       </c>
       <c r="E89" t="s">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="F89" t="s">
         <v>1000</v>
       </c>
       <c r="G89" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H89" t="s">
-        <v>62</v>
+        <v>104</v>
       </c>
       <c r="I89" t="s">
         <v>1047</v>
@@ -11387,7 +11375,7 @@
         <v>1051</v>
       </c>
       <c r="N89" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="O89" t="s">
         <v>1052</v>
@@ -11396,7 +11384,7 @@
         <v>1053</v>
       </c>
       <c r="Q89" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="R89" t="s">
         <v>1054</v>
@@ -11426,16 +11414,16 @@
         <v>1058</v>
       </c>
       <c r="E90" t="s">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="F90" t="s">
         <v>1000</v>
       </c>
       <c r="G90" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H90" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="I90" t="s">
         <v>1059</v>
@@ -11453,7 +11441,7 @@
         <v>1063</v>
       </c>
       <c r="N90" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="O90" t="s">
         <v>1064</v>
@@ -11462,7 +11450,7 @@
         <v>1065</v>
       </c>
       <c r="Q90" t="s">
-        <v>129</v>
+        <v>176</v>
       </c>
       <c r="R90" t="s">
         <v>1066</v>
@@ -11486,22 +11474,22 @@
         <v>1069</v>
       </c>
       <c r="C91" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="D91" t="s">
         <v>685</v>
       </c>
       <c r="E91" t="s">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="F91" t="s">
         <v>1070</v>
       </c>
       <c r="G91" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H91" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="I91" t="s">
         <v>1071</v>
@@ -11519,7 +11507,7 @@
         <v>1075</v>
       </c>
       <c r="N91" t="s">
-        <v>68</v>
+        <v>146</v>
       </c>
       <c r="O91" t="s">
         <v>1076</v>
@@ -11528,7 +11516,7 @@
         <v>1077</v>
       </c>
       <c r="Q91" t="s">
-        <v>165</v>
+        <v>112</v>
       </c>
       <c r="R91" t="s">
         <v>1078</v>
@@ -11558,16 +11546,16 @@
         <v>1082</v>
       </c>
       <c r="E92" t="s">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="F92" t="s">
         <v>1070</v>
       </c>
       <c r="G92" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H92" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="I92" t="s">
         <v>1083</v>
@@ -11585,7 +11573,7 @@
         <v>1087</v>
       </c>
       <c r="N92" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="O92" t="s">
         <v>1088</v>
@@ -11594,7 +11582,7 @@
         <v>1089</v>
       </c>
       <c r="Q92" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="R92" t="s">
         <v>1090</v>
@@ -11629,7 +11617,7 @@
       </c>
       <c r="G93"/>
       <c r="H93" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="I93" t="s">
         <v>1095</v>
@@ -11647,7 +11635,7 @@
         <v>1099</v>
       </c>
       <c r="N93" t="s">
-        <v>68</v>
+        <v>146</v>
       </c>
       <c r="O93" t="s">
         <v>1100</v>
@@ -11656,7 +11644,7 @@
         <v>1101</v>
       </c>
       <c r="Q93" t="s">
-        <v>165</v>
+        <v>112</v>
       </c>
       <c r="R93"/>
       <c r="S93"/>
@@ -11674,22 +11662,22 @@
         <v>1102</v>
       </c>
       <c r="C94" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D94" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E94" t="s">
-        <v>157</v>
+        <v>102</v>
       </c>
       <c r="F94" t="s">
         <v>1103</v>
       </c>
       <c r="G94" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H94" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="I94" t="s">
         <v>565</v>
@@ -11707,7 +11695,7 @@
         <v>1107</v>
       </c>
       <c r="N94" t="s">
-        <v>68</v>
+        <v>146</v>
       </c>
       <c r="O94" t="s">
         <v>1108</v>
@@ -11716,7 +11704,7 @@
         <v>1109</v>
       </c>
       <c r="Q94" t="s">
-        <v>165</v>
+        <v>112</v>
       </c>
       <c r="R94" t="s">
         <v>572</v>
@@ -11740,22 +11728,22 @@
         <v>1110</v>
       </c>
       <c r="C95" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="D95" t="s">
         <v>1111</v>
       </c>
       <c r="E95" t="s">
-        <v>157</v>
+        <v>102</v>
       </c>
       <c r="F95" t="s">
         <v>1112</v>
       </c>
       <c r="G95" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H95" t="s">
-        <v>62</v>
+        <v>104</v>
       </c>
       <c r="I95" t="s">
         <v>1113</v>
@@ -11771,7 +11759,7 @@
         <v>1116</v>
       </c>
       <c r="N95" t="s">
-        <v>68</v>
+        <v>146</v>
       </c>
       <c r="O95" t="s">
         <v>1117</v>
@@ -11780,7 +11768,7 @@
         <v>1118</v>
       </c>
       <c r="Q95" t="s">
-        <v>165</v>
+        <v>112</v>
       </c>
       <c r="R95" t="s">
         <v>1119</v>
@@ -11804,22 +11792,22 @@
         <v>1122</v>
       </c>
       <c r="C96" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="D96" t="s">
         <v>1123</v>
       </c>
       <c r="E96" t="s">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="F96" t="s">
         <v>1124</v>
       </c>
       <c r="G96" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H96" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="I96" t="s">
         <v>1125</v>
@@ -11835,7 +11823,7 @@
         <v>1128</v>
       </c>
       <c r="N96" t="s">
-        <v>68</v>
+        <v>146</v>
       </c>
       <c r="O96" t="s">
         <v>1129</v>
@@ -11844,7 +11832,7 @@
         <v>1130</v>
       </c>
       <c r="Q96" t="s">
-        <v>165</v>
+        <v>112</v>
       </c>
       <c r="R96" t="s">
         <v>1008</v>
@@ -11872,14 +11860,14 @@
       </c>
       <c r="D97"/>
       <c r="E97" t="s">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="F97" t="s">
         <v>1132</v>
       </c>
       <c r="G97"/>
       <c r="H97" t="s">
-        <v>62</v>
+        <v>104</v>
       </c>
       <c r="I97" t="s">
         <v>1133</v>
@@ -11893,7 +11881,7 @@
       <c r="L97"/>
       <c r="M97"/>
       <c r="N97" t="s">
-        <v>68</v>
+        <v>146</v>
       </c>
       <c r="O97" t="s">
         <v>1136</v>
@@ -11902,7 +11890,7 @@
         <v>1137</v>
       </c>
       <c r="Q97" t="s">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="R97" t="s">
         <v>1138</v>
@@ -11937,7 +11925,7 @@
       </c>
       <c r="G98"/>
       <c r="H98" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="I98" t="s">
         <v>1143</v>
@@ -11964,7 +11952,7 @@
         <v>1149</v>
       </c>
       <c r="Q98" t="s">
-        <v>165</v>
+        <v>112</v>
       </c>
       <c r="R98" t="s">
         <v>1150</v>
@@ -11999,7 +11987,7 @@
       </c>
       <c r="G99"/>
       <c r="H99" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="I99" t="s">
         <v>1154</v>
@@ -12026,7 +12014,7 @@
         <v>1161</v>
       </c>
       <c r="Q99" t="s">
-        <v>165</v>
+        <v>112</v>
       </c>
       <c r="R99" t="s">
         <v>1162</v>
@@ -12050,7 +12038,7 @@
         <v>1165</v>
       </c>
       <c r="C100" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D100" t="s">
         <v>855</v>
@@ -12062,10 +12050,10 @@
         <v>1166</v>
       </c>
       <c r="G100" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H100" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="I100" t="s">
         <v>1167</v>
@@ -12083,7 +12071,7 @@
         <v>1171</v>
       </c>
       <c r="N100" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="O100" t="s">
         <v>1172</v>
@@ -12092,7 +12080,7 @@
         <v>1173</v>
       </c>
       <c r="Q100" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="R100" t="s">
         <v>1174</v>
@@ -12116,22 +12104,22 @@
         <v>1177</v>
       </c>
       <c r="C101" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D101" t="s">
         <v>1178</v>
       </c>
       <c r="E101" t="s">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="F101" t="s">
         <v>1179</v>
       </c>
       <c r="G101" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H101" t="s">
-        <v>121</v>
+        <v>168</v>
       </c>
       <c r="I101" t="s">
         <v>1180</v>
@@ -12149,7 +12137,7 @@
         <v>1184</v>
       </c>
       <c r="N101" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="O101" t="s">
         <v>1185</v>
@@ -12158,7 +12146,7 @@
         <v>1186</v>
       </c>
       <c r="Q101" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="R101" t="s">
         <v>1187</v>
@@ -12188,16 +12176,16 @@
         <v>1191</v>
       </c>
       <c r="E102" t="s">
-        <v>157</v>
+        <v>102</v>
       </c>
       <c r="F102" t="s">
         <v>1179</v>
       </c>
       <c r="G102" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H102" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="I102" t="s">
         <v>1192</v>
@@ -12215,7 +12203,7 @@
         <v>1196</v>
       </c>
       <c r="N102" t="s">
-        <v>68</v>
+        <v>146</v>
       </c>
       <c r="O102" t="s">
         <v>1197</v>
@@ -12224,7 +12212,7 @@
         <v>1198</v>
       </c>
       <c r="Q102" t="s">
-        <v>165</v>
+        <v>112</v>
       </c>
       <c r="R102" t="s">
         <v>831</v>
@@ -12248,22 +12236,22 @@
         <v>1199</v>
       </c>
       <c r="C103" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D103" t="s">
         <v>1200</v>
       </c>
       <c r="E103" t="s">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="F103" t="s">
         <v>1179</v>
       </c>
       <c r="G103" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H103" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="I103" t="s">
         <v>1201</v>
@@ -12281,7 +12269,7 @@
         <v>1205</v>
       </c>
       <c r="N103" t="s">
-        <v>68</v>
+        <v>146</v>
       </c>
       <c r="O103" t="s">
         <v>1206</v>
@@ -12290,7 +12278,7 @@
         <v>1207</v>
       </c>
       <c r="Q103" t="s">
-        <v>129</v>
+        <v>176</v>
       </c>
       <c r="R103" t="s">
         <v>1208</v>
@@ -12320,16 +12308,16 @@
         <v>1212</v>
       </c>
       <c r="E104" t="s">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="F104" t="s">
         <v>1179</v>
       </c>
       <c r="G104" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H104" t="s">
-        <v>121</v>
+        <v>168</v>
       </c>
       <c r="I104" t="s">
         <v>1213</v>
@@ -12347,7 +12335,7 @@
         <v>1217</v>
       </c>
       <c r="N104" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="O104" t="s">
         <v>1218</v>
@@ -12356,7 +12344,7 @@
         <v>1219</v>
       </c>
       <c r="Q104" t="s">
-        <v>129</v>
+        <v>176</v>
       </c>
       <c r="R104" t="s">
         <v>750</v>
@@ -12380,22 +12368,22 @@
         <v>1220</v>
       </c>
       <c r="C105" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D105" t="s">
         <v>1221</v>
       </c>
       <c r="E105" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="F105" t="s">
         <v>1222</v>
       </c>
       <c r="G105" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H105" t="s">
-        <v>121</v>
+        <v>168</v>
       </c>
       <c r="I105" t="s">
         <v>1223</v>
@@ -12413,7 +12401,7 @@
         <v>1227</v>
       </c>
       <c r="N105" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="O105" t="s">
         <v>1228</v>
@@ -12422,7 +12410,7 @@
         <v>1229</v>
       </c>
       <c r="Q105" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="R105" t="s">
         <v>539</v>
@@ -12446,22 +12434,22 @@
         <v>1230</v>
       </c>
       <c r="C106" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="D106" t="s">
         <v>626</v>
       </c>
       <c r="E106" t="s">
-        <v>157</v>
+        <v>102</v>
       </c>
       <c r="F106" t="s">
         <v>1231</v>
       </c>
       <c r="G106" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H106" t="s">
-        <v>62</v>
+        <v>104</v>
       </c>
       <c r="I106" t="s">
         <v>1232</v>
@@ -12477,7 +12465,7 @@
         <v>1235</v>
       </c>
       <c r="N106" t="s">
-        <v>68</v>
+        <v>146</v>
       </c>
       <c r="O106" t="s">
         <v>1236</v>
@@ -12486,7 +12474,7 @@
         <v>1237</v>
       </c>
       <c r="Q106" t="s">
-        <v>129</v>
+        <v>176</v>
       </c>
       <c r="R106" t="s">
         <v>368</v>
@@ -12513,19 +12501,19 @@
         <v>23</v>
       </c>
       <c r="D107" t="s">
-        <v>120</v>
+        <v>167</v>
       </c>
       <c r="E107" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="F107" t="s">
         <v>1239</v>
       </c>
       <c r="G107" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H107" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="I107" t="s">
         <v>1240</v>
@@ -12543,7 +12531,7 @@
         <v>1244</v>
       </c>
       <c r="N107" t="s">
-        <v>68</v>
+        <v>146</v>
       </c>
       <c r="O107" t="s">
         <v>1245</v>
@@ -12552,7 +12540,7 @@
         <v>1246</v>
       </c>
       <c r="Q107" t="s">
-        <v>129</v>
+        <v>176</v>
       </c>
       <c r="R107" t="s">
         <v>354</v>
@@ -12576,22 +12564,22 @@
         <v>1247</v>
       </c>
       <c r="C108" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="D108" t="s">
         <v>1212</v>
       </c>
       <c r="E108" t="s">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="F108" t="s">
         <v>1248</v>
       </c>
       <c r="G108" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H108" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="I108" t="s">
         <v>1249</v>
@@ -12607,7 +12595,7 @@
         <v>1252</v>
       </c>
       <c r="N108" t="s">
-        <v>68</v>
+        <v>146</v>
       </c>
       <c r="O108" t="s">
         <v>1253</v>
@@ -12616,7 +12604,7 @@
         <v>1254</v>
       </c>
       <c r="Q108" t="s">
-        <v>165</v>
+        <v>112</v>
       </c>
       <c r="R108" t="s">
         <v>674</v>
@@ -12640,22 +12628,22 @@
         <v>1255</v>
       </c>
       <c r="C109" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="D109" t="s">
         <v>626</v>
       </c>
       <c r="E109" t="s">
-        <v>157</v>
+        <v>102</v>
       </c>
       <c r="F109" t="s">
         <v>1248</v>
       </c>
       <c r="G109" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H109" t="s">
-        <v>62</v>
+        <v>104</v>
       </c>
       <c r="I109" t="s">
         <v>1256</v>
@@ -12671,7 +12659,7 @@
         <v>1259</v>
       </c>
       <c r="N109" t="s">
-        <v>68</v>
+        <v>146</v>
       </c>
       <c r="O109" t="s">
         <v>1260</v>
@@ -12680,7 +12668,7 @@
         <v>1261</v>
       </c>
       <c r="Q109" t="s">
-        <v>129</v>
+        <v>176</v>
       </c>
       <c r="R109" t="s">
         <v>368</v>
@@ -12704,22 +12692,22 @@
         <v>1262</v>
       </c>
       <c r="C110" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="D110" t="s">
         <v>626</v>
       </c>
       <c r="E110" t="s">
-        <v>157</v>
+        <v>102</v>
       </c>
       <c r="F110" t="s">
         <v>1248</v>
       </c>
       <c r="G110" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H110" t="s">
-        <v>62</v>
+        <v>104</v>
       </c>
       <c r="I110" t="s">
         <v>1256</v>
@@ -12735,7 +12723,7 @@
         <v>1264</v>
       </c>
       <c r="N110" t="s">
-        <v>68</v>
+        <v>146</v>
       </c>
       <c r="O110" t="s">
         <v>1265</v>
@@ -12744,7 +12732,7 @@
         <v>1266</v>
       </c>
       <c r="Q110" t="s">
-        <v>129</v>
+        <v>176</v>
       </c>
       <c r="R110" t="s">
         <v>368</v>
@@ -12768,22 +12756,22 @@
         <v>1267</v>
       </c>
       <c r="C111" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="D111" t="s">
         <v>626</v>
       </c>
       <c r="E111" t="s">
-        <v>157</v>
+        <v>102</v>
       </c>
       <c r="F111" t="s">
         <v>1248</v>
       </c>
       <c r="G111" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H111" t="s">
-        <v>62</v>
+        <v>104</v>
       </c>
       <c r="I111" t="s">
         <v>1256</v>
@@ -12799,7 +12787,7 @@
         <v>1269</v>
       </c>
       <c r="N111" t="s">
-        <v>68</v>
+        <v>146</v>
       </c>
       <c r="O111" t="s">
         <v>1270</v>
@@ -12808,7 +12796,7 @@
         <v>1271</v>
       </c>
       <c r="Q111" t="s">
-        <v>129</v>
+        <v>176</v>
       </c>
       <c r="R111" t="s">
         <v>368</v>
@@ -12838,16 +12826,16 @@
         <v>707</v>
       </c>
       <c r="E112" t="s">
-        <v>157</v>
+        <v>102</v>
       </c>
       <c r="F112" t="s">
         <v>1273</v>
       </c>
       <c r="G112" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H112" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="I112" t="s">
         <v>1274</v>
@@ -12865,7 +12853,7 @@
         <v>1278</v>
       </c>
       <c r="N112" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="O112" t="s">
         <v>1279</v>
@@ -12874,7 +12862,7 @@
         <v>1280</v>
       </c>
       <c r="Q112" t="s">
-        <v>165</v>
+        <v>112</v>
       </c>
       <c r="R112" t="s">
         <v>1281</v>
@@ -12904,16 +12892,16 @@
         <v>766</v>
       </c>
       <c r="E113" t="s">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="F113" t="s">
         <v>1285</v>
       </c>
       <c r="G113" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H113" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="I113" t="s">
         <v>1286</v>
@@ -12931,7 +12919,7 @@
         <v>1290</v>
       </c>
       <c r="N113" t="s">
-        <v>68</v>
+        <v>146</v>
       </c>
       <c r="O113" t="s">
         <v>1291</v>
@@ -12940,7 +12928,7 @@
         <v>1292</v>
       </c>
       <c r="Q113" t="s">
-        <v>165</v>
+        <v>112</v>
       </c>
       <c r="R113" t="s">
         <v>342</v>
@@ -12970,16 +12958,16 @@
         <v>1294</v>
       </c>
       <c r="E114" t="s">
-        <v>157</v>
+        <v>102</v>
       </c>
       <c r="F114" t="s">
         <v>1285</v>
       </c>
       <c r="G114" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H114" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="I114" t="s">
         <v>1295</v>
@@ -12997,7 +12985,7 @@
         <v>1299</v>
       </c>
       <c r="N114" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="O114" t="s">
         <v>1300</v>
@@ -13006,7 +12994,7 @@
         <v>1301</v>
       </c>
       <c r="Q114" t="s">
-        <v>165</v>
+        <v>112</v>
       </c>
       <c r="R114" t="s">
         <v>1302</v>
@@ -13036,16 +13024,16 @@
         <v>1306</v>
       </c>
       <c r="E115" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="F115" t="s">
         <v>1285</v>
       </c>
       <c r="G115" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H115" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="I115" t="s">
         <v>1307</v>
@@ -13063,7 +13051,7 @@
         <v>1311</v>
       </c>
       <c r="N115" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="O115" t="s">
         <v>1312</v>
@@ -13072,7 +13060,7 @@
         <v>1313</v>
       </c>
       <c r="Q115" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="R115" t="s">
         <v>1314</v>
@@ -13134,7 +13122,7 @@
         <v>1326</v>
       </c>
       <c r="Q116" t="s">
-        <v>165</v>
+        <v>112</v>
       </c>
       <c r="R116" t="s">
         <v>1327</v>
@@ -13158,22 +13146,22 @@
         <v>1330</v>
       </c>
       <c r="C117" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D117" t="s">
         <v>604</v>
       </c>
       <c r="E117" t="s">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="F117" t="s">
         <v>1318</v>
       </c>
       <c r="G117" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H117" t="s">
-        <v>121</v>
+        <v>168</v>
       </c>
       <c r="I117" t="s">
         <v>1331</v>
@@ -13191,7 +13179,7 @@
         <v>1335</v>
       </c>
       <c r="N117" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="O117" t="s">
         <v>1336</v>
@@ -13200,7 +13188,7 @@
         <v>1337</v>
       </c>
       <c r="Q117" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="R117" t="s">
         <v>1338</v>
@@ -13224,22 +13212,22 @@
         <v>1341</v>
       </c>
       <c r="C118" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D118" t="s">
         <v>1342</v>
       </c>
       <c r="E118" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="F118" t="s">
         <v>1318</v>
       </c>
       <c r="G118" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H118" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="I118" t="s">
         <v>1343</v>
@@ -13257,7 +13245,7 @@
         <v>1347</v>
       </c>
       <c r="N118" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="O118" t="s">
         <v>1348</v>
@@ -13266,7 +13254,7 @@
         <v>1349</v>
       </c>
       <c r="Q118" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="R118" t="s">
         <v>1350</v>
@@ -13296,16 +13284,16 @@
         <v>1354</v>
       </c>
       <c r="E119" t="s">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="F119" t="s">
         <v>1318</v>
       </c>
       <c r="G119" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H119" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="I119" t="s">
         <v>1355</v>
@@ -13323,7 +13311,7 @@
         <v>1359</v>
       </c>
       <c r="N119" t="s">
-        <v>68</v>
+        <v>146</v>
       </c>
       <c r="O119" t="s">
         <v>1360</v>
@@ -13332,7 +13320,7 @@
         <v>1361</v>
       </c>
       <c r="Q119" t="s">
-        <v>129</v>
+        <v>176</v>
       </c>
       <c r="R119" t="s">
         <v>1019</v>
@@ -13356,22 +13344,22 @@
         <v>1362</v>
       </c>
       <c r="C120" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D120" t="s">
         <v>754</v>
       </c>
       <c r="E120" t="s">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="F120" t="s">
         <v>1318</v>
       </c>
       <c r="G120" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H120" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="I120" t="s">
         <v>1363</v>
@@ -13389,7 +13377,7 @@
         <v>1367</v>
       </c>
       <c r="N120" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="O120" t="s">
         <v>1368</v>
@@ -13398,7 +13386,7 @@
         <v>1369</v>
       </c>
       <c r="Q120" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="R120" t="s">
         <v>1370</v>
@@ -13422,22 +13410,22 @@
         <v>1373</v>
       </c>
       <c r="C121" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D121" t="s">
         <v>707</v>
       </c>
       <c r="E121" t="s">
-        <v>157</v>
+        <v>102</v>
       </c>
       <c r="F121" t="s">
         <v>1318</v>
       </c>
       <c r="G121" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H121" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="I121" t="s">
         <v>1374</v>
@@ -13464,7 +13452,7 @@
         <v>1381</v>
       </c>
       <c r="Q121" t="s">
-        <v>165</v>
+        <v>112</v>
       </c>
       <c r="R121" t="s">
         <v>1382</v>
@@ -13491,19 +13479,19 @@
         <v>23</v>
       </c>
       <c r="D122" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E122" t="s">
-        <v>157</v>
+        <v>102</v>
       </c>
       <c r="F122" t="s">
         <v>1386</v>
       </c>
       <c r="G122" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H122" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="I122" t="s">
         <v>1387</v>
@@ -13521,7 +13509,7 @@
         <v>1391</v>
       </c>
       <c r="N122" t="s">
-        <v>68</v>
+        <v>146</v>
       </c>
       <c r="O122" t="s">
         <v>1392</v>
@@ -13530,7 +13518,7 @@
         <v>1393</v>
       </c>
       <c r="Q122" t="s">
-        <v>165</v>
+        <v>112</v>
       </c>
       <c r="R122" t="s">
         <v>354</v>
@@ -13554,22 +13542,22 @@
         <v>1394</v>
       </c>
       <c r="C123" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D123" t="s">
         <v>576</v>
       </c>
       <c r="E123" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="F123" t="s">
         <v>1395</v>
       </c>
       <c r="G123" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H123" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="I123" t="s">
         <v>1396</v>
@@ -13587,7 +13575,7 @@
         <v>1400</v>
       </c>
       <c r="N123" t="s">
-        <v>68</v>
+        <v>146</v>
       </c>
       <c r="O123" t="s">
         <v>1401</v>
@@ -13596,7 +13584,7 @@
         <v>1402</v>
       </c>
       <c r="Q123" t="s">
-        <v>129</v>
+        <v>176</v>
       </c>
       <c r="R123" t="s">
         <v>876</v>
@@ -13620,22 +13608,22 @@
         <v>1403</v>
       </c>
       <c r="C124" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="D124" t="s">
         <v>1404</v>
       </c>
       <c r="E124" t="s">
-        <v>157</v>
+        <v>102</v>
       </c>
       <c r="F124" t="s">
         <v>1405</v>
       </c>
       <c r="G124" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H124" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="I124" t="s">
         <v>1406</v>
@@ -13651,7 +13639,7 @@
         <v>1409</v>
       </c>
       <c r="N124" t="s">
-        <v>68</v>
+        <v>146</v>
       </c>
       <c r="O124" t="s">
         <v>1410</v>
@@ -13660,7 +13648,7 @@
         <v>1411</v>
       </c>
       <c r="Q124" t="s">
-        <v>165</v>
+        <v>112</v>
       </c>
       <c r="R124" t="s">
         <v>876</v>
@@ -13684,22 +13672,22 @@
         <v>1412</v>
       </c>
       <c r="C125" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="D125" t="s">
         <v>1413</v>
       </c>
       <c r="E125" t="s">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="F125" t="s">
         <v>1405</v>
       </c>
       <c r="G125" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H125" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="I125" t="s">
         <v>1414</v>
@@ -13715,7 +13703,7 @@
         <v>1417</v>
       </c>
       <c r="N125" t="s">
-        <v>68</v>
+        <v>146</v>
       </c>
       <c r="O125" t="s">
         <v>1418</v>
@@ -13724,16 +13712,16 @@
         <v>1419</v>
       </c>
       <c r="Q125" t="s">
-        <v>165</v>
+        <v>112</v>
       </c>
       <c r="R125" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="S125" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="T125" t="s">
-        <v>40</v>
+        <v>71</v>
       </c>
       <c r="U125" t="s">
         <v>419</v>
@@ -13748,22 +13736,22 @@
         <v>1420</v>
       </c>
       <c r="C126" t="s">
-        <v>57</v>
+        <v>139</v>
       </c>
       <c r="D126" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="E126" t="s">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="F126" t="s">
         <v>1421</v>
       </c>
       <c r="G126" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H126" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="I126" t="s">
         <v>1422</v>
@@ -13781,7 +13769,7 @@
         <v>1426</v>
       </c>
       <c r="N126" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="O126" t="s">
         <v>1427</v>
@@ -13790,7 +13778,7 @@
         <v>1428</v>
       </c>
       <c r="Q126" t="s">
-        <v>129</v>
+        <v>176</v>
       </c>
       <c r="R126" t="s">
         <v>954</v>
@@ -13818,14 +13806,14 @@
       </c>
       <c r="D127"/>
       <c r="E127" t="s">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="F127" t="s">
         <v>1430</v>
       </c>
       <c r="G127"/>
       <c r="H127" t="s">
-        <v>62</v>
+        <v>104</v>
       </c>
       <c r="I127" t="s">
         <v>1431</v>
@@ -13848,7 +13836,7 @@
         <v>1436</v>
       </c>
       <c r="Q127" t="s">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="R127" t="s">
         <v>1437</v>
@@ -13883,7 +13871,7 @@
       </c>
       <c r="G128"/>
       <c r="H128" t="s">
-        <v>62</v>
+        <v>104</v>
       </c>
       <c r="I128" t="s">
         <v>1442</v>
@@ -13910,7 +13898,7 @@
         <v>1448</v>
       </c>
       <c r="Q128" t="s">
-        <v>165</v>
+        <v>112</v>
       </c>
       <c r="R128" t="s">
         <v>1449</v>
@@ -13940,16 +13928,16 @@
         <v>1453</v>
       </c>
       <c r="E129" t="s">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="F129" t="s">
         <v>1454</v>
       </c>
       <c r="G129" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H129" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="I129" t="s">
         <v>1455</v>
@@ -13967,7 +13955,7 @@
         <v>1459</v>
       </c>
       <c r="N129" t="s">
-        <v>68</v>
+        <v>146</v>
       </c>
       <c r="O129" t="s">
         <v>1460</v>
@@ -13976,7 +13964,7 @@
         <v>1461</v>
       </c>
       <c r="Q129" t="s">
-        <v>129</v>
+        <v>176</v>
       </c>
       <c r="R129" t="s">
         <v>1462</v>
@@ -14006,16 +13994,16 @@
         <v>1466</v>
       </c>
       <c r="E130" t="s">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="F130" t="s">
         <v>1467</v>
       </c>
       <c r="G130" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H130" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="I130" t="s">
         <v>1468</v>
@@ -14033,7 +14021,7 @@
         <v>1472</v>
       </c>
       <c r="N130" t="s">
-        <v>68</v>
+        <v>146</v>
       </c>
       <c r="O130" t="s">
         <v>1473</v>
@@ -14042,7 +14030,7 @@
         <v>1474</v>
       </c>
       <c r="Q130" t="s">
-        <v>129</v>
+        <v>176</v>
       </c>
       <c r="R130" t="s">
         <v>1475</v>
@@ -14069,19 +14057,19 @@
         <v>23</v>
       </c>
       <c r="D131" t="s">
-        <v>170</v>
+        <v>43</v>
       </c>
       <c r="E131" t="s">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="F131" t="s">
         <v>1467</v>
       </c>
       <c r="G131" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="H131" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="I131" t="s">
         <v>1479</v>
@@ -14099,7 +14087,7 @@
         <v>1483</v>
       </c>
       <c r="N131" t="s">
-        <v>68</v>
+        <v>146</v>
       </c>
       <c r="O131" t="s">
         <v>1484</v>
@@ -14108,7 +14096,7 @@
         <v>1485</v>
       </c>
       <c r="Q131" t="s">
-        <v>165</v>
+        <v>112</v>
       </c>
       <c r="R131" t="s">
         <v>831</v>
@@ -14132,22 +14120,22 @@
         <v>1486</v>
       </c>
       <c r="C132" t="s">
-        <v>57</v>
+        <v>139</v>
       </c>
       <c r="D132" t="s">
         <v>510</v>
       </c>
       <c r="E132" t="s">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="F132" t="s">
         <v>1487</v>
       </c>
       <c r="G132" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="H132" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="I132" t="s">
         <v>1488</v>
@@ -14165,7 +14153,7 @@
         <v>1492</v>
       </c>
       <c r="N132" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="O132" t="s">
         <v>1493</v>
@@ -14174,7 +14162,7 @@
         <v>1494</v>
       </c>
       <c r="Q132" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="R132" t="s">
         <v>1327</v>
@@ -14198,22 +14186,22 @@
         <v>1495</v>
       </c>
       <c r="C133" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D133" t="s">
         <v>1496</v>
       </c>
       <c r="E133" t="s">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="F133" t="s">
         <v>1487</v>
       </c>
       <c r="G133" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H133" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="I133" t="s">
         <v>1497</v>
@@ -14231,7 +14219,7 @@
         <v>1501</v>
       </c>
       <c r="N133" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="O133" t="s">
         <v>1502</v>
@@ -14240,7 +14228,7 @@
         <v>1503</v>
       </c>
       <c r="Q133" t="s">
-        <v>129</v>
+        <v>176</v>
       </c>
       <c r="R133" t="s">
         <v>1504</v>
@@ -14264,7 +14252,7 @@
         <v>1507</v>
       </c>
       <c r="C134" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D134" t="s">
         <v>1508</v>
@@ -14276,10 +14264,10 @@
         <v>1487</v>
       </c>
       <c r="G134" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H134" t="s">
-        <v>121</v>
+        <v>168</v>
       </c>
       <c r="I134" t="s">
         <v>1510</v>
@@ -14297,7 +14285,7 @@
         <v>1514</v>
       </c>
       <c r="N134" t="s">
-        <v>68</v>
+        <v>146</v>
       </c>
       <c r="O134" t="s">
         <v>1515</v>
@@ -14306,7 +14294,7 @@
         <v>1516</v>
       </c>
       <c r="Q134" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="R134" t="s">
         <v>1517</v>
@@ -14336,16 +14324,16 @@
         <v>475</v>
       </c>
       <c r="E135" t="s">
-        <v>157</v>
+        <v>102</v>
       </c>
       <c r="F135" t="s">
         <v>1487</v>
       </c>
       <c r="G135" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H135" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="I135" t="s">
         <v>1521</v>
@@ -14363,7 +14351,7 @@
         <v>1525</v>
       </c>
       <c r="N135" t="s">
-        <v>68</v>
+        <v>146</v>
       </c>
       <c r="O135" t="s">
         <v>1526</v>
@@ -14372,7 +14360,7 @@
         <v>1527</v>
       </c>
       <c r="Q135" t="s">
-        <v>165</v>
+        <v>112</v>
       </c>
       <c r="R135" t="s">
         <v>1528</v>
@@ -14402,16 +14390,16 @@
         <v>1496</v>
       </c>
       <c r="E136" t="s">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="F136" t="s">
         <v>1487</v>
       </c>
       <c r="G136" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H136" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="I136" t="s">
         <v>1532</v>
@@ -14429,7 +14417,7 @@
         <v>1536</v>
       </c>
       <c r="N136" t="s">
-        <v>68</v>
+        <v>146</v>
       </c>
       <c r="O136" t="s">
         <v>1537</v>
@@ -14438,7 +14426,7 @@
         <v>1538</v>
       </c>
       <c r="Q136" t="s">
-        <v>165</v>
+        <v>112</v>
       </c>
       <c r="R136" t="s">
         <v>1539</v>
@@ -14468,16 +14456,16 @@
         <v>1200</v>
       </c>
       <c r="E137" t="s">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="F137" t="s">
         <v>1487</v>
       </c>
       <c r="G137" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H137" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="I137" t="s">
         <v>1543</v>
@@ -14495,7 +14483,7 @@
         <v>1547</v>
       </c>
       <c r="N137" t="s">
-        <v>68</v>
+        <v>146</v>
       </c>
       <c r="O137" t="s">
         <v>1548</v>
@@ -14504,7 +14492,7 @@
         <v>1549</v>
       </c>
       <c r="Q137" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="R137" t="s">
         <v>1550</v>
@@ -14534,16 +14522,16 @@
         <v>1554</v>
       </c>
       <c r="E138" t="s">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="F138" t="s">
         <v>1555</v>
       </c>
       <c r="G138" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H138" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="I138" t="s">
         <v>1556</v>
@@ -14561,7 +14549,7 @@
         <v>1560</v>
       </c>
       <c r="N138" t="s">
-        <v>68</v>
+        <v>146</v>
       </c>
       <c r="O138" t="s">
         <v>1561</v>
@@ -14570,7 +14558,7 @@
         <v>1562</v>
       </c>
       <c r="Q138" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="R138" t="s">
         <v>876</v>
@@ -14600,16 +14588,16 @@
         <v>372</v>
       </c>
       <c r="E139" t="s">
-        <v>157</v>
+        <v>102</v>
       </c>
       <c r="F139" t="s">
         <v>1564</v>
       </c>
       <c r="G139" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H139" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="I139" t="s">
         <v>1565</v>
@@ -14627,7 +14615,7 @@
         <v>1569</v>
       </c>
       <c r="N139" t="s">
-        <v>68</v>
+        <v>146</v>
       </c>
       <c r="O139" t="s">
         <v>1570</v>
@@ -14636,7 +14624,7 @@
         <v>1571</v>
       </c>
       <c r="Q139" t="s">
-        <v>165</v>
+        <v>112</v>
       </c>
       <c r="R139" t="s">
         <v>471</v>
@@ -14666,16 +14654,16 @@
         <v>1573</v>
       </c>
       <c r="E140" t="s">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="F140" t="s">
         <v>1574</v>
       </c>
       <c r="G140" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="H140" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="I140" t="s">
         <v>1575</v>
@@ -14693,7 +14681,7 @@
         <v>1579</v>
       </c>
       <c r="N140" t="s">
-        <v>68</v>
+        <v>146</v>
       </c>
       <c r="O140" t="s">
         <v>1580</v>
@@ -14702,7 +14690,7 @@
         <v>1581</v>
       </c>
       <c r="Q140" t="s">
-        <v>165</v>
+        <v>112</v>
       </c>
       <c r="R140" t="s">
         <v>798</v>
@@ -14726,22 +14714,22 @@
         <v>1582</v>
       </c>
       <c r="C141" t="s">
-        <v>57</v>
+        <v>139</v>
       </c>
       <c r="D141" t="s">
         <v>1583</v>
       </c>
       <c r="E141" t="s">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="F141" t="s">
         <v>1584</v>
       </c>
       <c r="G141" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="H141" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="I141" t="s">
         <v>1585</v>
@@ -14759,7 +14747,7 @@
         <v>1589</v>
       </c>
       <c r="N141" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="O141" t="s">
         <v>1590</v>
@@ -14768,7 +14756,7 @@
         <v>1591</v>
       </c>
       <c r="Q141" t="s">
-        <v>165</v>
+        <v>112</v>
       </c>
       <c r="R141" t="s">
         <v>1350</v>
@@ -14792,22 +14780,22 @@
         <v>1592</v>
       </c>
       <c r="C142" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="D142" t="s">
         <v>707</v>
       </c>
       <c r="E142" t="s">
-        <v>157</v>
+        <v>102</v>
       </c>
       <c r="F142" t="s">
         <v>1584</v>
       </c>
       <c r="G142" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H142" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="I142" t="s">
         <v>1593</v>
@@ -14823,7 +14811,7 @@
         <v>1596</v>
       </c>
       <c r="N142" t="s">
-        <v>68</v>
+        <v>146</v>
       </c>
       <c r="O142" t="s">
         <v>1597</v>
@@ -14832,7 +14820,7 @@
         <v>1598</v>
       </c>
       <c r="Q142" t="s">
-        <v>129</v>
+        <v>176</v>
       </c>
       <c r="R142" t="s">
         <v>354</v>
@@ -14856,22 +14844,22 @@
         <v>1599</v>
       </c>
       <c r="C143" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="D143" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="E143" t="s">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="F143" t="s">
         <v>1600</v>
       </c>
       <c r="G143" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H143" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="I143" t="s">
         <v>1601</v>
@@ -14887,7 +14875,7 @@
         <v>1604</v>
       </c>
       <c r="N143" t="s">
-        <v>68</v>
+        <v>146</v>
       </c>
       <c r="O143" t="s">
         <v>1605</v>
@@ -14896,7 +14884,7 @@
         <v>1606</v>
       </c>
       <c r="Q143" t="s">
-        <v>165</v>
+        <v>112</v>
       </c>
       <c r="R143" t="s">
         <v>354</v>
@@ -14920,7 +14908,7 @@
         <v>1607</v>
       </c>
       <c r="C144" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D144" t="s">
         <v>1608</v>
@@ -14930,10 +14918,10 @@
         <v>1609</v>
       </c>
       <c r="G144" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H144" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="I144" t="s">
         <v>1610</v>
@@ -14951,7 +14939,7 @@
         <v>1614</v>
       </c>
       <c r="N144" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="O144" t="s">
         <v>1615</v>
@@ -14960,7 +14948,7 @@
         <v>1616</v>
       </c>
       <c r="Q144" t="s">
-        <v>129</v>
+        <v>176</v>
       </c>
       <c r="R144" t="s">
         <v>1617</v>
@@ -14990,16 +14978,16 @@
         <v>916</v>
       </c>
       <c r="E145" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="F145" t="s">
         <v>1621</v>
       </c>
       <c r="G145" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H145" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="I145" t="s">
         <v>1622</v>
@@ -15017,7 +15005,7 @@
         <v>1626</v>
       </c>
       <c r="N145" t="s">
-        <v>68</v>
+        <v>146</v>
       </c>
       <c r="O145" t="s">
         <v>1627</v>
@@ -15026,7 +15014,7 @@
         <v>1628</v>
       </c>
       <c r="Q145" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="R145" t="s">
         <v>1629</v>
@@ -15050,22 +15038,22 @@
         <v>1632</v>
       </c>
       <c r="C146" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D146" t="s">
         <v>741</v>
       </c>
       <c r="E146" t="s">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="F146" t="s">
         <v>1621</v>
       </c>
       <c r="G146" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H146" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="I146" t="s">
         <v>1633</v>
@@ -15083,7 +15071,7 @@
         <v>1637</v>
       </c>
       <c r="N146" t="s">
-        <v>68</v>
+        <v>146</v>
       </c>
       <c r="O146" t="s">
         <v>1638</v>
@@ -15092,7 +15080,7 @@
         <v>1639</v>
       </c>
       <c r="Q146" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="R146" t="s">
         <v>1640</v>
@@ -15116,19 +15104,19 @@
         <v>1643</v>
       </c>
       <c r="C147" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D147" t="s">
         <v>1644</v>
       </c>
       <c r="E147" t="s">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="F147" t="s">
         <v>1645</v>
       </c>
       <c r="G147" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="H147" t="s">
         <v>892</v>
@@ -15149,7 +15137,7 @@
         <v>1650</v>
       </c>
       <c r="N147" t="s">
-        <v>68</v>
+        <v>146</v>
       </c>
       <c r="O147" t="s">
         <v>1651</v>
@@ -15158,7 +15146,7 @@
         <v>1652</v>
       </c>
       <c r="Q147" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="R147" t="s">
         <v>1653</v>
@@ -15182,19 +15170,19 @@
         <v>1656</v>
       </c>
       <c r="C148" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D148" t="s">
         <v>1046</v>
       </c>
       <c r="E148" t="s">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="F148" t="s">
         <v>1645</v>
       </c>
       <c r="G148" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H148" t="s">
         <v>892</v>
@@ -15215,7 +15203,7 @@
         <v>1650</v>
       </c>
       <c r="N148" t="s">
-        <v>68</v>
+        <v>146</v>
       </c>
       <c r="O148" t="s">
         <v>1657</v>
@@ -15224,7 +15212,7 @@
         <v>1658</v>
       </c>
       <c r="Q148" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="R148" t="s">
         <v>1659</v>
@@ -15260,10 +15248,10 @@
         <v>1664</v>
       </c>
       <c r="G149" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H149" t="s">
-        <v>121</v>
+        <v>168</v>
       </c>
       <c r="I149" t="s">
         <v>1665</v>
@@ -15281,7 +15269,7 @@
         <v>1669</v>
       </c>
       <c r="N149" t="s">
-        <v>68</v>
+        <v>146</v>
       </c>
       <c r="O149" t="s">
         <v>1670</v>
@@ -15290,7 +15278,7 @@
         <v>1671</v>
       </c>
       <c r="Q149" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="R149" t="s">
         <v>674</v>
@@ -15317,19 +15305,19 @@
         <v>23</v>
       </c>
       <c r="D150" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="E150" t="s">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="F150" t="s">
         <v>1673</v>
       </c>
       <c r="G150" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="H150" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="I150" t="s">
         <v>1674</v>
@@ -15347,7 +15335,7 @@
         <v>1678</v>
       </c>
       <c r="N150" t="s">
-        <v>68</v>
+        <v>146</v>
       </c>
       <c r="O150" t="s">
         <v>1679</v>
@@ -15356,7 +15344,7 @@
         <v>1680</v>
       </c>
       <c r="Q150" t="s">
-        <v>165</v>
+        <v>112</v>
       </c>
       <c r="R150" t="s">
         <v>1681</v>
@@ -15386,16 +15374,16 @@
         <v>707</v>
       </c>
       <c r="E151" t="s">
-        <v>157</v>
+        <v>102</v>
       </c>
       <c r="F151" t="s">
         <v>1685</v>
       </c>
       <c r="G151" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H151" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="I151" t="s">
         <v>1686</v>
@@ -15413,7 +15401,7 @@
         <v>1690</v>
       </c>
       <c r="N151" t="s">
-        <v>68</v>
+        <v>146</v>
       </c>
       <c r="O151" t="s">
         <v>1691</v>
@@ -15422,7 +15410,7 @@
         <v>1692</v>
       </c>
       <c r="Q151" t="s">
-        <v>165</v>
+        <v>112</v>
       </c>
       <c r="R151" t="s">
         <v>1693</v>
@@ -15446,22 +15434,22 @@
         <v>1696</v>
       </c>
       <c r="C152" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="D152" t="s">
         <v>1697</v>
       </c>
       <c r="E152" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="F152" t="s">
         <v>1685</v>
       </c>
       <c r="G152" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H152" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="I152" t="s">
         <v>1698</v>
@@ -15477,7 +15465,7 @@
         <v>1701</v>
       </c>
       <c r="N152" t="s">
-        <v>68</v>
+        <v>146</v>
       </c>
       <c r="O152" t="s">
         <v>1702</v>
@@ -15486,7 +15474,7 @@
         <v>1703</v>
       </c>
       <c r="Q152" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="R152" t="s">
         <v>1693</v>
@@ -15510,22 +15498,22 @@
         <v>1704</v>
       </c>
       <c r="C153" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="D153" t="s">
         <v>1697</v>
       </c>
       <c r="E153" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="F153" t="s">
         <v>1685</v>
       </c>
       <c r="G153" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H153" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="I153" t="s">
         <v>1705</v>
@@ -15541,7 +15529,7 @@
         <v>1708</v>
       </c>
       <c r="N153" t="s">
-        <v>68</v>
+        <v>146</v>
       </c>
       <c r="O153" t="s">
         <v>1709</v>
@@ -15550,7 +15538,7 @@
         <v>1710</v>
       </c>
       <c r="Q153" t="s">
-        <v>129</v>
+        <v>176</v>
       </c>
       <c r="R153" t="s">
         <v>1693</v>
@@ -15574,7 +15562,7 @@
         <v>1711</v>
       </c>
       <c r="C154" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="D154" t="s">
         <v>1712</v>
@@ -15586,10 +15574,10 @@
         <v>1713</v>
       </c>
       <c r="G154" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H154" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="I154" t="s">
         <v>1714</v>
@@ -15605,7 +15593,7 @@
         <v>1717</v>
       </c>
       <c r="N154" t="s">
-        <v>68</v>
+        <v>146</v>
       </c>
       <c r="O154" t="s">
         <v>1718</v>
@@ -15614,7 +15602,7 @@
         <v>1719</v>
       </c>
       <c r="Q154" t="s">
-        <v>129</v>
+        <v>176</v>
       </c>
       <c r="R154" t="s">
         <v>674</v>
@@ -15638,22 +15626,22 @@
         <v>1720</v>
       </c>
       <c r="C155" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="D155" t="s">
         <v>1496</v>
       </c>
       <c r="E155" t="s">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="F155" t="s">
         <v>1721</v>
       </c>
       <c r="G155" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="H155" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="I155" t="s">
         <v>1722</v>
@@ -15669,7 +15657,7 @@
         <v>1725</v>
       </c>
       <c r="N155" t="s">
-        <v>68</v>
+        <v>146</v>
       </c>
       <c r="O155" t="s">
         <v>1726</v>
@@ -15678,7 +15666,7 @@
         <v>1727</v>
       </c>
       <c r="Q155" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="R155" t="s">
         <v>1728</v>
@@ -15713,7 +15701,7 @@
       </c>
       <c r="G156"/>
       <c r="H156" t="s">
-        <v>121</v>
+        <v>168</v>
       </c>
       <c r="I156" t="s">
         <v>1733</v>
@@ -15731,7 +15719,7 @@
         <v>1737</v>
       </c>
       <c r="N156" t="s">
-        <v>68</v>
+        <v>146</v>
       </c>
       <c r="O156" t="s">
         <v>1738</v>
@@ -15740,7 +15728,7 @@
         <v>1739</v>
       </c>
       <c r="Q156" t="s">
-        <v>165</v>
+        <v>112</v>
       </c>
       <c r="R156" t="s">
         <v>1740</v>

--- a/Objets_parlementaires_Jura.xlsx
+++ b/Objets_parlementaires_Jura.xlsx
@@ -122,6 +122,105 @@
     <t xml:space="preserve">Titre uniquement</t>
   </si>
   <si>
+    <t xml:space="preserve">26.3628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Juillard Charles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le Centre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VBS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cybersicherheit und digitale Souveränität. Eine nationale Roadmap für den Übergang zur Post-Quanten-Kryptografie in der Schweiz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cybersécurité et souveraineté numérique. Doter la Suisse d'une feuille de route nationale de transition vers la cryptographie post-quantique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cibersicurezza e sovranità digitale. Dotare la Svizzera di una tabella di marcia nazionale per la transizione verso la crittografia post-quantistica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé d’élaborer, en collaboration avec les cantons, les hautes écoles, les instituts de recherche, les autorités de surveillance sectorielles et le secteur privé, une feuille de route nationale pour la transition de la Suisse vers la cryptographie post-quantique. Cette feuille de route doit garantir la protection durable des données et des communications sensibles, la résilience des infrastructures critiques, la validité à long terme des signatures et des documents électroniques, l’interopérabilité internationale des systèmes suisses et la compétitivité des entreprises actives sur les marchés internationaux. Elle doit en particulier :&lt;/p&gt;&lt;ol style="list-style-type:lower-alpha;"&gt;&lt;li&gt;&lt;strong&gt;établir, d’ici à fin 2027 au plus tard, une stratégie nationale de migration — c’est-à-dire de remplacement progressif des algorithmes vulnérables — fondée sur les risques,&amp;nbsp;&lt;/strong&gt;comprenant un inventaire des usages cryptographiques critiques, une cartographie des dépendances, y compris à l’égard des fournisseurs étrangers, et le lancement de projets pilotes pour les cas d’usage présentant un risque élevé ou une longue durée de confidentialité ;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;fixer des jalons coordonnés avec les calendriers internationaux pertinents,&amp;nbsp;&lt;/strong&gt;notamment la migration prioritaire des cas d’usage à haut risque d’ici à fin 2030 et la transition progressive des autres systèmes critiques ou sensibles d’ici à fin 2035, sous réserve de la maturité des standards, de l’interopérabilité et de la proportionnalité des mesures ;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;désigner les responsabilités de pilotage et de coordination au sein de l’administration fédérale,&amp;nbsp;&lt;/strong&gt;en s’appuyant en particulier sur l’Office fédéral de la cybersécurité (OFCS, anciennement NCSC), l’Office fédéral de l’informatique et de la télécommunication (OFIT) et les autorités sectorielles compétentes, sans créer de structures redondantes, et présenter au Parlement un rapport biennal sur l’état d’avancement ;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;définir les exigences minimales applicables aux infrastructures critiques, aux systèmes d’information de la Confédération et aux fournisseurs de prestations numériques critiques,&amp;nbsp;&lt;/strong&gt;notamment en matière d’inventaire cryptographique standardisé et interopérable — fondé, lorsque cela est approprié, sur des formats reconnus tels que le Cryptographic Bill of Materials (CBOM) —, de crypto-agilité, de capacité de mise à jour et de gestion sécurisée des dépendances fournisseurs, ces inventaires étant traités comme des informations sensibles de sécurité à accès restreint et non destinées à publication détaillée ;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;intégrer des exigences de préparation à la cryptographie post-quantique dans les marchés publics fédéraux et dans les contrats fournisseurs&amp;nbsp;&lt;/strong&gt;pour les produits et services numériques dont la durée de vie, la criticité ou la durée de confidentialité attendue dépasse 2030 ;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;garantir la résilience quantique de la signature électronique et de l’archivage à long terme,&amp;nbsp;&lt;/strong&gt;afin de préserver la validité durable des signatures, certificats, horodatages, actes authentiques, dossiers médicaux, registres publics et archives, en cohérence avec les travaux de la Swiss Government PKI ;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;assurer la cohérence avec les cadres internationaux applicables,&amp;nbsp;&lt;/strong&gt;en particulier la feuille de route coordonnée adoptée par le NIS Cooperation Group de l’Union européenne le 11 juin 2025, ainsi que les exigences du Cyber Resilience Act applicables dès le 11 décembre 2027 aux produits placés sur le marché européen ;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;examiner les adaptations légales ou réglementaires nécessaires,&amp;nbsp;&lt;/strong&gt;notamment dans le cadre de la législation sur la sécurité de l’information, de l’ordonnance sur la cybersécurité, des prescriptions de marchés publics et des réglementations sectorielles applicables ;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;prévoir des mesures de soutien proportionnées pour les cantons, les PME, les hautes écoles et les entreprises suisses,&amp;nbsp;&lt;/strong&gt;notamment par des lignes directrices, des modèles d’inventaire, des projets pilotes, des tests d’interopérabilité et la mobilisation des compétences nationales, dans une logique de souveraineté technologique cohérente avec l’objectif de la motion 24.3209.&lt;/li&gt;&lt;/ol&gt;&lt;p&gt;La feuille de route respecte les principes de neutralité technologique, d’ouverture des standards, de sécurité par conception et de proportionnalité économique — les obligations étant graduées selon le risque, la criticité, la durée de confidentialité des données et la durée de vie des systèmes. Conformément à la tradition suisse de conditions-cadres favorables plutôt que de politique industrielle sélective, elle ne vise pas à privilégier un fournisseur ou une technologie, mais à fixer les exigences de sécurité applicables aux infrastructures de l’État. Les informations sensibles contenues dans les inventaires cryptographiques sont protégées.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, in Zusammenarbeit mit den Kantonen, den Hochschulen, den Forschungsinstituten, den branchenspezifischen Aufsichtsbehörden und der Privatwirtschaft eine nationale Roadmap für den Übergang der Schweiz zur Post-Quanten-Kryptografie auszuarbeiten. Diese Roadmap soll den nachhaltigen Schutz besonders schützenswerter Daten und sensitiver Kommunikation, die Widerstandsfähigkeit kritischer Infrastrukturen, die langfristige Gültigkeit elektronischer Signaturen und Dokumente, die internationale Interoperabilität der Schweizer Systeme und die Wettbewerbsfähigkeit der im internationalen Markt tätigen Unternehmen gewährleisten. Insbesondere ist Folgendes vorzusehen:&lt;/p&gt;&lt;ol style="list-style-type:lower-latin;"&gt;&lt;li&gt;&lt;strong&gt;Spätestens bis Ende 2027 muss eine nationale Migrationsstrategie – d. h. eine Strategie zur schrittweisen Ablösung anfälliger Algorithmen – auf der Grundlage einer Risikobewertung erarbeitet werden,&amp;nbsp;&lt;/strong&gt;einschliesslich einer Bestandsaufnahme kritischer kryptografischer Anwendungen, einer Kartografie der Abhängigkeiten, auch gegenüber ausländischen Anbietern, sowie der Lancierung von Pilotprojekten für Anwendungsfälle mit hohem Risiko oder langer Vertraulichkeitsdauer.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Es müssen Meilensteine festgelegt werden, die auf die einschlägigen internationalen Zeitpläne abgestimmt sind,&amp;nbsp;&lt;/strong&gt;insbesondere die vorrangige Umstellung für Anwendungsfälle mit hohem Risiko bis Ende 2030 und die schrittweise Umstellung der übrigen kritischen oder sensitiven Systeme bis Ende 2035; dies unter Berücksichtigung der Ausgereiftheit der Standards, der Interoperabilität und der Verhältnismässigkeit der Massnahmen.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Es müssen die Zuständigkeiten für die Steuerung und Koordination innerhalb der Bundesverwaltung festgelegt werden,&lt;/strong&gt; insbesondere unter Einbezug des Bundesamts für Cybersicherheit (BACS, ehemals NCSC), des Bundesamts für Informatik und Telekommunikation (BIT) sowie der spezifisch zuständigen Behörden. Redundante Strukturen müssen vermieden werden. Dem Parlament ist alle zwei Jahre ein Bericht über den Stand der Umsetzung vorzulegen.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Es müssen Mindestanforderungen für kritische Infrastrukturen, Informationssysteme des Bundes und Anbieter kritischer digitaler Dienste festgelegt werden,&amp;nbsp;&lt;/strong&gt;insbesondere betreffend ein standardisiertes und interoperables kryptografisches Inventar – das, soweit angemessen, auf anerkannten Formaten wie der Cryptographic Bill of Materials (CBOM) basiert –, Krypto-Agilität, Aktualisierbarkeit sowie die gesicherte Verwaltung von Lieferantenabhängigkeiten. Diese Inventare müssen als sensitive Sicherheitsinformationen mit eingeschränktem Zugriff behandelt werden und dürfen nicht detailliert veröffentlicht werden.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Anforderungen zur Vorbereitung auf die Post-Quanten-Kryptografie müssen in öffentliche Ausschreibungen des Bundes und in Lieferantenverträgen &lt;/strong&gt;für digitale Produkte und Dienstleistungen, deren Lebensdauer, Kritikalität oder erwartete Vertraulichkeitsdauer über das Jahr 2030 hinausgeht, aufgenommen werden.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Die Quantenresilienz der elektronischen Signatur und der Langzeitarchivierung ist zu gewährleisten,&lt;/strong&gt; um die dauerhafte Gültigkeit von Signaturen, Zertifikaten, Zeitstempeln, öffentlichen Urkunden, Patientendossier, öffentlichen Registern und Archiven in Übereinstimmung mit den Arbeiten der Swiss Government PKI sicherzustellen.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Die Übereinstimmung mit den geltenden internationalen Rahmenwerken ist sicherzustellen,&amp;nbsp;&lt;/strong&gt;insbesondere diejenige mit der koordinierten Roadmap, die am 11. Juni 2025 von der NIS-Kooperationsgruppe der Europäischen Union verabschiedet wurde, sowie diejenige mit den Anforderungen der Cyberresilienz-Verordnung, die ab dem 11. Dezember 2027 für Produkte gelten, die auf den europäischen Markt gebracht werden.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Der rechtlich und reglementarisch erforderliche Anpassungsbedarf ist zu prüfen,&lt;/strong&gt; insbesondere betreffend die Gesetzgebung zur Informationssicherheit, die Cybersicherheitsverordnung, die Vorschriften für das öffentliche Beschaffungswesen und die geltenden bereichsspezifischen Regelungen.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Für die Kantone, KMU, Hochschulen und Schweizer Unternehmen sind angemessene Unterstützungsmassnahmen vorzusehen,&lt;/strong&gt; insbesondere in Form von Leitlinien, Inventarvorlagen, Pilotprojekten, Interoperabilitätstests und durch die Mobilisierung nationaler Kompetenzen im Sinne einer technologischen Souveränität, die mit dem Ziel der Motion 24.3209 übereinstimmt.&lt;/li&gt;&lt;/ol&gt;&lt;p&gt;Die Roadmap berücksichtigt die Grundsätze der Technologieneutralität, der Offenheit der Standards, der Sicherheit durch Design und der wirtschaftlichen Verhältnismässigkeit – wobei die Verpflichtungen je nach Risiko, Kritikalität, Dauer der Vertraulichkeit der Daten und Lebensdauer der Systeme unterschiedlich ausgestaltet sind. Entsprechend der Schweizer Tradition, die eher auf günstige Rahmenbedingungen als auf eine selektive Industriepolitik setzt, zielt sie nicht darauf ab, einen bestimmten Anbieter oder eine bestimmte Technologie zu begünstigen, sondern die Sicherheitsanforderungen für staatliche Infrastrukturen festzulegen. Die in den kryptografischen Bestandesverzeichnissen enthaltenen sensitiven Informationen sind geschützt.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In Kommission des Nationalrats / En commission du Conseil national</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sicherheitspolitik|Medien und Kommunikation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politique de sécurité|Médias et communication</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politica di sicurezza|Media e comunicazione</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fraktion der Schweizerischen Volkspartei</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EJPD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Von Dänemark lernen. Bei längerfristigen Freiheitsstrafen muss die obligatorische Landesverweisung obligatorisch sein</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inspirons-nous du Danemark. Rendons réellement obligatoire l'expulsion en cas de peine privative de liberté de longue durée</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Imparare dalla Danimarca. Espulsione obbligatoria in caso di pene detentive di lunga durata</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé de présenter les modifications législatives nécessaires pour que lorsqu’un délinquant étranger est condamné à une peine privative de liberté de longue durée (un an au moins), que cette peine soit ferme ou assortie d’un sursis ou d’un sursis partiel, une expulsion soit obligatoirement ordonnée et exécutée.&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, die erforderlichen Gesetzesanpassungen vorzulegen, so dass für kriminelle Ausländer bei einer längerfristigen Freiheitsstrafe ab einem Jahr – unabhängig davon, ob diese unbedingt, teilbedingt oder bedingt ausfällt – in jedem Fall zwingend eine Landesverweisung angeordnet und vollzogen werden muss.&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Erledigt / Liquidé</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Élu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strafrecht|Migration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Droit pénal|Politique migratoire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diritto penale|Migrazione</t>
+  </si>
+  <si>
     <t xml:space="preserve">26.4146</t>
   </si>
   <si>
@@ -200,9 +299,6 @@
     <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20264127</t>
   </si>
   <si>
-    <t xml:space="preserve">Élu</t>
-  </si>
-  <si>
     <t xml:space="preserve">Staatspolitik|Sicherheitspolitik|Soziale Fragen</t>
   </si>
   <si>
@@ -305,18 +401,9 @@
     <t xml:space="preserve">26.3891</t>
   </si>
   <si>
-    <t xml:space="preserve">Juillard Charles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Le Centre</t>
-  </si>
-  <si>
     <t xml:space="preserve">2026-06-19</t>
   </si>
   <si>
-    <t xml:space="preserve">SR</t>
-  </si>
-  <si>
     <t xml:space="preserve">EFD</t>
   </si>
   <si>
@@ -482,48 +569,6 @@
     <t xml:space="preserve">Economia|Scienza e ricerca|Imposte|Salute</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VBS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cybersicherheit und digitale Souveränität. Eine nationale Roadmap für den Übergang zur Post-Quanten-Kryptografie in der Schweiz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cybersécurité et souveraineté numérique. Doter la Suisse d'une feuille de route nationale de transition vers la cryptographie post-quantique</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cibersicurezza e sovranità digitale. Dotare la Svizzera di una tabella di marcia nazionale per la transizione verso la crittografia post-quantistica</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé d’élaborer, en collaboration avec les cantons, les hautes écoles, les instituts de recherche, les autorités de surveillance sectorielles et le secteur privé, une feuille de route nationale pour la transition de la Suisse vers la cryptographie post-quantique. Cette feuille de route doit garantir la protection durable des données et des communications sensibles, la résilience des infrastructures critiques, la validité à long terme des signatures et des documents électroniques, l’interopérabilité internationale des systèmes suisses et la compétitivité des entreprises actives sur les marchés internationaux. Elle doit en particulier :&lt;/p&gt;&lt;ol style="list-style-type:lower-alpha;"&gt;&lt;li&gt;&lt;strong&gt;établir, d’ici à fin 2027 au plus tard, une stratégie nationale de migration — c’est-à-dire de remplacement progressif des algorithmes vulnérables — fondée sur les risques,&amp;nbsp;&lt;/strong&gt;comprenant un inventaire des usages cryptographiques critiques, une cartographie des dépendances, y compris à l’égard des fournisseurs étrangers, et le lancement de projets pilotes pour les cas d’usage présentant un risque élevé ou une longue durée de confidentialité ;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;fixer des jalons coordonnés avec les calendriers internationaux pertinents,&amp;nbsp;&lt;/strong&gt;notamment la migration prioritaire des cas d’usage à haut risque d’ici à fin 2030 et la transition progressive des autres systèmes critiques ou sensibles d’ici à fin 2035, sous réserve de la maturité des standards, de l’interopérabilité et de la proportionnalité des mesures ;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;désigner les responsabilités de pilotage et de coordination au sein de l’administration fédérale,&amp;nbsp;&lt;/strong&gt;en s’appuyant en particulier sur l’Office fédéral de la cybersécurité (OFCS, anciennement NCSC), l’Office fédéral de l’informatique et de la télécommunication (OFIT) et les autorités sectorielles compétentes, sans créer de structures redondantes, et présenter au Parlement un rapport biennal sur l’état d’avancement ;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;définir les exigences minimales applicables aux infrastructures critiques, aux systèmes d’information de la Confédération et aux fournisseurs de prestations numériques critiques,&amp;nbsp;&lt;/strong&gt;notamment en matière d’inventaire cryptographique standardisé et interopérable — fondé, lorsque cela est approprié, sur des formats reconnus tels que le Cryptographic Bill of Materials (CBOM) —, de crypto-agilité, de capacité de mise à jour et de gestion sécurisée des dépendances fournisseurs, ces inventaires étant traités comme des informations sensibles de sécurité à accès restreint et non destinées à publication détaillée ;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;intégrer des exigences de préparation à la cryptographie post-quantique dans les marchés publics fédéraux et dans les contrats fournisseurs&amp;nbsp;&lt;/strong&gt;pour les produits et services numériques dont la durée de vie, la criticité ou la durée de confidentialité attendue dépasse 2030 ;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;garantir la résilience quantique de la signature électronique et de l’archivage à long terme,&amp;nbsp;&lt;/strong&gt;afin de préserver la validité durable des signatures, certificats, horodatages, actes authentiques, dossiers médicaux, registres publics et archives, en cohérence avec les travaux de la Swiss Government PKI ;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;assurer la cohérence avec les cadres internationaux applicables,&amp;nbsp;&lt;/strong&gt;en particulier la feuille de route coordonnée adoptée par le NIS Cooperation Group de l’Union européenne le 11 juin 2025, ainsi que les exigences du Cyber Resilience Act applicables dès le 11 décembre 2027 aux produits placés sur le marché européen ;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;examiner les adaptations légales ou réglementaires nécessaires,&amp;nbsp;&lt;/strong&gt;notamment dans le cadre de la législation sur la sécurité de l’information, de l’ordonnance sur la cybersécurité, des prescriptions de marchés publics et des réglementations sectorielles applicables ;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;prévoir des mesures de soutien proportionnées pour les cantons, les PME, les hautes écoles et les entreprises suisses,&amp;nbsp;&lt;/strong&gt;notamment par des lignes directrices, des modèles d’inventaire, des projets pilotes, des tests d’interopérabilité et la mobilisation des compétences nationales, dans une logique de souveraineté technologique cohérente avec l’objectif de la motion 24.3209.&lt;/li&gt;&lt;/ol&gt;&lt;p&gt;La feuille de route respecte les principes de neutralité technologique, d’ouverture des standards, de sécurité par conception et de proportionnalité économique — les obligations étant graduées selon le risque, la criticité, la durée de confidentialité des données et la durée de vie des systèmes. Conformément à la tradition suisse de conditions-cadres favorables plutôt que de politique industrielle sélective, elle ne vise pas à privilégier un fournisseur ou une technologie, mais à fixer les exigences de sécurité applicables aux infrastructures de l’État. Les informations sensibles contenues dans les inventaires cryptographiques sont protégées.&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, in Zusammenarbeit mit den Kantonen, den Hochschulen, den Forschungsinstituten, den branchenspezifischen Aufsichtsbehörden und der Privatwirtschaft eine nationale Roadmap für den Übergang der Schweiz zur Post-Quanten-Kryptografie auszuarbeiten. Diese Roadmap soll den nachhaltigen Schutz besonders schützenswerter Daten und sensitiver Kommunikation, die Widerstandsfähigkeit kritischer Infrastrukturen, die langfristige Gültigkeit elektronischer Signaturen und Dokumente, die internationale Interoperabilität der Schweizer Systeme und die Wettbewerbsfähigkeit der im internationalen Markt tätigen Unternehmen gewährleisten. Insbesondere ist Folgendes vorzusehen:&lt;/p&gt;&lt;ol style="list-style-type:lower-latin;"&gt;&lt;li&gt;&lt;strong&gt;Spätestens bis Ende 2027 muss eine nationale Migrationsstrategie – d. h. eine Strategie zur schrittweisen Ablösung anfälliger Algorithmen – auf der Grundlage einer Risikobewertung erarbeitet werden,&amp;nbsp;&lt;/strong&gt;einschliesslich einer Bestandsaufnahme kritischer kryptografischer Anwendungen, einer Kartografie der Abhängigkeiten, auch gegenüber ausländischen Anbietern, sowie der Lancierung von Pilotprojekten für Anwendungsfälle mit hohem Risiko oder langer Vertraulichkeitsdauer.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Es müssen Meilensteine festgelegt werden, die auf die einschlägigen internationalen Zeitpläne abgestimmt sind,&amp;nbsp;&lt;/strong&gt;insbesondere die vorrangige Umstellung für Anwendungsfälle mit hohem Risiko bis Ende 2030 und die schrittweise Umstellung der übrigen kritischen oder sensitiven Systeme bis Ende 2035; dies unter Berücksichtigung der Ausgereiftheit der Standards, der Interoperabilität und der Verhältnismässigkeit der Massnahmen.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Es müssen die Zuständigkeiten für die Steuerung und Koordination innerhalb der Bundesverwaltung festgelegt werden,&lt;/strong&gt; insbesondere unter Einbezug des Bundesamts für Cybersicherheit (BACS, ehemals NCSC), des Bundesamts für Informatik und Telekommunikation (BIT) sowie der spezifisch zuständigen Behörden. Redundante Strukturen müssen vermieden werden. Dem Parlament ist alle zwei Jahre ein Bericht über den Stand der Umsetzung vorzulegen.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Es müssen Mindestanforderungen für kritische Infrastrukturen, Informationssysteme des Bundes und Anbieter kritischer digitaler Dienste festgelegt werden,&amp;nbsp;&lt;/strong&gt;insbesondere betreffend ein standardisiertes und interoperables kryptografisches Inventar – das, soweit angemessen, auf anerkannten Formaten wie der Cryptographic Bill of Materials (CBOM) basiert –, Krypto-Agilität, Aktualisierbarkeit sowie die gesicherte Verwaltung von Lieferantenabhängigkeiten. Diese Inventare müssen als sensitive Sicherheitsinformationen mit eingeschränktem Zugriff behandelt werden und dürfen nicht detailliert veröffentlicht werden.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Anforderungen zur Vorbereitung auf die Post-Quanten-Kryptografie müssen in öffentliche Ausschreibungen des Bundes und in Lieferantenverträgen &lt;/strong&gt;für digitale Produkte und Dienstleistungen, deren Lebensdauer, Kritikalität oder erwartete Vertraulichkeitsdauer über das Jahr 2030 hinausgeht, aufgenommen werden.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Die Quantenresilienz der elektronischen Signatur und der Langzeitarchivierung ist zu gewährleisten,&lt;/strong&gt; um die dauerhafte Gültigkeit von Signaturen, Zertifikaten, Zeitstempeln, öffentlichen Urkunden, Patientendossier, öffentlichen Registern und Archiven in Übereinstimmung mit den Arbeiten der Swiss Government PKI sicherzustellen.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Die Übereinstimmung mit den geltenden internationalen Rahmenwerken ist sicherzustellen,&amp;nbsp;&lt;/strong&gt;insbesondere diejenige mit der koordinierten Roadmap, die am 11. Juni 2025 von der NIS-Kooperationsgruppe der Europäischen Union verabschiedet wurde, sowie diejenige mit den Anforderungen der Cyberresilienz-Verordnung, die ab dem 11. Dezember 2027 für Produkte gelten, die auf den europäischen Markt gebracht werden.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Der rechtlich und reglementarisch erforderliche Anpassungsbedarf ist zu prüfen,&lt;/strong&gt; insbesondere betreffend die Gesetzgebung zur Informationssicherheit, die Cybersicherheitsverordnung, die Vorschriften für das öffentliche Beschaffungswesen und die geltenden bereichsspezifischen Regelungen.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Für die Kantone, KMU, Hochschulen und Schweizer Unternehmen sind angemessene Unterstützungsmassnahmen vorzusehen,&lt;/strong&gt; insbesondere in Form von Leitlinien, Inventarvorlagen, Pilotprojekten, Interoperabilitätstests und durch die Mobilisierung nationaler Kompetenzen im Sinne einer technologischen Souveränität, die mit dem Ziel der Motion 24.3209 übereinstimmt.&lt;/li&gt;&lt;/ol&gt;&lt;p&gt;Die Roadmap berücksichtigt die Grundsätze der Technologieneutralität, der Offenheit der Standards, der Sicherheit durch Design und der wirtschaftlichen Verhältnismässigkeit – wobei die Verpflichtungen je nach Risiko, Kritikalität, Dauer der Vertraulichkeit der Daten und Lebensdauer der Systeme unterschiedlich ausgestaltet sind. Entsprechend der Schweizer Tradition, die eher auf günstige Rahmenbedingungen als auf eine selektive Industriepolitik setzt, zielt sie nicht darauf ab, einen bestimmten Anbieter oder eine bestimmte Technologie zu begünstigen, sondern die Sicherheitsanforderungen für staatliche Infrastrukturen festzulegen. Die in den kryptografischen Bestandesverzeichnissen enthaltenen sensitiven Informationen sind geschützt.&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">In Kommission des Nationalrats / En commission du Conseil national</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sicherheitspolitik|Medien und Kommunikation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politique de sécurité|Médias et communication</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politica di sicurezza|Media e comunicazione</t>
-  </si>
-  <si>
     <t xml:space="preserve">26.3571</t>
   </si>
   <si>
@@ -533,39 +578,21 @@
     <t xml:space="preserve">2026-06-04</t>
   </si>
   <si>
-    <t xml:space="preserve">EJPD</t>
-  </si>
-  <si>
     <t xml:space="preserve">Von Dänemark lernen. Bei längerfristigen Freiheitsstrafen muss die obligatorische Landesverweisung tatsächlich obligatorisch sein</t>
   </si>
   <si>
     <t xml:space="preserve">S'inspirer du Danemark. En cas de peines privatives de liberté de longue durée, l'expulsion obligatoire doit être réellement obligatoire</t>
   </si>
   <si>
-    <t xml:space="preserve">Imparare dalla Danimarca. Espulsione obbligatoria in caso di pene detentive di lunga durata</t>
-  </si>
-  <si>
     <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé de présenter les modifications législatives nécessaires afin que les étrangers criminels condamnés à une peine privative de liberté d’un an ou plus – qu'elle soit ferme ou assortie d’un sursis total ou partiel – fassent dans tous les cas l'objet d'une expulsion, qui devra obligatoirement être exécutée.&amp;nbsp;&lt;/p&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, die erforderlichen Gesetzesanpassungen vorzulegen, so dass für kriminelle Ausländer bei einer längerfristigen Freiheitsstrafe ab einem Jahr – unabhängig davon, ob diese unbedingt, teilbedingt oder bedingt ausfällt – in jedem Fall zwingend eine Landesverweisung angeordnet und vollzogen werden muss.&amp;nbsp;&lt;/p&gt;</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263571</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263571</t>
   </si>
   <si>
-    <t xml:space="preserve">Strafrecht|Migration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Droit pénal|Politique migratoire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diritto penale|Migrazione</t>
-  </si>
-  <si>
     <t xml:space="preserve">26.3518</t>
   </si>
   <si>
@@ -606,33 +633,6 @@
   </si>
   <si>
     <t xml:space="preserve">Finanze|Imposte|Protezione sociale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fraktion der Schweizerischen Volkspartei</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-03-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Von Dänemark lernen. Bei längerfristigen Freiheitsstrafen muss die obligatorische Landesverweisung obligatorisch sein</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Inspirons-nous du Danemark. Rendons réellement obligatoire l'expulsion en cas de peine privative de liberté de longue durée</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé de présenter les modifications législatives nécessaires pour que lorsqu’un délinquant étranger est condamné à une peine privative de liberté de longue durée (un an au moins), que cette peine soit ferme ou assortie d’un sursis ou d’un sursis partiel, une expulsion soit obligatoirement ordonnée et exécutée.&amp;nbsp;&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Erledigt / Liquidé</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263131</t>
   </si>
   <si>
     <t xml:space="preserve">26.3597</t>
@@ -5885,191 +5885,205 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>20264146</v>
+        <v>20263628</v>
       </c>
       <c r="B3" t="s">
         <v>36</v>
       </c>
       <c r="C3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" t="s">
         <v>37</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>38</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>39</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>40</v>
       </c>
-      <c r="G3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H3"/>
+      <c r="H3" t="s">
+        <v>41</v>
+      </c>
       <c r="I3" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="J3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="K3" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="L3" t="s">
-        <v>42</v>
-      </c>
-      <c r="M3"/>
+        <v>45</v>
+      </c>
+      <c r="M3" t="s">
+        <v>46</v>
+      </c>
       <c r="N3" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="O3" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="P3" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="Q3" t="s">
         <v>35</v>
       </c>
       <c r="R3" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="S3" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="T3" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="U3" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="V3"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>20267829</v>
+        <v>20263131</v>
       </c>
       <c r="B4" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C4" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="D4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" t="s">
-        <v>25</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="E4"/>
       <c r="F4" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="G4" t="s">
         <v>27</v>
       </c>
-      <c r="H4"/>
+      <c r="H4" t="s">
+        <v>56</v>
+      </c>
       <c r="I4" t="s">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="J4" t="s">
-        <v>50</v>
-      </c>
-      <c r="K4"/>
+        <v>58</v>
+      </c>
+      <c r="K4" t="s">
+        <v>59</v>
+      </c>
       <c r="L4" t="s">
-        <v>51</v>
-      </c>
-      <c r="M4"/>
+        <v>60</v>
+      </c>
+      <c r="M4" t="s">
+        <v>61</v>
+      </c>
       <c r="N4" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="O4" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="P4" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="Q4" t="s">
-        <v>35</v>
-      </c>
-      <c r="R4"/>
-      <c r="S4"/>
-      <c r="T4"/>
+        <v>65</v>
+      </c>
+      <c r="R4" t="s">
+        <v>66</v>
+      </c>
+      <c r="S4" t="s">
+        <v>67</v>
+      </c>
+      <c r="T4" t="s">
+        <v>68</v>
+      </c>
       <c r="U4" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="V4"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>20264127</v>
+        <v>20264146</v>
       </c>
       <c r="B5" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="D5" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="E5" t="s">
-        <v>25</v>
+        <v>72</v>
       </c>
       <c r="F5" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="G5" t="s">
         <v>27</v>
       </c>
       <c r="H5"/>
       <c r="I5" t="s">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="J5" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="K5" t="s">
         <v>30</v>
       </c>
-      <c r="L5"/>
-      <c r="M5" t="s">
-        <v>59</v>
-      </c>
+      <c r="L5" t="s">
+        <v>75</v>
+      </c>
+      <c r="M5"/>
       <c r="N5" t="s">
         <v>32</v>
       </c>
       <c r="O5" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="P5" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="Q5" t="s">
-        <v>62</v>
+        <v>35</v>
       </c>
       <c r="R5" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="S5" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="T5" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="U5" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="V5"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>20267687</v>
+        <v>20267829</v>
       </c>
       <c r="B6" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="C6" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="D6" t="s">
         <v>24</v>
@@ -6078,348 +6092,332 @@
         <v>25</v>
       </c>
       <c r="F6" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="G6" t="s">
         <v>27</v>
       </c>
       <c r="H6"/>
       <c r="I6" t="s">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="J6" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="K6"/>
       <c r="L6" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="M6"/>
       <c r="N6" t="s">
         <v>32</v>
       </c>
       <c r="O6" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="P6" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="Q6" t="s">
         <v>35</v>
       </c>
-      <c r="R6" t="s">
-        <v>71</v>
-      </c>
-      <c r="S6" t="s">
-        <v>72</v>
-      </c>
-      <c r="T6" t="s">
+      <c r="R6"/>
+      <c r="S6"/>
+      <c r="T6"/>
+      <c r="U6" t="s">
         <v>73</v>
-      </c>
-      <c r="U6" t="s">
-        <v>56</v>
       </c>
       <c r="V6"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>20267688</v>
+        <v>20264127</v>
       </c>
       <c r="B7" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="C7" t="s">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="D7" t="s">
-        <v>24</v>
+        <v>88</v>
       </c>
       <c r="E7" t="s">
         <v>25</v>
       </c>
       <c r="F7" t="s">
-        <v>56</v>
+        <v>89</v>
       </c>
       <c r="G7" t="s">
         <v>27</v>
       </c>
       <c r="H7"/>
       <c r="I7" t="s">
-        <v>28</v>
+        <v>90</v>
       </c>
       <c r="J7" t="s">
-        <v>75</v>
-      </c>
-      <c r="K7"/>
-      <c r="L7" t="s">
-        <v>76</v>
-      </c>
-      <c r="M7"/>
+        <v>91</v>
+      </c>
+      <c r="K7" t="s">
+        <v>30</v>
+      </c>
+      <c r="L7"/>
+      <c r="M7" t="s">
+        <v>92</v>
+      </c>
       <c r="N7" t="s">
         <v>32</v>
       </c>
       <c r="O7" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="Q7" t="s">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="R7" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="S7" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="T7" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="U7" t="s">
-        <v>56</v>
+        <v>89</v>
       </c>
       <c r="V7"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>20260312</v>
+        <v>20267687</v>
       </c>
       <c r="B8" t="s">
+        <v>98</v>
+      </c>
+      <c r="C8" t="s">
         <v>82</v>
       </c>
-      <c r="C8" t="s">
-        <v>83</v>
-      </c>
       <c r="D8" t="s">
-        <v>84</v>
-      </c>
-      <c r="E8"/>
+        <v>24</v>
+      </c>
+      <c r="E8" t="s">
+        <v>25</v>
+      </c>
       <c r="F8" t="s">
-        <v>85</v>
-      </c>
-      <c r="G8"/>
-      <c r="H8" t="s">
-        <v>86</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="G8" t="s">
+        <v>27</v>
+      </c>
+      <c r="H8"/>
       <c r="I8" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="J8" t="s">
-        <v>88</v>
-      </c>
-      <c r="K8" t="s">
+        <v>99</v>
+      </c>
+      <c r="K8"/>
+      <c r="L8" t="s">
+        <v>100</v>
+      </c>
+      <c r="M8"/>
+      <c r="N8" t="s">
+        <v>32</v>
+      </c>
+      <c r="O8" t="s">
+        <v>101</v>
+      </c>
+      <c r="P8" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>35</v>
+      </c>
+      <c r="R8" t="s">
+        <v>103</v>
+      </c>
+      <c r="S8" t="s">
+        <v>104</v>
+      </c>
+      <c r="T8" t="s">
+        <v>105</v>
+      </c>
+      <c r="U8" t="s">
         <v>89</v>
-      </c>
-      <c r="L8" t="s">
-        <v>90</v>
-      </c>
-      <c r="M8" t="s">
-        <v>91</v>
-      </c>
-      <c r="N8" t="s">
-        <v>92</v>
-      </c>
-      <c r="O8" t="s">
-        <v>93</v>
-      </c>
-      <c r="P8" t="s">
-        <v>94</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>62</v>
-      </c>
-      <c r="R8"/>
-      <c r="S8"/>
-      <c r="T8"/>
-      <c r="U8" t="s">
-        <v>95</v>
       </c>
       <c r="V8"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>20263891</v>
+        <v>20267688</v>
       </c>
       <c r="B9" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="C9" t="s">
-        <v>37</v>
+        <v>82</v>
       </c>
       <c r="D9" t="s">
-        <v>97</v>
+        <v>24</v>
       </c>
       <c r="E9" t="s">
-        <v>98</v>
+        <v>25</v>
       </c>
       <c r="F9" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="G9" t="s">
-        <v>100</v>
-      </c>
-      <c r="H9" t="s">
-        <v>101</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="H9"/>
       <c r="I9" t="s">
-        <v>102</v>
+        <v>28</v>
       </c>
       <c r="J9" t="s">
-        <v>103</v>
-      </c>
-      <c r="K9" t="s">
-        <v>104</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="K9"/>
       <c r="L9" t="s">
-        <v>105</v>
-      </c>
-      <c r="M9" t="s">
-        <v>106</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="M9"/>
       <c r="N9" t="s">
-        <v>107</v>
+        <v>32</v>
       </c>
       <c r="O9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="P9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q9" t="s">
         <v>35</v>
       </c>
       <c r="R9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="S9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="T9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="U9" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="V9"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>20263916</v>
+        <v>20260312</v>
       </c>
       <c r="B10" t="s">
         <v>114</v>
       </c>
       <c r="C10" t="s">
-        <v>37</v>
+        <v>115</v>
       </c>
       <c r="D10" t="s">
-        <v>115</v>
-      </c>
-      <c r="E10" t="s">
-        <v>25</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="E10"/>
       <c r="F10" t="s">
-        <v>99</v>
-      </c>
-      <c r="G10" t="s">
-        <v>100</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="G10"/>
       <c r="H10" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="I10" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="J10" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="K10" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="L10" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="M10" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="N10" t="s">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="O10" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="P10" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="Q10" t="s">
-        <v>35</v>
-      </c>
-      <c r="R10" t="s">
-        <v>124</v>
-      </c>
-      <c r="S10" t="s">
-        <v>125</v>
-      </c>
-      <c r="T10" t="s">
-        <v>126</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="R10"/>
+      <c r="S10"/>
+      <c r="T10"/>
       <c r="U10" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="V10"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>20263968</v>
+        <v>20263891</v>
       </c>
       <c r="B11" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C11" t="s">
+        <v>70</v>
+      </c>
+      <c r="D11" t="s">
         <v>37</v>
       </c>
-      <c r="D11" t="s">
-        <v>128</v>
-      </c>
       <c r="E11" t="s">
+        <v>38</v>
+      </c>
+      <c r="F11" t="s">
         <v>129</v>
       </c>
-      <c r="F11" t="s">
-        <v>99</v>
-      </c>
       <c r="G11" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="H11" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="I11" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J11" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="K11" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L11" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="M11" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="N11" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O11" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="P11" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q11" t="s">
-        <v>138</v>
+        <v>35</v>
       </c>
       <c r="R11" t="s">
         <v>139</v>
@@ -6431,31 +6429,31 @@
         <v>141</v>
       </c>
       <c r="U11" t="s">
-        <v>113</v>
+        <v>142</v>
       </c>
       <c r="V11"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>20263997</v>
+        <v>20263916</v>
       </c>
       <c r="B12" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C12" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="D12" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E12" t="s">
-        <v>144</v>
+        <v>25</v>
       </c>
       <c r="F12" t="s">
-        <v>99</v>
+        <v>129</v>
       </c>
       <c r="G12" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="H12" t="s">
         <v>145</v>
@@ -6476,7 +6474,7 @@
         <v>150</v>
       </c>
       <c r="N12" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O12" t="s">
         <v>151</v>
@@ -6485,7 +6483,7 @@
         <v>152</v>
       </c>
       <c r="Q12" t="s">
-        <v>138</v>
+        <v>35</v>
       </c>
       <c r="R12" t="s">
         <v>153</v>
@@ -6497,34 +6495,34 @@
         <v>155</v>
       </c>
       <c r="U12" t="s">
-        <v>113</v>
+        <v>142</v>
       </c>
       <c r="V12"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>20263628</v>
+        <v>20263968</v>
       </c>
       <c r="B13" t="s">
         <v>156</v>
       </c>
       <c r="C13" t="s">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="D13" t="s">
-        <v>97</v>
+        <v>157</v>
       </c>
       <c r="E13" t="s">
-        <v>98</v>
+        <v>158</v>
       </c>
       <c r="F13" t="s">
-        <v>157</v>
+        <v>129</v>
       </c>
       <c r="G13" t="s">
-        <v>100</v>
+        <v>27</v>
       </c>
       <c r="H13" t="s">
-        <v>158</v>
+        <v>145</v>
       </c>
       <c r="I13" t="s">
         <v>159</v>
@@ -6551,114 +6549,112 @@
         <v>166</v>
       </c>
       <c r="Q13" t="s">
-        <v>35</v>
+        <v>167</v>
       </c>
       <c r="R13" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="S13" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="T13" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="U13" t="s">
-        <v>26</v>
-      </c>
-      <c r="V13" t="s">
-        <v>26</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="V13"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>20263571</v>
+        <v>20263997</v>
       </c>
       <c r="B14" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C14" t="s">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="D14" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E14" t="s">
-        <v>39</v>
+        <v>173</v>
       </c>
       <c r="F14" t="s">
-        <v>172</v>
+        <v>129</v>
       </c>
       <c r="G14" t="s">
-        <v>100</v>
+        <v>27</v>
       </c>
       <c r="H14" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I14" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="J14" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K14" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="L14" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="M14" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N14" t="s">
-        <v>107</v>
+        <v>164</v>
       </c>
       <c r="O14" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P14" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q14" t="s">
-        <v>62</v>
+        <v>167</v>
       </c>
       <c r="R14" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="S14" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="T14" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="U14" t="s">
-        <v>113</v>
+        <v>142</v>
       </c>
       <c r="V14"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>20263518</v>
+        <v>20263571</v>
       </c>
       <c r="B15" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C15" t="s">
         <v>23</v>
       </c>
       <c r="D15" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E15" t="s">
-        <v>186</v>
+        <v>72</v>
       </c>
       <c r="F15" t="s">
         <v>187</v>
       </c>
       <c r="G15" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="H15" t="s">
-        <v>101</v>
+        <v>56</v>
       </c>
       <c r="I15" t="s">
         <v>188</v>
@@ -6667,105 +6663,105 @@
         <v>189</v>
       </c>
       <c r="K15" t="s">
+        <v>59</v>
+      </c>
+      <c r="L15" t="s">
         <v>190</v>
       </c>
-      <c r="L15" t="s">
+      <c r="M15" t="s">
+        <v>61</v>
+      </c>
+      <c r="N15" t="s">
+        <v>136</v>
+      </c>
+      <c r="O15" t="s">
         <v>191</v>
       </c>
-      <c r="M15" t="s">
+      <c r="P15" t="s">
         <v>192</v>
       </c>
-      <c r="N15" t="s">
-        <v>107</v>
-      </c>
-      <c r="O15" t="s">
-        <v>193</v>
-      </c>
-      <c r="P15" t="s">
-        <v>194</v>
-      </c>
       <c r="Q15" t="s">
-        <v>138</v>
+        <v>65</v>
       </c>
       <c r="R15" t="s">
-        <v>195</v>
+        <v>66</v>
       </c>
       <c r="S15" t="s">
-        <v>196</v>
+        <v>67</v>
       </c>
       <c r="T15" t="s">
-        <v>197</v>
+        <v>68</v>
       </c>
       <c r="U15" t="s">
-        <v>113</v>
+        <v>142</v>
       </c>
       <c r="V15"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>20263131</v>
+        <v>20263518</v>
       </c>
       <c r="B16" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="C16" t="s">
         <v>23</v>
       </c>
       <c r="D16" t="s">
-        <v>199</v>
-      </c>
-      <c r="E16"/>
+        <v>194</v>
+      </c>
+      <c r="E16" t="s">
+        <v>195</v>
+      </c>
       <c r="F16" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="G16" t="s">
         <v>27</v>
       </c>
       <c r="H16" t="s">
-        <v>173</v>
+        <v>130</v>
       </c>
       <c r="I16" t="s">
+        <v>197</v>
+      </c>
+      <c r="J16" t="s">
+        <v>198</v>
+      </c>
+      <c r="K16" t="s">
+        <v>199</v>
+      </c>
+      <c r="L16" t="s">
+        <v>200</v>
+      </c>
+      <c r="M16" t="s">
         <v>201</v>
       </c>
-      <c r="J16" t="s">
+      <c r="N16" t="s">
+        <v>136</v>
+      </c>
+      <c r="O16" t="s">
         <v>202</v>
       </c>
-      <c r="K16" t="s">
-        <v>176</v>
-      </c>
-      <c r="L16" t="s">
+      <c r="P16" t="s">
         <v>203</v>
       </c>
-      <c r="M16" t="s">
-        <v>178</v>
-      </c>
-      <c r="N16" t="s">
+      <c r="Q16" t="s">
+        <v>167</v>
+      </c>
+      <c r="R16" t="s">
         <v>204</v>
       </c>
-      <c r="O16" t="s">
+      <c r="S16" t="s">
         <v>205</v>
       </c>
-      <c r="P16" t="s">
+      <c r="T16" t="s">
         <v>206</v>
       </c>
-      <c r="Q16" t="s">
-        <v>62</v>
-      </c>
-      <c r="R16" t="s">
-        <v>181</v>
-      </c>
-      <c r="S16" t="s">
-        <v>182</v>
-      </c>
-      <c r="T16" t="s">
-        <v>183</v>
-      </c>
       <c r="U16" t="s">
-        <v>26</v>
-      </c>
-      <c r="V16" t="s">
-        <v>26</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="V16"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -6778,19 +6774,19 @@
         <v>208</v>
       </c>
       <c r="D17" t="s">
-        <v>97</v>
+        <v>37</v>
       </c>
       <c r="E17" t="s">
-        <v>98</v>
+        <v>38</v>
       </c>
       <c r="F17" t="s">
         <v>209</v>
       </c>
       <c r="G17" t="s">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="H17" t="s">
-        <v>173</v>
+        <v>56</v>
       </c>
       <c r="I17" t="s">
         <v>210</v>
@@ -6808,7 +6804,7 @@
         <v>214</v>
       </c>
       <c r="N17" t="s">
-        <v>204</v>
+        <v>62</v>
       </c>
       <c r="O17" t="s">
         <v>215</v>
@@ -6841,7 +6837,7 @@
         <v>221</v>
       </c>
       <c r="C18" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="D18" t="s">
         <v>24</v>
@@ -6850,13 +6846,13 @@
         <v>25</v>
       </c>
       <c r="F18" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="G18" t="s">
         <v>27</v>
       </c>
       <c r="H18" t="s">
-        <v>145</v>
+        <v>174</v>
       </c>
       <c r="I18" t="s">
         <v>222</v>
@@ -6874,7 +6870,7 @@
         <v>226</v>
       </c>
       <c r="N18" t="s">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="O18" t="s">
         <v>227</v>
@@ -6907,16 +6903,16 @@
         <v>233</v>
       </c>
       <c r="C19" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="D19" t="s">
         <v>234</v>
       </c>
       <c r="E19" t="s">
+        <v>158</v>
+      </c>
+      <c r="F19" t="s">
         <v>129</v>
-      </c>
-      <c r="F19" t="s">
-        <v>99</v>
       </c>
       <c r="G19" t="s">
         <v>27</v>
@@ -6940,7 +6936,7 @@
         <v>240</v>
       </c>
       <c r="N19" t="s">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="O19" t="s">
         <v>241</v>
@@ -6973,16 +6969,16 @@
         <v>248</v>
       </c>
       <c r="C20" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="D20" t="s">
         <v>234</v>
       </c>
       <c r="E20" t="s">
+        <v>158</v>
+      </c>
+      <c r="F20" t="s">
         <v>129</v>
-      </c>
-      <c r="F20" t="s">
-        <v>99</v>
       </c>
       <c r="G20" t="s">
         <v>27</v>
@@ -7006,7 +7002,7 @@
         <v>253</v>
       </c>
       <c r="N20" t="s">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="O20" t="s">
         <v>254</v>
@@ -7039,13 +7035,13 @@
         <v>256</v>
       </c>
       <c r="C21" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="D21" t="s">
         <v>257</v>
       </c>
       <c r="E21" t="s">
-        <v>129</v>
+        <v>158</v>
       </c>
       <c r="F21" t="s">
         <v>258</v>
@@ -7054,7 +7050,7 @@
         <v>27</v>
       </c>
       <c r="H21" t="s">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="I21" t="s">
         <v>259</v>
@@ -7072,7 +7068,7 @@
         <v>263</v>
       </c>
       <c r="N21" t="s">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="O21" t="s">
         <v>264</v>
@@ -7081,7 +7077,7 @@
         <v>265</v>
       </c>
       <c r="Q21" t="s">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="R21" t="s">
         <v>266</v>
@@ -7105,7 +7101,7 @@
         <v>270</v>
       </c>
       <c r="C22" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="D22" t="s">
         <v>24</v>
@@ -7114,13 +7110,13 @@
         <v>25</v>
       </c>
       <c r="F22" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="G22" t="s">
         <v>27</v>
       </c>
       <c r="H22" t="s">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="I22" t="s">
         <v>271</v>
@@ -7138,7 +7134,7 @@
         <v>275</v>
       </c>
       <c r="N22" t="s">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="O22" t="s">
         <v>276</v>
@@ -7174,7 +7170,7 @@
         <v>23</v>
       </c>
       <c r="D23" t="s">
-        <v>115</v>
+        <v>144</v>
       </c>
       <c r="E23" t="s">
         <v>25</v>
@@ -7183,10 +7179,10 @@
         <v>282</v>
       </c>
       <c r="G23" t="s">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="H23" t="s">
-        <v>145</v>
+        <v>174</v>
       </c>
       <c r="I23" t="s">
         <v>283</v>
@@ -7204,7 +7200,7 @@
         <v>287</v>
       </c>
       <c r="N23" t="s">
-        <v>92</v>
+        <v>124</v>
       </c>
       <c r="O23" t="s">
         <v>288</v>
@@ -7237,13 +7233,13 @@
         <v>294</v>
       </c>
       <c r="C24" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="D24" t="s">
         <v>234</v>
       </c>
       <c r="E24" t="s">
-        <v>129</v>
+        <v>158</v>
       </c>
       <c r="F24" t="s">
         <v>295</v>
@@ -7270,7 +7266,7 @@
         <v>300</v>
       </c>
       <c r="N24" t="s">
-        <v>204</v>
+        <v>62</v>
       </c>
       <c r="O24" t="s">
         <v>301</v>
@@ -7291,7 +7287,7 @@
         <v>246</v>
       </c>
       <c r="U24" t="s">
-        <v>99</v>
+        <v>129</v>
       </c>
       <c r="V24"/>
     </row>
@@ -7306,19 +7302,19 @@
         <v>208</v>
       </c>
       <c r="D25" t="s">
-        <v>97</v>
+        <v>37</v>
       </c>
       <c r="E25" t="s">
-        <v>98</v>
+        <v>38</v>
       </c>
       <c r="F25" t="s">
         <v>304</v>
       </c>
       <c r="G25" t="s">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="H25" t="s">
-        <v>173</v>
+        <v>56</v>
       </c>
       <c r="I25" t="s">
         <v>305</v>
@@ -7369,7 +7365,7 @@
         <v>317</v>
       </c>
       <c r="C26" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="D26" t="s">
         <v>24</v>
@@ -7384,7 +7380,7 @@
         <v>27</v>
       </c>
       <c r="H26" t="s">
-        <v>173</v>
+        <v>56</v>
       </c>
       <c r="I26" t="s">
         <v>319</v>
@@ -7400,7 +7396,7 @@
         <v>322</v>
       </c>
       <c r="N26" t="s">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="O26" t="s">
         <v>323</v>
@@ -7433,7 +7429,7 @@
         <v>329</v>
       </c>
       <c r="C27" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="D27" t="s">
         <v>24</v>
@@ -7464,7 +7460,7 @@
         <v>334</v>
       </c>
       <c r="N27" t="s">
-        <v>204</v>
+        <v>62</v>
       </c>
       <c r="O27" t="s">
         <v>335</v>
@@ -7497,13 +7493,13 @@
         <v>340</v>
       </c>
       <c r="C28" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="D28" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="E28" t="s">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="F28" t="s">
         <v>330</v>
@@ -7528,7 +7524,7 @@
         <v>344</v>
       </c>
       <c r="N28" t="s">
-        <v>204</v>
+        <v>62</v>
       </c>
       <c r="O28" t="s">
         <v>345</v>
@@ -7561,7 +7557,7 @@
         <v>350</v>
       </c>
       <c r="C29" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="D29" t="s">
         <v>351</v>
@@ -7576,7 +7572,7 @@
         <v>27</v>
       </c>
       <c r="H29" t="s">
-        <v>145</v>
+        <v>174</v>
       </c>
       <c r="I29" t="s">
         <v>353</v>
@@ -7594,7 +7590,7 @@
         <v>357</v>
       </c>
       <c r="N29" t="s">
-        <v>204</v>
+        <v>62</v>
       </c>
       <c r="O29" t="s">
         <v>358</v>
@@ -7627,22 +7623,22 @@
         <v>364</v>
       </c>
       <c r="C30" t="s">
+        <v>70</v>
+      </c>
+      <c r="D30" t="s">
         <v>37</v>
       </c>
-      <c r="D30" t="s">
-        <v>97</v>
-      </c>
       <c r="E30" t="s">
-        <v>98</v>
+        <v>38</v>
       </c>
       <c r="F30" t="s">
-        <v>200</v>
+        <v>55</v>
       </c>
       <c r="G30" t="s">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="H30" t="s">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="I30" t="s">
         <v>365</v>
@@ -7660,7 +7656,7 @@
         <v>369</v>
       </c>
       <c r="N30" t="s">
-        <v>204</v>
+        <v>62</v>
       </c>
       <c r="O30" t="s">
         <v>370</v>
@@ -7699,7 +7695,7 @@
         <v>376</v>
       </c>
       <c r="E31" t="s">
-        <v>129</v>
+        <v>158</v>
       </c>
       <c r="F31" t="s">
         <v>282</v>
@@ -7726,7 +7722,7 @@
         <v>381</v>
       </c>
       <c r="N31" t="s">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="O31" t="s">
         <v>382</v>
@@ -7735,7 +7731,7 @@
         <v>383</v>
       </c>
       <c r="Q31" t="s">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="R31" t="s">
         <v>384</v>
@@ -7759,7 +7755,7 @@
         <v>388</v>
       </c>
       <c r="C32" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="D32" t="s">
         <v>389</v>
@@ -7774,7 +7770,7 @@
         <v>27</v>
       </c>
       <c r="H32" t="s">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="I32" t="s">
         <v>390</v>
@@ -7792,7 +7788,7 @@
         <v>394</v>
       </c>
       <c r="N32" t="s">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="O32" t="s">
         <v>395</v>
@@ -7838,7 +7834,7 @@
         <v>27</v>
       </c>
       <c r="H33" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="I33" t="s">
         <v>399</v>
@@ -7856,7 +7852,7 @@
         <v>403</v>
       </c>
       <c r="N33" t="s">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="O33" t="s">
         <v>404</v>
@@ -7889,13 +7885,13 @@
         <v>410</v>
       </c>
       <c r="C34" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="D34" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="E34" t="s">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="F34" t="s">
         <v>282</v>
@@ -7904,7 +7900,7 @@
         <v>27</v>
       </c>
       <c r="H34" t="s">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="I34" t="s">
         <v>411</v>
@@ -7922,7 +7918,7 @@
         <v>415</v>
       </c>
       <c r="N34" t="s">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="O34" t="s">
         <v>416</v>
@@ -7934,13 +7930,13 @@
         <v>35</v>
       </c>
       <c r="R34" t="s">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="S34" t="s">
-        <v>80</v>
+        <v>112</v>
       </c>
       <c r="T34" t="s">
-        <v>81</v>
+        <v>113</v>
       </c>
       <c r="U34" t="s">
         <v>409</v>
@@ -7955,13 +7951,13 @@
         <v>418</v>
       </c>
       <c r="C35" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="D35" t="s">
         <v>419</v>
       </c>
       <c r="E35" t="s">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="F35" t="s">
         <v>420</v>
@@ -7988,7 +7984,7 @@
         <v>426</v>
       </c>
       <c r="N35" t="s">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="O35" t="s">
         <v>427</v>
@@ -7997,7 +7993,7 @@
         <v>428</v>
       </c>
       <c r="Q35" t="s">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="R35" t="s">
         <v>429</v>
@@ -8027,16 +8023,16 @@
         <v>433</v>
       </c>
       <c r="E36" t="s">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="F36" t="s">
-        <v>200</v>
+        <v>55</v>
       </c>
       <c r="G36" t="s">
         <v>27</v>
       </c>
       <c r="H36" t="s">
-        <v>145</v>
+        <v>174</v>
       </c>
       <c r="I36" t="s">
         <v>434</v>
@@ -8054,7 +8050,7 @@
         <v>438</v>
       </c>
       <c r="N36" t="s">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="O36" t="s">
         <v>439</v>
@@ -8063,7 +8059,7 @@
         <v>440</v>
       </c>
       <c r="Q36" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="R36" t="s">
         <v>441</v>
@@ -8087,13 +8083,13 @@
         <v>445</v>
       </c>
       <c r="C37" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="D37" t="s">
         <v>446</v>
       </c>
       <c r="E37" t="s">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="F37" t="s">
         <v>447</v>
@@ -8102,7 +8098,7 @@
         <v>27</v>
       </c>
       <c r="H37" t="s">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="I37" t="s">
         <v>448</v>
@@ -8120,7 +8116,7 @@
         <v>452</v>
       </c>
       <c r="N37" t="s">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="O37" t="s">
         <v>453</v>
@@ -8132,13 +8128,13 @@
         <v>243</v>
       </c>
       <c r="R37" t="s">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="S37" t="s">
-        <v>80</v>
+        <v>112</v>
       </c>
       <c r="T37" t="s">
-        <v>81</v>
+        <v>113</v>
       </c>
       <c r="U37" t="s">
         <v>444</v>
@@ -8156,19 +8152,19 @@
         <v>23</v>
       </c>
       <c r="D38" t="s">
-        <v>97</v>
+        <v>37</v>
       </c>
       <c r="E38" t="s">
-        <v>98</v>
+        <v>38</v>
       </c>
       <c r="F38" t="s">
         <v>456</v>
       </c>
       <c r="G38" t="s">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="H38" t="s">
-        <v>173</v>
+        <v>56</v>
       </c>
       <c r="I38" t="s">
         <v>457</v>
@@ -8186,7 +8182,7 @@
         <v>461</v>
       </c>
       <c r="N38" t="s">
-        <v>164</v>
+        <v>47</v>
       </c>
       <c r="O38" t="s">
         <v>462</v>
@@ -8198,13 +8194,13 @@
         <v>35</v>
       </c>
       <c r="R38" t="s">
-        <v>63</v>
+        <v>95</v>
       </c>
       <c r="S38" t="s">
-        <v>64</v>
+        <v>96</v>
       </c>
       <c r="T38" t="s">
-        <v>65</v>
+        <v>97</v>
       </c>
       <c r="U38" t="s">
         <v>464</v>
@@ -8219,7 +8215,7 @@
         <v>465</v>
       </c>
       <c r="C39" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="D39" t="s">
         <v>351</v>
@@ -8250,7 +8246,7 @@
         <v>470</v>
       </c>
       <c r="N39" t="s">
-        <v>204</v>
+        <v>62</v>
       </c>
       <c r="O39" t="s">
         <v>471</v>
@@ -8283,7 +8279,7 @@
         <v>477</v>
       </c>
       <c r="C40" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="D40" t="s">
         <v>478</v>
@@ -8298,7 +8294,7 @@
         <v>27</v>
       </c>
       <c r="H40" t="s">
-        <v>173</v>
+        <v>56</v>
       </c>
       <c r="I40" t="s">
         <v>480</v>
@@ -8314,7 +8310,7 @@
         <v>483</v>
       </c>
       <c r="N40" t="s">
-        <v>204</v>
+        <v>62</v>
       </c>
       <c r="O40" t="s">
         <v>484</v>
@@ -8323,7 +8319,7 @@
         <v>485</v>
       </c>
       <c r="Q40" t="s">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="R40" t="s">
         <v>486</v>
@@ -8351,14 +8347,14 @@
       </c>
       <c r="D41"/>
       <c r="E41" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="F41" t="s">
         <v>491</v>
       </c>
       <c r="G41"/>
       <c r="H41" t="s">
-        <v>173</v>
+        <v>56</v>
       </c>
       <c r="I41" t="s">
         <v>492</v>
@@ -8372,7 +8368,7 @@
       <c r="L41"/>
       <c r="M41"/>
       <c r="N41" t="s">
-        <v>204</v>
+        <v>62</v>
       </c>
       <c r="O41" t="s">
         <v>495</v>
@@ -8405,13 +8401,13 @@
         <v>497</v>
       </c>
       <c r="C42" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="D42" t="s">
         <v>376</v>
       </c>
       <c r="E42" t="s">
-        <v>129</v>
+        <v>158</v>
       </c>
       <c r="F42" t="s">
         <v>498</v>
@@ -8420,7 +8416,7 @@
         <v>27</v>
       </c>
       <c r="H42" t="s">
-        <v>145</v>
+        <v>174</v>
       </c>
       <c r="I42" t="s">
         <v>499</v>
@@ -8436,7 +8432,7 @@
         <v>502</v>
       </c>
       <c r="N42" t="s">
-        <v>204</v>
+        <v>62</v>
       </c>
       <c r="O42" t="s">
         <v>503</v>
@@ -8445,7 +8441,7 @@
         <v>504</v>
       </c>
       <c r="Q42" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="R42" t="s">
         <v>505</v>
@@ -8475,7 +8471,7 @@
         <v>509</v>
       </c>
       <c r="E43" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="F43" t="s">
         <v>510</v>
@@ -8484,7 +8480,7 @@
         <v>27</v>
       </c>
       <c r="H43" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="I43" t="s">
         <v>511</v>
@@ -8502,7 +8498,7 @@
         <v>515</v>
       </c>
       <c r="N43" t="s">
-        <v>204</v>
+        <v>62</v>
       </c>
       <c r="O43" t="s">
         <v>516</v>
@@ -8511,16 +8507,16 @@
         <v>517</v>
       </c>
       <c r="Q43" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="R43" t="s">
-        <v>110</v>
+        <v>139</v>
       </c>
       <c r="S43" t="s">
-        <v>111</v>
+        <v>140</v>
       </c>
       <c r="T43" t="s">
-        <v>112</v>
+        <v>141</v>
       </c>
       <c r="U43" t="s">
         <v>476</v>
@@ -8535,7 +8531,7 @@
         <v>518</v>
       </c>
       <c r="C44" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="D44" t="s">
         <v>519</v>
@@ -8550,7 +8546,7 @@
         <v>27</v>
       </c>
       <c r="H44" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="I44" t="s">
         <v>521</v>
@@ -8568,7 +8564,7 @@
         <v>525</v>
       </c>
       <c r="N44" t="s">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="O44" t="s">
         <v>526</v>
@@ -8601,13 +8597,13 @@
         <v>531</v>
       </c>
       <c r="C45" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="D45" t="s">
         <v>532</v>
       </c>
       <c r="E45" t="s">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="F45" t="s">
         <v>456</v>
@@ -8616,7 +8612,7 @@
         <v>27</v>
       </c>
       <c r="H45" t="s">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="I45" t="s">
         <v>533</v>
@@ -8634,7 +8630,7 @@
         <v>537</v>
       </c>
       <c r="N45" t="s">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="O45" t="s">
         <v>538</v>
@@ -8643,7 +8639,7 @@
         <v>539</v>
       </c>
       <c r="Q45" t="s">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="R45" t="s">
         <v>540</v>
@@ -8670,19 +8666,19 @@
         <v>23</v>
       </c>
       <c r="D46" t="s">
-        <v>97</v>
+        <v>37</v>
       </c>
       <c r="E46" t="s">
-        <v>98</v>
+        <v>38</v>
       </c>
       <c r="F46" t="s">
         <v>544</v>
       </c>
       <c r="G46" t="s">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="H46" t="s">
-        <v>158</v>
+        <v>41</v>
       </c>
       <c r="I46" t="s">
         <v>545</v>
@@ -8700,7 +8696,7 @@
         <v>549</v>
       </c>
       <c r="N46" t="s">
-        <v>92</v>
+        <v>124</v>
       </c>
       <c r="O46" t="s">
         <v>550</v>
@@ -8736,19 +8732,19 @@
         <v>208</v>
       </c>
       <c r="D47" t="s">
-        <v>97</v>
+        <v>37</v>
       </c>
       <c r="E47" t="s">
-        <v>98</v>
+        <v>38</v>
       </c>
       <c r="F47" t="s">
         <v>544</v>
       </c>
       <c r="G47" t="s">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="H47" t="s">
-        <v>173</v>
+        <v>56</v>
       </c>
       <c r="I47" t="s">
         <v>556</v>
@@ -8799,22 +8795,22 @@
         <v>566</v>
       </c>
       <c r="C48" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="D48" t="s">
         <v>567</v>
       </c>
       <c r="E48" t="s">
-        <v>98</v>
+        <v>38</v>
       </c>
       <c r="F48" t="s">
         <v>568</v>
       </c>
       <c r="G48" t="s">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="H48" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="I48" t="s">
         <v>569</v>
@@ -8832,7 +8828,7 @@
         <v>573</v>
       </c>
       <c r="N48" t="s">
-        <v>204</v>
+        <v>62</v>
       </c>
       <c r="O48" t="s">
         <v>574</v>
@@ -8841,7 +8837,7 @@
         <v>575</v>
       </c>
       <c r="Q48" t="s">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="R48" t="s">
         <v>576</v>
@@ -8871,7 +8867,7 @@
         <v>433</v>
       </c>
       <c r="E49" t="s">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="F49" t="s">
         <v>352</v>
@@ -8880,7 +8876,7 @@
         <v>27</v>
       </c>
       <c r="H49" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="I49" t="s">
         <v>580</v>
@@ -8898,7 +8894,7 @@
         <v>584</v>
       </c>
       <c r="N49" t="s">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="O49" t="s">
         <v>585</v>
@@ -8907,16 +8903,16 @@
         <v>586</v>
       </c>
       <c r="Q49" t="s">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="R49" t="s">
-        <v>110</v>
+        <v>139</v>
       </c>
       <c r="S49" t="s">
-        <v>111</v>
+        <v>140</v>
       </c>
       <c r="T49" t="s">
-        <v>112</v>
+        <v>141</v>
       </c>
       <c r="U49" t="s">
         <v>476</v>
@@ -8931,7 +8927,7 @@
         <v>587</v>
       </c>
       <c r="C50" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="D50" t="s">
         <v>588</v>
@@ -8946,7 +8942,7 @@
         <v>27</v>
       </c>
       <c r="H50" t="s">
-        <v>158</v>
+        <v>41</v>
       </c>
       <c r="I50" t="s">
         <v>590</v>
@@ -8962,7 +8958,7 @@
         <v>593</v>
       </c>
       <c r="N50" t="s">
-        <v>204</v>
+        <v>62</v>
       </c>
       <c r="O50" t="s">
         <v>594</v>
@@ -8971,7 +8967,7 @@
         <v>595</v>
       </c>
       <c r="Q50" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="R50" t="s">
         <v>596</v>
@@ -8995,13 +8991,13 @@
         <v>599</v>
       </c>
       <c r="C51" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="D51" t="s">
         <v>419</v>
       </c>
       <c r="E51" t="s">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="F51" t="s">
         <v>589</v>
@@ -9010,7 +9006,7 @@
         <v>27</v>
       </c>
       <c r="H51" t="s">
-        <v>173</v>
+        <v>56</v>
       </c>
       <c r="I51" t="s">
         <v>600</v>
@@ -9026,7 +9022,7 @@
         <v>603</v>
       </c>
       <c r="N51" t="s">
-        <v>204</v>
+        <v>62</v>
       </c>
       <c r="O51" t="s">
         <v>604</v>
@@ -9035,16 +9031,16 @@
         <v>605</v>
       </c>
       <c r="Q51" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="R51" t="s">
-        <v>181</v>
+        <v>66</v>
       </c>
       <c r="S51" t="s">
-        <v>182</v>
+        <v>67</v>
       </c>
       <c r="T51" t="s">
-        <v>183</v>
+        <v>68</v>
       </c>
       <c r="U51" t="s">
         <v>476</v>
@@ -9072,7 +9068,7 @@
         <v>27</v>
       </c>
       <c r="H52" t="s">
-        <v>145</v>
+        <v>174</v>
       </c>
       <c r="I52" t="s">
         <v>609</v>
@@ -9099,7 +9095,7 @@
         <v>615</v>
       </c>
       <c r="Q52" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="R52" t="s">
         <v>616</v>
@@ -9129,16 +9125,16 @@
         <v>620</v>
       </c>
       <c r="E53" t="s">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="F53" t="s">
         <v>621</v>
       </c>
       <c r="G53" t="s">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="H53" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="I53" t="s">
         <v>622</v>
@@ -9156,7 +9152,7 @@
         <v>626</v>
       </c>
       <c r="N53" t="s">
-        <v>204</v>
+        <v>62</v>
       </c>
       <c r="O53" t="s">
         <v>627</v>
@@ -9165,7 +9161,7 @@
         <v>628</v>
       </c>
       <c r="Q53" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="R53" t="s">
         <v>629</v>
@@ -9195,7 +9191,7 @@
         <v>633</v>
       </c>
       <c r="E54" t="s">
-        <v>129</v>
+        <v>158</v>
       </c>
       <c r="F54" t="s">
         <v>621</v>
@@ -9204,7 +9200,7 @@
         <v>27</v>
       </c>
       <c r="H54" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="I54" t="s">
         <v>634</v>
@@ -9222,7 +9218,7 @@
         <v>638</v>
       </c>
       <c r="N54" t="s">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="O54" t="s">
         <v>639</v>
@@ -9231,7 +9227,7 @@
         <v>640</v>
       </c>
       <c r="Q54" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="R54" t="s">
         <v>429</v>
@@ -9255,7 +9251,7 @@
         <v>641</v>
       </c>
       <c r="C55" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="D55" t="s">
         <v>389</v>
@@ -9270,7 +9266,7 @@
         <v>27</v>
       </c>
       <c r="H55" t="s">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="I55" t="s">
         <v>642</v>
@@ -9288,7 +9284,7 @@
         <v>646</v>
       </c>
       <c r="N55" t="s">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="O55" t="s">
         <v>647</v>
@@ -9300,13 +9296,13 @@
         <v>243</v>
       </c>
       <c r="R55" t="s">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="S55" t="s">
-        <v>80</v>
+        <v>112</v>
       </c>
       <c r="T55" t="s">
-        <v>81</v>
+        <v>113</v>
       </c>
       <c r="U55" t="s">
         <v>476</v>
@@ -9324,7 +9320,7 @@
         <v>23</v>
       </c>
       <c r="D56" t="s">
-        <v>115</v>
+        <v>144</v>
       </c>
       <c r="E56" t="s">
         <v>25</v>
@@ -9333,10 +9329,10 @@
         <v>621</v>
       </c>
       <c r="G56" t="s">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="H56" t="s">
-        <v>145</v>
+        <v>174</v>
       </c>
       <c r="I56" t="s">
         <v>650</v>
@@ -9354,7 +9350,7 @@
         <v>654</v>
       </c>
       <c r="N56" t="s">
-        <v>92</v>
+        <v>124</v>
       </c>
       <c r="O56" t="s">
         <v>655</v>
@@ -9387,13 +9383,13 @@
         <v>660</v>
       </c>
       <c r="C57" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="D57" t="s">
         <v>661</v>
       </c>
       <c r="E57" t="s">
-        <v>98</v>
+        <v>38</v>
       </c>
       <c r="F57" t="s">
         <v>662</v>
@@ -9402,7 +9398,7 @@
         <v>27</v>
       </c>
       <c r="H57" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="I57" t="s">
         <v>663</v>
@@ -9420,7 +9416,7 @@
         <v>667</v>
       </c>
       <c r="N57" t="s">
-        <v>204</v>
+        <v>62</v>
       </c>
       <c r="O57" t="s">
         <v>668</v>
@@ -9453,19 +9449,19 @@
         <v>670</v>
       </c>
       <c r="C58" t="s">
+        <v>70</v>
+      </c>
+      <c r="D58" t="s">
         <v>37</v>
       </c>
-      <c r="D58" t="s">
-        <v>97</v>
-      </c>
       <c r="E58" t="s">
-        <v>98</v>
+        <v>38</v>
       </c>
       <c r="F58" t="s">
         <v>671</v>
       </c>
       <c r="G58" t="s">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="H58" t="s">
         <v>235</v>
@@ -9486,7 +9482,7 @@
         <v>676</v>
       </c>
       <c r="N58" t="s">
-        <v>204</v>
+        <v>62</v>
       </c>
       <c r="O58" t="s">
         <v>677</v>
@@ -9519,13 +9515,13 @@
         <v>682</v>
       </c>
       <c r="C59" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="D59" t="s">
         <v>683</v>
       </c>
       <c r="E59" t="s">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="F59" t="s">
         <v>671</v>
@@ -9534,7 +9530,7 @@
         <v>27</v>
       </c>
       <c r="H59" t="s">
-        <v>158</v>
+        <v>41</v>
       </c>
       <c r="I59" t="s">
         <v>684</v>
@@ -9552,7 +9548,7 @@
         <v>688</v>
       </c>
       <c r="N59" t="s">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="O59" t="s">
         <v>689</v>
@@ -9561,7 +9557,7 @@
         <v>690</v>
       </c>
       <c r="Q59" t="s">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="R59" t="s">
         <v>691</v>
@@ -9585,22 +9581,22 @@
         <v>694</v>
       </c>
       <c r="C60" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="D60" t="s">
         <v>695</v>
       </c>
       <c r="E60" t="s">
-        <v>98</v>
+        <v>38</v>
       </c>
       <c r="F60" t="s">
         <v>696</v>
       </c>
       <c r="G60" t="s">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="H60" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="I60" t="s">
         <v>697</v>
@@ -9618,7 +9614,7 @@
         <v>701</v>
       </c>
       <c r="N60" t="s">
-        <v>204</v>
+        <v>62</v>
       </c>
       <c r="O60" t="s">
         <v>702</v>
@@ -9654,10 +9650,10 @@
         <v>708</v>
       </c>
       <c r="D61" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="E61" t="s">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="F61" t="s">
         <v>709</v>
@@ -9666,7 +9662,7 @@
         <v>27</v>
       </c>
       <c r="H61" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="I61" t="s">
         <v>710</v>
@@ -9732,7 +9728,7 @@
         <v>27</v>
       </c>
       <c r="H62" t="s">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="I62" t="s">
         <v>724</v>
@@ -9750,7 +9746,7 @@
         <v>728</v>
       </c>
       <c r="N62" t="s">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="O62" t="s">
         <v>729</v>
@@ -9759,16 +9755,16 @@
         <v>730</v>
       </c>
       <c r="Q62" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="R62" t="s">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="S62" t="s">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="T62" t="s">
-        <v>47</v>
+        <v>80</v>
       </c>
       <c r="U62" t="s">
         <v>476</v>
@@ -9783,13 +9779,13 @@
         <v>731</v>
       </c>
       <c r="C63" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="D63" t="s">
-        <v>143</v>
+        <v>172</v>
       </c>
       <c r="E63" t="s">
-        <v>144</v>
+        <v>173</v>
       </c>
       <c r="F63" t="s">
         <v>723</v>
@@ -9798,7 +9794,7 @@
         <v>27</v>
       </c>
       <c r="H63" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="I63" t="s">
         <v>732</v>
@@ -9814,7 +9810,7 @@
         <v>735</v>
       </c>
       <c r="N63" t="s">
-        <v>204</v>
+        <v>62</v>
       </c>
       <c r="O63" t="s">
         <v>736</v>
@@ -9847,13 +9843,13 @@
         <v>738</v>
       </c>
       <c r="C64" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="D64" t="s">
         <v>739</v>
       </c>
       <c r="E64" t="s">
-        <v>98</v>
+        <v>38</v>
       </c>
       <c r="F64" t="s">
         <v>723</v>
@@ -9878,7 +9874,7 @@
         <v>743</v>
       </c>
       <c r="N64" t="s">
-        <v>204</v>
+        <v>62</v>
       </c>
       <c r="O64" t="s">
         <v>744</v>
@@ -9887,7 +9883,7 @@
         <v>745</v>
       </c>
       <c r="Q64" t="s">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="R64" t="s">
         <v>746</v>
@@ -9911,13 +9907,13 @@
         <v>749</v>
       </c>
       <c r="C65" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="D65" t="s">
         <v>683</v>
       </c>
       <c r="E65" t="s">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="F65" t="s">
         <v>750</v>
@@ -9926,7 +9922,7 @@
         <v>27</v>
       </c>
       <c r="H65" t="s">
-        <v>173</v>
+        <v>56</v>
       </c>
       <c r="I65" t="s">
         <v>751</v>
@@ -9942,7 +9938,7 @@
         <v>754</v>
       </c>
       <c r="N65" t="s">
-        <v>204</v>
+        <v>62</v>
       </c>
       <c r="O65" t="s">
         <v>755</v>
@@ -9975,13 +9971,13 @@
         <v>760</v>
       </c>
       <c r="C66" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="D66" t="s">
         <v>761</v>
       </c>
       <c r="E66" t="s">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="F66" t="s">
         <v>762</v>
@@ -9990,7 +9986,7 @@
         <v>27</v>
       </c>
       <c r="H66" t="s">
-        <v>158</v>
+        <v>41</v>
       </c>
       <c r="I66" t="s">
         <v>763</v>
@@ -10008,7 +10004,7 @@
         <v>767</v>
       </c>
       <c r="N66" t="s">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="O66" t="s">
         <v>768</v>
@@ -10017,7 +10013,7 @@
         <v>769</v>
       </c>
       <c r="Q66" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="R66" t="s">
         <v>770</v>
@@ -10041,13 +10037,13 @@
         <v>773</v>
       </c>
       <c r="C67" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="D67" t="s">
         <v>761</v>
       </c>
       <c r="E67" t="s">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="F67" t="s">
         <v>762</v>
@@ -10056,7 +10052,7 @@
         <v>27</v>
       </c>
       <c r="H67" t="s">
-        <v>158</v>
+        <v>41</v>
       </c>
       <c r="I67" t="s">
         <v>774</v>
@@ -10072,7 +10068,7 @@
         <v>777</v>
       </c>
       <c r="N67" t="s">
-        <v>204</v>
+        <v>62</v>
       </c>
       <c r="O67" t="s">
         <v>778</v>
@@ -10081,7 +10077,7 @@
         <v>779</v>
       </c>
       <c r="Q67" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="R67" t="s">
         <v>780</v>
@@ -10105,7 +10101,7 @@
         <v>783</v>
       </c>
       <c r="C68" t="s">
-        <v>83</v>
+        <v>115</v>
       </c>
       <c r="D68" t="s">
         <v>784</v>
@@ -10116,7 +10112,7 @@
       </c>
       <c r="G68"/>
       <c r="H68" t="s">
-        <v>173</v>
+        <v>56</v>
       </c>
       <c r="I68" t="s">
         <v>786</v>
@@ -10134,7 +10130,7 @@
         <v>790</v>
       </c>
       <c r="N68" t="s">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="O68" t="s">
         <v>791</v>
@@ -10143,7 +10139,7 @@
         <v>792</v>
       </c>
       <c r="Q68" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="R68"/>
       <c r="S68"/>
@@ -10161,7 +10157,7 @@
         <v>793</v>
       </c>
       <c r="C69" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="D69" t="s">
         <v>794</v>
@@ -10176,7 +10172,7 @@
         <v>27</v>
       </c>
       <c r="H69" t="s">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="I69" t="s">
         <v>796</v>
@@ -10194,7 +10190,7 @@
         <v>800</v>
       </c>
       <c r="N69" t="s">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="O69" t="s">
         <v>801</v>
@@ -10203,7 +10199,7 @@
         <v>802</v>
       </c>
       <c r="Q69" t="s">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="R69" t="s">
         <v>803</v>
@@ -10227,7 +10223,7 @@
         <v>806</v>
       </c>
       <c r="C70" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="D70" t="s">
         <v>807</v>
@@ -10242,7 +10238,7 @@
         <v>27</v>
       </c>
       <c r="H70" t="s">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="I70" t="s">
         <v>808</v>
@@ -10260,7 +10256,7 @@
         <v>812</v>
       </c>
       <c r="N70" t="s">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="O70" t="s">
         <v>813</v>
@@ -10269,7 +10265,7 @@
         <v>814</v>
       </c>
       <c r="Q70" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="R70" t="s">
         <v>815</v>
@@ -10299,7 +10295,7 @@
         <v>819</v>
       </c>
       <c r="E71" t="s">
-        <v>98</v>
+        <v>38</v>
       </c>
       <c r="F71" t="s">
         <v>795</v>
@@ -10308,7 +10304,7 @@
         <v>27</v>
       </c>
       <c r="H71" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="I71" t="s">
         <v>820</v>
@@ -10335,7 +10331,7 @@
         <v>827</v>
       </c>
       <c r="Q71" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="R71" t="s">
         <v>828</v>
@@ -10372,7 +10368,7 @@
         <v>27</v>
       </c>
       <c r="H72" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="I72" t="s">
         <v>833</v>
@@ -10390,7 +10386,7 @@
         <v>837</v>
       </c>
       <c r="N72" t="s">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="O72" t="s">
         <v>838</v>
@@ -10423,7 +10419,7 @@
         <v>843</v>
       </c>
       <c r="C73" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="D73" t="s">
         <v>844</v>
@@ -10438,7 +10434,7 @@
         <v>27</v>
       </c>
       <c r="H73" t="s">
-        <v>145</v>
+        <v>174</v>
       </c>
       <c r="I73" t="s">
         <v>845</v>
@@ -10456,7 +10452,7 @@
         <v>849</v>
       </c>
       <c r="N73" t="s">
-        <v>204</v>
+        <v>62</v>
       </c>
       <c r="O73" t="s">
         <v>850</v>
@@ -10465,7 +10461,7 @@
         <v>851</v>
       </c>
       <c r="Q73" t="s">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="R73" t="s">
         <v>852</v>
@@ -10489,7 +10485,7 @@
         <v>855</v>
       </c>
       <c r="C74" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="D74" t="s">
         <v>856</v>
@@ -10504,7 +10500,7 @@
         <v>27</v>
       </c>
       <c r="H74" t="s">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="I74" t="s">
         <v>858</v>
@@ -10522,7 +10518,7 @@
         <v>862</v>
       </c>
       <c r="N74" t="s">
-        <v>204</v>
+        <v>62</v>
       </c>
       <c r="O74" t="s">
         <v>863</v>
@@ -10534,13 +10530,13 @@
         <v>243</v>
       </c>
       <c r="R74" t="s">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="S74" t="s">
-        <v>80</v>
+        <v>112</v>
       </c>
       <c r="T74" t="s">
-        <v>81</v>
+        <v>113</v>
       </c>
       <c r="U74" t="s">
         <v>476</v>
@@ -10568,7 +10564,7 @@
         <v>27</v>
       </c>
       <c r="H75" t="s">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="I75" t="s">
         <v>867</v>
@@ -10595,7 +10591,7 @@
         <v>873</v>
       </c>
       <c r="Q75" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="R75" t="s">
         <v>874</v>
@@ -10619,13 +10615,13 @@
         <v>877</v>
       </c>
       <c r="C76" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="D76" t="s">
         <v>633</v>
       </c>
       <c r="E76" t="s">
-        <v>129</v>
+        <v>158</v>
       </c>
       <c r="F76" t="s">
         <v>857</v>
@@ -10634,7 +10630,7 @@
         <v>27</v>
       </c>
       <c r="H76" t="s">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="I76" t="s">
         <v>878</v>
@@ -10652,7 +10648,7 @@
         <v>882</v>
       </c>
       <c r="N76" t="s">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="O76" t="s">
         <v>883</v>
@@ -10685,7 +10681,7 @@
         <v>888</v>
       </c>
       <c r="C77" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="D77" t="s">
         <v>889</v>
@@ -10697,10 +10693,10 @@
         <v>890</v>
       </c>
       <c r="G77" t="s">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="H77" t="s">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="I77" t="s">
         <v>891</v>
@@ -10718,7 +10714,7 @@
         <v>895</v>
       </c>
       <c r="N77" t="s">
-        <v>204</v>
+        <v>62</v>
       </c>
       <c r="O77" t="s">
         <v>896</v>
@@ -10727,7 +10723,7 @@
         <v>897</v>
       </c>
       <c r="Q77" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="R77" t="s">
         <v>803</v>
@@ -10757,7 +10753,7 @@
         <v>899</v>
       </c>
       <c r="E78" t="s">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="F78" t="s">
         <v>900</v>
@@ -10766,7 +10762,7 @@
         <v>27</v>
       </c>
       <c r="H78" t="s">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="I78" t="s">
         <v>901</v>
@@ -10784,7 +10780,7 @@
         <v>905</v>
       </c>
       <c r="N78" t="s">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="O78" t="s">
         <v>906</v>
@@ -10793,7 +10789,7 @@
         <v>907</v>
       </c>
       <c r="Q78" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="R78" t="s">
         <v>372</v>
@@ -10832,7 +10828,7 @@
         <v>27</v>
       </c>
       <c r="H79" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="I79" t="s">
         <v>912</v>
@@ -10850,7 +10846,7 @@
         <v>916</v>
       </c>
       <c r="N79" t="s">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="O79" t="s">
         <v>917</v>
@@ -10859,7 +10855,7 @@
         <v>918</v>
       </c>
       <c r="Q79" t="s">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="R79" t="s">
         <v>919</v>
@@ -10889,7 +10885,7 @@
         <v>683</v>
       </c>
       <c r="E80" t="s">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="F80" t="s">
         <v>911</v>
@@ -10898,7 +10894,7 @@
         <v>27</v>
       </c>
       <c r="H80" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="I80" t="s">
         <v>923</v>
@@ -10916,7 +10912,7 @@
         <v>927</v>
       </c>
       <c r="N80" t="s">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="O80" t="s">
         <v>928</v>
@@ -10962,7 +10958,7 @@
         <v>27</v>
       </c>
       <c r="H81" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="I81" t="s">
         <v>936</v>
@@ -11019,7 +11015,7 @@
         <v>944</v>
       </c>
       <c r="E82" t="s">
-        <v>98</v>
+        <v>38</v>
       </c>
       <c r="F82" t="s">
         <v>945</v>
@@ -11055,7 +11051,7 @@
         <v>953</v>
       </c>
       <c r="Q82" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="R82" t="s">
         <v>954</v>
@@ -11079,13 +11075,13 @@
         <v>957</v>
       </c>
       <c r="C83" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="D83" t="s">
         <v>958</v>
       </c>
       <c r="E83" t="s">
-        <v>98</v>
+        <v>38</v>
       </c>
       <c r="F83" t="s">
         <v>945</v>
@@ -11094,7 +11090,7 @@
         <v>27</v>
       </c>
       <c r="H83" t="s">
-        <v>145</v>
+        <v>174</v>
       </c>
       <c r="I83" t="s">
         <v>959</v>
@@ -11112,7 +11108,7 @@
         <v>963</v>
       </c>
       <c r="N83" t="s">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="O83" t="s">
         <v>964</v>
@@ -11121,7 +11117,7 @@
         <v>965</v>
       </c>
       <c r="Q83" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="R83" t="s">
         <v>966</v>
@@ -11145,13 +11141,13 @@
         <v>969</v>
       </c>
       <c r="C84" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="D84" t="s">
         <v>970</v>
       </c>
       <c r="E84" t="s">
-        <v>129</v>
+        <v>158</v>
       </c>
       <c r="F84" t="s">
         <v>945</v>
@@ -11160,7 +11156,7 @@
         <v>27</v>
       </c>
       <c r="H84" t="s">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="I84" t="s">
         <v>971</v>
@@ -11178,7 +11174,7 @@
         <v>975</v>
       </c>
       <c r="N84" t="s">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="O84" t="s">
         <v>976</v>
@@ -11187,16 +11183,16 @@
         <v>977</v>
       </c>
       <c r="Q84" t="s">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="R84" t="s">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="S84" t="s">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="T84" t="s">
-        <v>47</v>
+        <v>80</v>
       </c>
       <c r="U84" t="s">
         <v>476</v>
@@ -11217,16 +11213,16 @@
         <v>979</v>
       </c>
       <c r="E85" t="s">
-        <v>98</v>
+        <v>38</v>
       </c>
       <c r="F85" t="s">
         <v>980</v>
       </c>
       <c r="G85" t="s">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="H85" t="s">
-        <v>145</v>
+        <v>174</v>
       </c>
       <c r="I85" t="s">
         <v>981</v>
@@ -11244,7 +11240,7 @@
         <v>985</v>
       </c>
       <c r="N85" t="s">
-        <v>204</v>
+        <v>62</v>
       </c>
       <c r="O85" t="s">
         <v>986</v>
@@ -11280,19 +11276,19 @@
         <v>23</v>
       </c>
       <c r="D86" t="s">
-        <v>97</v>
+        <v>37</v>
       </c>
       <c r="E86" t="s">
-        <v>98</v>
+        <v>38</v>
       </c>
       <c r="F86" t="s">
         <v>980</v>
       </c>
       <c r="G86" t="s">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="H86" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="I86" t="s">
         <v>992</v>
@@ -11310,7 +11306,7 @@
         <v>996</v>
       </c>
       <c r="N86" t="s">
-        <v>92</v>
+        <v>124</v>
       </c>
       <c r="O86" t="s">
         <v>997</v>
@@ -11343,22 +11339,22 @@
         <v>999</v>
       </c>
       <c r="C87" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="D87" t="s">
         <v>567</v>
       </c>
       <c r="E87" t="s">
-        <v>98</v>
+        <v>38</v>
       </c>
       <c r="F87" t="s">
         <v>1000</v>
       </c>
       <c r="G87" t="s">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="H87" t="s">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="I87" t="s">
         <v>1001</v>
@@ -11376,7 +11372,7 @@
         <v>1005</v>
       </c>
       <c r="N87" t="s">
-        <v>204</v>
+        <v>62</v>
       </c>
       <c r="O87" t="s">
         <v>1006</v>
@@ -11385,7 +11381,7 @@
         <v>1007</v>
       </c>
       <c r="Q87" t="s">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="R87" t="s">
         <v>1008</v>
@@ -11409,7 +11405,7 @@
         <v>1011</v>
       </c>
       <c r="C88" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="D88" t="s">
         <v>844</v>
@@ -11424,7 +11420,7 @@
         <v>27</v>
       </c>
       <c r="H88" t="s">
-        <v>145</v>
+        <v>174</v>
       </c>
       <c r="I88" t="s">
         <v>1013</v>
@@ -11442,7 +11438,7 @@
         <v>1017</v>
       </c>
       <c r="N88" t="s">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="O88" t="s">
         <v>1018</v>
@@ -11451,7 +11447,7 @@
         <v>1019</v>
       </c>
       <c r="Q88" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="R88" t="s">
         <v>1020</v>
@@ -11475,7 +11471,7 @@
         <v>1023</v>
       </c>
       <c r="C89" t="s">
-        <v>83</v>
+        <v>115</v>
       </c>
       <c r="D89" t="s">
         <v>1024</v>
@@ -11486,7 +11482,7 @@
       </c>
       <c r="G89"/>
       <c r="H89" t="s">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="I89" t="s">
         <v>1026</v>
@@ -11504,7 +11500,7 @@
         <v>1030</v>
       </c>
       <c r="N89" t="s">
-        <v>164</v>
+        <v>47</v>
       </c>
       <c r="O89" t="s">
         <v>1031</v>
@@ -11513,7 +11509,7 @@
         <v>1032</v>
       </c>
       <c r="Q89" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="R89"/>
       <c r="S89"/>
@@ -11531,7 +11527,7 @@
         <v>1033</v>
       </c>
       <c r="C90" t="s">
-        <v>83</v>
+        <v>115</v>
       </c>
       <c r="D90" t="s">
         <v>1034</v>
@@ -11542,7 +11538,7 @@
       </c>
       <c r="G90"/>
       <c r="H90" t="s">
-        <v>173</v>
+        <v>56</v>
       </c>
       <c r="I90" t="s">
         <v>786</v>
@@ -11560,7 +11556,7 @@
         <v>1037</v>
       </c>
       <c r="N90" t="s">
-        <v>204</v>
+        <v>62</v>
       </c>
       <c r="O90" t="s">
         <v>1038</v>
@@ -11569,7 +11565,7 @@
         <v>1039</v>
       </c>
       <c r="Q90" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="R90"/>
       <c r="S90"/>
@@ -11597,10 +11593,10 @@
         <v>1042</v>
       </c>
       <c r="G91" t="s">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="H91" t="s">
-        <v>173</v>
+        <v>56</v>
       </c>
       <c r="I91" t="s">
         <v>1043</v>
@@ -11618,7 +11614,7 @@
         <v>1047</v>
       </c>
       <c r="N91" t="s">
-        <v>164</v>
+        <v>47</v>
       </c>
       <c r="O91" t="s">
         <v>1048</v>
@@ -11627,7 +11623,7 @@
         <v>1049</v>
       </c>
       <c r="Q91" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="R91" t="s">
         <v>1050</v>
@@ -11666,7 +11662,7 @@
         <v>27</v>
       </c>
       <c r="H92" t="s">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="I92" t="s">
         <v>1055</v>
@@ -11684,7 +11680,7 @@
         <v>1059</v>
       </c>
       <c r="N92" t="s">
-        <v>204</v>
+        <v>62</v>
       </c>
       <c r="O92" t="s">
         <v>1060</v>
@@ -11693,7 +11689,7 @@
         <v>1061</v>
       </c>
       <c r="Q92" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="R92" t="s">
         <v>1062</v>
@@ -11717,7 +11713,7 @@
         <v>1065</v>
       </c>
       <c r="C93" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="D93" t="s">
         <v>909</v>
@@ -11732,7 +11728,7 @@
         <v>27</v>
       </c>
       <c r="H93" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="I93" t="s">
         <v>1066</v>
@@ -11750,7 +11746,7 @@
         <v>1070</v>
       </c>
       <c r="N93" t="s">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="O93" t="s">
         <v>1071</v>
@@ -11783,13 +11779,13 @@
         <v>1076</v>
       </c>
       <c r="C94" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="D94" t="s">
         <v>1077</v>
       </c>
       <c r="E94" t="s">
-        <v>98</v>
+        <v>38</v>
       </c>
       <c r="F94" t="s">
         <v>1054</v>
@@ -11816,7 +11812,7 @@
         <v>1082</v>
       </c>
       <c r="N94" t="s">
-        <v>204</v>
+        <v>62</v>
       </c>
       <c r="O94" t="s">
         <v>1083</v>
@@ -11825,7 +11821,7 @@
         <v>1084</v>
       </c>
       <c r="Q94" t="s">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="R94" t="s">
         <v>1085</v>
@@ -11855,7 +11851,7 @@
         <v>633</v>
       </c>
       <c r="E95" t="s">
-        <v>129</v>
+        <v>158</v>
       </c>
       <c r="F95" t="s">
         <v>1054</v>
@@ -11864,7 +11860,7 @@
         <v>27</v>
       </c>
       <c r="H95" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="I95" t="s">
         <v>1089</v>
@@ -11930,7 +11926,7 @@
         <v>27</v>
       </c>
       <c r="H96" t="s">
-        <v>173</v>
+        <v>56</v>
       </c>
       <c r="I96" t="s">
         <v>1101</v>
@@ -11948,7 +11944,7 @@
         <v>1105</v>
       </c>
       <c r="N96" t="s">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="O96" t="s">
         <v>1106</v>
@@ -11957,7 +11953,7 @@
         <v>1107</v>
       </c>
       <c r="Q96" t="s">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="R96" t="s">
         <v>1108</v>
@@ -11981,7 +11977,7 @@
         <v>1111</v>
       </c>
       <c r="C97" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="D97" t="s">
         <v>1112</v>
@@ -11996,7 +11992,7 @@
         <v>27</v>
       </c>
       <c r="H97" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="I97" t="s">
         <v>1113</v>
@@ -12014,7 +12010,7 @@
         <v>1117</v>
       </c>
       <c r="N97" t="s">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="O97" t="s">
         <v>1118</v>
@@ -12047,13 +12043,13 @@
         <v>1123</v>
       </c>
       <c r="C98" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="D98" t="s">
         <v>739</v>
       </c>
       <c r="E98" t="s">
-        <v>98</v>
+        <v>38</v>
       </c>
       <c r="F98" t="s">
         <v>1124</v>
@@ -12062,7 +12058,7 @@
         <v>27</v>
       </c>
       <c r="H98" t="s">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="I98" t="s">
         <v>1125</v>
@@ -12080,7 +12076,7 @@
         <v>1129</v>
       </c>
       <c r="N98" t="s">
-        <v>204</v>
+        <v>62</v>
       </c>
       <c r="O98" t="s">
         <v>1130</v>
@@ -12089,7 +12085,7 @@
         <v>1131</v>
       </c>
       <c r="Q98" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="R98" t="s">
         <v>1132</v>
@@ -12113,7 +12109,7 @@
         <v>1135</v>
       </c>
       <c r="C99" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="D99" t="s">
         <v>1136</v>
@@ -12128,7 +12124,7 @@
         <v>27</v>
       </c>
       <c r="H99" t="s">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="I99" t="s">
         <v>1137</v>
@@ -12146,7 +12142,7 @@
         <v>1141</v>
       </c>
       <c r="N99" t="s">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="O99" t="s">
         <v>1142</v>
@@ -12155,7 +12151,7 @@
         <v>1143</v>
       </c>
       <c r="Q99" t="s">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="R99" t="s">
         <v>1144</v>
@@ -12179,7 +12175,7 @@
         <v>1147</v>
       </c>
       <c r="C100" t="s">
-        <v>83</v>
+        <v>115</v>
       </c>
       <c r="D100" t="s">
         <v>1148</v>
@@ -12190,7 +12186,7 @@
       </c>
       <c r="G100"/>
       <c r="H100" t="s">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="I100" t="s">
         <v>1149</v>
@@ -12208,7 +12204,7 @@
         <v>1153</v>
       </c>
       <c r="N100" t="s">
-        <v>204</v>
+        <v>62</v>
       </c>
       <c r="O100" t="s">
         <v>1154</v>
@@ -12217,7 +12213,7 @@
         <v>1155</v>
       </c>
       <c r="Q100" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="R100"/>
       <c r="S100"/>
@@ -12238,10 +12234,10 @@
         <v>23</v>
       </c>
       <c r="D101" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="E101" t="s">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="F101" t="s">
         <v>1157</v>
@@ -12250,7 +12246,7 @@
         <v>27</v>
       </c>
       <c r="H101" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="I101" t="s">
         <v>622</v>
@@ -12268,7 +12264,7 @@
         <v>1161</v>
       </c>
       <c r="N101" t="s">
-        <v>204</v>
+        <v>62</v>
       </c>
       <c r="O101" t="s">
         <v>1162</v>
@@ -12277,7 +12273,7 @@
         <v>1163</v>
       </c>
       <c r="Q101" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="R101" t="s">
         <v>629</v>
@@ -12301,13 +12297,13 @@
         <v>1164</v>
       </c>
       <c r="C102" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="D102" t="s">
         <v>1165</v>
       </c>
       <c r="E102" t="s">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="F102" t="s">
         <v>1166</v>
@@ -12316,7 +12312,7 @@
         <v>27</v>
       </c>
       <c r="H102" t="s">
-        <v>173</v>
+        <v>56</v>
       </c>
       <c r="I102" t="s">
         <v>1167</v>
@@ -12332,7 +12328,7 @@
         <v>1170</v>
       </c>
       <c r="N102" t="s">
-        <v>204</v>
+        <v>62</v>
       </c>
       <c r="O102" t="s">
         <v>1171</v>
@@ -12341,7 +12337,7 @@
         <v>1172</v>
       </c>
       <c r="Q102" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="R102" t="s">
         <v>1173</v>
@@ -12365,7 +12361,7 @@
         <v>1176</v>
       </c>
       <c r="C103" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="D103" t="s">
         <v>1177</v>
@@ -12380,7 +12376,7 @@
         <v>27</v>
       </c>
       <c r="H103" t="s">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="I103" t="s">
         <v>1179</v>
@@ -12396,7 +12392,7 @@
         <v>1182</v>
       </c>
       <c r="N103" t="s">
-        <v>204</v>
+        <v>62</v>
       </c>
       <c r="O103" t="s">
         <v>1183</v>
@@ -12405,7 +12401,7 @@
         <v>1184</v>
       </c>
       <c r="Q103" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="R103" t="s">
         <v>1062</v>
@@ -12433,14 +12429,14 @@
       </c>
       <c r="D104"/>
       <c r="E104" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="F104" t="s">
         <v>1186</v>
       </c>
       <c r="G104"/>
       <c r="H104" t="s">
-        <v>173</v>
+        <v>56</v>
       </c>
       <c r="I104" t="s">
         <v>1187</v>
@@ -12454,7 +12450,7 @@
       <c r="L104"/>
       <c r="M104"/>
       <c r="N104" t="s">
-        <v>204</v>
+        <v>62</v>
       </c>
       <c r="O104" t="s">
         <v>1190</v>
@@ -12487,7 +12483,7 @@
         <v>1195</v>
       </c>
       <c r="C105" t="s">
-        <v>83</v>
+        <v>115</v>
       </c>
       <c r="D105" t="s">
         <v>1148</v>
@@ -12498,7 +12494,7 @@
       </c>
       <c r="G105"/>
       <c r="H105" t="s">
-        <v>145</v>
+        <v>174</v>
       </c>
       <c r="I105" t="s">
         <v>1197</v>
@@ -12516,7 +12512,7 @@
         <v>1201</v>
       </c>
       <c r="N105" t="s">
-        <v>164</v>
+        <v>47</v>
       </c>
       <c r="O105" t="s">
         <v>1202</v>
@@ -12525,7 +12521,7 @@
         <v>1203</v>
       </c>
       <c r="Q105" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="R105" t="s">
         <v>1204</v>
@@ -12549,7 +12545,7 @@
         <v>1207</v>
       </c>
       <c r="C106" t="s">
-        <v>83</v>
+        <v>115</v>
       </c>
       <c r="D106" t="s">
         <v>1148</v>
@@ -12560,7 +12556,7 @@
       </c>
       <c r="G106"/>
       <c r="H106" t="s">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="I106" t="s">
         <v>1208</v>
@@ -12587,7 +12583,7 @@
         <v>1215</v>
       </c>
       <c r="Q106" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="R106" t="s">
         <v>1216</v>
@@ -12626,7 +12622,7 @@
         <v>27</v>
       </c>
       <c r="H107" t="s">
-        <v>145</v>
+        <v>174</v>
       </c>
       <c r="I107" t="s">
         <v>1221</v>
@@ -12644,7 +12640,7 @@
         <v>1225</v>
       </c>
       <c r="N107" t="s">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="O107" t="s">
         <v>1226</v>
@@ -12653,7 +12649,7 @@
         <v>1227</v>
       </c>
       <c r="Q107" t="s">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="R107" t="s">
         <v>1228</v>
@@ -12683,7 +12679,7 @@
         <v>1232</v>
       </c>
       <c r="E108" t="s">
-        <v>98</v>
+        <v>38</v>
       </c>
       <c r="F108" t="s">
         <v>1233</v>
@@ -12710,7 +12706,7 @@
         <v>1238</v>
       </c>
       <c r="N108" t="s">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="O108" t="s">
         <v>1239</v>
@@ -12719,7 +12715,7 @@
         <v>1240</v>
       </c>
       <c r="Q108" t="s">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="R108" t="s">
         <v>1241</v>
@@ -12743,13 +12739,13 @@
         <v>1244</v>
       </c>
       <c r="C109" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="D109" t="s">
         <v>1245</v>
       </c>
       <c r="E109" t="s">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="F109" t="s">
         <v>1233</v>
@@ -12758,7 +12754,7 @@
         <v>27</v>
       </c>
       <c r="H109" t="s">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="I109" t="s">
         <v>1246</v>
@@ -12776,7 +12772,7 @@
         <v>1250</v>
       </c>
       <c r="N109" t="s">
-        <v>204</v>
+        <v>62</v>
       </c>
       <c r="O109" t="s">
         <v>1251</v>
@@ -12785,7 +12781,7 @@
         <v>1252</v>
       </c>
       <c r="Q109" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="R109" t="s">
         <v>885</v>
@@ -12824,7 +12820,7 @@
         <v>27</v>
       </c>
       <c r="H110" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="I110" t="s">
         <v>1255</v>
@@ -12842,7 +12838,7 @@
         <v>1259</v>
       </c>
       <c r="N110" t="s">
-        <v>204</v>
+        <v>62</v>
       </c>
       <c r="O110" t="s">
         <v>1260</v>
@@ -12875,13 +12871,13 @@
         <v>1265</v>
       </c>
       <c r="C111" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="D111" t="s">
         <v>1266</v>
       </c>
       <c r="E111" t="s">
-        <v>98</v>
+        <v>38</v>
       </c>
       <c r="F111" t="s">
         <v>1233</v>
@@ -12908,7 +12904,7 @@
         <v>1271</v>
       </c>
       <c r="N111" t="s">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="O111" t="s">
         <v>1272</v>
@@ -12947,7 +12943,7 @@
         <v>1275</v>
       </c>
       <c r="E112" t="s">
-        <v>129</v>
+        <v>158</v>
       </c>
       <c r="F112" t="s">
         <v>1276</v>
@@ -12974,7 +12970,7 @@
         <v>1281</v>
       </c>
       <c r="N112" t="s">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="O112" t="s">
         <v>1282</v>
@@ -12983,7 +12979,7 @@
         <v>1283</v>
       </c>
       <c r="Q112" t="s">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="R112" t="s">
         <v>596</v>
@@ -13007,13 +13003,13 @@
         <v>1284</v>
       </c>
       <c r="C113" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="D113" t="s">
         <v>683</v>
       </c>
       <c r="E113" t="s">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="F113" t="s">
         <v>1285</v>
@@ -13022,7 +13018,7 @@
         <v>27</v>
       </c>
       <c r="H113" t="s">
-        <v>173</v>
+        <v>56</v>
       </c>
       <c r="I113" t="s">
         <v>1286</v>
@@ -13038,7 +13034,7 @@
         <v>1289</v>
       </c>
       <c r="N113" t="s">
-        <v>204</v>
+        <v>62</v>
       </c>
       <c r="O113" t="s">
         <v>1290</v>
@@ -13071,13 +13067,13 @@
         <v>1292</v>
       </c>
       <c r="C114" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="D114" t="s">
         <v>234</v>
       </c>
       <c r="E114" t="s">
-        <v>129</v>
+        <v>158</v>
       </c>
       <c r="F114" t="s">
         <v>1293</v>
@@ -13086,7 +13082,7 @@
         <v>27</v>
       </c>
       <c r="H114" t="s">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="I114" t="s">
         <v>1294</v>
@@ -13104,7 +13100,7 @@
         <v>1298</v>
       </c>
       <c r="N114" t="s">
-        <v>204</v>
+        <v>62</v>
       </c>
       <c r="O114" t="s">
         <v>1299</v>
@@ -13116,13 +13112,13 @@
         <v>243</v>
       </c>
       <c r="R114" t="s">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="S114" t="s">
-        <v>80</v>
+        <v>112</v>
       </c>
       <c r="T114" t="s">
-        <v>81</v>
+        <v>113</v>
       </c>
       <c r="U114" t="s">
         <v>476</v>
@@ -13137,13 +13133,13 @@
         <v>1301</v>
       </c>
       <c r="C115" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="D115" t="s">
         <v>1266</v>
       </c>
       <c r="E115" t="s">
-        <v>98</v>
+        <v>38</v>
       </c>
       <c r="F115" t="s">
         <v>1302</v>
@@ -13152,7 +13148,7 @@
         <v>27</v>
       </c>
       <c r="H115" t="s">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="I115" t="s">
         <v>1303</v>
@@ -13168,7 +13164,7 @@
         <v>1306</v>
       </c>
       <c r="N115" t="s">
-        <v>204</v>
+        <v>62</v>
       </c>
       <c r="O115" t="s">
         <v>1307</v>
@@ -13177,16 +13173,16 @@
         <v>1308</v>
       </c>
       <c r="Q115" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="R115" t="s">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="S115" t="s">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="T115" t="s">
-        <v>47</v>
+        <v>80</v>
       </c>
       <c r="U115" t="s">
         <v>476</v>
@@ -13201,13 +13197,13 @@
         <v>1309</v>
       </c>
       <c r="C116" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="D116" t="s">
         <v>683</v>
       </c>
       <c r="E116" t="s">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="F116" t="s">
         <v>1302</v>
@@ -13216,7 +13212,7 @@
         <v>27</v>
       </c>
       <c r="H116" t="s">
-        <v>173</v>
+        <v>56</v>
       </c>
       <c r="I116" t="s">
         <v>1310</v>
@@ -13232,7 +13228,7 @@
         <v>1313</v>
       </c>
       <c r="N116" t="s">
-        <v>204</v>
+        <v>62</v>
       </c>
       <c r="O116" t="s">
         <v>1314</v>
@@ -13265,13 +13261,13 @@
         <v>1316</v>
       </c>
       <c r="C117" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="D117" t="s">
         <v>683</v>
       </c>
       <c r="E117" t="s">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="F117" t="s">
         <v>1302</v>
@@ -13280,7 +13276,7 @@
         <v>27</v>
       </c>
       <c r="H117" t="s">
-        <v>173</v>
+        <v>56</v>
       </c>
       <c r="I117" t="s">
         <v>1310</v>
@@ -13296,7 +13292,7 @@
         <v>1318</v>
       </c>
       <c r="N117" t="s">
-        <v>204</v>
+        <v>62</v>
       </c>
       <c r="O117" t="s">
         <v>1319</v>
@@ -13329,13 +13325,13 @@
         <v>1321</v>
       </c>
       <c r="C118" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="D118" t="s">
         <v>683</v>
       </c>
       <c r="E118" t="s">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="F118" t="s">
         <v>1302</v>
@@ -13344,7 +13340,7 @@
         <v>27</v>
       </c>
       <c r="H118" t="s">
-        <v>173</v>
+        <v>56</v>
       </c>
       <c r="I118" t="s">
         <v>1310</v>
@@ -13360,7 +13356,7 @@
         <v>1323</v>
       </c>
       <c r="N118" t="s">
-        <v>204</v>
+        <v>62</v>
       </c>
       <c r="O118" t="s">
         <v>1324</v>
@@ -13393,13 +13389,13 @@
         <v>1326</v>
       </c>
       <c r="C119" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="D119" t="s">
         <v>761</v>
       </c>
       <c r="E119" t="s">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="F119" t="s">
         <v>1327</v>
@@ -13408,7 +13404,7 @@
         <v>27</v>
       </c>
       <c r="H119" t="s">
-        <v>145</v>
+        <v>174</v>
       </c>
       <c r="I119" t="s">
         <v>1328</v>
@@ -13426,7 +13422,7 @@
         <v>1332</v>
       </c>
       <c r="N119" t="s">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="O119" t="s">
         <v>1333</v>
@@ -13435,7 +13431,7 @@
         <v>1334</v>
       </c>
       <c r="Q119" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="R119" t="s">
         <v>1335</v>
@@ -13459,13 +13455,13 @@
         <v>1338</v>
       </c>
       <c r="C120" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="D120" t="s">
         <v>819</v>
       </c>
       <c r="E120" t="s">
-        <v>98</v>
+        <v>38</v>
       </c>
       <c r="F120" t="s">
         <v>1339</v>
@@ -13474,7 +13470,7 @@
         <v>27</v>
       </c>
       <c r="H120" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="I120" t="s">
         <v>1340</v>
@@ -13492,7 +13488,7 @@
         <v>1344</v>
       </c>
       <c r="N120" t="s">
-        <v>204</v>
+        <v>62</v>
       </c>
       <c r="O120" t="s">
         <v>1345</v>
@@ -13501,7 +13497,7 @@
         <v>1346</v>
       </c>
       <c r="Q120" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="R120" t="s">
         <v>406</v>
@@ -13525,13 +13521,13 @@
         <v>1347</v>
       </c>
       <c r="C121" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="D121" t="s">
         <v>1348</v>
       </c>
       <c r="E121" t="s">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="F121" t="s">
         <v>1339</v>
@@ -13540,7 +13536,7 @@
         <v>27</v>
       </c>
       <c r="H121" t="s">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="I121" t="s">
         <v>1349</v>
@@ -13558,7 +13554,7 @@
         <v>1353</v>
       </c>
       <c r="N121" t="s">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="O121" t="s">
         <v>1354</v>
@@ -13567,7 +13563,7 @@
         <v>1355</v>
       </c>
       <c r="Q121" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="R121" t="s">
         <v>1356</v>
@@ -13591,13 +13587,13 @@
         <v>1359</v>
       </c>
       <c r="C122" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="D122" t="s">
         <v>1360</v>
       </c>
       <c r="E122" t="s">
-        <v>129</v>
+        <v>158</v>
       </c>
       <c r="F122" t="s">
         <v>1339</v>
@@ -13606,7 +13602,7 @@
         <v>27</v>
       </c>
       <c r="H122" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="I122" t="s">
         <v>1361</v>
@@ -13624,7 +13620,7 @@
         <v>1365</v>
       </c>
       <c r="N122" t="s">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="O122" t="s">
         <v>1366</v>
@@ -13633,7 +13629,7 @@
         <v>1367</v>
       </c>
       <c r="Q122" t="s">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="R122" t="s">
         <v>1368</v>
@@ -13657,7 +13653,7 @@
         <v>1371</v>
       </c>
       <c r="C123" t="s">
-        <v>83</v>
+        <v>115</v>
       </c>
       <c r="D123" t="s">
         <v>1148</v>
@@ -13668,7 +13664,7 @@
       </c>
       <c r="G123"/>
       <c r="H123" t="s">
-        <v>86</v>
+        <v>118</v>
       </c>
       <c r="I123" t="s">
         <v>1373</v>
@@ -13686,7 +13682,7 @@
         <v>1377</v>
       </c>
       <c r="N123" t="s">
-        <v>164</v>
+        <v>47</v>
       </c>
       <c r="O123" t="s">
         <v>1378</v>
@@ -13695,7 +13691,7 @@
         <v>1379</v>
       </c>
       <c r="Q123" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="R123" t="s">
         <v>1380</v>
@@ -13725,7 +13721,7 @@
         <v>661</v>
       </c>
       <c r="E124" t="s">
-        <v>98</v>
+        <v>38</v>
       </c>
       <c r="F124" t="s">
         <v>1372</v>
@@ -13752,7 +13748,7 @@
         <v>1388</v>
       </c>
       <c r="N124" t="s">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="O124" t="s">
         <v>1389</v>
@@ -13761,7 +13757,7 @@
         <v>1390</v>
       </c>
       <c r="Q124" t="s">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="R124" t="s">
         <v>1391</v>
@@ -13791,7 +13787,7 @@
         <v>1395</v>
       </c>
       <c r="E125" t="s">
-        <v>129</v>
+        <v>158</v>
       </c>
       <c r="F125" t="s">
         <v>1372</v>
@@ -13800,7 +13796,7 @@
         <v>27</v>
       </c>
       <c r="H125" t="s">
-        <v>145</v>
+        <v>174</v>
       </c>
       <c r="I125" t="s">
         <v>1396</v>
@@ -13818,7 +13814,7 @@
         <v>1400</v>
       </c>
       <c r="N125" t="s">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="O125" t="s">
         <v>1401</v>
@@ -13827,7 +13823,7 @@
         <v>1402</v>
       </c>
       <c r="Q125" t="s">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="R125" t="s">
         <v>1403</v>
@@ -13851,7 +13847,7 @@
         <v>1406</v>
       </c>
       <c r="C126" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="D126" t="s">
         <v>1407</v>
@@ -13866,7 +13862,7 @@
         <v>27</v>
       </c>
       <c r="H126" t="s">
-        <v>145</v>
+        <v>174</v>
       </c>
       <c r="I126" t="s">
         <v>1408</v>
@@ -13884,7 +13880,7 @@
         <v>1412</v>
       </c>
       <c r="N126" t="s">
-        <v>204</v>
+        <v>62</v>
       </c>
       <c r="O126" t="s">
         <v>1413</v>
@@ -13932,7 +13928,7 @@
         <v>27</v>
       </c>
       <c r="H127" t="s">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="I127" t="s">
         <v>1416</v>
@@ -13950,7 +13946,7 @@
         <v>1420</v>
       </c>
       <c r="N127" t="s">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="O127" t="s">
         <v>1421</v>
@@ -13959,7 +13955,7 @@
         <v>1422</v>
       </c>
       <c r="Q127" t="s">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="R127" t="s">
         <v>1423</v>
@@ -13989,7 +13985,7 @@
         <v>761</v>
       </c>
       <c r="E128" t="s">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="F128" t="s">
         <v>1372</v>
@@ -13998,7 +13994,7 @@
         <v>27</v>
       </c>
       <c r="H128" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="I128" t="s">
         <v>1427</v>
@@ -14025,7 +14021,7 @@
         <v>1434</v>
       </c>
       <c r="Q128" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="R128" t="s">
         <v>1435</v>
@@ -14049,13 +14045,13 @@
         <v>1438</v>
       </c>
       <c r="C129" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="D129" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="E129" t="s">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="F129" t="s">
         <v>1439</v>
@@ -14064,7 +14060,7 @@
         <v>27</v>
       </c>
       <c r="H129" t="s">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="I129" t="s">
         <v>1440</v>
@@ -14082,7 +14078,7 @@
         <v>1444</v>
       </c>
       <c r="N129" t="s">
-        <v>204</v>
+        <v>62</v>
       </c>
       <c r="O129" t="s">
         <v>1445</v>
@@ -14091,16 +14087,16 @@
         <v>1446</v>
       </c>
       <c r="Q129" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="R129" t="s">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="S129" t="s">
-        <v>80</v>
+        <v>112</v>
       </c>
       <c r="T129" t="s">
-        <v>81</v>
+        <v>113</v>
       </c>
       <c r="U129" t="s">
         <v>476</v>
@@ -14121,7 +14117,7 @@
         <v>633</v>
       </c>
       <c r="E130" t="s">
-        <v>129</v>
+        <v>158</v>
       </c>
       <c r="F130" t="s">
         <v>1448</v>
@@ -14130,7 +14126,7 @@
         <v>27</v>
       </c>
       <c r="H130" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="I130" t="s">
         <v>1449</v>
@@ -14148,7 +14144,7 @@
         <v>1453</v>
       </c>
       <c r="N130" t="s">
-        <v>204</v>
+        <v>62</v>
       </c>
       <c r="O130" t="s">
         <v>1454</v>
@@ -14181,13 +14177,13 @@
         <v>1456</v>
       </c>
       <c r="C131" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="D131" t="s">
         <v>1457</v>
       </c>
       <c r="E131" t="s">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="F131" t="s">
         <v>1458</v>
@@ -14196,7 +14192,7 @@
         <v>27</v>
       </c>
       <c r="H131" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="I131" t="s">
         <v>1459</v>
@@ -14212,7 +14208,7 @@
         <v>1462</v>
       </c>
       <c r="N131" t="s">
-        <v>204</v>
+        <v>62</v>
       </c>
       <c r="O131" t="s">
         <v>1463</v>
@@ -14221,7 +14217,7 @@
         <v>1464</v>
       </c>
       <c r="Q131" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="R131" t="s">
         <v>930</v>
@@ -14245,7 +14241,7 @@
         <v>1465</v>
       </c>
       <c r="C132" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="D132" t="s">
         <v>1466</v>
@@ -14260,7 +14256,7 @@
         <v>27</v>
       </c>
       <c r="H132" t="s">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="I132" t="s">
         <v>1467</v>
@@ -14276,7 +14272,7 @@
         <v>1470</v>
       </c>
       <c r="N132" t="s">
-        <v>204</v>
+        <v>62</v>
       </c>
       <c r="O132" t="s">
         <v>1471</v>
@@ -14285,16 +14281,16 @@
         <v>1472</v>
       </c>
       <c r="Q132" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="R132" t="s">
-        <v>139</v>
+        <v>168</v>
       </c>
       <c r="S132" t="s">
-        <v>140</v>
+        <v>169</v>
       </c>
       <c r="T132" t="s">
-        <v>141</v>
+        <v>170</v>
       </c>
       <c r="U132" t="s">
         <v>476</v>
@@ -14324,7 +14320,7 @@
         <v>27</v>
       </c>
       <c r="H133" t="s">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="I133" t="s">
         <v>1475</v>
@@ -14342,7 +14338,7 @@
         <v>1479</v>
       </c>
       <c r="N133" t="s">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="O133" t="s">
         <v>1480</v>
@@ -14379,14 +14375,14 @@
       </c>
       <c r="D134"/>
       <c r="E134" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="F134" t="s">
         <v>1483</v>
       </c>
       <c r="G134"/>
       <c r="H134" t="s">
-        <v>173</v>
+        <v>56</v>
       </c>
       <c r="I134" t="s">
         <v>1484</v>
@@ -14433,7 +14429,7 @@
         <v>1493</v>
       </c>
       <c r="C135" t="s">
-        <v>83</v>
+        <v>115</v>
       </c>
       <c r="D135" t="s">
         <v>1148</v>
@@ -14444,7 +14440,7 @@
       </c>
       <c r="G135"/>
       <c r="H135" t="s">
-        <v>173</v>
+        <v>56</v>
       </c>
       <c r="I135" t="s">
         <v>1495</v>
@@ -14471,7 +14467,7 @@
         <v>1501</v>
       </c>
       <c r="Q135" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="R135" t="s">
         <v>1502</v>
@@ -14495,7 +14491,7 @@
         <v>1505</v>
       </c>
       <c r="C136" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="D136" t="s">
         <v>1506</v>
@@ -14510,7 +14506,7 @@
         <v>27</v>
       </c>
       <c r="H136" t="s">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="I136" t="s">
         <v>1508</v>
@@ -14528,7 +14524,7 @@
         <v>1512</v>
       </c>
       <c r="N136" t="s">
-        <v>204</v>
+        <v>62</v>
       </c>
       <c r="O136" t="s">
         <v>1513</v>
@@ -14561,7 +14557,7 @@
         <v>1518</v>
       </c>
       <c r="C137" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="D137" t="s">
         <v>1519</v>
@@ -14576,7 +14572,7 @@
         <v>27</v>
       </c>
       <c r="H137" t="s">
-        <v>145</v>
+        <v>174</v>
       </c>
       <c r="I137" t="s">
         <v>1521</v>
@@ -14594,7 +14590,7 @@
         <v>1525</v>
       </c>
       <c r="N137" t="s">
-        <v>204</v>
+        <v>62</v>
       </c>
       <c r="O137" t="s">
         <v>1526</v>
@@ -14627,10 +14623,10 @@
         <v>1531</v>
       </c>
       <c r="C138" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="D138" t="s">
-        <v>115</v>
+        <v>144</v>
       </c>
       <c r="E138" t="s">
         <v>25</v>
@@ -14639,10 +14635,10 @@
         <v>1520</v>
       </c>
       <c r="G138" t="s">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="H138" t="s">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="I138" t="s">
         <v>1532</v>
@@ -14660,7 +14656,7 @@
         <v>1536</v>
       </c>
       <c r="N138" t="s">
-        <v>204</v>
+        <v>62</v>
       </c>
       <c r="O138" t="s">
         <v>1537</v>
@@ -14669,7 +14665,7 @@
         <v>1538</v>
       </c>
       <c r="Q138" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="R138" t="s">
         <v>885</v>
@@ -14699,16 +14695,16 @@
         <v>567</v>
       </c>
       <c r="E139" t="s">
-        <v>98</v>
+        <v>38</v>
       </c>
       <c r="F139" t="s">
         <v>1540</v>
       </c>
       <c r="G139" t="s">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="H139" t="s">
-        <v>145</v>
+        <v>174</v>
       </c>
       <c r="I139" t="s">
         <v>1541</v>
@@ -14735,7 +14731,7 @@
         <v>1547</v>
       </c>
       <c r="Q139" t="s">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="R139" t="s">
         <v>1380</v>
@@ -14765,7 +14761,7 @@
         <v>1549</v>
       </c>
       <c r="E140" t="s">
-        <v>98</v>
+        <v>38</v>
       </c>
       <c r="F140" t="s">
         <v>1540</v>
@@ -14774,7 +14770,7 @@
         <v>27</v>
       </c>
       <c r="H140" t="s">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="I140" t="s">
         <v>1550</v>
@@ -14792,7 +14788,7 @@
         <v>1554</v>
       </c>
       <c r="N140" t="s">
-        <v>92</v>
+        <v>124</v>
       </c>
       <c r="O140" t="s">
         <v>1555</v>
@@ -14858,7 +14854,7 @@
         <v>1567</v>
       </c>
       <c r="N141" t="s">
-        <v>204</v>
+        <v>62</v>
       </c>
       <c r="O141" t="s">
         <v>1568</v>
@@ -14867,7 +14863,7 @@
         <v>1569</v>
       </c>
       <c r="Q141" t="s">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="R141" t="s">
         <v>1570</v>
@@ -14891,13 +14887,13 @@
         <v>1573</v>
       </c>
       <c r="C142" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="D142" t="s">
         <v>532</v>
       </c>
       <c r="E142" t="s">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="F142" t="s">
         <v>1540</v>
@@ -14906,7 +14902,7 @@
         <v>27</v>
       </c>
       <c r="H142" t="s">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="I142" t="s">
         <v>1574</v>
@@ -14924,7 +14920,7 @@
         <v>1578</v>
       </c>
       <c r="N142" t="s">
-        <v>204</v>
+        <v>62</v>
       </c>
       <c r="O142" t="s">
         <v>1579</v>
@@ -14933,7 +14929,7 @@
         <v>1580</v>
       </c>
       <c r="Q142" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="R142" t="s">
         <v>1581</v>
@@ -14957,13 +14953,13 @@
         <v>1584</v>
       </c>
       <c r="C143" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="D143" t="s">
         <v>1549</v>
       </c>
       <c r="E143" t="s">
-        <v>98</v>
+        <v>38</v>
       </c>
       <c r="F143" t="s">
         <v>1540</v>
@@ -14972,7 +14968,7 @@
         <v>27</v>
       </c>
       <c r="H143" t="s">
-        <v>145</v>
+        <v>174</v>
       </c>
       <c r="I143" t="s">
         <v>1585</v>
@@ -14990,7 +14986,7 @@
         <v>1589</v>
       </c>
       <c r="N143" t="s">
-        <v>204</v>
+        <v>62</v>
       </c>
       <c r="O143" t="s">
         <v>1590</v>
@@ -14999,7 +14995,7 @@
         <v>1591</v>
       </c>
       <c r="Q143" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="R143" t="s">
         <v>1592</v>
@@ -15023,7 +15019,7 @@
         <v>1595</v>
       </c>
       <c r="C144" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="D144" t="s">
         <v>1254</v>
@@ -15038,7 +15034,7 @@
         <v>27</v>
       </c>
       <c r="H144" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="I144" t="s">
         <v>1596</v>
@@ -15056,7 +15052,7 @@
         <v>1600</v>
       </c>
       <c r="N144" t="s">
-        <v>204</v>
+        <v>62</v>
       </c>
       <c r="O144" t="s">
         <v>1601</v>
@@ -15065,7 +15061,7 @@
         <v>1602</v>
       </c>
       <c r="Q144" t="s">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="R144" t="s">
         <v>1603</v>
@@ -15089,13 +15085,13 @@
         <v>1606</v>
       </c>
       <c r="C145" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="D145" t="s">
         <v>1607</v>
       </c>
       <c r="E145" t="s">
-        <v>98</v>
+        <v>38</v>
       </c>
       <c r="F145" t="s">
         <v>1608</v>
@@ -15104,7 +15100,7 @@
         <v>27</v>
       </c>
       <c r="H145" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="I145" t="s">
         <v>1609</v>
@@ -15122,7 +15118,7 @@
         <v>1613</v>
       </c>
       <c r="N145" t="s">
-        <v>204</v>
+        <v>62</v>
       </c>
       <c r="O145" t="s">
         <v>1614</v>
@@ -15131,7 +15127,7 @@
         <v>1615</v>
       </c>
       <c r="Q145" t="s">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="R145" t="s">
         <v>930</v>
@@ -15155,13 +15151,13 @@
         <v>1616</v>
       </c>
       <c r="C146" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="D146" t="s">
         <v>433</v>
       </c>
       <c r="E146" t="s">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="F146" t="s">
         <v>1617</v>
@@ -15170,7 +15166,7 @@
         <v>27</v>
       </c>
       <c r="H146" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="I146" t="s">
         <v>1618</v>
@@ -15188,7 +15184,7 @@
         <v>1622</v>
       </c>
       <c r="N146" t="s">
-        <v>204</v>
+        <v>62</v>
       </c>
       <c r="O146" t="s">
         <v>1623</v>
@@ -15197,7 +15193,7 @@
         <v>1624</v>
       </c>
       <c r="Q146" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="R146" t="s">
         <v>528</v>
@@ -15221,7 +15217,7 @@
         <v>1625</v>
       </c>
       <c r="C147" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="D147" t="s">
         <v>1626</v>
@@ -15233,10 +15229,10 @@
         <v>1627</v>
       </c>
       <c r="G147" t="s">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="H147" t="s">
-        <v>145</v>
+        <v>174</v>
       </c>
       <c r="I147" t="s">
         <v>1628</v>
@@ -15254,7 +15250,7 @@
         <v>1632</v>
       </c>
       <c r="N147" t="s">
-        <v>204</v>
+        <v>62</v>
       </c>
       <c r="O147" t="s">
         <v>1633</v>
@@ -15263,7 +15259,7 @@
         <v>1634</v>
       </c>
       <c r="Q147" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="R147" t="s">
         <v>852</v>
@@ -15299,10 +15295,10 @@
         <v>1637</v>
       </c>
       <c r="G148" t="s">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="H148" t="s">
-        <v>145</v>
+        <v>174</v>
       </c>
       <c r="I148" t="s">
         <v>1638</v>
@@ -15329,7 +15325,7 @@
         <v>1644</v>
       </c>
       <c r="Q148" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="R148" t="s">
         <v>1403</v>
@@ -15353,13 +15349,13 @@
         <v>1645</v>
       </c>
       <c r="C149" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="D149" t="s">
         <v>761</v>
       </c>
       <c r="E149" t="s">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="F149" t="s">
         <v>1637</v>
@@ -15368,7 +15364,7 @@
         <v>27</v>
       </c>
       <c r="H149" t="s">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="I149" t="s">
         <v>1646</v>
@@ -15384,7 +15380,7 @@
         <v>1649</v>
       </c>
       <c r="N149" t="s">
-        <v>204</v>
+        <v>62</v>
       </c>
       <c r="O149" t="s">
         <v>1650</v>
@@ -15396,13 +15392,13 @@
         <v>243</v>
       </c>
       <c r="R149" t="s">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="S149" t="s">
-        <v>80</v>
+        <v>112</v>
       </c>
       <c r="T149" t="s">
-        <v>81</v>
+        <v>113</v>
       </c>
       <c r="U149" t="s">
         <v>476</v>
@@ -15417,7 +15413,7 @@
         <v>1652</v>
       </c>
       <c r="C150" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="D150" t="s">
         <v>389</v>
@@ -15432,7 +15428,7 @@
         <v>27</v>
       </c>
       <c r="H150" t="s">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="I150" t="s">
         <v>1654</v>
@@ -15448,7 +15444,7 @@
         <v>1657</v>
       </c>
       <c r="N150" t="s">
-        <v>204</v>
+        <v>62</v>
       </c>
       <c r="O150" t="s">
         <v>1658</v>
@@ -15457,16 +15453,16 @@
         <v>1659</v>
       </c>
       <c r="Q150" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="R150" t="s">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="S150" t="s">
-        <v>80</v>
+        <v>112</v>
       </c>
       <c r="T150" t="s">
-        <v>81</v>
+        <v>113</v>
       </c>
       <c r="U150" t="s">
         <v>476</v>
@@ -15494,7 +15490,7 @@
         <v>27</v>
       </c>
       <c r="H151" t="s">
-        <v>145</v>
+        <v>174</v>
       </c>
       <c r="I151" t="s">
         <v>1663</v>
@@ -15545,13 +15541,13 @@
         <v>1673</v>
       </c>
       <c r="C152" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="D152" t="s">
         <v>970</v>
       </c>
       <c r="E152" t="s">
-        <v>129</v>
+        <v>158</v>
       </c>
       <c r="F152" t="s">
         <v>1674</v>
@@ -15560,7 +15556,7 @@
         <v>27</v>
       </c>
       <c r="H152" t="s">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="I152" t="s">
         <v>1675</v>
@@ -15578,7 +15574,7 @@
         <v>1679</v>
       </c>
       <c r="N152" t="s">
-        <v>204</v>
+        <v>62</v>
       </c>
       <c r="O152" t="s">
         <v>1680</v>
@@ -15587,7 +15583,7 @@
         <v>1681</v>
       </c>
       <c r="Q152" t="s">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="R152" t="s">
         <v>1682</v>
@@ -15626,7 +15622,7 @@
         <v>27</v>
       </c>
       <c r="H153" t="s">
-        <v>145</v>
+        <v>174</v>
       </c>
       <c r="I153" t="s">
         <v>1686</v>
@@ -15644,7 +15640,7 @@
         <v>1690</v>
       </c>
       <c r="N153" t="s">
-        <v>204</v>
+        <v>62</v>
       </c>
       <c r="O153" t="s">
         <v>1691</v>
@@ -15653,7 +15649,7 @@
         <v>1692</v>
       </c>
       <c r="Q153" t="s">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="R153" t="s">
         <v>1693</v>
@@ -15689,7 +15685,7 @@
         <v>1698</v>
       </c>
       <c r="G154" t="s">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="H154" t="s">
         <v>946</v>
@@ -15710,7 +15706,7 @@
         <v>1703</v>
       </c>
       <c r="N154" t="s">
-        <v>204</v>
+        <v>62</v>
       </c>
       <c r="O154" t="s">
         <v>1704</v>
@@ -15719,7 +15715,7 @@
         <v>1705</v>
       </c>
       <c r="Q154" t="s">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="R154" t="s">
         <v>1706</v>
@@ -15776,7 +15772,7 @@
         <v>1703</v>
       </c>
       <c r="N155" t="s">
-        <v>204</v>
+        <v>62</v>
       </c>
       <c r="O155" t="s">
         <v>1710</v>
@@ -15785,7 +15781,7 @@
         <v>1711</v>
       </c>
       <c r="Q155" t="s">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="R155" t="s">
         <v>1712</v>
@@ -15809,7 +15805,7 @@
         <v>1715</v>
       </c>
       <c r="C156" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="D156" t="s">
         <v>1716</v>
@@ -15842,7 +15838,7 @@
         <v>1722</v>
       </c>
       <c r="N156" t="s">
-        <v>204</v>
+        <v>62</v>
       </c>
       <c r="O156" t="s">
         <v>1723</v>
@@ -15851,16 +15847,16 @@
         <v>1724</v>
       </c>
       <c r="Q156" t="s">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="R156" t="s">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="S156" t="s">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="T156" t="s">
-        <v>47</v>
+        <v>80</v>
       </c>
       <c r="U156" t="s">
         <v>476</v>
@@ -15875,22 +15871,22 @@
         <v>1725</v>
       </c>
       <c r="C157" t="s">
+        <v>70</v>
+      </c>
+      <c r="D157" t="s">
         <v>37</v>
       </c>
-      <c r="D157" t="s">
-        <v>97</v>
-      </c>
       <c r="E157" t="s">
-        <v>98</v>
+        <v>38</v>
       </c>
       <c r="F157" t="s">
         <v>1726</v>
       </c>
       <c r="G157" t="s">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="H157" t="s">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="I157" t="s">
         <v>1727</v>
@@ -15908,7 +15904,7 @@
         <v>1731</v>
       </c>
       <c r="N157" t="s">
-        <v>204</v>
+        <v>62</v>
       </c>
       <c r="O157" t="s">
         <v>1732</v>
@@ -15917,7 +15913,7 @@
         <v>1733</v>
       </c>
       <c r="Q157" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="R157" t="s">
         <v>1734</v>
@@ -15941,13 +15937,13 @@
         <v>1737</v>
       </c>
       <c r="C158" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="D158" t="s">
         <v>761</v>
       </c>
       <c r="E158" t="s">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="F158" t="s">
         <v>1738</v>
@@ -15956,7 +15952,7 @@
         <v>27</v>
       </c>
       <c r="H158" t="s">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="I158" t="s">
         <v>1739</v>
@@ -15974,7 +15970,7 @@
         <v>1743</v>
       </c>
       <c r="N158" t="s">
-        <v>204</v>
+        <v>62</v>
       </c>
       <c r="O158" t="s">
         <v>1744</v>
@@ -15983,7 +15979,7 @@
         <v>1745</v>
       </c>
       <c r="Q158" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="R158" t="s">
         <v>1746</v>
@@ -16007,13 +16003,13 @@
         <v>1749</v>
       </c>
       <c r="C159" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="D159" t="s">
         <v>1750</v>
       </c>
       <c r="E159" t="s">
-        <v>129</v>
+        <v>158</v>
       </c>
       <c r="F159" t="s">
         <v>1738</v>
@@ -16022,7 +16018,7 @@
         <v>27</v>
       </c>
       <c r="H159" t="s">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="I159" t="s">
         <v>1751</v>
@@ -16038,7 +16034,7 @@
         <v>1754</v>
       </c>
       <c r="N159" t="s">
-        <v>204</v>
+        <v>62</v>
       </c>
       <c r="O159" t="s">
         <v>1755</v>
@@ -16047,7 +16043,7 @@
         <v>1756</v>
       </c>
       <c r="Q159" t="s">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="R159" t="s">
         <v>1746</v>
@@ -16071,13 +16067,13 @@
         <v>1757</v>
       </c>
       <c r="C160" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="D160" t="s">
         <v>1750</v>
       </c>
       <c r="E160" t="s">
-        <v>129</v>
+        <v>158</v>
       </c>
       <c r="F160" t="s">
         <v>1738</v>
@@ -16086,7 +16082,7 @@
         <v>27</v>
       </c>
       <c r="H160" t="s">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="I160" t="s">
         <v>1758</v>
@@ -16102,7 +16098,7 @@
         <v>1761</v>
       </c>
       <c r="N160" t="s">
-        <v>204</v>
+        <v>62</v>
       </c>
       <c r="O160" t="s">
         <v>1762</v>
@@ -16135,7 +16131,7 @@
         <v>1764</v>
       </c>
       <c r="C161" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="D161" t="s">
         <v>1765</v>
@@ -16150,7 +16146,7 @@
         <v>27</v>
       </c>
       <c r="H161" t="s">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="I161" t="s">
         <v>1767</v>
@@ -16166,7 +16162,7 @@
         <v>1770</v>
       </c>
       <c r="N161" t="s">
-        <v>204</v>
+        <v>62</v>
       </c>
       <c r="O161" t="s">
         <v>1771</v>
@@ -16178,13 +16174,13 @@
         <v>243</v>
       </c>
       <c r="R161" t="s">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="S161" t="s">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="T161" t="s">
-        <v>47</v>
+        <v>80</v>
       </c>
       <c r="U161" t="s">
         <v>476</v>
@@ -16199,13 +16195,13 @@
         <v>1773</v>
       </c>
       <c r="C162" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="D162" t="s">
         <v>1549</v>
       </c>
       <c r="E162" t="s">
-        <v>98</v>
+        <v>38</v>
       </c>
       <c r="F162" t="s">
         <v>1774</v>
@@ -16214,7 +16210,7 @@
         <v>27</v>
       </c>
       <c r="H162" t="s">
-        <v>145</v>
+        <v>174</v>
       </c>
       <c r="I162" t="s">
         <v>1775</v>
@@ -16230,7 +16226,7 @@
         <v>1778</v>
       </c>
       <c r="N162" t="s">
-        <v>204</v>
+        <v>62</v>
       </c>
       <c r="O162" t="s">
         <v>1779</v>
@@ -16239,7 +16235,7 @@
         <v>1780</v>
       </c>
       <c r="Q162" t="s">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="R162" t="s">
         <v>1781</v>
@@ -16263,7 +16259,7 @@
         <v>1784</v>
       </c>
       <c r="C163" t="s">
-        <v>83</v>
+        <v>115</v>
       </c>
       <c r="D163" t="s">
         <v>1148</v>
@@ -16292,7 +16288,7 @@
         <v>1790</v>
       </c>
       <c r="N163" t="s">
-        <v>204</v>
+        <v>62</v>
       </c>
       <c r="O163" t="s">
         <v>1791</v>
@@ -16301,7 +16297,7 @@
         <v>1792</v>
       </c>
       <c r="Q163" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="R163" t="s">
         <v>1793</v>

--- a/Objets_parlementaires_Jura.xlsx
+++ b/Objets_parlementaires_Jura.xlsx
@@ -80,24 +80,105 @@
     <t xml:space="preserve">Statut_Change_Date</t>
   </si>
   <si>
+    <t xml:space="preserve">26.7687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fra.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dobler Loïc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grenzsicherheit: Instabilität als Führungsstil?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sécurité aux frontières : l'instabilité comme mode de gestion ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Depuis le 1er août, l'Office fédéral de la douane et de la sécurité des frontières a réduit ses régions de 6 à 4. Dès janvier 2027, ses niveaux locaux passeront de 23 à 16, avec 25 postes de cadres en moins ; les cadres en poste devront se porter candidats aux postes restants. Ce maillon essentiel aux régions frontalières connaît depuis des années des tensions internes .&amp;nbsp;&lt;br&gt;Le Conseil fédéral garantit-il enfin une stabilité durable à son personnel et aux régions frontalières ?&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Am 1. August hat das Bundesamt für Zoll und Grenzsicherheit die Zahl seiner Regionen von 6 auf 4 reduziert. Ab Januar 2027 wird die Zahl der Lokalebenen von 23 auf 16 sinken, wobei 25 Kaderstellen wegfallen; die derzeitigen Führungskräfte müssen sich um die verbleibenden Stellen bewerben. Seit Jahren ist dieses für die Grenzregionen unverzichtbare Bindeglied von internen Spannungen geprägt.&amp;nbsp;&lt;br&gt;Gewährleistet der Bundesrat endlich dauerhafte Stabilität für sein Personal und für die Grenzregionen?&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Erledigt / Liquidé</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20267687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20267687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Titre uniquement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staatspolitik|Internationale Politik</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politique d'Etat|Politique internationale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politica nazionale|Politica internazionale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVEK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Schienengüterverkehr: Wird die Westschweiz geopfert? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fret ferroviaire : la Suisse romande sacrifiée ? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Dès décembre 2026, les CFF réorganisent le trafic par wagons isolés, touchant 200 collaborateurs. Une cinquantaine de points de desserte sur 280 ne seront plus desservis. Les équipes de manœuvre de Suisse romande sont particulièrement touchées, avec des changements à Yverdon, Payerne, Fribourg, Delémont et Martigny.&amp;nbsp;&lt;br&gt;Le Conseil fédéral veille-t-il à ce que les CFF assurent une répartition équilibrée des prestations et des emplois entre les régions par les CFF ?&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Ab Dezember 2026 wird die SBB den Einzelwagenladungsverkehr neu organisieren, wovon 200 Mitarbeitende betroffen sind. Etwa 50 von insgesamt 280 Verladestellen werden nicht mehr bedient werden. Besonders betroffen sind die Rangierteams in der Westschweiz, wo es zu Änderungen in Yverdon, Payerne, Freiburg, Delsberg und Martigny kommt.&amp;nbsp;&lt;br&gt;Sorgt der Bundesrat dafür, dass die SBB eine ausgewogene Verteilung der Leistungen und Arbeitsplätze auf die Regionen gewährleistet?&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20267688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20267688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verkehr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transports</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trasporti</t>
+  </si>
+  <si>
     <t xml:space="preserve">26.4169</t>
   </si>
   <si>
     <t xml:space="preserve">Mo.</t>
   </si>
   <si>
-    <t xml:space="preserve">Dobler Loïc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PS</t>
-  </si>
-  <si>
     <t xml:space="preserve">2026-09-17</t>
   </si>
   <si>
-    <t xml:space="preserve">NR</t>
-  </si>
-  <si>
     <t xml:space="preserve">Titel folgt</t>
   </si>
   <si>
@@ -119,9 +200,6 @@
     <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20264169</t>
   </si>
   <si>
-    <t xml:space="preserve">Titre uniquement</t>
-  </si>
-  <si>
     <t xml:space="preserve">Soziale Fragen|Sozialer Schutz</t>
   </si>
   <si>
@@ -209,9 +287,6 @@
     <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, die erforderlichen Gesetzesanpassungen vorzulegen, so dass für kriminelle Ausländer bei einer längerfristigen Freiheitsstrafe ab einem Jahr – unabhängig davon, ob diese unbedingt, teilbedingt oder bedingt ausfällt – in jedem Fall zwingend eine Landesverweisung angeordnet und vollzogen werden muss.&amp;nbsp;&lt;/p&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">Erledigt / Liquidé</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263131</t>
   </si>
   <si>
@@ -269,12 +344,6 @@
     <t xml:space="preserve">26.7829</t>
   </si>
   <si>
-    <t xml:space="preserve">Fra.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UVEK</t>
-  </si>
-  <si>
     <t xml:space="preserve">Der Bund gibt den Apron im Doubs auf</t>
   </si>
   <si>
@@ -299,9 +368,6 @@
     <t xml:space="preserve">Locher Miriam</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-15</t>
-  </si>
-  <si>
     <t xml:space="preserve">Bedrohungsmanagement schweizweit stärken, Gefährdung früh erkennen und Gewalttaten verhindern</t>
   </si>
   <si>
@@ -324,72 +390,6 @@
   </si>
   <si>
     <t xml:space="preserve">Politica nazionale|Politica di sicurezza|Questioni sociali</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EFD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grenzsicherheit: Instabilität als Führungsstil?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sécurité aux frontières : l'instabilité comme mode de gestion ?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Depuis le 1er août, l'Office fédéral de la douane et de la sécurité des frontières a réduit ses régions de 6 à 4. Dès janvier 2027, ses niveaux locaux passeront de 23 à 16, avec 25 postes de cadres en moins ; les cadres en poste devront se porter candidats aux postes restants. Ce maillon essentiel aux régions frontalières connaît depuis des années des tensions internes .&amp;nbsp;&lt;br&gt;Le Conseil fédéral garantit-il enfin une stabilité durable à son personnel et aux régions frontalières ?&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Am 1. August hat das Bundesamt für Zoll und Grenzsicherheit die Zahl seiner Regionen von 6 auf 4 reduziert. Ab Januar 2027 wird die Zahl der Lokalebenen von 23 auf 16 sinken, wobei 25 Kaderstellen wegfallen; die derzeitigen Führungskräfte müssen sich um die verbleibenden Stellen bewerben. Seit Jahren ist dieses für die Grenzregionen unverzichtbare Bindeglied von internen Spannungen geprägt.&amp;nbsp;&lt;br&gt;Gewährleistet der Bundesrat endlich dauerhafte Stabilität für sein Personal und für die Grenzregionen?&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20267687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20267687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staatspolitik|Internationale Politik</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politique d'Etat|Politique internationale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politica nazionale|Politica internazionale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Schienengüterverkehr: Wird die Westschweiz geopfert? </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fret ferroviaire : la Suisse romande sacrifiée ? </t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Dès décembre 2026, les CFF réorganisent le trafic par wagons isolés, touchant 200 collaborateurs. Une cinquantaine de points de desserte sur 280 ne seront plus desservis. Les équipes de manœuvre de Suisse romande sont particulièrement touchées, avec des changements à Yverdon, Payerne, Fribourg, Delémont et Martigny.&amp;nbsp;&lt;br&gt;Le Conseil fédéral veille-t-il à ce que les CFF assurent une répartition équilibrée des prestations et des emplois entre les régions par les CFF ?&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Ab Dezember 2026 wird die SBB den Einzelwagenladungsverkehr neu organisieren, wovon 200 Mitarbeitende betroffen sind. Etwa 50 von insgesamt 280 Verladestellen werden nicht mehr bedient werden. Besonders betroffen sind die Rangierteams in der Westschweiz, wo es zu Änderungen in Yverdon, Payerne, Freiburg, Delsberg und Martigny kommt.&amp;nbsp;&lt;br&gt;Sorgt der Bundesrat dafür, dass die SBB eine ausgewogene Verteilung der Leistungen und Arbeitsplätze auf die Regionen gewährleistet?&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20267688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20267688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verkehr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transports</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trasporti</t>
   </si>
   <si>
     <t xml:space="preserve">26.312</t>
@@ -5850,7 +5850,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>20264169</v>
+        <v>20267687</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
@@ -5870,270 +5870,272 @@
       <c r="G2" t="s">
         <v>27</v>
       </c>
-      <c r="H2"/>
+      <c r="H2" t="s">
+        <v>28</v>
+      </c>
       <c r="I2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J2" t="s">
-        <v>29</v>
-      </c>
-      <c r="K2" t="s">
         <v>30</v>
       </c>
+      <c r="K2"/>
       <c r="L2" t="s">
         <v>31</v>
       </c>
-      <c r="M2"/>
+      <c r="M2" t="s">
+        <v>32</v>
+      </c>
       <c r="N2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="R2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="T2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="U2" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="V2"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>20263628</v>
+        <v>20267688</v>
       </c>
       <c r="B3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C3" t="s">
         <v>23</v>
       </c>
       <c r="D3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3" t="s">
+        <v>42</v>
+      </c>
+      <c r="I3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J3" t="s">
+        <v>44</v>
+      </c>
+      <c r="K3"/>
+      <c r="L3" t="s">
+        <v>45</v>
+      </c>
+      <c r="M3" t="s">
+        <v>46</v>
+      </c>
+      <c r="N3" t="s">
+        <v>33</v>
+      </c>
+      <c r="O3" t="s">
+        <v>47</v>
+      </c>
+      <c r="P3" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>36</v>
+      </c>
+      <c r="R3" t="s">
+        <v>49</v>
+      </c>
+      <c r="S3" t="s">
+        <v>50</v>
+      </c>
+      <c r="T3" t="s">
+        <v>51</v>
+      </c>
+      <c r="U3" t="s">
         <v>40</v>
-      </c>
-      <c r="E3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G3" t="s">
-        <v>43</v>
-      </c>
-      <c r="H3" t="s">
-        <v>44</v>
-      </c>
-      <c r="I3" t="s">
-        <v>45</v>
-      </c>
-      <c r="J3" t="s">
-        <v>46</v>
-      </c>
-      <c r="K3" t="s">
-        <v>47</v>
-      </c>
-      <c r="L3" t="s">
-        <v>48</v>
-      </c>
-      <c r="M3" t="s">
-        <v>49</v>
-      </c>
-      <c r="N3" t="s">
-        <v>50</v>
-      </c>
-      <c r="O3" t="s">
-        <v>51</v>
-      </c>
-      <c r="P3" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>35</v>
-      </c>
-      <c r="R3" t="s">
-        <v>53</v>
-      </c>
-      <c r="S3" t="s">
-        <v>54</v>
-      </c>
-      <c r="T3" t="s">
-        <v>55</v>
-      </c>
-      <c r="U3" t="s">
-        <v>26</v>
       </c>
       <c r="V3"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>20263131</v>
+        <v>20264169</v>
       </c>
       <c r="B4" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="D4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E4"/>
+        <v>24</v>
+      </c>
+      <c r="E4" t="s">
+        <v>25</v>
+      </c>
       <c r="F4" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="G4" t="s">
         <v>27</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4"/>
+      <c r="I4" t="s">
+        <v>55</v>
+      </c>
+      <c r="J4" t="s">
+        <v>56</v>
+      </c>
+      <c r="K4" t="s">
+        <v>57</v>
+      </c>
+      <c r="L4" t="s">
+        <v>58</v>
+      </c>
+      <c r="M4"/>
+      <c r="N4" t="s">
         <v>59</v>
       </c>
-      <c r="I4" t="s">
+      <c r="O4" t="s">
         <v>60</v>
       </c>
-      <c r="J4" t="s">
+      <c r="P4" t="s">
         <v>61</v>
       </c>
-      <c r="K4" t="s">
+      <c r="Q4" t="s">
+        <v>36</v>
+      </c>
+      <c r="R4" t="s">
         <v>62</v>
       </c>
-      <c r="L4" t="s">
+      <c r="S4" t="s">
         <v>63</v>
       </c>
-      <c r="M4" t="s">
+      <c r="T4" t="s">
         <v>64</v>
       </c>
-      <c r="N4" t="s">
-        <v>65</v>
-      </c>
-      <c r="O4" t="s">
-        <v>66</v>
-      </c>
-      <c r="P4" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>68</v>
-      </c>
-      <c r="R4" t="s">
-        <v>69</v>
-      </c>
-      <c r="S4" t="s">
-        <v>70</v>
-      </c>
-      <c r="T4" t="s">
-        <v>71</v>
-      </c>
       <c r="U4" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="V4"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>20264146</v>
+        <v>20263628</v>
       </c>
       <c r="B5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D5" t="s">
+        <v>66</v>
+      </c>
+      <c r="E5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F5" t="s">
+        <v>68</v>
+      </c>
+      <c r="G5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H5" t="s">
+        <v>70</v>
+      </c>
+      <c r="I5" t="s">
+        <v>71</v>
+      </c>
+      <c r="J5" t="s">
         <v>72</v>
       </c>
-      <c r="C5" t="s">
+      <c r="K5" t="s">
         <v>73</v>
       </c>
-      <c r="D5" t="s">
+      <c r="L5" t="s">
         <v>74</v>
       </c>
-      <c r="E5" t="s">
+      <c r="M5" t="s">
         <v>75</v>
       </c>
-      <c r="F5" t="s">
+      <c r="N5" t="s">
         <v>76</v>
       </c>
-      <c r="G5" t="s">
-        <v>27</v>
-      </c>
-      <c r="H5"/>
-      <c r="I5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J5" t="s">
+      <c r="O5" t="s">
         <v>77</v>
       </c>
-      <c r="K5" t="s">
-        <v>30</v>
-      </c>
-      <c r="L5" t="s">
+      <c r="P5" t="s">
         <v>78</v>
       </c>
-      <c r="M5"/>
-      <c r="N5" t="s">
-        <v>32</v>
-      </c>
-      <c r="O5" t="s">
+      <c r="Q5" t="s">
+        <v>36</v>
+      </c>
+      <c r="R5" t="s">
         <v>79</v>
       </c>
-      <c r="P5" t="s">
+      <c r="S5" t="s">
         <v>80</v>
       </c>
-      <c r="Q5" t="s">
-        <v>35</v>
-      </c>
-      <c r="R5" t="s">
+      <c r="T5" t="s">
         <v>81</v>
       </c>
-      <c r="S5" t="s">
-        <v>82</v>
-      </c>
-      <c r="T5" t="s">
-        <v>83</v>
-      </c>
       <c r="U5" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="V5"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>20267829</v>
+        <v>20263131</v>
       </c>
       <c r="B6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D6" t="s">
+        <v>83</v>
+      </c>
+      <c r="E6"/>
+      <c r="F6" t="s">
         <v>84</v>
-      </c>
-      <c r="C6" t="s">
-        <v>85</v>
-      </c>
-      <c r="D6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F6" t="s">
-        <v>76</v>
       </c>
       <c r="G6" t="s">
         <v>27</v>
       </c>
       <c r="H6" t="s">
+        <v>85</v>
+      </c>
+      <c r="I6" t="s">
         <v>86</v>
       </c>
-      <c r="I6" t="s">
+      <c r="J6" t="s">
         <v>87</v>
       </c>
-      <c r="J6" t="s">
+      <c r="K6" t="s">
         <v>88</v>
       </c>
-      <c r="K6"/>
       <c r="L6" t="s">
         <v>89</v>
       </c>
@@ -6141,7 +6143,7 @@
         <v>90</v>
       </c>
       <c r="N6" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="O6" t="s">
         <v>91</v>
@@ -6150,87 +6152,93 @@
         <v>92</v>
       </c>
       <c r="Q6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R6"/>
-      <c r="S6"/>
-      <c r="T6"/>
+        <v>93</v>
+      </c>
+      <c r="R6" t="s">
+        <v>94</v>
+      </c>
+      <c r="S6" t="s">
+        <v>95</v>
+      </c>
+      <c r="T6" t="s">
+        <v>96</v>
+      </c>
       <c r="U6" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="V6"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>20264127</v>
+        <v>20264146</v>
       </c>
       <c r="B7" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C7" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D7" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="E7" t="s">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="F7" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G7" t="s">
         <v>27</v>
       </c>
       <c r="H7"/>
       <c r="I7" t="s">
-        <v>96</v>
+        <v>55</v>
       </c>
       <c r="J7" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="K7" t="s">
-        <v>30</v>
-      </c>
-      <c r="L7"/>
-      <c r="M7" t="s">
-        <v>98</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="L7" t="s">
+        <v>103</v>
+      </c>
+      <c r="M7"/>
       <c r="N7" t="s">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="O7" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="P7" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="Q7" t="s">
-        <v>68</v>
+        <v>36</v>
       </c>
       <c r="R7" t="s">
+        <v>106</v>
+      </c>
+      <c r="S7" t="s">
+        <v>107</v>
+      </c>
+      <c r="T7" t="s">
+        <v>108</v>
+      </c>
+      <c r="U7" t="s">
         <v>101</v>
-      </c>
-      <c r="S7" t="s">
-        <v>102</v>
-      </c>
-      <c r="T7" t="s">
-        <v>103</v>
-      </c>
-      <c r="U7" t="s">
-        <v>95</v>
       </c>
       <c r="V7"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>20267687</v>
+        <v>20267829</v>
       </c>
       <c r="B8" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C8" t="s">
-        <v>85</v>
+        <v>23</v>
       </c>
       <c r="D8" t="s">
         <v>24</v>
@@ -6239,95 +6247,85 @@
         <v>25</v>
       </c>
       <c r="F8" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G8" t="s">
         <v>27</v>
       </c>
       <c r="H8" t="s">
-        <v>105</v>
+        <v>42</v>
       </c>
       <c r="I8" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="J8" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="K8"/>
       <c r="L8" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="M8" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="N8" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="O8" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="P8" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="Q8" t="s">
-        <v>35</v>
-      </c>
-      <c r="R8" t="s">
-        <v>112</v>
-      </c>
-      <c r="S8" t="s">
-        <v>113</v>
-      </c>
-      <c r="T8" t="s">
-        <v>114</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="R8"/>
+      <c r="S8"/>
+      <c r="T8"/>
       <c r="U8" t="s">
-        <v>115</v>
-      </c>
-      <c r="V8" t="s">
-        <v>115</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="V8"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>20267688</v>
+        <v>20264127</v>
       </c>
       <c r="B9" t="s">
         <v>116</v>
       </c>
       <c r="C9" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="D9" t="s">
-        <v>24</v>
+        <v>117</v>
       </c>
       <c r="E9" t="s">
         <v>25</v>
       </c>
       <c r="F9" t="s">
-        <v>95</v>
+        <v>26</v>
       </c>
       <c r="G9" t="s">
         <v>27</v>
       </c>
-      <c r="H9" t="s">
-        <v>86</v>
-      </c>
+      <c r="H9"/>
       <c r="I9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J9" t="s">
-        <v>118</v>
-      </c>
-      <c r="K9"/>
-      <c r="L9" t="s">
         <v>119</v>
       </c>
+      <c r="K9" t="s">
+        <v>57</v>
+      </c>
+      <c r="L9"/>
       <c r="M9" t="s">
         <v>120</v>
       </c>
       <c r="N9" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="O9" t="s">
         <v>121</v>
@@ -6336,7 +6334,7 @@
         <v>122</v>
       </c>
       <c r="Q9" t="s">
-        <v>35</v>
+        <v>93</v>
       </c>
       <c r="R9" t="s">
         <v>123</v>
@@ -6348,11 +6346,9 @@
         <v>125</v>
       </c>
       <c r="U9" t="s">
-        <v>115</v>
-      </c>
-      <c r="V9" t="s">
-        <v>115</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="V9"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -6400,7 +6396,7 @@
         <v>138</v>
       </c>
       <c r="Q10" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="R10"/>
       <c r="S10"/>
@@ -6418,22 +6414,22 @@
         <v>140</v>
       </c>
       <c r="C11" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D11" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="E11" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="F11" t="s">
         <v>141</v>
       </c>
       <c r="G11" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="H11" t="s">
-        <v>105</v>
+        <v>28</v>
       </c>
       <c r="I11" t="s">
         <v>142</v>
@@ -6460,7 +6456,7 @@
         <v>149</v>
       </c>
       <c r="Q11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="R11" t="s">
         <v>150</v>
@@ -6484,7 +6480,7 @@
         <v>154</v>
       </c>
       <c r="C12" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D12" t="s">
         <v>155</v>
@@ -6496,10 +6492,10 @@
         <v>141</v>
       </c>
       <c r="G12" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="H12" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="I12" t="s">
         <v>156</v>
@@ -6526,7 +6522,7 @@
         <v>162</v>
       </c>
       <c r="Q12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="R12" t="s">
         <v>163</v>
@@ -6550,7 +6546,7 @@
         <v>166</v>
       </c>
       <c r="C13" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D13" t="s">
         <v>167</v>
@@ -6565,7 +6561,7 @@
         <v>27</v>
       </c>
       <c r="H13" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="I13" t="s">
         <v>169</v>
@@ -6616,7 +6612,7 @@
         <v>181</v>
       </c>
       <c r="C14" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D14" t="s">
         <v>182</v>
@@ -6682,22 +6678,22 @@
         <v>195</v>
       </c>
       <c r="C15" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="D15" t="s">
         <v>196</v>
       </c>
       <c r="E15" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="F15" t="s">
         <v>197</v>
       </c>
       <c r="G15" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="H15" t="s">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="I15" t="s">
         <v>198</v>
@@ -6706,13 +6702,13 @@
         <v>199</v>
       </c>
       <c r="K15" t="s">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="L15" t="s">
         <v>200</v>
       </c>
       <c r="M15" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="N15" t="s">
         <v>147</v>
@@ -6724,16 +6720,16 @@
         <v>202</v>
       </c>
       <c r="Q15" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="R15" t="s">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="S15" t="s">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="T15" t="s">
-        <v>71</v>
+        <v>96</v>
       </c>
       <c r="U15" t="s">
         <v>153</v>
@@ -6748,7 +6744,7 @@
         <v>203</v>
       </c>
       <c r="C16" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="D16" t="s">
         <v>204</v>
@@ -6763,7 +6759,7 @@
         <v>27</v>
       </c>
       <c r="H16" t="s">
-        <v>105</v>
+        <v>28</v>
       </c>
       <c r="I16" t="s">
         <v>207</v>
@@ -6817,19 +6813,19 @@
         <v>218</v>
       </c>
       <c r="D17" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="E17" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="F17" t="s">
         <v>219</v>
       </c>
       <c r="G17" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="H17" t="s">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="I17" t="s">
         <v>220</v>
@@ -6847,7 +6843,7 @@
         <v>224</v>
       </c>
       <c r="N17" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="O17" t="s">
         <v>225</v>
@@ -6856,7 +6852,7 @@
         <v>226</v>
       </c>
       <c r="Q17" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="R17" t="s">
         <v>227</v>
@@ -6880,7 +6876,7 @@
         <v>231</v>
       </c>
       <c r="C18" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D18" t="s">
         <v>24</v>
@@ -6922,7 +6918,7 @@
         <v>238</v>
       </c>
       <c r="Q18" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="R18" t="s">
         <v>239</v>
@@ -6946,7 +6942,7 @@
         <v>243</v>
       </c>
       <c r="C19" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D19" t="s">
         <v>244</v>
@@ -7012,7 +7008,7 @@
         <v>258</v>
       </c>
       <c r="C20" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D20" t="s">
         <v>244</v>
@@ -7078,7 +7074,7 @@
         <v>266</v>
       </c>
       <c r="C21" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D21" t="s">
         <v>267</v>
@@ -7093,7 +7089,7 @@
         <v>27</v>
       </c>
       <c r="H21" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="I21" t="s">
         <v>269</v>
@@ -7144,7 +7140,7 @@
         <v>280</v>
       </c>
       <c r="C22" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D22" t="s">
         <v>24</v>
@@ -7159,7 +7155,7 @@
         <v>27</v>
       </c>
       <c r="H22" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="I22" t="s">
         <v>281</v>
@@ -7186,7 +7182,7 @@
         <v>287</v>
       </c>
       <c r="Q22" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="R22" t="s">
         <v>288</v>
@@ -7210,7 +7206,7 @@
         <v>291</v>
       </c>
       <c r="C23" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="D23" t="s">
         <v>155</v>
@@ -7222,7 +7218,7 @@
         <v>292</v>
       </c>
       <c r="G23" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="H23" t="s">
         <v>184</v>
@@ -7252,7 +7248,7 @@
         <v>299</v>
       </c>
       <c r="Q23" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="R23" t="s">
         <v>300</v>
@@ -7276,7 +7272,7 @@
         <v>304</v>
       </c>
       <c r="C24" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D24" t="s">
         <v>244</v>
@@ -7309,7 +7305,7 @@
         <v>310</v>
       </c>
       <c r="N24" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="O24" t="s">
         <v>311</v>
@@ -7345,19 +7341,19 @@
         <v>218</v>
       </c>
       <c r="D25" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="E25" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="F25" t="s">
         <v>314</v>
       </c>
       <c r="G25" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="H25" t="s">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="I25" t="s">
         <v>315</v>
@@ -7384,7 +7380,7 @@
         <v>322</v>
       </c>
       <c r="Q25" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="R25" t="s">
         <v>323</v>
@@ -7408,7 +7404,7 @@
         <v>327</v>
       </c>
       <c r="C26" t="s">
-        <v>85</v>
+        <v>23</v>
       </c>
       <c r="D26" t="s">
         <v>24</v>
@@ -7423,7 +7419,7 @@
         <v>27</v>
       </c>
       <c r="H26" t="s">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="I26" t="s">
         <v>329</v>
@@ -7448,7 +7444,7 @@
         <v>334</v>
       </c>
       <c r="Q26" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="R26" t="s">
         <v>335</v>
@@ -7472,7 +7468,7 @@
         <v>339</v>
       </c>
       <c r="C27" t="s">
-        <v>85</v>
+        <v>23</v>
       </c>
       <c r="D27" t="s">
         <v>24</v>
@@ -7503,7 +7499,7 @@
         <v>344</v>
       </c>
       <c r="N27" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="O27" t="s">
         <v>345</v>
@@ -7512,7 +7508,7 @@
         <v>346</v>
       </c>
       <c r="Q27" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="R27" t="s">
         <v>347</v>
@@ -7536,13 +7532,13 @@
         <v>350</v>
       </c>
       <c r="C28" t="s">
-        <v>85</v>
+        <v>23</v>
       </c>
       <c r="D28" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="E28" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="F28" t="s">
         <v>340</v>
@@ -7567,7 +7563,7 @@
         <v>354</v>
       </c>
       <c r="N28" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="O28" t="s">
         <v>355</v>
@@ -7576,7 +7572,7 @@
         <v>356</v>
       </c>
       <c r="Q28" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="R28" t="s">
         <v>357</v>
@@ -7600,7 +7596,7 @@
         <v>360</v>
       </c>
       <c r="C29" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D29" t="s">
         <v>361</v>
@@ -7633,7 +7629,7 @@
         <v>367</v>
       </c>
       <c r="N29" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="O29" t="s">
         <v>368</v>
@@ -7642,7 +7638,7 @@
         <v>369</v>
       </c>
       <c r="Q29" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="R29" t="s">
         <v>370</v>
@@ -7666,22 +7662,22 @@
         <v>374</v>
       </c>
       <c r="C30" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D30" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="E30" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="F30" t="s">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="G30" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="H30" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="I30" t="s">
         <v>375</v>
@@ -7699,7 +7695,7 @@
         <v>379</v>
       </c>
       <c r="N30" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="O30" t="s">
         <v>380</v>
@@ -7708,7 +7704,7 @@
         <v>381</v>
       </c>
       <c r="Q30" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="R30" t="s">
         <v>382</v>
@@ -7732,7 +7728,7 @@
         <v>385</v>
       </c>
       <c r="C31" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="D31" t="s">
         <v>386</v>
@@ -7798,7 +7794,7 @@
         <v>398</v>
       </c>
       <c r="C32" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D32" t="s">
         <v>399</v>
@@ -7813,7 +7809,7 @@
         <v>27</v>
       </c>
       <c r="H32" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="I32" t="s">
         <v>400</v>
@@ -7864,7 +7860,7 @@
         <v>407</v>
       </c>
       <c r="C33" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="D33" t="s">
         <v>408</v>
@@ -7877,7 +7873,7 @@
         <v>27</v>
       </c>
       <c r="H33" t="s">
-        <v>105</v>
+        <v>28</v>
       </c>
       <c r="I33" t="s">
         <v>409</v>
@@ -7928,13 +7924,13 @@
         <v>420</v>
       </c>
       <c r="C34" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D34" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="E34" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="F34" t="s">
         <v>292</v>
@@ -7943,7 +7939,7 @@
         <v>27</v>
       </c>
       <c r="H34" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="I34" t="s">
         <v>421</v>
@@ -7970,16 +7966,16 @@
         <v>427</v>
       </c>
       <c r="Q34" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="R34" t="s">
-        <v>123</v>
+        <v>49</v>
       </c>
       <c r="S34" t="s">
-        <v>124</v>
+        <v>50</v>
       </c>
       <c r="T34" t="s">
-        <v>125</v>
+        <v>51</v>
       </c>
       <c r="U34" t="s">
         <v>419</v>
@@ -7994,13 +7990,13 @@
         <v>428</v>
       </c>
       <c r="C35" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D35" t="s">
         <v>429</v>
       </c>
       <c r="E35" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="F35" t="s">
         <v>430</v>
@@ -8060,16 +8056,16 @@
         <v>442</v>
       </c>
       <c r="C36" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="D36" t="s">
         <v>443</v>
       </c>
       <c r="E36" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="F36" t="s">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="G36" t="s">
         <v>27</v>
@@ -8102,7 +8098,7 @@
         <v>450</v>
       </c>
       <c r="Q36" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="R36" t="s">
         <v>451</v>
@@ -8126,13 +8122,13 @@
         <v>455</v>
       </c>
       <c r="C37" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D37" t="s">
         <v>456</v>
       </c>
       <c r="E37" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="F37" t="s">
         <v>457</v>
@@ -8141,7 +8137,7 @@
         <v>27</v>
       </c>
       <c r="H37" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="I37" t="s">
         <v>458</v>
@@ -8171,13 +8167,13 @@
         <v>253</v>
       </c>
       <c r="R37" t="s">
-        <v>123</v>
+        <v>49</v>
       </c>
       <c r="S37" t="s">
-        <v>124</v>
+        <v>50</v>
       </c>
       <c r="T37" t="s">
-        <v>125</v>
+        <v>51</v>
       </c>
       <c r="U37" t="s">
         <v>454</v>
@@ -8192,22 +8188,22 @@
         <v>465</v>
       </c>
       <c r="C38" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="D38" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="E38" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="F38" t="s">
         <v>466</v>
       </c>
       <c r="G38" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="H38" t="s">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="I38" t="s">
         <v>467</v>
@@ -8225,7 +8221,7 @@
         <v>471</v>
       </c>
       <c r="N38" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="O38" t="s">
         <v>472</v>
@@ -8234,16 +8230,16 @@
         <v>473</v>
       </c>
       <c r="Q38" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="R38" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
       <c r="S38" t="s">
-        <v>102</v>
+        <v>124</v>
       </c>
       <c r="T38" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="U38" t="s">
         <v>474</v>
@@ -8258,7 +8254,7 @@
         <v>475</v>
       </c>
       <c r="C39" t="s">
-        <v>85</v>
+        <v>23</v>
       </c>
       <c r="D39" t="s">
         <v>361</v>
@@ -8289,7 +8285,7 @@
         <v>480</v>
       </c>
       <c r="N39" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="O39" t="s">
         <v>481</v>
@@ -8298,7 +8294,7 @@
         <v>482</v>
       </c>
       <c r="Q39" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="R39" t="s">
         <v>483</v>
@@ -8322,7 +8318,7 @@
         <v>487</v>
       </c>
       <c r="C40" t="s">
-        <v>85</v>
+        <v>23</v>
       </c>
       <c r="D40" t="s">
         <v>488</v>
@@ -8337,7 +8333,7 @@
         <v>27</v>
       </c>
       <c r="H40" t="s">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="I40" t="s">
         <v>490</v>
@@ -8353,7 +8349,7 @@
         <v>493</v>
       </c>
       <c r="N40" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="O40" t="s">
         <v>494</v>
@@ -8397,7 +8393,7 @@
       </c>
       <c r="G41"/>
       <c r="H41" t="s">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="I41" t="s">
         <v>502</v>
@@ -8411,7 +8407,7 @@
       <c r="L41"/>
       <c r="M41"/>
       <c r="N41" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="O41" t="s">
         <v>505</v>
@@ -8420,7 +8416,7 @@
         <v>506</v>
       </c>
       <c r="Q41" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="R41" t="s">
         <v>439</v>
@@ -8444,7 +8440,7 @@
         <v>507</v>
       </c>
       <c r="C42" t="s">
-        <v>85</v>
+        <v>23</v>
       </c>
       <c r="D42" t="s">
         <v>386</v>
@@ -8475,7 +8471,7 @@
         <v>512</v>
       </c>
       <c r="N42" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="O42" t="s">
         <v>513</v>
@@ -8484,7 +8480,7 @@
         <v>514</v>
       </c>
       <c r="Q42" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="R42" t="s">
         <v>515</v>
@@ -8508,7 +8504,7 @@
         <v>518</v>
       </c>
       <c r="C43" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="D43" t="s">
         <v>519</v>
@@ -8523,7 +8519,7 @@
         <v>27</v>
       </c>
       <c r="H43" t="s">
-        <v>105</v>
+        <v>28</v>
       </c>
       <c r="I43" t="s">
         <v>521</v>
@@ -8541,7 +8537,7 @@
         <v>525</v>
       </c>
       <c r="N43" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="O43" t="s">
         <v>526</v>
@@ -8550,7 +8546,7 @@
         <v>527</v>
       </c>
       <c r="Q43" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="R43" t="s">
         <v>150</v>
@@ -8574,7 +8570,7 @@
         <v>528</v>
       </c>
       <c r="C44" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D44" t="s">
         <v>529</v>
@@ -8589,7 +8585,7 @@
         <v>27</v>
       </c>
       <c r="H44" t="s">
-        <v>105</v>
+        <v>28</v>
       </c>
       <c r="I44" t="s">
         <v>531</v>
@@ -8640,13 +8636,13 @@
         <v>541</v>
       </c>
       <c r="C45" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D45" t="s">
         <v>542</v>
       </c>
       <c r="E45" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="F45" t="s">
         <v>466</v>
@@ -8655,7 +8651,7 @@
         <v>27</v>
       </c>
       <c r="H45" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="I45" t="s">
         <v>543</v>
@@ -8706,22 +8702,22 @@
         <v>553</v>
       </c>
       <c r="C46" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="D46" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="E46" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="F46" t="s">
         <v>554</v>
       </c>
       <c r="G46" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="H46" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="I46" t="s">
         <v>555</v>
@@ -8748,7 +8744,7 @@
         <v>561</v>
       </c>
       <c r="Q46" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="R46" t="s">
         <v>562</v>
@@ -8775,19 +8771,19 @@
         <v>218</v>
       </c>
       <c r="D47" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="E47" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="F47" t="s">
         <v>554</v>
       </c>
       <c r="G47" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="H47" t="s">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="I47" t="s">
         <v>566</v>
@@ -8814,7 +8810,7 @@
         <v>572</v>
       </c>
       <c r="Q47" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="R47" t="s">
         <v>573</v>
@@ -8838,22 +8834,22 @@
         <v>576</v>
       </c>
       <c r="C48" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D48" t="s">
         <v>577</v>
       </c>
       <c r="E48" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="F48" t="s">
         <v>578</v>
       </c>
       <c r="G48" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="H48" t="s">
-        <v>105</v>
+        <v>28</v>
       </c>
       <c r="I48" t="s">
         <v>579</v>
@@ -8871,7 +8867,7 @@
         <v>583</v>
       </c>
       <c r="N48" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="O48" t="s">
         <v>584</v>
@@ -8904,13 +8900,13 @@
         <v>589</v>
       </c>
       <c r="C49" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="D49" t="s">
         <v>443</v>
       </c>
       <c r="E49" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="F49" t="s">
         <v>362</v>
@@ -8919,7 +8915,7 @@
         <v>27</v>
       </c>
       <c r="H49" t="s">
-        <v>105</v>
+        <v>28</v>
       </c>
       <c r="I49" t="s">
         <v>590</v>
@@ -8970,7 +8966,7 @@
         <v>597</v>
       </c>
       <c r="C50" t="s">
-        <v>85</v>
+        <v>23</v>
       </c>
       <c r="D50" t="s">
         <v>598</v>
@@ -8985,7 +8981,7 @@
         <v>27</v>
       </c>
       <c r="H50" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="I50" t="s">
         <v>600</v>
@@ -9001,7 +8997,7 @@
         <v>603</v>
       </c>
       <c r="N50" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="O50" t="s">
         <v>604</v>
@@ -9010,7 +9006,7 @@
         <v>605</v>
       </c>
       <c r="Q50" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="R50" t="s">
         <v>606</v>
@@ -9034,13 +9030,13 @@
         <v>609</v>
       </c>
       <c r="C51" t="s">
-        <v>85</v>
+        <v>23</v>
       </c>
       <c r="D51" t="s">
         <v>429</v>
       </c>
       <c r="E51" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="F51" t="s">
         <v>599</v>
@@ -9049,7 +9045,7 @@
         <v>27</v>
       </c>
       <c r="H51" t="s">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="I51" t="s">
         <v>610</v>
@@ -9065,7 +9061,7 @@
         <v>613</v>
       </c>
       <c r="N51" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="O51" t="s">
         <v>614</v>
@@ -9074,16 +9070,16 @@
         <v>615</v>
       </c>
       <c r="Q51" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="R51" t="s">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="S51" t="s">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="T51" t="s">
-        <v>71</v>
+        <v>96</v>
       </c>
       <c r="U51" t="s">
         <v>486</v>
@@ -9138,7 +9134,7 @@
         <v>625</v>
       </c>
       <c r="Q52" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="R52" t="s">
         <v>626</v>
@@ -9162,22 +9158,22 @@
         <v>629</v>
       </c>
       <c r="C53" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="D53" t="s">
         <v>630</v>
       </c>
       <c r="E53" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="F53" t="s">
         <v>631</v>
       </c>
       <c r="G53" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="H53" t="s">
-        <v>105</v>
+        <v>28</v>
       </c>
       <c r="I53" t="s">
         <v>632</v>
@@ -9195,7 +9191,7 @@
         <v>636</v>
       </c>
       <c r="N53" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="O53" t="s">
         <v>637</v>
@@ -9204,7 +9200,7 @@
         <v>638</v>
       </c>
       <c r="Q53" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="R53" t="s">
         <v>639</v>
@@ -9243,7 +9239,7 @@
         <v>27</v>
       </c>
       <c r="H54" t="s">
-        <v>105</v>
+        <v>28</v>
       </c>
       <c r="I54" t="s">
         <v>644</v>
@@ -9270,7 +9266,7 @@
         <v>650</v>
       </c>
       <c r="Q54" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="R54" t="s">
         <v>439</v>
@@ -9294,7 +9290,7 @@
         <v>651</v>
       </c>
       <c r="C55" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D55" t="s">
         <v>399</v>
@@ -9309,7 +9305,7 @@
         <v>27</v>
       </c>
       <c r="H55" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="I55" t="s">
         <v>652</v>
@@ -9339,13 +9335,13 @@
         <v>253</v>
       </c>
       <c r="R55" t="s">
-        <v>123</v>
+        <v>49</v>
       </c>
       <c r="S55" t="s">
-        <v>124</v>
+        <v>50</v>
       </c>
       <c r="T55" t="s">
-        <v>125</v>
+        <v>51</v>
       </c>
       <c r="U55" t="s">
         <v>486</v>
@@ -9360,7 +9356,7 @@
         <v>659</v>
       </c>
       <c r="C56" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="D56" t="s">
         <v>155</v>
@@ -9372,7 +9368,7 @@
         <v>631</v>
       </c>
       <c r="G56" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="H56" t="s">
         <v>184</v>
@@ -9402,7 +9398,7 @@
         <v>666</v>
       </c>
       <c r="Q56" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="R56" t="s">
         <v>667</v>
@@ -9426,13 +9422,13 @@
         <v>670</v>
       </c>
       <c r="C57" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D57" t="s">
         <v>671</v>
       </c>
       <c r="E57" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="F57" t="s">
         <v>672</v>
@@ -9441,7 +9437,7 @@
         <v>27</v>
       </c>
       <c r="H57" t="s">
-        <v>105</v>
+        <v>28</v>
       </c>
       <c r="I57" t="s">
         <v>673</v>
@@ -9459,7 +9455,7 @@
         <v>677</v>
       </c>
       <c r="N57" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="O57" t="s">
         <v>678</v>
@@ -9492,19 +9488,19 @@
         <v>680</v>
       </c>
       <c r="C58" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D58" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="E58" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="F58" t="s">
         <v>681</v>
       </c>
       <c r="G58" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="H58" t="s">
         <v>245</v>
@@ -9525,7 +9521,7 @@
         <v>686</v>
       </c>
       <c r="N58" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="O58" t="s">
         <v>687</v>
@@ -9558,13 +9554,13 @@
         <v>692</v>
       </c>
       <c r="C59" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D59" t="s">
         <v>693</v>
       </c>
       <c r="E59" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="F59" t="s">
         <v>681</v>
@@ -9573,7 +9569,7 @@
         <v>27</v>
       </c>
       <c r="H59" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="I59" t="s">
         <v>694</v>
@@ -9624,22 +9620,22 @@
         <v>704</v>
       </c>
       <c r="C60" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D60" t="s">
         <v>705</v>
       </c>
       <c r="E60" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="F60" t="s">
         <v>706</v>
       </c>
       <c r="G60" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="H60" t="s">
-        <v>105</v>
+        <v>28</v>
       </c>
       <c r="I60" t="s">
         <v>707</v>
@@ -9657,7 +9653,7 @@
         <v>711</v>
       </c>
       <c r="N60" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="O60" t="s">
         <v>712</v>
@@ -9693,10 +9689,10 @@
         <v>718</v>
       </c>
       <c r="D61" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="E61" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="F61" t="s">
         <v>719</v>
@@ -9705,7 +9701,7 @@
         <v>27</v>
       </c>
       <c r="H61" t="s">
-        <v>105</v>
+        <v>28</v>
       </c>
       <c r="I61" t="s">
         <v>720</v>
@@ -9732,7 +9728,7 @@
         <v>727</v>
       </c>
       <c r="Q61" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="R61" t="s">
         <v>728</v>
@@ -9756,7 +9752,7 @@
         <v>731</v>
       </c>
       <c r="C62" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="D62" t="s">
         <v>732</v>
@@ -9771,7 +9767,7 @@
         <v>27</v>
       </c>
       <c r="H62" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="I62" t="s">
         <v>734</v>
@@ -9798,16 +9794,16 @@
         <v>740</v>
       </c>
       <c r="Q62" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="R62" t="s">
-        <v>81</v>
+        <v>106</v>
       </c>
       <c r="S62" t="s">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="T62" t="s">
-        <v>83</v>
+        <v>108</v>
       </c>
       <c r="U62" t="s">
         <v>486</v>
@@ -9822,7 +9818,7 @@
         <v>741</v>
       </c>
       <c r="C63" t="s">
-        <v>85</v>
+        <v>23</v>
       </c>
       <c r="D63" t="s">
         <v>182</v>
@@ -9837,7 +9833,7 @@
         <v>27</v>
       </c>
       <c r="H63" t="s">
-        <v>105</v>
+        <v>28</v>
       </c>
       <c r="I63" t="s">
         <v>742</v>
@@ -9853,7 +9849,7 @@
         <v>745</v>
       </c>
       <c r="N63" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="O63" t="s">
         <v>746</v>
@@ -9886,13 +9882,13 @@
         <v>748</v>
       </c>
       <c r="C64" t="s">
-        <v>85</v>
+        <v>23</v>
       </c>
       <c r="D64" t="s">
         <v>749</v>
       </c>
       <c r="E64" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="F64" t="s">
         <v>733</v>
@@ -9917,7 +9913,7 @@
         <v>753</v>
       </c>
       <c r="N64" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="O64" t="s">
         <v>754</v>
@@ -9950,13 +9946,13 @@
         <v>759</v>
       </c>
       <c r="C65" t="s">
-        <v>85</v>
+        <v>23</v>
       </c>
       <c r="D65" t="s">
         <v>693</v>
       </c>
       <c r="E65" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="F65" t="s">
         <v>760</v>
@@ -9965,7 +9961,7 @@
         <v>27</v>
       </c>
       <c r="H65" t="s">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="I65" t="s">
         <v>761</v>
@@ -9981,7 +9977,7 @@
         <v>764</v>
       </c>
       <c r="N65" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="O65" t="s">
         <v>765</v>
@@ -10014,13 +10010,13 @@
         <v>770</v>
       </c>
       <c r="C66" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D66" t="s">
         <v>771</v>
       </c>
       <c r="E66" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="F66" t="s">
         <v>772</v>
@@ -10029,7 +10025,7 @@
         <v>27</v>
       </c>
       <c r="H66" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="I66" t="s">
         <v>773</v>
@@ -10056,7 +10052,7 @@
         <v>779</v>
       </c>
       <c r="Q66" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="R66" t="s">
         <v>780</v>
@@ -10080,13 +10076,13 @@
         <v>783</v>
       </c>
       <c r="C67" t="s">
-        <v>85</v>
+        <v>23</v>
       </c>
       <c r="D67" t="s">
         <v>771</v>
       </c>
       <c r="E67" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="F67" t="s">
         <v>772</v>
@@ -10095,7 +10091,7 @@
         <v>27</v>
       </c>
       <c r="H67" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="I67" t="s">
         <v>784</v>
@@ -10111,7 +10107,7 @@
         <v>787</v>
       </c>
       <c r="N67" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="O67" t="s">
         <v>788</v>
@@ -10120,7 +10116,7 @@
         <v>789</v>
       </c>
       <c r="Q67" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="R67" t="s">
         <v>790</v>
@@ -10155,7 +10151,7 @@
       </c>
       <c r="G68"/>
       <c r="H68" t="s">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="I68" t="s">
         <v>796</v>
@@ -10182,7 +10178,7 @@
         <v>802</v>
       </c>
       <c r="Q68" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="R68"/>
       <c r="S68"/>
@@ -10200,7 +10196,7 @@
         <v>803</v>
       </c>
       <c r="C69" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D69" t="s">
         <v>804</v>
@@ -10215,7 +10211,7 @@
         <v>27</v>
       </c>
       <c r="H69" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="I69" t="s">
         <v>806</v>
@@ -10266,7 +10262,7 @@
         <v>816</v>
       </c>
       <c r="C70" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D70" t="s">
         <v>817</v>
@@ -10281,7 +10277,7 @@
         <v>27</v>
       </c>
       <c r="H70" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="I70" t="s">
         <v>818</v>
@@ -10308,7 +10304,7 @@
         <v>824</v>
       </c>
       <c r="Q70" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="R70" t="s">
         <v>825</v>
@@ -10338,7 +10334,7 @@
         <v>829</v>
       </c>
       <c r="E71" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="F71" t="s">
         <v>805</v>
@@ -10347,7 +10343,7 @@
         <v>27</v>
       </c>
       <c r="H71" t="s">
-        <v>105</v>
+        <v>28</v>
       </c>
       <c r="I71" t="s">
         <v>830</v>
@@ -10374,7 +10370,7 @@
         <v>837</v>
       </c>
       <c r="Q71" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="R71" t="s">
         <v>838</v>
@@ -10398,7 +10394,7 @@
         <v>841</v>
       </c>
       <c r="C72" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="D72" t="s">
         <v>408</v>
@@ -10411,7 +10407,7 @@
         <v>27</v>
       </c>
       <c r="H72" t="s">
-        <v>105</v>
+        <v>28</v>
       </c>
       <c r="I72" t="s">
         <v>843</v>
@@ -10462,7 +10458,7 @@
         <v>853</v>
       </c>
       <c r="C73" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D73" t="s">
         <v>854</v>
@@ -10495,7 +10491,7 @@
         <v>859</v>
       </c>
       <c r="N73" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="O73" t="s">
         <v>860</v>
@@ -10528,7 +10524,7 @@
         <v>865</v>
       </c>
       <c r="C74" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D74" t="s">
         <v>866</v>
@@ -10543,7 +10539,7 @@
         <v>27</v>
       </c>
       <c r="H74" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="I74" t="s">
         <v>868</v>
@@ -10561,7 +10557,7 @@
         <v>872</v>
       </c>
       <c r="N74" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="O74" t="s">
         <v>873</v>
@@ -10573,13 +10569,13 @@
         <v>253</v>
       </c>
       <c r="R74" t="s">
-        <v>123</v>
+        <v>49</v>
       </c>
       <c r="S74" t="s">
-        <v>124</v>
+        <v>50</v>
       </c>
       <c r="T74" t="s">
-        <v>125</v>
+        <v>51</v>
       </c>
       <c r="U74" t="s">
         <v>486</v>
@@ -10607,7 +10603,7 @@
         <v>27</v>
       </c>
       <c r="H75" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="I75" t="s">
         <v>877</v>
@@ -10634,7 +10630,7 @@
         <v>883</v>
       </c>
       <c r="Q75" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="R75" t="s">
         <v>884</v>
@@ -10658,7 +10654,7 @@
         <v>887</v>
       </c>
       <c r="C76" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D76" t="s">
         <v>643</v>
@@ -10673,7 +10669,7 @@
         <v>27</v>
       </c>
       <c r="H76" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="I76" t="s">
         <v>888</v>
@@ -10724,7 +10720,7 @@
         <v>898</v>
       </c>
       <c r="C77" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D77" t="s">
         <v>899</v>
@@ -10736,10 +10732,10 @@
         <v>900</v>
       </c>
       <c r="G77" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="H77" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="I77" t="s">
         <v>901</v>
@@ -10757,7 +10753,7 @@
         <v>905</v>
       </c>
       <c r="N77" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="O77" t="s">
         <v>906</v>
@@ -10766,7 +10762,7 @@
         <v>907</v>
       </c>
       <c r="Q77" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="R77" t="s">
         <v>813</v>
@@ -10790,13 +10786,13 @@
         <v>908</v>
       </c>
       <c r="C78" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="D78" t="s">
         <v>909</v>
       </c>
       <c r="E78" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="F78" t="s">
         <v>910</v>
@@ -10805,7 +10801,7 @@
         <v>27</v>
       </c>
       <c r="H78" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="I78" t="s">
         <v>911</v>
@@ -10832,7 +10828,7 @@
         <v>917</v>
       </c>
       <c r="Q78" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="R78" t="s">
         <v>382</v>
@@ -10856,7 +10852,7 @@
         <v>918</v>
       </c>
       <c r="C79" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="D79" t="s">
         <v>919</v>
@@ -10871,7 +10867,7 @@
         <v>27</v>
       </c>
       <c r="H79" t="s">
-        <v>105</v>
+        <v>28</v>
       </c>
       <c r="I79" t="s">
         <v>922</v>
@@ -10922,13 +10918,13 @@
         <v>932</v>
       </c>
       <c r="C80" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="D80" t="s">
         <v>693</v>
       </c>
       <c r="E80" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="F80" t="s">
         <v>921</v>
@@ -10937,7 +10933,7 @@
         <v>27</v>
       </c>
       <c r="H80" t="s">
-        <v>105</v>
+        <v>28</v>
       </c>
       <c r="I80" t="s">
         <v>933</v>
@@ -10988,7 +10984,7 @@
         <v>943</v>
       </c>
       <c r="C81" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="D81" t="s">
         <v>944</v>
@@ -11001,7 +10997,7 @@
         <v>27</v>
       </c>
       <c r="H81" t="s">
-        <v>105</v>
+        <v>28</v>
       </c>
       <c r="I81" t="s">
         <v>946</v>
@@ -11058,7 +11054,7 @@
         <v>954</v>
       </c>
       <c r="E82" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="F82" t="s">
         <v>955</v>
@@ -11094,7 +11090,7 @@
         <v>963</v>
       </c>
       <c r="Q82" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="R82" t="s">
         <v>964</v>
@@ -11118,13 +11114,13 @@
         <v>967</v>
       </c>
       <c r="C83" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D83" t="s">
         <v>968</v>
       </c>
       <c r="E83" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="F83" t="s">
         <v>955</v>
@@ -11160,7 +11156,7 @@
         <v>975</v>
       </c>
       <c r="Q83" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="R83" t="s">
         <v>976</v>
@@ -11184,7 +11180,7 @@
         <v>979</v>
       </c>
       <c r="C84" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D84" t="s">
         <v>980</v>
@@ -11199,7 +11195,7 @@
         <v>27</v>
       </c>
       <c r="H84" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="I84" t="s">
         <v>981</v>
@@ -11229,13 +11225,13 @@
         <v>177</v>
       </c>
       <c r="R84" t="s">
-        <v>81</v>
+        <v>106</v>
       </c>
       <c r="S84" t="s">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="T84" t="s">
-        <v>83</v>
+        <v>108</v>
       </c>
       <c r="U84" t="s">
         <v>486</v>
@@ -11250,19 +11246,19 @@
         <v>988</v>
       </c>
       <c r="C85" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="D85" t="s">
         <v>989</v>
       </c>
       <c r="E85" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="F85" t="s">
         <v>990</v>
       </c>
       <c r="G85" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="H85" t="s">
         <v>184</v>
@@ -11283,7 +11279,7 @@
         <v>995</v>
       </c>
       <c r="N85" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="O85" t="s">
         <v>996</v>
@@ -11316,22 +11312,22 @@
         <v>1001</v>
       </c>
       <c r="C86" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="D86" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="E86" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="F86" t="s">
         <v>990</v>
       </c>
       <c r="G86" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="H86" t="s">
-        <v>105</v>
+        <v>28</v>
       </c>
       <c r="I86" t="s">
         <v>1002</v>
@@ -11382,22 +11378,22 @@
         <v>1009</v>
       </c>
       <c r="C87" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D87" t="s">
         <v>577</v>
       </c>
       <c r="E87" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="F87" t="s">
         <v>1010</v>
       </c>
       <c r="G87" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="H87" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="I87" t="s">
         <v>1011</v>
@@ -11415,7 +11411,7 @@
         <v>1015</v>
       </c>
       <c r="N87" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="O87" t="s">
         <v>1016</v>
@@ -11448,7 +11444,7 @@
         <v>1021</v>
       </c>
       <c r="C88" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D88" t="s">
         <v>854</v>
@@ -11490,7 +11486,7 @@
         <v>1029</v>
       </c>
       <c r="Q88" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="R88" t="s">
         <v>1030</v>
@@ -11525,7 +11521,7 @@
       </c>
       <c r="G89"/>
       <c r="H89" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="I89" t="s">
         <v>1036</v>
@@ -11543,7 +11539,7 @@
         <v>1040</v>
       </c>
       <c r="N89" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="O89" t="s">
         <v>1041</v>
@@ -11552,7 +11548,7 @@
         <v>1042</v>
       </c>
       <c r="Q89" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="R89"/>
       <c r="S89"/>
@@ -11581,7 +11577,7 @@
       </c>
       <c r="G90"/>
       <c r="H90" t="s">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="I90" t="s">
         <v>796</v>
@@ -11599,7 +11595,7 @@
         <v>1047</v>
       </c>
       <c r="N90" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="O90" t="s">
         <v>1048</v>
@@ -11608,7 +11604,7 @@
         <v>1049</v>
       </c>
       <c r="Q90" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="R90"/>
       <c r="S90"/>
@@ -11636,10 +11632,10 @@
         <v>1052</v>
       </c>
       <c r="G91" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="H91" t="s">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="I91" t="s">
         <v>1053</v>
@@ -11657,7 +11653,7 @@
         <v>1057</v>
       </c>
       <c r="N91" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="O91" t="s">
         <v>1058</v>
@@ -11666,7 +11662,7 @@
         <v>1059</v>
       </c>
       <c r="Q91" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="R91" t="s">
         <v>1060</v>
@@ -11705,7 +11701,7 @@
         <v>27</v>
       </c>
       <c r="H92" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="I92" t="s">
         <v>1065</v>
@@ -11723,7 +11719,7 @@
         <v>1069</v>
       </c>
       <c r="N92" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="O92" t="s">
         <v>1070</v>
@@ -11732,7 +11728,7 @@
         <v>1071</v>
       </c>
       <c r="Q92" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="R92" t="s">
         <v>1072</v>
@@ -11756,7 +11752,7 @@
         <v>1075</v>
       </c>
       <c r="C93" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D93" t="s">
         <v>919</v>
@@ -11771,7 +11767,7 @@
         <v>27</v>
       </c>
       <c r="H93" t="s">
-        <v>105</v>
+        <v>28</v>
       </c>
       <c r="I93" t="s">
         <v>1076</v>
@@ -11822,13 +11818,13 @@
         <v>1086</v>
       </c>
       <c r="C94" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D94" t="s">
         <v>1087</v>
       </c>
       <c r="E94" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="F94" t="s">
         <v>1064</v>
@@ -11855,7 +11851,7 @@
         <v>1092</v>
       </c>
       <c r="N94" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="O94" t="s">
         <v>1093</v>
@@ -11888,7 +11884,7 @@
         <v>1098</v>
       </c>
       <c r="C95" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="D95" t="s">
         <v>643</v>
@@ -11903,7 +11899,7 @@
         <v>27</v>
       </c>
       <c r="H95" t="s">
-        <v>105</v>
+        <v>28</v>
       </c>
       <c r="I95" t="s">
         <v>1099</v>
@@ -11954,7 +11950,7 @@
         <v>1109</v>
       </c>
       <c r="C96" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="D96" t="s">
         <v>1110</v>
@@ -11969,7 +11965,7 @@
         <v>27</v>
       </c>
       <c r="H96" t="s">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="I96" t="s">
         <v>1111</v>
@@ -12020,7 +12016,7 @@
         <v>1121</v>
       </c>
       <c r="C97" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D97" t="s">
         <v>1122</v>
@@ -12035,7 +12031,7 @@
         <v>27</v>
       </c>
       <c r="H97" t="s">
-        <v>105</v>
+        <v>28</v>
       </c>
       <c r="I97" t="s">
         <v>1123</v>
@@ -12086,13 +12082,13 @@
         <v>1133</v>
       </c>
       <c r="C98" t="s">
-        <v>85</v>
+        <v>23</v>
       </c>
       <c r="D98" t="s">
         <v>749</v>
       </c>
       <c r="E98" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="F98" t="s">
         <v>1134</v>
@@ -12101,7 +12097,7 @@
         <v>27</v>
       </c>
       <c r="H98" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="I98" t="s">
         <v>1135</v>
@@ -12119,7 +12115,7 @@
         <v>1139</v>
       </c>
       <c r="N98" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="O98" t="s">
         <v>1140</v>
@@ -12128,7 +12124,7 @@
         <v>1141</v>
       </c>
       <c r="Q98" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="R98" t="s">
         <v>1142</v>
@@ -12152,7 +12148,7 @@
         <v>1145</v>
       </c>
       <c r="C99" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D99" t="s">
         <v>1146</v>
@@ -12167,7 +12163,7 @@
         <v>27</v>
       </c>
       <c r="H99" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="I99" t="s">
         <v>1147</v>
@@ -12229,7 +12225,7 @@
       </c>
       <c r="G100"/>
       <c r="H100" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="I100" t="s">
         <v>1159</v>
@@ -12247,7 +12243,7 @@
         <v>1163</v>
       </c>
       <c r="N100" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="O100" t="s">
         <v>1164</v>
@@ -12256,7 +12252,7 @@
         <v>1165</v>
       </c>
       <c r="Q100" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="R100"/>
       <c r="S100"/>
@@ -12274,13 +12270,13 @@
         <v>1166</v>
       </c>
       <c r="C101" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="D101" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="E101" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="F101" t="s">
         <v>1167</v>
@@ -12289,7 +12285,7 @@
         <v>27</v>
       </c>
       <c r="H101" t="s">
-        <v>105</v>
+        <v>28</v>
       </c>
       <c r="I101" t="s">
         <v>632</v>
@@ -12307,7 +12303,7 @@
         <v>1171</v>
       </c>
       <c r="N101" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="O101" t="s">
         <v>1172</v>
@@ -12316,7 +12312,7 @@
         <v>1173</v>
       </c>
       <c r="Q101" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="R101" t="s">
         <v>639</v>
@@ -12340,13 +12336,13 @@
         <v>1174</v>
       </c>
       <c r="C102" t="s">
-        <v>85</v>
+        <v>23</v>
       </c>
       <c r="D102" t="s">
         <v>1175</v>
       </c>
       <c r="E102" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="F102" t="s">
         <v>1176</v>
@@ -12355,7 +12351,7 @@
         <v>27</v>
       </c>
       <c r="H102" t="s">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="I102" t="s">
         <v>1177</v>
@@ -12371,7 +12367,7 @@
         <v>1180</v>
       </c>
       <c r="N102" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="O102" t="s">
         <v>1181</v>
@@ -12380,7 +12376,7 @@
         <v>1182</v>
       </c>
       <c r="Q102" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="R102" t="s">
         <v>1183</v>
@@ -12404,7 +12400,7 @@
         <v>1186</v>
       </c>
       <c r="C103" t="s">
-        <v>85</v>
+        <v>23</v>
       </c>
       <c r="D103" t="s">
         <v>1187</v>
@@ -12419,7 +12415,7 @@
         <v>27</v>
       </c>
       <c r="H103" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="I103" t="s">
         <v>1189</v>
@@ -12435,7 +12431,7 @@
         <v>1192</v>
       </c>
       <c r="N103" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="O103" t="s">
         <v>1193</v>
@@ -12444,7 +12440,7 @@
         <v>1194</v>
       </c>
       <c r="Q103" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="R103" t="s">
         <v>1072</v>
@@ -12479,7 +12475,7 @@
       </c>
       <c r="G104"/>
       <c r="H104" t="s">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="I104" t="s">
         <v>1197</v>
@@ -12493,7 +12489,7 @@
       <c r="L104"/>
       <c r="M104"/>
       <c r="N104" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="O104" t="s">
         <v>1200</v>
@@ -12502,7 +12498,7 @@
         <v>1201</v>
       </c>
       <c r="Q104" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="R104" t="s">
         <v>1202</v>
@@ -12555,7 +12551,7 @@
         <v>1211</v>
       </c>
       <c r="N105" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="O105" t="s">
         <v>1212</v>
@@ -12564,7 +12560,7 @@
         <v>1213</v>
       </c>
       <c r="Q105" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="R105" t="s">
         <v>1214</v>
@@ -12599,7 +12595,7 @@
       </c>
       <c r="G106"/>
       <c r="H106" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="I106" t="s">
         <v>1218</v>
@@ -12626,7 +12622,7 @@
         <v>1225</v>
       </c>
       <c r="Q106" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="R106" t="s">
         <v>1226</v>
@@ -12650,7 +12646,7 @@
         <v>1229</v>
       </c>
       <c r="C107" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="D107" t="s">
         <v>919</v>
@@ -12716,13 +12712,13 @@
         <v>1241</v>
       </c>
       <c r="C108" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="D108" t="s">
         <v>1242</v>
       </c>
       <c r="E108" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="F108" t="s">
         <v>1243</v>
@@ -12782,13 +12778,13 @@
         <v>1254</v>
       </c>
       <c r="C109" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D109" t="s">
         <v>1255</v>
       </c>
       <c r="E109" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="F109" t="s">
         <v>1243</v>
@@ -12797,7 +12793,7 @@
         <v>27</v>
       </c>
       <c r="H109" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="I109" t="s">
         <v>1256</v>
@@ -12815,7 +12811,7 @@
         <v>1260</v>
       </c>
       <c r="N109" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="O109" t="s">
         <v>1261</v>
@@ -12824,7 +12820,7 @@
         <v>1262</v>
       </c>
       <c r="Q109" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="R109" t="s">
         <v>895</v>
@@ -12848,7 +12844,7 @@
         <v>1263</v>
       </c>
       <c r="C110" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="D110" t="s">
         <v>1264</v>
@@ -12863,7 +12859,7 @@
         <v>27</v>
       </c>
       <c r="H110" t="s">
-        <v>105</v>
+        <v>28</v>
       </c>
       <c r="I110" t="s">
         <v>1265</v>
@@ -12881,7 +12877,7 @@
         <v>1269</v>
       </c>
       <c r="N110" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="O110" t="s">
         <v>1270</v>
@@ -12914,13 +12910,13 @@
         <v>1275</v>
       </c>
       <c r="C111" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D111" t="s">
         <v>1276</v>
       </c>
       <c r="E111" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="F111" t="s">
         <v>1243</v>
@@ -12980,7 +12976,7 @@
         <v>1284</v>
       </c>
       <c r="C112" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="D112" t="s">
         <v>1285</v>
@@ -13046,13 +13042,13 @@
         <v>1294</v>
       </c>
       <c r="C113" t="s">
-        <v>85</v>
+        <v>23</v>
       </c>
       <c r="D113" t="s">
         <v>693</v>
       </c>
       <c r="E113" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="F113" t="s">
         <v>1295</v>
@@ -13061,7 +13057,7 @@
         <v>27</v>
       </c>
       <c r="H113" t="s">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="I113" t="s">
         <v>1296</v>
@@ -13077,7 +13073,7 @@
         <v>1299</v>
       </c>
       <c r="N113" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="O113" t="s">
         <v>1300</v>
@@ -13110,7 +13106,7 @@
         <v>1302</v>
       </c>
       <c r="C114" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D114" t="s">
         <v>244</v>
@@ -13125,7 +13121,7 @@
         <v>27</v>
       </c>
       <c r="H114" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="I114" t="s">
         <v>1304</v>
@@ -13143,7 +13139,7 @@
         <v>1308</v>
       </c>
       <c r="N114" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="O114" t="s">
         <v>1309</v>
@@ -13155,13 +13151,13 @@
         <v>253</v>
       </c>
       <c r="R114" t="s">
-        <v>123</v>
+        <v>49</v>
       </c>
       <c r="S114" t="s">
-        <v>124</v>
+        <v>50</v>
       </c>
       <c r="T114" t="s">
-        <v>125</v>
+        <v>51</v>
       </c>
       <c r="U114" t="s">
         <v>486</v>
@@ -13176,13 +13172,13 @@
         <v>1311</v>
       </c>
       <c r="C115" t="s">
-        <v>85</v>
+        <v>23</v>
       </c>
       <c r="D115" t="s">
         <v>1276</v>
       </c>
       <c r="E115" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="F115" t="s">
         <v>1312</v>
@@ -13191,7 +13187,7 @@
         <v>27</v>
       </c>
       <c r="H115" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="I115" t="s">
         <v>1313</v>
@@ -13207,7 +13203,7 @@
         <v>1316</v>
       </c>
       <c r="N115" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="O115" t="s">
         <v>1317</v>
@@ -13216,16 +13212,16 @@
         <v>1318</v>
       </c>
       <c r="Q115" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="R115" t="s">
-        <v>81</v>
+        <v>106</v>
       </c>
       <c r="S115" t="s">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="T115" t="s">
-        <v>83</v>
+        <v>108</v>
       </c>
       <c r="U115" t="s">
         <v>486</v>
@@ -13240,13 +13236,13 @@
         <v>1319</v>
       </c>
       <c r="C116" t="s">
-        <v>85</v>
+        <v>23</v>
       </c>
       <c r="D116" t="s">
         <v>693</v>
       </c>
       <c r="E116" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="F116" t="s">
         <v>1312</v>
@@ -13255,7 +13251,7 @@
         <v>27</v>
       </c>
       <c r="H116" t="s">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="I116" t="s">
         <v>1320</v>
@@ -13271,7 +13267,7 @@
         <v>1323</v>
       </c>
       <c r="N116" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="O116" t="s">
         <v>1324</v>
@@ -13304,13 +13300,13 @@
         <v>1326</v>
       </c>
       <c r="C117" t="s">
-        <v>85</v>
+        <v>23</v>
       </c>
       <c r="D117" t="s">
         <v>693</v>
       </c>
       <c r="E117" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="F117" t="s">
         <v>1312</v>
@@ -13319,7 +13315,7 @@
         <v>27</v>
       </c>
       <c r="H117" t="s">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="I117" t="s">
         <v>1320</v>
@@ -13335,7 +13331,7 @@
         <v>1328</v>
       </c>
       <c r="N117" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="O117" t="s">
         <v>1329</v>
@@ -13368,13 +13364,13 @@
         <v>1331</v>
       </c>
       <c r="C118" t="s">
-        <v>85</v>
+        <v>23</v>
       </c>
       <c r="D118" t="s">
         <v>693</v>
       </c>
       <c r="E118" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="F118" t="s">
         <v>1312</v>
@@ -13383,7 +13379,7 @@
         <v>27</v>
       </c>
       <c r="H118" t="s">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="I118" t="s">
         <v>1320</v>
@@ -13399,7 +13395,7 @@
         <v>1333</v>
       </c>
       <c r="N118" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="O118" t="s">
         <v>1334</v>
@@ -13432,13 +13428,13 @@
         <v>1336</v>
       </c>
       <c r="C119" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D119" t="s">
         <v>771</v>
       </c>
       <c r="E119" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="F119" t="s">
         <v>1337</v>
@@ -13474,7 +13470,7 @@
         <v>1344</v>
       </c>
       <c r="Q119" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="R119" t="s">
         <v>1345</v>
@@ -13498,13 +13494,13 @@
         <v>1348</v>
       </c>
       <c r="C120" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D120" t="s">
         <v>829</v>
       </c>
       <c r="E120" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="F120" t="s">
         <v>1349</v>
@@ -13513,7 +13509,7 @@
         <v>27</v>
       </c>
       <c r="H120" t="s">
-        <v>105</v>
+        <v>28</v>
       </c>
       <c r="I120" t="s">
         <v>1350</v>
@@ -13531,7 +13527,7 @@
         <v>1354</v>
       </c>
       <c r="N120" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="O120" t="s">
         <v>1355</v>
@@ -13540,7 +13536,7 @@
         <v>1356</v>
       </c>
       <c r="Q120" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="R120" t="s">
         <v>416</v>
@@ -13564,13 +13560,13 @@
         <v>1357</v>
       </c>
       <c r="C121" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D121" t="s">
         <v>1358</v>
       </c>
       <c r="E121" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="F121" t="s">
         <v>1349</v>
@@ -13579,7 +13575,7 @@
         <v>27</v>
       </c>
       <c r="H121" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="I121" t="s">
         <v>1359</v>
@@ -13606,7 +13602,7 @@
         <v>1365</v>
       </c>
       <c r="Q121" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="R121" t="s">
         <v>1366</v>
@@ -13630,7 +13626,7 @@
         <v>1369</v>
       </c>
       <c r="C122" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D122" t="s">
         <v>1370</v>
@@ -13645,7 +13641,7 @@
         <v>27</v>
       </c>
       <c r="H122" t="s">
-        <v>105</v>
+        <v>28</v>
       </c>
       <c r="I122" t="s">
         <v>1371</v>
@@ -13725,7 +13721,7 @@
         <v>1387</v>
       </c>
       <c r="N123" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="O123" t="s">
         <v>1388</v>
@@ -13734,16 +13730,16 @@
         <v>1389</v>
       </c>
       <c r="Q123" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="R123" t="s">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="S123" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="T123" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="U123" t="s">
         <v>486</v>
@@ -13758,13 +13754,13 @@
         <v>1390</v>
       </c>
       <c r="C124" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="D124" t="s">
         <v>671</v>
       </c>
       <c r="E124" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="F124" t="s">
         <v>1382</v>
@@ -13824,7 +13820,7 @@
         <v>1401</v>
       </c>
       <c r="C125" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="D125" t="s">
         <v>1402</v>
@@ -13890,7 +13886,7 @@
         <v>1413</v>
       </c>
       <c r="C126" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D126" t="s">
         <v>1414</v>
@@ -13923,7 +13919,7 @@
         <v>1419</v>
       </c>
       <c r="N126" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="O126" t="s">
         <v>1420</v>
@@ -13956,7 +13952,7 @@
         <v>1422</v>
       </c>
       <c r="C127" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="D127" t="s">
         <v>817</v>
@@ -13971,7 +13967,7 @@
         <v>27</v>
       </c>
       <c r="H127" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="I127" t="s">
         <v>1423</v>
@@ -14022,13 +14018,13 @@
         <v>1433</v>
       </c>
       <c r="C128" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="D128" t="s">
         <v>771</v>
       </c>
       <c r="E128" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="F128" t="s">
         <v>1382</v>
@@ -14037,7 +14033,7 @@
         <v>27</v>
       </c>
       <c r="H128" t="s">
-        <v>105</v>
+        <v>28</v>
       </c>
       <c r="I128" t="s">
         <v>1434</v>
@@ -14064,7 +14060,7 @@
         <v>1441</v>
       </c>
       <c r="Q128" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="R128" t="s">
         <v>1442</v>
@@ -14088,13 +14084,13 @@
         <v>1445</v>
       </c>
       <c r="C129" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D129" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="E129" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="F129" t="s">
         <v>1446</v>
@@ -14103,7 +14099,7 @@
         <v>27</v>
       </c>
       <c r="H129" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="I129" t="s">
         <v>1447</v>
@@ -14121,7 +14117,7 @@
         <v>1451</v>
       </c>
       <c r="N129" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="O129" t="s">
         <v>1452</v>
@@ -14130,16 +14126,16 @@
         <v>1453</v>
       </c>
       <c r="Q129" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="R129" t="s">
-        <v>123</v>
+        <v>49</v>
       </c>
       <c r="S129" t="s">
-        <v>124</v>
+        <v>50</v>
       </c>
       <c r="T129" t="s">
-        <v>125</v>
+        <v>51</v>
       </c>
       <c r="U129" t="s">
         <v>486</v>
@@ -14154,7 +14150,7 @@
         <v>1454</v>
       </c>
       <c r="C130" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="D130" t="s">
         <v>643</v>
@@ -14169,7 +14165,7 @@
         <v>27</v>
       </c>
       <c r="H130" t="s">
-        <v>105</v>
+        <v>28</v>
       </c>
       <c r="I130" t="s">
         <v>1456</v>
@@ -14187,7 +14183,7 @@
         <v>1460</v>
       </c>
       <c r="N130" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="O130" t="s">
         <v>1461</v>
@@ -14220,13 +14216,13 @@
         <v>1463</v>
       </c>
       <c r="C131" t="s">
-        <v>85</v>
+        <v>23</v>
       </c>
       <c r="D131" t="s">
         <v>1464</v>
       </c>
       <c r="E131" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="F131" t="s">
         <v>1465</v>
@@ -14235,7 +14231,7 @@
         <v>27</v>
       </c>
       <c r="H131" t="s">
-        <v>105</v>
+        <v>28</v>
       </c>
       <c r="I131" t="s">
         <v>1466</v>
@@ -14251,7 +14247,7 @@
         <v>1469</v>
       </c>
       <c r="N131" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="O131" t="s">
         <v>1470</v>
@@ -14260,7 +14256,7 @@
         <v>1471</v>
       </c>
       <c r="Q131" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="R131" t="s">
         <v>940</v>
@@ -14284,7 +14280,7 @@
         <v>1472</v>
       </c>
       <c r="C132" t="s">
-        <v>85</v>
+        <v>23</v>
       </c>
       <c r="D132" t="s">
         <v>1473</v>
@@ -14299,7 +14295,7 @@
         <v>27</v>
       </c>
       <c r="H132" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="I132" t="s">
         <v>1474</v>
@@ -14315,7 +14311,7 @@
         <v>1477</v>
       </c>
       <c r="N132" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="O132" t="s">
         <v>1478</v>
@@ -14324,7 +14320,7 @@
         <v>1479</v>
       </c>
       <c r="Q132" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="R132" t="s">
         <v>178</v>
@@ -14363,7 +14359,7 @@
         <v>27</v>
       </c>
       <c r="H133" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="I133" t="s">
         <v>1482</v>
@@ -14425,7 +14421,7 @@
       </c>
       <c r="G134"/>
       <c r="H134" t="s">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="I134" t="s">
         <v>1491</v>
@@ -14448,7 +14444,7 @@
         <v>1496</v>
       </c>
       <c r="Q134" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="R134" t="s">
         <v>1497</v>
@@ -14483,7 +14479,7 @@
       </c>
       <c r="G135"/>
       <c r="H135" t="s">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="I135" t="s">
         <v>1502</v>
@@ -14510,7 +14506,7 @@
         <v>1508</v>
       </c>
       <c r="Q135" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="R135" t="s">
         <v>1509</v>
@@ -14534,7 +14530,7 @@
         <v>1512</v>
       </c>
       <c r="C136" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D136" t="s">
         <v>1513</v>
@@ -14549,7 +14545,7 @@
         <v>27</v>
       </c>
       <c r="H136" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="I136" t="s">
         <v>1515</v>
@@ -14567,7 +14563,7 @@
         <v>1519</v>
       </c>
       <c r="N136" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="O136" t="s">
         <v>1520</v>
@@ -14600,7 +14596,7 @@
         <v>1525</v>
       </c>
       <c r="C137" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D137" t="s">
         <v>1526</v>
@@ -14633,7 +14629,7 @@
         <v>1532</v>
       </c>
       <c r="N137" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="O137" t="s">
         <v>1533</v>
@@ -14666,7 +14662,7 @@
         <v>1538</v>
       </c>
       <c r="C138" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D138" t="s">
         <v>155</v>
@@ -14678,10 +14674,10 @@
         <v>1527</v>
       </c>
       <c r="G138" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="H138" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="I138" t="s">
         <v>1539</v>
@@ -14699,7 +14695,7 @@
         <v>1543</v>
       </c>
       <c r="N138" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="O138" t="s">
         <v>1544</v>
@@ -14708,7 +14704,7 @@
         <v>1545</v>
       </c>
       <c r="Q138" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="R138" t="s">
         <v>895</v>
@@ -14738,13 +14734,13 @@
         <v>577</v>
       </c>
       <c r="E139" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="F139" t="s">
         <v>1547</v>
       </c>
       <c r="G139" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="H139" t="s">
         <v>184</v>
@@ -14777,13 +14773,13 @@
         <v>177</v>
       </c>
       <c r="R139" t="s">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="S139" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="T139" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="U139" t="s">
         <v>486</v>
@@ -14798,13 +14794,13 @@
         <v>1555</v>
       </c>
       <c r="C140" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="D140" t="s">
         <v>1556</v>
       </c>
       <c r="E140" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="F140" t="s">
         <v>1547</v>
@@ -14813,7 +14809,7 @@
         <v>27</v>
       </c>
       <c r="H140" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="I140" t="s">
         <v>1557</v>
@@ -14864,7 +14860,7 @@
         <v>1567</v>
       </c>
       <c r="C141" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="D141" t="s">
         <v>1568</v>
@@ -14897,7 +14893,7 @@
         <v>1574</v>
       </c>
       <c r="N141" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="O141" t="s">
         <v>1575</v>
@@ -14930,13 +14926,13 @@
         <v>1580</v>
       </c>
       <c r="C142" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D142" t="s">
         <v>542</v>
       </c>
       <c r="E142" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="F142" t="s">
         <v>1547</v>
@@ -14945,7 +14941,7 @@
         <v>27</v>
       </c>
       <c r="H142" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="I142" t="s">
         <v>1581</v>
@@ -14963,7 +14959,7 @@
         <v>1585</v>
       </c>
       <c r="N142" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="O142" t="s">
         <v>1586</v>
@@ -14972,7 +14968,7 @@
         <v>1587</v>
       </c>
       <c r="Q142" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="R142" t="s">
         <v>1588</v>
@@ -14996,13 +14992,13 @@
         <v>1591</v>
       </c>
       <c r="C143" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D143" t="s">
         <v>1556</v>
       </c>
       <c r="E143" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="F143" t="s">
         <v>1547</v>
@@ -15029,7 +15025,7 @@
         <v>1596</v>
       </c>
       <c r="N143" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="O143" t="s">
         <v>1597</v>
@@ -15038,7 +15034,7 @@
         <v>1598</v>
       </c>
       <c r="Q143" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="R143" t="s">
         <v>1599</v>
@@ -15062,7 +15058,7 @@
         <v>1602</v>
       </c>
       <c r="C144" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D144" t="s">
         <v>1264</v>
@@ -15077,7 +15073,7 @@
         <v>27</v>
       </c>
       <c r="H144" t="s">
-        <v>105</v>
+        <v>28</v>
       </c>
       <c r="I144" t="s">
         <v>1603</v>
@@ -15095,7 +15091,7 @@
         <v>1607</v>
       </c>
       <c r="N144" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="O144" t="s">
         <v>1608</v>
@@ -15128,13 +15124,13 @@
         <v>1613</v>
       </c>
       <c r="C145" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D145" t="s">
         <v>1614</v>
       </c>
       <c r="E145" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="F145" t="s">
         <v>1615</v>
@@ -15143,7 +15139,7 @@
         <v>27</v>
       </c>
       <c r="H145" t="s">
-        <v>105</v>
+        <v>28</v>
       </c>
       <c r="I145" t="s">
         <v>1616</v>
@@ -15161,7 +15157,7 @@
         <v>1620</v>
       </c>
       <c r="N145" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="O145" t="s">
         <v>1621</v>
@@ -15194,13 +15190,13 @@
         <v>1623</v>
       </c>
       <c r="C146" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D146" t="s">
         <v>443</v>
       </c>
       <c r="E146" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="F146" t="s">
         <v>1624</v>
@@ -15209,7 +15205,7 @@
         <v>27</v>
       </c>
       <c r="H146" t="s">
-        <v>105</v>
+        <v>28</v>
       </c>
       <c r="I146" t="s">
         <v>1625</v>
@@ -15227,7 +15223,7 @@
         <v>1629</v>
       </c>
       <c r="N146" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="O146" t="s">
         <v>1630</v>
@@ -15236,7 +15232,7 @@
         <v>1631</v>
       </c>
       <c r="Q146" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="R146" t="s">
         <v>538</v>
@@ -15260,7 +15256,7 @@
         <v>1632</v>
       </c>
       <c r="C147" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D147" t="s">
         <v>1633</v>
@@ -15272,7 +15268,7 @@
         <v>1634</v>
       </c>
       <c r="G147" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="H147" t="s">
         <v>184</v>
@@ -15293,7 +15289,7 @@
         <v>1639</v>
       </c>
       <c r="N147" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="O147" t="s">
         <v>1640</v>
@@ -15302,7 +15298,7 @@
         <v>1641</v>
       </c>
       <c r="Q147" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="R147" t="s">
         <v>862</v>
@@ -15338,7 +15334,7 @@
         <v>1644</v>
       </c>
       <c r="G148" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="H148" t="s">
         <v>184</v>
@@ -15368,7 +15364,7 @@
         <v>1651</v>
       </c>
       <c r="Q148" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="R148" t="s">
         <v>1410</v>
@@ -15392,13 +15388,13 @@
         <v>1652</v>
       </c>
       <c r="C149" t="s">
-        <v>85</v>
+        <v>23</v>
       </c>
       <c r="D149" t="s">
         <v>771</v>
       </c>
       <c r="E149" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="F149" t="s">
         <v>1644</v>
@@ -15407,7 +15403,7 @@
         <v>27</v>
       </c>
       <c r="H149" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="I149" t="s">
         <v>1653</v>
@@ -15423,7 +15419,7 @@
         <v>1656</v>
       </c>
       <c r="N149" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="O149" t="s">
         <v>1657</v>
@@ -15435,13 +15431,13 @@
         <v>253</v>
       </c>
       <c r="R149" t="s">
-        <v>123</v>
+        <v>49</v>
       </c>
       <c r="S149" t="s">
-        <v>124</v>
+        <v>50</v>
       </c>
       <c r="T149" t="s">
-        <v>125</v>
+        <v>51</v>
       </c>
       <c r="U149" t="s">
         <v>486</v>
@@ -15456,7 +15452,7 @@
         <v>1659</v>
       </c>
       <c r="C150" t="s">
-        <v>85</v>
+        <v>23</v>
       </c>
       <c r="D150" t="s">
         <v>399</v>
@@ -15471,7 +15467,7 @@
         <v>27</v>
       </c>
       <c r="H150" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="I150" t="s">
         <v>1661</v>
@@ -15487,7 +15483,7 @@
         <v>1664</v>
       </c>
       <c r="N150" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="O150" t="s">
         <v>1665</v>
@@ -15496,16 +15492,16 @@
         <v>1666</v>
       </c>
       <c r="Q150" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="R150" t="s">
-        <v>123</v>
+        <v>49</v>
       </c>
       <c r="S150" t="s">
-        <v>124</v>
+        <v>50</v>
       </c>
       <c r="T150" t="s">
-        <v>125</v>
+        <v>51</v>
       </c>
       <c r="U150" t="s">
         <v>486</v>
@@ -15520,7 +15516,7 @@
         <v>1667</v>
       </c>
       <c r="C151" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="D151" t="s">
         <v>1668</v>
@@ -15584,7 +15580,7 @@
         <v>1680</v>
       </c>
       <c r="C152" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D152" t="s">
         <v>980</v>
@@ -15599,7 +15595,7 @@
         <v>27</v>
       </c>
       <c r="H152" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="I152" t="s">
         <v>1682</v>
@@ -15617,7 +15613,7 @@
         <v>1686</v>
       </c>
       <c r="N152" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="O152" t="s">
         <v>1687</v>
@@ -15650,7 +15646,7 @@
         <v>1692</v>
       </c>
       <c r="C153" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="D153" t="s">
         <v>804</v>
@@ -15683,7 +15679,7 @@
         <v>1697</v>
       </c>
       <c r="N153" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="O153" t="s">
         <v>1698</v>
@@ -15716,7 +15712,7 @@
         <v>1703</v>
       </c>
       <c r="C154" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="D154" t="s">
         <v>1704</v>
@@ -15728,7 +15724,7 @@
         <v>1705</v>
       </c>
       <c r="G154" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="H154" t="s">
         <v>956</v>
@@ -15749,7 +15745,7 @@
         <v>1710</v>
       </c>
       <c r="N154" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="O154" t="s">
         <v>1711</v>
@@ -15782,7 +15778,7 @@
         <v>1716</v>
       </c>
       <c r="C155" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="D155" t="s">
         <v>1110</v>
@@ -15815,7 +15811,7 @@
         <v>1710</v>
       </c>
       <c r="N155" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="O155" t="s">
         <v>1717</v>
@@ -15848,7 +15844,7 @@
         <v>1722</v>
       </c>
       <c r="C156" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D156" t="s">
         <v>1723</v>
@@ -15881,7 +15877,7 @@
         <v>1729</v>
       </c>
       <c r="N156" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="O156" t="s">
         <v>1730</v>
@@ -15893,13 +15889,13 @@
         <v>177</v>
       </c>
       <c r="R156" t="s">
-        <v>81</v>
+        <v>106</v>
       </c>
       <c r="S156" t="s">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="T156" t="s">
-        <v>83</v>
+        <v>108</v>
       </c>
       <c r="U156" t="s">
         <v>486</v>
@@ -15914,22 +15910,22 @@
         <v>1732</v>
       </c>
       <c r="C157" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D157" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="E157" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="F157" t="s">
         <v>1733</v>
       </c>
       <c r="G157" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="H157" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="I157" t="s">
         <v>1734</v>
@@ -15947,7 +15943,7 @@
         <v>1738</v>
       </c>
       <c r="N157" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="O157" t="s">
         <v>1739</v>
@@ -15956,7 +15952,7 @@
         <v>1740</v>
       </c>
       <c r="Q157" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="R157" t="s">
         <v>1741</v>
@@ -15980,13 +15976,13 @@
         <v>1744</v>
       </c>
       <c r="C158" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D158" t="s">
         <v>771</v>
       </c>
       <c r="E158" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="F158" t="s">
         <v>1745</v>
@@ -15995,7 +15991,7 @@
         <v>27</v>
       </c>
       <c r="H158" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="I158" t="s">
         <v>1746</v>
@@ -16013,7 +16009,7 @@
         <v>1750</v>
       </c>
       <c r="N158" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="O158" t="s">
         <v>1751</v>
@@ -16022,7 +16018,7 @@
         <v>1752</v>
       </c>
       <c r="Q158" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="R158" t="s">
         <v>1753</v>
@@ -16046,7 +16042,7 @@
         <v>1756</v>
       </c>
       <c r="C159" t="s">
-        <v>85</v>
+        <v>23</v>
       </c>
       <c r="D159" t="s">
         <v>1757</v>
@@ -16061,7 +16057,7 @@
         <v>27</v>
       </c>
       <c r="H159" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="I159" t="s">
         <v>1758</v>
@@ -16077,7 +16073,7 @@
         <v>1761</v>
       </c>
       <c r="N159" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="O159" t="s">
         <v>1762</v>
@@ -16110,7 +16106,7 @@
         <v>1764</v>
       </c>
       <c r="C160" t="s">
-        <v>85</v>
+        <v>23</v>
       </c>
       <c r="D160" t="s">
         <v>1757</v>
@@ -16125,7 +16121,7 @@
         <v>27</v>
       </c>
       <c r="H160" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="I160" t="s">
         <v>1765</v>
@@ -16141,7 +16137,7 @@
         <v>1768</v>
       </c>
       <c r="N160" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="O160" t="s">
         <v>1769</v>
@@ -16174,7 +16170,7 @@
         <v>1771</v>
       </c>
       <c r="C161" t="s">
-        <v>85</v>
+        <v>23</v>
       </c>
       <c r="D161" t="s">
         <v>1772</v>
@@ -16189,7 +16185,7 @@
         <v>27</v>
       </c>
       <c r="H161" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="I161" t="s">
         <v>1774</v>
@@ -16205,7 +16201,7 @@
         <v>1777</v>
       </c>
       <c r="N161" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="O161" t="s">
         <v>1778</v>
@@ -16217,13 +16213,13 @@
         <v>253</v>
       </c>
       <c r="R161" t="s">
-        <v>81</v>
+        <v>106</v>
       </c>
       <c r="S161" t="s">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="T161" t="s">
-        <v>83</v>
+        <v>108</v>
       </c>
       <c r="U161" t="s">
         <v>486</v>
@@ -16238,13 +16234,13 @@
         <v>1780</v>
       </c>
       <c r="C162" t="s">
-        <v>85</v>
+        <v>23</v>
       </c>
       <c r="D162" t="s">
         <v>1556</v>
       </c>
       <c r="E162" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="F162" t="s">
         <v>1781</v>
@@ -16269,7 +16265,7 @@
         <v>1785</v>
       </c>
       <c r="N162" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="O162" t="s">
         <v>1786</v>
@@ -16331,7 +16327,7 @@
         <v>1797</v>
       </c>
       <c r="N163" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="O163" t="s">
         <v>1798</v>
@@ -16340,7 +16336,7 @@
         <v>1799</v>
       </c>
       <c r="Q163" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="R163" t="s">
         <v>1800</v>

--- a/Objets_parlementaires_Jura.xlsx
+++ b/Objets_parlementaires_Jura.xlsx
@@ -80,6 +80,117 @@
     <t xml:space="preserve">Statut_Change_Date</t>
   </si>
   <si>
+    <t xml:space="preserve">26.3891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ip.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Juillard Charles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le Centre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Für eine neue Finanzierungsquelle für grosse öffentliche Ausgabenposten. Eine befristete Solidaritätsabgabe auf den Zahlungsverkehr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pour une nouvelle source de financement des grands dossiers en charge des collectivités publiques. Une contribution de solidarité temporaire prélevée sur les mouvements financiers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Una nuova fonte di finanziamento per i grandi progetti a carico delle collettività pubbliche. Un contributo di solidarietà temporaneo prelevato sui movimenti finanziari</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;La Confédération doit faire face à des défis financiers importants que les sources de financements actuelles n'arriveront sans doute pas à financer. Il y a les impôts, les taxes, la TVA notamment; mais celles-ci ne suffisent plus à financer des grands projets dont le pays a besoin. Il s'agit notamment de l'AVS, des infrastructures de transport, de la sécurité du pays (armée notamment), la prévention des dangers naturels liés au changement climatique (tâche partagée avec les cantons et les communes). Mes questions portent sur la création temporaire (10 ans) d'une forme de contribution de solidarité pour les "grands travaux" des 3 niveaux politiques suisses.&amp;nbsp;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Je demande au Conseil fédéral de bien vouloir répondre aux questions suivantes:&lt;/p&gt;&lt;p&gt;1. Le Conseil fédéral a-t-il déjà mené des réflexions quant à la mise en œuvre de nouvelles sources de financement, si oui lesquelles?&lt;/p&gt;&lt;p&gt;2. Sachant que le nombre annuel des mouvements financiers ( et non les transactions financières) s'élève à environ 5560 mio pour un volume financier d'environ CHF 17'530 milliards ( pour 2025), le prélèvement de 1 pour-mille sur ces transactions pourrait rapporter environ CHF 17,5 milliards/an, que ces montants pourraient être versés dans 3 fonds spécifiques (prévoyance sociale, sécurité, dangers naturels) gérés par la Confédération ou la BNS, le Conseil fédéral est-il prêt à examiner rapidement cette nouvelle source de financement et, cas échéant de proposer un projet au Parlement?&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Der Bund steht vor erheblichen finanziellen Herausforderungen, für welche die heutigen Finanzierungsquellen offenkundig nicht ausreichen. Zu diesen Finanzierungsquellen gehören insbesondere Steuern, Abgaben und die Mehrwertsteuer. Diese reichen jedoch nicht mehr aus, um die Finanzierung grosser Ausgabenposten von nationaler Bedeutung sicherzustellen. Hierzu zählen insbesondere die AHV, die Verkehrsinfrastruktur, die Sicherheit des Landes (insbesondere die Armee) sowie die Prävention von Naturgefahren im Zusammenhang mit dem Klimawandel (eine gemeinsam mit den Kantonen und Gemeinden wahrgenommene Aufgabe). Meine Fragen betreffen die Einführung eines (auf zehn Jahre) befristeten Solidaritätsbeitrags für die «grossen Ausgabenposten» der drei politischen Ebenen der Schweiz.&amp;nbsp;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Ich bitte den Bundesrat, die folgenden Fragen zu beantworten:&lt;/p&gt;&lt;p&gt;1. Hat der Bundesrat bereits Überlegungen zu neuen Finanzierungsquellen angestellt, und wenn ja, welche?&lt;/p&gt;&lt;p&gt;2. Ausgehend davon, dass jährlich rund 5560&amp;nbsp;Millionen Finanzströme (und nicht Finanztransaktionen) mit einem Gesamtvolumen von rund 17&amp;nbsp;530&amp;nbsp;Milliarden Franken (2025) abgewickelt werden, könnte eine Abgabe von 1&amp;nbsp;Promille auf diesen Finanzströmen jährliche Einnahmen von rund 17,5&amp;nbsp;Milliarden Franken generieren. Diese Mittel könnten drei Fonds (für die soziale Wohlfahrt, die Sicherheit sowie die Prävention von Naturgefahren) zufliessen, die vom Bund oder von der Schweizerischen Nationalbank verwaltet würden. Ist der Bundesrat bereit, diese neue Finanzierungsquelle rasch zu prüfen und gegebenenfalls dem Parlament eine entsprechende Vorlage zu unterbreiten?&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Erledigt / Liquidé</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Titre uniquement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finanzwesen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finances</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finanze</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CSSS-N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commissions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13. AHV-Rente. Zuweisung der Steuermehreinnahmen der Kantone und Gemeinden an die AHV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13e rente AVS. Affectation des recettes fiscales supplémentaires des cantons et des communes à l'AVS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">13esima mensilità AVS. Destinare le entrate fiscali supplementari dei Cantoni e dei Comuni all'AVS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé de modifier les bases légales de sorte que les recettes fiscales supplémentaires générées par l’introduction de la 13&lt;sup&gt;e&lt;/sup&gt; rente AVS, pour les cantons et les communes, soient intégralement reversées à la Confédération&lt;u&gt;,&lt;/u&gt; qui les transfère directement à l'AVS.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Une minorité de la commission (Rechsteiner Thomas, Alijaj, Blunschy, Crottaz, Gysi Barbara, Hess Lorenz, Roduit, Piller Carrard, Porchet, Weichelt, Wyss, Zybach) propose de rejeter la motion.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, die gesetzlichen Grundlagen so anzupassen, dass die durch die Einführung der 13. AHV-Rente entstehenden Steuermehreinnahmen bei Kantonen und Gemeinden vollständig dem Bund zufliessen, der diese Mittel direkt an die AHV weiterleitet.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Eine Minderheit&amp;nbsp;der Kommission&amp;nbsp;(Rechsteiner Thomas, Alijaj, Blunschy, Crottaz, Gysi Barbara, Hess Lorenz, Roduit, Piller Carrard, Porchet, Weichelt, Wyss, Zybach) beantragt, die Motion abzulehnen.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conseil fédéral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finanzwesen|Steuer|Sozialer Schutz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finances|Fiscalité|Protection sociale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finanze|Imposte|Protezione sociale</t>
+  </si>
+  <si>
     <t xml:space="preserve">26.7901</t>
   </si>
   <si>
@@ -95,9 +206,6 @@
     <t xml:space="preserve">2026-09-22</t>
   </si>
   <si>
-    <t xml:space="preserve">NR</t>
-  </si>
-  <si>
     <t xml:space="preserve">Titel folgt</t>
   </si>
   <si>
@@ -116,9 +224,6 @@
     <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20267901</t>
   </si>
   <si>
-    <t xml:space="preserve">Titre uniquement</t>
-  </si>
-  <si>
     <t xml:space="preserve">Internationale Politik|Finanzwesen|Landwirtschaft</t>
   </si>
   <si>
@@ -134,9 +239,6 @@
     <t xml:space="preserve">2026-09-15</t>
   </si>
   <si>
-    <t xml:space="preserve">EFD</t>
-  </si>
-  <si>
     <t xml:space="preserve">Grenzsicherheit: Instabilität als Führungsstil?</t>
   </si>
   <si>
@@ -149,9 +251,6 @@
     <t xml:space="preserve">&lt;p&gt;Am 1. August hat das Bundesamt für Zoll und Grenzsicherheit die Zahl seiner Regionen von 6 auf 4 reduziert. Ab Januar 2027 wird die Zahl der Lokalebenen von 23 auf 16 sinken, wobei 25 Kaderstellen wegfallen; die derzeitigen Führungskräfte müssen sich um die verbleibenden Stellen bewerben. Seit Jahren ist dieses für die Grenzregionen unverzichtbare Bindeglied von internen Spannungen geprägt.&amp;nbsp;&lt;br&gt;Gewährleistet der Bundesrat endlich dauerhafte Stabilität für sein Personal und für die Grenzregionen?&lt;/p&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">Erledigt / Liquidé</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20267687</t>
   </si>
   <si>
@@ -206,9 +305,6 @@
     <t xml:space="preserve">26.4169</t>
   </si>
   <si>
-    <t xml:space="preserve">Mo.</t>
-  </si>
-  <si>
     <t xml:space="preserve">2026-09-17</t>
   </si>
   <si>
@@ -239,18 +335,9 @@
     <t xml:space="preserve">26.3628</t>
   </si>
   <si>
-    <t xml:space="preserve">Juillard Charles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Le Centre</t>
-  </si>
-  <si>
     <t xml:space="preserve">2026-06-11</t>
   </si>
   <si>
-    <t xml:space="preserve">SR</t>
-  </si>
-  <si>
     <t xml:space="preserve">VBS</t>
   </si>
   <si>
@@ -335,9 +422,6 @@
     <t xml:space="preserve">26.4146</t>
   </si>
   <si>
-    <t xml:space="preserve">Ip.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Stettler Thomas</t>
   </si>
   <si>
@@ -470,45 +554,6 @@
     <t xml:space="preserve">2026-09-14</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Für eine neue Finanzierungsquelle für grosse öffentliche Ausgabenposten. Eine befristete Solidaritätsabgabe auf den Zahlungsverkehr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pour une nouvelle source de financement des grands dossiers en charge des collectivités publiques. Une contribution de solidarité temporaire prélevée sur les mouvements financiers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Una nuova fonte di finanziamento per i grandi progetti a carico delle collettività pubbliche. Un contributo di solidarietà temporaneo prelevato sui movimenti finanziari</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;La Confédération doit faire face à des défis financiers importants que les sources de financements actuelles n'arriveront sans doute pas à financer. Il y a les impôts, les taxes, la TVA notamment; mais celles-ci ne suffisent plus à financer des grands projets dont le pays a besoin. Il s'agit notamment de l'AVS, des infrastructures de transport, de la sécurité du pays (armée notamment), la prévention des dangers naturels liés au changement climatique (tâche partagée avec les cantons et les communes). Mes questions portent sur la création temporaire (10 ans) d'une forme de contribution de solidarité pour les "grands travaux" des 3 niveaux politiques suisses.&amp;nbsp;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Je demande au Conseil fédéral de bien vouloir répondre aux questions suivantes:&lt;/p&gt;&lt;p&gt;1. Le Conseil fédéral a-t-il déjà mené des réflexions quant à la mise en œuvre de nouvelles sources de financement, si oui lesquelles?&lt;/p&gt;&lt;p&gt;2. Sachant que le nombre annuel des mouvements financiers ( et non les transactions financières) s'élève à environ 5560 mio pour un volume financier d'environ CHF 17'530 milliards ( pour 2025), le prélèvement de 1 pour-mille sur ces transactions pourrait rapporter environ CHF 17,5 milliards/an, que ces montants pourraient être versés dans 3 fonds spécifiques (prévoyance sociale, sécurité, dangers naturels) gérés par la Confédération ou la BNS, le Conseil fédéral est-il prêt à examiner rapidement cette nouvelle source de financement et, cas échéant de proposer un projet au Parlement?&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Der Bund steht vor erheblichen finanziellen Herausforderungen, für welche die heutigen Finanzierungsquellen offenkundig nicht ausreichen. Zu diesen Finanzierungsquellen gehören insbesondere Steuern, Abgaben und die Mehrwertsteuer. Diese reichen jedoch nicht mehr aus, um die Finanzierung grosser Ausgabenposten von nationaler Bedeutung sicherzustellen. Hierzu zählen insbesondere die AHV, die Verkehrsinfrastruktur, die Sicherheit des Landes (insbesondere die Armee) sowie die Prävention von Naturgefahren im Zusammenhang mit dem Klimawandel (eine gemeinsam mit den Kantonen und Gemeinden wahrgenommene Aufgabe). Meine Fragen betreffen die Einführung eines (auf zehn Jahre) befristeten Solidaritätsbeitrags für die «grossen Ausgabenposten» der drei politischen Ebenen der Schweiz.&amp;nbsp;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Ich bitte den Bundesrat, die folgenden Fragen zu beantworten:&lt;/p&gt;&lt;p&gt;1. Hat der Bundesrat bereits Überlegungen zu neuen Finanzierungsquellen angestellt, und wenn ja, welche?&lt;/p&gt;&lt;p&gt;2. Ausgehend davon, dass jährlich rund 5560&amp;nbsp;Millionen Finanzströme (und nicht Finanztransaktionen) mit einem Gesamtvolumen von rund 17&amp;nbsp;530&amp;nbsp;Milliarden Franken (2025) abgewickelt werden, könnte eine Abgabe von 1&amp;nbsp;Promille auf diesen Finanzströmen jährliche Einnahmen von rund 17,5&amp;nbsp;Milliarden Franken generieren. Diese Mittel könnten drei Fonds (für die soziale Wohlfahrt, die Sicherheit sowie die Prävention von Naturgefahren) zufliessen, die vom Bund oder von der Schweizerischen Nationalbank verwaltet würden. Ist der Bundesrat bereit, diese neue Finanzierungsquelle rasch zu prüfen und gegebenenfalls dem Parlament eine entsprechende Vorlage zu unterbreiten?&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finanzwesen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finances</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finanze</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-23</t>
-  </si>
-  <si>
     <t xml:space="preserve">26.3916</t>
   </si>
   <si>
@@ -584,9 +629,6 @@
     <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263968</t>
   </si>
   <si>
-    <t xml:space="preserve">Conseil fédéral</t>
-  </si>
-  <si>
     <t xml:space="preserve">26.3997</t>
   </si>
   <si>
@@ -651,48 +693,6 @@
   </si>
   <si>
     <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CSSS-N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Commissions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-04-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13. AHV-Rente. Zuweisung der Steuermehreinnahmen der Kantone und Gemeinden an die AHV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13e rente AVS. Affectation des recettes fiscales supplémentaires des cantons et des communes à l'AVS </t>
-  </si>
-  <si>
-    <t xml:space="preserve">13esima mensilità AVS. Destinare le entrate fiscali supplementari dei Cantoni e dei Comuni all'AVS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé de modifier les bases légales de sorte que les recettes fiscales supplémentaires générées par l’introduction de la 13&lt;sup&gt;e&lt;/sup&gt; rente AVS, pour les cantons et les communes, soient intégralement reversées à la Confédération&lt;u&gt;,&lt;/u&gt; qui les transfère directement à l'AVS.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Une minorité de la commission (Rechsteiner Thomas, Alijaj, Blunschy, Crottaz, Gysi Barbara, Hess Lorenz, Roduit, Piller Carrard, Porchet, Weichelt, Wyss, Zybach) propose de rejeter la motion.&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, die gesetzlichen Grundlagen so anzupassen, dass die durch die Einführung der 13. AHV-Rente entstehenden Steuermehreinnahmen bei Kantonen und Gemeinden vollständig dem Bund zufliessen, der diese Mittel direkt an die AHV weiterleitet.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Eine Minderheit&amp;nbsp;der Kommission&amp;nbsp;(Rechsteiner Thomas, Alijaj, Blunschy, Crottaz, Gysi Barbara, Hess Lorenz, Roduit, Piller Carrard, Porchet, Weichelt, Wyss, Zybach) beantragt, die Motion abzulehnen.&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finanzwesen|Steuer|Sozialer Schutz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finances|Fiscalité|Protection sociale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finanze|Imposte|Protezione sociale</t>
   </si>
   <si>
     <t xml:space="preserve">26.3597</t>
@@ -5877,7 +5877,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>20267901</v>
+        <v>20263891</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
@@ -5897,349 +5897,351 @@
       <c r="G2" t="s">
         <v>27</v>
       </c>
-      <c r="H2"/>
+      <c r="H2" t="s">
+        <v>28</v>
+      </c>
       <c r="I2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J2" t="s">
-        <v>29</v>
-      </c>
-      <c r="K2"/>
+        <v>30</v>
+      </c>
+      <c r="K2" t="s">
+        <v>31</v>
+      </c>
       <c r="L2" t="s">
-        <v>30</v>
-      </c>
-      <c r="M2"/>
+        <v>32</v>
+      </c>
+      <c r="M2" t="s">
+        <v>33</v>
+      </c>
       <c r="N2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="O2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="P2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="Q2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="R2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="S2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="T2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="U2" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="V2"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>20267687</v>
+        <v>20263518</v>
       </c>
       <c r="B3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D3" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="E3" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="F3" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="G3" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H3" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="I3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L3" t="s">
+        <v>51</v>
+      </c>
+      <c r="M3" t="s">
+        <v>52</v>
+      </c>
+      <c r="N3" t="s">
+        <v>34</v>
+      </c>
+      <c r="O3" t="s">
+        <v>53</v>
+      </c>
+      <c r="P3" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>55</v>
+      </c>
+      <c r="R3" t="s">
+        <v>56</v>
+      </c>
+      <c r="S3" t="s">
+        <v>57</v>
+      </c>
+      <c r="T3" t="s">
+        <v>58</v>
+      </c>
+      <c r="U3" t="s">
         <v>41</v>
-      </c>
-      <c r="J3" t="s">
-        <v>42</v>
-      </c>
-      <c r="K3"/>
-      <c r="L3" t="s">
-        <v>43</v>
-      </c>
-      <c r="M3" t="s">
-        <v>44</v>
-      </c>
-      <c r="N3" t="s">
-        <v>45</v>
-      </c>
-      <c r="O3" t="s">
-        <v>46</v>
-      </c>
-      <c r="P3" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>34</v>
-      </c>
-      <c r="R3" t="s">
-        <v>48</v>
-      </c>
-      <c r="S3" t="s">
-        <v>49</v>
-      </c>
-      <c r="T3" t="s">
-        <v>50</v>
-      </c>
-      <c r="U3" t="s">
-        <v>51</v>
       </c>
       <c r="V3"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>20267688</v>
+        <v>20267901</v>
       </c>
       <c r="B4" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="E4" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="F4" t="s">
-        <v>39</v>
+        <v>63</v>
       </c>
       <c r="G4" t="s">
-        <v>27</v>
-      </c>
-      <c r="H4" t="s">
-        <v>53</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="H4"/>
       <c r="I4" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="J4" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="K4"/>
       <c r="L4" t="s">
-        <v>56</v>
-      </c>
-      <c r="M4" t="s">
-        <v>57</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="M4"/>
       <c r="N4" t="s">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="O4" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="P4" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="Q4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="R4" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="S4" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="T4" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="U4" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="V4"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>20264169</v>
+        <v>20267687</v>
       </c>
       <c r="B5" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="C5" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D5" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="E5" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="F5" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="G5" t="s">
-        <v>27</v>
-      </c>
-      <c r="H5"/>
+        <v>47</v>
+      </c>
+      <c r="H5" t="s">
+        <v>28</v>
+      </c>
       <c r="I5" t="s">
-        <v>28</v>
+        <v>75</v>
       </c>
       <c r="J5" t="s">
-        <v>66</v>
-      </c>
-      <c r="K5" t="s">
-        <v>67</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="K5"/>
       <c r="L5" t="s">
-        <v>68</v>
-      </c>
-      <c r="M5"/>
+        <v>77</v>
+      </c>
+      <c r="M5" t="s">
+        <v>78</v>
+      </c>
       <c r="N5" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="O5" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="P5" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="Q5" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="R5" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="S5" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="T5" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="U5" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="V5"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>20263628</v>
+        <v>20267688</v>
       </c>
       <c r="B6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C6" t="s">
+        <v>60</v>
+      </c>
+      <c r="D6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E6" t="s">
+        <v>62</v>
+      </c>
+      <c r="F6" t="s">
         <v>74</v>
       </c>
-      <c r="C6" t="s">
-        <v>64</v>
-      </c>
-      <c r="D6" t="s">
-        <v>75</v>
-      </c>
-      <c r="E6" t="s">
-        <v>76</v>
-      </c>
-      <c r="F6" t="s">
-        <v>77</v>
-      </c>
       <c r="G6" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="H6" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="I6" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="J6" t="s">
-        <v>81</v>
-      </c>
-      <c r="K6" t="s">
-        <v>82</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="K6"/>
       <c r="L6" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="M6" t="s">
+        <v>90</v>
+      </c>
+      <c r="N6" t="s">
+        <v>34</v>
+      </c>
+      <c r="O6" t="s">
+        <v>91</v>
+      </c>
+      <c r="P6" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>37</v>
+      </c>
+      <c r="R6" t="s">
+        <v>93</v>
+      </c>
+      <c r="S6" t="s">
+        <v>94</v>
+      </c>
+      <c r="T6" t="s">
+        <v>95</v>
+      </c>
+      <c r="U6" t="s">
         <v>84</v>
-      </c>
-      <c r="N6" t="s">
-        <v>85</v>
-      </c>
-      <c r="O6" t="s">
-        <v>86</v>
-      </c>
-      <c r="P6" t="s">
-        <v>87</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>34</v>
-      </c>
-      <c r="R6" t="s">
-        <v>88</v>
-      </c>
-      <c r="S6" t="s">
-        <v>89</v>
-      </c>
-      <c r="T6" t="s">
-        <v>90</v>
-      </c>
-      <c r="U6" t="s">
-        <v>65</v>
       </c>
       <c r="V6"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>20263131</v>
+        <v>20264169</v>
       </c>
       <c r="B7" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="C7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D7" t="s">
+        <v>61</v>
+      </c>
+      <c r="E7" t="s">
+        <v>62</v>
+      </c>
+      <c r="F7" t="s">
+        <v>97</v>
+      </c>
+      <c r="G7" t="s">
+        <v>47</v>
+      </c>
+      <c r="H7"/>
+      <c r="I7" t="s">
         <v>64</v>
       </c>
-      <c r="D7" t="s">
-        <v>92</v>
-      </c>
-      <c r="E7"/>
-      <c r="F7" t="s">
-        <v>93</v>
-      </c>
-      <c r="G7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H7" t="s">
-        <v>94</v>
-      </c>
-      <c r="I7" t="s">
-        <v>95</v>
-      </c>
       <c r="J7" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="K7" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="L7" t="s">
-        <v>98</v>
-      </c>
-      <c r="M7" t="s">
-        <v>99</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="M7"/>
       <c r="N7" t="s">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="O7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="P7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Q7" t="s">
-        <v>102</v>
+        <v>37</v>
       </c>
       <c r="R7" t="s">
         <v>103</v>
@@ -6251,412 +6253,408 @@
         <v>105</v>
       </c>
       <c r="U7" t="s">
-        <v>65</v>
+        <v>97</v>
       </c>
       <c r="V7"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>20264146</v>
+        <v>20263628</v>
       </c>
       <c r="B8" t="s">
         <v>106</v>
       </c>
       <c r="C8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" t="s">
         <v>107</v>
-      </c>
-      <c r="D8" t="s">
-        <v>108</v>
-      </c>
-      <c r="E8" t="s">
-        <v>109</v>
-      </c>
-      <c r="F8" t="s">
-        <v>110</v>
       </c>
       <c r="G8" t="s">
         <v>27</v>
       </c>
-      <c r="H8"/>
+      <c r="H8" t="s">
+        <v>108</v>
+      </c>
       <c r="I8" t="s">
-        <v>28</v>
+        <v>109</v>
       </c>
       <c r="J8" t="s">
+        <v>110</v>
+      </c>
+      <c r="K8" t="s">
         <v>111</v>
-      </c>
-      <c r="K8" t="s">
-        <v>67</v>
       </c>
       <c r="L8" t="s">
         <v>112</v>
       </c>
-      <c r="M8"/>
+      <c r="M8" t="s">
+        <v>113</v>
+      </c>
       <c r="N8" t="s">
-        <v>31</v>
+        <v>114</v>
       </c>
       <c r="O8" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="P8" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="Q8" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="R8" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="S8" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="T8" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="U8" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="V8"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>20267829</v>
+        <v>20263131</v>
       </c>
       <c r="B9" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C9" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E9" t="s">
-        <v>25</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="E9"/>
       <c r="F9" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="G9" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H9" t="s">
-        <v>53</v>
+        <v>123</v>
       </c>
       <c r="I9" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="J9" t="s">
-        <v>120</v>
-      </c>
-      <c r="K9"/>
+        <v>125</v>
+      </c>
+      <c r="K9" t="s">
+        <v>126</v>
+      </c>
       <c r="L9" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="M9" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="N9" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O9" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="P9" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="Q9" t="s">
-        <v>34</v>
+        <v>131</v>
       </c>
       <c r="R9" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="S9" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="T9" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="U9" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="V9"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>20264127</v>
+        <v>20264146</v>
       </c>
       <c r="B10" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="C10" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D10" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="E10" t="s">
-        <v>25</v>
+        <v>137</v>
       </c>
       <c r="F10" t="s">
-        <v>39</v>
+        <v>138</v>
       </c>
       <c r="G10" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H10"/>
       <c r="I10" t="s">
-        <v>130</v>
+        <v>64</v>
       </c>
       <c r="J10" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="K10" t="s">
+        <v>99</v>
+      </c>
+      <c r="L10" t="s">
+        <v>140</v>
+      </c>
+      <c r="M10"/>
+      <c r="N10" t="s">
         <v>67</v>
       </c>
-      <c r="L10"/>
-      <c r="M10" t="s">
-        <v>132</v>
-      </c>
-      <c r="N10" t="s">
-        <v>31</v>
-      </c>
       <c r="O10" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="P10" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="Q10" t="s">
-        <v>102</v>
+        <v>37</v>
       </c>
       <c r="R10" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="S10" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="T10" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="U10" t="s">
-        <v>39</v>
+        <v>138</v>
       </c>
       <c r="V10"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>20260312</v>
+        <v>20267829</v>
       </c>
       <c r="B11" t="s">
+        <v>146</v>
+      </c>
+      <c r="C11" t="s">
+        <v>60</v>
+      </c>
+      <c r="D11" t="s">
+        <v>61</v>
+      </c>
+      <c r="E11" t="s">
+        <v>62</v>
+      </c>
+      <c r="F11" t="s">
         <v>138</v>
       </c>
-      <c r="C11" t="s">
-        <v>139</v>
-      </c>
-      <c r="D11" t="s">
-        <v>140</v>
-      </c>
-      <c r="E11"/>
-      <c r="F11" t="s">
-        <v>141</v>
-      </c>
-      <c r="G11"/>
+      <c r="G11" t="s">
+        <v>47</v>
+      </c>
       <c r="H11" t="s">
-        <v>142</v>
+        <v>86</v>
       </c>
       <c r="I11" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="J11" t="s">
-        <v>144</v>
-      </c>
-      <c r="K11" t="s">
-        <v>145</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="K11"/>
       <c r="L11" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="M11" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="N11" t="s">
-        <v>148</v>
+        <v>34</v>
       </c>
       <c r="O11" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="P11" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="Q11" t="s">
-        <v>102</v>
-      </c>
-      <c r="R11"/>
-      <c r="S11"/>
-      <c r="T11"/>
+        <v>37</v>
+      </c>
+      <c r="R11" t="s">
+        <v>153</v>
+      </c>
+      <c r="S11" t="s">
+        <v>154</v>
+      </c>
+      <c r="T11" t="s">
+        <v>155</v>
+      </c>
       <c r="U11" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="V11"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>20263891</v>
+        <v>20264127</v>
       </c>
       <c r="B12" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="C12" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D12" t="s">
-        <v>75</v>
+        <v>157</v>
       </c>
       <c r="E12" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="F12" t="s">
-        <v>153</v>
+        <v>74</v>
       </c>
       <c r="G12" t="s">
-        <v>78</v>
-      </c>
-      <c r="H12" t="s">
-        <v>40</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="H12"/>
       <c r="I12" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="J12" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="K12" t="s">
-        <v>156</v>
-      </c>
-      <c r="L12" t="s">
-        <v>157</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="L12"/>
       <c r="M12" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="N12" t="s">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="O12" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="P12" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="Q12" t="s">
-        <v>34</v>
+        <v>131</v>
       </c>
       <c r="R12" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="S12" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="T12" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="U12" t="s">
-        <v>164</v>
-      </c>
-      <c r="V12" t="s">
-        <v>164</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="V12"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>20263916</v>
+        <v>20260312</v>
       </c>
       <c r="B13" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C13" t="s">
-        <v>107</v>
+        <v>167</v>
       </c>
       <c r="D13" t="s">
-        <v>166</v>
-      </c>
-      <c r="E13" t="s">
-        <v>25</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="E13"/>
       <c r="F13" t="s">
-        <v>153</v>
-      </c>
-      <c r="G13" t="s">
-        <v>78</v>
-      </c>
+        <v>169</v>
+      </c>
+      <c r="G13"/>
       <c r="H13" t="s">
-        <v>53</v>
+        <v>170</v>
       </c>
       <c r="I13" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="J13" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="K13" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="L13" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="M13" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="N13" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="O13" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="P13" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="Q13" t="s">
-        <v>34</v>
-      </c>
-      <c r="R13" t="s">
-        <v>175</v>
-      </c>
-      <c r="S13" t="s">
-        <v>176</v>
-      </c>
-      <c r="T13" t="s">
-        <v>177</v>
-      </c>
+        <v>131</v>
+      </c>
+      <c r="R13"/>
+      <c r="S13"/>
+      <c r="T13"/>
       <c r="U13" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="V13"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>20263968</v>
+        <v>20263916</v>
       </c>
       <c r="B14" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C14" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D14" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E14" t="s">
-        <v>181</v>
+        <v>62</v>
       </c>
       <c r="F14" t="s">
-        <v>153</v>
+        <v>26</v>
       </c>
       <c r="G14" t="s">
         <v>27</v>
       </c>
       <c r="H14" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="I14" t="s">
         <v>182</v>
@@ -6683,221 +6681,219 @@
         <v>189</v>
       </c>
       <c r="Q14" t="s">
+        <v>37</v>
+      </c>
+      <c r="R14" t="s">
         <v>190</v>
       </c>
-      <c r="R14" t="s">
-        <v>125</v>
-      </c>
       <c r="S14" t="s">
-        <v>126</v>
+        <v>191</v>
       </c>
       <c r="T14" t="s">
-        <v>127</v>
+        <v>192</v>
       </c>
       <c r="U14" t="s">
-        <v>178</v>
+        <v>193</v>
       </c>
       <c r="V14"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>20263997</v>
+        <v>20263968</v>
       </c>
       <c r="B15" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="C15" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D15" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="E15" t="s">
+        <v>196</v>
+      </c>
+      <c r="F15" t="s">
+        <v>26</v>
+      </c>
+      <c r="G15" t="s">
+        <v>47</v>
+      </c>
+      <c r="H15" t="s">
+        <v>86</v>
+      </c>
+      <c r="I15" t="s">
+        <v>197</v>
+      </c>
+      <c r="J15" t="s">
+        <v>198</v>
+      </c>
+      <c r="K15" t="s">
+        <v>199</v>
+      </c>
+      <c r="L15" t="s">
+        <v>200</v>
+      </c>
+      <c r="M15" t="s">
+        <v>201</v>
+      </c>
+      <c r="N15" t="s">
+        <v>202</v>
+      </c>
+      <c r="O15" t="s">
+        <v>203</v>
+      </c>
+      <c r="P15" t="s">
+        <v>204</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>55</v>
+      </c>
+      <c r="R15" t="s">
+        <v>153</v>
+      </c>
+      <c r="S15" t="s">
+        <v>154</v>
+      </c>
+      <c r="T15" t="s">
+        <v>155</v>
+      </c>
+      <c r="U15" t="s">
         <v>193</v>
-      </c>
-      <c r="F15" t="s">
-        <v>153</v>
-      </c>
-      <c r="G15" t="s">
-        <v>27</v>
-      </c>
-      <c r="H15" t="s">
-        <v>194</v>
-      </c>
-      <c r="I15" t="s">
-        <v>195</v>
-      </c>
-      <c r="J15" t="s">
-        <v>196</v>
-      </c>
-      <c r="K15" t="s">
-        <v>197</v>
-      </c>
-      <c r="L15" t="s">
-        <v>198</v>
-      </c>
-      <c r="M15" t="s">
-        <v>199</v>
-      </c>
-      <c r="N15" t="s">
-        <v>187</v>
-      </c>
-      <c r="O15" t="s">
-        <v>200</v>
-      </c>
-      <c r="P15" t="s">
-        <v>201</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>190</v>
-      </c>
-      <c r="R15" t="s">
-        <v>202</v>
-      </c>
-      <c r="S15" t="s">
-        <v>203</v>
-      </c>
-      <c r="T15" t="s">
-        <v>204</v>
-      </c>
-      <c r="U15" t="s">
-        <v>178</v>
       </c>
       <c r="V15"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>20263571</v>
+        <v>20263997</v>
       </c>
       <c r="B16" t="s">
         <v>205</v>
       </c>
       <c r="C16" t="s">
-        <v>64</v>
+        <v>23</v>
       </c>
       <c r="D16" t="s">
         <v>206</v>
       </c>
       <c r="E16" t="s">
-        <v>109</v>
+        <v>207</v>
       </c>
       <c r="F16" t="s">
-        <v>207</v>
+        <v>26</v>
       </c>
       <c r="G16" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="H16" t="s">
-        <v>94</v>
+        <v>208</v>
       </c>
       <c r="I16" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="J16" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K16" t="s">
-        <v>97</v>
+        <v>211</v>
       </c>
       <c r="L16" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="M16" t="s">
-        <v>99</v>
+        <v>213</v>
       </c>
       <c r="N16" t="s">
-        <v>172</v>
+        <v>202</v>
       </c>
       <c r="O16" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="P16" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="Q16" t="s">
-        <v>102</v>
+        <v>55</v>
       </c>
       <c r="R16" t="s">
-        <v>103</v>
+        <v>216</v>
       </c>
       <c r="S16" t="s">
-        <v>104</v>
+        <v>217</v>
       </c>
       <c r="T16" t="s">
-        <v>105</v>
+        <v>218</v>
       </c>
       <c r="U16" t="s">
-        <v>178</v>
+        <v>193</v>
       </c>
       <c r="V16"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>20263518</v>
+        <v>20263571</v>
       </c>
       <c r="B17" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="C17" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="D17" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="E17" t="s">
-        <v>215</v>
+        <v>137</v>
       </c>
       <c r="F17" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G17" t="s">
         <v>27</v>
       </c>
       <c r="H17" t="s">
-        <v>40</v>
+        <v>123</v>
       </c>
       <c r="I17" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="J17" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="K17" t="s">
-        <v>219</v>
+        <v>126</v>
       </c>
       <c r="L17" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="M17" t="s">
-        <v>221</v>
+        <v>128</v>
       </c>
       <c r="N17" t="s">
-        <v>45</v>
+        <v>187</v>
       </c>
       <c r="O17" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="P17" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Q17" t="s">
-        <v>190</v>
+        <v>131</v>
       </c>
       <c r="R17" t="s">
-        <v>224</v>
+        <v>132</v>
       </c>
       <c r="S17" t="s">
-        <v>225</v>
+        <v>133</v>
       </c>
       <c r="T17" t="s">
-        <v>226</v>
+        <v>134</v>
       </c>
       <c r="U17" t="s">
-        <v>164</v>
-      </c>
-      <c r="V17" t="s">
-        <v>164</v>
-      </c>
+        <v>193</v>
+      </c>
+      <c r="V17"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -6910,19 +6906,19 @@
         <v>228</v>
       </c>
       <c r="D18" t="s">
-        <v>75</v>
+        <v>24</v>
       </c>
       <c r="E18" t="s">
-        <v>76</v>
+        <v>25</v>
       </c>
       <c r="F18" t="s">
         <v>229</v>
       </c>
       <c r="G18" t="s">
-        <v>78</v>
+        <v>27</v>
       </c>
       <c r="H18" t="s">
-        <v>94</v>
+        <v>123</v>
       </c>
       <c r="I18" t="s">
         <v>230</v>
@@ -6940,7 +6936,7 @@
         <v>234</v>
       </c>
       <c r="N18" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O18" t="s">
         <v>235</v>
@@ -6949,7 +6945,7 @@
         <v>236</v>
       </c>
       <c r="Q18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="R18" t="s">
         <v>237</v>
@@ -6973,22 +6969,22 @@
         <v>241</v>
       </c>
       <c r="C19" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D19" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="E19" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="F19" t="s">
-        <v>207</v>
+        <v>221</v>
       </c>
       <c r="G19" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H19" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="I19" t="s">
         <v>242</v>
@@ -7006,7 +7002,7 @@
         <v>246</v>
       </c>
       <c r="N19" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="O19" t="s">
         <v>247</v>
@@ -7015,7 +7011,7 @@
         <v>248</v>
       </c>
       <c r="Q19" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="R19" t="s">
         <v>249</v>
@@ -7039,19 +7035,19 @@
         <v>253</v>
       </c>
       <c r="C20" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D20" t="s">
         <v>254</v>
       </c>
       <c r="E20" t="s">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="F20" t="s">
-        <v>153</v>
+        <v>26</v>
       </c>
       <c r="G20" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H20" t="s">
         <v>255</v>
@@ -7072,7 +7068,7 @@
         <v>260</v>
       </c>
       <c r="N20" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="O20" t="s">
         <v>261</v>
@@ -7105,19 +7101,19 @@
         <v>268</v>
       </c>
       <c r="C21" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D21" t="s">
         <v>254</v>
       </c>
       <c r="E21" t="s">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="F21" t="s">
-        <v>153</v>
+        <v>26</v>
       </c>
       <c r="G21" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H21" t="s">
         <v>255</v>
@@ -7138,7 +7134,7 @@
         <v>273</v>
       </c>
       <c r="N21" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="O21" t="s">
         <v>274</v>
@@ -7171,22 +7167,22 @@
         <v>276</v>
       </c>
       <c r="C22" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D22" t="s">
         <v>277</v>
       </c>
       <c r="E22" t="s">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="F22" t="s">
         <v>278</v>
       </c>
       <c r="G22" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H22" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="I22" t="s">
         <v>279</v>
@@ -7204,7 +7200,7 @@
         <v>283</v>
       </c>
       <c r="N22" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="O22" t="s">
         <v>284</v>
@@ -7213,7 +7209,7 @@
         <v>285</v>
       </c>
       <c r="Q22" t="s">
-        <v>190</v>
+        <v>55</v>
       </c>
       <c r="R22" t="s">
         <v>286</v>
@@ -7237,22 +7233,22 @@
         <v>290</v>
       </c>
       <c r="C23" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D23" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="E23" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="F23" t="s">
-        <v>207</v>
+        <v>221</v>
       </c>
       <c r="G23" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H23" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="I23" t="s">
         <v>291</v>
@@ -7270,7 +7266,7 @@
         <v>295</v>
       </c>
       <c r="N23" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="O23" t="s">
         <v>296</v>
@@ -7279,7 +7275,7 @@
         <v>297</v>
       </c>
       <c r="Q23" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="R23" t="s">
         <v>298</v>
@@ -7303,22 +7299,22 @@
         <v>301</v>
       </c>
       <c r="C24" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="D24" t="s">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="E24" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="F24" t="s">
         <v>302</v>
       </c>
       <c r="G24" t="s">
-        <v>78</v>
+        <v>27</v>
       </c>
       <c r="H24" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="I24" t="s">
         <v>303</v>
@@ -7336,7 +7332,7 @@
         <v>307</v>
       </c>
       <c r="N24" t="s">
-        <v>148</v>
+        <v>176</v>
       </c>
       <c r="O24" t="s">
         <v>308</v>
@@ -7345,7 +7341,7 @@
         <v>309</v>
       </c>
       <c r="Q24" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="R24" t="s">
         <v>310</v>
@@ -7369,19 +7365,19 @@
         <v>314</v>
       </c>
       <c r="C25" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D25" t="s">
         <v>254</v>
       </c>
       <c r="E25" t="s">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="F25" t="s">
         <v>315</v>
       </c>
       <c r="G25" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H25" t="s">
         <v>255</v>
@@ -7402,7 +7398,7 @@
         <v>320</v>
       </c>
       <c r="N25" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O25" t="s">
         <v>321</v>
@@ -7423,7 +7419,7 @@
         <v>266</v>
       </c>
       <c r="U25" t="s">
-        <v>153</v>
+        <v>26</v>
       </c>
       <c r="V25"/>
     </row>
@@ -7438,19 +7434,19 @@
         <v>228</v>
       </c>
       <c r="D26" t="s">
-        <v>75</v>
+        <v>24</v>
       </c>
       <c r="E26" t="s">
-        <v>76</v>
+        <v>25</v>
       </c>
       <c r="F26" t="s">
         <v>324</v>
       </c>
       <c r="G26" t="s">
-        <v>78</v>
+        <v>27</v>
       </c>
       <c r="H26" t="s">
-        <v>94</v>
+        <v>123</v>
       </c>
       <c r="I26" t="s">
         <v>325</v>
@@ -7477,7 +7473,7 @@
         <v>332</v>
       </c>
       <c r="Q26" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="R26" t="s">
         <v>333</v>
@@ -7501,22 +7497,22 @@
         <v>337</v>
       </c>
       <c r="C27" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="D27" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="E27" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="F27" t="s">
         <v>338</v>
       </c>
       <c r="G27" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H27" t="s">
-        <v>94</v>
+        <v>123</v>
       </c>
       <c r="I27" t="s">
         <v>339</v>
@@ -7532,7 +7528,7 @@
         <v>342</v>
       </c>
       <c r="N27" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="O27" t="s">
         <v>343</v>
@@ -7541,7 +7537,7 @@
         <v>344</v>
       </c>
       <c r="Q27" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="R27" t="s">
         <v>345</v>
@@ -7565,19 +7561,19 @@
         <v>349</v>
       </c>
       <c r="C28" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="D28" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="E28" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="F28" t="s">
         <v>350</v>
       </c>
       <c r="G28" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H28" t="s">
         <v>255</v>
@@ -7596,7 +7592,7 @@
         <v>354</v>
       </c>
       <c r="N28" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O28" t="s">
         <v>355</v>
@@ -7605,7 +7601,7 @@
         <v>356</v>
       </c>
       <c r="Q28" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="R28" t="s">
         <v>357</v>
@@ -7629,19 +7625,19 @@
         <v>360</v>
       </c>
       <c r="C29" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="D29" t="s">
-        <v>108</v>
+        <v>136</v>
       </c>
       <c r="E29" t="s">
-        <v>109</v>
+        <v>137</v>
       </c>
       <c r="F29" t="s">
         <v>350</v>
       </c>
       <c r="G29" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H29" t="s">
         <v>255</v>
@@ -7660,7 +7656,7 @@
         <v>364</v>
       </c>
       <c r="N29" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O29" t="s">
         <v>365</v>
@@ -7669,7 +7665,7 @@
         <v>366</v>
       </c>
       <c r="Q29" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="R29" t="s">
         <v>367</v>
@@ -7693,22 +7689,22 @@
         <v>370</v>
       </c>
       <c r="C30" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D30" t="s">
         <v>371</v>
       </c>
       <c r="E30" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="F30" t="s">
         <v>372</v>
       </c>
       <c r="G30" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H30" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="I30" t="s">
         <v>373</v>
@@ -7726,7 +7722,7 @@
         <v>377</v>
       </c>
       <c r="N30" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O30" t="s">
         <v>378</v>
@@ -7735,7 +7731,7 @@
         <v>379</v>
       </c>
       <c r="Q30" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="R30" t="s">
         <v>380</v>
@@ -7759,22 +7755,22 @@
         <v>384</v>
       </c>
       <c r="C31" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D31" t="s">
-        <v>75</v>
+        <v>24</v>
       </c>
       <c r="E31" t="s">
-        <v>76</v>
+        <v>25</v>
       </c>
       <c r="F31" t="s">
-        <v>93</v>
+        <v>122</v>
       </c>
       <c r="G31" t="s">
-        <v>78</v>
+        <v>27</v>
       </c>
       <c r="H31" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="I31" t="s">
         <v>385</v>
@@ -7792,7 +7788,7 @@
         <v>389</v>
       </c>
       <c r="N31" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O31" t="s">
         <v>390</v>
@@ -7801,7 +7797,7 @@
         <v>391</v>
       </c>
       <c r="Q31" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="R31" t="s">
         <v>392</v>
@@ -7825,19 +7821,19 @@
         <v>395</v>
       </c>
       <c r="C32" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="D32" t="s">
         <v>396</v>
       </c>
       <c r="E32" t="s">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="F32" t="s">
         <v>302</v>
       </c>
       <c r="G32" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H32" t="s">
         <v>255</v>
@@ -7858,7 +7854,7 @@
         <v>401</v>
       </c>
       <c r="N32" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="O32" t="s">
         <v>402</v>
@@ -7867,7 +7863,7 @@
         <v>403</v>
       </c>
       <c r="Q32" t="s">
-        <v>190</v>
+        <v>55</v>
       </c>
       <c r="R32" t="s">
         <v>404</v>
@@ -7891,22 +7887,22 @@
         <v>408</v>
       </c>
       <c r="C33" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D33" t="s">
         <v>409</v>
       </c>
       <c r="E33" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="F33" t="s">
         <v>315</v>
       </c>
       <c r="G33" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H33" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="I33" t="s">
         <v>410</v>
@@ -7924,7 +7920,7 @@
         <v>414</v>
       </c>
       <c r="N33" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="O33" t="s">
         <v>415</v>
@@ -7957,7 +7953,7 @@
         <v>417</v>
       </c>
       <c r="C34" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="D34" t="s">
         <v>418</v>
@@ -7967,10 +7963,10 @@
         <v>302</v>
       </c>
       <c r="G34" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H34" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="I34" t="s">
         <v>419</v>
@@ -7988,7 +7984,7 @@
         <v>423</v>
       </c>
       <c r="N34" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="O34" t="s">
         <v>424</v>
@@ -8021,22 +8017,22 @@
         <v>430</v>
       </c>
       <c r="C35" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D35" t="s">
-        <v>108</v>
+        <v>136</v>
       </c>
       <c r="E35" t="s">
-        <v>109</v>
+        <v>137</v>
       </c>
       <c r="F35" t="s">
         <v>302</v>
       </c>
       <c r="G35" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H35" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="I35" t="s">
         <v>431</v>
@@ -8054,7 +8050,7 @@
         <v>435</v>
       </c>
       <c r="N35" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="O35" t="s">
         <v>436</v>
@@ -8063,16 +8059,16 @@
         <v>437</v>
       </c>
       <c r="Q35" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="R35" t="s">
-        <v>60</v>
+        <v>93</v>
       </c>
       <c r="S35" t="s">
-        <v>61</v>
+        <v>94</v>
       </c>
       <c r="T35" t="s">
-        <v>62</v>
+        <v>95</v>
       </c>
       <c r="U35" t="s">
         <v>429</v>
@@ -8087,19 +8083,19 @@
         <v>438</v>
       </c>
       <c r="C36" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D36" t="s">
         <v>439</v>
       </c>
       <c r="E36" t="s">
-        <v>109</v>
+        <v>137</v>
       </c>
       <c r="F36" t="s">
         <v>440</v>
       </c>
       <c r="G36" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H36" t="s">
         <v>441</v>
@@ -8120,7 +8116,7 @@
         <v>446</v>
       </c>
       <c r="N36" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="O36" t="s">
         <v>447</v>
@@ -8129,7 +8125,7 @@
         <v>448</v>
       </c>
       <c r="Q36" t="s">
-        <v>190</v>
+        <v>55</v>
       </c>
       <c r="R36" t="s">
         <v>449</v>
@@ -8153,22 +8149,22 @@
         <v>452</v>
       </c>
       <c r="C37" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="D37" t="s">
         <v>453</v>
       </c>
       <c r="E37" t="s">
-        <v>109</v>
+        <v>137</v>
       </c>
       <c r="F37" t="s">
-        <v>93</v>
+        <v>122</v>
       </c>
       <c r="G37" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H37" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="I37" t="s">
         <v>454</v>
@@ -8186,7 +8182,7 @@
         <v>458</v>
       </c>
       <c r="N37" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="O37" t="s">
         <v>459</v>
@@ -8195,7 +8191,7 @@
         <v>460</v>
       </c>
       <c r="Q37" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="R37" t="s">
         <v>461</v>
@@ -8219,22 +8215,22 @@
         <v>465</v>
       </c>
       <c r="C38" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D38" t="s">
         <v>466</v>
       </c>
       <c r="E38" t="s">
-        <v>109</v>
+        <v>137</v>
       </c>
       <c r="F38" t="s">
         <v>467</v>
       </c>
       <c r="G38" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H38" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="I38" t="s">
         <v>468</v>
@@ -8252,7 +8248,7 @@
         <v>472</v>
       </c>
       <c r="N38" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="O38" t="s">
         <v>473</v>
@@ -8264,13 +8260,13 @@
         <v>263</v>
       </c>
       <c r="R38" t="s">
-        <v>60</v>
+        <v>93</v>
       </c>
       <c r="S38" t="s">
-        <v>61</v>
+        <v>94</v>
       </c>
       <c r="T38" t="s">
-        <v>62</v>
+        <v>95</v>
       </c>
       <c r="U38" t="s">
         <v>464</v>
@@ -8285,22 +8281,22 @@
         <v>475</v>
       </c>
       <c r="C39" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="D39" t="s">
-        <v>75</v>
+        <v>24</v>
       </c>
       <c r="E39" t="s">
-        <v>76</v>
+        <v>25</v>
       </c>
       <c r="F39" t="s">
         <v>476</v>
       </c>
       <c r="G39" t="s">
-        <v>78</v>
+        <v>27</v>
       </c>
       <c r="H39" t="s">
-        <v>94</v>
+        <v>123</v>
       </c>
       <c r="I39" t="s">
         <v>477</v>
@@ -8318,7 +8314,7 @@
         <v>481</v>
       </c>
       <c r="N39" t="s">
-        <v>85</v>
+        <v>114</v>
       </c>
       <c r="O39" t="s">
         <v>482</v>
@@ -8327,16 +8323,16 @@
         <v>483</v>
       </c>
       <c r="Q39" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="R39" t="s">
-        <v>135</v>
+        <v>163</v>
       </c>
       <c r="S39" t="s">
-        <v>136</v>
+        <v>164</v>
       </c>
       <c r="T39" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
       <c r="U39" t="s">
         <v>484</v>
@@ -8351,19 +8347,19 @@
         <v>485</v>
       </c>
       <c r="C40" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="D40" t="s">
         <v>371</v>
       </c>
       <c r="E40" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="F40" t="s">
         <v>486</v>
       </c>
       <c r="G40" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H40" t="s">
         <v>255</v>
@@ -8382,7 +8378,7 @@
         <v>490</v>
       </c>
       <c r="N40" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O40" t="s">
         <v>491</v>
@@ -8391,7 +8387,7 @@
         <v>492</v>
       </c>
       <c r="Q40" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="R40" t="s">
         <v>493</v>
@@ -8415,7 +8411,7 @@
         <v>497</v>
       </c>
       <c r="C41" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="D41" t="s">
         <v>498</v>
@@ -8427,10 +8423,10 @@
         <v>467</v>
       </c>
       <c r="G41" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H41" t="s">
-        <v>94</v>
+        <v>123</v>
       </c>
       <c r="I41" t="s">
         <v>500</v>
@@ -8446,7 +8442,7 @@
         <v>503</v>
       </c>
       <c r="N41" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O41" t="s">
         <v>504</v>
@@ -8455,7 +8451,7 @@
         <v>505</v>
       </c>
       <c r="Q41" t="s">
-        <v>190</v>
+        <v>55</v>
       </c>
       <c r="R41" t="s">
         <v>506</v>
@@ -8483,14 +8479,14 @@
       </c>
       <c r="D42"/>
       <c r="E42" t="s">
-        <v>215</v>
+        <v>45</v>
       </c>
       <c r="F42" t="s">
         <v>511</v>
       </c>
       <c r="G42"/>
       <c r="H42" t="s">
-        <v>94</v>
+        <v>123</v>
       </c>
       <c r="I42" t="s">
         <v>512</v>
@@ -8504,7 +8500,7 @@
       <c r="L42"/>
       <c r="M42"/>
       <c r="N42" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O42" t="s">
         <v>515</v>
@@ -8513,7 +8509,7 @@
         <v>516</v>
       </c>
       <c r="Q42" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="R42" t="s">
         <v>449</v>
@@ -8537,22 +8533,22 @@
         <v>517</v>
       </c>
       <c r="C43" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="D43" t="s">
         <v>396</v>
       </c>
       <c r="E43" t="s">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="F43" t="s">
         <v>518</v>
       </c>
       <c r="G43" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H43" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="I43" t="s">
         <v>519</v>
@@ -8568,7 +8564,7 @@
         <v>522</v>
       </c>
       <c r="N43" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O43" t="s">
         <v>523</v>
@@ -8577,7 +8573,7 @@
         <v>524</v>
       </c>
       <c r="Q43" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="R43" t="s">
         <v>525</v>
@@ -8601,22 +8597,22 @@
         <v>528</v>
       </c>
       <c r="C44" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="D44" t="s">
         <v>529</v>
       </c>
       <c r="E44" t="s">
-        <v>215</v>
+        <v>45</v>
       </c>
       <c r="F44" t="s">
         <v>530</v>
       </c>
       <c r="G44" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H44" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="I44" t="s">
         <v>531</v>
@@ -8634,7 +8630,7 @@
         <v>535</v>
       </c>
       <c r="N44" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O44" t="s">
         <v>536</v>
@@ -8643,16 +8639,16 @@
         <v>537</v>
       </c>
       <c r="Q44" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="R44" t="s">
-        <v>161</v>
+        <v>38</v>
       </c>
       <c r="S44" t="s">
-        <v>162</v>
+        <v>39</v>
       </c>
       <c r="T44" t="s">
-        <v>163</v>
+        <v>40</v>
       </c>
       <c r="U44" t="s">
         <v>496</v>
@@ -8667,7 +8663,7 @@
         <v>538</v>
       </c>
       <c r="C45" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D45" t="s">
         <v>539</v>
@@ -8679,10 +8675,10 @@
         <v>476</v>
       </c>
       <c r="G45" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H45" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="I45" t="s">
         <v>541</v>
@@ -8700,7 +8696,7 @@
         <v>545</v>
       </c>
       <c r="N45" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="O45" t="s">
         <v>546</v>
@@ -8733,22 +8729,22 @@
         <v>551</v>
       </c>
       <c r="C46" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D46" t="s">
         <v>552</v>
       </c>
       <c r="E46" t="s">
-        <v>109</v>
+        <v>137</v>
       </c>
       <c r="F46" t="s">
         <v>476</v>
       </c>
       <c r="G46" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H46" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="I46" t="s">
         <v>553</v>
@@ -8766,7 +8762,7 @@
         <v>557</v>
       </c>
       <c r="N46" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="O46" t="s">
         <v>558</v>
@@ -8775,7 +8771,7 @@
         <v>559</v>
       </c>
       <c r="Q46" t="s">
-        <v>190</v>
+        <v>55</v>
       </c>
       <c r="R46" t="s">
         <v>560</v>
@@ -8799,22 +8795,22 @@
         <v>563</v>
       </c>
       <c r="C47" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="D47" t="s">
-        <v>75</v>
+        <v>24</v>
       </c>
       <c r="E47" t="s">
-        <v>76</v>
+        <v>25</v>
       </c>
       <c r="F47" t="s">
         <v>564</v>
       </c>
       <c r="G47" t="s">
-        <v>78</v>
+        <v>27</v>
       </c>
       <c r="H47" t="s">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="I47" t="s">
         <v>565</v>
@@ -8832,7 +8828,7 @@
         <v>569</v>
       </c>
       <c r="N47" t="s">
-        <v>148</v>
+        <v>176</v>
       </c>
       <c r="O47" t="s">
         <v>570</v>
@@ -8841,7 +8837,7 @@
         <v>571</v>
       </c>
       <c r="Q47" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="R47" t="s">
         <v>572</v>
@@ -8868,19 +8864,19 @@
         <v>228</v>
       </c>
       <c r="D48" t="s">
-        <v>75</v>
+        <v>24</v>
       </c>
       <c r="E48" t="s">
-        <v>76</v>
+        <v>25</v>
       </c>
       <c r="F48" t="s">
         <v>564</v>
       </c>
       <c r="G48" t="s">
-        <v>78</v>
+        <v>27</v>
       </c>
       <c r="H48" t="s">
-        <v>94</v>
+        <v>123</v>
       </c>
       <c r="I48" t="s">
         <v>576</v>
@@ -8907,7 +8903,7 @@
         <v>582</v>
       </c>
       <c r="Q48" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="R48" t="s">
         <v>583</v>
@@ -8931,22 +8927,22 @@
         <v>586</v>
       </c>
       <c r="C49" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D49" t="s">
         <v>587</v>
       </c>
       <c r="E49" t="s">
-        <v>76</v>
+        <v>25</v>
       </c>
       <c r="F49" t="s">
         <v>588</v>
       </c>
       <c r="G49" t="s">
-        <v>78</v>
+        <v>27</v>
       </c>
       <c r="H49" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="I49" t="s">
         <v>589</v>
@@ -8964,7 +8960,7 @@
         <v>593</v>
       </c>
       <c r="N49" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O49" t="s">
         <v>594</v>
@@ -8973,7 +8969,7 @@
         <v>595</v>
       </c>
       <c r="Q49" t="s">
-        <v>190</v>
+        <v>55</v>
       </c>
       <c r="R49" t="s">
         <v>596</v>
@@ -8997,22 +8993,22 @@
         <v>599</v>
       </c>
       <c r="C50" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="D50" t="s">
         <v>453</v>
       </c>
       <c r="E50" t="s">
-        <v>109</v>
+        <v>137</v>
       </c>
       <c r="F50" t="s">
         <v>372</v>
       </c>
       <c r="G50" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H50" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="I50" t="s">
         <v>600</v>
@@ -9030,7 +9026,7 @@
         <v>604</v>
       </c>
       <c r="N50" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="O50" t="s">
         <v>605</v>
@@ -9039,16 +9035,16 @@
         <v>606</v>
       </c>
       <c r="Q50" t="s">
-        <v>190</v>
+        <v>55</v>
       </c>
       <c r="R50" t="s">
-        <v>161</v>
+        <v>38</v>
       </c>
       <c r="S50" t="s">
-        <v>162</v>
+        <v>39</v>
       </c>
       <c r="T50" t="s">
-        <v>163</v>
+        <v>40</v>
       </c>
       <c r="U50" t="s">
         <v>496</v>
@@ -9063,22 +9059,22 @@
         <v>607</v>
       </c>
       <c r="C51" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="D51" t="s">
         <v>608</v>
       </c>
       <c r="E51" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="F51" t="s">
         <v>609</v>
       </c>
       <c r="G51" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H51" t="s">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="I51" t="s">
         <v>610</v>
@@ -9094,7 +9090,7 @@
         <v>613</v>
       </c>
       <c r="N51" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O51" t="s">
         <v>614</v>
@@ -9103,7 +9099,7 @@
         <v>615</v>
       </c>
       <c r="Q51" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="R51" t="s">
         <v>616</v>
@@ -9127,22 +9123,22 @@
         <v>619</v>
       </c>
       <c r="C52" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="D52" t="s">
         <v>439</v>
       </c>
       <c r="E52" t="s">
-        <v>109</v>
+        <v>137</v>
       </c>
       <c r="F52" t="s">
         <v>609</v>
       </c>
       <c r="G52" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H52" t="s">
-        <v>94</v>
+        <v>123</v>
       </c>
       <c r="I52" t="s">
         <v>620</v>
@@ -9158,7 +9154,7 @@
         <v>623</v>
       </c>
       <c r="N52" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O52" t="s">
         <v>624</v>
@@ -9167,16 +9163,16 @@
         <v>625</v>
       </c>
       <c r="Q52" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="R52" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="S52" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="T52" t="s">
-        <v>105</v>
+        <v>134</v>
       </c>
       <c r="U52" t="s">
         <v>496</v>
@@ -9201,10 +9197,10 @@
         <v>628</v>
       </c>
       <c r="G53" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H53" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="I53" t="s">
         <v>629</v>
@@ -9231,7 +9227,7 @@
         <v>635</v>
       </c>
       <c r="Q53" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="R53" t="s">
         <v>636</v>
@@ -9255,22 +9251,22 @@
         <v>639</v>
       </c>
       <c r="C54" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="D54" t="s">
         <v>640</v>
       </c>
       <c r="E54" t="s">
-        <v>109</v>
+        <v>137</v>
       </c>
       <c r="F54" t="s">
         <v>641</v>
       </c>
       <c r="G54" t="s">
-        <v>78</v>
+        <v>27</v>
       </c>
       <c r="H54" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="I54" t="s">
         <v>642</v>
@@ -9288,7 +9284,7 @@
         <v>646</v>
       </c>
       <c r="N54" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O54" t="s">
         <v>647</v>
@@ -9297,7 +9293,7 @@
         <v>648</v>
       </c>
       <c r="Q54" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="R54" t="s">
         <v>649</v>
@@ -9327,16 +9323,16 @@
         <v>653</v>
       </c>
       <c r="E55" t="s">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="F55" t="s">
         <v>641</v>
       </c>
       <c r="G55" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H55" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="I55" t="s">
         <v>654</v>
@@ -9354,7 +9350,7 @@
         <v>658</v>
       </c>
       <c r="N55" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="O55" t="s">
         <v>659</v>
@@ -9363,7 +9359,7 @@
         <v>660</v>
       </c>
       <c r="Q55" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="R55" t="s">
         <v>449</v>
@@ -9387,22 +9383,22 @@
         <v>661</v>
       </c>
       <c r="C56" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D56" t="s">
         <v>409</v>
       </c>
       <c r="E56" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="F56" t="s">
         <v>641</v>
       </c>
       <c r="G56" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H56" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="I56" t="s">
         <v>662</v>
@@ -9420,7 +9416,7 @@
         <v>666</v>
       </c>
       <c r="N56" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="O56" t="s">
         <v>667</v>
@@ -9432,13 +9428,13 @@
         <v>263</v>
       </c>
       <c r="R56" t="s">
-        <v>60</v>
+        <v>93</v>
       </c>
       <c r="S56" t="s">
-        <v>61</v>
+        <v>94</v>
       </c>
       <c r="T56" t="s">
-        <v>62</v>
+        <v>95</v>
       </c>
       <c r="U56" t="s">
         <v>496</v>
@@ -9453,22 +9449,22 @@
         <v>669</v>
       </c>
       <c r="C57" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="D57" t="s">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="E57" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="F57" t="s">
         <v>641</v>
       </c>
       <c r="G57" t="s">
-        <v>78</v>
+        <v>27</v>
       </c>
       <c r="H57" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="I57" t="s">
         <v>670</v>
@@ -9486,7 +9482,7 @@
         <v>674</v>
       </c>
       <c r="N57" t="s">
-        <v>148</v>
+        <v>176</v>
       </c>
       <c r="O57" t="s">
         <v>675</v>
@@ -9495,7 +9491,7 @@
         <v>676</v>
       </c>
       <c r="Q57" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="R57" t="s">
         <v>677</v>
@@ -9519,22 +9515,22 @@
         <v>680</v>
       </c>
       <c r="C58" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D58" t="s">
         <v>681</v>
       </c>
       <c r="E58" t="s">
-        <v>76</v>
+        <v>25</v>
       </c>
       <c r="F58" t="s">
         <v>682</v>
       </c>
       <c r="G58" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H58" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="I58" t="s">
         <v>683</v>
@@ -9552,7 +9548,7 @@
         <v>687</v>
       </c>
       <c r="N58" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O58" t="s">
         <v>688</v>
@@ -9585,19 +9581,19 @@
         <v>690</v>
       </c>
       <c r="C59" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D59" t="s">
-        <v>75</v>
+        <v>24</v>
       </c>
       <c r="E59" t="s">
-        <v>76</v>
+        <v>25</v>
       </c>
       <c r="F59" t="s">
         <v>691</v>
       </c>
       <c r="G59" t="s">
-        <v>78</v>
+        <v>27</v>
       </c>
       <c r="H59" t="s">
         <v>255</v>
@@ -9618,7 +9614,7 @@
         <v>696</v>
       </c>
       <c r="N59" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O59" t="s">
         <v>697</v>
@@ -9651,22 +9647,22 @@
         <v>702</v>
       </c>
       <c r="C60" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D60" t="s">
         <v>703</v>
       </c>
       <c r="E60" t="s">
-        <v>109</v>
+        <v>137</v>
       </c>
       <c r="F60" t="s">
         <v>691</v>
       </c>
       <c r="G60" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H60" t="s">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="I60" t="s">
         <v>704</v>
@@ -9684,7 +9680,7 @@
         <v>708</v>
       </c>
       <c r="N60" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="O60" t="s">
         <v>709</v>
@@ -9693,7 +9689,7 @@
         <v>710</v>
       </c>
       <c r="Q60" t="s">
-        <v>190</v>
+        <v>55</v>
       </c>
       <c r="R60" t="s">
         <v>711</v>
@@ -9717,22 +9713,22 @@
         <v>714</v>
       </c>
       <c r="C61" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D61" t="s">
         <v>715</v>
       </c>
       <c r="E61" t="s">
-        <v>76</v>
+        <v>25</v>
       </c>
       <c r="F61" t="s">
         <v>716</v>
       </c>
       <c r="G61" t="s">
-        <v>78</v>
+        <v>27</v>
       </c>
       <c r="H61" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="I61" t="s">
         <v>717</v>
@@ -9750,7 +9746,7 @@
         <v>721</v>
       </c>
       <c r="N61" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O61" t="s">
         <v>722</v>
@@ -9786,19 +9782,19 @@
         <v>728</v>
       </c>
       <c r="D62" t="s">
-        <v>108</v>
+        <v>136</v>
       </c>
       <c r="E62" t="s">
-        <v>109</v>
+        <v>137</v>
       </c>
       <c r="F62" t="s">
         <v>729</v>
       </c>
       <c r="G62" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H62" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="I62" t="s">
         <v>730</v>
@@ -9825,7 +9821,7 @@
         <v>737</v>
       </c>
       <c r="Q62" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="R62" t="s">
         <v>738</v>
@@ -9849,7 +9845,7 @@
         <v>741</v>
       </c>
       <c r="C63" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="D63" t="s">
         <v>742</v>
@@ -9861,10 +9857,10 @@
         <v>743</v>
       </c>
       <c r="G63" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H63" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="I63" t="s">
         <v>744</v>
@@ -9882,7 +9878,7 @@
         <v>748</v>
       </c>
       <c r="N63" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="O63" t="s">
         <v>749</v>
@@ -9891,16 +9887,16 @@
         <v>750</v>
       </c>
       <c r="Q63" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="R63" t="s">
-        <v>115</v>
+        <v>143</v>
       </c>
       <c r="S63" t="s">
-        <v>116</v>
+        <v>144</v>
       </c>
       <c r="T63" t="s">
-        <v>117</v>
+        <v>145</v>
       </c>
       <c r="U63" t="s">
         <v>496</v>
@@ -9915,22 +9911,22 @@
         <v>751</v>
       </c>
       <c r="C64" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="D64" t="s">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="E64" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="F64" t="s">
         <v>743</v>
       </c>
       <c r="G64" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H64" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="I64" t="s">
         <v>752</v>
@@ -9946,7 +9942,7 @@
         <v>755</v>
       </c>
       <c r="N64" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O64" t="s">
         <v>756</v>
@@ -9979,19 +9975,19 @@
         <v>758</v>
       </c>
       <c r="C65" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="D65" t="s">
         <v>759</v>
       </c>
       <c r="E65" t="s">
-        <v>76</v>
+        <v>25</v>
       </c>
       <c r="F65" t="s">
         <v>743</v>
       </c>
       <c r="G65" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H65" t="s">
         <v>255</v>
@@ -10010,7 +10006,7 @@
         <v>763</v>
       </c>
       <c r="N65" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O65" t="s">
         <v>764</v>
@@ -10019,7 +10015,7 @@
         <v>765</v>
       </c>
       <c r="Q65" t="s">
-        <v>190</v>
+        <v>55</v>
       </c>
       <c r="R65" t="s">
         <v>766</v>
@@ -10043,22 +10039,22 @@
         <v>769</v>
       </c>
       <c r="C66" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="D66" t="s">
         <v>703</v>
       </c>
       <c r="E66" t="s">
-        <v>109</v>
+        <v>137</v>
       </c>
       <c r="F66" t="s">
         <v>770</v>
       </c>
       <c r="G66" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H66" t="s">
-        <v>94</v>
+        <v>123</v>
       </c>
       <c r="I66" t="s">
         <v>771</v>
@@ -10074,7 +10070,7 @@
         <v>774</v>
       </c>
       <c r="N66" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O66" t="s">
         <v>775</v>
@@ -10107,22 +10103,22 @@
         <v>780</v>
       </c>
       <c r="C67" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D67" t="s">
         <v>781</v>
       </c>
       <c r="E67" t="s">
-        <v>109</v>
+        <v>137</v>
       </c>
       <c r="F67" t="s">
         <v>782</v>
       </c>
       <c r="G67" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H67" t="s">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="I67" t="s">
         <v>783</v>
@@ -10140,7 +10136,7 @@
         <v>787</v>
       </c>
       <c r="N67" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="O67" t="s">
         <v>788</v>
@@ -10149,7 +10145,7 @@
         <v>789</v>
       </c>
       <c r="Q67" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="R67" t="s">
         <v>790</v>
@@ -10173,22 +10169,22 @@
         <v>793</v>
       </c>
       <c r="C68" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="D68" t="s">
         <v>781</v>
       </c>
       <c r="E68" t="s">
-        <v>109</v>
+        <v>137</v>
       </c>
       <c r="F68" t="s">
         <v>782</v>
       </c>
       <c r="G68" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H68" t="s">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="I68" t="s">
         <v>794</v>
@@ -10204,7 +10200,7 @@
         <v>797</v>
       </c>
       <c r="N68" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O68" t="s">
         <v>798</v>
@@ -10213,7 +10209,7 @@
         <v>799</v>
       </c>
       <c r="Q68" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="R68" t="s">
         <v>800</v>
@@ -10237,7 +10233,7 @@
         <v>803</v>
       </c>
       <c r="C69" t="s">
-        <v>139</v>
+        <v>167</v>
       </c>
       <c r="D69" t="s">
         <v>804</v>
@@ -10248,7 +10244,7 @@
       </c>
       <c r="G69"/>
       <c r="H69" t="s">
-        <v>94</v>
+        <v>123</v>
       </c>
       <c r="I69" t="s">
         <v>806</v>
@@ -10266,7 +10262,7 @@
         <v>810</v>
       </c>
       <c r="N69" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="O69" t="s">
         <v>811</v>
@@ -10275,7 +10271,7 @@
         <v>812</v>
       </c>
       <c r="Q69" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="R69"/>
       <c r="S69"/>
@@ -10293,22 +10289,22 @@
         <v>813</v>
       </c>
       <c r="C70" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D70" t="s">
         <v>814</v>
       </c>
       <c r="E70" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="F70" t="s">
         <v>815</v>
       </c>
       <c r="G70" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H70" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="I70" t="s">
         <v>816</v>
@@ -10326,7 +10322,7 @@
         <v>820</v>
       </c>
       <c r="N70" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="O70" t="s">
         <v>821</v>
@@ -10335,7 +10331,7 @@
         <v>822</v>
       </c>
       <c r="Q70" t="s">
-        <v>190</v>
+        <v>55</v>
       </c>
       <c r="R70" t="s">
         <v>823</v>
@@ -10359,22 +10355,22 @@
         <v>826</v>
       </c>
       <c r="C71" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D71" t="s">
         <v>827</v>
       </c>
       <c r="E71" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="F71" t="s">
         <v>815</v>
       </c>
       <c r="G71" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H71" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="I71" t="s">
         <v>828</v>
@@ -10392,7 +10388,7 @@
         <v>832</v>
       </c>
       <c r="N71" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="O71" t="s">
         <v>833</v>
@@ -10401,7 +10397,7 @@
         <v>834</v>
       </c>
       <c r="Q71" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="R71" t="s">
         <v>835</v>
@@ -10431,16 +10427,16 @@
         <v>839</v>
       </c>
       <c r="E72" t="s">
-        <v>76</v>
+        <v>25</v>
       </c>
       <c r="F72" t="s">
         <v>815</v>
       </c>
       <c r="G72" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H72" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="I72" t="s">
         <v>840</v>
@@ -10467,7 +10463,7 @@
         <v>847</v>
       </c>
       <c r="Q72" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="R72" t="s">
         <v>848</v>
@@ -10491,7 +10487,7 @@
         <v>851</v>
       </c>
       <c r="C73" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="D73" t="s">
         <v>418</v>
@@ -10501,10 +10497,10 @@
         <v>852</v>
       </c>
       <c r="G73" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H73" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="I73" t="s">
         <v>853</v>
@@ -10522,7 +10518,7 @@
         <v>857</v>
       </c>
       <c r="N73" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="O73" t="s">
         <v>858</v>
@@ -10555,22 +10551,22 @@
         <v>863</v>
       </c>
       <c r="C74" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D74" t="s">
         <v>864</v>
       </c>
       <c r="E74" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="F74" t="s">
         <v>852</v>
       </c>
       <c r="G74" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H74" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="I74" t="s">
         <v>865</v>
@@ -10588,7 +10584,7 @@
         <v>869</v>
       </c>
       <c r="N74" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O74" t="s">
         <v>870</v>
@@ -10597,7 +10593,7 @@
         <v>871</v>
       </c>
       <c r="Q74" t="s">
-        <v>190</v>
+        <v>55</v>
       </c>
       <c r="R74" t="s">
         <v>872</v>
@@ -10621,22 +10617,22 @@
         <v>875</v>
       </c>
       <c r="C75" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D75" t="s">
         <v>876</v>
       </c>
       <c r="E75" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="F75" t="s">
         <v>877</v>
       </c>
       <c r="G75" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H75" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="I75" t="s">
         <v>878</v>
@@ -10654,7 +10650,7 @@
         <v>882</v>
       </c>
       <c r="N75" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O75" t="s">
         <v>883</v>
@@ -10666,13 +10662,13 @@
         <v>263</v>
       </c>
       <c r="R75" t="s">
-        <v>60</v>
+        <v>93</v>
       </c>
       <c r="S75" t="s">
-        <v>61</v>
+        <v>94</v>
       </c>
       <c r="T75" t="s">
-        <v>62</v>
+        <v>95</v>
       </c>
       <c r="U75" t="s">
         <v>496</v>
@@ -10697,10 +10693,10 @@
         <v>877</v>
       </c>
       <c r="G76" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H76" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="I76" t="s">
         <v>887</v>
@@ -10727,7 +10723,7 @@
         <v>893</v>
       </c>
       <c r="Q76" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="R76" t="s">
         <v>894</v>
@@ -10751,22 +10747,22 @@
         <v>897</v>
       </c>
       <c r="C77" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D77" t="s">
         <v>653</v>
       </c>
       <c r="E77" t="s">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="F77" t="s">
         <v>877</v>
       </c>
       <c r="G77" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H77" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="I77" t="s">
         <v>898</v>
@@ -10784,7 +10780,7 @@
         <v>902</v>
       </c>
       <c r="N77" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="O77" t="s">
         <v>903</v>
@@ -10817,7 +10813,7 @@
         <v>908</v>
       </c>
       <c r="C78" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D78" t="s">
         <v>909</v>
@@ -10829,10 +10825,10 @@
         <v>910</v>
       </c>
       <c r="G78" t="s">
-        <v>78</v>
+        <v>27</v>
       </c>
       <c r="H78" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="I78" t="s">
         <v>911</v>
@@ -10850,7 +10846,7 @@
         <v>915</v>
       </c>
       <c r="N78" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O78" t="s">
         <v>916</v>
@@ -10859,7 +10855,7 @@
         <v>917</v>
       </c>
       <c r="Q78" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="R78" t="s">
         <v>823</v>
@@ -10883,22 +10879,22 @@
         <v>918</v>
       </c>
       <c r="C79" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="D79" t="s">
         <v>919</v>
       </c>
       <c r="E79" t="s">
-        <v>109</v>
+        <v>137</v>
       </c>
       <c r="F79" t="s">
         <v>920</v>
       </c>
       <c r="G79" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H79" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="I79" t="s">
         <v>921</v>
@@ -10916,7 +10912,7 @@
         <v>925</v>
       </c>
       <c r="N79" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="O79" t="s">
         <v>926</v>
@@ -10925,7 +10921,7 @@
         <v>927</v>
       </c>
       <c r="Q79" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="R79" t="s">
         <v>392</v>
@@ -10949,7 +10945,7 @@
         <v>928</v>
       </c>
       <c r="C80" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="D80" t="s">
         <v>929</v>
@@ -10961,10 +10957,10 @@
         <v>931</v>
       </c>
       <c r="G80" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H80" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="I80" t="s">
         <v>932</v>
@@ -10982,7 +10978,7 @@
         <v>936</v>
       </c>
       <c r="N80" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="O80" t="s">
         <v>937</v>
@@ -10991,7 +10987,7 @@
         <v>938</v>
       </c>
       <c r="Q80" t="s">
-        <v>190</v>
+        <v>55</v>
       </c>
       <c r="R80" t="s">
         <v>939</v>
@@ -11015,22 +11011,22 @@
         <v>942</v>
       </c>
       <c r="C81" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="D81" t="s">
         <v>703</v>
       </c>
       <c r="E81" t="s">
-        <v>109</v>
+        <v>137</v>
       </c>
       <c r="F81" t="s">
         <v>931</v>
       </c>
       <c r="G81" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H81" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="I81" t="s">
         <v>943</v>
@@ -11048,7 +11044,7 @@
         <v>947</v>
       </c>
       <c r="N81" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="O81" t="s">
         <v>948</v>
@@ -11081,7 +11077,7 @@
         <v>953</v>
       </c>
       <c r="C82" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="D82" t="s">
         <v>954</v>
@@ -11091,10 +11087,10 @@
         <v>955</v>
       </c>
       <c r="G82" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H82" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="I82" t="s">
         <v>956</v>
@@ -11151,13 +11147,13 @@
         <v>964</v>
       </c>
       <c r="E83" t="s">
-        <v>76</v>
+        <v>25</v>
       </c>
       <c r="F83" t="s">
         <v>965</v>
       </c>
       <c r="G83" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H83" t="s">
         <v>966</v>
@@ -11187,7 +11183,7 @@
         <v>973</v>
       </c>
       <c r="Q83" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="R83" t="s">
         <v>974</v>
@@ -11211,22 +11207,22 @@
         <v>977</v>
       </c>
       <c r="C84" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D84" t="s">
         <v>978</v>
       </c>
       <c r="E84" t="s">
-        <v>76</v>
+        <v>25</v>
       </c>
       <c r="F84" t="s">
         <v>965</v>
       </c>
       <c r="G84" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H84" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="I84" t="s">
         <v>979</v>
@@ -11244,7 +11240,7 @@
         <v>983</v>
       </c>
       <c r="N84" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="O84" t="s">
         <v>984</v>
@@ -11253,7 +11249,7 @@
         <v>985</v>
       </c>
       <c r="Q84" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="R84" t="s">
         <v>986</v>
@@ -11277,22 +11273,22 @@
         <v>989</v>
       </c>
       <c r="C85" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D85" t="s">
         <v>990</v>
       </c>
       <c r="E85" t="s">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="F85" t="s">
         <v>965</v>
       </c>
       <c r="G85" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H85" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="I85" t="s">
         <v>991</v>
@@ -11310,7 +11306,7 @@
         <v>995</v>
       </c>
       <c r="N85" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="O85" t="s">
         <v>996</v>
@@ -11319,16 +11315,16 @@
         <v>997</v>
       </c>
       <c r="Q85" t="s">
-        <v>190</v>
+        <v>55</v>
       </c>
       <c r="R85" t="s">
-        <v>115</v>
+        <v>143</v>
       </c>
       <c r="S85" t="s">
-        <v>116</v>
+        <v>144</v>
       </c>
       <c r="T85" t="s">
-        <v>117</v>
+        <v>145</v>
       </c>
       <c r="U85" t="s">
         <v>496</v>
@@ -11343,22 +11339,22 @@
         <v>998</v>
       </c>
       <c r="C86" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="D86" t="s">
         <v>999</v>
       </c>
       <c r="E86" t="s">
-        <v>76</v>
+        <v>25</v>
       </c>
       <c r="F86" t="s">
         <v>1000</v>
       </c>
       <c r="G86" t="s">
-        <v>78</v>
+        <v>27</v>
       </c>
       <c r="H86" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="I86" t="s">
         <v>1001</v>
@@ -11376,7 +11372,7 @@
         <v>1005</v>
       </c>
       <c r="N86" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O86" t="s">
         <v>1006</v>
@@ -11409,22 +11405,22 @@
         <v>1011</v>
       </c>
       <c r="C87" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="D87" t="s">
-        <v>75</v>
+        <v>24</v>
       </c>
       <c r="E87" t="s">
-        <v>76</v>
+        <v>25</v>
       </c>
       <c r="F87" t="s">
         <v>1000</v>
       </c>
       <c r="G87" t="s">
-        <v>78</v>
+        <v>27</v>
       </c>
       <c r="H87" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="I87" t="s">
         <v>1012</v>
@@ -11442,7 +11438,7 @@
         <v>1016</v>
       </c>
       <c r="N87" t="s">
-        <v>148</v>
+        <v>176</v>
       </c>
       <c r="O87" t="s">
         <v>1017</v>
@@ -11475,22 +11471,22 @@
         <v>1019</v>
       </c>
       <c r="C88" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D88" t="s">
         <v>587</v>
       </c>
       <c r="E88" t="s">
-        <v>76</v>
+        <v>25</v>
       </c>
       <c r="F88" t="s">
         <v>1020</v>
       </c>
       <c r="G88" t="s">
-        <v>78</v>
+        <v>27</v>
       </c>
       <c r="H88" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="I88" t="s">
         <v>1021</v>
@@ -11508,7 +11504,7 @@
         <v>1025</v>
       </c>
       <c r="N88" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O88" t="s">
         <v>1026</v>
@@ -11517,7 +11513,7 @@
         <v>1027</v>
       </c>
       <c r="Q88" t="s">
-        <v>190</v>
+        <v>55</v>
       </c>
       <c r="R88" t="s">
         <v>1028</v>
@@ -11541,22 +11537,22 @@
         <v>1031</v>
       </c>
       <c r="C89" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D89" t="s">
         <v>864</v>
       </c>
       <c r="E89" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="F89" t="s">
         <v>1032</v>
       </c>
       <c r="G89" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H89" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="I89" t="s">
         <v>1033</v>
@@ -11574,7 +11570,7 @@
         <v>1037</v>
       </c>
       <c r="N89" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="O89" t="s">
         <v>1038</v>
@@ -11583,7 +11579,7 @@
         <v>1039</v>
       </c>
       <c r="Q89" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="R89" t="s">
         <v>1040</v>
@@ -11607,7 +11603,7 @@
         <v>1043</v>
       </c>
       <c r="C90" t="s">
-        <v>139</v>
+        <v>167</v>
       </c>
       <c r="D90" t="s">
         <v>1044</v>
@@ -11618,7 +11614,7 @@
       </c>
       <c r="G90"/>
       <c r="H90" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="I90" t="s">
         <v>1046</v>
@@ -11636,7 +11632,7 @@
         <v>1050</v>
       </c>
       <c r="N90" t="s">
-        <v>85</v>
+        <v>114</v>
       </c>
       <c r="O90" t="s">
         <v>1051</v>
@@ -11645,7 +11641,7 @@
         <v>1052</v>
       </c>
       <c r="Q90" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="R90"/>
       <c r="S90"/>
@@ -11663,7 +11659,7 @@
         <v>1053</v>
       </c>
       <c r="C91" t="s">
-        <v>139</v>
+        <v>167</v>
       </c>
       <c r="D91" t="s">
         <v>1054</v>
@@ -11674,7 +11670,7 @@
       </c>
       <c r="G91"/>
       <c r="H91" t="s">
-        <v>94</v>
+        <v>123</v>
       </c>
       <c r="I91" t="s">
         <v>806</v>
@@ -11692,7 +11688,7 @@
         <v>1057</v>
       </c>
       <c r="N91" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O91" t="s">
         <v>1058</v>
@@ -11701,7 +11697,7 @@
         <v>1059</v>
       </c>
       <c r="Q91" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="R91"/>
       <c r="S91"/>
@@ -11729,10 +11725,10 @@
         <v>1062</v>
       </c>
       <c r="G92" t="s">
-        <v>78</v>
+        <v>27</v>
       </c>
       <c r="H92" t="s">
-        <v>94</v>
+        <v>123</v>
       </c>
       <c r="I92" t="s">
         <v>1063</v>
@@ -11750,7 +11746,7 @@
         <v>1067</v>
       </c>
       <c r="N92" t="s">
-        <v>85</v>
+        <v>114</v>
       </c>
       <c r="O92" t="s">
         <v>1068</v>
@@ -11759,7 +11755,7 @@
         <v>1069</v>
       </c>
       <c r="Q92" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="R92" t="s">
         <v>1070</v>
@@ -11789,16 +11785,16 @@
         <v>827</v>
       </c>
       <c r="E93" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="F93" t="s">
         <v>1074</v>
       </c>
       <c r="G93" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H93" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="I93" t="s">
         <v>1075</v>
@@ -11816,7 +11812,7 @@
         <v>1079</v>
       </c>
       <c r="N93" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O93" t="s">
         <v>1080</v>
@@ -11825,7 +11821,7 @@
         <v>1081</v>
       </c>
       <c r="Q93" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="R93" t="s">
         <v>1082</v>
@@ -11849,7 +11845,7 @@
         <v>1085</v>
       </c>
       <c r="C94" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D94" t="s">
         <v>929</v>
@@ -11861,10 +11857,10 @@
         <v>1074</v>
       </c>
       <c r="G94" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H94" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="I94" t="s">
         <v>1086</v>
@@ -11882,7 +11878,7 @@
         <v>1090</v>
       </c>
       <c r="N94" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="O94" t="s">
         <v>1091</v>
@@ -11915,19 +11911,19 @@
         <v>1096</v>
       </c>
       <c r="C95" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D95" t="s">
         <v>1097</v>
       </c>
       <c r="E95" t="s">
-        <v>76</v>
+        <v>25</v>
       </c>
       <c r="F95" t="s">
         <v>1074</v>
       </c>
       <c r="G95" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H95" t="s">
         <v>441</v>
@@ -11948,7 +11944,7 @@
         <v>1102</v>
       </c>
       <c r="N95" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O95" t="s">
         <v>1103</v>
@@ -11957,7 +11953,7 @@
         <v>1104</v>
       </c>
       <c r="Q95" t="s">
-        <v>190</v>
+        <v>55</v>
       </c>
       <c r="R95" t="s">
         <v>1105</v>
@@ -11981,22 +11977,22 @@
         <v>1108</v>
       </c>
       <c r="C96" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="D96" t="s">
         <v>653</v>
       </c>
       <c r="E96" t="s">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="F96" t="s">
         <v>1074</v>
       </c>
       <c r="G96" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H96" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="I96" t="s">
         <v>1109</v>
@@ -12047,22 +12043,22 @@
         <v>1119</v>
       </c>
       <c r="C97" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="D97" t="s">
         <v>1120</v>
       </c>
       <c r="E97" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="F97" t="s">
         <v>1074</v>
       </c>
       <c r="G97" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H97" t="s">
-        <v>94</v>
+        <v>123</v>
       </c>
       <c r="I97" t="s">
         <v>1121</v>
@@ -12080,7 +12076,7 @@
         <v>1125</v>
       </c>
       <c r="N97" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="O97" t="s">
         <v>1126</v>
@@ -12089,7 +12085,7 @@
         <v>1127</v>
       </c>
       <c r="Q97" t="s">
-        <v>190</v>
+        <v>55</v>
       </c>
       <c r="R97" t="s">
         <v>1128</v>
@@ -12113,22 +12109,22 @@
         <v>1131</v>
       </c>
       <c r="C98" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D98" t="s">
         <v>1132</v>
       </c>
       <c r="E98" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="F98" t="s">
         <v>1074</v>
       </c>
       <c r="G98" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H98" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="I98" t="s">
         <v>1133</v>
@@ -12146,7 +12142,7 @@
         <v>1137</v>
       </c>
       <c r="N98" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="O98" t="s">
         <v>1138</v>
@@ -12179,22 +12175,22 @@
         <v>1143</v>
       </c>
       <c r="C99" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="D99" t="s">
         <v>759</v>
       </c>
       <c r="E99" t="s">
-        <v>76</v>
+        <v>25</v>
       </c>
       <c r="F99" t="s">
         <v>1144</v>
       </c>
       <c r="G99" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H99" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="I99" t="s">
         <v>1145</v>
@@ -12212,7 +12208,7 @@
         <v>1149</v>
       </c>
       <c r="N99" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O99" t="s">
         <v>1150</v>
@@ -12221,7 +12217,7 @@
         <v>1151</v>
       </c>
       <c r="Q99" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="R99" t="s">
         <v>1152</v>
@@ -12245,22 +12241,22 @@
         <v>1155</v>
       </c>
       <c r="C100" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D100" t="s">
         <v>1156</v>
       </c>
       <c r="E100" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="F100" t="s">
         <v>1144</v>
       </c>
       <c r="G100" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H100" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="I100" t="s">
         <v>1157</v>
@@ -12278,7 +12274,7 @@
         <v>1161</v>
       </c>
       <c r="N100" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="O100" t="s">
         <v>1162</v>
@@ -12287,7 +12283,7 @@
         <v>1163</v>
       </c>
       <c r="Q100" t="s">
-        <v>190</v>
+        <v>55</v>
       </c>
       <c r="R100" t="s">
         <v>1164</v>
@@ -12311,7 +12307,7 @@
         <v>1167</v>
       </c>
       <c r="C101" t="s">
-        <v>139</v>
+        <v>167</v>
       </c>
       <c r="D101" t="s">
         <v>1168</v>
@@ -12322,7 +12318,7 @@
       </c>
       <c r="G101"/>
       <c r="H101" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="I101" t="s">
         <v>1169</v>
@@ -12340,7 +12336,7 @@
         <v>1173</v>
       </c>
       <c r="N101" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O101" t="s">
         <v>1174</v>
@@ -12349,7 +12345,7 @@
         <v>1175</v>
       </c>
       <c r="Q101" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="R101"/>
       <c r="S101"/>
@@ -12367,22 +12363,22 @@
         <v>1176</v>
       </c>
       <c r="C102" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="D102" t="s">
-        <v>108</v>
+        <v>136</v>
       </c>
       <c r="E102" t="s">
-        <v>109</v>
+        <v>137</v>
       </c>
       <c r="F102" t="s">
         <v>1177</v>
       </c>
       <c r="G102" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H102" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="I102" t="s">
         <v>642</v>
@@ -12400,7 +12396,7 @@
         <v>1181</v>
       </c>
       <c r="N102" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O102" t="s">
         <v>1182</v>
@@ -12409,7 +12405,7 @@
         <v>1183</v>
       </c>
       <c r="Q102" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="R102" t="s">
         <v>649</v>
@@ -12433,22 +12429,22 @@
         <v>1184</v>
       </c>
       <c r="C103" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="D103" t="s">
         <v>1185</v>
       </c>
       <c r="E103" t="s">
-        <v>109</v>
+        <v>137</v>
       </c>
       <c r="F103" t="s">
         <v>1186</v>
       </c>
       <c r="G103" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H103" t="s">
-        <v>94</v>
+        <v>123</v>
       </c>
       <c r="I103" t="s">
         <v>1187</v>
@@ -12464,7 +12460,7 @@
         <v>1190</v>
       </c>
       <c r="N103" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O103" t="s">
         <v>1191</v>
@@ -12473,7 +12469,7 @@
         <v>1192</v>
       </c>
       <c r="Q103" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="R103" t="s">
         <v>1193</v>
@@ -12497,22 +12493,22 @@
         <v>1196</v>
       </c>
       <c r="C104" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="D104" t="s">
         <v>1197</v>
       </c>
       <c r="E104" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="F104" t="s">
         <v>1198</v>
       </c>
       <c r="G104" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H104" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="I104" t="s">
         <v>1199</v>
@@ -12528,7 +12524,7 @@
         <v>1202</v>
       </c>
       <c r="N104" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O104" t="s">
         <v>1203</v>
@@ -12537,7 +12533,7 @@
         <v>1204</v>
       </c>
       <c r="Q104" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="R104" t="s">
         <v>1082</v>
@@ -12565,14 +12561,14 @@
       </c>
       <c r="D105"/>
       <c r="E105" t="s">
-        <v>215</v>
+        <v>45</v>
       </c>
       <c r="F105" t="s">
         <v>1206</v>
       </c>
       <c r="G105"/>
       <c r="H105" t="s">
-        <v>94</v>
+        <v>123</v>
       </c>
       <c r="I105" t="s">
         <v>1207</v>
@@ -12586,7 +12582,7 @@
       <c r="L105"/>
       <c r="M105"/>
       <c r="N105" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O105" t="s">
         <v>1210</v>
@@ -12595,7 +12591,7 @@
         <v>1211</v>
       </c>
       <c r="Q105" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="R105" t="s">
         <v>1212</v>
@@ -12619,7 +12615,7 @@
         <v>1215</v>
       </c>
       <c r="C106" t="s">
-        <v>139</v>
+        <v>167</v>
       </c>
       <c r="D106" t="s">
         <v>1168</v>
@@ -12630,7 +12626,7 @@
       </c>
       <c r="G106"/>
       <c r="H106" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="I106" t="s">
         <v>1217</v>
@@ -12648,7 +12644,7 @@
         <v>1221</v>
       </c>
       <c r="N106" t="s">
-        <v>85</v>
+        <v>114</v>
       </c>
       <c r="O106" t="s">
         <v>1222</v>
@@ -12657,7 +12653,7 @@
         <v>1223</v>
       </c>
       <c r="Q106" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="R106" t="s">
         <v>1224</v>
@@ -12681,7 +12677,7 @@
         <v>1227</v>
       </c>
       <c r="C107" t="s">
-        <v>139</v>
+        <v>167</v>
       </c>
       <c r="D107" t="s">
         <v>1168</v>
@@ -12692,7 +12688,7 @@
       </c>
       <c r="G107"/>
       <c r="H107" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="I107" t="s">
         <v>1228</v>
@@ -12719,7 +12715,7 @@
         <v>1235</v>
       </c>
       <c r="Q107" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="R107" t="s">
         <v>1236</v>
@@ -12743,7 +12739,7 @@
         <v>1239</v>
       </c>
       <c r="C108" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="D108" t="s">
         <v>929</v>
@@ -12755,10 +12751,10 @@
         <v>1240</v>
       </c>
       <c r="G108" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H108" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="I108" t="s">
         <v>1241</v>
@@ -12776,7 +12772,7 @@
         <v>1245</v>
       </c>
       <c r="N108" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="O108" t="s">
         <v>1246</v>
@@ -12785,7 +12781,7 @@
         <v>1247</v>
       </c>
       <c r="Q108" t="s">
-        <v>190</v>
+        <v>55</v>
       </c>
       <c r="R108" t="s">
         <v>1248</v>
@@ -12809,19 +12805,19 @@
         <v>1251</v>
       </c>
       <c r="C109" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="D109" t="s">
         <v>1252</v>
       </c>
       <c r="E109" t="s">
-        <v>76</v>
+        <v>25</v>
       </c>
       <c r="F109" t="s">
         <v>1253</v>
       </c>
       <c r="G109" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H109" t="s">
         <v>255</v>
@@ -12842,7 +12838,7 @@
         <v>1258</v>
       </c>
       <c r="N109" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="O109" t="s">
         <v>1259</v>
@@ -12851,7 +12847,7 @@
         <v>1260</v>
       </c>
       <c r="Q109" t="s">
-        <v>190</v>
+        <v>55</v>
       </c>
       <c r="R109" t="s">
         <v>1261</v>
@@ -12875,22 +12871,22 @@
         <v>1264</v>
       </c>
       <c r="C110" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D110" t="s">
         <v>1265</v>
       </c>
       <c r="E110" t="s">
-        <v>109</v>
+        <v>137</v>
       </c>
       <c r="F110" t="s">
         <v>1253</v>
       </c>
       <c r="G110" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H110" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="I110" t="s">
         <v>1266</v>
@@ -12908,7 +12904,7 @@
         <v>1270</v>
       </c>
       <c r="N110" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O110" t="s">
         <v>1271</v>
@@ -12917,7 +12913,7 @@
         <v>1272</v>
       </c>
       <c r="Q110" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="R110" t="s">
         <v>905</v>
@@ -12941,22 +12937,22 @@
         <v>1273</v>
       </c>
       <c r="C111" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="D111" t="s">
         <v>1274</v>
       </c>
       <c r="E111" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="F111" t="s">
         <v>1253</v>
       </c>
       <c r="G111" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H111" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="I111" t="s">
         <v>1275</v>
@@ -12974,7 +12970,7 @@
         <v>1279</v>
       </c>
       <c r="N111" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O111" t="s">
         <v>1280</v>
@@ -13007,19 +13003,19 @@
         <v>1285</v>
       </c>
       <c r="C112" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D112" t="s">
         <v>1286</v>
       </c>
       <c r="E112" t="s">
-        <v>76</v>
+        <v>25</v>
       </c>
       <c r="F112" t="s">
         <v>1253</v>
       </c>
       <c r="G112" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H112" t="s">
         <v>255</v>
@@ -13040,7 +13036,7 @@
         <v>1291</v>
       </c>
       <c r="N112" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="O112" t="s">
         <v>1292</v>
@@ -13073,19 +13069,19 @@
         <v>1294</v>
       </c>
       <c r="C113" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="D113" t="s">
         <v>1295</v>
       </c>
       <c r="E113" t="s">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="F113" t="s">
         <v>1296</v>
       </c>
       <c r="G113" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H113" t="s">
         <v>255</v>
@@ -13106,7 +13102,7 @@
         <v>1301</v>
       </c>
       <c r="N113" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="O113" t="s">
         <v>1302</v>
@@ -13115,7 +13111,7 @@
         <v>1303</v>
       </c>
       <c r="Q113" t="s">
-        <v>190</v>
+        <v>55</v>
       </c>
       <c r="R113" t="s">
         <v>616</v>
@@ -13139,22 +13135,22 @@
         <v>1304</v>
       </c>
       <c r="C114" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="D114" t="s">
         <v>703</v>
       </c>
       <c r="E114" t="s">
-        <v>109</v>
+        <v>137</v>
       </c>
       <c r="F114" t="s">
         <v>1305</v>
       </c>
       <c r="G114" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H114" t="s">
-        <v>94</v>
+        <v>123</v>
       </c>
       <c r="I114" t="s">
         <v>1306</v>
@@ -13170,7 +13166,7 @@
         <v>1309</v>
       </c>
       <c r="N114" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O114" t="s">
         <v>1310</v>
@@ -13203,22 +13199,22 @@
         <v>1312</v>
       </c>
       <c r="C115" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D115" t="s">
         <v>254</v>
       </c>
       <c r="E115" t="s">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="F115" t="s">
         <v>1313</v>
       </c>
       <c r="G115" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H115" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="I115" t="s">
         <v>1314</v>
@@ -13236,7 +13232,7 @@
         <v>1318</v>
       </c>
       <c r="N115" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O115" t="s">
         <v>1319</v>
@@ -13248,13 +13244,13 @@
         <v>263</v>
       </c>
       <c r="R115" t="s">
-        <v>60</v>
+        <v>93</v>
       </c>
       <c r="S115" t="s">
-        <v>61</v>
+        <v>94</v>
       </c>
       <c r="T115" t="s">
-        <v>62</v>
+        <v>95</v>
       </c>
       <c r="U115" t="s">
         <v>496</v>
@@ -13269,22 +13265,22 @@
         <v>1321</v>
       </c>
       <c r="C116" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="D116" t="s">
         <v>1286</v>
       </c>
       <c r="E116" t="s">
-        <v>76</v>
+        <v>25</v>
       </c>
       <c r="F116" t="s">
         <v>1322</v>
       </c>
       <c r="G116" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H116" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="I116" t="s">
         <v>1323</v>
@@ -13300,7 +13296,7 @@
         <v>1326</v>
       </c>
       <c r="N116" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O116" t="s">
         <v>1327</v>
@@ -13309,16 +13305,16 @@
         <v>1328</v>
       </c>
       <c r="Q116" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="R116" t="s">
-        <v>115</v>
+        <v>143</v>
       </c>
       <c r="S116" t="s">
-        <v>116</v>
+        <v>144</v>
       </c>
       <c r="T116" t="s">
-        <v>117</v>
+        <v>145</v>
       </c>
       <c r="U116" t="s">
         <v>496</v>
@@ -13333,22 +13329,22 @@
         <v>1329</v>
       </c>
       <c r="C117" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="D117" t="s">
         <v>703</v>
       </c>
       <c r="E117" t="s">
-        <v>109</v>
+        <v>137</v>
       </c>
       <c r="F117" t="s">
         <v>1322</v>
       </c>
       <c r="G117" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H117" t="s">
-        <v>94</v>
+        <v>123</v>
       </c>
       <c r="I117" t="s">
         <v>1330</v>
@@ -13364,7 +13360,7 @@
         <v>1333</v>
       </c>
       <c r="N117" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O117" t="s">
         <v>1334</v>
@@ -13397,22 +13393,22 @@
         <v>1336</v>
       </c>
       <c r="C118" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="D118" t="s">
         <v>703</v>
       </c>
       <c r="E118" t="s">
-        <v>109</v>
+        <v>137</v>
       </c>
       <c r="F118" t="s">
         <v>1322</v>
       </c>
       <c r="G118" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H118" t="s">
-        <v>94</v>
+        <v>123</v>
       </c>
       <c r="I118" t="s">
         <v>1330</v>
@@ -13428,7 +13424,7 @@
         <v>1338</v>
       </c>
       <c r="N118" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O118" t="s">
         <v>1339</v>
@@ -13461,22 +13457,22 @@
         <v>1341</v>
       </c>
       <c r="C119" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="D119" t="s">
         <v>703</v>
       </c>
       <c r="E119" t="s">
-        <v>109</v>
+        <v>137</v>
       </c>
       <c r="F119" t="s">
         <v>1322</v>
       </c>
       <c r="G119" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H119" t="s">
-        <v>94</v>
+        <v>123</v>
       </c>
       <c r="I119" t="s">
         <v>1330</v>
@@ -13492,7 +13488,7 @@
         <v>1343</v>
       </c>
       <c r="N119" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O119" t="s">
         <v>1344</v>
@@ -13525,22 +13521,22 @@
         <v>1346</v>
       </c>
       <c r="C120" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D120" t="s">
         <v>781</v>
       </c>
       <c r="E120" t="s">
-        <v>109</v>
+        <v>137</v>
       </c>
       <c r="F120" t="s">
         <v>1347</v>
       </c>
       <c r="G120" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H120" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="I120" t="s">
         <v>1348</v>
@@ -13558,7 +13554,7 @@
         <v>1352</v>
       </c>
       <c r="N120" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="O120" t="s">
         <v>1353</v>
@@ -13567,7 +13563,7 @@
         <v>1354</v>
       </c>
       <c r="Q120" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="R120" t="s">
         <v>1355</v>
@@ -13591,22 +13587,22 @@
         <v>1358</v>
       </c>
       <c r="C121" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D121" t="s">
         <v>839</v>
       </c>
       <c r="E121" t="s">
-        <v>76</v>
+        <v>25</v>
       </c>
       <c r="F121" t="s">
         <v>1359</v>
       </c>
       <c r="G121" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H121" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="I121" t="s">
         <v>1360</v>
@@ -13624,7 +13620,7 @@
         <v>1364</v>
       </c>
       <c r="N121" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O121" t="s">
         <v>1365</v>
@@ -13633,7 +13629,7 @@
         <v>1366</v>
       </c>
       <c r="Q121" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="R121" t="s">
         <v>426</v>
@@ -13657,22 +13653,22 @@
         <v>1367</v>
       </c>
       <c r="C122" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D122" t="s">
         <v>1368</v>
       </c>
       <c r="E122" t="s">
-        <v>109</v>
+        <v>137</v>
       </c>
       <c r="F122" t="s">
         <v>1359</v>
       </c>
       <c r="G122" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H122" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="I122" t="s">
         <v>1369</v>
@@ -13690,7 +13686,7 @@
         <v>1373</v>
       </c>
       <c r="N122" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="O122" t="s">
         <v>1374</v>
@@ -13699,7 +13695,7 @@
         <v>1375</v>
       </c>
       <c r="Q122" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="R122" t="s">
         <v>1376</v>
@@ -13723,22 +13719,22 @@
         <v>1379</v>
       </c>
       <c r="C123" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D123" t="s">
         <v>1380</v>
       </c>
       <c r="E123" t="s">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="F123" t="s">
         <v>1359</v>
       </c>
       <c r="G123" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H123" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="I123" t="s">
         <v>1381</v>
@@ -13756,7 +13752,7 @@
         <v>1385</v>
       </c>
       <c r="N123" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="O123" t="s">
         <v>1386</v>
@@ -13765,7 +13761,7 @@
         <v>1387</v>
       </c>
       <c r="Q123" t="s">
-        <v>190</v>
+        <v>55</v>
       </c>
       <c r="R123" t="s">
         <v>1388</v>
@@ -13789,7 +13785,7 @@
         <v>1391</v>
       </c>
       <c r="C124" t="s">
-        <v>139</v>
+        <v>167</v>
       </c>
       <c r="D124" t="s">
         <v>1168</v>
@@ -13800,7 +13796,7 @@
       </c>
       <c r="G124"/>
       <c r="H124" t="s">
-        <v>142</v>
+        <v>170</v>
       </c>
       <c r="I124" t="s">
         <v>1393</v>
@@ -13818,7 +13814,7 @@
         <v>1397</v>
       </c>
       <c r="N124" t="s">
-        <v>85</v>
+        <v>114</v>
       </c>
       <c r="O124" t="s">
         <v>1398</v>
@@ -13827,16 +13823,16 @@
         <v>1399</v>
       </c>
       <c r="Q124" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="R124" t="s">
-        <v>71</v>
+        <v>103</v>
       </c>
       <c r="S124" t="s">
-        <v>72</v>
+        <v>104</v>
       </c>
       <c r="T124" t="s">
-        <v>73</v>
+        <v>105</v>
       </c>
       <c r="U124" t="s">
         <v>496</v>
@@ -13851,19 +13847,19 @@
         <v>1400</v>
       </c>
       <c r="C125" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="D125" t="s">
         <v>681</v>
       </c>
       <c r="E125" t="s">
-        <v>76</v>
+        <v>25</v>
       </c>
       <c r="F125" t="s">
         <v>1392</v>
       </c>
       <c r="G125" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H125" t="s">
         <v>255</v>
@@ -13884,7 +13880,7 @@
         <v>1405</v>
       </c>
       <c r="N125" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="O125" t="s">
         <v>1406</v>
@@ -13893,7 +13889,7 @@
         <v>1407</v>
       </c>
       <c r="Q125" t="s">
-        <v>190</v>
+        <v>55</v>
       </c>
       <c r="R125" t="s">
         <v>1408</v>
@@ -13917,22 +13913,22 @@
         <v>1411</v>
       </c>
       <c r="C126" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="D126" t="s">
         <v>1412</v>
       </c>
       <c r="E126" t="s">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="F126" t="s">
         <v>1392</v>
       </c>
       <c r="G126" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H126" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="I126" t="s">
         <v>1413</v>
@@ -13950,7 +13946,7 @@
         <v>1417</v>
       </c>
       <c r="N126" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="O126" t="s">
         <v>1418</v>
@@ -13959,7 +13955,7 @@
         <v>1419</v>
       </c>
       <c r="Q126" t="s">
-        <v>190</v>
+        <v>55</v>
       </c>
       <c r="R126" t="s">
         <v>1420</v>
@@ -13983,22 +13979,22 @@
         <v>1423</v>
       </c>
       <c r="C127" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D127" t="s">
         <v>1424</v>
       </c>
       <c r="E127" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="F127" t="s">
         <v>1392</v>
       </c>
       <c r="G127" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H127" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="I127" t="s">
         <v>1425</v>
@@ -14016,7 +14012,7 @@
         <v>1429</v>
       </c>
       <c r="N127" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O127" t="s">
         <v>1430</v>
@@ -14049,22 +14045,22 @@
         <v>1432</v>
       </c>
       <c r="C128" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="D128" t="s">
         <v>827</v>
       </c>
       <c r="E128" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="F128" t="s">
         <v>1392</v>
       </c>
       <c r="G128" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H128" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="I128" t="s">
         <v>1433</v>
@@ -14082,7 +14078,7 @@
         <v>1437</v>
       </c>
       <c r="N128" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="O128" t="s">
         <v>1438</v>
@@ -14091,7 +14087,7 @@
         <v>1439</v>
       </c>
       <c r="Q128" t="s">
-        <v>190</v>
+        <v>55</v>
       </c>
       <c r="R128" t="s">
         <v>1440</v>
@@ -14115,22 +14111,22 @@
         <v>1443</v>
       </c>
       <c r="C129" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="D129" t="s">
         <v>781</v>
       </c>
       <c r="E129" t="s">
-        <v>109</v>
+        <v>137</v>
       </c>
       <c r="F129" t="s">
         <v>1392</v>
       </c>
       <c r="G129" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H129" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="I129" t="s">
         <v>1444</v>
@@ -14157,7 +14153,7 @@
         <v>1451</v>
       </c>
       <c r="Q129" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="R129" t="s">
         <v>1452</v>
@@ -14181,22 +14177,22 @@
         <v>1455</v>
       </c>
       <c r="C130" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D130" t="s">
-        <v>108</v>
+        <v>136</v>
       </c>
       <c r="E130" t="s">
-        <v>109</v>
+        <v>137</v>
       </c>
       <c r="F130" t="s">
         <v>1456</v>
       </c>
       <c r="G130" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H130" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="I130" t="s">
         <v>1457</v>
@@ -14214,7 +14210,7 @@
         <v>1461</v>
       </c>
       <c r="N130" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O130" t="s">
         <v>1462</v>
@@ -14223,16 +14219,16 @@
         <v>1463</v>
       </c>
       <c r="Q130" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="R130" t="s">
-        <v>60</v>
+        <v>93</v>
       </c>
       <c r="S130" t="s">
-        <v>61</v>
+        <v>94</v>
       </c>
       <c r="T130" t="s">
-        <v>62</v>
+        <v>95</v>
       </c>
       <c r="U130" t="s">
         <v>496</v>
@@ -14247,22 +14243,22 @@
         <v>1464</v>
       </c>
       <c r="C131" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="D131" t="s">
         <v>653</v>
       </c>
       <c r="E131" t="s">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="F131" t="s">
         <v>1465</v>
       </c>
       <c r="G131" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H131" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="I131" t="s">
         <v>1466</v>
@@ -14280,7 +14276,7 @@
         <v>1470</v>
       </c>
       <c r="N131" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O131" t="s">
         <v>1471</v>
@@ -14313,22 +14309,22 @@
         <v>1473</v>
       </c>
       <c r="C132" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="D132" t="s">
         <v>1474</v>
       </c>
       <c r="E132" t="s">
-        <v>109</v>
+        <v>137</v>
       </c>
       <c r="F132" t="s">
         <v>1475</v>
       </c>
       <c r="G132" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H132" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="I132" t="s">
         <v>1476</v>
@@ -14344,7 +14340,7 @@
         <v>1479</v>
       </c>
       <c r="N132" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O132" t="s">
         <v>1480</v>
@@ -14353,7 +14349,7 @@
         <v>1481</v>
       </c>
       <c r="Q132" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="R132" t="s">
         <v>950</v>
@@ -14377,22 +14373,22 @@
         <v>1482</v>
       </c>
       <c r="C133" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="D133" t="s">
         <v>1483</v>
       </c>
       <c r="E133" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="F133" t="s">
         <v>1475</v>
       </c>
       <c r="G133" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H133" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="I133" t="s">
         <v>1484</v>
@@ -14408,7 +14404,7 @@
         <v>1487</v>
       </c>
       <c r="N133" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O133" t="s">
         <v>1488</v>
@@ -14417,16 +14413,16 @@
         <v>1489</v>
       </c>
       <c r="Q133" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="R133" t="s">
-        <v>125</v>
+        <v>153</v>
       </c>
       <c r="S133" t="s">
-        <v>126</v>
+        <v>154</v>
       </c>
       <c r="T133" t="s">
-        <v>127</v>
+        <v>155</v>
       </c>
       <c r="U133" t="s">
         <v>496</v>
@@ -14447,16 +14443,16 @@
         <v>409</v>
       </c>
       <c r="E134" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="F134" t="s">
         <v>1491</v>
       </c>
       <c r="G134" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H134" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="I134" t="s">
         <v>1492</v>
@@ -14474,7 +14470,7 @@
         <v>1496</v>
       </c>
       <c r="N134" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="O134" t="s">
         <v>1497</v>
@@ -14511,14 +14507,14 @@
       </c>
       <c r="D135"/>
       <c r="E135" t="s">
-        <v>215</v>
+        <v>45</v>
       </c>
       <c r="F135" t="s">
         <v>1500</v>
       </c>
       <c r="G135"/>
       <c r="H135" t="s">
-        <v>94</v>
+        <v>123</v>
       </c>
       <c r="I135" t="s">
         <v>1501</v>
@@ -14532,7 +14528,7 @@
       <c r="L135"/>
       <c r="M135"/>
       <c r="N135" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O135" t="s">
         <v>1504</v>
@@ -14541,7 +14537,7 @@
         <v>1505</v>
       </c>
       <c r="Q135" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="R135" t="s">
         <v>1506</v>
@@ -14565,7 +14561,7 @@
         <v>1509</v>
       </c>
       <c r="C136" t="s">
-        <v>139</v>
+        <v>167</v>
       </c>
       <c r="D136" t="s">
         <v>1168</v>
@@ -14576,7 +14572,7 @@
       </c>
       <c r="G136"/>
       <c r="H136" t="s">
-        <v>94</v>
+        <v>123</v>
       </c>
       <c r="I136" t="s">
         <v>1511</v>
@@ -14603,7 +14599,7 @@
         <v>1517</v>
       </c>
       <c r="Q136" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="R136" t="s">
         <v>1518</v>
@@ -14627,22 +14623,22 @@
         <v>1521</v>
       </c>
       <c r="C137" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D137" t="s">
         <v>1522</v>
       </c>
       <c r="E137" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="F137" t="s">
         <v>1523</v>
       </c>
       <c r="G137" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H137" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="I137" t="s">
         <v>1524</v>
@@ -14660,7 +14656,7 @@
         <v>1528</v>
       </c>
       <c r="N137" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O137" t="s">
         <v>1529</v>
@@ -14693,22 +14689,22 @@
         <v>1534</v>
       </c>
       <c r="C138" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D138" t="s">
         <v>1535</v>
       </c>
       <c r="E138" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="F138" t="s">
         <v>1536</v>
       </c>
       <c r="G138" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H138" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="I138" t="s">
         <v>1537</v>
@@ -14726,7 +14722,7 @@
         <v>1541</v>
       </c>
       <c r="N138" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O138" t="s">
         <v>1542</v>
@@ -14759,22 +14755,22 @@
         <v>1547</v>
       </c>
       <c r="C139" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D139" t="s">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="E139" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="F139" t="s">
         <v>1536</v>
       </c>
       <c r="G139" t="s">
-        <v>78</v>
+        <v>27</v>
       </c>
       <c r="H139" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="I139" t="s">
         <v>1548</v>
@@ -14792,7 +14788,7 @@
         <v>1552</v>
       </c>
       <c r="N139" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O139" t="s">
         <v>1553</v>
@@ -14801,7 +14797,7 @@
         <v>1554</v>
       </c>
       <c r="Q139" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="R139" t="s">
         <v>905</v>
@@ -14831,16 +14827,16 @@
         <v>587</v>
       </c>
       <c r="E140" t="s">
-        <v>76</v>
+        <v>25</v>
       </c>
       <c r="F140" t="s">
         <v>1556</v>
       </c>
       <c r="G140" t="s">
-        <v>78</v>
+        <v>27</v>
       </c>
       <c r="H140" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="I140" t="s">
         <v>1557</v>
@@ -14867,16 +14863,16 @@
         <v>1563</v>
       </c>
       <c r="Q140" t="s">
-        <v>190</v>
+        <v>55</v>
       </c>
       <c r="R140" t="s">
-        <v>71</v>
+        <v>103</v>
       </c>
       <c r="S140" t="s">
-        <v>72</v>
+        <v>104</v>
       </c>
       <c r="T140" t="s">
-        <v>73</v>
+        <v>105</v>
       </c>
       <c r="U140" t="s">
         <v>496</v>
@@ -14891,22 +14887,22 @@
         <v>1564</v>
       </c>
       <c r="C141" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="D141" t="s">
         <v>1565</v>
       </c>
       <c r="E141" t="s">
-        <v>76</v>
+        <v>25</v>
       </c>
       <c r="F141" t="s">
         <v>1556</v>
       </c>
       <c r="G141" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H141" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="I141" t="s">
         <v>1566</v>
@@ -14924,7 +14920,7 @@
         <v>1570</v>
       </c>
       <c r="N141" t="s">
-        <v>148</v>
+        <v>176</v>
       </c>
       <c r="O141" t="s">
         <v>1571</v>
@@ -14957,7 +14953,7 @@
         <v>1576</v>
       </c>
       <c r="C142" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="D142" t="s">
         <v>1577</v>
@@ -14969,7 +14965,7 @@
         <v>1556</v>
       </c>
       <c r="G142" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H142" t="s">
         <v>255</v>
@@ -14990,7 +14986,7 @@
         <v>1583</v>
       </c>
       <c r="N142" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O142" t="s">
         <v>1584</v>
@@ -14999,7 +14995,7 @@
         <v>1585</v>
       </c>
       <c r="Q142" t="s">
-        <v>190</v>
+        <v>55</v>
       </c>
       <c r="R142" t="s">
         <v>1586</v>
@@ -15023,22 +15019,22 @@
         <v>1589</v>
       </c>
       <c r="C143" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D143" t="s">
         <v>552</v>
       </c>
       <c r="E143" t="s">
-        <v>109</v>
+        <v>137</v>
       </c>
       <c r="F143" t="s">
         <v>1556</v>
       </c>
       <c r="G143" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H143" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="I143" t="s">
         <v>1590</v>
@@ -15056,7 +15052,7 @@
         <v>1594</v>
       </c>
       <c r="N143" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O143" t="s">
         <v>1595</v>
@@ -15065,7 +15061,7 @@
         <v>1596</v>
       </c>
       <c r="Q143" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="R143" t="s">
         <v>1597</v>
@@ -15089,22 +15085,22 @@
         <v>1600</v>
       </c>
       <c r="C144" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D144" t="s">
         <v>1565</v>
       </c>
       <c r="E144" t="s">
-        <v>76</v>
+        <v>25</v>
       </c>
       <c r="F144" t="s">
         <v>1556</v>
       </c>
       <c r="G144" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H144" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="I144" t="s">
         <v>1601</v>
@@ -15122,7 +15118,7 @@
         <v>1605</v>
       </c>
       <c r="N144" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O144" t="s">
         <v>1606</v>
@@ -15131,7 +15127,7 @@
         <v>1607</v>
       </c>
       <c r="Q144" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="R144" t="s">
         <v>1608</v>
@@ -15155,22 +15151,22 @@
         <v>1611</v>
       </c>
       <c r="C145" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D145" t="s">
         <v>1274</v>
       </c>
       <c r="E145" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="F145" t="s">
         <v>1556</v>
       </c>
       <c r="G145" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H145" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="I145" t="s">
         <v>1612</v>
@@ -15188,7 +15184,7 @@
         <v>1616</v>
       </c>
       <c r="N145" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O145" t="s">
         <v>1617</v>
@@ -15197,7 +15193,7 @@
         <v>1618</v>
       </c>
       <c r="Q145" t="s">
-        <v>190</v>
+        <v>55</v>
       </c>
       <c r="R145" t="s">
         <v>1619</v>
@@ -15221,22 +15217,22 @@
         <v>1622</v>
       </c>
       <c r="C146" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D146" t="s">
         <v>1623</v>
       </c>
       <c r="E146" t="s">
-        <v>76</v>
+        <v>25</v>
       </c>
       <c r="F146" t="s">
         <v>1624</v>
       </c>
       <c r="G146" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H146" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="I146" t="s">
         <v>1625</v>
@@ -15254,7 +15250,7 @@
         <v>1629</v>
       </c>
       <c r="N146" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O146" t="s">
         <v>1630</v>
@@ -15263,7 +15259,7 @@
         <v>1631</v>
       </c>
       <c r="Q146" t="s">
-        <v>190</v>
+        <v>55</v>
       </c>
       <c r="R146" t="s">
         <v>950</v>
@@ -15287,22 +15283,22 @@
         <v>1632</v>
       </c>
       <c r="C147" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D147" t="s">
         <v>453</v>
       </c>
       <c r="E147" t="s">
-        <v>109</v>
+        <v>137</v>
       </c>
       <c r="F147" t="s">
         <v>1633</v>
       </c>
       <c r="G147" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H147" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="I147" t="s">
         <v>1634</v>
@@ -15320,7 +15316,7 @@
         <v>1638</v>
       </c>
       <c r="N147" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O147" t="s">
         <v>1639</v>
@@ -15329,7 +15325,7 @@
         <v>1640</v>
       </c>
       <c r="Q147" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="R147" t="s">
         <v>548</v>
@@ -15353,22 +15349,22 @@
         <v>1641</v>
       </c>
       <c r="C148" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D148" t="s">
         <v>1642</v>
       </c>
       <c r="E148" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="F148" t="s">
         <v>1643</v>
       </c>
       <c r="G148" t="s">
-        <v>78</v>
+        <v>27</v>
       </c>
       <c r="H148" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="I148" t="s">
         <v>1644</v>
@@ -15386,7 +15382,7 @@
         <v>1648</v>
       </c>
       <c r="N148" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O148" t="s">
         <v>1649</v>
@@ -15395,7 +15391,7 @@
         <v>1650</v>
       </c>
       <c r="Q148" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="R148" t="s">
         <v>872</v>
@@ -15425,16 +15421,16 @@
         <v>1652</v>
       </c>
       <c r="E149" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="F149" t="s">
         <v>1653</v>
       </c>
       <c r="G149" t="s">
-        <v>78</v>
+        <v>27</v>
       </c>
       <c r="H149" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="I149" t="s">
         <v>1654</v>
@@ -15461,7 +15457,7 @@
         <v>1660</v>
       </c>
       <c r="Q149" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="R149" t="s">
         <v>1420</v>
@@ -15485,22 +15481,22 @@
         <v>1661</v>
       </c>
       <c r="C150" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="D150" t="s">
         <v>781</v>
       </c>
       <c r="E150" t="s">
-        <v>109</v>
+        <v>137</v>
       </c>
       <c r="F150" t="s">
         <v>1653</v>
       </c>
       <c r="G150" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H150" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="I150" t="s">
         <v>1662</v>
@@ -15516,7 +15512,7 @@
         <v>1665</v>
       </c>
       <c r="N150" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O150" t="s">
         <v>1666</v>
@@ -15528,13 +15524,13 @@
         <v>263</v>
       </c>
       <c r="R150" t="s">
-        <v>60</v>
+        <v>93</v>
       </c>
       <c r="S150" t="s">
-        <v>61</v>
+        <v>94</v>
       </c>
       <c r="T150" t="s">
-        <v>62</v>
+        <v>95</v>
       </c>
       <c r="U150" t="s">
         <v>496</v>
@@ -15549,22 +15545,22 @@
         <v>1668</v>
       </c>
       <c r="C151" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="D151" t="s">
         <v>409</v>
       </c>
       <c r="E151" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="F151" t="s">
         <v>1669</v>
       </c>
       <c r="G151" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H151" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="I151" t="s">
         <v>1670</v>
@@ -15580,7 +15576,7 @@
         <v>1673</v>
       </c>
       <c r="N151" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O151" t="s">
         <v>1674</v>
@@ -15589,16 +15585,16 @@
         <v>1675</v>
       </c>
       <c r="Q151" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="R151" t="s">
-        <v>60</v>
+        <v>93</v>
       </c>
       <c r="S151" t="s">
-        <v>61</v>
+        <v>94</v>
       </c>
       <c r="T151" t="s">
-        <v>62</v>
+        <v>95</v>
       </c>
       <c r="U151" t="s">
         <v>496</v>
@@ -15613,7 +15609,7 @@
         <v>1676</v>
       </c>
       <c r="C152" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="D152" t="s">
         <v>1677</v>
@@ -15623,10 +15619,10 @@
         <v>1678</v>
       </c>
       <c r="G152" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H152" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="I152" t="s">
         <v>1679</v>
@@ -15677,22 +15673,22 @@
         <v>1689</v>
       </c>
       <c r="C153" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D153" t="s">
         <v>990</v>
       </c>
       <c r="E153" t="s">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="F153" t="s">
         <v>1690</v>
       </c>
       <c r="G153" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H153" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="I153" t="s">
         <v>1691</v>
@@ -15710,7 +15706,7 @@
         <v>1695</v>
       </c>
       <c r="N153" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O153" t="s">
         <v>1696</v>
@@ -15719,7 +15715,7 @@
         <v>1697</v>
       </c>
       <c r="Q153" t="s">
-        <v>190</v>
+        <v>55</v>
       </c>
       <c r="R153" t="s">
         <v>1698</v>
@@ -15743,22 +15739,22 @@
         <v>1701</v>
       </c>
       <c r="C154" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="D154" t="s">
         <v>814</v>
       </c>
       <c r="E154" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="F154" t="s">
         <v>1690</v>
       </c>
       <c r="G154" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H154" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="I154" t="s">
         <v>1702</v>
@@ -15776,7 +15772,7 @@
         <v>1706</v>
       </c>
       <c r="N154" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O154" t="s">
         <v>1707</v>
@@ -15785,7 +15781,7 @@
         <v>1708</v>
       </c>
       <c r="Q154" t="s">
-        <v>190</v>
+        <v>55</v>
       </c>
       <c r="R154" t="s">
         <v>1709</v>
@@ -15809,19 +15805,19 @@
         <v>1712</v>
       </c>
       <c r="C155" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="D155" t="s">
         <v>1713</v>
       </c>
       <c r="E155" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="F155" t="s">
         <v>1714</v>
       </c>
       <c r="G155" t="s">
-        <v>78</v>
+        <v>27</v>
       </c>
       <c r="H155" t="s">
         <v>966</v>
@@ -15842,7 +15838,7 @@
         <v>1719</v>
       </c>
       <c r="N155" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O155" t="s">
         <v>1720</v>
@@ -15851,7 +15847,7 @@
         <v>1721</v>
       </c>
       <c r="Q155" t="s">
-        <v>190</v>
+        <v>55</v>
       </c>
       <c r="R155" t="s">
         <v>1722</v>
@@ -15875,19 +15871,19 @@
         <v>1725</v>
       </c>
       <c r="C156" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="D156" t="s">
         <v>1120</v>
       </c>
       <c r="E156" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="F156" t="s">
         <v>1714</v>
       </c>
       <c r="G156" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H156" t="s">
         <v>966</v>
@@ -15908,7 +15904,7 @@
         <v>1719</v>
       </c>
       <c r="N156" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O156" t="s">
         <v>1726</v>
@@ -15917,7 +15913,7 @@
         <v>1727</v>
       </c>
       <c r="Q156" t="s">
-        <v>190</v>
+        <v>55</v>
       </c>
       <c r="R156" t="s">
         <v>1728</v>
@@ -15941,7 +15937,7 @@
         <v>1731</v>
       </c>
       <c r="C157" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D157" t="s">
         <v>1732</v>
@@ -15953,7 +15949,7 @@
         <v>1733</v>
       </c>
       <c r="G157" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H157" t="s">
         <v>255</v>
@@ -15974,7 +15970,7 @@
         <v>1738</v>
       </c>
       <c r="N157" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O157" t="s">
         <v>1739</v>
@@ -15983,16 +15979,16 @@
         <v>1740</v>
       </c>
       <c r="Q157" t="s">
-        <v>190</v>
+        <v>55</v>
       </c>
       <c r="R157" t="s">
-        <v>115</v>
+        <v>143</v>
       </c>
       <c r="S157" t="s">
-        <v>116</v>
+        <v>144</v>
       </c>
       <c r="T157" t="s">
-        <v>117</v>
+        <v>145</v>
       </c>
       <c r="U157" t="s">
         <v>496</v>
@@ -16007,22 +16003,22 @@
         <v>1741</v>
       </c>
       <c r="C158" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D158" t="s">
-        <v>75</v>
+        <v>24</v>
       </c>
       <c r="E158" t="s">
-        <v>76</v>
+        <v>25</v>
       </c>
       <c r="F158" t="s">
         <v>1742</v>
       </c>
       <c r="G158" t="s">
-        <v>78</v>
+        <v>27</v>
       </c>
       <c r="H158" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="I158" t="s">
         <v>1743</v>
@@ -16040,7 +16036,7 @@
         <v>1747</v>
       </c>
       <c r="N158" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O158" t="s">
         <v>1748</v>
@@ -16049,7 +16045,7 @@
         <v>1749</v>
       </c>
       <c r="Q158" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="R158" t="s">
         <v>1750</v>
@@ -16073,22 +16069,22 @@
         <v>1753</v>
       </c>
       <c r="C159" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D159" t="s">
         <v>781</v>
       </c>
       <c r="E159" t="s">
-        <v>109</v>
+        <v>137</v>
       </c>
       <c r="F159" t="s">
         <v>1754</v>
       </c>
       <c r="G159" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H159" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="I159" t="s">
         <v>1755</v>
@@ -16106,7 +16102,7 @@
         <v>1759</v>
       </c>
       <c r="N159" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O159" t="s">
         <v>1760</v>
@@ -16115,7 +16111,7 @@
         <v>1761</v>
       </c>
       <c r="Q159" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="R159" t="s">
         <v>1762</v>
@@ -16139,22 +16135,22 @@
         <v>1765</v>
       </c>
       <c r="C160" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="D160" t="s">
         <v>1766</v>
       </c>
       <c r="E160" t="s">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="F160" t="s">
         <v>1754</v>
       </c>
       <c r="G160" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H160" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="I160" t="s">
         <v>1767</v>
@@ -16170,7 +16166,7 @@
         <v>1770</v>
       </c>
       <c r="N160" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O160" t="s">
         <v>1771</v>
@@ -16179,7 +16175,7 @@
         <v>1772</v>
       </c>
       <c r="Q160" t="s">
-        <v>190</v>
+        <v>55</v>
       </c>
       <c r="R160" t="s">
         <v>1762</v>
@@ -16203,22 +16199,22 @@
         <v>1773</v>
       </c>
       <c r="C161" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="D161" t="s">
         <v>1766</v>
       </c>
       <c r="E161" t="s">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="F161" t="s">
         <v>1754</v>
       </c>
       <c r="G161" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H161" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="I161" t="s">
         <v>1774</v>
@@ -16234,7 +16230,7 @@
         <v>1777</v>
       </c>
       <c r="N161" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O161" t="s">
         <v>1778</v>
@@ -16267,7 +16263,7 @@
         <v>1780</v>
       </c>
       <c r="C162" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="D162" t="s">
         <v>1781</v>
@@ -16279,10 +16275,10 @@
         <v>1782</v>
       </c>
       <c r="G162" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H162" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="I162" t="s">
         <v>1783</v>
@@ -16298,7 +16294,7 @@
         <v>1786</v>
       </c>
       <c r="N162" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O162" t="s">
         <v>1787</v>
@@ -16310,13 +16306,13 @@
         <v>263</v>
       </c>
       <c r="R162" t="s">
-        <v>115</v>
+        <v>143</v>
       </c>
       <c r="S162" t="s">
-        <v>116</v>
+        <v>144</v>
       </c>
       <c r="T162" t="s">
-        <v>117</v>
+        <v>145</v>
       </c>
       <c r="U162" t="s">
         <v>496</v>
@@ -16331,22 +16327,22 @@
         <v>1789</v>
       </c>
       <c r="C163" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="D163" t="s">
         <v>1565</v>
       </c>
       <c r="E163" t="s">
-        <v>76</v>
+        <v>25</v>
       </c>
       <c r="F163" t="s">
         <v>1790</v>
       </c>
       <c r="G163" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H163" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="I163" t="s">
         <v>1791</v>
@@ -16362,7 +16358,7 @@
         <v>1794</v>
       </c>
       <c r="N163" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O163" t="s">
         <v>1795</v>
@@ -16371,7 +16367,7 @@
         <v>1796</v>
       </c>
       <c r="Q163" t="s">
-        <v>190</v>
+        <v>55</v>
       </c>
       <c r="R163" t="s">
         <v>1797</v>
@@ -16395,7 +16391,7 @@
         <v>1800</v>
       </c>
       <c r="C164" t="s">
-        <v>139</v>
+        <v>167</v>
       </c>
       <c r="D164" t="s">
         <v>1168</v>
@@ -16424,7 +16420,7 @@
         <v>1806</v>
       </c>
       <c r="N164" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O164" t="s">
         <v>1807</v>
@@ -16433,7 +16429,7 @@
         <v>1808</v>
       </c>
       <c r="Q164" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="R164" t="s">
         <v>1809</v>

--- a/Objets_parlementaires_Jura.xlsx
+++ b/Objets_parlementaires_Jura.xlsx
@@ -80,6 +80,63 @@
     <t xml:space="preserve">Statut_Change_Date</t>
   </si>
   <si>
+    <t xml:space="preserve">26.7901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fra.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dobler Loïc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WBF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mercosur: Wie sollen die 517 Millionen für die Landwirtschaft finanziert werden?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mercosur : comment financer les 517 millions pour l'agriculture ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Les Chambres fédérales ont validé l'accord avec le Mercosur, convaincues par une enveloppe de 517 millions de francs pour l'agriculture entre 2028 et 2033. Reste une question laissée dans l'ombre du débat : ce demi-milliard n'est financé par aucune source identifiée.&lt;br&gt;Le Conseil fédéral peut-il indiquer dès aujourd'hui où seront trouvées ces montants, et quels postes du budget fédéral seront concernés ?&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Die eidgenössischen Räte haben das Mercosur-Abkommen genehmigt, überzeugt durch zusätzliche Mittel in Höhe von 517&amp;nbsp;Millionen&amp;nbsp;Franken für die Landwirtschaft für die Jahre&amp;nbsp;2028 bis 2033. Ein Detail verblieb jedoch in der Debatte ungeklärt: Für die halbe Milliarde besteht bislang keine konkrete Finanzierungsquelle.&lt;br&gt;Kann der Bundesrat bereits jetzt angeben, woher die erwähnten Mittel stammen sollen und welche Positionen des Bundeshaushalts betroffen sein werden?&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Erledigt / Liquidé</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20267901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20267901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Titre uniquement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Internationale Politik|Finanzwesen|Landwirtschaft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politique internationale|Finances|Agriculture</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politica internazionale|Finanze|Agricoltura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-28</t>
+  </si>
+  <si>
     <t xml:space="preserve">26.4261</t>
   </si>
   <si>
@@ -119,9 +176,6 @@
     <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20264261</t>
   </si>
   <si>
-    <t xml:space="preserve">Titre uniquement</t>
-  </si>
-  <si>
     <t xml:space="preserve">Staatspolitik|Sozialer Schutz|Gesundheit</t>
   </si>
   <si>
@@ -155,9 +209,6 @@
     <t xml:space="preserve">&lt;p&gt;Der Bund steht vor erheblichen finanziellen Herausforderungen, für welche die heutigen Finanzierungsquellen offenkundig nicht ausreichen. Zu diesen Finanzierungsquellen gehören insbesondere Steuern, Abgaben und die Mehrwertsteuer. Diese reichen jedoch nicht mehr aus, um die Finanzierung grosser Ausgabenposten von nationaler Bedeutung sicherzustellen. Hierzu zählen insbesondere die AHV, die Verkehrsinfrastruktur, die Sicherheit des Landes (insbesondere die Armee) sowie die Prävention von Naturgefahren im Zusammenhang mit dem Klimawandel (eine gemeinsam mit den Kantonen und Gemeinden wahrgenommene Aufgabe). Meine Fragen betreffen die Einführung eines (auf zehn Jahre) befristeten Solidaritätsbeitrags für die «grossen Ausgabenposten» der drei politischen Ebenen der Schweiz.&amp;nbsp;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Ich bitte den Bundesrat, die folgenden Fragen zu beantworten:&lt;/p&gt;&lt;p&gt;1. Hat der Bundesrat bereits Überlegungen zu neuen Finanzierungsquellen angestellt, und wenn ja, welche?&lt;/p&gt;&lt;p&gt;2. Ausgehend davon, dass jährlich rund 5560&amp;nbsp;Millionen Finanzströme (und nicht Finanztransaktionen) mit einem Gesamtvolumen von rund 17&amp;nbsp;530&amp;nbsp;Milliarden Franken (2025) abgewickelt werden, könnte eine Abgabe von 1&amp;nbsp;Promille auf diesen Finanzströmen jährliche Einnahmen von rund 17,5&amp;nbsp;Milliarden Franken generieren. Diese Mittel könnten drei Fonds (für die soziale Wohlfahrt, die Sicherheit sowie die Prävention von Naturgefahren) zufliessen, die vom Bund oder von der Schweizerischen Nationalbank verwaltet würden. Ist der Bundesrat bereit, diese neue Finanzierungsquelle rasch zu prüfen und gegebenenfalls dem Parlament eine entsprechende Vorlage zu unterbreiten?&lt;/p&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">Erledigt / Liquidé</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263891</t>
   </si>
   <si>
@@ -191,9 +242,6 @@
     <t xml:space="preserve">2026-04-16</t>
   </si>
   <si>
-    <t xml:space="preserve">NR</t>
-  </si>
-  <si>
     <t xml:space="preserve">13. AHV-Rente. Zuweisung der Steuermehreinnahmen der Kantone und Gemeinden an die AHV</t>
   </si>
   <si>
@@ -225,54 +273,6 @@
   </si>
   <si>
     <t xml:space="preserve">Finanze|Imposte|Protezione sociale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fra.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dobler Loïc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WBF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mercosur: Wie sollen die 517 Millionen für die Landwirtschaft finanziert werden?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mercosur : comment financer les 517 millions pour l'agriculture ?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Les Chambres fédérales ont validé l'accord avec le Mercosur, convaincues par une enveloppe de 517 millions de francs pour l'agriculture entre 2028 et 2033. Reste une question laissée dans l'ombre du débat : ce demi-milliard n'est financé par aucune source identifiée.&lt;br&gt;Le Conseil fédéral peut-il indiquer dès aujourd'hui où seront trouvées ces montants, et quels postes du budget fédéral seront concernés ?&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Die eidgenössischen Räte haben das Mercosur-Abkommen genehmigt, überzeugt durch zusätzliche Mittel in Höhe von 517&amp;nbsp;Millionen&amp;nbsp;Franken für die Landwirtschaft für die Jahre&amp;nbsp;2028 bis 2033. Ein Detail verblieb jedoch in der Debatte ungeklärt: Für die halbe Milliarde besteht bislang keine konkrete Finanzierungsquelle.&lt;br&gt;Kann der Bundesrat bereits jetzt angeben, woher die erwähnten Mittel stammen sollen und welche Positionen des Bundeshaushalts betroffen sein werden?&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20267901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20267901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Internationale Politik|Finanzwesen|Landwirtschaft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politique internationale|Finances|Agriculture</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politica internazionale|Finanze|Agricoltura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-28</t>
   </si>
   <si>
     <t xml:space="preserve">26.7687</t>
@@ -5913,7 +5913,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>20264261</v>
+        <v>20267901</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
@@ -5933,136 +5933,134 @@
       <c r="G2" t="s">
         <v>27</v>
       </c>
-      <c r="H2"/>
+      <c r="H2" t="s">
+        <v>28</v>
+      </c>
       <c r="I2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J2" t="s">
-        <v>29</v>
-      </c>
-      <c r="K2" t="s">
         <v>30</v>
       </c>
+      <c r="K2"/>
       <c r="L2" t="s">
         <v>31</v>
       </c>
-      <c r="M2"/>
+      <c r="M2" t="s">
+        <v>32</v>
+      </c>
       <c r="N2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="R2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="T2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="U2" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="V2"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>20263891</v>
+        <v>20264261</v>
       </c>
       <c r="B3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D3" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="E3" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="F3" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H3" t="s">
-        <v>41</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="H3"/>
       <c r="I3" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="J3" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="K3" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="L3" t="s">
+        <v>50</v>
+      </c>
+      <c r="M3"/>
+      <c r="N3" t="s">
+        <v>51</v>
+      </c>
+      <c r="O3" t="s">
+        <v>52</v>
+      </c>
+      <c r="P3" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>36</v>
+      </c>
+      <c r="R3" t="s">
+        <v>54</v>
+      </c>
+      <c r="S3" t="s">
+        <v>55</v>
+      </c>
+      <c r="T3" t="s">
+        <v>56</v>
+      </c>
+      <c r="U3" t="s">
         <v>45</v>
-      </c>
-      <c r="M3" t="s">
-        <v>46</v>
-      </c>
-      <c r="N3" t="s">
-        <v>47</v>
-      </c>
-      <c r="O3" t="s">
-        <v>48</v>
-      </c>
-      <c r="P3" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>35</v>
-      </c>
-      <c r="R3" t="s">
-        <v>50</v>
-      </c>
-      <c r="S3" t="s">
-        <v>51</v>
-      </c>
-      <c r="T3" t="s">
-        <v>52</v>
-      </c>
-      <c r="U3" t="s">
-        <v>53</v>
       </c>
       <c r="V3"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>20263518</v>
+        <v>20263891</v>
       </c>
       <c r="B4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C4" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="D4" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="E4" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="F4" t="s">
         <v>58</v>
       </c>
       <c r="G4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H4" t="s">
         <v>59</v>
-      </c>
-      <c r="H4" t="s">
-        <v>41</v>
       </c>
       <c r="I4" t="s">
         <v>60</v>
@@ -6080,7 +6078,7 @@
         <v>64</v>
       </c>
       <c r="N4" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="O4" t="s">
         <v>65</v>
@@ -6089,25 +6087,25 @@
         <v>66</v>
       </c>
       <c r="Q4" t="s">
+        <v>36</v>
+      </c>
+      <c r="R4" t="s">
         <v>67</v>
       </c>
-      <c r="R4" t="s">
+      <c r="S4" t="s">
         <v>68</v>
       </c>
-      <c r="S4" t="s">
+      <c r="T4" t="s">
         <v>69</v>
       </c>
-      <c r="T4" t="s">
+      <c r="U4" t="s">
         <v>70</v>
-      </c>
-      <c r="U4" t="s">
-        <v>53</v>
       </c>
       <c r="V4"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>20267901</v>
+        <v>20263518</v>
       </c>
       <c r="B5" t="s">
         <v>71</v>
@@ -6125,18 +6123,20 @@
         <v>75</v>
       </c>
       <c r="G5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H5" t="s">
         <v>59</v>
       </c>
-      <c r="H5" t="s">
+      <c r="I5" t="s">
         <v>76</v>
       </c>
-      <c r="I5" t="s">
+      <c r="J5" t="s">
         <v>77</v>
       </c>
-      <c r="J5" t="s">
+      <c r="K5" t="s">
         <v>78</v>
       </c>
-      <c r="K5"/>
       <c r="L5" t="s">
         <v>79</v>
       </c>
@@ -6144,7 +6144,7 @@
         <v>80</v>
       </c>
       <c r="N5" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="O5" t="s">
         <v>81</v>
@@ -6153,23 +6153,21 @@
         <v>82</v>
       </c>
       <c r="Q5" t="s">
-        <v>35</v>
+        <v>83</v>
       </c>
       <c r="R5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="S5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="U5" t="s">
-        <v>86</v>
-      </c>
-      <c r="V5" t="s">
-        <v>86</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="V5"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -6179,22 +6177,22 @@
         <v>87</v>
       </c>
       <c r="C6" t="s">
-        <v>72</v>
+        <v>23</v>
       </c>
       <c r="D6" t="s">
-        <v>73</v>
+        <v>24</v>
       </c>
       <c r="E6" t="s">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="F6" t="s">
         <v>88</v>
       </c>
       <c r="G6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H6" t="s">
         <v>59</v>
-      </c>
-      <c r="H6" t="s">
-        <v>41</v>
       </c>
       <c r="I6" t="s">
         <v>89</v>
@@ -6210,7 +6208,7 @@
         <v>92</v>
       </c>
       <c r="N6" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="O6" t="s">
         <v>93</v>
@@ -6219,7 +6217,7 @@
         <v>94</v>
       </c>
       <c r="Q6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="R6" t="s">
         <v>95</v>
@@ -6243,19 +6241,19 @@
         <v>99</v>
       </c>
       <c r="C7" t="s">
-        <v>72</v>
+        <v>23</v>
       </c>
       <c r="D7" t="s">
-        <v>73</v>
+        <v>24</v>
       </c>
       <c r="E7" t="s">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="F7" t="s">
         <v>88</v>
       </c>
       <c r="G7" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H7" t="s">
         <v>100</v>
@@ -6274,7 +6272,7 @@
         <v>104</v>
       </c>
       <c r="N7" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="O7" t="s">
         <v>105</v>
@@ -6283,7 +6281,7 @@
         <v>106</v>
       </c>
       <c r="Q7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="R7" t="s">
         <v>107</v>
@@ -6307,36 +6305,36 @@
         <v>110</v>
       </c>
       <c r="C8" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D8" t="s">
-        <v>73</v>
+        <v>24</v>
       </c>
       <c r="E8" t="s">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="F8" t="s">
         <v>111</v>
       </c>
       <c r="G8" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H8"/>
       <c r="I8" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="J8" t="s">
         <v>112</v>
       </c>
       <c r="K8" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="L8" t="s">
         <v>113</v>
       </c>
       <c r="M8"/>
       <c r="N8" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="O8" t="s">
         <v>114</v>
@@ -6345,7 +6343,7 @@
         <v>115</v>
       </c>
       <c r="Q8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="R8" t="s">
         <v>116</v>
@@ -6369,19 +6367,19 @@
         <v>119</v>
       </c>
       <c r="C9" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D9" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="E9" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="F9" t="s">
         <v>120</v>
       </c>
       <c r="G9" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="H9" t="s">
         <v>121</v>
@@ -6411,7 +6409,7 @@
         <v>129</v>
       </c>
       <c r="Q9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="R9" t="s">
         <v>130</v>
@@ -6435,7 +6433,7 @@
         <v>133</v>
       </c>
       <c r="C10" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D10" t="s">
         <v>134</v>
@@ -6445,7 +6443,7 @@
         <v>135</v>
       </c>
       <c r="G10" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H10" t="s">
         <v>136</v>
@@ -6466,7 +6464,7 @@
         <v>141</v>
       </c>
       <c r="N10" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="O10" t="s">
         <v>142</v>
@@ -6499,7 +6497,7 @@
         <v>148</v>
       </c>
       <c r="C11" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D11" t="s">
         <v>149</v>
@@ -6511,24 +6509,24 @@
         <v>151</v>
       </c>
       <c r="G11" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H11"/>
       <c r="I11" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="J11" t="s">
         <v>152</v>
       </c>
       <c r="K11" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="L11" t="s">
         <v>153</v>
       </c>
       <c r="M11"/>
       <c r="N11" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="O11" t="s">
         <v>154</v>
@@ -6537,7 +6535,7 @@
         <v>155</v>
       </c>
       <c r="Q11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="R11" t="s">
         <v>156</v>
@@ -6561,19 +6559,19 @@
         <v>159</v>
       </c>
       <c r="C12" t="s">
-        <v>72</v>
+        <v>23</v>
       </c>
       <c r="D12" t="s">
-        <v>73</v>
+        <v>24</v>
       </c>
       <c r="E12" t="s">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="F12" t="s">
         <v>151</v>
       </c>
       <c r="G12" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H12" t="s">
         <v>100</v>
@@ -6592,7 +6590,7 @@
         <v>163</v>
       </c>
       <c r="N12" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="O12" t="s">
         <v>164</v>
@@ -6601,7 +6599,7 @@
         <v>165</v>
       </c>
       <c r="Q12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="R12" t="s">
         <v>166</v>
@@ -6625,19 +6623,19 @@
         <v>169</v>
       </c>
       <c r="C13" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D13" t="s">
         <v>170</v>
       </c>
       <c r="E13" t="s">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="F13" t="s">
         <v>88</v>
       </c>
       <c r="G13" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H13"/>
       <c r="I13" t="s">
@@ -6647,14 +6645,14 @@
         <v>172</v>
       </c>
       <c r="K13" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="L13"/>
       <c r="M13" t="s">
         <v>173</v>
       </c>
       <c r="N13" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="O13" t="s">
         <v>174</v>
@@ -6743,19 +6741,19 @@
         <v>193</v>
       </c>
       <c r="C15" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D15" t="s">
         <v>194</v>
       </c>
       <c r="E15" t="s">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="F15" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="G15" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="H15" t="s">
         <v>100</v>
@@ -6785,7 +6783,7 @@
         <v>202</v>
       </c>
       <c r="Q15" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="R15" t="s">
         <v>203</v>
@@ -6809,7 +6807,7 @@
         <v>207</v>
       </c>
       <c r="C16" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D16" t="s">
         <v>208</v>
@@ -6818,10 +6816,10 @@
         <v>209</v>
       </c>
       <c r="F16" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="G16" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H16" t="s">
         <v>100</v>
@@ -6851,7 +6849,7 @@
         <v>217</v>
       </c>
       <c r="Q16" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="R16" t="s">
         <v>166</v>
@@ -6875,7 +6873,7 @@
         <v>218</v>
       </c>
       <c r="C17" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D17" t="s">
         <v>219</v>
@@ -6884,10 +6882,10 @@
         <v>220</v>
       </c>
       <c r="F17" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="G17" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H17" t="s">
         <v>221</v>
@@ -6917,7 +6915,7 @@
         <v>228</v>
       </c>
       <c r="Q17" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="R17" t="s">
         <v>229</v>
@@ -6941,7 +6939,7 @@
         <v>232</v>
       </c>
       <c r="C18" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D18" t="s">
         <v>233</v>
@@ -6953,7 +6951,7 @@
         <v>234</v>
       </c>
       <c r="G18" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="H18" t="s">
         <v>136</v>
@@ -7010,16 +7008,16 @@
         <v>241</v>
       </c>
       <c r="D19" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="E19" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="F19" t="s">
         <v>242</v>
       </c>
       <c r="G19" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="H19" t="s">
         <v>136</v>
@@ -7040,7 +7038,7 @@
         <v>247</v>
       </c>
       <c r="N19" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="O19" t="s">
         <v>248</v>
@@ -7049,7 +7047,7 @@
         <v>249</v>
       </c>
       <c r="Q19" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="R19" t="s">
         <v>250</v>
@@ -7073,19 +7071,19 @@
         <v>254</v>
       </c>
       <c r="C20" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D20" t="s">
-        <v>73</v>
+        <v>24</v>
       </c>
       <c r="E20" t="s">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="F20" t="s">
         <v>234</v>
       </c>
       <c r="G20" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H20" t="s">
         <v>221</v>
@@ -7115,7 +7113,7 @@
         <v>261</v>
       </c>
       <c r="Q20" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="R20" t="s">
         <v>262</v>
@@ -7139,7 +7137,7 @@
         <v>266</v>
       </c>
       <c r="C21" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D21" t="s">
         <v>267</v>
@@ -7148,13 +7146,13 @@
         <v>209</v>
       </c>
       <c r="F21" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="G21" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H21" t="s">
-        <v>76</v>
+        <v>28</v>
       </c>
       <c r="I21" t="s">
         <v>268</v>
@@ -7205,7 +7203,7 @@
         <v>280</v>
       </c>
       <c r="C22" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D22" t="s">
         <v>267</v>
@@ -7214,13 +7212,13 @@
         <v>209</v>
       </c>
       <c r="F22" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="G22" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H22" t="s">
-        <v>76</v>
+        <v>28</v>
       </c>
       <c r="I22" t="s">
         <v>281</v>
@@ -7271,7 +7269,7 @@
         <v>288</v>
       </c>
       <c r="C23" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D23" t="s">
         <v>289</v>
@@ -7283,7 +7281,7 @@
         <v>290</v>
       </c>
       <c r="G23" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H23" t="s">
         <v>100</v>
@@ -7313,7 +7311,7 @@
         <v>297</v>
       </c>
       <c r="Q23" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="R23" t="s">
         <v>298</v>
@@ -7337,19 +7335,19 @@
         <v>302</v>
       </c>
       <c r="C24" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D24" t="s">
-        <v>73</v>
+        <v>24</v>
       </c>
       <c r="E24" t="s">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="F24" t="s">
         <v>234</v>
       </c>
       <c r="G24" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H24" t="s">
         <v>100</v>
@@ -7379,7 +7377,7 @@
         <v>309</v>
       </c>
       <c r="Q24" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="R24" t="s">
         <v>310</v>
@@ -7403,19 +7401,19 @@
         <v>313</v>
       </c>
       <c r="C25" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D25" t="s">
         <v>194</v>
       </c>
       <c r="E25" t="s">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="F25" t="s">
         <v>314</v>
       </c>
       <c r="G25" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="H25" t="s">
         <v>221</v>
@@ -7445,7 +7443,7 @@
         <v>321</v>
       </c>
       <c r="Q25" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="R25" t="s">
         <v>322</v>
@@ -7469,7 +7467,7 @@
         <v>326</v>
       </c>
       <c r="C26" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D26" t="s">
         <v>267</v>
@@ -7481,10 +7479,10 @@
         <v>327</v>
       </c>
       <c r="G26" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H26" t="s">
-        <v>76</v>
+        <v>28</v>
       </c>
       <c r="I26" t="s">
         <v>328</v>
@@ -7502,7 +7500,7 @@
         <v>332</v>
       </c>
       <c r="N26" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="O26" t="s">
         <v>333</v>
@@ -7523,7 +7521,7 @@
         <v>278</v>
       </c>
       <c r="U26" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="V26"/>
     </row>
@@ -7538,16 +7536,16 @@
         <v>241</v>
       </c>
       <c r="D27" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="E27" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="F27" t="s">
         <v>336</v>
       </c>
       <c r="G27" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="H27" t="s">
         <v>136</v>
@@ -7577,7 +7575,7 @@
         <v>344</v>
       </c>
       <c r="Q27" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="R27" t="s">
         <v>345</v>
@@ -7601,19 +7599,19 @@
         <v>349</v>
       </c>
       <c r="C28" t="s">
-        <v>72</v>
+        <v>23</v>
       </c>
       <c r="D28" t="s">
-        <v>73</v>
+        <v>24</v>
       </c>
       <c r="E28" t="s">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="F28" t="s">
         <v>350</v>
       </c>
       <c r="G28" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H28" t="s">
         <v>136</v>
@@ -7641,7 +7639,7 @@
         <v>356</v>
       </c>
       <c r="Q28" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="R28" t="s">
         <v>357</v>
@@ -7665,22 +7663,22 @@
         <v>361</v>
       </c>
       <c r="C29" t="s">
-        <v>72</v>
+        <v>23</v>
       </c>
       <c r="D29" t="s">
-        <v>73</v>
+        <v>24</v>
       </c>
       <c r="E29" t="s">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="F29" t="s">
         <v>362</v>
       </c>
       <c r="G29" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H29" t="s">
-        <v>76</v>
+        <v>28</v>
       </c>
       <c r="I29" t="s">
         <v>363</v>
@@ -7696,7 +7694,7 @@
         <v>366</v>
       </c>
       <c r="N29" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="O29" t="s">
         <v>367</v>
@@ -7705,7 +7703,7 @@
         <v>368</v>
       </c>
       <c r="Q29" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="R29" t="s">
         <v>369</v>
@@ -7729,7 +7727,7 @@
         <v>372</v>
       </c>
       <c r="C30" t="s">
-        <v>72</v>
+        <v>23</v>
       </c>
       <c r="D30" t="s">
         <v>149</v>
@@ -7741,10 +7739,10 @@
         <v>362</v>
       </c>
       <c r="G30" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H30" t="s">
-        <v>76</v>
+        <v>28</v>
       </c>
       <c r="I30" t="s">
         <v>373</v>
@@ -7760,7 +7758,7 @@
         <v>376</v>
       </c>
       <c r="N30" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="O30" t="s">
         <v>377</v>
@@ -7769,7 +7767,7 @@
         <v>378</v>
       </c>
       <c r="Q30" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="R30" t="s">
         <v>379</v>
@@ -7793,19 +7791,19 @@
         <v>382</v>
       </c>
       <c r="C31" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D31" t="s">
         <v>383</v>
       </c>
       <c r="E31" t="s">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="F31" t="s">
         <v>384</v>
       </c>
       <c r="G31" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H31" t="s">
         <v>221</v>
@@ -7826,7 +7824,7 @@
         <v>389</v>
       </c>
       <c r="N31" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="O31" t="s">
         <v>390</v>
@@ -7835,7 +7833,7 @@
         <v>391</v>
       </c>
       <c r="Q31" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="R31" t="s">
         <v>392</v>
@@ -7859,19 +7857,19 @@
         <v>396</v>
       </c>
       <c r="C32" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D32" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="E32" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="F32" t="s">
         <v>135</v>
       </c>
       <c r="G32" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="H32" t="s">
         <v>100</v>
@@ -7892,7 +7890,7 @@
         <v>401</v>
       </c>
       <c r="N32" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="O32" t="s">
         <v>402</v>
@@ -7901,7 +7899,7 @@
         <v>403</v>
       </c>
       <c r="Q32" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="R32" t="s">
         <v>404</v>
@@ -7925,7 +7923,7 @@
         <v>407</v>
       </c>
       <c r="C33" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D33" t="s">
         <v>408</v>
@@ -7937,10 +7935,10 @@
         <v>314</v>
       </c>
       <c r="G33" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H33" t="s">
-        <v>76</v>
+        <v>28</v>
       </c>
       <c r="I33" t="s">
         <v>409</v>
@@ -7967,7 +7965,7 @@
         <v>415</v>
       </c>
       <c r="Q33" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="R33" t="s">
         <v>416</v>
@@ -7991,19 +7989,19 @@
         <v>420</v>
       </c>
       <c r="C34" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D34" t="s">
         <v>421</v>
       </c>
       <c r="E34" t="s">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="F34" t="s">
         <v>327</v>
       </c>
       <c r="G34" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H34" t="s">
         <v>100</v>
@@ -8057,7 +8055,7 @@
         <v>429</v>
       </c>
       <c r="C35" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D35" t="s">
         <v>430</v>
@@ -8067,10 +8065,10 @@
         <v>314</v>
       </c>
       <c r="G35" t="s">
+        <v>27</v>
+      </c>
+      <c r="H35" t="s">
         <v>59</v>
-      </c>
-      <c r="H35" t="s">
-        <v>41</v>
       </c>
       <c r="I35" t="s">
         <v>431</v>
@@ -8121,7 +8119,7 @@
         <v>442</v>
       </c>
       <c r="C36" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D36" t="s">
         <v>149</v>
@@ -8133,7 +8131,7 @@
         <v>314</v>
       </c>
       <c r="G36" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H36" t="s">
         <v>100</v>
@@ -8163,7 +8161,7 @@
         <v>449</v>
       </c>
       <c r="Q36" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="R36" t="s">
         <v>107</v>
@@ -8187,7 +8185,7 @@
         <v>450</v>
       </c>
       <c r="C37" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D37" t="s">
         <v>451</v>
@@ -8199,7 +8197,7 @@
         <v>452</v>
       </c>
       <c r="G37" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H37" t="s">
         <v>453</v>
@@ -8229,7 +8227,7 @@
         <v>460</v>
       </c>
       <c r="Q37" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="R37" t="s">
         <v>461</v>
@@ -8253,7 +8251,7 @@
         <v>464</v>
       </c>
       <c r="C38" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D38" t="s">
         <v>465</v>
@@ -8265,7 +8263,7 @@
         <v>135</v>
       </c>
       <c r="G38" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H38" t="s">
         <v>221</v>
@@ -8319,7 +8317,7 @@
         <v>477</v>
       </c>
       <c r="C39" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D39" t="s">
         <v>478</v>
@@ -8331,7 +8329,7 @@
         <v>479</v>
       </c>
       <c r="G39" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H39" t="s">
         <v>100</v>
@@ -8385,19 +8383,19 @@
         <v>487</v>
       </c>
       <c r="C40" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D40" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="E40" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="F40" t="s">
         <v>488</v>
       </c>
       <c r="G40" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="H40" t="s">
         <v>136</v>
@@ -8427,7 +8425,7 @@
         <v>495</v>
       </c>
       <c r="Q40" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="R40" t="s">
         <v>176</v>
@@ -8451,22 +8449,22 @@
         <v>497</v>
       </c>
       <c r="C41" t="s">
-        <v>72</v>
+        <v>23</v>
       </c>
       <c r="D41" t="s">
         <v>383</v>
       </c>
       <c r="E41" t="s">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="F41" t="s">
         <v>498</v>
       </c>
       <c r="G41" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H41" t="s">
-        <v>76</v>
+        <v>28</v>
       </c>
       <c r="I41" t="s">
         <v>499</v>
@@ -8482,7 +8480,7 @@
         <v>502</v>
       </c>
       <c r="N41" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="O41" t="s">
         <v>503</v>
@@ -8491,7 +8489,7 @@
         <v>504</v>
       </c>
       <c r="Q41" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="R41" t="s">
         <v>505</v>
@@ -8515,7 +8513,7 @@
         <v>509</v>
       </c>
       <c r="C42" t="s">
-        <v>72</v>
+        <v>23</v>
       </c>
       <c r="D42" t="s">
         <v>510</v>
@@ -8527,7 +8525,7 @@
         <v>479</v>
       </c>
       <c r="G42" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H42" t="s">
         <v>136</v>
@@ -8546,7 +8544,7 @@
         <v>515</v>
       </c>
       <c r="N42" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="O42" t="s">
         <v>516</v>
@@ -8555,7 +8553,7 @@
         <v>517</v>
       </c>
       <c r="Q42" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="R42" t="s">
         <v>518</v>
@@ -8583,7 +8581,7 @@
       </c>
       <c r="D43"/>
       <c r="E43" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="F43" t="s">
         <v>523</v>
@@ -8604,7 +8602,7 @@
       <c r="L43"/>
       <c r="M43"/>
       <c r="N43" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="O43" t="s">
         <v>527</v>
@@ -8613,7 +8611,7 @@
         <v>528</v>
       </c>
       <c r="Q43" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="R43" t="s">
         <v>461</v>
@@ -8637,7 +8635,7 @@
         <v>529</v>
       </c>
       <c r="C44" t="s">
-        <v>72</v>
+        <v>23</v>
       </c>
       <c r="D44" t="s">
         <v>408</v>
@@ -8649,7 +8647,7 @@
         <v>530</v>
       </c>
       <c r="G44" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H44" t="s">
         <v>221</v>
@@ -8668,7 +8666,7 @@
         <v>534</v>
       </c>
       <c r="N44" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="O44" t="s">
         <v>535</v>
@@ -8701,22 +8699,22 @@
         <v>540</v>
       </c>
       <c r="C45" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D45" t="s">
         <v>541</v>
       </c>
       <c r="E45" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="F45" t="s">
         <v>542</v>
       </c>
       <c r="G45" t="s">
+        <v>27</v>
+      </c>
+      <c r="H45" t="s">
         <v>59</v>
-      </c>
-      <c r="H45" t="s">
-        <v>41</v>
       </c>
       <c r="I45" t="s">
         <v>543</v>
@@ -8734,7 +8732,7 @@
         <v>547</v>
       </c>
       <c r="N45" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="O45" t="s">
         <v>548</v>
@@ -8746,13 +8744,13 @@
         <v>144</v>
       </c>
       <c r="R45" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="S45" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="T45" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="U45" t="s">
         <v>508</v>
@@ -8767,7 +8765,7 @@
         <v>550</v>
       </c>
       <c r="C46" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D46" t="s">
         <v>551</v>
@@ -8779,10 +8777,10 @@
         <v>488</v>
       </c>
       <c r="G46" t="s">
+        <v>27</v>
+      </c>
+      <c r="H46" t="s">
         <v>59</v>
-      </c>
-      <c r="H46" t="s">
-        <v>41</v>
       </c>
       <c r="I46" t="s">
         <v>553</v>
@@ -8833,7 +8831,7 @@
         <v>563</v>
       </c>
       <c r="C47" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D47" t="s">
         <v>564</v>
@@ -8845,7 +8843,7 @@
         <v>488</v>
       </c>
       <c r="G47" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H47" t="s">
         <v>100</v>
@@ -8875,7 +8873,7 @@
         <v>571</v>
       </c>
       <c r="Q47" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="R47" t="s">
         <v>572</v>
@@ -8899,19 +8897,19 @@
         <v>575</v>
       </c>
       <c r="C48" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D48" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="E48" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="F48" t="s">
         <v>576</v>
       </c>
       <c r="G48" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="H48" t="s">
         <v>121</v>
@@ -8941,7 +8939,7 @@
         <v>583</v>
       </c>
       <c r="Q48" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="R48" t="s">
         <v>584</v>
@@ -8968,16 +8966,16 @@
         <v>241</v>
       </c>
       <c r="D49" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="E49" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="F49" t="s">
         <v>576</v>
       </c>
       <c r="G49" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="H49" t="s">
         <v>136</v>
@@ -9007,7 +9005,7 @@
         <v>594</v>
       </c>
       <c r="Q49" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="R49" t="s">
         <v>595</v>
@@ -9031,22 +9029,22 @@
         <v>598</v>
       </c>
       <c r="C50" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D50" t="s">
         <v>599</v>
       </c>
       <c r="E50" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="F50" t="s">
         <v>600</v>
       </c>
       <c r="G50" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="H50" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="I50" t="s">
         <v>601</v>
@@ -9064,7 +9062,7 @@
         <v>605</v>
       </c>
       <c r="N50" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="O50" t="s">
         <v>606</v>
@@ -9073,7 +9071,7 @@
         <v>607</v>
       </c>
       <c r="Q50" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="R50" t="s">
         <v>608</v>
@@ -9097,7 +9095,7 @@
         <v>611</v>
       </c>
       <c r="C51" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D51" t="s">
         <v>465</v>
@@ -9109,10 +9107,10 @@
         <v>384</v>
       </c>
       <c r="G51" t="s">
+        <v>27</v>
+      </c>
+      <c r="H51" t="s">
         <v>59</v>
-      </c>
-      <c r="H51" t="s">
-        <v>41</v>
       </c>
       <c r="I51" t="s">
         <v>612</v>
@@ -9139,16 +9137,16 @@
         <v>618</v>
       </c>
       <c r="Q51" t="s">
+        <v>83</v>
+      </c>
+      <c r="R51" t="s">
         <v>67</v>
       </c>
-      <c r="R51" t="s">
-        <v>50</v>
-      </c>
       <c r="S51" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="T51" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="U51" t="s">
         <v>508</v>
@@ -9163,19 +9161,19 @@
         <v>619</v>
       </c>
       <c r="C52" t="s">
-        <v>72</v>
+        <v>23</v>
       </c>
       <c r="D52" t="s">
         <v>620</v>
       </c>
       <c r="E52" t="s">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="F52" t="s">
         <v>621</v>
       </c>
       <c r="G52" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H52" t="s">
         <v>121</v>
@@ -9194,7 +9192,7 @@
         <v>625</v>
       </c>
       <c r="N52" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="O52" t="s">
         <v>626</v>
@@ -9227,7 +9225,7 @@
         <v>631</v>
       </c>
       <c r="C53" t="s">
-        <v>72</v>
+        <v>23</v>
       </c>
       <c r="D53" t="s">
         <v>451</v>
@@ -9239,7 +9237,7 @@
         <v>621</v>
       </c>
       <c r="G53" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H53" t="s">
         <v>136</v>
@@ -9258,7 +9256,7 @@
         <v>635</v>
       </c>
       <c r="N53" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="O53" t="s">
         <v>636</v>
@@ -9301,7 +9299,7 @@
         <v>640</v>
       </c>
       <c r="G54" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H54" t="s">
         <v>221</v>
@@ -9355,7 +9353,7 @@
         <v>651</v>
       </c>
       <c r="C55" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D55" t="s">
         <v>652</v>
@@ -9367,10 +9365,10 @@
         <v>653</v>
       </c>
       <c r="G55" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="H55" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="I55" t="s">
         <v>654</v>
@@ -9388,7 +9386,7 @@
         <v>658</v>
       </c>
       <c r="N55" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="O55" t="s">
         <v>659</v>
@@ -9433,10 +9431,10 @@
         <v>653</v>
       </c>
       <c r="G56" t="s">
+        <v>27</v>
+      </c>
+      <c r="H56" t="s">
         <v>59</v>
-      </c>
-      <c r="H56" t="s">
-        <v>41</v>
       </c>
       <c r="I56" t="s">
         <v>666</v>
@@ -9487,19 +9485,19 @@
         <v>673</v>
       </c>
       <c r="C57" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D57" t="s">
         <v>421</v>
       </c>
       <c r="E57" t="s">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="F57" t="s">
         <v>653</v>
       </c>
       <c r="G57" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H57" t="s">
         <v>100</v>
@@ -9553,19 +9551,19 @@
         <v>681</v>
       </c>
       <c r="C58" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D58" t="s">
         <v>194</v>
       </c>
       <c r="E58" t="s">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="F58" t="s">
         <v>653</v>
       </c>
       <c r="G58" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="H58" t="s">
         <v>221</v>
@@ -9595,7 +9593,7 @@
         <v>688</v>
       </c>
       <c r="Q58" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="R58" t="s">
         <v>689</v>
@@ -9619,22 +9617,22 @@
         <v>692</v>
       </c>
       <c r="C59" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D59" t="s">
         <v>693</v>
       </c>
       <c r="E59" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="F59" t="s">
         <v>694</v>
       </c>
       <c r="G59" t="s">
+        <v>27</v>
+      </c>
+      <c r="H59" t="s">
         <v>59</v>
-      </c>
-      <c r="H59" t="s">
-        <v>41</v>
       </c>
       <c r="I59" t="s">
         <v>695</v>
@@ -9652,7 +9650,7 @@
         <v>699</v>
       </c>
       <c r="N59" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="O59" t="s">
         <v>700</v>
@@ -9685,22 +9683,22 @@
         <v>702</v>
       </c>
       <c r="C60" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D60" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="E60" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="F60" t="s">
         <v>703</v>
       </c>
       <c r="G60" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="H60" t="s">
-        <v>76</v>
+        <v>28</v>
       </c>
       <c r="I60" t="s">
         <v>704</v>
@@ -9718,7 +9716,7 @@
         <v>708</v>
       </c>
       <c r="N60" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="O60" t="s">
         <v>709</v>
@@ -9751,7 +9749,7 @@
         <v>714</v>
       </c>
       <c r="C61" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D61" t="s">
         <v>715</v>
@@ -9763,7 +9761,7 @@
         <v>703</v>
       </c>
       <c r="G61" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H61" t="s">
         <v>121</v>
@@ -9793,7 +9791,7 @@
         <v>722</v>
       </c>
       <c r="Q61" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="R61" t="s">
         <v>723</v>
@@ -9817,22 +9815,22 @@
         <v>726</v>
       </c>
       <c r="C62" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D62" t="s">
         <v>727</v>
       </c>
       <c r="E62" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="F62" t="s">
         <v>728</v>
       </c>
       <c r="G62" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="H62" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="I62" t="s">
         <v>729</v>
@@ -9850,7 +9848,7 @@
         <v>733</v>
       </c>
       <c r="N62" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="O62" t="s">
         <v>734</v>
@@ -9895,10 +9893,10 @@
         <v>741</v>
       </c>
       <c r="G63" t="s">
+        <v>27</v>
+      </c>
+      <c r="H63" t="s">
         <v>59</v>
-      </c>
-      <c r="H63" t="s">
-        <v>41</v>
       </c>
       <c r="I63" t="s">
         <v>742</v>
@@ -9925,7 +9923,7 @@
         <v>749</v>
       </c>
       <c r="Q63" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="R63" t="s">
         <v>750</v>
@@ -9949,7 +9947,7 @@
         <v>753</v>
       </c>
       <c r="C64" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D64" t="s">
         <v>754</v>
@@ -9961,7 +9959,7 @@
         <v>755</v>
       </c>
       <c r="G64" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H64" t="s">
         <v>100</v>
@@ -10015,7 +10013,7 @@
         <v>763</v>
       </c>
       <c r="C65" t="s">
-        <v>72</v>
+        <v>23</v>
       </c>
       <c r="D65" t="s">
         <v>219</v>
@@ -10027,10 +10025,10 @@
         <v>755</v>
       </c>
       <c r="G65" t="s">
+        <v>27</v>
+      </c>
+      <c r="H65" t="s">
         <v>59</v>
-      </c>
-      <c r="H65" t="s">
-        <v>41</v>
       </c>
       <c r="I65" t="s">
         <v>764</v>
@@ -10046,7 +10044,7 @@
         <v>767</v>
       </c>
       <c r="N65" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="O65" t="s">
         <v>768</v>
@@ -10079,22 +10077,22 @@
         <v>770</v>
       </c>
       <c r="C66" t="s">
-        <v>72</v>
+        <v>23</v>
       </c>
       <c r="D66" t="s">
         <v>771</v>
       </c>
       <c r="E66" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="F66" t="s">
         <v>755</v>
       </c>
       <c r="G66" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H66" t="s">
-        <v>76</v>
+        <v>28</v>
       </c>
       <c r="I66" t="s">
         <v>772</v>
@@ -10110,7 +10108,7 @@
         <v>775</v>
       </c>
       <c r="N66" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="O66" t="s">
         <v>776</v>
@@ -10119,7 +10117,7 @@
         <v>777</v>
       </c>
       <c r="Q66" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="R66" t="s">
         <v>778</v>
@@ -10143,7 +10141,7 @@
         <v>781</v>
       </c>
       <c r="C67" t="s">
-        <v>72</v>
+        <v>23</v>
       </c>
       <c r="D67" t="s">
         <v>715</v>
@@ -10155,7 +10153,7 @@
         <v>782</v>
       </c>
       <c r="G67" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H67" t="s">
         <v>136</v>
@@ -10174,7 +10172,7 @@
         <v>786</v>
       </c>
       <c r="N67" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="O67" t="s">
         <v>787</v>
@@ -10207,7 +10205,7 @@
         <v>792</v>
       </c>
       <c r="C68" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D68" t="s">
         <v>793</v>
@@ -10219,7 +10217,7 @@
         <v>794</v>
       </c>
       <c r="G68" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H68" t="s">
         <v>121</v>
@@ -10273,7 +10271,7 @@
         <v>805</v>
       </c>
       <c r="C69" t="s">
-        <v>72</v>
+        <v>23</v>
       </c>
       <c r="D69" t="s">
         <v>793</v>
@@ -10285,7 +10283,7 @@
         <v>794</v>
       </c>
       <c r="G69" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H69" t="s">
         <v>121</v>
@@ -10304,7 +10302,7 @@
         <v>809</v>
       </c>
       <c r="N69" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="O69" t="s">
         <v>810</v>
@@ -10393,19 +10391,19 @@
         <v>825</v>
       </c>
       <c r="C71" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D71" t="s">
         <v>826</v>
       </c>
       <c r="E71" t="s">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="F71" t="s">
         <v>827</v>
       </c>
       <c r="G71" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H71" t="s">
         <v>100</v>
@@ -10435,7 +10433,7 @@
         <v>834</v>
       </c>
       <c r="Q71" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="R71" t="s">
         <v>835</v>
@@ -10459,19 +10457,19 @@
         <v>838</v>
       </c>
       <c r="C72" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D72" t="s">
         <v>839</v>
       </c>
       <c r="E72" t="s">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="F72" t="s">
         <v>827</v>
       </c>
       <c r="G72" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H72" t="s">
         <v>100</v>
@@ -10531,16 +10529,16 @@
         <v>851</v>
       </c>
       <c r="E73" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="F73" t="s">
         <v>827</v>
       </c>
       <c r="G73" t="s">
+        <v>27</v>
+      </c>
+      <c r="H73" t="s">
         <v>59</v>
-      </c>
-      <c r="H73" t="s">
-        <v>41</v>
       </c>
       <c r="I73" t="s">
         <v>852</v>
@@ -10591,7 +10589,7 @@
         <v>863</v>
       </c>
       <c r="C74" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D74" t="s">
         <v>430</v>
@@ -10601,10 +10599,10 @@
         <v>864</v>
       </c>
       <c r="G74" t="s">
+        <v>27</v>
+      </c>
+      <c r="H74" t="s">
         <v>59</v>
-      </c>
-      <c r="H74" t="s">
-        <v>41</v>
       </c>
       <c r="I74" t="s">
         <v>865</v>
@@ -10655,19 +10653,19 @@
         <v>875</v>
       </c>
       <c r="C75" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D75" t="s">
         <v>876</v>
       </c>
       <c r="E75" t="s">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="F75" t="s">
         <v>864</v>
       </c>
       <c r="G75" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H75" t="s">
         <v>221</v>
@@ -10688,7 +10686,7 @@
         <v>881</v>
       </c>
       <c r="N75" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="O75" t="s">
         <v>882</v>
@@ -10697,7 +10695,7 @@
         <v>883</v>
       </c>
       <c r="Q75" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="R75" t="s">
         <v>884</v>
@@ -10721,19 +10719,19 @@
         <v>887</v>
       </c>
       <c r="C76" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D76" t="s">
         <v>888</v>
       </c>
       <c r="E76" t="s">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="F76" t="s">
         <v>889</v>
       </c>
       <c r="G76" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H76" t="s">
         <v>100</v>
@@ -10754,7 +10752,7 @@
         <v>894</v>
       </c>
       <c r="N76" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="O76" t="s">
         <v>895</v>
@@ -10797,7 +10795,7 @@
         <v>889</v>
       </c>
       <c r="G77" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H77" t="s">
         <v>100</v>
@@ -10851,7 +10849,7 @@
         <v>909</v>
       </c>
       <c r="C78" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D78" t="s">
         <v>665</v>
@@ -10863,7 +10861,7 @@
         <v>889</v>
       </c>
       <c r="G78" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H78" t="s">
         <v>100</v>
@@ -10917,7 +10915,7 @@
         <v>920</v>
       </c>
       <c r="C79" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D79" t="s">
         <v>921</v>
@@ -10929,7 +10927,7 @@
         <v>922</v>
       </c>
       <c r="G79" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="H79" t="s">
         <v>100</v>
@@ -10950,7 +10948,7 @@
         <v>927</v>
       </c>
       <c r="N79" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="O79" t="s">
         <v>928</v>
@@ -10983,7 +10981,7 @@
         <v>930</v>
       </c>
       <c r="C80" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D80" t="s">
         <v>931</v>
@@ -10995,7 +10993,7 @@
         <v>932</v>
       </c>
       <c r="G80" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H80" t="s">
         <v>100</v>
@@ -11049,7 +11047,7 @@
         <v>940</v>
       </c>
       <c r="C81" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D81" t="s">
         <v>941</v>
@@ -11061,10 +11059,10 @@
         <v>943</v>
       </c>
       <c r="G81" t="s">
+        <v>27</v>
+      </c>
+      <c r="H81" t="s">
         <v>59</v>
-      </c>
-      <c r="H81" t="s">
-        <v>41</v>
       </c>
       <c r="I81" t="s">
         <v>944</v>
@@ -11091,7 +11089,7 @@
         <v>950</v>
       </c>
       <c r="Q81" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="R81" t="s">
         <v>951</v>
@@ -11115,7 +11113,7 @@
         <v>954</v>
       </c>
       <c r="C82" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D82" t="s">
         <v>715</v>
@@ -11127,10 +11125,10 @@
         <v>943</v>
       </c>
       <c r="G82" t="s">
+        <v>27</v>
+      </c>
+      <c r="H82" t="s">
         <v>59</v>
-      </c>
-      <c r="H82" t="s">
-        <v>41</v>
       </c>
       <c r="I82" t="s">
         <v>955</v>
@@ -11181,7 +11179,7 @@
         <v>965</v>
       </c>
       <c r="C83" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D83" t="s">
         <v>966</v>
@@ -11191,10 +11189,10 @@
         <v>967</v>
       </c>
       <c r="G83" t="s">
+        <v>27</v>
+      </c>
+      <c r="H83" t="s">
         <v>59</v>
-      </c>
-      <c r="H83" t="s">
-        <v>41</v>
       </c>
       <c r="I83" t="s">
         <v>968</v>
@@ -11251,13 +11249,13 @@
         <v>976</v>
       </c>
       <c r="E84" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="F84" t="s">
         <v>977</v>
       </c>
       <c r="G84" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H84" t="s">
         <v>978</v>
@@ -11311,19 +11309,19 @@
         <v>989</v>
       </c>
       <c r="C85" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D85" t="s">
         <v>990</v>
       </c>
       <c r="E85" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="F85" t="s">
         <v>977</v>
       </c>
       <c r="G85" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H85" t="s">
         <v>221</v>
@@ -11377,7 +11375,7 @@
         <v>1001</v>
       </c>
       <c r="C86" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D86" t="s">
         <v>1002</v>
@@ -11389,7 +11387,7 @@
         <v>977</v>
       </c>
       <c r="G86" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H86" t="s">
         <v>100</v>
@@ -11419,7 +11417,7 @@
         <v>1009</v>
       </c>
       <c r="Q86" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="R86" t="s">
         <v>156</v>
@@ -11443,19 +11441,19 @@
         <v>1010</v>
       </c>
       <c r="C87" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D87" t="s">
         <v>1011</v>
       </c>
       <c r="E87" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="F87" t="s">
         <v>1012</v>
       </c>
       <c r="G87" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="H87" t="s">
         <v>221</v>
@@ -11476,7 +11474,7 @@
         <v>1017</v>
       </c>
       <c r="N87" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="O87" t="s">
         <v>1018</v>
@@ -11509,22 +11507,22 @@
         <v>1023</v>
       </c>
       <c r="C88" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D88" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="E88" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="F88" t="s">
         <v>1012</v>
       </c>
       <c r="G88" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="H88" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="I88" t="s">
         <v>1024</v>
@@ -11575,19 +11573,19 @@
         <v>1031</v>
       </c>
       <c r="C89" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D89" t="s">
         <v>599</v>
       </c>
       <c r="E89" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="F89" t="s">
         <v>1032</v>
       </c>
       <c r="G89" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="H89" t="s">
         <v>100</v>
@@ -11608,7 +11606,7 @@
         <v>1037</v>
       </c>
       <c r="N89" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="O89" t="s">
         <v>1038</v>
@@ -11617,7 +11615,7 @@
         <v>1039</v>
       </c>
       <c r="Q89" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="R89" t="s">
         <v>1040</v>
@@ -11641,19 +11639,19 @@
         <v>1043</v>
       </c>
       <c r="C90" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D90" t="s">
         <v>876</v>
       </c>
       <c r="E90" t="s">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="F90" t="s">
         <v>1044</v>
       </c>
       <c r="G90" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H90" t="s">
         <v>221</v>
@@ -11792,7 +11790,7 @@
         <v>1069</v>
       </c>
       <c r="N92" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="O92" t="s">
         <v>1070</v>
@@ -11829,7 +11827,7 @@
         <v>1074</v>
       </c>
       <c r="G93" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="H93" t="s">
         <v>136</v>
@@ -11889,13 +11887,13 @@
         <v>839</v>
       </c>
       <c r="E94" t="s">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="F94" t="s">
         <v>1086</v>
       </c>
       <c r="G94" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H94" t="s">
         <v>100</v>
@@ -11916,7 +11914,7 @@
         <v>1091</v>
       </c>
       <c r="N94" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="O94" t="s">
         <v>1092</v>
@@ -11949,7 +11947,7 @@
         <v>1097</v>
       </c>
       <c r="C95" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D95" t="s">
         <v>941</v>
@@ -11961,10 +11959,10 @@
         <v>1086</v>
       </c>
       <c r="G95" t="s">
+        <v>27</v>
+      </c>
+      <c r="H95" t="s">
         <v>59</v>
-      </c>
-      <c r="H95" t="s">
-        <v>41</v>
       </c>
       <c r="I95" t="s">
         <v>1098</v>
@@ -12015,19 +12013,19 @@
         <v>1108</v>
       </c>
       <c r="C96" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D96" t="s">
         <v>1109</v>
       </c>
       <c r="E96" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="F96" t="s">
         <v>1086</v>
       </c>
       <c r="G96" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H96" t="s">
         <v>453</v>
@@ -12048,7 +12046,7 @@
         <v>1114</v>
       </c>
       <c r="N96" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="O96" t="s">
         <v>1115</v>
@@ -12057,7 +12055,7 @@
         <v>1116</v>
       </c>
       <c r="Q96" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="R96" t="s">
         <v>1117</v>
@@ -12081,7 +12079,7 @@
         <v>1120</v>
       </c>
       <c r="C97" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D97" t="s">
         <v>665</v>
@@ -12093,10 +12091,10 @@
         <v>1086</v>
       </c>
       <c r="G97" t="s">
+        <v>27</v>
+      </c>
+      <c r="H97" t="s">
         <v>59</v>
-      </c>
-      <c r="H97" t="s">
-        <v>41</v>
       </c>
       <c r="I97" t="s">
         <v>1121</v>
@@ -12147,19 +12145,19 @@
         <v>1131</v>
       </c>
       <c r="C98" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D98" t="s">
         <v>1132</v>
       </c>
       <c r="E98" t="s">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="F98" t="s">
         <v>1086</v>
       </c>
       <c r="G98" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H98" t="s">
         <v>136</v>
@@ -12189,7 +12187,7 @@
         <v>1139</v>
       </c>
       <c r="Q98" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="R98" t="s">
         <v>1140</v>
@@ -12213,22 +12211,22 @@
         <v>1143</v>
       </c>
       <c r="C99" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D99" t="s">
         <v>1144</v>
       </c>
       <c r="E99" t="s">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="F99" t="s">
         <v>1086</v>
       </c>
       <c r="G99" t="s">
+        <v>27</v>
+      </c>
+      <c r="H99" t="s">
         <v>59</v>
-      </c>
-      <c r="H99" t="s">
-        <v>41</v>
       </c>
       <c r="I99" t="s">
         <v>1145</v>
@@ -12279,19 +12277,19 @@
         <v>1155</v>
       </c>
       <c r="C100" t="s">
-        <v>72</v>
+        <v>23</v>
       </c>
       <c r="D100" t="s">
         <v>771</v>
       </c>
       <c r="E100" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="F100" t="s">
         <v>1156</v>
       </c>
       <c r="G100" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H100" t="s">
         <v>100</v>
@@ -12312,7 +12310,7 @@
         <v>1161</v>
       </c>
       <c r="N100" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="O100" t="s">
         <v>1162</v>
@@ -12345,19 +12343,19 @@
         <v>1167</v>
       </c>
       <c r="C101" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D101" t="s">
         <v>1168</v>
       </c>
       <c r="E101" t="s">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="F101" t="s">
         <v>1156</v>
       </c>
       <c r="G101" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H101" t="s">
         <v>100</v>
@@ -12387,7 +12385,7 @@
         <v>1175</v>
       </c>
       <c r="Q101" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="R101" t="s">
         <v>1176</v>
@@ -12440,7 +12438,7 @@
         <v>1185</v>
       </c>
       <c r="N102" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="O102" t="s">
         <v>1186</v>
@@ -12467,7 +12465,7 @@
         <v>1188</v>
       </c>
       <c r="C103" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D103" t="s">
         <v>149</v>
@@ -12479,10 +12477,10 @@
         <v>1189</v>
       </c>
       <c r="G103" t="s">
+        <v>27</v>
+      </c>
+      <c r="H103" t="s">
         <v>59</v>
-      </c>
-      <c r="H103" t="s">
-        <v>41</v>
       </c>
       <c r="I103" t="s">
         <v>654</v>
@@ -12500,7 +12498,7 @@
         <v>1193</v>
       </c>
       <c r="N103" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="O103" t="s">
         <v>1194</v>
@@ -12533,7 +12531,7 @@
         <v>1196</v>
       </c>
       <c r="C104" t="s">
-        <v>72</v>
+        <v>23</v>
       </c>
       <c r="D104" t="s">
         <v>1197</v>
@@ -12545,7 +12543,7 @@
         <v>1198</v>
       </c>
       <c r="G104" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H104" t="s">
         <v>136</v>
@@ -12564,7 +12562,7 @@
         <v>1202</v>
       </c>
       <c r="N104" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="O104" t="s">
         <v>1203</v>
@@ -12597,19 +12595,19 @@
         <v>1208</v>
       </c>
       <c r="C105" t="s">
-        <v>72</v>
+        <v>23</v>
       </c>
       <c r="D105" t="s">
         <v>1209</v>
       </c>
       <c r="E105" t="s">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="F105" t="s">
         <v>1210</v>
       </c>
       <c r="G105" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H105" t="s">
         <v>100</v>
@@ -12628,7 +12626,7 @@
         <v>1214</v>
       </c>
       <c r="N105" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="O105" t="s">
         <v>1215</v>
@@ -12665,7 +12663,7 @@
       </c>
       <c r="D106"/>
       <c r="E106" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="F106" t="s">
         <v>1218</v>
@@ -12686,7 +12684,7 @@
       <c r="L106"/>
       <c r="M106"/>
       <c r="N106" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="O106" t="s">
         <v>1222</v>
@@ -12695,7 +12693,7 @@
         <v>1223</v>
       </c>
       <c r="Q106" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="R106" t="s">
         <v>1224</v>
@@ -12843,7 +12841,7 @@
         <v>1251</v>
       </c>
       <c r="C109" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D109" t="s">
         <v>941</v>
@@ -12855,7 +12853,7 @@
         <v>1252</v>
       </c>
       <c r="G109" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H109" t="s">
         <v>221</v>
@@ -12885,7 +12883,7 @@
         <v>1259</v>
       </c>
       <c r="Q109" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="R109" t="s">
         <v>1260</v>
@@ -12909,22 +12907,22 @@
         <v>1263</v>
       </c>
       <c r="C110" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D110" t="s">
         <v>1264</v>
       </c>
       <c r="E110" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="F110" t="s">
         <v>1265</v>
       </c>
       <c r="G110" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H110" t="s">
-        <v>76</v>
+        <v>28</v>
       </c>
       <c r="I110" t="s">
         <v>1266</v>
@@ -12951,7 +12949,7 @@
         <v>1272</v>
       </c>
       <c r="Q110" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="R110" t="s">
         <v>1273</v>
@@ -12975,7 +12973,7 @@
         <v>1276</v>
       </c>
       <c r="C111" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D111" t="s">
         <v>1277</v>
@@ -12987,7 +12985,7 @@
         <v>1265</v>
       </c>
       <c r="G111" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H111" t="s">
         <v>100</v>
@@ -13008,7 +13006,7 @@
         <v>1282</v>
       </c>
       <c r="N111" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="O111" t="s">
         <v>1283</v>
@@ -13041,22 +13039,22 @@
         <v>1285</v>
       </c>
       <c r="C112" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D112" t="s">
         <v>1286</v>
       </c>
       <c r="E112" t="s">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="F112" t="s">
         <v>1265</v>
       </c>
       <c r="G112" t="s">
+        <v>27</v>
+      </c>
+      <c r="H112" t="s">
         <v>59</v>
-      </c>
-      <c r="H112" t="s">
-        <v>41</v>
       </c>
       <c r="I112" t="s">
         <v>1287</v>
@@ -13074,7 +13072,7 @@
         <v>1291</v>
       </c>
       <c r="N112" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="O112" t="s">
         <v>1292</v>
@@ -13107,22 +13105,22 @@
         <v>1297</v>
       </c>
       <c r="C113" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D113" t="s">
         <v>1298</v>
       </c>
       <c r="E113" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="F113" t="s">
         <v>1265</v>
       </c>
       <c r="G113" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H113" t="s">
-        <v>76</v>
+        <v>28</v>
       </c>
       <c r="I113" t="s">
         <v>1299</v>
@@ -13173,7 +13171,7 @@
         <v>1306</v>
       </c>
       <c r="C114" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D114" t="s">
         <v>1307</v>
@@ -13185,10 +13183,10 @@
         <v>1308</v>
       </c>
       <c r="G114" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H114" t="s">
-        <v>76</v>
+        <v>28</v>
       </c>
       <c r="I114" t="s">
         <v>1309</v>
@@ -13215,7 +13213,7 @@
         <v>1315</v>
       </c>
       <c r="Q114" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="R114" t="s">
         <v>628</v>
@@ -13239,7 +13237,7 @@
         <v>1316</v>
       </c>
       <c r="C115" t="s">
-        <v>72</v>
+        <v>23</v>
       </c>
       <c r="D115" t="s">
         <v>715</v>
@@ -13251,7 +13249,7 @@
         <v>1317</v>
       </c>
       <c r="G115" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H115" t="s">
         <v>136</v>
@@ -13270,7 +13268,7 @@
         <v>1321</v>
       </c>
       <c r="N115" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="O115" t="s">
         <v>1322</v>
@@ -13303,7 +13301,7 @@
         <v>1324</v>
       </c>
       <c r="C116" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D116" t="s">
         <v>267</v>
@@ -13315,7 +13313,7 @@
         <v>1325</v>
       </c>
       <c r="G116" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H116" t="s">
         <v>100</v>
@@ -13336,7 +13334,7 @@
         <v>1330</v>
       </c>
       <c r="N116" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="O116" t="s">
         <v>1331</v>
@@ -13369,19 +13367,19 @@
         <v>1333</v>
       </c>
       <c r="C117" t="s">
-        <v>72</v>
+        <v>23</v>
       </c>
       <c r="D117" t="s">
         <v>1298</v>
       </c>
       <c r="E117" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="F117" t="s">
         <v>1334</v>
       </c>
       <c r="G117" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H117" t="s">
         <v>100</v>
@@ -13400,7 +13398,7 @@
         <v>1338</v>
       </c>
       <c r="N117" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="O117" t="s">
         <v>1339</v>
@@ -13433,7 +13431,7 @@
         <v>1341</v>
       </c>
       <c r="C118" t="s">
-        <v>72</v>
+        <v>23</v>
       </c>
       <c r="D118" t="s">
         <v>715</v>
@@ -13445,7 +13443,7 @@
         <v>1334</v>
       </c>
       <c r="G118" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H118" t="s">
         <v>136</v>
@@ -13464,7 +13462,7 @@
         <v>1345</v>
       </c>
       <c r="N118" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="O118" t="s">
         <v>1346</v>
@@ -13497,7 +13495,7 @@
         <v>1348</v>
       </c>
       <c r="C119" t="s">
-        <v>72</v>
+        <v>23</v>
       </c>
       <c r="D119" t="s">
         <v>715</v>
@@ -13509,7 +13507,7 @@
         <v>1334</v>
       </c>
       <c r="G119" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H119" t="s">
         <v>136</v>
@@ -13528,7 +13526,7 @@
         <v>1350</v>
       </c>
       <c r="N119" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="O119" t="s">
         <v>1351</v>
@@ -13561,7 +13559,7 @@
         <v>1353</v>
       </c>
       <c r="C120" t="s">
-        <v>72</v>
+        <v>23</v>
       </c>
       <c r="D120" t="s">
         <v>715</v>
@@ -13573,7 +13571,7 @@
         <v>1334</v>
       </c>
       <c r="G120" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H120" t="s">
         <v>136</v>
@@ -13592,7 +13590,7 @@
         <v>1355</v>
       </c>
       <c r="N120" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="O120" t="s">
         <v>1356</v>
@@ -13625,7 +13623,7 @@
         <v>1358</v>
       </c>
       <c r="C121" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D121" t="s">
         <v>793</v>
@@ -13637,7 +13635,7 @@
         <v>1359</v>
       </c>
       <c r="G121" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H121" t="s">
         <v>221</v>
@@ -13691,22 +13689,22 @@
         <v>1370</v>
       </c>
       <c r="C122" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D122" t="s">
         <v>851</v>
       </c>
       <c r="E122" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="F122" t="s">
         <v>1371</v>
       </c>
       <c r="G122" t="s">
+        <v>27</v>
+      </c>
+      <c r="H122" t="s">
         <v>59</v>
-      </c>
-      <c r="H122" t="s">
-        <v>41</v>
       </c>
       <c r="I122" t="s">
         <v>1372</v>
@@ -13724,7 +13722,7 @@
         <v>1376</v>
       </c>
       <c r="N122" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="O122" t="s">
         <v>1377</v>
@@ -13757,7 +13755,7 @@
         <v>1379</v>
       </c>
       <c r="C123" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D123" t="s">
         <v>1380</v>
@@ -13769,7 +13767,7 @@
         <v>1371</v>
       </c>
       <c r="G123" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H123" t="s">
         <v>100</v>
@@ -13823,7 +13821,7 @@
         <v>1391</v>
       </c>
       <c r="C124" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D124" t="s">
         <v>1392</v>
@@ -13835,10 +13833,10 @@
         <v>1371</v>
       </c>
       <c r="G124" t="s">
+        <v>27</v>
+      </c>
+      <c r="H124" t="s">
         <v>59</v>
-      </c>
-      <c r="H124" t="s">
-        <v>41</v>
       </c>
       <c r="I124" t="s">
         <v>1393</v>
@@ -13865,7 +13863,7 @@
         <v>1399</v>
       </c>
       <c r="Q124" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="R124" t="s">
         <v>1400</v>
@@ -13951,22 +13949,22 @@
         <v>1412</v>
       </c>
       <c r="C126" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D126" t="s">
         <v>693</v>
       </c>
       <c r="E126" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="F126" t="s">
         <v>1404</v>
       </c>
       <c r="G126" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H126" t="s">
-        <v>76</v>
+        <v>28</v>
       </c>
       <c r="I126" t="s">
         <v>1413</v>
@@ -13993,7 +13991,7 @@
         <v>1419</v>
       </c>
       <c r="Q126" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="R126" t="s">
         <v>1420</v>
@@ -14017,7 +14015,7 @@
         <v>1423</v>
       </c>
       <c r="C127" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D127" t="s">
         <v>1424</v>
@@ -14029,7 +14027,7 @@
         <v>1404</v>
       </c>
       <c r="G127" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H127" t="s">
         <v>221</v>
@@ -14059,7 +14057,7 @@
         <v>1431</v>
       </c>
       <c r="Q127" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="R127" t="s">
         <v>1432</v>
@@ -14083,19 +14081,19 @@
         <v>1435</v>
       </c>
       <c r="C128" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D128" t="s">
         <v>1436</v>
       </c>
       <c r="E128" t="s">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="F128" t="s">
         <v>1404</v>
       </c>
       <c r="G128" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H128" t="s">
         <v>221</v>
@@ -14116,7 +14114,7 @@
         <v>1441</v>
       </c>
       <c r="N128" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="O128" t="s">
         <v>1442</v>
@@ -14149,19 +14147,19 @@
         <v>1444</v>
       </c>
       <c r="C129" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D129" t="s">
         <v>839</v>
       </c>
       <c r="E129" t="s">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="F129" t="s">
         <v>1404</v>
       </c>
       <c r="G129" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H129" t="s">
         <v>100</v>
@@ -14191,7 +14189,7 @@
         <v>1451</v>
       </c>
       <c r="Q129" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="R129" t="s">
         <v>1452</v>
@@ -14215,7 +14213,7 @@
         <v>1455</v>
       </c>
       <c r="C130" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D130" t="s">
         <v>793</v>
@@ -14227,10 +14225,10 @@
         <v>1404</v>
       </c>
       <c r="G130" t="s">
+        <v>27</v>
+      </c>
+      <c r="H130" t="s">
         <v>59</v>
-      </c>
-      <c r="H130" t="s">
-        <v>41</v>
       </c>
       <c r="I130" t="s">
         <v>1456</v>
@@ -14281,7 +14279,7 @@
         <v>1467</v>
       </c>
       <c r="C131" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D131" t="s">
         <v>149</v>
@@ -14293,7 +14291,7 @@
         <v>1468</v>
       </c>
       <c r="G131" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H131" t="s">
         <v>100</v>
@@ -14314,7 +14312,7 @@
         <v>1473</v>
       </c>
       <c r="N131" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="O131" t="s">
         <v>1474</v>
@@ -14347,7 +14345,7 @@
         <v>1476</v>
       </c>
       <c r="C132" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D132" t="s">
         <v>665</v>
@@ -14359,10 +14357,10 @@
         <v>1477</v>
       </c>
       <c r="G132" t="s">
+        <v>27</v>
+      </c>
+      <c r="H132" t="s">
         <v>59</v>
-      </c>
-      <c r="H132" t="s">
-        <v>41</v>
       </c>
       <c r="I132" t="s">
         <v>1478</v>
@@ -14380,7 +14378,7 @@
         <v>1482</v>
       </c>
       <c r="N132" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="O132" t="s">
         <v>1483</v>
@@ -14413,7 +14411,7 @@
         <v>1485</v>
       </c>
       <c r="C133" t="s">
-        <v>72</v>
+        <v>23</v>
       </c>
       <c r="D133" t="s">
         <v>1486</v>
@@ -14425,10 +14423,10 @@
         <v>1487</v>
       </c>
       <c r="G133" t="s">
+        <v>27</v>
+      </c>
+      <c r="H133" t="s">
         <v>59</v>
-      </c>
-      <c r="H133" t="s">
-        <v>41</v>
       </c>
       <c r="I133" t="s">
         <v>1488</v>
@@ -14444,7 +14442,7 @@
         <v>1491</v>
       </c>
       <c r="N133" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="O133" t="s">
         <v>1492</v>
@@ -14477,19 +14475,19 @@
         <v>1494</v>
       </c>
       <c r="C134" t="s">
-        <v>72</v>
+        <v>23</v>
       </c>
       <c r="D134" t="s">
         <v>1495</v>
       </c>
       <c r="E134" t="s">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="F134" t="s">
         <v>1487</v>
       </c>
       <c r="G134" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H134" t="s">
         <v>100</v>
@@ -14508,7 +14506,7 @@
         <v>1499</v>
       </c>
       <c r="N134" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="O134" t="s">
         <v>1500</v>
@@ -14547,13 +14545,13 @@
         <v>421</v>
       </c>
       <c r="E135" t="s">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="F135" t="s">
         <v>1503</v>
       </c>
       <c r="G135" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H135" t="s">
         <v>100</v>
@@ -14611,7 +14609,7 @@
       </c>
       <c r="D136"/>
       <c r="E136" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="F136" t="s">
         <v>1512</v>
@@ -14632,7 +14630,7 @@
       <c r="L136"/>
       <c r="M136"/>
       <c r="N136" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="O136" t="s">
         <v>1516</v>
@@ -14641,7 +14639,7 @@
         <v>1517</v>
       </c>
       <c r="Q136" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="R136" t="s">
         <v>1518</v>
@@ -14727,19 +14725,19 @@
         <v>1533</v>
       </c>
       <c r="C138" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D138" t="s">
         <v>1534</v>
       </c>
       <c r="E138" t="s">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="F138" t="s">
         <v>1535</v>
       </c>
       <c r="G138" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H138" t="s">
         <v>100</v>
@@ -14760,7 +14758,7 @@
         <v>1540</v>
       </c>
       <c r="N138" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="O138" t="s">
         <v>1541</v>
@@ -14793,19 +14791,19 @@
         <v>1546</v>
       </c>
       <c r="C139" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D139" t="s">
         <v>1547</v>
       </c>
       <c r="E139" t="s">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="F139" t="s">
         <v>1548</v>
       </c>
       <c r="G139" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H139" t="s">
         <v>221</v>
@@ -14826,7 +14824,7 @@
         <v>1553</v>
       </c>
       <c r="N139" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="O139" t="s">
         <v>1554</v>
@@ -14859,19 +14857,19 @@
         <v>1559</v>
       </c>
       <c r="C140" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D140" t="s">
         <v>194</v>
       </c>
       <c r="E140" t="s">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="F140" t="s">
         <v>1548</v>
       </c>
       <c r="G140" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="H140" t="s">
         <v>100</v>
@@ -14892,7 +14890,7 @@
         <v>1564</v>
       </c>
       <c r="N140" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="O140" t="s">
         <v>1565</v>
@@ -14931,13 +14929,13 @@
         <v>599</v>
       </c>
       <c r="E141" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="F141" t="s">
         <v>1568</v>
       </c>
       <c r="G141" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="H141" t="s">
         <v>221</v>
@@ -14967,7 +14965,7 @@
         <v>1575</v>
       </c>
       <c r="Q141" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="R141" t="s">
         <v>116</v>
@@ -14991,19 +14989,19 @@
         <v>1576</v>
       </c>
       <c r="C142" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D142" t="s">
         <v>1577</v>
       </c>
       <c r="E142" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="F142" t="s">
         <v>1568</v>
       </c>
       <c r="G142" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H142" t="s">
         <v>100</v>
@@ -15057,7 +15055,7 @@
         <v>1588</v>
       </c>
       <c r="C143" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D143" t="s">
         <v>1589</v>
@@ -15069,10 +15067,10 @@
         <v>1568</v>
       </c>
       <c r="G143" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H143" t="s">
-        <v>76</v>
+        <v>28</v>
       </c>
       <c r="I143" t="s">
         <v>1591</v>
@@ -15090,7 +15088,7 @@
         <v>1595</v>
       </c>
       <c r="N143" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="O143" t="s">
         <v>1596</v>
@@ -15099,7 +15097,7 @@
         <v>1597</v>
       </c>
       <c r="Q143" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="R143" t="s">
         <v>1598</v>
@@ -15123,7 +15121,7 @@
         <v>1601</v>
       </c>
       <c r="C144" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D144" t="s">
         <v>564</v>
@@ -15135,7 +15133,7 @@
         <v>1568</v>
       </c>
       <c r="G144" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H144" t="s">
         <v>100</v>
@@ -15156,7 +15154,7 @@
         <v>1606</v>
       </c>
       <c r="N144" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="O144" t="s">
         <v>1607</v>
@@ -15189,19 +15187,19 @@
         <v>1612</v>
       </c>
       <c r="C145" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D145" t="s">
         <v>1577</v>
       </c>
       <c r="E145" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="F145" t="s">
         <v>1568</v>
       </c>
       <c r="G145" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H145" t="s">
         <v>221</v>
@@ -15222,7 +15220,7 @@
         <v>1617</v>
       </c>
       <c r="N145" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="O145" t="s">
         <v>1618</v>
@@ -15255,22 +15253,22 @@
         <v>1623</v>
       </c>
       <c r="C146" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D146" t="s">
         <v>1286</v>
       </c>
       <c r="E146" t="s">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="F146" t="s">
         <v>1568</v>
       </c>
       <c r="G146" t="s">
+        <v>27</v>
+      </c>
+      <c r="H146" t="s">
         <v>59</v>
-      </c>
-      <c r="H146" t="s">
-        <v>41</v>
       </c>
       <c r="I146" t="s">
         <v>1624</v>
@@ -15288,7 +15286,7 @@
         <v>1628</v>
       </c>
       <c r="N146" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="O146" t="s">
         <v>1629</v>
@@ -15297,7 +15295,7 @@
         <v>1630</v>
       </c>
       <c r="Q146" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="R146" t="s">
         <v>1631</v>
@@ -15321,22 +15319,22 @@
         <v>1634</v>
       </c>
       <c r="C147" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D147" t="s">
         <v>1635</v>
       </c>
       <c r="E147" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="F147" t="s">
         <v>1636</v>
       </c>
       <c r="G147" t="s">
+        <v>27</v>
+      </c>
+      <c r="H147" t="s">
         <v>59</v>
-      </c>
-      <c r="H147" t="s">
-        <v>41</v>
       </c>
       <c r="I147" t="s">
         <v>1637</v>
@@ -15354,7 +15352,7 @@
         <v>1641</v>
       </c>
       <c r="N147" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="O147" t="s">
         <v>1642</v>
@@ -15363,7 +15361,7 @@
         <v>1643</v>
       </c>
       <c r="Q147" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="R147" t="s">
         <v>962</v>
@@ -15387,7 +15385,7 @@
         <v>1644</v>
       </c>
       <c r="C148" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D148" t="s">
         <v>465</v>
@@ -15399,10 +15397,10 @@
         <v>1645</v>
       </c>
       <c r="G148" t="s">
+        <v>27</v>
+      </c>
+      <c r="H148" t="s">
         <v>59</v>
-      </c>
-      <c r="H148" t="s">
-        <v>41</v>
       </c>
       <c r="I148" t="s">
         <v>1646</v>
@@ -15420,7 +15418,7 @@
         <v>1650</v>
       </c>
       <c r="N148" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="O148" t="s">
         <v>1651</v>
@@ -15453,19 +15451,19 @@
         <v>1653</v>
       </c>
       <c r="C149" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D149" t="s">
         <v>1654</v>
       </c>
       <c r="E149" t="s">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="F149" t="s">
         <v>1655</v>
       </c>
       <c r="G149" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="H149" t="s">
         <v>221</v>
@@ -15486,7 +15484,7 @@
         <v>1660</v>
       </c>
       <c r="N149" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="O149" t="s">
         <v>1661</v>
@@ -15525,13 +15523,13 @@
         <v>1664</v>
       </c>
       <c r="E150" t="s">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="F150" t="s">
         <v>1665</v>
       </c>
       <c r="G150" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="H150" t="s">
         <v>221</v>
@@ -15585,7 +15583,7 @@
         <v>1673</v>
       </c>
       <c r="C151" t="s">
-        <v>72</v>
+        <v>23</v>
       </c>
       <c r="D151" t="s">
         <v>793</v>
@@ -15597,7 +15595,7 @@
         <v>1665</v>
       </c>
       <c r="G151" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H151" t="s">
         <v>100</v>
@@ -15616,7 +15614,7 @@
         <v>1677</v>
       </c>
       <c r="N151" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="O151" t="s">
         <v>1678</v>
@@ -15649,19 +15647,19 @@
         <v>1680</v>
       </c>
       <c r="C152" t="s">
-        <v>72</v>
+        <v>23</v>
       </c>
       <c r="D152" t="s">
         <v>421</v>
       </c>
       <c r="E152" t="s">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="F152" t="s">
         <v>1681</v>
       </c>
       <c r="G152" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H152" t="s">
         <v>100</v>
@@ -15680,7 +15678,7 @@
         <v>1685</v>
       </c>
       <c r="N152" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="O152" t="s">
         <v>1686</v>
@@ -15713,7 +15711,7 @@
         <v>1688</v>
       </c>
       <c r="C153" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D153" t="s">
         <v>1689</v>
@@ -15723,7 +15721,7 @@
         <v>1690</v>
       </c>
       <c r="G153" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H153" t="s">
         <v>221</v>
@@ -15777,7 +15775,7 @@
         <v>1701</v>
       </c>
       <c r="C154" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D154" t="s">
         <v>1002</v>
@@ -15789,7 +15787,7 @@
         <v>1702</v>
       </c>
       <c r="G154" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H154" t="s">
         <v>100</v>
@@ -15810,7 +15808,7 @@
         <v>1707</v>
       </c>
       <c r="N154" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="O154" t="s">
         <v>1708</v>
@@ -15819,7 +15817,7 @@
         <v>1709</v>
       </c>
       <c r="Q154" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="R154" t="s">
         <v>1710</v>
@@ -15843,19 +15841,19 @@
         <v>1713</v>
       </c>
       <c r="C155" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D155" t="s">
         <v>826</v>
       </c>
       <c r="E155" t="s">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="F155" t="s">
         <v>1702</v>
       </c>
       <c r="G155" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H155" t="s">
         <v>221</v>
@@ -15876,7 +15874,7 @@
         <v>1718</v>
       </c>
       <c r="N155" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="O155" t="s">
         <v>1719</v>
@@ -15885,7 +15883,7 @@
         <v>1720</v>
       </c>
       <c r="Q155" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="R155" t="s">
         <v>1721</v>
@@ -15909,19 +15907,19 @@
         <v>1724</v>
       </c>
       <c r="C156" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D156" t="s">
         <v>1725</v>
       </c>
       <c r="E156" t="s">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="F156" t="s">
         <v>1726</v>
       </c>
       <c r="G156" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="H156" t="s">
         <v>978</v>
@@ -15942,7 +15940,7 @@
         <v>1731</v>
       </c>
       <c r="N156" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="O156" t="s">
         <v>1732</v>
@@ -15951,7 +15949,7 @@
         <v>1733</v>
       </c>
       <c r="Q156" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="R156" t="s">
         <v>1734</v>
@@ -15975,19 +15973,19 @@
         <v>1737</v>
       </c>
       <c r="C157" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D157" t="s">
         <v>1132</v>
       </c>
       <c r="E157" t="s">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="F157" t="s">
         <v>1726</v>
       </c>
       <c r="G157" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H157" t="s">
         <v>978</v>
@@ -16008,7 +16006,7 @@
         <v>1731</v>
       </c>
       <c r="N157" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="O157" t="s">
         <v>1738</v>
@@ -16017,7 +16015,7 @@
         <v>1739</v>
       </c>
       <c r="Q157" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="R157" t="s">
         <v>1740</v>
@@ -16041,7 +16039,7 @@
         <v>1743</v>
       </c>
       <c r="C158" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D158" t="s">
         <v>1744</v>
@@ -16053,10 +16051,10 @@
         <v>1745</v>
       </c>
       <c r="G158" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H158" t="s">
-        <v>76</v>
+        <v>28</v>
       </c>
       <c r="I158" t="s">
         <v>1746</v>
@@ -16074,7 +16072,7 @@
         <v>1750</v>
       </c>
       <c r="N158" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="O158" t="s">
         <v>1751</v>
@@ -16083,7 +16081,7 @@
         <v>1752</v>
       </c>
       <c r="Q158" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="R158" t="s">
         <v>156</v>
@@ -16107,19 +16105,19 @@
         <v>1753</v>
       </c>
       <c r="C159" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D159" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="E159" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="F159" t="s">
         <v>1754</v>
       </c>
       <c r="G159" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="H159" t="s">
         <v>100</v>
@@ -16140,7 +16138,7 @@
         <v>1759</v>
       </c>
       <c r="N159" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="O159" t="s">
         <v>1760</v>
@@ -16173,7 +16171,7 @@
         <v>1765</v>
       </c>
       <c r="C160" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D160" t="s">
         <v>793</v>
@@ -16185,7 +16183,7 @@
         <v>1766</v>
       </c>
       <c r="G160" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H160" t="s">
         <v>100</v>
@@ -16206,7 +16204,7 @@
         <v>1771</v>
       </c>
       <c r="N160" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="O160" t="s">
         <v>1772</v>
@@ -16239,7 +16237,7 @@
         <v>1777</v>
       </c>
       <c r="C161" t="s">
-        <v>72</v>
+        <v>23</v>
       </c>
       <c r="D161" t="s">
         <v>1778</v>
@@ -16251,7 +16249,7 @@
         <v>1766</v>
       </c>
       <c r="G161" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H161" t="s">
         <v>100</v>
@@ -16270,7 +16268,7 @@
         <v>1782</v>
       </c>
       <c r="N161" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="O161" t="s">
         <v>1783</v>
@@ -16279,7 +16277,7 @@
         <v>1784</v>
       </c>
       <c r="Q161" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="R161" t="s">
         <v>1774</v>
@@ -16303,7 +16301,7 @@
         <v>1785</v>
       </c>
       <c r="C162" t="s">
-        <v>72</v>
+        <v>23</v>
       </c>
       <c r="D162" t="s">
         <v>1778</v>
@@ -16315,7 +16313,7 @@
         <v>1766</v>
       </c>
       <c r="G162" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H162" t="s">
         <v>100</v>
@@ -16334,7 +16332,7 @@
         <v>1789</v>
       </c>
       <c r="N162" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="O162" t="s">
         <v>1790</v>
@@ -16367,7 +16365,7 @@
         <v>1792</v>
       </c>
       <c r="C163" t="s">
-        <v>72</v>
+        <v>23</v>
       </c>
       <c r="D163" t="s">
         <v>1793</v>
@@ -16379,7 +16377,7 @@
         <v>1794</v>
       </c>
       <c r="G163" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H163" t="s">
         <v>100</v>
@@ -16398,7 +16396,7 @@
         <v>1798</v>
       </c>
       <c r="N163" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="O163" t="s">
         <v>1799</v>
@@ -16431,19 +16429,19 @@
         <v>1801</v>
       </c>
       <c r="C164" t="s">
-        <v>72</v>
+        <v>23</v>
       </c>
       <c r="D164" t="s">
         <v>1577</v>
       </c>
       <c r="E164" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="F164" t="s">
         <v>1802</v>
       </c>
       <c r="G164" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H164" t="s">
         <v>221</v>
@@ -16462,7 +16460,7 @@
         <v>1806</v>
       </c>
       <c r="N164" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="O164" t="s">
         <v>1807</v>
@@ -16471,7 +16469,7 @@
         <v>1808</v>
       </c>
       <c r="Q164" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="R164" t="s">
         <v>1809</v>
@@ -16506,7 +16504,7 @@
       </c>
       <c r="G165"/>
       <c r="H165" t="s">
-        <v>76</v>
+        <v>28</v>
       </c>
       <c r="I165" t="s">
         <v>1814</v>
@@ -16524,7 +16522,7 @@
         <v>1818</v>
       </c>
       <c r="N165" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="O165" t="s">
         <v>1819</v>

--- a/Objets_parlementaires_Jura.xlsx
+++ b/Objets_parlementaires_Jura.xlsx
@@ -122,21 +122,144 @@
     <t xml:space="preserve">Élu</t>
   </si>
   <si>
+    <t xml:space="preserve">26.3563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ip.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dobler Loïc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVEK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wie sieht bei der Post die geografische Verteilung der Arbeitsplätze aus?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quelle répartition géographique des emplois postaux ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qual è la ripartizione geografica dei posti di lavoro nel settore postale?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;La Confédération est l'actionnaire unique de La Poste Suisse SA et lui assigne tous les quatre ans des objectifs stratégiques (art. 7 LOP). Les objectifs 2025-2028, adoptés le 29 janvier 2025, ne contiennent aucune exigence de répartition géographique des emplois entre les cantons. L'objectif 3.1 en matière de personnel demande une politique progressiste en matière de personnel et une augmentation de la proportion de femmes aux postes de cadres. Les rapports annuels de réalisation ne comportent aucun indicateur territorial relatif à l'emploi.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Cette lacune est préoccupante. La Poste restructure en effet profondément son réseau depuis plusieurs années : fermetures d'offices et transformation en agences dans des commerces privés. Les cantons périphériques sont les plus touchés. Paradoxalement, les objectifs stratégiques prévoient déjà une logique territoriale pour les prestations, l'accessibilité au service universel étant mesurée au niveau cantonal. Il n'y a aucune raison que cette logique ne s'applique pas aussi aux emplois.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Les emplois des entreprises dont la Confédération est propriétaire sont généralement stables et soumis à des conditions conventionnelles attractives. Ils devraient se développer sur l'ensemble du territoire, et a fortiori dans les régions où ces mêmes entreprises suppriment des postes par ailleurs.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Le DETEC doit par ailleurs soumettre un projet de révision de la législation postale d'ici fin juin 2026, ce qui rend la présente interpellation particulièrement actuelle.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Je pose dès lors les questions suivantes au Conseil fédéral :&lt;/p&gt;&lt;ol&gt;&lt;li&gt;Quelle est l'évolution des emplois à La Poste (en EPT) par canton sur les dix dernières années ?&lt;/li&gt;&lt;li&gt;Quelle est l'évolution du nombre d'offices par canton depuis 2010 ?&lt;/li&gt;&lt;li&gt;Pour quelle raison les objectifs stratégiques ne comportent-ils aucun indicateur de répartition géographique des emplois ?&lt;/li&gt;&lt;li&gt;Le Conseil fédéral considère-t-il la répartition territoriale des emplois des entités paraétatiques comme relevant de sa responsabilité ?&lt;/li&gt;&lt;li&gt;Dans le cadre de la révision législative en cours ou à venir, est-il prêt à introduire un tel indicateur pour La Poste, les CFF et Swisscom ?&lt;/li&gt;&lt;/ol&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Der Bund ist Alleinaktionär der Schweizerischen&amp;nbsp;Post&amp;nbsp;AG und legt alle vier Jahre die strategischen Ziele für sie fest&amp;nbsp;(Art.&amp;nbsp;7 des Postorganisationsgesetzes). Die am 29.&amp;nbsp;Januar&amp;nbsp;2025 verabschiedeten Ziele für den Zeitraum 2025–2028 enthalten keine Vorgaben zur geografischen Verteilung der Arbeitsplätze auf die Kantone. Ziffer&amp;nbsp;3.1 sieht eine fortschrittliche Personalpolitik und eine Erhöhung des Frauenanteils in Kaderpositionen vor. Die jährlichen Berichte über die Erreichung der strategischen Ziele enthalten keinen Indikator zur geografischen Verteilung der Arbeitsplätze.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Diese Lücke gibt Anlass zur Sorge. Die Post nimmt seit mehreren Jahren eine tiefgreifende Umstrukturierung ihres Netzes vor: Poststellen werden geschlossen und in Agenturen in privaten Geschäften umgewandelt. Die Randkantone sind am stärksten davon betroffen. Paradoxerweise ist in den strategischen Zielen bereits ein geografischer Ansatz für die Leistungen vorgesehen, indem die Erreichbarkeit der Grundversorgung auf kantonaler Ebene gemessen wird. Es gibt keinen Grund, warum diese Logik nicht auch für die Arbeitsplätze gelten sollte.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Unternehmen, die im Eigentum des Bundes sind, bieten in der Regel sichere Arbeitsplätze mit attraktiven Anstellungsbedingungen an. Solche Arbeitsplätze sollten schweizweit gefördert werden, und erst recht in den Regionen, in denen dieselben Unternehmen Stellen abbauen.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Das Eidgenössische Departement für Umwelt, Verkehr, Energie und Kommunikation muss im Übrigen bis Ende Juni&amp;nbsp;2026 eine Vernehmlassungsvorlage für eine Revision der Postgesetzgebung unterbreiten, was der vorliegenden Interpellation besondere Aktualität verleiht.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Ich bitte den Bundesrat, folgende Fragen zu beantworten:&lt;/p&gt;&lt;ol&gt;&lt;li&gt;Wie hat sich die Anzahl der Arbeitsplätze bei der Post&amp;nbsp;(in Vollzeitäquivalenten) in den einzelnen Kantonen in den letzten zehn Jahren entwickelt?&lt;/li&gt;&lt;li&gt;Wie hat sich die Anzahl der Poststellen pro Kanton seit 2010 entwickelt?&lt;/li&gt;&lt;li&gt;Weshalb enthalten die strategischen Ziele keinen Indikator zur geografischen Verteilung der Arbeitsplätze?&lt;/li&gt;&lt;li&gt;Ist der Bundesrat der Ansicht, dass die geografische Verteilung der Arbeitsplätze in bundesnahen Betrieben in seiner Verantwortung liegt?&lt;/li&gt;&lt;li&gt;Ist der Bundesrat bereit, im Rahmen der laufenden oder anstehenden Revision der Postgesetzgebung einen solchen Indikator für die Post, die SBB und die Swisscom einzuführen?&lt;/li&gt;&lt;/ol&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Erledigt / Liquidé</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Titre uniquement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staatspolitik|Wirtschaft|Medien und Kommunikation|Beschäftigung und Arbeit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politique d'Etat|Économie|Médias et communication|Emploi et travail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politica nazionale|Economia|Media e comunicazione|Occupazione e lavoro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EDI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arztzeugnisse für Kurzabwesenheiten. Unnötige Kosten für die obligatorische Krankenversicherung?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Certificats médicaux pour courtes absences. Un coût inutile pour la LAMal ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Certificati medici per assenze brevi. Un costo inutile per la LAMal?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;De nombreux employeurs exigent un certificat médical dès le premier ou le deuxième jour d'absence de leurs employées et employés, y compris pour des maladies bénignes de courte durée. Cette pratique contraint les salarié·e·s à consulter un médecin ou une médecin non pas pour des raisons thérapeutiques, mais pour satisfaire une exigence administrative. Ces consultations sont remboursées par la LAMal, après déduction de la franchise et de la quote-part. Elles génèrent donc des coûts réels pour les salarié·e·s et pour le système de santé, sans aucune valeur médicale ajoutée.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Le Code des obligations ne fixe aucun délai minimal avant qu'un employeur puisse exiger un tel certificat, laissant une liberté totale sur ce point. Certaines conventions collectives de travail prévoient des règles plus protectrices, mais elles ne couvrent pas l'ensemble des travailleuses et travailleurs.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Si un employeur juge nécessaire d'exiger une attestation médicale avant tout délai raisonnable, il est logique que les frais qui en découlent lui incombent. Il n'appartient pas à l'assurance obligatoire des soins, financée par l'ensemble des assuré·e·s, de couvrir des dépenses qui résultent d'une exigence administrative privée. De leur côté, les salarié·e·s concerné·e·s contribuent financièrement au travers de leur franchise et quote-part. À l'heure où la maîtrise des coûts de la santé est une priorité politique affichée, cette source de dépenses évitable mérite d'être examinée.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Je pose les questions suivantes au Conseil fédéral :&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;ol&gt;&lt;li&gt;Dispose-t-il de données sur le nombre de consultations médicales annuelles dont le seul motif est la délivrance d'un certificat exigé par un employeur ou une employeuse pour une courte absence ?&lt;/li&gt;&lt;li&gt;Quel est le coût estimé de ces consultations pour la LAMal ?&lt;/li&gt;&lt;li&gt;Est-il prêt à examiner une réglementation fixant un délai minimal avant qu'un employeur puisse exiger un certificat médical ?&lt;/li&gt;&lt;li&gt;Est-il prêt à examiner une modification légale permettant de mettre les frais de ces consultations à la charge de l'employeur ou de l'employeuse qui les exige, plutôt qu'à celle de l'assurance obligatoire des soins ?&lt;/li&gt;&lt;/ol&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Viele Arbeitgeber verlangen von ihren Angestellten bei Krankheit bereits ab dem ersten oder zweiten Abwesenheitstag ein Arztzeugnis, auch bei leichter, kurzer Krankheit. Diese Praxis zwingt die Arbeitnehmerinnen und Arbeitnehmer dazu, einen Arzt oder eine Ärztin nicht wegen eines medizinischen Problems aufzusuchen, sondern um einer administrativen Vorgabe des Arbeitgebers nachzukommen. Diese Konsultationen werden nach Abzug der Franchise und des Selbstbehalts von der obligatorischen Krankenversicherung vergütet. Sie generieren somit tatsächliche Kosten für die Arbeitnehmerinnen und Arbeitnehmer sowie für das Gesundheitssystem, ohne dass sie einen medizinischen Mehrwert bieten.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Das Obligationenrecht legt keine Mindestfrist fest, nach deren Ablauf ein Arbeitgeber ein Arztzeugnis verlangen kann – diesbezüglich herrscht völlige Freiheit. Einige Gesamtarbeitsverträge sehen strengere Vorschriften zum Schutz der Arbeitnehmerinnen und Arbeitnehmer vor, doch diese gelten nicht für die Gesamtheit der Arbeitnehmerinnen und Arbeitnehmer.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Wenn ein Arbeitgeber es für notwendig erachtet, bereits vor Ablauf einer angemessenen Frist ein Arztzeugnis zu verlangen, wäre es nur folgerichtig, wenn die damit verbundenen Kosten zu seinen Lasten gingen. Es ist nicht Aufgabe der obligatorischen Krankenpflegeversicherung, die von allen Versicherten finanziert wird, Kosten zu übernehmen, die sich aus einer privaten administrativen Forderung ergeben. Die betroffenen Arbeitnehmerinnen und Arbeitnehmer leisten ihrerseits einen finanziellen Beitrag in Form ihrer Franchise und ihres Selbstbehalts. In einer Zeit, in der die Kostendämpfung im Gesundheitswesen eine erklärte politische Priorität ist, sollte dieser vermeidbare Kostenfaktor genauer unter die Lupe genommen werden.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Ich bitte den Bundesrat, folgende Fragen zu beantworten:&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;ol&gt;&lt;li&gt;Verfügt der Bundesrat über Daten zur Anzahl der jährlichen Arztbesuche, deren einziger Grund die Ausstellung eines Arztzeugnisses ist, die ein Arbeitgeber für eine Kurzabwesenheit verlangt?&lt;/li&gt;&lt;li&gt;Wie hoch werden die Kosten dieser Konsultationen für die obligatorische Krankenversicherung geschätzt?&lt;/li&gt;&lt;li&gt;Ist der Bundesrat bereit, eine Regelung zu prüfen, die eine Mindestfrist festlegt, bevor ein Arbeitgeber ein Arztzeugnis verlangen darf?&lt;/li&gt;&lt;li&gt;Ist der Bundesrat bereit, eine Gesetzesänderung zu prüfen, die es ermöglicht, die Kosten für diese Konsultationen dem entsprechenden Arbeitgeber anzulasten, anstatt der obligatorischen Krankenversicherung?&lt;/li&gt;&lt;/ol&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beschäftigung und Arbeit|Zivilrecht|Gesundheit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emploi et travail|Droit civil|Santé</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Occupazione e lavoro|Diritto civile|Salute</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Friedli Esther</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UDC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EJPD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Von Dänemark lernen. Bei längerfristigen Freiheitsstrafen muss die obligatorische Landesverweisung tatsächlich obligatorisch sein</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S'inspirer du Danemark. En cas de peines privatives de liberté de longue durée, l'expulsion obligatoire doit être réellement obligatoire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Imparare dalla Danimarca. Espulsione obbligatoria in caso di pene detentive di lunga durata</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé de présenter les modifications législatives nécessaires afin que les étrangers criminels condamnés à une peine privative de liberté d’un an ou plus – qu'elle soit ferme ou assortie d’un sursis total ou partiel – fassent dans tous les cas l'objet d'une expulsion, qui devra obligatoirement être exécutée.&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, die erforderlichen Gesetzesanpassungen vorzulegen, so dass für kriminelle Ausländer bei einer längerfristigen Freiheitsstrafe ab einem Jahr – unabhängig davon, ob diese unbedingt, teilbedingt oder bedingt ausfällt – in jedem Fall zwingend eine Landesverweisung angeordnet und vollzogen werden muss.&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strafrecht|Migration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Droit pénal|Politique migratoire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diritto penale|Migrazione</t>
+  </si>
+  <si>
     <t xml:space="preserve">26.4418</t>
   </si>
   <si>
-    <t xml:space="preserve">Ip.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dobler Loïc</t>
-  </si>
-  <si>
     <t xml:space="preserve">2026-10-01</t>
   </si>
   <si>
-    <t xml:space="preserve">NR</t>
-  </si>
-  <si>
     <t xml:space="preserve">Primes maladie : le ping-pong des responsabilités</t>
   </si>
   <si>
@@ -167,9 +290,6 @@
     <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20264338</t>
   </si>
   <si>
-    <t xml:space="preserve">Titre uniquement</t>
-  </si>
-  <si>
     <t xml:space="preserve">Sicherheitspolitik|Sozialer Schutz</t>
   </si>
   <si>
@@ -227,9 +347,6 @@
     <t xml:space="preserve">&lt;p&gt;Die eidgenössischen Räte haben das Mercosur-Abkommen genehmigt, überzeugt durch zusätzliche Mittel in Höhe von 517&amp;nbsp;Millionen&amp;nbsp;Franken für die Landwirtschaft für die Jahre&amp;nbsp;2028 bis 2033. Ein Detail verblieb jedoch in der Debatte ungeklärt: Für die halbe Milliarde besteht bislang keine konkrete Finanzierungsquelle.&lt;br&gt;Kann der Bundesrat bereits jetzt angeben, woher die erwähnten Mittel stammen sollen und welche Positionen des Bundeshaushalts betroffen sein werden?&lt;/p&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">Erledigt / Liquidé</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20267901</t>
   </si>
   <si>
@@ -407,9 +524,6 @@
     <t xml:space="preserve">26.7688</t>
   </si>
   <si>
-    <t xml:space="preserve">UVEK</t>
-  </si>
-  <si>
     <t xml:space="preserve">Schienengüterverkehr: Wird die Westschweiz geopfert? </t>
   </si>
   <si>
@@ -515,48 +629,27 @@
     <t xml:space="preserve">2026-03-16</t>
   </si>
   <si>
-    <t xml:space="preserve">EJPD</t>
-  </si>
-  <si>
     <t xml:space="preserve">Von Dänemark lernen. Bei längerfristigen Freiheitsstrafen muss die obligatorische Landesverweisung obligatorisch sein</t>
   </si>
   <si>
     <t xml:space="preserve">Inspirons-nous du Danemark. Rendons réellement obligatoire l'expulsion en cas de peine privative de liberté de longue durée</t>
   </si>
   <si>
-    <t xml:space="preserve">Imparare dalla Danimarca. Espulsione obbligatoria in caso di pene detentive di lunga durata</t>
-  </si>
-  <si>
     <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé de présenter les modifications législatives nécessaires pour que lorsqu’un délinquant étranger est condamné à une peine privative de liberté de longue durée (un an au moins), que cette peine soit ferme ou assortie d’un sursis ou d’un sursis partiel, une expulsion soit obligatoirement ordonnée et exécutée.&amp;nbsp;&lt;/p&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, die erforderlichen Gesetzesanpassungen vorzulegen, so dass für kriminelle Ausländer bei einer längerfristigen Freiheitsstrafe ab einem Jahr – unabhängig davon, ob diese unbedingt, teilbedingt oder bedingt ausfällt – in jedem Fall zwingend eine Landesverweisung angeordnet und vollzogen werden muss.&amp;nbsp;&lt;/p&gt;</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263131</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263131</t>
   </si>
   <si>
-    <t xml:space="preserve">Strafrecht|Migration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Droit pénal|Politique migratoire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diritto penale|Migrazione</t>
-  </si>
-  <si>
     <t xml:space="preserve">26.4146</t>
   </si>
   <si>
     <t xml:space="preserve">Stettler Thomas</t>
   </si>
   <si>
-    <t xml:space="preserve">UDC</t>
-  </si>
-  <si>
     <t xml:space="preserve">2026-09-16</t>
   </si>
   <si>
@@ -767,9 +860,6 @@
     <t xml:space="preserve">PEV</t>
   </si>
   <si>
-    <t xml:space="preserve">EDI</t>
-  </si>
-  <si>
     <t xml:space="preserve">Von Zielkonflikten zur Quadratur des Kreises. Nutzen, Kosten, Wettbewerbsfähigkeit bei Life Science</t>
   </si>
   <si>
@@ -800,30 +890,6 @@
     <t xml:space="preserve">Economia|Scienza e ricerca|Imposte|Salute</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Friedli Esther</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Von Dänemark lernen. Bei längerfristigen Freiheitsstrafen muss die obligatorische Landesverweisung tatsächlich obligatorisch sein</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S'inspirer du Danemark. En cas de peines privatives de liberté de longue durée, l'expulsion obligatoire doit être réellement obligatoire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé de présenter les modifications législatives nécessaires afin que les étrangers criminels condamnés à une peine privative de liberté d’un an ou plus – qu'elle soit ferme ou assortie d’un sursis total ou partiel – fassent dans tous les cas l'objet d'une expulsion, qui devra obligatoirement être exécutée.&amp;nbsp;&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263571</t>
-  </si>
-  <si>
     <t xml:space="preserve">26.3597</t>
   </si>
   <si>
@@ -866,39 +932,6 @@
     <t xml:space="preserve">2026-09-07</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arztzeugnisse für Kurzabwesenheiten. Unnötige Kosten für die obligatorische Krankenversicherung?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Certificats médicaux pour courtes absences. Un coût inutile pour la LAMal ?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Certificati medici per assenze brevi. Un costo inutile per la LAMal?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;De nombreux employeurs exigent un certificat médical dès le premier ou le deuxième jour d'absence de leurs employées et employés, y compris pour des maladies bénignes de courte durée. Cette pratique contraint les salarié·e·s à consulter un médecin ou une médecin non pas pour des raisons thérapeutiques, mais pour satisfaire une exigence administrative. Ces consultations sont remboursées par la LAMal, après déduction de la franchise et de la quote-part. Elles génèrent donc des coûts réels pour les salarié·e·s et pour le système de santé, sans aucune valeur médicale ajoutée.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Le Code des obligations ne fixe aucun délai minimal avant qu'un employeur puisse exiger un tel certificat, laissant une liberté totale sur ce point. Certaines conventions collectives de travail prévoient des règles plus protectrices, mais elles ne couvrent pas l'ensemble des travailleuses et travailleurs.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Si un employeur juge nécessaire d'exiger une attestation médicale avant tout délai raisonnable, il est logique que les frais qui en découlent lui incombent. Il n'appartient pas à l'assurance obligatoire des soins, financée par l'ensemble des assuré·e·s, de couvrir des dépenses qui résultent d'une exigence administrative privée. De leur côté, les salarié·e·s concerné·e·s contribuent financièrement au travers de leur franchise et quote-part. À l'heure où la maîtrise des coûts de la santé est une priorité politique affichée, cette source de dépenses évitable mérite d'être examinée.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Je pose les questions suivantes au Conseil fédéral :&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;ol&gt;&lt;li&gt;Dispose-t-il de données sur le nombre de consultations médicales annuelles dont le seul motif est la délivrance d'un certificat exigé par un employeur ou une employeuse pour une courte absence ?&lt;/li&gt;&lt;li&gt;Quel est le coût estimé de ces consultations pour la LAMal ?&lt;/li&gt;&lt;li&gt;Est-il prêt à examiner une réglementation fixant un délai minimal avant qu'un employeur puisse exiger un certificat médical ?&lt;/li&gt;&lt;li&gt;Est-il prêt à examiner une modification légale permettant de mettre les frais de ces consultations à la charge de l'employeur ou de l'employeuse qui les exige, plutôt qu'à celle de l'assurance obligatoire des soins ?&lt;/li&gt;&lt;/ol&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Viele Arbeitgeber verlangen von ihren Angestellten bei Krankheit bereits ab dem ersten oder zweiten Abwesenheitstag ein Arztzeugnis, auch bei leichter, kurzer Krankheit. Diese Praxis zwingt die Arbeitnehmerinnen und Arbeitnehmer dazu, einen Arzt oder eine Ärztin nicht wegen eines medizinischen Problems aufzusuchen, sondern um einer administrativen Vorgabe des Arbeitgebers nachzukommen. Diese Konsultationen werden nach Abzug der Franchise und des Selbstbehalts von der obligatorischen Krankenversicherung vergütet. Sie generieren somit tatsächliche Kosten für die Arbeitnehmerinnen und Arbeitnehmer sowie für das Gesundheitssystem, ohne dass sie einen medizinischen Mehrwert bieten.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Das Obligationenrecht legt keine Mindestfrist fest, nach deren Ablauf ein Arbeitgeber ein Arztzeugnis verlangen kann – diesbezüglich herrscht völlige Freiheit. Einige Gesamtarbeitsverträge sehen strengere Vorschriften zum Schutz der Arbeitnehmerinnen und Arbeitnehmer vor, doch diese gelten nicht für die Gesamtheit der Arbeitnehmerinnen und Arbeitnehmer.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Wenn ein Arbeitgeber es für notwendig erachtet, bereits vor Ablauf einer angemessenen Frist ein Arztzeugnis zu verlangen, wäre es nur folgerichtig, wenn die damit verbundenen Kosten zu seinen Lasten gingen. Es ist nicht Aufgabe der obligatorischen Krankenpflegeversicherung, die von allen Versicherten finanziert wird, Kosten zu übernehmen, die sich aus einer privaten administrativen Forderung ergeben. Die betroffenen Arbeitnehmerinnen und Arbeitnehmer leisten ihrerseits einen finanziellen Beitrag in Form ihrer Franchise und ihres Selbstbehalts. In einer Zeit, in der die Kostendämpfung im Gesundheitswesen eine erklärte politische Priorität ist, sollte dieser vermeidbare Kostenfaktor genauer unter die Lupe genommen werden.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Ich bitte den Bundesrat, folgende Fragen zu beantworten:&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;ol&gt;&lt;li&gt;Verfügt der Bundesrat über Daten zur Anzahl der jährlichen Arztbesuche, deren einziger Grund die Ausstellung eines Arztzeugnisses ist, die ein Arbeitgeber für eine Kurzabwesenheit verlangt?&lt;/li&gt;&lt;li&gt;Wie hoch werden die Kosten dieser Konsultationen für die obligatorische Krankenversicherung geschätzt?&lt;/li&gt;&lt;li&gt;Ist der Bundesrat bereit, eine Regelung zu prüfen, die eine Mindestfrist festlegt, bevor ein Arbeitgeber ein Arztzeugnis verlangen darf?&lt;/li&gt;&lt;li&gt;Ist der Bundesrat bereit, eine Gesetzesänderung zu prüfen, die es ermöglicht, die Kosten für diese Konsultationen dem entsprechenden Arbeitgeber anzulasten, anstatt der obligatorischen Krankenversicherung?&lt;/li&gt;&lt;/ol&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beschäftigung und Arbeit|Zivilrecht|Gesundheit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Emploi et travail|Droit civil|Santé</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Occupazione e lavoro|Diritto civile|Salute</t>
-  </si>
-  <si>
     <t xml:space="preserve">26.3936</t>
   </si>
   <si>
@@ -1005,39 +1038,6 @@
   </si>
   <si>
     <t xml:space="preserve">2026-08-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wie sieht bei der Post die geografische Verteilung der Arbeitsplätze aus?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quelle répartition géographique des emplois postaux ?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qual è la ripartizione geografica dei posti di lavoro nel settore postale?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;La Confédération est l'actionnaire unique de La Poste Suisse SA et lui assigne tous les quatre ans des objectifs stratégiques (art. 7 LOP). Les objectifs 2025-2028, adoptés le 29 janvier 2025, ne contiennent aucune exigence de répartition géographique des emplois entre les cantons. L'objectif 3.1 en matière de personnel demande une politique progressiste en matière de personnel et une augmentation de la proportion de femmes aux postes de cadres. Les rapports annuels de réalisation ne comportent aucun indicateur territorial relatif à l'emploi.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Cette lacune est préoccupante. La Poste restructure en effet profondément son réseau depuis plusieurs années : fermetures d'offices et transformation en agences dans des commerces privés. Les cantons périphériques sont les plus touchés. Paradoxalement, les objectifs stratégiques prévoient déjà une logique territoriale pour les prestations, l'accessibilité au service universel étant mesurée au niveau cantonal. Il n'y a aucune raison que cette logique ne s'applique pas aussi aux emplois.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Les emplois des entreprises dont la Confédération est propriétaire sont généralement stables et soumis à des conditions conventionnelles attractives. Ils devraient se développer sur l'ensemble du territoire, et a fortiori dans les régions où ces mêmes entreprises suppriment des postes par ailleurs.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Le DETEC doit par ailleurs soumettre un projet de révision de la législation postale d'ici fin juin 2026, ce qui rend la présente interpellation particulièrement actuelle.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Je pose dès lors les questions suivantes au Conseil fédéral :&lt;/p&gt;&lt;ol&gt;&lt;li&gt;Quelle est l'évolution des emplois à La Poste (en EPT) par canton sur les dix dernières années ?&lt;/li&gt;&lt;li&gt;Quelle est l'évolution du nombre d'offices par canton depuis 2010 ?&lt;/li&gt;&lt;li&gt;Pour quelle raison les objectifs stratégiques ne comportent-ils aucun indicateur de répartition géographique des emplois ?&lt;/li&gt;&lt;li&gt;Le Conseil fédéral considère-t-il la répartition territoriale des emplois des entités paraétatiques comme relevant de sa responsabilité ?&lt;/li&gt;&lt;li&gt;Dans le cadre de la révision législative en cours ou à venir, est-il prêt à introduire un tel indicateur pour La Poste, les CFF et Swisscom ?&lt;/li&gt;&lt;/ol&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Der Bund ist Alleinaktionär der Schweizerischen&amp;nbsp;Post&amp;nbsp;AG und legt alle vier Jahre die strategischen Ziele für sie fest&amp;nbsp;(Art.&amp;nbsp;7 des Postorganisationsgesetzes). Die am 29.&amp;nbsp;Januar&amp;nbsp;2025 verabschiedeten Ziele für den Zeitraum 2025–2028 enthalten keine Vorgaben zur geografischen Verteilung der Arbeitsplätze auf die Kantone. Ziffer&amp;nbsp;3.1 sieht eine fortschrittliche Personalpolitik und eine Erhöhung des Frauenanteils in Kaderpositionen vor. Die jährlichen Berichte über die Erreichung der strategischen Ziele enthalten keinen Indikator zur geografischen Verteilung der Arbeitsplätze.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Diese Lücke gibt Anlass zur Sorge. Die Post nimmt seit mehreren Jahren eine tiefgreifende Umstrukturierung ihres Netzes vor: Poststellen werden geschlossen und in Agenturen in privaten Geschäften umgewandelt. Die Randkantone sind am stärksten davon betroffen. Paradoxerweise ist in den strategischen Zielen bereits ein geografischer Ansatz für die Leistungen vorgesehen, indem die Erreichbarkeit der Grundversorgung auf kantonaler Ebene gemessen wird. Es gibt keinen Grund, warum diese Logik nicht auch für die Arbeitsplätze gelten sollte.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Unternehmen, die im Eigentum des Bundes sind, bieten in der Regel sichere Arbeitsplätze mit attraktiven Anstellungsbedingungen an. Solche Arbeitsplätze sollten schweizweit gefördert werden, und erst recht in den Regionen, in denen dieselben Unternehmen Stellen abbauen.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Das Eidgenössische Departement für Umwelt, Verkehr, Energie und Kommunikation muss im Übrigen bis Ende Juni&amp;nbsp;2026 eine Vernehmlassungsvorlage für eine Revision der Postgesetzgebung unterbreiten, was der vorliegenden Interpellation besondere Aktualität verleiht.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Ich bitte den Bundesrat, folgende Fragen zu beantworten:&lt;/p&gt;&lt;ol&gt;&lt;li&gt;Wie hat sich die Anzahl der Arbeitsplätze bei der Post&amp;nbsp;(in Vollzeitäquivalenten) in den einzelnen Kantonen in den letzten zehn Jahren entwickelt?&lt;/li&gt;&lt;li&gt;Wie hat sich die Anzahl der Poststellen pro Kanton seit 2010 entwickelt?&lt;/li&gt;&lt;li&gt;Weshalb enthalten die strategischen Ziele keinen Indikator zur geografischen Verteilung der Arbeitsplätze?&lt;/li&gt;&lt;li&gt;Ist der Bundesrat der Ansicht, dass die geografische Verteilung der Arbeitsplätze in bundesnahen Betrieben in seiner Verantwortung liegt?&lt;/li&gt;&lt;li&gt;Ist der Bundesrat bereit, im Rahmen der laufenden oder anstehenden Revision der Postgesetzgebung einen solchen Indikator für die Post, die SBB und die Swisscom einzuführen?&lt;/li&gt;&lt;/ol&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staatspolitik|Wirtschaft|Medien und Kommunikation|Beschäftigung und Arbeit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politique d'Etat|Économie|Médias et communication|Emploi et travail</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politica nazionale|Economia|Media e comunicazione|Occupazione e lavoro</t>
   </si>
   <si>
     <t xml:space="preserve">26.3411</t>
@@ -6056,7 +6056,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>20264418</v>
+        <v>20263563</v>
       </c>
       <c r="B3" t="s">
         <v>36</v>
@@ -6076,49 +6076,59 @@
       <c r="G3" t="s">
         <v>40</v>
       </c>
-      <c r="H3"/>
+      <c r="H3" t="s">
+        <v>41</v>
+      </c>
       <c r="I3" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="J3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="K3" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="L3" t="s">
-        <v>42</v>
-      </c>
-      <c r="M3"/>
+        <v>45</v>
+      </c>
+      <c r="M3" t="s">
+        <v>46</v>
+      </c>
       <c r="N3" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="O3" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="P3" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="Q3" t="s">
-        <v>35</v>
-      </c>
-      <c r="R3"/>
-      <c r="S3"/>
-      <c r="T3"/>
+        <v>50</v>
+      </c>
+      <c r="R3" t="s">
+        <v>51</v>
+      </c>
+      <c r="S3" t="s">
+        <v>52</v>
+      </c>
+      <c r="T3" t="s">
+        <v>53</v>
+      </c>
       <c r="U3" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="V3"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>20264338</v>
+        <v>20263564</v>
       </c>
       <c r="B4" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="D4" t="s">
         <v>38</v>
@@ -6127,122 +6137,130 @@
         <v>25</v>
       </c>
       <c r="F4" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="G4" t="s">
         <v>40</v>
       </c>
-      <c r="H4"/>
+      <c r="H4" t="s">
+        <v>55</v>
+      </c>
       <c r="I4" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="J4" t="s">
+        <v>57</v>
+      </c>
+      <c r="K4" t="s">
+        <v>58</v>
+      </c>
+      <c r="L4" t="s">
+        <v>59</v>
+      </c>
+      <c r="M4" t="s">
+        <v>60</v>
+      </c>
+      <c r="N4" t="s">
         <v>47</v>
       </c>
-      <c r="K4" t="s">
-        <v>30</v>
-      </c>
-      <c r="L4" t="s">
-        <v>48</v>
-      </c>
-      <c r="M4"/>
-      <c r="N4" t="s">
-        <v>32</v>
-      </c>
       <c r="O4" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="P4" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q4" t="s">
         <v>50</v>
       </c>
-      <c r="Q4" t="s">
-        <v>51</v>
-      </c>
       <c r="R4" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="S4" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="T4" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="U4" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="V4"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>20264339</v>
+        <v>20263571</v>
       </c>
       <c r="B5" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="D5" t="s">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="E5" t="s">
-        <v>25</v>
+        <v>68</v>
       </c>
       <c r="F5" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="G5" t="s">
-        <v>40</v>
-      </c>
-      <c r="H5"/>
+        <v>27</v>
+      </c>
+      <c r="H5" t="s">
+        <v>69</v>
+      </c>
       <c r="I5" t="s">
-        <v>28</v>
+        <v>70</v>
       </c>
       <c r="J5" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="K5" t="s">
-        <v>30</v>
+        <v>72</v>
       </c>
       <c r="L5" t="s">
-        <v>57</v>
-      </c>
-      <c r="M5"/>
+        <v>73</v>
+      </c>
+      <c r="M5" t="s">
+        <v>74</v>
+      </c>
       <c r="N5" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="O5" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="P5" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="Q5" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="R5" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="S5" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="T5" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="U5" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="V5"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>20267901</v>
+        <v>20264418</v>
       </c>
       <c r="B6" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="C6" t="s">
-        <v>64</v>
+        <v>37</v>
       </c>
       <c r="D6" t="s">
         <v>38</v>
@@ -6251,205 +6269,193 @@
         <v>25</v>
       </c>
       <c r="F6" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="G6" t="s">
         <v>40</v>
       </c>
-      <c r="H6" t="s">
-        <v>66</v>
-      </c>
+      <c r="H6"/>
       <c r="I6" t="s">
-        <v>67</v>
+        <v>28</v>
       </c>
       <c r="J6" t="s">
-        <v>68</v>
-      </c>
-      <c r="K6"/>
+        <v>82</v>
+      </c>
+      <c r="K6" t="s">
+        <v>30</v>
+      </c>
       <c r="L6" t="s">
-        <v>69</v>
-      </c>
-      <c r="M6" t="s">
-        <v>70</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="M6"/>
       <c r="N6" t="s">
-        <v>71</v>
+        <v>32</v>
       </c>
       <c r="O6" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="Q6" t="s">
-        <v>51</v>
-      </c>
-      <c r="R6" t="s">
-        <v>74</v>
-      </c>
-      <c r="S6" t="s">
-        <v>75</v>
-      </c>
-      <c r="T6" t="s">
-        <v>76</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="R6"/>
+      <c r="S6"/>
+      <c r="T6"/>
       <c r="U6" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="V6"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>20264261</v>
+        <v>20264338</v>
       </c>
       <c r="B7" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="D7" t="s">
-        <v>79</v>
+        <v>38</v>
       </c>
       <c r="E7" t="s">
-        <v>80</v>
+        <v>25</v>
       </c>
       <c r="F7" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G7" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="H7"/>
       <c r="I7" t="s">
         <v>28</v>
       </c>
       <c r="J7" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="K7" t="s">
         <v>30</v>
       </c>
       <c r="L7" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="M7"/>
       <c r="N7" t="s">
         <v>32</v>
       </c>
       <c r="O7" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="Q7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="R7" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="S7" t="s">
+        <v>93</v>
+      </c>
+      <c r="T7" t="s">
+        <v>94</v>
+      </c>
+      <c r="U7" t="s">
         <v>87</v>
-      </c>
-      <c r="T7" t="s">
-        <v>88</v>
-      </c>
-      <c r="U7" t="s">
-        <v>81</v>
       </c>
       <c r="V7"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>20263891</v>
+        <v>20264339</v>
       </c>
       <c r="B8" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="C8" t="s">
         <v>37</v>
       </c>
       <c r="D8" t="s">
-        <v>79</v>
+        <v>38</v>
       </c>
       <c r="E8" t="s">
-        <v>80</v>
+        <v>25</v>
       </c>
       <c r="F8" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="G8" t="s">
-        <v>27</v>
-      </c>
-      <c r="H8" t="s">
-        <v>91</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="H8"/>
       <c r="I8" t="s">
-        <v>92</v>
+        <v>28</v>
       </c>
       <c r="J8" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="K8" t="s">
-        <v>94</v>
+        <v>30</v>
       </c>
       <c r="L8" t="s">
-        <v>95</v>
-      </c>
-      <c r="M8" t="s">
-        <v>96</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="M8"/>
       <c r="N8" t="s">
-        <v>71</v>
+        <v>32</v>
       </c>
       <c r="O8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="P8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="R8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="S8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="U8" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="V8"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>20263518</v>
+        <v>20267901</v>
       </c>
       <c r="B9" t="s">
         <v>103</v>
       </c>
       <c r="C9" t="s">
-        <v>23</v>
+        <v>104</v>
       </c>
       <c r="D9" t="s">
-        <v>104</v>
+        <v>38</v>
       </c>
       <c r="E9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" t="s">
         <v>105</v>
-      </c>
-      <c r="F9" t="s">
-        <v>106</v>
       </c>
       <c r="G9" t="s">
         <v>40</v>
       </c>
       <c r="H9" t="s">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="I9" t="s">
         <v>107</v>
@@ -6457,137 +6463,135 @@
       <c r="J9" t="s">
         <v>108</v>
       </c>
-      <c r="K9" t="s">
+      <c r="K9"/>
+      <c r="L9" t="s">
         <v>109</v>
       </c>
-      <c r="L9" t="s">
+      <c r="M9" t="s">
         <v>110</v>
       </c>
-      <c r="M9" t="s">
+      <c r="N9" t="s">
+        <v>47</v>
+      </c>
+      <c r="O9" t="s">
         <v>111</v>
       </c>
-      <c r="N9" t="s">
-        <v>71</v>
-      </c>
-      <c r="O9" t="s">
+      <c r="P9" t="s">
         <v>112</v>
       </c>
-      <c r="P9" t="s">
+      <c r="Q9" t="s">
+        <v>50</v>
+      </c>
+      <c r="R9" t="s">
         <v>113</v>
       </c>
-      <c r="Q9" t="s">
+      <c r="S9" t="s">
         <v>114</v>
       </c>
-      <c r="R9" t="s">
+      <c r="T9" t="s">
         <v>115</v>
       </c>
-      <c r="S9" t="s">
+      <c r="U9" t="s">
         <v>116</v>
-      </c>
-      <c r="T9" t="s">
-        <v>117</v>
-      </c>
-      <c r="U9" t="s">
-        <v>102</v>
       </c>
       <c r="V9"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>20267687</v>
+        <v>20264261</v>
       </c>
       <c r="B10" t="s">
+        <v>117</v>
+      </c>
+      <c r="C10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" t="s">
         <v>118</v>
       </c>
-      <c r="C10" t="s">
-        <v>64</v>
-      </c>
-      <c r="D10" t="s">
-        <v>38</v>
-      </c>
       <c r="E10" t="s">
-        <v>25</v>
+        <v>119</v>
       </c>
       <c r="F10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G10" t="s">
-        <v>40</v>
-      </c>
-      <c r="H10" t="s">
-        <v>91</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="H10"/>
       <c r="I10" t="s">
-        <v>120</v>
+        <v>28</v>
       </c>
       <c r="J10" t="s">
         <v>121</v>
       </c>
-      <c r="K10"/>
+      <c r="K10" t="s">
+        <v>30</v>
+      </c>
       <c r="L10" t="s">
         <v>122</v>
       </c>
-      <c r="M10" t="s">
+      <c r="M10"/>
+      <c r="N10" t="s">
+        <v>32</v>
+      </c>
+      <c r="O10" t="s">
         <v>123</v>
       </c>
-      <c r="N10" t="s">
-        <v>71</v>
-      </c>
-      <c r="O10" t="s">
+      <c r="P10" t="s">
         <v>124</v>
       </c>
-      <c r="P10" t="s">
+      <c r="Q10" t="s">
+        <v>50</v>
+      </c>
+      <c r="R10" t="s">
         <v>125</v>
       </c>
-      <c r="Q10" t="s">
-        <v>51</v>
-      </c>
-      <c r="R10" t="s">
+      <c r="S10" t="s">
         <v>126</v>
       </c>
-      <c r="S10" t="s">
+      <c r="T10" t="s">
         <v>127</v>
       </c>
-      <c r="T10" t="s">
-        <v>128</v>
-      </c>
       <c r="U10" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="V10"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>20267688</v>
+        <v>20263891</v>
       </c>
       <c r="B11" t="s">
+        <v>128</v>
+      </c>
+      <c r="C11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" t="s">
+        <v>118</v>
+      </c>
+      <c r="E11" t="s">
+        <v>119</v>
+      </c>
+      <c r="F11" t="s">
+        <v>129</v>
+      </c>
+      <c r="G11" t="s">
+        <v>27</v>
+      </c>
+      <c r="H11" t="s">
         <v>130</v>
       </c>
-      <c r="C11" t="s">
-        <v>64</v>
-      </c>
-      <c r="D11" t="s">
-        <v>38</v>
-      </c>
-      <c r="E11" t="s">
-        <v>25</v>
-      </c>
-      <c r="F11" t="s">
-        <v>119</v>
-      </c>
-      <c r="G11" t="s">
-        <v>40</v>
-      </c>
-      <c r="H11" t="s">
+      <c r="I11" t="s">
         <v>131</v>
       </c>
-      <c r="I11" t="s">
+      <c r="J11" t="s">
         <v>132</v>
       </c>
-      <c r="J11" t="s">
+      <c r="K11" t="s">
         <v>133</v>
       </c>
-      <c r="K11"/>
       <c r="L11" t="s">
         <v>134</v>
       </c>
@@ -6595,7 +6599,7 @@
         <v>135</v>
       </c>
       <c r="N11" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="O11" t="s">
         <v>136</v>
@@ -6604,7 +6608,7 @@
         <v>137</v>
       </c>
       <c r="Q11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="R11" t="s">
         <v>138</v>
@@ -6616,220 +6620,222 @@
         <v>140</v>
       </c>
       <c r="U11" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="V11"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>20264169</v>
+        <v>20263518</v>
       </c>
       <c r="B12" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C12" t="s">
         <v>23</v>
       </c>
       <c r="D12" t="s">
-        <v>38</v>
+        <v>143</v>
       </c>
       <c r="E12" t="s">
-        <v>25</v>
+        <v>144</v>
       </c>
       <c r="F12" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="G12" t="s">
         <v>40</v>
       </c>
-      <c r="H12"/>
+      <c r="H12" t="s">
+        <v>130</v>
+      </c>
       <c r="I12" t="s">
-        <v>28</v>
+        <v>146</v>
       </c>
       <c r="J12" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="K12" t="s">
-        <v>30</v>
+        <v>148</v>
       </c>
       <c r="L12" t="s">
-        <v>144</v>
-      </c>
-      <c r="M12"/>
+        <v>149</v>
+      </c>
+      <c r="M12" t="s">
+        <v>150</v>
+      </c>
       <c r="N12" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="O12" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="P12" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="Q12" t="s">
-        <v>51</v>
+        <v>153</v>
       </c>
       <c r="R12" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="S12" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="T12" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="U12" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="V12"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>20263628</v>
+        <v>20267687</v>
       </c>
       <c r="B13" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="C13" t="s">
-        <v>23</v>
+        <v>104</v>
       </c>
       <c r="D13" t="s">
-        <v>79</v>
+        <v>38</v>
       </c>
       <c r="E13" t="s">
-        <v>80</v>
+        <v>25</v>
       </c>
       <c r="F13" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="G13" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="H13" t="s">
-        <v>152</v>
+        <v>130</v>
       </c>
       <c r="I13" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="J13" t="s">
-        <v>154</v>
-      </c>
-      <c r="K13" t="s">
-        <v>155</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="K13"/>
       <c r="L13" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="M13" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="N13" t="s">
-        <v>158</v>
+        <v>47</v>
       </c>
       <c r="O13" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="P13" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="Q13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="R13" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="S13" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="T13" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="U13" t="s">
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="V13"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>20263131</v>
+        <v>20267688</v>
       </c>
       <c r="B14" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="C14" t="s">
-        <v>23</v>
+        <v>104</v>
       </c>
       <c r="D14" t="s">
-        <v>165</v>
-      </c>
-      <c r="E14"/>
+        <v>38</v>
+      </c>
+      <c r="E14" t="s">
+        <v>25</v>
+      </c>
       <c r="F14" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="G14" t="s">
         <v>40</v>
       </c>
       <c r="H14" t="s">
-        <v>167</v>
+        <v>41</v>
       </c>
       <c r="I14" t="s">
+        <v>170</v>
+      </c>
+      <c r="J14" t="s">
+        <v>171</v>
+      </c>
+      <c r="K14"/>
+      <c r="L14" t="s">
+        <v>172</v>
+      </c>
+      <c r="M14" t="s">
+        <v>173</v>
+      </c>
+      <c r="N14" t="s">
+        <v>47</v>
+      </c>
+      <c r="O14" t="s">
+        <v>174</v>
+      </c>
+      <c r="P14" t="s">
+        <v>175</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>50</v>
+      </c>
+      <c r="R14" t="s">
+        <v>176</v>
+      </c>
+      <c r="S14" t="s">
+        <v>177</v>
+      </c>
+      <c r="T14" t="s">
+        <v>178</v>
+      </c>
+      <c r="U14" t="s">
         <v>168</v>
-      </c>
-      <c r="J14" t="s">
-        <v>169</v>
-      </c>
-      <c r="K14" t="s">
-        <v>170</v>
-      </c>
-      <c r="L14" t="s">
-        <v>171</v>
-      </c>
-      <c r="M14" t="s">
-        <v>172</v>
-      </c>
-      <c r="N14" t="s">
-        <v>71</v>
-      </c>
-      <c r="O14" t="s">
-        <v>173</v>
-      </c>
-      <c r="P14" t="s">
-        <v>174</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>35</v>
-      </c>
-      <c r="R14" t="s">
-        <v>175</v>
-      </c>
-      <c r="S14" t="s">
-        <v>176</v>
-      </c>
-      <c r="T14" t="s">
-        <v>177</v>
-      </c>
-      <c r="U14" t="s">
-        <v>142</v>
       </c>
       <c r="V14"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>20264146</v>
+        <v>20264169</v>
       </c>
       <c r="B15" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C15" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="D15" t="s">
-        <v>179</v>
+        <v>38</v>
       </c>
       <c r="E15" t="s">
+        <v>25</v>
+      </c>
+      <c r="F15" t="s">
         <v>180</v>
-      </c>
-      <c r="F15" t="s">
-        <v>181</v>
       </c>
       <c r="G15" t="s">
         <v>40</v>
@@ -6839,888 +6845,876 @@
         <v>28</v>
       </c>
       <c r="J15" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="K15" t="s">
         <v>30</v>
       </c>
       <c r="L15" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="M15"/>
       <c r="N15" t="s">
         <v>32</v>
       </c>
       <c r="O15" t="s">
+        <v>183</v>
+      </c>
+      <c r="P15" t="s">
         <v>184</v>
       </c>
-      <c r="P15" t="s">
+      <c r="Q15" t="s">
+        <v>50</v>
+      </c>
+      <c r="R15" t="s">
         <v>185</v>
       </c>
-      <c r="Q15" t="s">
-        <v>51</v>
-      </c>
-      <c r="R15" t="s">
+      <c r="S15" t="s">
         <v>186</v>
       </c>
-      <c r="S15" t="s">
+      <c r="T15" t="s">
         <v>187</v>
       </c>
-      <c r="T15" t="s">
-        <v>188</v>
-      </c>
       <c r="U15" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="V15"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>20267829</v>
+        <v>20263628</v>
       </c>
       <c r="B16" t="s">
+        <v>188</v>
+      </c>
+      <c r="C16" t="s">
+        <v>23</v>
+      </c>
+      <c r="D16" t="s">
+        <v>118</v>
+      </c>
+      <c r="E16" t="s">
+        <v>119</v>
+      </c>
+      <c r="F16" t="s">
         <v>189</v>
       </c>
-      <c r="C16" t="s">
-        <v>64</v>
-      </c>
-      <c r="D16" t="s">
-        <v>38</v>
-      </c>
-      <c r="E16" t="s">
-        <v>25</v>
-      </c>
-      <c r="F16" t="s">
-        <v>181</v>
-      </c>
       <c r="G16" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="H16" t="s">
-        <v>131</v>
+        <v>190</v>
       </c>
       <c r="I16" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="J16" t="s">
-        <v>191</v>
-      </c>
-      <c r="K16"/>
+        <v>192</v>
+      </c>
+      <c r="K16" t="s">
+        <v>193</v>
+      </c>
       <c r="L16" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="M16" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="N16" t="s">
-        <v>71</v>
+        <v>196</v>
       </c>
       <c r="O16" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="P16" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="Q16" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="R16" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="S16" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="T16" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="U16" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="V16"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>20264127</v>
+        <v>20263131</v>
       </c>
       <c r="B17" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C17" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="D17" t="s">
-        <v>200</v>
-      </c>
-      <c r="E17" t="s">
-        <v>25</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="E17"/>
       <c r="F17" t="s">
-        <v>119</v>
+        <v>204</v>
       </c>
       <c r="G17" t="s">
         <v>40</v>
       </c>
-      <c r="H17"/>
+      <c r="H17" t="s">
+        <v>69</v>
+      </c>
       <c r="I17" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="J17" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="K17" t="s">
-        <v>203</v>
-      </c>
-      <c r="L17"/>
+        <v>72</v>
+      </c>
+      <c r="L17" t="s">
+        <v>207</v>
+      </c>
       <c r="M17" t="s">
-        <v>204</v>
+        <v>74</v>
       </c>
       <c r="N17" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="O17" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="P17" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="Q17" t="s">
         <v>35</v>
       </c>
       <c r="R17" t="s">
-        <v>207</v>
+        <v>77</v>
       </c>
       <c r="S17" t="s">
-        <v>208</v>
+        <v>78</v>
       </c>
       <c r="T17" t="s">
-        <v>209</v>
+        <v>79</v>
       </c>
       <c r="U17" t="s">
-        <v>119</v>
+        <v>180</v>
       </c>
       <c r="V17"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>20260312</v>
+        <v>20264146</v>
       </c>
       <c r="B18" t="s">
         <v>210</v>
       </c>
       <c r="C18" t="s">
+        <v>37</v>
+      </c>
+      <c r="D18" t="s">
         <v>211</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
+        <v>68</v>
+      </c>
+      <c r="F18" t="s">
         <v>212</v>
       </c>
-      <c r="E18"/>
-      <c r="F18" t="s">
+      <c r="G18" t="s">
+        <v>40</v>
+      </c>
+      <c r="H18"/>
+      <c r="I18" t="s">
+        <v>28</v>
+      </c>
+      <c r="J18" t="s">
         <v>213</v>
       </c>
-      <c r="G18"/>
-      <c r="H18" t="s">
+      <c r="K18" t="s">
+        <v>30</v>
+      </c>
+      <c r="L18" t="s">
         <v>214</v>
       </c>
-      <c r="I18" t="s">
+      <c r="M18"/>
+      <c r="N18" t="s">
+        <v>32</v>
+      </c>
+      <c r="O18" t="s">
         <v>215</v>
       </c>
-      <c r="J18" t="s">
+      <c r="P18" t="s">
         <v>216</v>
       </c>
-      <c r="K18" t="s">
+      <c r="Q18" t="s">
+        <v>50</v>
+      </c>
+      <c r="R18" t="s">
         <v>217</v>
       </c>
-      <c r="L18" t="s">
+      <c r="S18" t="s">
         <v>218</v>
       </c>
-      <c r="M18" t="s">
+      <c r="T18" t="s">
         <v>219</v>
       </c>
-      <c r="N18" t="s">
-        <v>220</v>
-      </c>
-      <c r="O18" t="s">
-        <v>221</v>
-      </c>
-      <c r="P18" t="s">
-        <v>222</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>35</v>
-      </c>
-      <c r="R18"/>
-      <c r="S18"/>
-      <c r="T18"/>
       <c r="U18" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="V18"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>20263916</v>
+        <v>20267829</v>
       </c>
       <c r="B19" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C19" t="s">
-        <v>37</v>
+        <v>104</v>
       </c>
       <c r="D19" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="E19" t="s">
         <v>25</v>
       </c>
       <c r="F19" t="s">
-        <v>90</v>
+        <v>212</v>
       </c>
       <c r="G19" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="H19" t="s">
-        <v>131</v>
+        <v>41</v>
       </c>
       <c r="I19" t="s">
+        <v>221</v>
+      </c>
+      <c r="J19" t="s">
+        <v>222</v>
+      </c>
+      <c r="K19"/>
+      <c r="L19" t="s">
+        <v>223</v>
+      </c>
+      <c r="M19" t="s">
+        <v>224</v>
+      </c>
+      <c r="N19" t="s">
+        <v>47</v>
+      </c>
+      <c r="O19" t="s">
         <v>225</v>
       </c>
-      <c r="J19" t="s">
+      <c r="P19" t="s">
         <v>226</v>
       </c>
-      <c r="K19" t="s">
+      <c r="Q19" t="s">
+        <v>50</v>
+      </c>
+      <c r="R19" t="s">
         <v>227</v>
       </c>
-      <c r="L19" t="s">
+      <c r="S19" t="s">
         <v>228</v>
       </c>
-      <c r="M19" t="s">
+      <c r="T19" t="s">
         <v>229</v>
       </c>
-      <c r="N19" t="s">
-        <v>230</v>
-      </c>
-      <c r="O19" t="s">
-        <v>231</v>
-      </c>
-      <c r="P19" t="s">
-        <v>232</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>51</v>
-      </c>
-      <c r="R19" t="s">
-        <v>233</v>
-      </c>
-      <c r="S19" t="s">
-        <v>234</v>
-      </c>
-      <c r="T19" t="s">
-        <v>235</v>
-      </c>
       <c r="U19" t="s">
-        <v>236</v>
+        <v>212</v>
       </c>
       <c r="V19"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>20263968</v>
+        <v>20264127</v>
       </c>
       <c r="B20" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="C20" t="s">
         <v>37</v>
       </c>
       <c r="D20" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="E20" t="s">
-        <v>239</v>
+        <v>25</v>
       </c>
       <c r="F20" t="s">
-        <v>90</v>
+        <v>158</v>
       </c>
       <c r="G20" t="s">
         <v>40</v>
       </c>
-      <c r="H20" t="s">
-        <v>131</v>
-      </c>
+      <c r="H20"/>
       <c r="I20" t="s">
+        <v>232</v>
+      </c>
+      <c r="J20" t="s">
+        <v>233</v>
+      </c>
+      <c r="K20" t="s">
+        <v>234</v>
+      </c>
+      <c r="L20"/>
+      <c r="M20" t="s">
+        <v>235</v>
+      </c>
+      <c r="N20" t="s">
+        <v>32</v>
+      </c>
+      <c r="O20" t="s">
+        <v>236</v>
+      </c>
+      <c r="P20" t="s">
+        <v>237</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>35</v>
+      </c>
+      <c r="R20" t="s">
+        <v>238</v>
+      </c>
+      <c r="S20" t="s">
+        <v>239</v>
+      </c>
+      <c r="T20" t="s">
         <v>240</v>
       </c>
-      <c r="J20" t="s">
-        <v>241</v>
-      </c>
-      <c r="K20" t="s">
-        <v>242</v>
-      </c>
-      <c r="L20" t="s">
-        <v>243</v>
-      </c>
-      <c r="M20" t="s">
-        <v>244</v>
-      </c>
-      <c r="N20" t="s">
-        <v>245</v>
-      </c>
-      <c r="O20" t="s">
-        <v>246</v>
-      </c>
-      <c r="P20" t="s">
-        <v>247</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>114</v>
-      </c>
-      <c r="R20" t="s">
-        <v>196</v>
-      </c>
-      <c r="S20" t="s">
-        <v>197</v>
-      </c>
-      <c r="T20" t="s">
-        <v>198</v>
-      </c>
       <c r="U20" t="s">
-        <v>236</v>
+        <v>158</v>
       </c>
       <c r="V20"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>20263997</v>
+        <v>20260312</v>
       </c>
       <c r="B21" t="s">
+        <v>241</v>
+      </c>
+      <c r="C21" t="s">
+        <v>242</v>
+      </c>
+      <c r="D21" t="s">
+        <v>243</v>
+      </c>
+      <c r="E21"/>
+      <c r="F21" t="s">
+        <v>244</v>
+      </c>
+      <c r="G21"/>
+      <c r="H21" t="s">
+        <v>245</v>
+      </c>
+      <c r="I21" t="s">
+        <v>246</v>
+      </c>
+      <c r="J21" t="s">
+        <v>247</v>
+      </c>
+      <c r="K21" t="s">
         <v>248</v>
       </c>
-      <c r="C21" t="s">
-        <v>37</v>
-      </c>
-      <c r="D21" t="s">
+      <c r="L21" t="s">
         <v>249</v>
       </c>
-      <c r="E21" t="s">
+      <c r="M21" t="s">
         <v>250</v>
       </c>
-      <c r="F21" t="s">
-        <v>90</v>
-      </c>
-      <c r="G21" t="s">
-        <v>40</v>
-      </c>
-      <c r="H21" t="s">
+      <c r="N21" t="s">
         <v>251</v>
       </c>
-      <c r="I21" t="s">
+      <c r="O21" t="s">
         <v>252</v>
       </c>
-      <c r="J21" t="s">
+      <c r="P21" t="s">
         <v>253</v>
       </c>
-      <c r="K21" t="s">
+      <c r="Q21" t="s">
+        <v>35</v>
+      </c>
+      <c r="R21"/>
+      <c r="S21"/>
+      <c r="T21"/>
+      <c r="U21" t="s">
         <v>254</v>
-      </c>
-      <c r="L21" t="s">
-        <v>255</v>
-      </c>
-      <c r="M21" t="s">
-        <v>256</v>
-      </c>
-      <c r="N21" t="s">
-        <v>245</v>
-      </c>
-      <c r="O21" t="s">
-        <v>257</v>
-      </c>
-      <c r="P21" t="s">
-        <v>258</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>114</v>
-      </c>
-      <c r="R21" t="s">
-        <v>259</v>
-      </c>
-      <c r="S21" t="s">
-        <v>260</v>
-      </c>
-      <c r="T21" t="s">
-        <v>261</v>
-      </c>
-      <c r="U21" t="s">
-        <v>236</v>
       </c>
       <c r="V21"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>20263571</v>
+        <v>20263916</v>
       </c>
       <c r="B22" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="C22" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="D22" t="s">
-        <v>263</v>
+        <v>24</v>
       </c>
       <c r="E22" t="s">
-        <v>180</v>
+        <v>25</v>
       </c>
       <c r="F22" t="s">
-        <v>264</v>
+        <v>129</v>
       </c>
       <c r="G22" t="s">
         <v>27</v>
       </c>
       <c r="H22" t="s">
-        <v>167</v>
+        <v>41</v>
       </c>
       <c r="I22" t="s">
+        <v>256</v>
+      </c>
+      <c r="J22" t="s">
+        <v>257</v>
+      </c>
+      <c r="K22" t="s">
+        <v>258</v>
+      </c>
+      <c r="L22" t="s">
+        <v>259</v>
+      </c>
+      <c r="M22" t="s">
+        <v>260</v>
+      </c>
+      <c r="N22" t="s">
+        <v>261</v>
+      </c>
+      <c r="O22" t="s">
+        <v>262</v>
+      </c>
+      <c r="P22" t="s">
+        <v>263</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>50</v>
+      </c>
+      <c r="R22" t="s">
+        <v>264</v>
+      </c>
+      <c r="S22" t="s">
         <v>265</v>
       </c>
-      <c r="J22" t="s">
+      <c r="T22" t="s">
         <v>266</v>
       </c>
-      <c r="K22" t="s">
-        <v>170</v>
-      </c>
-      <c r="L22" t="s">
+      <c r="U22" t="s">
         <v>267</v>
       </c>
-      <c r="M22" t="s">
-        <v>172</v>
-      </c>
-      <c r="N22" t="s">
-        <v>71</v>
-      </c>
-      <c r="O22" t="s">
-        <v>268</v>
-      </c>
-      <c r="P22" t="s">
-        <v>269</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>35</v>
-      </c>
-      <c r="R22" t="s">
-        <v>175</v>
-      </c>
-      <c r="S22" t="s">
-        <v>176</v>
-      </c>
-      <c r="T22" t="s">
-        <v>177</v>
-      </c>
-      <c r="U22" t="s">
-        <v>26</v>
-      </c>
-      <c r="V22" t="s">
-        <v>26</v>
-      </c>
+      <c r="V22"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>20263597</v>
+        <v>20263968</v>
       </c>
       <c r="B23" t="s">
+        <v>268</v>
+      </c>
+      <c r="C23" t="s">
+        <v>37</v>
+      </c>
+      <c r="D23" t="s">
+        <v>269</v>
+      </c>
+      <c r="E23" t="s">
         <v>270</v>
       </c>
-      <c r="C23" t="s">
+      <c r="F23" t="s">
+        <v>129</v>
+      </c>
+      <c r="G23" t="s">
+        <v>40</v>
+      </c>
+      <c r="H23" t="s">
+        <v>41</v>
+      </c>
+      <c r="I23" t="s">
         <v>271</v>
       </c>
-      <c r="D23" t="s">
-        <v>79</v>
-      </c>
-      <c r="E23" t="s">
-        <v>80</v>
-      </c>
-      <c r="F23" t="s">
+      <c r="J23" t="s">
         <v>272</v>
       </c>
-      <c r="G23" t="s">
-        <v>27</v>
-      </c>
-      <c r="H23" t="s">
-        <v>167</v>
-      </c>
-      <c r="I23" t="s">
+      <c r="K23" t="s">
         <v>273</v>
       </c>
-      <c r="J23" t="s">
+      <c r="L23" t="s">
         <v>274</v>
       </c>
-      <c r="K23" t="s">
+      <c r="M23" t="s">
         <v>275</v>
       </c>
-      <c r="L23" t="s">
+      <c r="N23" t="s">
         <v>276</v>
       </c>
-      <c r="M23" t="s">
+      <c r="O23" t="s">
         <v>277</v>
       </c>
-      <c r="N23" t="s">
-        <v>71</v>
-      </c>
-      <c r="O23" t="s">
+      <c r="P23" t="s">
         <v>278</v>
       </c>
-      <c r="P23" t="s">
-        <v>279</v>
-      </c>
       <c r="Q23" t="s">
-        <v>51</v>
+        <v>153</v>
       </c>
       <c r="R23" t="s">
-        <v>280</v>
+        <v>227</v>
       </c>
       <c r="S23" t="s">
-        <v>281</v>
+        <v>228</v>
       </c>
       <c r="T23" t="s">
-        <v>282</v>
+        <v>229</v>
       </c>
       <c r="U23" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="V23"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>20263564</v>
+        <v>20263997</v>
       </c>
       <c r="B24" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="C24" t="s">
         <v>37</v>
       </c>
       <c r="D24" t="s">
-        <v>38</v>
+        <v>280</v>
       </c>
       <c r="E24" t="s">
-        <v>25</v>
+        <v>281</v>
       </c>
       <c r="F24" t="s">
-        <v>264</v>
+        <v>129</v>
       </c>
       <c r="G24" t="s">
         <v>40</v>
       </c>
       <c r="H24" t="s">
-        <v>251</v>
+        <v>55</v>
       </c>
       <c r="I24" t="s">
+        <v>282</v>
+      </c>
+      <c r="J24" t="s">
+        <v>283</v>
+      </c>
+      <c r="K24" t="s">
+        <v>284</v>
+      </c>
+      <c r="L24" t="s">
         <v>285</v>
       </c>
-      <c r="J24" t="s">
+      <c r="M24" t="s">
         <v>286</v>
       </c>
-      <c r="K24" t="s">
+      <c r="N24" t="s">
+        <v>276</v>
+      </c>
+      <c r="O24" t="s">
         <v>287</v>
       </c>
-      <c r="L24" t="s">
+      <c r="P24" t="s">
         <v>288</v>
       </c>
-      <c r="M24" t="s">
+      <c r="Q24" t="s">
+        <v>153</v>
+      </c>
+      <c r="R24" t="s">
         <v>289</v>
       </c>
-      <c r="N24" t="s">
-        <v>71</v>
-      </c>
-      <c r="O24" t="s">
+      <c r="S24" t="s">
         <v>290</v>
       </c>
-      <c r="P24" t="s">
+      <c r="T24" t="s">
         <v>291</v>
       </c>
-      <c r="Q24" t="s">
-        <v>51</v>
-      </c>
-      <c r="R24" t="s">
-        <v>292</v>
-      </c>
-      <c r="S24" t="s">
-        <v>293</v>
-      </c>
-      <c r="T24" t="s">
-        <v>294</v>
-      </c>
       <c r="U24" t="s">
-        <v>26</v>
-      </c>
-      <c r="V24" t="s">
-        <v>26</v>
-      </c>
+        <v>267</v>
+      </c>
+      <c r="V24"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>20263936</v>
+        <v>20263597</v>
       </c>
       <c r="B25" t="s">
+        <v>292</v>
+      </c>
+      <c r="C25" t="s">
+        <v>293</v>
+      </c>
+      <c r="D25" t="s">
+        <v>118</v>
+      </c>
+      <c r="E25" t="s">
+        <v>119</v>
+      </c>
+      <c r="F25" t="s">
+        <v>294</v>
+      </c>
+      <c r="G25" t="s">
+        <v>27</v>
+      </c>
+      <c r="H25" t="s">
+        <v>69</v>
+      </c>
+      <c r="I25" t="s">
         <v>295</v>
       </c>
-      <c r="C25" t="s">
-        <v>37</v>
-      </c>
-      <c r="D25" t="s">
+      <c r="J25" t="s">
         <v>296</v>
       </c>
-      <c r="E25" t="s">
-        <v>239</v>
-      </c>
-      <c r="F25" t="s">
-        <v>90</v>
-      </c>
-      <c r="G25" t="s">
-        <v>40</v>
-      </c>
-      <c r="H25" t="s">
-        <v>66</v>
-      </c>
-      <c r="I25" t="s">
+      <c r="K25" t="s">
         <v>297</v>
       </c>
-      <c r="J25" t="s">
+      <c r="L25" t="s">
         <v>298</v>
       </c>
-      <c r="K25" t="s">
+      <c r="M25" t="s">
         <v>299</v>
       </c>
-      <c r="L25" t="s">
+      <c r="N25" t="s">
+        <v>47</v>
+      </c>
+      <c r="O25" t="s">
         <v>300</v>
       </c>
-      <c r="M25" t="s">
+      <c r="P25" t="s">
         <v>301</v>
       </c>
-      <c r="N25" t="s">
-        <v>245</v>
-      </c>
-      <c r="O25" t="s">
+      <c r="Q25" t="s">
+        <v>50</v>
+      </c>
+      <c r="R25" t="s">
         <v>302</v>
       </c>
-      <c r="P25" t="s">
+      <c r="S25" t="s">
         <v>303</v>
       </c>
-      <c r="Q25" t="s">
+      <c r="T25" t="s">
         <v>304</v>
       </c>
-      <c r="R25" t="s">
+      <c r="U25" t="s">
         <v>305</v>
-      </c>
-      <c r="S25" t="s">
-        <v>306</v>
-      </c>
-      <c r="T25" t="s">
-        <v>307</v>
-      </c>
-      <c r="U25" t="s">
-        <v>308</v>
       </c>
       <c r="V25"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>20263949</v>
+        <v>20263936</v>
       </c>
       <c r="B26" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="C26" t="s">
         <v>37</v>
       </c>
       <c r="D26" t="s">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="E26" t="s">
-        <v>239</v>
+        <v>270</v>
       </c>
       <c r="F26" t="s">
-        <v>90</v>
+        <v>129</v>
       </c>
       <c r="G26" t="s">
         <v>40</v>
       </c>
       <c r="H26" t="s">
-        <v>66</v>
+        <v>106</v>
       </c>
       <c r="I26" t="s">
+        <v>308</v>
+      </c>
+      <c r="J26" t="s">
+        <v>309</v>
+      </c>
+      <c r="K26" t="s">
         <v>310</v>
       </c>
-      <c r="J26" t="s">
+      <c r="L26" t="s">
         <v>311</v>
       </c>
-      <c r="K26" t="s">
+      <c r="M26" t="s">
         <v>312</v>
       </c>
-      <c r="L26" t="s">
+      <c r="N26" t="s">
+        <v>276</v>
+      </c>
+      <c r="O26" t="s">
         <v>313</v>
       </c>
-      <c r="M26" t="s">
+      <c r="P26" t="s">
         <v>314</v>
       </c>
-      <c r="N26" t="s">
-        <v>245</v>
-      </c>
-      <c r="O26" t="s">
+      <c r="Q26" t="s">
         <v>315</v>
       </c>
-      <c r="P26" t="s">
+      <c r="R26" t="s">
         <v>316</v>
       </c>
-      <c r="Q26" t="s">
-        <v>304</v>
-      </c>
-      <c r="R26" t="s">
-        <v>305</v>
-      </c>
       <c r="S26" t="s">
-        <v>306</v>
+        <v>317</v>
       </c>
       <c r="T26" t="s">
-        <v>307</v>
+        <v>318</v>
       </c>
       <c r="U26" t="s">
-        <v>308</v>
+        <v>319</v>
       </c>
       <c r="V26"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>20263601</v>
+        <v>20263949</v>
       </c>
       <c r="B27" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="C27" t="s">
         <v>37</v>
       </c>
       <c r="D27" t="s">
-        <v>318</v>
+        <v>307</v>
       </c>
       <c r="E27" t="s">
-        <v>239</v>
+        <v>270</v>
       </c>
       <c r="F27" t="s">
-        <v>319</v>
+        <v>129</v>
       </c>
       <c r="G27" t="s">
         <v>40</v>
       </c>
       <c r="H27" t="s">
-        <v>131</v>
+        <v>106</v>
       </c>
       <c r="I27" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="J27" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K27" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L27" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M27" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="N27" t="s">
-        <v>245</v>
+        <v>276</v>
       </c>
       <c r="O27" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="P27" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q27" t="s">
-        <v>114</v>
+        <v>315</v>
       </c>
       <c r="R27" t="s">
-        <v>327</v>
+        <v>316</v>
       </c>
       <c r="S27" t="s">
-        <v>328</v>
+        <v>317</v>
       </c>
       <c r="T27" t="s">
-        <v>329</v>
+        <v>318</v>
       </c>
       <c r="U27" t="s">
-        <v>330</v>
+        <v>319</v>
       </c>
       <c r="V27"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>20263563</v>
+        <v>20263601</v>
       </c>
       <c r="B28" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C28" t="s">
         <v>37</v>
       </c>
       <c r="D28" t="s">
-        <v>38</v>
+        <v>329</v>
       </c>
       <c r="E28" t="s">
-        <v>25</v>
+        <v>270</v>
       </c>
       <c r="F28" t="s">
-        <v>264</v>
+        <v>330</v>
       </c>
       <c r="G28" t="s">
         <v>40</v>
       </c>
       <c r="H28" t="s">
-        <v>131</v>
+        <v>41</v>
       </c>
       <c r="I28" t="s">
+        <v>331</v>
+      </c>
+      <c r="J28" t="s">
         <v>332</v>
       </c>
-      <c r="J28" t="s">
+      <c r="K28" t="s">
         <v>333</v>
       </c>
-      <c r="K28" t="s">
+      <c r="L28" t="s">
         <v>334</v>
       </c>
-      <c r="L28" t="s">
+      <c r="M28" t="s">
         <v>335</v>
       </c>
-      <c r="M28" t="s">
+      <c r="N28" t="s">
+        <v>276</v>
+      </c>
+      <c r="O28" t="s">
         <v>336</v>
       </c>
-      <c r="N28" t="s">
-        <v>71</v>
-      </c>
-      <c r="O28" t="s">
+      <c r="P28" t="s">
         <v>337</v>
       </c>
-      <c r="P28" t="s">
+      <c r="Q28" t="s">
+        <v>153</v>
+      </c>
+      <c r="R28" t="s">
         <v>338</v>
       </c>
-      <c r="Q28" t="s">
-        <v>51</v>
-      </c>
-      <c r="R28" t="s">
+      <c r="S28" t="s">
         <v>339</v>
       </c>
-      <c r="S28" t="s">
+      <c r="T28" t="s">
         <v>340</v>
       </c>
-      <c r="T28" t="s">
+      <c r="U28" t="s">
         <v>341</v>
       </c>
-      <c r="U28" t="s">
-        <v>26</v>
-      </c>
-      <c r="V28" t="s">
-        <v>26</v>
-      </c>
+      <c r="V28"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -7745,7 +7739,7 @@
         <v>27</v>
       </c>
       <c r="H29" t="s">
-        <v>251</v>
+        <v>55</v>
       </c>
       <c r="I29" t="s">
         <v>344</v>
@@ -7763,7 +7757,7 @@
         <v>348</v>
       </c>
       <c r="N29" t="s">
-        <v>220</v>
+        <v>251</v>
       </c>
       <c r="O29" t="s">
         <v>349</v>
@@ -7772,7 +7766,7 @@
         <v>350</v>
       </c>
       <c r="Q29" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="R29" t="s">
         <v>351</v>
@@ -7799,10 +7793,10 @@
         <v>37</v>
       </c>
       <c r="D30" t="s">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="E30" t="s">
-        <v>239</v>
+        <v>270</v>
       </c>
       <c r="F30" t="s">
         <v>356</v>
@@ -7811,7 +7805,7 @@
         <v>40</v>
       </c>
       <c r="H30" t="s">
-        <v>66</v>
+        <v>106</v>
       </c>
       <c r="I30" t="s">
         <v>357</v>
@@ -7829,7 +7823,7 @@
         <v>361</v>
       </c>
       <c r="N30" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="O30" t="s">
         <v>362</v>
@@ -7838,19 +7832,19 @@
         <v>363</v>
       </c>
       <c r="Q30" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="R30" t="s">
-        <v>305</v>
+        <v>316</v>
       </c>
       <c r="S30" t="s">
-        <v>306</v>
+        <v>317</v>
       </c>
       <c r="T30" t="s">
-        <v>307</v>
+        <v>318</v>
       </c>
       <c r="U30" t="s">
-        <v>90</v>
+        <v>129</v>
       </c>
       <c r="V30"/>
     </row>
@@ -7862,13 +7856,13 @@
         <v>364</v>
       </c>
       <c r="C31" t="s">
-        <v>271</v>
+        <v>293</v>
       </c>
       <c r="D31" t="s">
-        <v>79</v>
+        <v>118</v>
       </c>
       <c r="E31" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="F31" t="s">
         <v>365</v>
@@ -7877,7 +7871,7 @@
         <v>27</v>
       </c>
       <c r="H31" t="s">
-        <v>167</v>
+        <v>69</v>
       </c>
       <c r="I31" t="s">
         <v>366</v>
@@ -7904,7 +7898,7 @@
         <v>373</v>
       </c>
       <c r="Q31" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="R31" t="s">
         <v>374</v>
@@ -7928,7 +7922,7 @@
         <v>378</v>
       </c>
       <c r="C32" t="s">
-        <v>64</v>
+        <v>104</v>
       </c>
       <c r="D32" t="s">
         <v>38</v>
@@ -7943,7 +7937,7 @@
         <v>40</v>
       </c>
       <c r="H32" t="s">
-        <v>167</v>
+        <v>69</v>
       </c>
       <c r="I32" t="s">
         <v>380</v>
@@ -7959,7 +7953,7 @@
         <v>383</v>
       </c>
       <c r="N32" t="s">
-        <v>245</v>
+        <v>276</v>
       </c>
       <c r="O32" t="s">
         <v>384</v>
@@ -7968,7 +7962,7 @@
         <v>385</v>
       </c>
       <c r="Q32" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="R32" t="s">
         <v>386</v>
@@ -7992,7 +7986,7 @@
         <v>390</v>
       </c>
       <c r="C33" t="s">
-        <v>64</v>
+        <v>104</v>
       </c>
       <c r="D33" t="s">
         <v>38</v>
@@ -8007,7 +8001,7 @@
         <v>40</v>
       </c>
       <c r="H33" t="s">
-        <v>66</v>
+        <v>106</v>
       </c>
       <c r="I33" t="s">
         <v>392</v>
@@ -8023,7 +8017,7 @@
         <v>395</v>
       </c>
       <c r="N33" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="O33" t="s">
         <v>396</v>
@@ -8032,7 +8026,7 @@
         <v>397</v>
       </c>
       <c r="Q33" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="R33" t="s">
         <v>398</v>
@@ -8056,13 +8050,13 @@
         <v>401</v>
       </c>
       <c r="C34" t="s">
-        <v>64</v>
+        <v>104</v>
       </c>
       <c r="D34" t="s">
-        <v>179</v>
+        <v>211</v>
       </c>
       <c r="E34" t="s">
-        <v>180</v>
+        <v>68</v>
       </c>
       <c r="F34" t="s">
         <v>391</v>
@@ -8071,7 +8065,7 @@
         <v>40</v>
       </c>
       <c r="H34" t="s">
-        <v>66</v>
+        <v>106</v>
       </c>
       <c r="I34" t="s">
         <v>402</v>
@@ -8087,7 +8081,7 @@
         <v>405</v>
       </c>
       <c r="N34" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="O34" t="s">
         <v>406</v>
@@ -8096,7 +8090,7 @@
         <v>407</v>
       </c>
       <c r="Q34" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="R34" t="s">
         <v>408</v>
@@ -8135,7 +8129,7 @@
         <v>40</v>
       </c>
       <c r="H35" t="s">
-        <v>251</v>
+        <v>55</v>
       </c>
       <c r="I35" t="s">
         <v>414</v>
@@ -8153,7 +8147,7 @@
         <v>418</v>
       </c>
       <c r="N35" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="O35" t="s">
         <v>419</v>
@@ -8162,7 +8156,7 @@
         <v>420</v>
       </c>
       <c r="Q35" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="R35" t="s">
         <v>421</v>
@@ -8189,19 +8183,19 @@
         <v>37</v>
       </c>
       <c r="D36" t="s">
-        <v>79</v>
+        <v>118</v>
       </c>
       <c r="E36" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="F36" t="s">
-        <v>166</v>
+        <v>204</v>
       </c>
       <c r="G36" t="s">
         <v>27</v>
       </c>
       <c r="H36" t="s">
-        <v>131</v>
+        <v>41</v>
       </c>
       <c r="I36" t="s">
         <v>426</v>
@@ -8219,7 +8213,7 @@
         <v>430</v>
       </c>
       <c r="N36" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="O36" t="s">
         <v>431</v>
@@ -8228,7 +8222,7 @@
         <v>432</v>
       </c>
       <c r="Q36" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="R36" t="s">
         <v>433</v>
@@ -8258,7 +8252,7 @@
         <v>437</v>
       </c>
       <c r="E37" t="s">
-        <v>239</v>
+        <v>270</v>
       </c>
       <c r="F37" t="s">
         <v>343</v>
@@ -8267,7 +8261,7 @@
         <v>40</v>
       </c>
       <c r="H37" t="s">
-        <v>66</v>
+        <v>106</v>
       </c>
       <c r="I37" t="s">
         <v>438</v>
@@ -8285,7 +8279,7 @@
         <v>442</v>
       </c>
       <c r="N37" t="s">
-        <v>245</v>
+        <v>276</v>
       </c>
       <c r="O37" t="s">
         <v>443</v>
@@ -8294,7 +8288,7 @@
         <v>444</v>
       </c>
       <c r="Q37" t="s">
-        <v>114</v>
+        <v>153</v>
       </c>
       <c r="R37" t="s">
         <v>445</v>
@@ -8333,7 +8327,7 @@
         <v>40</v>
       </c>
       <c r="H38" t="s">
-        <v>131</v>
+        <v>41</v>
       </c>
       <c r="I38" t="s">
         <v>451</v>
@@ -8351,7 +8345,7 @@
         <v>455</v>
       </c>
       <c r="N38" t="s">
-        <v>245</v>
+        <v>276</v>
       </c>
       <c r="O38" t="s">
         <v>456</v>
@@ -8360,7 +8354,7 @@
         <v>457</v>
       </c>
       <c r="Q38" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="R38" t="s">
         <v>433</v>
@@ -8397,7 +8391,7 @@
         <v>40</v>
       </c>
       <c r="H39" t="s">
-        <v>91</v>
+        <v>130</v>
       </c>
       <c r="I39" t="s">
         <v>460</v>
@@ -8415,7 +8409,7 @@
         <v>464</v>
       </c>
       <c r="N39" t="s">
-        <v>245</v>
+        <v>276</v>
       </c>
       <c r="O39" t="s">
         <v>465</v>
@@ -8424,7 +8418,7 @@
         <v>466</v>
       </c>
       <c r="Q39" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="R39" t="s">
         <v>467</v>
@@ -8451,10 +8445,10 @@
         <v>37</v>
       </c>
       <c r="D40" t="s">
-        <v>179</v>
+        <v>211</v>
       </c>
       <c r="E40" t="s">
-        <v>180</v>
+        <v>68</v>
       </c>
       <c r="F40" t="s">
         <v>343</v>
@@ -8463,7 +8457,7 @@
         <v>40</v>
       </c>
       <c r="H40" t="s">
-        <v>131</v>
+        <v>41</v>
       </c>
       <c r="I40" t="s">
         <v>472</v>
@@ -8481,7 +8475,7 @@
         <v>476</v>
       </c>
       <c r="N40" t="s">
-        <v>245</v>
+        <v>276</v>
       </c>
       <c r="O40" t="s">
         <v>477</v>
@@ -8490,16 +8484,16 @@
         <v>478</v>
       </c>
       <c r="Q40" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="R40" t="s">
-        <v>138</v>
+        <v>176</v>
       </c>
       <c r="S40" t="s">
-        <v>139</v>
+        <v>177</v>
       </c>
       <c r="T40" t="s">
-        <v>140</v>
+        <v>178</v>
       </c>
       <c r="U40" t="s">
         <v>470</v>
@@ -8520,7 +8514,7 @@
         <v>480</v>
       </c>
       <c r="E41" t="s">
-        <v>180</v>
+        <v>68</v>
       </c>
       <c r="F41" t="s">
         <v>481</v>
@@ -8547,7 +8541,7 @@
         <v>487</v>
       </c>
       <c r="N41" t="s">
-        <v>245</v>
+        <v>276</v>
       </c>
       <c r="O41" t="s">
         <v>488</v>
@@ -8556,7 +8550,7 @@
         <v>489</v>
       </c>
       <c r="Q41" t="s">
-        <v>114</v>
+        <v>153</v>
       </c>
       <c r="R41" t="s">
         <v>490</v>
@@ -8586,16 +8580,16 @@
         <v>494</v>
       </c>
       <c r="E42" t="s">
-        <v>180</v>
+        <v>68</v>
       </c>
       <c r="F42" t="s">
-        <v>166</v>
+        <v>204</v>
       </c>
       <c r="G42" t="s">
         <v>40</v>
       </c>
       <c r="H42" t="s">
-        <v>251</v>
+        <v>55</v>
       </c>
       <c r="I42" t="s">
         <v>495</v>
@@ -8613,7 +8607,7 @@
         <v>499</v>
       </c>
       <c r="N42" t="s">
-        <v>245</v>
+        <v>276</v>
       </c>
       <c r="O42" t="s">
         <v>500</v>
@@ -8652,7 +8646,7 @@
         <v>507</v>
       </c>
       <c r="E43" t="s">
-        <v>180</v>
+        <v>68</v>
       </c>
       <c r="F43" t="s">
         <v>508</v>
@@ -8661,7 +8655,7 @@
         <v>40</v>
       </c>
       <c r="H43" t="s">
-        <v>131</v>
+        <v>41</v>
       </c>
       <c r="I43" t="s">
         <v>509</v>
@@ -8679,7 +8673,7 @@
         <v>513</v>
       </c>
       <c r="N43" t="s">
-        <v>245</v>
+        <v>276</v>
       </c>
       <c r="O43" t="s">
         <v>514</v>
@@ -8688,16 +8682,16 @@
         <v>515</v>
       </c>
       <c r="Q43" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="R43" t="s">
-        <v>138</v>
+        <v>176</v>
       </c>
       <c r="S43" t="s">
-        <v>139</v>
+        <v>177</v>
       </c>
       <c r="T43" t="s">
-        <v>140</v>
+        <v>178</v>
       </c>
       <c r="U43" t="s">
         <v>505</v>
@@ -8715,10 +8709,10 @@
         <v>23</v>
       </c>
       <c r="D44" t="s">
-        <v>79</v>
+        <v>118</v>
       </c>
       <c r="E44" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="F44" t="s">
         <v>517</v>
@@ -8727,7 +8721,7 @@
         <v>27</v>
       </c>
       <c r="H44" t="s">
-        <v>167</v>
+        <v>69</v>
       </c>
       <c r="I44" t="s">
         <v>518</v>
@@ -8745,7 +8739,7 @@
         <v>522</v>
       </c>
       <c r="N44" t="s">
-        <v>158</v>
+        <v>196</v>
       </c>
       <c r="O44" t="s">
         <v>523</v>
@@ -8754,16 +8748,16 @@
         <v>524</v>
       </c>
       <c r="Q44" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="R44" t="s">
-        <v>207</v>
+        <v>238</v>
       </c>
       <c r="S44" t="s">
-        <v>208</v>
+        <v>239</v>
       </c>
       <c r="T44" t="s">
-        <v>209</v>
+        <v>240</v>
       </c>
       <c r="U44" t="s">
         <v>525</v>
@@ -8778,7 +8772,7 @@
         <v>526</v>
       </c>
       <c r="C45" t="s">
-        <v>64</v>
+        <v>104</v>
       </c>
       <c r="D45" t="s">
         <v>412</v>
@@ -8793,7 +8787,7 @@
         <v>40</v>
       </c>
       <c r="H45" t="s">
-        <v>66</v>
+        <v>106</v>
       </c>
       <c r="I45" t="s">
         <v>528</v>
@@ -8809,7 +8803,7 @@
         <v>531</v>
       </c>
       <c r="N45" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="O45" t="s">
         <v>532</v>
@@ -8818,7 +8812,7 @@
         <v>533</v>
       </c>
       <c r="Q45" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="R45" t="s">
         <v>534</v>
@@ -8842,7 +8836,7 @@
         <v>538</v>
       </c>
       <c r="C46" t="s">
-        <v>64</v>
+        <v>104</v>
       </c>
       <c r="D46" t="s">
         <v>539</v>
@@ -8857,7 +8851,7 @@
         <v>40</v>
       </c>
       <c r="H46" t="s">
-        <v>167</v>
+        <v>69</v>
       </c>
       <c r="I46" t="s">
         <v>541</v>
@@ -8873,7 +8867,7 @@
         <v>544</v>
       </c>
       <c r="N46" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="O46" t="s">
         <v>545</v>
@@ -8882,7 +8876,7 @@
         <v>546</v>
       </c>
       <c r="Q46" t="s">
-        <v>114</v>
+        <v>153</v>
       </c>
       <c r="R46" t="s">
         <v>547</v>
@@ -8910,14 +8904,14 @@
       </c>
       <c r="D47"/>
       <c r="E47" t="s">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="F47" t="s">
         <v>552</v>
       </c>
       <c r="G47"/>
       <c r="H47" t="s">
-        <v>167</v>
+        <v>69</v>
       </c>
       <c r="I47" t="s">
         <v>553</v>
@@ -8931,7 +8925,7 @@
       <c r="L47"/>
       <c r="M47"/>
       <c r="N47" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="O47" t="s">
         <v>556</v>
@@ -8940,7 +8934,7 @@
         <v>557</v>
       </c>
       <c r="Q47" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="R47" t="s">
         <v>490</v>
@@ -8964,13 +8958,13 @@
         <v>558</v>
       </c>
       <c r="C48" t="s">
-        <v>64</v>
+        <v>104</v>
       </c>
       <c r="D48" t="s">
         <v>437</v>
       </c>
       <c r="E48" t="s">
-        <v>239</v>
+        <v>270</v>
       </c>
       <c r="F48" t="s">
         <v>559</v>
@@ -8979,7 +8973,7 @@
         <v>40</v>
       </c>
       <c r="H48" t="s">
-        <v>251</v>
+        <v>55</v>
       </c>
       <c r="I48" t="s">
         <v>560</v>
@@ -8995,7 +8989,7 @@
         <v>563</v>
       </c>
       <c r="N48" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="O48" t="s">
         <v>564</v>
@@ -9034,7 +9028,7 @@
         <v>570</v>
       </c>
       <c r="E49" t="s">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="F49" t="s">
         <v>571</v>
@@ -9043,7 +9037,7 @@
         <v>40</v>
       </c>
       <c r="H49" t="s">
-        <v>91</v>
+        <v>130</v>
       </c>
       <c r="I49" t="s">
         <v>572</v>
@@ -9061,7 +9055,7 @@
         <v>576</v>
       </c>
       <c r="N49" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="O49" t="s">
         <v>577</v>
@@ -9073,13 +9067,13 @@
         <v>35</v>
       </c>
       <c r="R49" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="S49" t="s">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="T49" t="s">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="U49" t="s">
         <v>537</v>
@@ -9109,7 +9103,7 @@
         <v>40</v>
       </c>
       <c r="H50" t="s">
-        <v>91</v>
+        <v>130</v>
       </c>
       <c r="I50" t="s">
         <v>582</v>
@@ -9127,7 +9121,7 @@
         <v>586</v>
       </c>
       <c r="N50" t="s">
-        <v>245</v>
+        <v>276</v>
       </c>
       <c r="O50" t="s">
         <v>587</v>
@@ -9136,7 +9130,7 @@
         <v>588</v>
       </c>
       <c r="Q50" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="R50" t="s">
         <v>589</v>
@@ -9166,7 +9160,7 @@
         <v>593</v>
       </c>
       <c r="E51" t="s">
-        <v>180</v>
+        <v>68</v>
       </c>
       <c r="F51" t="s">
         <v>517</v>
@@ -9175,7 +9169,7 @@
         <v>40</v>
       </c>
       <c r="H51" t="s">
-        <v>131</v>
+        <v>41</v>
       </c>
       <c r="I51" t="s">
         <v>594</v>
@@ -9193,7 +9187,7 @@
         <v>598</v>
       </c>
       <c r="N51" t="s">
-        <v>245</v>
+        <v>276</v>
       </c>
       <c r="O51" t="s">
         <v>599</v>
@@ -9202,7 +9196,7 @@
         <v>600</v>
       </c>
       <c r="Q51" t="s">
-        <v>114</v>
+        <v>153</v>
       </c>
       <c r="R51" t="s">
         <v>601</v>
@@ -9229,10 +9223,10 @@
         <v>23</v>
       </c>
       <c r="D52" t="s">
-        <v>79</v>
+        <v>118</v>
       </c>
       <c r="E52" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="F52" t="s">
         <v>605</v>
@@ -9241,7 +9235,7 @@
         <v>27</v>
       </c>
       <c r="H52" t="s">
-        <v>152</v>
+        <v>190</v>
       </c>
       <c r="I52" t="s">
         <v>606</v>
@@ -9259,7 +9253,7 @@
         <v>610</v>
       </c>
       <c r="N52" t="s">
-        <v>220</v>
+        <v>251</v>
       </c>
       <c r="O52" t="s">
         <v>611</v>
@@ -9268,7 +9262,7 @@
         <v>612</v>
       </c>
       <c r="Q52" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="R52" t="s">
         <v>613</v>
@@ -9292,13 +9286,13 @@
         <v>616</v>
       </c>
       <c r="C53" t="s">
-        <v>271</v>
+        <v>293</v>
       </c>
       <c r="D53" t="s">
-        <v>79</v>
+        <v>118</v>
       </c>
       <c r="E53" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="F53" t="s">
         <v>605</v>
@@ -9307,7 +9301,7 @@
         <v>27</v>
       </c>
       <c r="H53" t="s">
-        <v>167</v>
+        <v>69</v>
       </c>
       <c r="I53" t="s">
         <v>617</v>
@@ -9334,7 +9328,7 @@
         <v>623</v>
       </c>
       <c r="Q53" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="R53" t="s">
         <v>624</v>
@@ -9364,7 +9358,7 @@
         <v>628</v>
       </c>
       <c r="E54" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="F54" t="s">
         <v>629</v>
@@ -9373,7 +9367,7 @@
         <v>27</v>
       </c>
       <c r="H54" t="s">
-        <v>91</v>
+        <v>130</v>
       </c>
       <c r="I54" t="s">
         <v>630</v>
@@ -9391,7 +9385,7 @@
         <v>634</v>
       </c>
       <c r="N54" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="O54" t="s">
         <v>635</v>
@@ -9400,7 +9394,7 @@
         <v>636</v>
       </c>
       <c r="Q54" t="s">
-        <v>114</v>
+        <v>153</v>
       </c>
       <c r="R54" t="s">
         <v>637</v>
@@ -9430,7 +9424,7 @@
         <v>494</v>
       </c>
       <c r="E55" t="s">
-        <v>180</v>
+        <v>68</v>
       </c>
       <c r="F55" t="s">
         <v>413</v>
@@ -9439,7 +9433,7 @@
         <v>40</v>
       </c>
       <c r="H55" t="s">
-        <v>91</v>
+        <v>130</v>
       </c>
       <c r="I55" t="s">
         <v>641</v>
@@ -9457,7 +9451,7 @@
         <v>645</v>
       </c>
       <c r="N55" t="s">
-        <v>245</v>
+        <v>276</v>
       </c>
       <c r="O55" t="s">
         <v>646</v>
@@ -9466,16 +9460,16 @@
         <v>647</v>
       </c>
       <c r="Q55" t="s">
-        <v>114</v>
+        <v>153</v>
       </c>
       <c r="R55" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="S55" t="s">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="T55" t="s">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="U55" t="s">
         <v>537</v>
@@ -9490,7 +9484,7 @@
         <v>648</v>
       </c>
       <c r="C56" t="s">
-        <v>64</v>
+        <v>104</v>
       </c>
       <c r="D56" t="s">
         <v>649</v>
@@ -9505,7 +9499,7 @@
         <v>40</v>
       </c>
       <c r="H56" t="s">
-        <v>152</v>
+        <v>190</v>
       </c>
       <c r="I56" t="s">
         <v>651</v>
@@ -9521,7 +9515,7 @@
         <v>654</v>
       </c>
       <c r="N56" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="O56" t="s">
         <v>655</v>
@@ -9554,13 +9548,13 @@
         <v>660</v>
       </c>
       <c r="C57" t="s">
-        <v>64</v>
+        <v>104</v>
       </c>
       <c r="D57" t="s">
         <v>480</v>
       </c>
       <c r="E57" t="s">
-        <v>180</v>
+        <v>68</v>
       </c>
       <c r="F57" t="s">
         <v>650</v>
@@ -9569,7 +9563,7 @@
         <v>40</v>
       </c>
       <c r="H57" t="s">
-        <v>167</v>
+        <v>69</v>
       </c>
       <c r="I57" t="s">
         <v>661</v>
@@ -9585,7 +9579,7 @@
         <v>664</v>
       </c>
       <c r="N57" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="O57" t="s">
         <v>665</v>
@@ -9597,13 +9591,13 @@
         <v>35</v>
       </c>
       <c r="R57" t="s">
-        <v>175</v>
+        <v>77</v>
       </c>
       <c r="S57" t="s">
-        <v>176</v>
+        <v>78</v>
       </c>
       <c r="T57" t="s">
-        <v>177</v>
+        <v>79</v>
       </c>
       <c r="U57" t="s">
         <v>537</v>
@@ -9618,7 +9612,7 @@
         <v>667</v>
       </c>
       <c r="C58" t="s">
-        <v>271</v>
+        <v>293</v>
       </c>
       <c r="D58" t="s">
         <v>668</v>
@@ -9631,7 +9625,7 @@
         <v>40</v>
       </c>
       <c r="H58" t="s">
-        <v>251</v>
+        <v>55</v>
       </c>
       <c r="I58" t="s">
         <v>670</v>
@@ -9688,7 +9682,7 @@
         <v>681</v>
       </c>
       <c r="E59" t="s">
-        <v>180</v>
+        <v>68</v>
       </c>
       <c r="F59" t="s">
         <v>682</v>
@@ -9697,7 +9691,7 @@
         <v>27</v>
       </c>
       <c r="H59" t="s">
-        <v>91</v>
+        <v>130</v>
       </c>
       <c r="I59" t="s">
         <v>683</v>
@@ -9715,7 +9709,7 @@
         <v>687</v>
       </c>
       <c r="N59" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="O59" t="s">
         <v>688</v>
@@ -9748,13 +9742,13 @@
         <v>693</v>
       </c>
       <c r="C60" t="s">
-        <v>271</v>
+        <v>293</v>
       </c>
       <c r="D60" t="s">
         <v>694</v>
       </c>
       <c r="E60" t="s">
-        <v>239</v>
+        <v>270</v>
       </c>
       <c r="F60" t="s">
         <v>682</v>
@@ -9763,7 +9757,7 @@
         <v>40</v>
       </c>
       <c r="H60" t="s">
-        <v>91</v>
+        <v>130</v>
       </c>
       <c r="I60" t="s">
         <v>695</v>
@@ -9781,7 +9775,7 @@
         <v>699</v>
       </c>
       <c r="N60" t="s">
-        <v>245</v>
+        <v>276</v>
       </c>
       <c r="O60" t="s">
         <v>700</v>
@@ -9829,7 +9823,7 @@
         <v>40</v>
       </c>
       <c r="H61" t="s">
-        <v>131</v>
+        <v>41</v>
       </c>
       <c r="I61" t="s">
         <v>703</v>
@@ -9847,7 +9841,7 @@
         <v>707</v>
       </c>
       <c r="N61" t="s">
-        <v>245</v>
+        <v>276</v>
       </c>
       <c r="O61" t="s">
         <v>708</v>
@@ -9856,16 +9850,16 @@
         <v>709</v>
       </c>
       <c r="Q61" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="R61" t="s">
-        <v>138</v>
+        <v>176</v>
       </c>
       <c r="S61" t="s">
-        <v>139</v>
+        <v>177</v>
       </c>
       <c r="T61" t="s">
-        <v>140</v>
+        <v>178</v>
       </c>
       <c r="U61" t="s">
         <v>537</v>
@@ -9895,7 +9889,7 @@
         <v>27</v>
       </c>
       <c r="H62" t="s">
-        <v>251</v>
+        <v>55</v>
       </c>
       <c r="I62" t="s">
         <v>711</v>
@@ -9913,7 +9907,7 @@
         <v>715</v>
       </c>
       <c r="N62" t="s">
-        <v>220</v>
+        <v>251</v>
       </c>
       <c r="O62" t="s">
         <v>716</v>
@@ -9922,7 +9916,7 @@
         <v>717</v>
       </c>
       <c r="Q62" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="R62" t="s">
         <v>718</v>
@@ -9952,7 +9946,7 @@
         <v>722</v>
       </c>
       <c r="E63" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="F63" t="s">
         <v>723</v>
@@ -9961,7 +9955,7 @@
         <v>40</v>
       </c>
       <c r="H63" t="s">
-        <v>91</v>
+        <v>130</v>
       </c>
       <c r="I63" t="s">
         <v>724</v>
@@ -9979,7 +9973,7 @@
         <v>728</v>
       </c>
       <c r="N63" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="O63" t="s">
         <v>729</v>
@@ -9988,7 +9982,7 @@
         <v>730</v>
       </c>
       <c r="Q63" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="R63" t="s">
         <v>589</v>
@@ -10015,10 +10009,10 @@
         <v>37</v>
       </c>
       <c r="D64" t="s">
-        <v>79</v>
+        <v>118</v>
       </c>
       <c r="E64" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="F64" t="s">
         <v>732</v>
@@ -10027,7 +10021,7 @@
         <v>27</v>
       </c>
       <c r="H64" t="s">
-        <v>66</v>
+        <v>106</v>
       </c>
       <c r="I64" t="s">
         <v>733</v>
@@ -10045,7 +10039,7 @@
         <v>737</v>
       </c>
       <c r="N64" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="O64" t="s">
         <v>738</v>
@@ -10054,7 +10048,7 @@
         <v>739</v>
       </c>
       <c r="Q64" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="R64" t="s">
         <v>740</v>
@@ -10084,7 +10078,7 @@
         <v>744</v>
       </c>
       <c r="E65" t="s">
-        <v>180</v>
+        <v>68</v>
       </c>
       <c r="F65" t="s">
         <v>732</v>
@@ -10093,7 +10087,7 @@
         <v>40</v>
       </c>
       <c r="H65" t="s">
-        <v>152</v>
+        <v>190</v>
       </c>
       <c r="I65" t="s">
         <v>745</v>
@@ -10111,7 +10105,7 @@
         <v>749</v>
       </c>
       <c r="N65" t="s">
-        <v>245</v>
+        <v>276</v>
       </c>
       <c r="O65" t="s">
         <v>750</v>
@@ -10120,7 +10114,7 @@
         <v>751</v>
       </c>
       <c r="Q65" t="s">
-        <v>114</v>
+        <v>153</v>
       </c>
       <c r="R65" t="s">
         <v>752</v>
@@ -10150,7 +10144,7 @@
         <v>756</v>
       </c>
       <c r="E66" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="F66" t="s">
         <v>757</v>
@@ -10159,7 +10153,7 @@
         <v>27</v>
       </c>
       <c r="H66" t="s">
-        <v>91</v>
+        <v>130</v>
       </c>
       <c r="I66" t="s">
         <v>758</v>
@@ -10177,7 +10171,7 @@
         <v>762</v>
       </c>
       <c r="N66" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="O66" t="s">
         <v>763</v>
@@ -10186,7 +10180,7 @@
         <v>764</v>
       </c>
       <c r="Q66" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="R66" t="s">
         <v>765</v>
@@ -10213,10 +10207,10 @@
         <v>769</v>
       </c>
       <c r="D67" t="s">
-        <v>179</v>
+        <v>211</v>
       </c>
       <c r="E67" t="s">
-        <v>180</v>
+        <v>68</v>
       </c>
       <c r="F67" t="s">
         <v>770</v>
@@ -10225,7 +10219,7 @@
         <v>40</v>
       </c>
       <c r="H67" t="s">
-        <v>91</v>
+        <v>130</v>
       </c>
       <c r="I67" t="s">
         <v>771</v>
@@ -10252,7 +10246,7 @@
         <v>778</v>
       </c>
       <c r="Q67" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="R67" t="s">
         <v>779</v>
@@ -10291,7 +10285,7 @@
         <v>40</v>
       </c>
       <c r="H68" t="s">
-        <v>131</v>
+        <v>41</v>
       </c>
       <c r="I68" t="s">
         <v>785</v>
@@ -10309,7 +10303,7 @@
         <v>789</v>
       </c>
       <c r="N68" t="s">
-        <v>245</v>
+        <v>276</v>
       </c>
       <c r="O68" t="s">
         <v>790</v>
@@ -10321,13 +10315,13 @@
         <v>35</v>
       </c>
       <c r="R68" t="s">
-        <v>186</v>
+        <v>217</v>
       </c>
       <c r="S68" t="s">
-        <v>187</v>
+        <v>218</v>
       </c>
       <c r="T68" t="s">
-        <v>188</v>
+        <v>219</v>
       </c>
       <c r="U68" t="s">
         <v>537</v>
@@ -10342,13 +10336,13 @@
         <v>792</v>
       </c>
       <c r="C69" t="s">
-        <v>64</v>
+        <v>104</v>
       </c>
       <c r="D69" t="s">
-        <v>249</v>
+        <v>280</v>
       </c>
       <c r="E69" t="s">
-        <v>250</v>
+        <v>281</v>
       </c>
       <c r="F69" t="s">
         <v>784</v>
@@ -10357,7 +10351,7 @@
         <v>40</v>
       </c>
       <c r="H69" t="s">
-        <v>91</v>
+        <v>130</v>
       </c>
       <c r="I69" t="s">
         <v>793</v>
@@ -10373,7 +10367,7 @@
         <v>796</v>
       </c>
       <c r="N69" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="O69" t="s">
         <v>797</v>
@@ -10382,7 +10376,7 @@
         <v>798</v>
       </c>
       <c r="Q69" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="R69" t="s">
         <v>589</v>
@@ -10406,13 +10400,13 @@
         <v>799</v>
       </c>
       <c r="C70" t="s">
-        <v>64</v>
+        <v>104</v>
       </c>
       <c r="D70" t="s">
         <v>800</v>
       </c>
       <c r="E70" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="F70" t="s">
         <v>784</v>
@@ -10421,7 +10415,7 @@
         <v>40</v>
       </c>
       <c r="H70" t="s">
-        <v>66</v>
+        <v>106</v>
       </c>
       <c r="I70" t="s">
         <v>801</v>
@@ -10437,7 +10431,7 @@
         <v>804</v>
       </c>
       <c r="N70" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="O70" t="s">
         <v>805</v>
@@ -10446,7 +10440,7 @@
         <v>806</v>
       </c>
       <c r="Q70" t="s">
-        <v>114</v>
+        <v>153</v>
       </c>
       <c r="R70" t="s">
         <v>807</v>
@@ -10470,13 +10464,13 @@
         <v>810</v>
       </c>
       <c r="C71" t="s">
-        <v>64</v>
+        <v>104</v>
       </c>
       <c r="D71" t="s">
         <v>744</v>
       </c>
       <c r="E71" t="s">
-        <v>180</v>
+        <v>68</v>
       </c>
       <c r="F71" t="s">
         <v>811</v>
@@ -10485,7 +10479,7 @@
         <v>40</v>
       </c>
       <c r="H71" t="s">
-        <v>167</v>
+        <v>69</v>
       </c>
       <c r="I71" t="s">
         <v>812</v>
@@ -10501,7 +10495,7 @@
         <v>815</v>
       </c>
       <c r="N71" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="O71" t="s">
         <v>816</v>
@@ -10510,7 +10504,7 @@
         <v>817</v>
       </c>
       <c r="Q71" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="R71" t="s">
         <v>818</v>
@@ -10540,7 +10534,7 @@
         <v>822</v>
       </c>
       <c r="E72" t="s">
-        <v>180</v>
+        <v>68</v>
       </c>
       <c r="F72" t="s">
         <v>823</v>
@@ -10549,7 +10543,7 @@
         <v>40</v>
       </c>
       <c r="H72" t="s">
-        <v>152</v>
+        <v>190</v>
       </c>
       <c r="I72" t="s">
         <v>824</v>
@@ -10567,7 +10561,7 @@
         <v>828</v>
       </c>
       <c r="N72" t="s">
-        <v>245</v>
+        <v>276</v>
       </c>
       <c r="O72" t="s">
         <v>829</v>
@@ -10600,13 +10594,13 @@
         <v>834</v>
       </c>
       <c r="C73" t="s">
-        <v>64</v>
+        <v>104</v>
       </c>
       <c r="D73" t="s">
         <v>822</v>
       </c>
       <c r="E73" t="s">
-        <v>180</v>
+        <v>68</v>
       </c>
       <c r="F73" t="s">
         <v>823</v>
@@ -10615,7 +10609,7 @@
         <v>40</v>
       </c>
       <c r="H73" t="s">
-        <v>152</v>
+        <v>190</v>
       </c>
       <c r="I73" t="s">
         <v>835</v>
@@ -10631,7 +10625,7 @@
         <v>838</v>
       </c>
       <c r="N73" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="O73" t="s">
         <v>839</v>
@@ -10664,7 +10658,7 @@
         <v>844</v>
       </c>
       <c r="C74" t="s">
-        <v>211</v>
+        <v>242</v>
       </c>
       <c r="D74" t="s">
         <v>845</v>
@@ -10675,7 +10669,7 @@
       </c>
       <c r="G74"/>
       <c r="H74" t="s">
-        <v>167</v>
+        <v>69</v>
       </c>
       <c r="I74" t="s">
         <v>847</v>
@@ -10693,7 +10687,7 @@
         <v>851</v>
       </c>
       <c r="N74" t="s">
-        <v>230</v>
+        <v>261</v>
       </c>
       <c r="O74" t="s">
         <v>852</v>
@@ -10735,7 +10729,7 @@
         <v>40</v>
       </c>
       <c r="H75" t="s">
-        <v>131</v>
+        <v>41</v>
       </c>
       <c r="I75" t="s">
         <v>857</v>
@@ -10753,7 +10747,7 @@
         <v>861</v>
       </c>
       <c r="N75" t="s">
-        <v>245</v>
+        <v>276</v>
       </c>
       <c r="O75" t="s">
         <v>862</v>
@@ -10762,7 +10756,7 @@
         <v>863</v>
       </c>
       <c r="Q75" t="s">
-        <v>114</v>
+        <v>153</v>
       </c>
       <c r="R75" t="s">
         <v>864</v>
@@ -10801,7 +10795,7 @@
         <v>40</v>
       </c>
       <c r="H76" t="s">
-        <v>131</v>
+        <v>41</v>
       </c>
       <c r="I76" t="s">
         <v>869</v>
@@ -10819,7 +10813,7 @@
         <v>873</v>
       </c>
       <c r="N76" t="s">
-        <v>245</v>
+        <v>276</v>
       </c>
       <c r="O76" t="s">
         <v>874</v>
@@ -10852,13 +10846,13 @@
         <v>879</v>
       </c>
       <c r="C77" t="s">
-        <v>271</v>
+        <v>293</v>
       </c>
       <c r="D77" t="s">
         <v>880</v>
       </c>
       <c r="E77" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="F77" t="s">
         <v>856</v>
@@ -10867,7 +10861,7 @@
         <v>40</v>
       </c>
       <c r="H77" t="s">
-        <v>91</v>
+        <v>130</v>
       </c>
       <c r="I77" t="s">
         <v>881</v>
@@ -10931,7 +10925,7 @@
         <v>40</v>
       </c>
       <c r="H78" t="s">
-        <v>91</v>
+        <v>130</v>
       </c>
       <c r="I78" t="s">
         <v>894</v>
@@ -10949,7 +10943,7 @@
         <v>898</v>
       </c>
       <c r="N78" t="s">
-        <v>245</v>
+        <v>276</v>
       </c>
       <c r="O78" t="s">
         <v>899</v>
@@ -10958,7 +10952,7 @@
         <v>900</v>
       </c>
       <c r="Q78" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="R78" t="s">
         <v>901</v>
@@ -10997,7 +10991,7 @@
         <v>40</v>
       </c>
       <c r="H79" t="s">
-        <v>251</v>
+        <v>55</v>
       </c>
       <c r="I79" t="s">
         <v>906</v>
@@ -11015,7 +11009,7 @@
         <v>910</v>
       </c>
       <c r="N79" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="O79" t="s">
         <v>911</v>
@@ -11024,7 +11018,7 @@
         <v>912</v>
       </c>
       <c r="Q79" t="s">
-        <v>114</v>
+        <v>153</v>
       </c>
       <c r="R79" t="s">
         <v>913</v>
@@ -11063,7 +11057,7 @@
         <v>40</v>
       </c>
       <c r="H80" t="s">
-        <v>131</v>
+        <v>41</v>
       </c>
       <c r="I80" t="s">
         <v>919</v>
@@ -11081,7 +11075,7 @@
         <v>923</v>
       </c>
       <c r="N80" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="O80" t="s">
         <v>924</v>
@@ -11090,16 +11084,16 @@
         <v>925</v>
       </c>
       <c r="Q80" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="R80" t="s">
-        <v>138</v>
+        <v>176</v>
       </c>
       <c r="S80" t="s">
-        <v>139</v>
+        <v>177</v>
       </c>
       <c r="T80" t="s">
-        <v>140</v>
+        <v>178</v>
       </c>
       <c r="U80" t="s">
         <v>537</v>
@@ -11114,7 +11108,7 @@
         <v>926</v>
       </c>
       <c r="C81" t="s">
-        <v>271</v>
+        <v>293</v>
       </c>
       <c r="D81" t="s">
         <v>927</v>
@@ -11127,7 +11121,7 @@
         <v>40</v>
       </c>
       <c r="H81" t="s">
-        <v>131</v>
+        <v>41</v>
       </c>
       <c r="I81" t="s">
         <v>928</v>
@@ -11184,7 +11178,7 @@
         <v>694</v>
       </c>
       <c r="E82" t="s">
-        <v>239</v>
+        <v>270</v>
       </c>
       <c r="F82" t="s">
         <v>918</v>
@@ -11193,7 +11187,7 @@
         <v>40</v>
       </c>
       <c r="H82" t="s">
-        <v>131</v>
+        <v>41</v>
       </c>
       <c r="I82" t="s">
         <v>939</v>
@@ -11211,7 +11205,7 @@
         <v>943</v>
       </c>
       <c r="N82" t="s">
-        <v>245</v>
+        <v>276</v>
       </c>
       <c r="O82" t="s">
         <v>944</v>
@@ -11220,7 +11214,7 @@
         <v>945</v>
       </c>
       <c r="Q82" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="R82" t="s">
         <v>946</v>
@@ -11259,7 +11253,7 @@
         <v>27</v>
       </c>
       <c r="H83" t="s">
-        <v>131</v>
+        <v>41</v>
       </c>
       <c r="I83" t="s">
         <v>952</v>
@@ -11277,7 +11271,7 @@
         <v>956</v>
       </c>
       <c r="N83" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="O83" t="s">
         <v>957</v>
@@ -11316,7 +11310,7 @@
         <v>960</v>
       </c>
       <c r="E84" t="s">
-        <v>180</v>
+        <v>68</v>
       </c>
       <c r="F84" t="s">
         <v>961</v>
@@ -11325,7 +11319,7 @@
         <v>40</v>
       </c>
       <c r="H84" t="s">
-        <v>131</v>
+        <v>41</v>
       </c>
       <c r="I84" t="s">
         <v>962</v>
@@ -11343,7 +11337,7 @@
         <v>966</v>
       </c>
       <c r="N84" t="s">
-        <v>245</v>
+        <v>276</v>
       </c>
       <c r="O84" t="s">
         <v>967</v>
@@ -11391,7 +11385,7 @@
         <v>40</v>
       </c>
       <c r="H85" t="s">
-        <v>91</v>
+        <v>130</v>
       </c>
       <c r="I85" t="s">
         <v>973</v>
@@ -11409,7 +11403,7 @@
         <v>977</v>
       </c>
       <c r="N85" t="s">
-        <v>245</v>
+        <v>276</v>
       </c>
       <c r="O85" t="s">
         <v>978</v>
@@ -11418,7 +11412,7 @@
         <v>979</v>
       </c>
       <c r="Q85" t="s">
-        <v>114</v>
+        <v>153</v>
       </c>
       <c r="R85" t="s">
         <v>980</v>
@@ -11448,7 +11442,7 @@
         <v>744</v>
       </c>
       <c r="E86" t="s">
-        <v>180</v>
+        <v>68</v>
       </c>
       <c r="F86" t="s">
         <v>972</v>
@@ -11457,7 +11451,7 @@
         <v>40</v>
       </c>
       <c r="H86" t="s">
-        <v>91</v>
+        <v>130</v>
       </c>
       <c r="I86" t="s">
         <v>984</v>
@@ -11475,7 +11469,7 @@
         <v>988</v>
       </c>
       <c r="N86" t="s">
-        <v>245</v>
+        <v>276</v>
       </c>
       <c r="O86" t="s">
         <v>989</v>
@@ -11484,7 +11478,7 @@
         <v>990</v>
       </c>
       <c r="Q86" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="R86" t="s">
         <v>991</v>
@@ -11521,7 +11515,7 @@
         <v>40</v>
       </c>
       <c r="H87" t="s">
-        <v>91</v>
+        <v>130</v>
       </c>
       <c r="I87" t="s">
         <v>997</v>
@@ -11548,7 +11542,7 @@
         <v>1003</v>
       </c>
       <c r="Q87" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="R87" t="s">
         <v>991</v>
@@ -11572,13 +11566,13 @@
         <v>1004</v>
       </c>
       <c r="C88" t="s">
-        <v>271</v>
+        <v>293</v>
       </c>
       <c r="D88" t="s">
         <v>1005</v>
       </c>
       <c r="E88" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="F88" t="s">
         <v>1006</v>
@@ -11644,7 +11638,7 @@
         <v>1019</v>
       </c>
       <c r="E89" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="F89" t="s">
         <v>1006</v>
@@ -11653,7 +11647,7 @@
         <v>40</v>
       </c>
       <c r="H89" t="s">
-        <v>251</v>
+        <v>55</v>
       </c>
       <c r="I89" t="s">
         <v>1020</v>
@@ -11671,7 +11665,7 @@
         <v>1024</v>
       </c>
       <c r="N89" t="s">
-        <v>245</v>
+        <v>276</v>
       </c>
       <c r="O89" t="s">
         <v>1025</v>
@@ -11710,7 +11704,7 @@
         <v>1031</v>
       </c>
       <c r="E90" t="s">
-        <v>239</v>
+        <v>270</v>
       </c>
       <c r="F90" t="s">
         <v>1006</v>
@@ -11719,7 +11713,7 @@
         <v>40</v>
       </c>
       <c r="H90" t="s">
-        <v>131</v>
+        <v>41</v>
       </c>
       <c r="I90" t="s">
         <v>1032</v>
@@ -11737,7 +11731,7 @@
         <v>1036</v>
       </c>
       <c r="N90" t="s">
-        <v>245</v>
+        <v>276</v>
       </c>
       <c r="O90" t="s">
         <v>1037</v>
@@ -11746,16 +11740,16 @@
         <v>1038</v>
       </c>
       <c r="Q90" t="s">
-        <v>114</v>
+        <v>153</v>
       </c>
       <c r="R90" t="s">
-        <v>186</v>
+        <v>217</v>
       </c>
       <c r="S90" t="s">
-        <v>187</v>
+        <v>218</v>
       </c>
       <c r="T90" t="s">
-        <v>188</v>
+        <v>219</v>
       </c>
       <c r="U90" t="s">
         <v>537</v>
@@ -11776,7 +11770,7 @@
         <v>1040</v>
       </c>
       <c r="E91" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="F91" t="s">
         <v>1041</v>
@@ -11785,7 +11779,7 @@
         <v>27</v>
       </c>
       <c r="H91" t="s">
-        <v>251</v>
+        <v>55</v>
       </c>
       <c r="I91" t="s">
         <v>1042</v>
@@ -11803,7 +11797,7 @@
         <v>1046</v>
       </c>
       <c r="N91" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="O91" t="s">
         <v>1047</v>
@@ -11812,7 +11806,7 @@
         <v>1048</v>
       </c>
       <c r="Q91" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="R91" t="s">
         <v>1049</v>
@@ -11839,10 +11833,10 @@
         <v>23</v>
       </c>
       <c r="D92" t="s">
-        <v>79</v>
+        <v>118</v>
       </c>
       <c r="E92" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="F92" t="s">
         <v>1041</v>
@@ -11851,7 +11845,7 @@
         <v>27</v>
       </c>
       <c r="H92" t="s">
-        <v>91</v>
+        <v>130</v>
       </c>
       <c r="I92" t="s">
         <v>1053</v>
@@ -11869,7 +11863,7 @@
         <v>1057</v>
       </c>
       <c r="N92" t="s">
-        <v>220</v>
+        <v>251</v>
       </c>
       <c r="O92" t="s">
         <v>1058</v>
@@ -11878,7 +11872,7 @@
         <v>1059</v>
       </c>
       <c r="Q92" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="R92" t="s">
         <v>991</v>
@@ -11908,7 +11902,7 @@
         <v>628</v>
       </c>
       <c r="E93" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="F93" t="s">
         <v>1061</v>
@@ -11917,7 +11911,7 @@
         <v>27</v>
       </c>
       <c r="H93" t="s">
-        <v>131</v>
+        <v>41</v>
       </c>
       <c r="I93" t="s">
         <v>1062</v>
@@ -11935,7 +11929,7 @@
         <v>1066</v>
       </c>
       <c r="N93" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="O93" t="s">
         <v>1067</v>
@@ -11944,7 +11938,7 @@
         <v>1068</v>
       </c>
       <c r="Q93" t="s">
-        <v>114</v>
+        <v>153</v>
       </c>
       <c r="R93" t="s">
         <v>1069</v>
@@ -11983,7 +11977,7 @@
         <v>40</v>
       </c>
       <c r="H94" t="s">
-        <v>251</v>
+        <v>55</v>
       </c>
       <c r="I94" t="s">
         <v>1074</v>
@@ -12001,7 +11995,7 @@
         <v>1078</v>
       </c>
       <c r="N94" t="s">
-        <v>245</v>
+        <v>276</v>
       </c>
       <c r="O94" t="s">
         <v>1079</v>
@@ -12034,7 +12028,7 @@
         <v>1084</v>
       </c>
       <c r="C95" t="s">
-        <v>211</v>
+        <v>242</v>
       </c>
       <c r="D95" t="s">
         <v>1085</v>
@@ -12045,7 +12039,7 @@
       </c>
       <c r="G95"/>
       <c r="H95" t="s">
-        <v>131</v>
+        <v>41</v>
       </c>
       <c r="I95" t="s">
         <v>1087</v>
@@ -12063,7 +12057,7 @@
         <v>1091</v>
       </c>
       <c r="N95" t="s">
-        <v>158</v>
+        <v>196</v>
       </c>
       <c r="O95" t="s">
         <v>1092</v>
@@ -12090,7 +12084,7 @@
         <v>1094</v>
       </c>
       <c r="C96" t="s">
-        <v>211</v>
+        <v>242</v>
       </c>
       <c r="D96" t="s">
         <v>1095</v>
@@ -12101,7 +12095,7 @@
       </c>
       <c r="G96"/>
       <c r="H96" t="s">
-        <v>167</v>
+        <v>69</v>
       </c>
       <c r="I96" t="s">
         <v>847</v>
@@ -12119,7 +12113,7 @@
         <v>1098</v>
       </c>
       <c r="N96" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="O96" t="s">
         <v>1099</v>
@@ -12159,7 +12153,7 @@
         <v>27</v>
       </c>
       <c r="H97" t="s">
-        <v>167</v>
+        <v>69</v>
       </c>
       <c r="I97" t="s">
         <v>1104</v>
@@ -12177,7 +12171,7 @@
         <v>1108</v>
       </c>
       <c r="N97" t="s">
-        <v>158</v>
+        <v>196</v>
       </c>
       <c r="O97" t="s">
         <v>1109</v>
@@ -12225,7 +12219,7 @@
         <v>40</v>
       </c>
       <c r="H98" t="s">
-        <v>131</v>
+        <v>41</v>
       </c>
       <c r="I98" t="s">
         <v>1116</v>
@@ -12243,7 +12237,7 @@
         <v>1120</v>
       </c>
       <c r="N98" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="O98" t="s">
         <v>1121</v>
@@ -12291,7 +12285,7 @@
         <v>40</v>
       </c>
       <c r="H99" t="s">
-        <v>91</v>
+        <v>130</v>
       </c>
       <c r="I99" t="s">
         <v>1127</v>
@@ -12309,7 +12303,7 @@
         <v>1131</v>
       </c>
       <c r="N99" t="s">
-        <v>245</v>
+        <v>276</v>
       </c>
       <c r="O99" t="s">
         <v>1132</v>
@@ -12318,7 +12312,7 @@
         <v>1133</v>
       </c>
       <c r="Q99" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="R99" t="s">
         <v>1134</v>
@@ -12348,7 +12342,7 @@
         <v>1138</v>
       </c>
       <c r="E100" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="F100" t="s">
         <v>1115</v>
@@ -12375,7 +12369,7 @@
         <v>1143</v>
       </c>
       <c r="N100" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="O100" t="s">
         <v>1144</v>
@@ -12384,7 +12378,7 @@
         <v>1145</v>
       </c>
       <c r="Q100" t="s">
-        <v>114</v>
+        <v>153</v>
       </c>
       <c r="R100" t="s">
         <v>1146</v>
@@ -12414,7 +12408,7 @@
         <v>694</v>
       </c>
       <c r="E101" t="s">
-        <v>239</v>
+        <v>270</v>
       </c>
       <c r="F101" t="s">
         <v>1115</v>
@@ -12423,7 +12417,7 @@
         <v>40</v>
       </c>
       <c r="H101" t="s">
-        <v>91</v>
+        <v>130</v>
       </c>
       <c r="I101" t="s">
         <v>1150</v>
@@ -12450,7 +12444,7 @@
         <v>1156</v>
       </c>
       <c r="Q101" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="R101" t="s">
         <v>1157</v>
@@ -12489,7 +12483,7 @@
         <v>40</v>
       </c>
       <c r="H102" t="s">
-        <v>167</v>
+        <v>69</v>
       </c>
       <c r="I102" t="s">
         <v>1162</v>
@@ -12507,7 +12501,7 @@
         <v>1166</v>
       </c>
       <c r="N102" t="s">
-        <v>245</v>
+        <v>276</v>
       </c>
       <c r="O102" t="s">
         <v>1167</v>
@@ -12516,7 +12510,7 @@
         <v>1168</v>
       </c>
       <c r="Q102" t="s">
-        <v>114</v>
+        <v>153</v>
       </c>
       <c r="R102" t="s">
         <v>1169</v>
@@ -12555,7 +12549,7 @@
         <v>40</v>
       </c>
       <c r="H103" t="s">
-        <v>91</v>
+        <v>130</v>
       </c>
       <c r="I103" t="s">
         <v>1174</v>
@@ -12573,7 +12567,7 @@
         <v>1178</v>
       </c>
       <c r="N103" t="s">
-        <v>245</v>
+        <v>276</v>
       </c>
       <c r="O103" t="s">
         <v>1179</v>
@@ -12582,7 +12576,7 @@
         <v>1180</v>
       </c>
       <c r="Q103" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="R103" t="s">
         <v>1181</v>
@@ -12606,13 +12600,13 @@
         <v>1184</v>
       </c>
       <c r="C104" t="s">
-        <v>64</v>
+        <v>104</v>
       </c>
       <c r="D104" t="s">
         <v>800</v>
       </c>
       <c r="E104" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="F104" t="s">
         <v>1185</v>
@@ -12621,7 +12615,7 @@
         <v>40</v>
       </c>
       <c r="H104" t="s">
-        <v>131</v>
+        <v>41</v>
       </c>
       <c r="I104" t="s">
         <v>1186</v>
@@ -12639,7 +12633,7 @@
         <v>1190</v>
       </c>
       <c r="N104" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="O104" t="s">
         <v>1191</v>
@@ -12687,7 +12681,7 @@
         <v>40</v>
       </c>
       <c r="H105" t="s">
-        <v>131</v>
+        <v>41</v>
       </c>
       <c r="I105" t="s">
         <v>1198</v>
@@ -12705,7 +12699,7 @@
         <v>1202</v>
       </c>
       <c r="N105" t="s">
-        <v>245</v>
+        <v>276</v>
       </c>
       <c r="O105" t="s">
         <v>1203</v>
@@ -12714,7 +12708,7 @@
         <v>1204</v>
       </c>
       <c r="Q105" t="s">
-        <v>114</v>
+        <v>153</v>
       </c>
       <c r="R105" t="s">
         <v>1205</v>
@@ -12738,7 +12732,7 @@
         <v>1208</v>
       </c>
       <c r="C106" t="s">
-        <v>211</v>
+        <v>242</v>
       </c>
       <c r="D106" t="s">
         <v>1209</v>
@@ -12749,7 +12743,7 @@
       </c>
       <c r="G106"/>
       <c r="H106" t="s">
-        <v>131</v>
+        <v>41</v>
       </c>
       <c r="I106" t="s">
         <v>1210</v>
@@ -12767,7 +12761,7 @@
         <v>1214</v>
       </c>
       <c r="N106" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="O106" t="s">
         <v>1215</v>
@@ -12797,10 +12791,10 @@
         <v>23</v>
       </c>
       <c r="D107" t="s">
-        <v>179</v>
+        <v>211</v>
       </c>
       <c r="E107" t="s">
-        <v>180</v>
+        <v>68</v>
       </c>
       <c r="F107" t="s">
         <v>1218</v>
@@ -12809,7 +12803,7 @@
         <v>40</v>
       </c>
       <c r="H107" t="s">
-        <v>91</v>
+        <v>130</v>
       </c>
       <c r="I107" t="s">
         <v>683</v>
@@ -12827,7 +12821,7 @@
         <v>1222</v>
       </c>
       <c r="N107" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="O107" t="s">
         <v>1223</v>
@@ -12860,13 +12854,13 @@
         <v>1225</v>
       </c>
       <c r="C108" t="s">
-        <v>64</v>
+        <v>104</v>
       </c>
       <c r="D108" t="s">
         <v>1226</v>
       </c>
       <c r="E108" t="s">
-        <v>180</v>
+        <v>68</v>
       </c>
       <c r="F108" t="s">
         <v>1227</v>
@@ -12875,7 +12869,7 @@
         <v>40</v>
       </c>
       <c r="H108" t="s">
-        <v>167</v>
+        <v>69</v>
       </c>
       <c r="I108" t="s">
         <v>1228</v>
@@ -12891,7 +12885,7 @@
         <v>1231</v>
       </c>
       <c r="N108" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="O108" t="s">
         <v>1232</v>
@@ -12924,7 +12918,7 @@
         <v>1237</v>
       </c>
       <c r="C109" t="s">
-        <v>64</v>
+        <v>104</v>
       </c>
       <c r="D109" t="s">
         <v>1238</v>
@@ -12939,7 +12933,7 @@
         <v>40</v>
       </c>
       <c r="H109" t="s">
-        <v>131</v>
+        <v>41</v>
       </c>
       <c r="I109" t="s">
         <v>1240</v>
@@ -12955,7 +12949,7 @@
         <v>1243</v>
       </c>
       <c r="N109" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="O109" t="s">
         <v>1244</v>
@@ -12992,14 +12986,14 @@
       </c>
       <c r="D110"/>
       <c r="E110" t="s">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="F110" t="s">
         <v>1247</v>
       </c>
       <c r="G110"/>
       <c r="H110" t="s">
-        <v>167</v>
+        <v>69</v>
       </c>
       <c r="I110" t="s">
         <v>1248</v>
@@ -13013,7 +13007,7 @@
       <c r="L110"/>
       <c r="M110"/>
       <c r="N110" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="O110" t="s">
         <v>1251</v>
@@ -13022,7 +13016,7 @@
         <v>1252</v>
       </c>
       <c r="Q110" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="R110" t="s">
         <v>1253</v>
@@ -13046,7 +13040,7 @@
         <v>1256</v>
       </c>
       <c r="C111" t="s">
-        <v>211</v>
+        <v>242</v>
       </c>
       <c r="D111" t="s">
         <v>1209</v>
@@ -13057,7 +13051,7 @@
       </c>
       <c r="G111"/>
       <c r="H111" t="s">
-        <v>251</v>
+        <v>55</v>
       </c>
       <c r="I111" t="s">
         <v>1258</v>
@@ -13075,7 +13069,7 @@
         <v>1262</v>
       </c>
       <c r="N111" t="s">
-        <v>158</v>
+        <v>196</v>
       </c>
       <c r="O111" t="s">
         <v>1263</v>
@@ -13108,7 +13102,7 @@
         <v>1268</v>
       </c>
       <c r="C112" t="s">
-        <v>211</v>
+        <v>242</v>
       </c>
       <c r="D112" t="s">
         <v>1209</v>
@@ -13119,7 +13113,7 @@
       </c>
       <c r="G112"/>
       <c r="H112" t="s">
-        <v>131</v>
+        <v>41</v>
       </c>
       <c r="I112" t="s">
         <v>1269</v>
@@ -13185,7 +13179,7 @@
         <v>40</v>
       </c>
       <c r="H113" t="s">
-        <v>251</v>
+        <v>55</v>
       </c>
       <c r="I113" t="s">
         <v>1282</v>
@@ -13203,7 +13197,7 @@
         <v>1286</v>
       </c>
       <c r="N113" t="s">
-        <v>245</v>
+        <v>276</v>
       </c>
       <c r="O113" t="s">
         <v>1287</v>
@@ -13212,7 +13206,7 @@
         <v>1288</v>
       </c>
       <c r="Q113" t="s">
-        <v>114</v>
+        <v>153</v>
       </c>
       <c r="R113" t="s">
         <v>1289</v>
@@ -13242,7 +13236,7 @@
         <v>1293</v>
       </c>
       <c r="E114" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="F114" t="s">
         <v>1294</v>
@@ -13251,7 +13245,7 @@
         <v>40</v>
       </c>
       <c r="H114" t="s">
-        <v>66</v>
+        <v>106</v>
       </c>
       <c r="I114" t="s">
         <v>1295</v>
@@ -13269,7 +13263,7 @@
         <v>1299</v>
       </c>
       <c r="N114" t="s">
-        <v>245</v>
+        <v>276</v>
       </c>
       <c r="O114" t="s">
         <v>1300</v>
@@ -13278,7 +13272,7 @@
         <v>1301</v>
       </c>
       <c r="Q114" t="s">
-        <v>114</v>
+        <v>153</v>
       </c>
       <c r="R114" t="s">
         <v>1302</v>
@@ -13308,7 +13302,7 @@
         <v>1306</v>
       </c>
       <c r="E115" t="s">
-        <v>180</v>
+        <v>68</v>
       </c>
       <c r="F115" t="s">
         <v>1294</v>
@@ -13317,7 +13311,7 @@
         <v>40</v>
       </c>
       <c r="H115" t="s">
-        <v>131</v>
+        <v>41</v>
       </c>
       <c r="I115" t="s">
         <v>1307</v>
@@ -13335,7 +13329,7 @@
         <v>1311</v>
       </c>
       <c r="N115" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="O115" t="s">
         <v>1312</v>
@@ -13383,7 +13377,7 @@
         <v>40</v>
       </c>
       <c r="H116" t="s">
-        <v>91</v>
+        <v>130</v>
       </c>
       <c r="I116" t="s">
         <v>1316</v>
@@ -13401,7 +13395,7 @@
         <v>1320</v>
       </c>
       <c r="N116" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="O116" t="s">
         <v>1321</v>
@@ -13410,7 +13404,7 @@
         <v>1322</v>
       </c>
       <c r="Q116" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="R116" t="s">
         <v>1323</v>
@@ -13440,7 +13434,7 @@
         <v>1327</v>
       </c>
       <c r="E117" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="F117" t="s">
         <v>1294</v>
@@ -13449,7 +13443,7 @@
         <v>40</v>
       </c>
       <c r="H117" t="s">
-        <v>66</v>
+        <v>106</v>
       </c>
       <c r="I117" t="s">
         <v>1328</v>
@@ -13467,7 +13461,7 @@
         <v>1332</v>
       </c>
       <c r="N117" t="s">
-        <v>245</v>
+        <v>276</v>
       </c>
       <c r="O117" t="s">
         <v>1333</v>
@@ -13476,7 +13470,7 @@
         <v>1334</v>
       </c>
       <c r="Q117" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="R117" t="s">
         <v>864</v>
@@ -13506,7 +13500,7 @@
         <v>1336</v>
       </c>
       <c r="E118" t="s">
-        <v>239</v>
+        <v>270</v>
       </c>
       <c r="F118" t="s">
         <v>1337</v>
@@ -13515,7 +13509,7 @@
         <v>40</v>
       </c>
       <c r="H118" t="s">
-        <v>66</v>
+        <v>106</v>
       </c>
       <c r="I118" t="s">
         <v>1338</v>
@@ -13533,7 +13527,7 @@
         <v>1342</v>
       </c>
       <c r="N118" t="s">
-        <v>245</v>
+        <v>276</v>
       </c>
       <c r="O118" t="s">
         <v>1343</v>
@@ -13542,7 +13536,7 @@
         <v>1344</v>
       </c>
       <c r="Q118" t="s">
-        <v>114</v>
+        <v>153</v>
       </c>
       <c r="R118" t="s">
         <v>657</v>
@@ -13566,13 +13560,13 @@
         <v>1345</v>
       </c>
       <c r="C119" t="s">
-        <v>64</v>
+        <v>104</v>
       </c>
       <c r="D119" t="s">
         <v>744</v>
       </c>
       <c r="E119" t="s">
-        <v>180</v>
+        <v>68</v>
       </c>
       <c r="F119" t="s">
         <v>1346</v>
@@ -13581,7 +13575,7 @@
         <v>40</v>
       </c>
       <c r="H119" t="s">
-        <v>167</v>
+        <v>69</v>
       </c>
       <c r="I119" t="s">
         <v>1347</v>
@@ -13597,7 +13591,7 @@
         <v>1350</v>
       </c>
       <c r="N119" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="O119" t="s">
         <v>1351</v>
@@ -13606,7 +13600,7 @@
         <v>1352</v>
       </c>
       <c r="Q119" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="R119" t="s">
         <v>490</v>
@@ -13633,10 +13627,10 @@
         <v>37</v>
       </c>
       <c r="D120" t="s">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="E120" t="s">
-        <v>239</v>
+        <v>270</v>
       </c>
       <c r="F120" t="s">
         <v>1354</v>
@@ -13645,7 +13639,7 @@
         <v>40</v>
       </c>
       <c r="H120" t="s">
-        <v>131</v>
+        <v>41</v>
       </c>
       <c r="I120" t="s">
         <v>1355</v>
@@ -13663,7 +13657,7 @@
         <v>1359</v>
       </c>
       <c r="N120" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="O120" t="s">
         <v>1360</v>
@@ -13672,16 +13666,16 @@
         <v>1361</v>
       </c>
       <c r="Q120" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="R120" t="s">
-        <v>138</v>
+        <v>176</v>
       </c>
       <c r="S120" t="s">
-        <v>139</v>
+        <v>177</v>
       </c>
       <c r="T120" t="s">
-        <v>140</v>
+        <v>178</v>
       </c>
       <c r="U120" t="s">
         <v>537</v>
@@ -13696,13 +13690,13 @@
         <v>1362</v>
       </c>
       <c r="C121" t="s">
-        <v>64</v>
+        <v>104</v>
       </c>
       <c r="D121" t="s">
         <v>1327</v>
       </c>
       <c r="E121" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="F121" t="s">
         <v>1363</v>
@@ -13711,7 +13705,7 @@
         <v>40</v>
       </c>
       <c r="H121" t="s">
-        <v>131</v>
+        <v>41</v>
       </c>
       <c r="I121" t="s">
         <v>1364</v>
@@ -13727,7 +13721,7 @@
         <v>1367</v>
       </c>
       <c r="N121" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="O121" t="s">
         <v>1368</v>
@@ -13739,13 +13733,13 @@
         <v>35</v>
       </c>
       <c r="R121" t="s">
-        <v>186</v>
+        <v>217</v>
       </c>
       <c r="S121" t="s">
-        <v>187</v>
+        <v>218</v>
       </c>
       <c r="T121" t="s">
-        <v>188</v>
+        <v>219</v>
       </c>
       <c r="U121" t="s">
         <v>537</v>
@@ -13760,13 +13754,13 @@
         <v>1370</v>
       </c>
       <c r="C122" t="s">
-        <v>64</v>
+        <v>104</v>
       </c>
       <c r="D122" t="s">
         <v>744</v>
       </c>
       <c r="E122" t="s">
-        <v>180</v>
+        <v>68</v>
       </c>
       <c r="F122" t="s">
         <v>1363</v>
@@ -13775,7 +13769,7 @@
         <v>40</v>
       </c>
       <c r="H122" t="s">
-        <v>167</v>
+        <v>69</v>
       </c>
       <c r="I122" t="s">
         <v>1371</v>
@@ -13791,7 +13785,7 @@
         <v>1374</v>
       </c>
       <c r="N122" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="O122" t="s">
         <v>1375</v>
@@ -13800,7 +13794,7 @@
         <v>1376</v>
       </c>
       <c r="Q122" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="R122" t="s">
         <v>490</v>
@@ -13824,13 +13818,13 @@
         <v>1377</v>
       </c>
       <c r="C123" t="s">
-        <v>64</v>
+        <v>104</v>
       </c>
       <c r="D123" t="s">
         <v>744</v>
       </c>
       <c r="E123" t="s">
-        <v>180</v>
+        <v>68</v>
       </c>
       <c r="F123" t="s">
         <v>1363</v>
@@ -13839,7 +13833,7 @@
         <v>40</v>
       </c>
       <c r="H123" t="s">
-        <v>167</v>
+        <v>69</v>
       </c>
       <c r="I123" t="s">
         <v>1371</v>
@@ -13855,7 +13849,7 @@
         <v>1379</v>
       </c>
       <c r="N123" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="O123" t="s">
         <v>1380</v>
@@ -13864,7 +13858,7 @@
         <v>1381</v>
       </c>
       <c r="Q123" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="R123" t="s">
         <v>490</v>
@@ -13888,13 +13882,13 @@
         <v>1382</v>
       </c>
       <c r="C124" t="s">
-        <v>64</v>
+        <v>104</v>
       </c>
       <c r="D124" t="s">
         <v>744</v>
       </c>
       <c r="E124" t="s">
-        <v>180</v>
+        <v>68</v>
       </c>
       <c r="F124" t="s">
         <v>1363</v>
@@ -13903,7 +13897,7 @@
         <v>40</v>
       </c>
       <c r="H124" t="s">
-        <v>167</v>
+        <v>69</v>
       </c>
       <c r="I124" t="s">
         <v>1371</v>
@@ -13919,7 +13913,7 @@
         <v>1384</v>
       </c>
       <c r="N124" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="O124" t="s">
         <v>1385</v>
@@ -13928,7 +13922,7 @@
         <v>1386</v>
       </c>
       <c r="Q124" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="R124" t="s">
         <v>490</v>
@@ -13958,7 +13952,7 @@
         <v>822</v>
       </c>
       <c r="E125" t="s">
-        <v>180</v>
+        <v>68</v>
       </c>
       <c r="F125" t="s">
         <v>1388</v>
@@ -13967,7 +13961,7 @@
         <v>40</v>
       </c>
       <c r="H125" t="s">
-        <v>251</v>
+        <v>55</v>
       </c>
       <c r="I125" t="s">
         <v>1389</v>
@@ -13985,7 +13979,7 @@
         <v>1393</v>
       </c>
       <c r="N125" t="s">
-        <v>245</v>
+        <v>276</v>
       </c>
       <c r="O125" t="s">
         <v>1394</v>
@@ -14024,7 +14018,7 @@
         <v>880</v>
       </c>
       <c r="E126" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="F126" t="s">
         <v>1400</v>
@@ -14033,7 +14027,7 @@
         <v>40</v>
       </c>
       <c r="H126" t="s">
-        <v>91</v>
+        <v>130</v>
       </c>
       <c r="I126" t="s">
         <v>1401</v>
@@ -14051,7 +14045,7 @@
         <v>1405</v>
       </c>
       <c r="N126" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="O126" t="s">
         <v>1406</v>
@@ -14090,7 +14084,7 @@
         <v>1409</v>
       </c>
       <c r="E127" t="s">
-        <v>180</v>
+        <v>68</v>
       </c>
       <c r="F127" t="s">
         <v>1400</v>
@@ -14099,7 +14093,7 @@
         <v>40</v>
       </c>
       <c r="H127" t="s">
-        <v>131</v>
+        <v>41</v>
       </c>
       <c r="I127" t="s">
         <v>1410</v>
@@ -14117,7 +14111,7 @@
         <v>1414</v>
       </c>
       <c r="N127" t="s">
-        <v>245</v>
+        <v>276</v>
       </c>
       <c r="O127" t="s">
         <v>1415</v>
@@ -14156,7 +14150,7 @@
         <v>1421</v>
       </c>
       <c r="E128" t="s">
-        <v>239</v>
+        <v>270</v>
       </c>
       <c r="F128" t="s">
         <v>1400</v>
@@ -14165,7 +14159,7 @@
         <v>40</v>
       </c>
       <c r="H128" t="s">
-        <v>91</v>
+        <v>130</v>
       </c>
       <c r="I128" t="s">
         <v>1422</v>
@@ -14183,7 +14177,7 @@
         <v>1426</v>
       </c>
       <c r="N128" t="s">
-        <v>245</v>
+        <v>276</v>
       </c>
       <c r="O128" t="s">
         <v>1427</v>
@@ -14192,7 +14186,7 @@
         <v>1428</v>
       </c>
       <c r="Q128" t="s">
-        <v>114</v>
+        <v>153</v>
       </c>
       <c r="R128" t="s">
         <v>1429</v>
@@ -14216,7 +14210,7 @@
         <v>1432</v>
       </c>
       <c r="C129" t="s">
-        <v>211</v>
+        <v>242</v>
       </c>
       <c r="D129" t="s">
         <v>1209</v>
@@ -14227,7 +14221,7 @@
       </c>
       <c r="G129"/>
       <c r="H129" t="s">
-        <v>214</v>
+        <v>245</v>
       </c>
       <c r="I129" t="s">
         <v>1434</v>
@@ -14245,7 +14239,7 @@
         <v>1438</v>
       </c>
       <c r="N129" t="s">
-        <v>158</v>
+        <v>196</v>
       </c>
       <c r="O129" t="s">
         <v>1439</v>
@@ -14257,13 +14251,13 @@
         <v>35</v>
       </c>
       <c r="R129" t="s">
-        <v>147</v>
+        <v>185</v>
       </c>
       <c r="S129" t="s">
-        <v>148</v>
+        <v>186</v>
       </c>
       <c r="T129" t="s">
-        <v>149</v>
+        <v>187</v>
       </c>
       <c r="U129" t="s">
         <v>537</v>
@@ -14284,7 +14278,7 @@
         <v>722</v>
       </c>
       <c r="E130" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="F130" t="s">
         <v>1433</v>
@@ -14293,7 +14287,7 @@
         <v>40</v>
       </c>
       <c r="H130" t="s">
-        <v>66</v>
+        <v>106</v>
       </c>
       <c r="I130" t="s">
         <v>1442</v>
@@ -14311,7 +14305,7 @@
         <v>1446</v>
       </c>
       <c r="N130" t="s">
-        <v>245</v>
+        <v>276</v>
       </c>
       <c r="O130" t="s">
         <v>1447</v>
@@ -14320,7 +14314,7 @@
         <v>1448</v>
       </c>
       <c r="Q130" t="s">
-        <v>114</v>
+        <v>153</v>
       </c>
       <c r="R130" t="s">
         <v>1449</v>
@@ -14350,7 +14344,7 @@
         <v>1453</v>
       </c>
       <c r="E131" t="s">
-        <v>239</v>
+        <v>270</v>
       </c>
       <c r="F131" t="s">
         <v>1433</v>
@@ -14359,7 +14353,7 @@
         <v>40</v>
       </c>
       <c r="H131" t="s">
-        <v>251</v>
+        <v>55</v>
       </c>
       <c r="I131" t="s">
         <v>1454</v>
@@ -14377,7 +14371,7 @@
         <v>1458</v>
       </c>
       <c r="N131" t="s">
-        <v>245</v>
+        <v>276</v>
       </c>
       <c r="O131" t="s">
         <v>1459</v>
@@ -14386,7 +14380,7 @@
         <v>1460</v>
       </c>
       <c r="Q131" t="s">
-        <v>114</v>
+        <v>153</v>
       </c>
       <c r="R131" t="s">
         <v>1461</v>
@@ -14425,7 +14419,7 @@
         <v>40</v>
       </c>
       <c r="H132" t="s">
-        <v>251</v>
+        <v>55</v>
       </c>
       <c r="I132" t="s">
         <v>1466</v>
@@ -14443,7 +14437,7 @@
         <v>1470</v>
       </c>
       <c r="N132" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="O132" t="s">
         <v>1471</v>
@@ -14452,7 +14446,7 @@
         <v>1472</v>
       </c>
       <c r="Q132" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="R132" t="s">
         <v>1134</v>
@@ -14491,7 +14485,7 @@
         <v>40</v>
       </c>
       <c r="H133" t="s">
-        <v>131</v>
+        <v>41</v>
       </c>
       <c r="I133" t="s">
         <v>1474</v>
@@ -14509,7 +14503,7 @@
         <v>1478</v>
       </c>
       <c r="N133" t="s">
-        <v>245</v>
+        <v>276</v>
       </c>
       <c r="O133" t="s">
         <v>1479</v>
@@ -14518,7 +14512,7 @@
         <v>1480</v>
       </c>
       <c r="Q133" t="s">
-        <v>114</v>
+        <v>153</v>
       </c>
       <c r="R133" t="s">
         <v>1481</v>
@@ -14548,7 +14542,7 @@
         <v>822</v>
       </c>
       <c r="E134" t="s">
-        <v>180</v>
+        <v>68</v>
       </c>
       <c r="F134" t="s">
         <v>1433</v>
@@ -14557,7 +14551,7 @@
         <v>40</v>
       </c>
       <c r="H134" t="s">
-        <v>91</v>
+        <v>130</v>
       </c>
       <c r="I134" t="s">
         <v>1485</v>
@@ -14611,10 +14605,10 @@
         <v>37</v>
       </c>
       <c r="D135" t="s">
-        <v>179</v>
+        <v>211</v>
       </c>
       <c r="E135" t="s">
-        <v>180</v>
+        <v>68</v>
       </c>
       <c r="F135" t="s">
         <v>1497</v>
@@ -14623,7 +14617,7 @@
         <v>40</v>
       </c>
       <c r="H135" t="s">
-        <v>131</v>
+        <v>41</v>
       </c>
       <c r="I135" t="s">
         <v>1498</v>
@@ -14641,7 +14635,7 @@
         <v>1502</v>
       </c>
       <c r="N135" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="O135" t="s">
         <v>1503</v>
@@ -14653,13 +14647,13 @@
         <v>35</v>
       </c>
       <c r="R135" t="s">
-        <v>138</v>
+        <v>176</v>
       </c>
       <c r="S135" t="s">
-        <v>139</v>
+        <v>177</v>
       </c>
       <c r="T135" t="s">
-        <v>140</v>
+        <v>178</v>
       </c>
       <c r="U135" t="s">
         <v>537</v>
@@ -14680,7 +14674,7 @@
         <v>694</v>
       </c>
       <c r="E136" t="s">
-        <v>239</v>
+        <v>270</v>
       </c>
       <c r="F136" t="s">
         <v>1506</v>
@@ -14689,7 +14683,7 @@
         <v>40</v>
       </c>
       <c r="H136" t="s">
-        <v>91</v>
+        <v>130</v>
       </c>
       <c r="I136" t="s">
         <v>1507</v>
@@ -14707,7 +14701,7 @@
         <v>1511</v>
       </c>
       <c r="N136" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="O136" t="s">
         <v>1512</v>
@@ -14716,7 +14710,7 @@
         <v>1513</v>
       </c>
       <c r="Q136" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="R136" t="s">
         <v>991</v>
@@ -14740,13 +14734,13 @@
         <v>1514</v>
       </c>
       <c r="C137" t="s">
-        <v>64</v>
+        <v>104</v>
       </c>
       <c r="D137" t="s">
         <v>1515</v>
       </c>
       <c r="E137" t="s">
-        <v>180</v>
+        <v>68</v>
       </c>
       <c r="F137" t="s">
         <v>1516</v>
@@ -14755,7 +14749,7 @@
         <v>40</v>
       </c>
       <c r="H137" t="s">
-        <v>91</v>
+        <v>130</v>
       </c>
       <c r="I137" t="s">
         <v>1517</v>
@@ -14771,7 +14765,7 @@
         <v>1520</v>
       </c>
       <c r="N137" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="O137" t="s">
         <v>1521</v>
@@ -14804,7 +14798,7 @@
         <v>1523</v>
       </c>
       <c r="C138" t="s">
-        <v>64</v>
+        <v>104</v>
       </c>
       <c r="D138" t="s">
         <v>1524</v>
@@ -14819,7 +14813,7 @@
         <v>40</v>
       </c>
       <c r="H138" t="s">
-        <v>131</v>
+        <v>41</v>
       </c>
       <c r="I138" t="s">
         <v>1525</v>
@@ -14835,7 +14829,7 @@
         <v>1528</v>
       </c>
       <c r="N138" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="O138" t="s">
         <v>1529</v>
@@ -14847,13 +14841,13 @@
         <v>35</v>
       </c>
       <c r="R138" t="s">
-        <v>196</v>
+        <v>227</v>
       </c>
       <c r="S138" t="s">
-        <v>197</v>
+        <v>228</v>
       </c>
       <c r="T138" t="s">
-        <v>198</v>
+        <v>229</v>
       </c>
       <c r="U138" t="s">
         <v>537</v>
@@ -14868,7 +14862,7 @@
         <v>1531</v>
       </c>
       <c r="C139" t="s">
-        <v>271</v>
+        <v>293</v>
       </c>
       <c r="D139" t="s">
         <v>450</v>
@@ -14883,7 +14877,7 @@
         <v>40</v>
       </c>
       <c r="H139" t="s">
-        <v>131</v>
+        <v>41</v>
       </c>
       <c r="I139" t="s">
         <v>1533</v>
@@ -14901,7 +14895,7 @@
         <v>1537</v>
       </c>
       <c r="N139" t="s">
-        <v>245</v>
+        <v>276</v>
       </c>
       <c r="O139" t="s">
         <v>1538</v>
@@ -14910,7 +14904,7 @@
         <v>1539</v>
       </c>
       <c r="Q139" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="R139" t="s">
         <v>1069</v>
@@ -14938,14 +14932,14 @@
       </c>
       <c r="D140"/>
       <c r="E140" t="s">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="F140" t="s">
         <v>1541</v>
       </c>
       <c r="G140"/>
       <c r="H140" t="s">
-        <v>167</v>
+        <v>69</v>
       </c>
       <c r="I140" t="s">
         <v>1542</v>
@@ -14959,7 +14953,7 @@
       <c r="L140"/>
       <c r="M140"/>
       <c r="N140" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="O140" t="s">
         <v>1545</v>
@@ -14968,7 +14962,7 @@
         <v>1546</v>
       </c>
       <c r="Q140" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="R140" t="s">
         <v>1547</v>
@@ -14992,7 +14986,7 @@
         <v>1550</v>
       </c>
       <c r="C141" t="s">
-        <v>211</v>
+        <v>242</v>
       </c>
       <c r="D141" t="s">
         <v>1209</v>
@@ -15003,7 +14997,7 @@
       </c>
       <c r="G141"/>
       <c r="H141" t="s">
-        <v>167</v>
+        <v>69</v>
       </c>
       <c r="I141" t="s">
         <v>1552</v>
@@ -15069,7 +15063,7 @@
         <v>40</v>
       </c>
       <c r="H142" t="s">
-        <v>131</v>
+        <v>41</v>
       </c>
       <c r="I142" t="s">
         <v>1565</v>
@@ -15087,7 +15081,7 @@
         <v>1569</v>
       </c>
       <c r="N142" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="O142" t="s">
         <v>1570</v>
@@ -15096,7 +15090,7 @@
         <v>1571</v>
       </c>
       <c r="Q142" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="R142" t="s">
         <v>1572</v>
@@ -15135,7 +15129,7 @@
         <v>40</v>
       </c>
       <c r="H143" t="s">
-        <v>251</v>
+        <v>55</v>
       </c>
       <c r="I143" t="s">
         <v>1578</v>
@@ -15153,7 +15147,7 @@
         <v>1582</v>
       </c>
       <c r="N143" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="O143" t="s">
         <v>1583</v>
@@ -15162,7 +15156,7 @@
         <v>1584</v>
       </c>
       <c r="Q143" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="R143" t="s">
         <v>1585</v>
@@ -15201,7 +15195,7 @@
         <v>27</v>
       </c>
       <c r="H144" t="s">
-        <v>131</v>
+        <v>41</v>
       </c>
       <c r="I144" t="s">
         <v>1589</v>
@@ -15219,7 +15213,7 @@
         <v>1593</v>
       </c>
       <c r="N144" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="O144" t="s">
         <v>1594</v>
@@ -15252,13 +15246,13 @@
         <v>1596</v>
       </c>
       <c r="C145" t="s">
-        <v>271</v>
+        <v>293</v>
       </c>
       <c r="D145" t="s">
         <v>628</v>
       </c>
       <c r="E145" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="F145" t="s">
         <v>1597</v>
@@ -15267,7 +15261,7 @@
         <v>27</v>
       </c>
       <c r="H145" t="s">
-        <v>251</v>
+        <v>55</v>
       </c>
       <c r="I145" t="s">
         <v>1598</v>
@@ -15294,16 +15288,16 @@
         <v>1604</v>
       </c>
       <c r="Q145" t="s">
-        <v>114</v>
+        <v>153</v>
       </c>
       <c r="R145" t="s">
-        <v>147</v>
+        <v>185</v>
       </c>
       <c r="S145" t="s">
-        <v>148</v>
+        <v>186</v>
       </c>
       <c r="T145" t="s">
-        <v>149</v>
+        <v>187</v>
       </c>
       <c r="U145" t="s">
         <v>537</v>
@@ -15324,7 +15318,7 @@
         <v>1606</v>
       </c>
       <c r="E146" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="F146" t="s">
         <v>1597</v>
@@ -15333,7 +15327,7 @@
         <v>40</v>
       </c>
       <c r="H146" t="s">
-        <v>131</v>
+        <v>41</v>
       </c>
       <c r="I146" t="s">
         <v>1607</v>
@@ -15351,7 +15345,7 @@
         <v>1611</v>
       </c>
       <c r="N146" t="s">
-        <v>220</v>
+        <v>251</v>
       </c>
       <c r="O146" t="s">
         <v>1612</v>
@@ -15360,7 +15354,7 @@
         <v>1613</v>
       </c>
       <c r="Q146" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="R146" t="s">
         <v>1614</v>
@@ -15399,7 +15393,7 @@
         <v>40</v>
       </c>
       <c r="H147" t="s">
-        <v>66</v>
+        <v>106</v>
       </c>
       <c r="I147" t="s">
         <v>1620</v>
@@ -15417,7 +15411,7 @@
         <v>1624</v>
       </c>
       <c r="N147" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="O147" t="s">
         <v>1625</v>
@@ -15426,7 +15420,7 @@
         <v>1626</v>
       </c>
       <c r="Q147" t="s">
-        <v>114</v>
+        <v>153</v>
       </c>
       <c r="R147" t="s">
         <v>1627</v>
@@ -15456,7 +15450,7 @@
         <v>593</v>
       </c>
       <c r="E148" t="s">
-        <v>180</v>
+        <v>68</v>
       </c>
       <c r="F148" t="s">
         <v>1597</v>
@@ -15465,7 +15459,7 @@
         <v>40</v>
       </c>
       <c r="H148" t="s">
-        <v>131</v>
+        <v>41</v>
       </c>
       <c r="I148" t="s">
         <v>1631</v>
@@ -15483,7 +15477,7 @@
         <v>1635</v>
       </c>
       <c r="N148" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="O148" t="s">
         <v>1636</v>
@@ -15522,7 +15516,7 @@
         <v>1606</v>
       </c>
       <c r="E149" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="F149" t="s">
         <v>1597</v>
@@ -15531,7 +15525,7 @@
         <v>40</v>
       </c>
       <c r="H149" t="s">
-        <v>251</v>
+        <v>55</v>
       </c>
       <c r="I149" t="s">
         <v>1642</v>
@@ -15549,7 +15543,7 @@
         <v>1646</v>
       </c>
       <c r="N149" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="O149" t="s">
         <v>1647</v>
@@ -15597,7 +15591,7 @@
         <v>40</v>
       </c>
       <c r="H150" t="s">
-        <v>91</v>
+        <v>130</v>
       </c>
       <c r="I150" t="s">
         <v>1653</v>
@@ -15615,7 +15609,7 @@
         <v>1657</v>
       </c>
       <c r="N150" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="O150" t="s">
         <v>1658</v>
@@ -15624,7 +15618,7 @@
         <v>1659</v>
       </c>
       <c r="Q150" t="s">
-        <v>114</v>
+        <v>153</v>
       </c>
       <c r="R150" t="s">
         <v>1660</v>
@@ -15654,7 +15648,7 @@
         <v>1664</v>
       </c>
       <c r="E151" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="F151" t="s">
         <v>1665</v>
@@ -15663,7 +15657,7 @@
         <v>40</v>
       </c>
       <c r="H151" t="s">
-        <v>91</v>
+        <v>130</v>
       </c>
       <c r="I151" t="s">
         <v>1666</v>
@@ -15681,7 +15675,7 @@
         <v>1670</v>
       </c>
       <c r="N151" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="O151" t="s">
         <v>1671</v>
@@ -15690,7 +15684,7 @@
         <v>1672</v>
       </c>
       <c r="Q151" t="s">
-        <v>114</v>
+        <v>153</v>
       </c>
       <c r="R151" t="s">
         <v>991</v>
@@ -15720,7 +15714,7 @@
         <v>494</v>
       </c>
       <c r="E152" t="s">
-        <v>180</v>
+        <v>68</v>
       </c>
       <c r="F152" t="s">
         <v>1674</v>
@@ -15729,7 +15723,7 @@
         <v>40</v>
       </c>
       <c r="H152" t="s">
-        <v>91</v>
+        <v>130</v>
       </c>
       <c r="I152" t="s">
         <v>1675</v>
@@ -15747,7 +15741,7 @@
         <v>1679</v>
       </c>
       <c r="N152" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="O152" t="s">
         <v>1680</v>
@@ -15795,7 +15789,7 @@
         <v>27</v>
       </c>
       <c r="H153" t="s">
-        <v>251</v>
+        <v>55</v>
       </c>
       <c r="I153" t="s">
         <v>1685</v>
@@ -15813,7 +15807,7 @@
         <v>1689</v>
       </c>
       <c r="N153" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="O153" t="s">
         <v>1690</v>
@@ -15846,7 +15840,7 @@
         <v>1692</v>
       </c>
       <c r="C154" t="s">
-        <v>271</v>
+        <v>293</v>
       </c>
       <c r="D154" t="s">
         <v>1693</v>
@@ -15861,7 +15855,7 @@
         <v>27</v>
       </c>
       <c r="H154" t="s">
-        <v>251</v>
+        <v>55</v>
       </c>
       <c r="I154" t="s">
         <v>1695</v>
@@ -15912,13 +15906,13 @@
         <v>1702</v>
       </c>
       <c r="C155" t="s">
-        <v>64</v>
+        <v>104</v>
       </c>
       <c r="D155" t="s">
         <v>822</v>
       </c>
       <c r="E155" t="s">
-        <v>180</v>
+        <v>68</v>
       </c>
       <c r="F155" t="s">
         <v>1694</v>
@@ -15927,7 +15921,7 @@
         <v>40</v>
       </c>
       <c r="H155" t="s">
-        <v>131</v>
+        <v>41</v>
       </c>
       <c r="I155" t="s">
         <v>1703</v>
@@ -15943,7 +15937,7 @@
         <v>1706</v>
       </c>
       <c r="N155" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="O155" t="s">
         <v>1707</v>
@@ -15952,16 +15946,16 @@
         <v>1708</v>
       </c>
       <c r="Q155" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="R155" t="s">
-        <v>138</v>
+        <v>176</v>
       </c>
       <c r="S155" t="s">
-        <v>139</v>
+        <v>177</v>
       </c>
       <c r="T155" t="s">
-        <v>140</v>
+        <v>178</v>
       </c>
       <c r="U155" t="s">
         <v>537</v>
@@ -15976,7 +15970,7 @@
         <v>1709</v>
       </c>
       <c r="C156" t="s">
-        <v>64</v>
+        <v>104</v>
       </c>
       <c r="D156" t="s">
         <v>450</v>
@@ -15991,7 +15985,7 @@
         <v>40</v>
       </c>
       <c r="H156" t="s">
-        <v>131</v>
+        <v>41</v>
       </c>
       <c r="I156" t="s">
         <v>1711</v>
@@ -16007,7 +16001,7 @@
         <v>1714</v>
       </c>
       <c r="N156" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="O156" t="s">
         <v>1715</v>
@@ -16019,13 +16013,13 @@
         <v>35</v>
       </c>
       <c r="R156" t="s">
-        <v>138</v>
+        <v>176</v>
       </c>
       <c r="S156" t="s">
-        <v>139</v>
+        <v>177</v>
       </c>
       <c r="T156" t="s">
-        <v>140</v>
+        <v>178</v>
       </c>
       <c r="U156" t="s">
         <v>537</v>
@@ -16053,7 +16047,7 @@
         <v>40</v>
       </c>
       <c r="H157" t="s">
-        <v>251</v>
+        <v>55</v>
       </c>
       <c r="I157" t="s">
         <v>1720</v>
@@ -16080,7 +16074,7 @@
         <v>1726</v>
       </c>
       <c r="Q157" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="R157" t="s">
         <v>1727</v>
@@ -16110,7 +16104,7 @@
         <v>1031</v>
       </c>
       <c r="E158" t="s">
-        <v>239</v>
+        <v>270</v>
       </c>
       <c r="F158" t="s">
         <v>1731</v>
@@ -16119,7 +16113,7 @@
         <v>40</v>
       </c>
       <c r="H158" t="s">
-        <v>131</v>
+        <v>41</v>
       </c>
       <c r="I158" t="s">
         <v>1732</v>
@@ -16137,7 +16131,7 @@
         <v>1736</v>
       </c>
       <c r="N158" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="O158" t="s">
         <v>1737</v>
@@ -16146,7 +16140,7 @@
         <v>1738</v>
       </c>
       <c r="Q158" t="s">
-        <v>114</v>
+        <v>153</v>
       </c>
       <c r="R158" t="s">
         <v>1739</v>
@@ -16185,7 +16179,7 @@
         <v>40</v>
       </c>
       <c r="H159" t="s">
-        <v>251</v>
+        <v>55</v>
       </c>
       <c r="I159" t="s">
         <v>1743</v>
@@ -16203,7 +16197,7 @@
         <v>1747</v>
       </c>
       <c r="N159" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="O159" t="s">
         <v>1748</v>
@@ -16212,7 +16206,7 @@
         <v>1749</v>
       </c>
       <c r="Q159" t="s">
-        <v>114</v>
+        <v>153</v>
       </c>
       <c r="R159" t="s">
         <v>1750</v>
@@ -16269,7 +16263,7 @@
         <v>1760</v>
       </c>
       <c r="N160" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="O160" t="s">
         <v>1761</v>
@@ -16278,7 +16272,7 @@
         <v>1762</v>
       </c>
       <c r="Q160" t="s">
-        <v>114</v>
+        <v>153</v>
       </c>
       <c r="R160" t="s">
         <v>1763</v>
@@ -16335,7 +16329,7 @@
         <v>1760</v>
       </c>
       <c r="N161" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="O161" t="s">
         <v>1767</v>
@@ -16344,7 +16338,7 @@
         <v>1768</v>
       </c>
       <c r="Q161" t="s">
-        <v>114</v>
+        <v>153</v>
       </c>
       <c r="R161" t="s">
         <v>1769</v>
@@ -16383,7 +16377,7 @@
         <v>40</v>
       </c>
       <c r="H162" t="s">
-        <v>66</v>
+        <v>106</v>
       </c>
       <c r="I162" t="s">
         <v>1775</v>
@@ -16401,7 +16395,7 @@
         <v>1779</v>
       </c>
       <c r="N162" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="O162" t="s">
         <v>1780</v>
@@ -16410,16 +16404,16 @@
         <v>1781</v>
       </c>
       <c r="Q162" t="s">
-        <v>114</v>
+        <v>153</v>
       </c>
       <c r="R162" t="s">
-        <v>186</v>
+        <v>217</v>
       </c>
       <c r="S162" t="s">
-        <v>187</v>
+        <v>218</v>
       </c>
       <c r="T162" t="s">
-        <v>188</v>
+        <v>219</v>
       </c>
       <c r="U162" t="s">
         <v>537</v>
@@ -16437,10 +16431,10 @@
         <v>37</v>
       </c>
       <c r="D163" t="s">
-        <v>79</v>
+        <v>118</v>
       </c>
       <c r="E163" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="F163" t="s">
         <v>1783</v>
@@ -16449,7 +16443,7 @@
         <v>27</v>
       </c>
       <c r="H163" t="s">
-        <v>131</v>
+        <v>41</v>
       </c>
       <c r="I163" t="s">
         <v>1784</v>
@@ -16467,7 +16461,7 @@
         <v>1788</v>
       </c>
       <c r="N163" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="O163" t="s">
         <v>1789</v>
@@ -16506,7 +16500,7 @@
         <v>822</v>
       </c>
       <c r="E164" t="s">
-        <v>180</v>
+        <v>68</v>
       </c>
       <c r="F164" t="s">
         <v>1795</v>
@@ -16515,7 +16509,7 @@
         <v>40</v>
       </c>
       <c r="H164" t="s">
-        <v>131</v>
+        <v>41</v>
       </c>
       <c r="I164" t="s">
         <v>1796</v>
@@ -16533,7 +16527,7 @@
         <v>1800</v>
       </c>
       <c r="N164" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="O164" t="s">
         <v>1801</v>
@@ -16566,13 +16560,13 @@
         <v>1806</v>
       </c>
       <c r="C165" t="s">
-        <v>64</v>
+        <v>104</v>
       </c>
       <c r="D165" t="s">
         <v>1807</v>
       </c>
       <c r="E165" t="s">
-        <v>239</v>
+        <v>270</v>
       </c>
       <c r="F165" t="s">
         <v>1795</v>
@@ -16581,7 +16575,7 @@
         <v>40</v>
       </c>
       <c r="H165" t="s">
-        <v>131</v>
+        <v>41</v>
       </c>
       <c r="I165" t="s">
         <v>1808</v>
@@ -16597,7 +16591,7 @@
         <v>1811</v>
       </c>
       <c r="N165" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="O165" t="s">
         <v>1812</v>
@@ -16606,7 +16600,7 @@
         <v>1813</v>
       </c>
       <c r="Q165" t="s">
-        <v>114</v>
+        <v>153</v>
       </c>
       <c r="R165" t="s">
         <v>1803</v>
@@ -16630,13 +16624,13 @@
         <v>1814</v>
       </c>
       <c r="C166" t="s">
-        <v>64</v>
+        <v>104</v>
       </c>
       <c r="D166" t="s">
         <v>1807</v>
       </c>
       <c r="E166" t="s">
-        <v>239</v>
+        <v>270</v>
       </c>
       <c r="F166" t="s">
         <v>1795</v>
@@ -16645,7 +16639,7 @@
         <v>40</v>
       </c>
       <c r="H166" t="s">
-        <v>131</v>
+        <v>41</v>
       </c>
       <c r="I166" t="s">
         <v>1815</v>
@@ -16661,7 +16655,7 @@
         <v>1818</v>
       </c>
       <c r="N166" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="O166" t="s">
         <v>1819</v>
@@ -16670,7 +16664,7 @@
         <v>1820</v>
       </c>
       <c r="Q166" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="R166" t="s">
         <v>1803</v>
@@ -16694,7 +16688,7 @@
         <v>1821</v>
       </c>
       <c r="C167" t="s">
-        <v>64</v>
+        <v>104</v>
       </c>
       <c r="D167" t="s">
         <v>1822</v>
@@ -16709,7 +16703,7 @@
         <v>40</v>
       </c>
       <c r="H167" t="s">
-        <v>131</v>
+        <v>41</v>
       </c>
       <c r="I167" t="s">
         <v>1824</v>
@@ -16725,7 +16719,7 @@
         <v>1827</v>
       </c>
       <c r="N167" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="O167" t="s">
         <v>1828</v>
@@ -16734,16 +16728,16 @@
         <v>1829</v>
       </c>
       <c r="Q167" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="R167" t="s">
-        <v>186</v>
+        <v>217</v>
       </c>
       <c r="S167" t="s">
-        <v>187</v>
+        <v>218</v>
       </c>
       <c r="T167" t="s">
-        <v>188</v>
+        <v>219</v>
       </c>
       <c r="U167" t="s">
         <v>537</v>
@@ -16758,13 +16752,13 @@
         <v>1830</v>
       </c>
       <c r="C168" t="s">
-        <v>64</v>
+        <v>104</v>
       </c>
       <c r="D168" t="s">
         <v>1606</v>
       </c>
       <c r="E168" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="F168" t="s">
         <v>1831</v>
@@ -16773,7 +16767,7 @@
         <v>40</v>
       </c>
       <c r="H168" t="s">
-        <v>251</v>
+        <v>55</v>
       </c>
       <c r="I168" t="s">
         <v>1832</v>
@@ -16789,7 +16783,7 @@
         <v>1835</v>
       </c>
       <c r="N168" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="O168" t="s">
         <v>1836</v>
@@ -16798,7 +16792,7 @@
         <v>1837</v>
       </c>
       <c r="Q168" t="s">
-        <v>114</v>
+        <v>153</v>
       </c>
       <c r="R168" t="s">
         <v>1838</v>
@@ -16822,7 +16816,7 @@
         <v>1841</v>
       </c>
       <c r="C169" t="s">
-        <v>211</v>
+        <v>242</v>
       </c>
       <c r="D169" t="s">
         <v>1209</v>
@@ -16833,7 +16827,7 @@
       </c>
       <c r="G169"/>
       <c r="H169" t="s">
-        <v>66</v>
+        <v>106</v>
       </c>
       <c r="I169" t="s">
         <v>1843</v>
@@ -16851,7 +16845,7 @@
         <v>1847</v>
       </c>
       <c r="N169" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="O169" t="s">
         <v>1848</v>

--- a/Objets_parlementaires_Jura.xlsx
+++ b/Objets_parlementaires_Jura.xlsx
@@ -782,7 +782,7 @@
     <t xml:space="preserve">26.3916</t>
   </si>
   <si>
-    <t xml:space="preserve">Gewährleistung des Betriebs der Opferhilfe-Nummer 142 in der ganzen Schweiz</t>
+    <t xml:space="preserve">Gewährleistung des Betriebs der Opferhilfenummer 142 in der ganzen Schweiz</t>
   </si>
   <si>
     <t xml:space="preserve">Garantir le fonctionnement de la ligne d'aide aux victimes 142 sur l'ensemble du territoire</t>

--- a/Objets_parlementaires_Jura.xlsx
+++ b/Objets_parlementaires_Jura.xlsx
@@ -80,6 +80,63 @@
     <t xml:space="preserve">Statut_Change_Date</t>
   </si>
   <si>
+    <t xml:space="preserve">26.7473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fra.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dobler Loïc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EJPD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arbeitsbedingungen beim Staatssekretariat für Migration: Ein Wendepunkt für das Bundespersonal?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conditions d'emploi au SEM : un tournant pour le personnel fédéral ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Selon une communication interne du SEM, une modification réglementaire entrant en vigueur prochainement autoriserait le maintien en CDD jusqu'à six ans d'employés fédéraux, les privant de la protection de l'art. 9 LPers. Alors que le SEM supprime déjà de nombreux postes, cette logique pourrait s'étendre à tout poste sans financement garanti.&amp;nbsp;&lt;br&gt;Le Conseil fédéral confirme-t-il cette modification et quelles garanties prévoit-il pour les employés concernés ?&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Laut einer internen Mitteilung des Staatssekretariats für Migration&amp;nbsp;(SEM) soll eine demnächst in Kraft tretende Änderung der rechtlichen Bestimmungen es ermöglichen, Bundesangestellte bis zu sechs Jahre lang in einem befristeten Arbeitsverhältnis zu halten, wodurch ihnen der Schutz von Artikel&amp;nbsp;9 des Bundespersonalgesetzes entzogen würde. Das SEM streicht bereits zahlreiche Stellen. Aufgrund der vorgesehenen Änderung könnten alle Stellen ohne gesicherte Finanzierung gestrichen werden.&amp;nbsp;&lt;br&gt;Bestätigt der Bundesrat diese Änderung und welche Garantien sieht er für die betroffenen Arbeitnehmenden vor?&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Erledigt / Liquidé</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20267473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20267473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Titre uniquement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staatspolitik|Beschäftigung und Arbeit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politique d'Etat|Emploi et travail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politica nazionale|Occupazione e lavoro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-06</t>
+  </si>
+  <si>
     <t xml:space="preserve">26.4701</t>
   </si>
   <si>
@@ -89,9 +146,6 @@
     <t xml:space="preserve">Crevoisier Crelier Mathilde</t>
   </si>
   <si>
-    <t xml:space="preserve">PS</t>
-  </si>
-  <si>
     <t xml:space="preserve">2026-10-02</t>
   </si>
   <si>
@@ -137,15 +191,9 @@
     <t xml:space="preserve">Ip.</t>
   </si>
   <si>
-    <t xml:space="preserve">Dobler Loïc</t>
-  </si>
-  <si>
     <t xml:space="preserve">2026-06-04</t>
   </si>
   <si>
-    <t xml:space="preserve">NR</t>
-  </si>
-  <si>
     <t xml:space="preserve">UVEK</t>
   </si>
   <si>
@@ -164,18 +212,12 @@
     <t xml:space="preserve">&lt;p&gt;Der Bund ist Alleinaktionär der Schweizerischen&amp;nbsp;Post&amp;nbsp;AG und legt alle vier Jahre die strategischen Ziele für sie fest&amp;nbsp;(Art.&amp;nbsp;7 des Postorganisationsgesetzes). Die am 29.&amp;nbsp;Januar&amp;nbsp;2025 verabschiedeten Ziele für den Zeitraum 2025–2028 enthalten keine Vorgaben zur geografischen Verteilung der Arbeitsplätze auf die Kantone. Ziffer&amp;nbsp;3.1 sieht eine fortschrittliche Personalpolitik und eine Erhöhung des Frauenanteils in Kaderpositionen vor. Die jährlichen Berichte über die Erreichung der strategischen Ziele enthalten keinen Indikator zur geografischen Verteilung der Arbeitsplätze.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Diese Lücke gibt Anlass zur Sorge. Die Post nimmt seit mehreren Jahren eine tiefgreifende Umstrukturierung ihres Netzes vor: Poststellen werden geschlossen und in Agenturen in privaten Geschäften umgewandelt. Die Randkantone sind am stärksten davon betroffen. Paradoxerweise ist in den strategischen Zielen bereits ein geografischer Ansatz für die Leistungen vorgesehen, indem die Erreichbarkeit der Grundversorgung auf kantonaler Ebene gemessen wird. Es gibt keinen Grund, warum diese Logik nicht auch für die Arbeitsplätze gelten sollte.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Unternehmen, die im Eigentum des Bundes sind, bieten in der Regel sichere Arbeitsplätze mit attraktiven Anstellungsbedingungen an. Solche Arbeitsplätze sollten schweizweit gefördert werden, und erst recht in den Regionen, in denen dieselben Unternehmen Stellen abbauen.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Das Eidgenössische Departement für Umwelt, Verkehr, Energie und Kommunikation muss im Übrigen bis Ende Juni&amp;nbsp;2026 eine Vernehmlassungsvorlage für eine Revision der Postgesetzgebung unterbreiten, was der vorliegenden Interpellation besondere Aktualität verleiht.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;Ich bitte den Bundesrat, folgende Fragen zu beantworten:&lt;/p&gt;&lt;ol&gt;&lt;li&gt;Wie hat sich die Anzahl der Arbeitsplätze bei der Post&amp;nbsp;(in Vollzeitäquivalenten) in den einzelnen Kantonen in den letzten zehn Jahren entwickelt?&lt;/li&gt;&lt;li&gt;Wie hat sich die Anzahl der Poststellen pro Kanton seit 2010 entwickelt?&lt;/li&gt;&lt;li&gt;Weshalb enthalten die strategischen Ziele keinen Indikator zur geografischen Verteilung der Arbeitsplätze?&lt;/li&gt;&lt;li&gt;Ist der Bundesrat der Ansicht, dass die geografische Verteilung der Arbeitsplätze in bundesnahen Betrieben in seiner Verantwortung liegt?&lt;/li&gt;&lt;li&gt;Ist der Bundesrat bereit, im Rahmen der laufenden oder anstehenden Revision der Postgesetzgebung einen solchen Indikator für die Post, die SBB und die Swisscom einzuführen?&lt;/li&gt;&lt;/ol&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">Erledigt / Liquidé</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263563</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263563</t>
   </si>
   <si>
-    <t xml:space="preserve">Titre uniquement</t>
-  </si>
-  <si>
     <t xml:space="preserve">Staatspolitik|Wirtschaft|Medien und Kommunikation|Beschäftigung und Arbeit</t>
   </si>
   <si>
@@ -230,9 +272,6 @@
     <t xml:space="preserve">UDC</t>
   </si>
   <si>
-    <t xml:space="preserve">EJPD</t>
-  </si>
-  <si>
     <t xml:space="preserve">Von Dänemark lernen. Bei längerfristigen Freiheitsstrafen muss die obligatorische Landesverweisung tatsächlich obligatorisch sein</t>
   </si>
   <si>
@@ -335,9 +374,6 @@
     <t xml:space="preserve">26.7901</t>
   </si>
   <si>
-    <t xml:space="preserve">Fra.</t>
-  </si>
-  <si>
     <t xml:space="preserve">2026-09-22</t>
   </si>
   <si>
@@ -1155,42 +1191,6 @@
   </si>
   <si>
     <t xml:space="preserve">2026-06-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arbeitsbedingungen beim Staatssekretariat für Migration: Ein Wendepunkt für das Bundespersonal?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Conditions d'emploi au SEM : un tournant pour le personnel fédéral ?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Selon une communication interne du SEM, une modification réglementaire entrant en vigueur prochainement autoriserait le maintien en CDD jusqu'à six ans d'employés fédéraux, les privant de la protection de l'art. 9 LPers. Alors que le SEM supprime déjà de nombreux postes, cette logique pourrait s'étendre à tout poste sans financement garanti.&amp;nbsp;&lt;br&gt;Le Conseil fédéral confirme-t-il cette modification et quelles garanties prévoit-il pour les employés concernés ?&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Laut einer internen Mitteilung des Staatssekretariats für Migration&amp;nbsp;(SEM) soll eine demnächst in Kraft tretende Änderung der rechtlichen Bestimmungen es ermöglichen, Bundesangestellte bis zu sechs Jahre lang in einem befristeten Arbeitsverhältnis zu halten, wodurch ihnen der Schutz von Artikel&amp;nbsp;9 des Bundespersonalgesetzes entzogen würde. Das SEM streicht bereits zahlreiche Stellen. Aufgrund der vorgesehenen Änderung könnten alle Stellen ohne gesicherte Finanzierung gestrichen werden.&amp;nbsp;&lt;br&gt;Bestätigt der Bundesrat diese Änderung und welche Garantien sieht er für die betroffenen Arbeitnehmenden vor?&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20267473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20267473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staatspolitik|Beschäftigung und Arbeit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politique d'Etat|Emploi et travail</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politica nazionale|Occupazione e lavoro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-06</t>
   </si>
   <si>
     <t xml:space="preserve">26.7426</t>
@@ -6000,7 +6000,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>20264701</v>
+        <v>20267473</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
@@ -6020,86 +6020,84 @@
       <c r="G2" t="s">
         <v>27</v>
       </c>
-      <c r="H2"/>
+      <c r="H2" t="s">
+        <v>28</v>
+      </c>
       <c r="I2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J2" t="s">
-        <v>29</v>
-      </c>
-      <c r="K2" t="s">
         <v>30</v>
       </c>
+      <c r="K2"/>
       <c r="L2" t="s">
         <v>31</v>
       </c>
-      <c r="M2"/>
+      <c r="M2" t="s">
+        <v>32</v>
+      </c>
       <c r="N2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="R2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="T2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="U2" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="V2"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>20263563</v>
+        <v>20264701</v>
       </c>
       <c r="B3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E3" t="s">
         <v>25</v>
       </c>
       <c r="F3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G3" t="s">
-        <v>43</v>
-      </c>
-      <c r="H3" t="s">
-        <v>44</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="H3"/>
       <c r="I3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L3" t="s">
-        <v>48</v>
-      </c>
-      <c r="M3" t="s">
         <v>49</v>
       </c>
+      <c r="M3"/>
       <c r="N3" t="s">
         <v>50</v>
       </c>
@@ -6122,94 +6120,94 @@
         <v>56</v>
       </c>
       <c r="U3" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="V3"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>20263564</v>
+        <v>20263563</v>
       </c>
       <c r="B4" t="s">
         <v>57</v>
       </c>
       <c r="C4" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="D4" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="E4" t="s">
         <v>25</v>
       </c>
       <c r="F4" t="s">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="G4" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H4" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="I4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="J4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="L4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="M4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="N4" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="O4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="P4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Q4" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="R4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="S4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="T4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="U4" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="V4"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>20263571</v>
+        <v>20263564</v>
       </c>
       <c r="B5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="D5" t="s">
-        <v>70</v>
+        <v>24</v>
       </c>
       <c r="E5" t="s">
-        <v>71</v>
+        <v>25</v>
       </c>
       <c r="F5" t="s">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="G5" t="s">
         <v>27</v>
@@ -6233,7 +6231,7 @@
         <v>77</v>
       </c>
       <c r="N5" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="O5" t="s">
         <v>78</v>
@@ -6242,7 +6240,7 @@
         <v>79</v>
       </c>
       <c r="Q5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="R5" t="s">
         <v>80</v>
@@ -6254,228 +6252,230 @@
         <v>82</v>
       </c>
       <c r="U5" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="V5"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>20264418</v>
+        <v>20263571</v>
       </c>
       <c r="B6" t="s">
         <v>83</v>
       </c>
       <c r="C6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D6" t="s">
-        <v>41</v>
+        <v>84</v>
       </c>
       <c r="E6" t="s">
-        <v>25</v>
+        <v>85</v>
       </c>
       <c r="F6" t="s">
-        <v>84</v>
+        <v>59</v>
       </c>
       <c r="G6" t="s">
-        <v>43</v>
-      </c>
-      <c r="H6"/>
+        <v>45</v>
+      </c>
+      <c r="H6" t="s">
+        <v>28</v>
+      </c>
       <c r="I6" t="s">
-        <v>28</v>
+        <v>86</v>
       </c>
       <c r="J6" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K6" t="s">
-        <v>30</v>
+        <v>88</v>
       </c>
       <c r="L6" t="s">
-        <v>86</v>
-      </c>
-      <c r="M6"/>
+        <v>89</v>
+      </c>
+      <c r="M6" t="s">
+        <v>90</v>
+      </c>
       <c r="N6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O6" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="P6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="Q6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R6"/>
-      <c r="S6"/>
-      <c r="T6"/>
+        <v>53</v>
+      </c>
+      <c r="R6" t="s">
+        <v>93</v>
+      </c>
+      <c r="S6" t="s">
+        <v>94</v>
+      </c>
+      <c r="T6" t="s">
+        <v>95</v>
+      </c>
       <c r="U6" t="s">
-        <v>84</v>
+        <v>44</v>
       </c>
       <c r="V6"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>20264338</v>
+        <v>20264418</v>
       </c>
       <c r="B7" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="C7" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="D7" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="E7" t="s">
         <v>25</v>
       </c>
       <c r="F7" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="G7" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H7"/>
       <c r="I7" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="J7" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="K7" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="L7" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="M7"/>
       <c r="N7" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="O7" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="P7" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="Q7" t="s">
         <v>53</v>
       </c>
-      <c r="R7" t="s">
-        <v>95</v>
-      </c>
-      <c r="S7" t="s">
-        <v>96</v>
-      </c>
-      <c r="T7" t="s">
+      <c r="R7"/>
+      <c r="S7"/>
+      <c r="T7"/>
+      <c r="U7" t="s">
         <v>97</v>
-      </c>
-      <c r="U7" t="s">
-        <v>90</v>
       </c>
       <c r="V7"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>20264339</v>
+        <v>20264338</v>
       </c>
       <c r="B8" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D8" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="E8" t="s">
         <v>25</v>
       </c>
       <c r="F8" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="G8" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H8"/>
       <c r="I8" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="J8" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="K8" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="L8" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="M8"/>
       <c r="N8" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="O8" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="P8" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="Q8" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="R8" t="s">
+        <v>108</v>
+      </c>
+      <c r="S8" t="s">
+        <v>109</v>
+      </c>
+      <c r="T8" t="s">
+        <v>110</v>
+      </c>
+      <c r="U8" t="s">
         <v>103</v>
-      </c>
-      <c r="S8" t="s">
-        <v>104</v>
-      </c>
-      <c r="T8" t="s">
-        <v>105</v>
-      </c>
-      <c r="U8" t="s">
-        <v>90</v>
       </c>
       <c r="V8"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>20267901</v>
+        <v>20264339</v>
       </c>
       <c r="B9" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="C9" t="s">
-        <v>107</v>
+        <v>58</v>
       </c>
       <c r="D9" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="E9" t="s">
         <v>25</v>
       </c>
       <c r="F9" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="G9" t="s">
-        <v>43</v>
-      </c>
-      <c r="H9" t="s">
-        <v>109</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="H9"/>
       <c r="I9" t="s">
-        <v>110</v>
+        <v>46</v>
       </c>
       <c r="J9" t="s">
-        <v>111</v>
-      </c>
-      <c r="K9"/>
+        <v>112</v>
+      </c>
+      <c r="K9" t="s">
+        <v>48</v>
+      </c>
       <c r="L9" t="s">
-        <v>112</v>
-      </c>
-      <c r="M9" t="s">
         <v>113</v>
       </c>
+      <c r="M9"/>
       <c r="N9" t="s">
         <v>50</v>
       </c>
@@ -6486,7 +6486,7 @@
         <v>115</v>
       </c>
       <c r="Q9" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="R9" t="s">
         <v>116</v>
@@ -6498,48 +6498,50 @@
         <v>118</v>
       </c>
       <c r="U9" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="V9"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>20264261</v>
+        <v>20267901</v>
       </c>
       <c r="B10" t="s">
+        <v>119</v>
+      </c>
+      <c r="C10" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E10" t="s">
+        <v>25</v>
+      </c>
+      <c r="F10" t="s">
         <v>120</v>
-      </c>
-      <c r="C10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D10" t="s">
-        <v>121</v>
-      </c>
-      <c r="E10" t="s">
-        <v>122</v>
-      </c>
-      <c r="F10" t="s">
-        <v>123</v>
       </c>
       <c r="G10" t="s">
         <v>27</v>
       </c>
-      <c r="H10"/>
+      <c r="H10" t="s">
+        <v>121</v>
+      </c>
       <c r="I10" t="s">
-        <v>28</v>
+        <v>122</v>
       </c>
       <c r="J10" t="s">
+        <v>123</v>
+      </c>
+      <c r="K10"/>
+      <c r="L10" t="s">
         <v>124</v>
       </c>
-      <c r="K10" t="s">
-        <v>30</v>
-      </c>
-      <c r="L10" t="s">
+      <c r="M10" t="s">
         <v>125</v>
       </c>
-      <c r="M10"/>
       <c r="N10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O10" t="s">
         <v>126</v>
@@ -6548,7 +6550,7 @@
         <v>127</v>
       </c>
       <c r="Q10" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="R10" t="s">
         <v>128</v>
@@ -6560,174 +6562,172 @@
         <v>130</v>
       </c>
       <c r="U10" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="V10"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>20263891</v>
+        <v>20264261</v>
       </c>
       <c r="B11" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C11" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="D11" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="E11" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="F11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="G11" t="s">
-        <v>27</v>
-      </c>
-      <c r="H11" t="s">
-        <v>133</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="H11"/>
       <c r="I11" t="s">
-        <v>134</v>
+        <v>46</v>
       </c>
       <c r="J11" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="K11" t="s">
-        <v>136</v>
+        <v>48</v>
       </c>
       <c r="L11" t="s">
         <v>137</v>
       </c>
-      <c r="M11" t="s">
-        <v>138</v>
-      </c>
+      <c r="M11"/>
       <c r="N11" t="s">
         <v>50</v>
       </c>
       <c r="O11" t="s">
+        <v>138</v>
+      </c>
+      <c r="P11" t="s">
         <v>139</v>
       </c>
-      <c r="P11" t="s">
+      <c r="Q11" t="s">
+        <v>36</v>
+      </c>
+      <c r="R11" t="s">
         <v>140</v>
       </c>
-      <c r="Q11" t="s">
-        <v>53</v>
-      </c>
-      <c r="R11" t="s">
+      <c r="S11" t="s">
         <v>141</v>
       </c>
-      <c r="S11" t="s">
+      <c r="T11" t="s">
         <v>142</v>
       </c>
-      <c r="T11" t="s">
-        <v>143</v>
-      </c>
       <c r="U11" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="V11"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>20263518</v>
+        <v>20263891</v>
       </c>
       <c r="B12" t="s">
+        <v>143</v>
+      </c>
+      <c r="C12" t="s">
+        <v>58</v>
+      </c>
+      <c r="D12" t="s">
+        <v>133</v>
+      </c>
+      <c r="E12" t="s">
+        <v>134</v>
+      </c>
+      <c r="F12" t="s">
+        <v>144</v>
+      </c>
+      <c r="G12" t="s">
+        <v>45</v>
+      </c>
+      <c r="H12" t="s">
         <v>145</v>
       </c>
-      <c r="C12" t="s">
-        <v>23</v>
-      </c>
-      <c r="D12" t="s">
+      <c r="I12" t="s">
         <v>146</v>
       </c>
-      <c r="E12" t="s">
+      <c r="J12" t="s">
         <v>147</v>
       </c>
-      <c r="F12" t="s">
+      <c r="K12" t="s">
         <v>148</v>
       </c>
-      <c r="G12" t="s">
-        <v>43</v>
-      </c>
-      <c r="H12" t="s">
-        <v>133</v>
-      </c>
-      <c r="I12" t="s">
+      <c r="L12" t="s">
         <v>149</v>
       </c>
-      <c r="J12" t="s">
+      <c r="M12" t="s">
         <v>150</v>
       </c>
-      <c r="K12" t="s">
+      <c r="N12" t="s">
+        <v>33</v>
+      </c>
+      <c r="O12" t="s">
         <v>151</v>
       </c>
-      <c r="L12" t="s">
+      <c r="P12" t="s">
         <v>152</v>
       </c>
-      <c r="M12" t="s">
+      <c r="Q12" t="s">
+        <v>36</v>
+      </c>
+      <c r="R12" t="s">
         <v>153</v>
       </c>
-      <c r="N12" t="s">
-        <v>50</v>
-      </c>
-      <c r="O12" t="s">
+      <c r="S12" t="s">
         <v>154</v>
       </c>
-      <c r="P12" t="s">
+      <c r="T12" t="s">
         <v>155</v>
       </c>
-      <c r="Q12" t="s">
+      <c r="U12" t="s">
         <v>156</v>
-      </c>
-      <c r="R12" t="s">
-        <v>157</v>
-      </c>
-      <c r="S12" t="s">
-        <v>158</v>
-      </c>
-      <c r="T12" t="s">
-        <v>159</v>
-      </c>
-      <c r="U12" t="s">
-        <v>144</v>
       </c>
       <c r="V12"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>20267687</v>
+        <v>20263518</v>
       </c>
       <c r="B13" t="s">
+        <v>157</v>
+      </c>
+      <c r="C13" t="s">
+        <v>42</v>
+      </c>
+      <c r="D13" t="s">
+        <v>158</v>
+      </c>
+      <c r="E13" t="s">
+        <v>159</v>
+      </c>
+      <c r="F13" t="s">
         <v>160</v>
       </c>
-      <c r="C13" t="s">
-        <v>107</v>
-      </c>
-      <c r="D13" t="s">
-        <v>41</v>
-      </c>
-      <c r="E13" t="s">
-        <v>25</v>
-      </c>
-      <c r="F13" t="s">
+      <c r="G13" t="s">
+        <v>27</v>
+      </c>
+      <c r="H13" t="s">
+        <v>145</v>
+      </c>
+      <c r="I13" t="s">
         <v>161</v>
       </c>
-      <c r="G13" t="s">
-        <v>43</v>
-      </c>
-      <c r="H13" t="s">
-        <v>133</v>
-      </c>
-      <c r="I13" t="s">
+      <c r="J13" t="s">
         <v>162</v>
       </c>
-      <c r="J13" t="s">
+      <c r="K13" t="s">
         <v>163</v>
       </c>
-      <c r="K13"/>
       <c r="L13" t="s">
         <v>164</v>
       </c>
@@ -6735,7 +6735,7 @@
         <v>165</v>
       </c>
       <c r="N13" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="O13" t="s">
         <v>166</v>
@@ -6744,142 +6744,144 @@
         <v>167</v>
       </c>
       <c r="Q13" t="s">
-        <v>53</v>
+        <v>168</v>
       </c>
       <c r="R13" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="S13" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="T13" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="U13" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="V13"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>20267688</v>
+        <v>20267687</v>
       </c>
       <c r="B14" t="s">
         <v>172</v>
       </c>
       <c r="C14" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D14" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="E14" t="s">
         <v>25</v>
       </c>
       <c r="F14" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="G14" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H14" t="s">
-        <v>44</v>
+        <v>145</v>
       </c>
       <c r="I14" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="J14" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="K14"/>
       <c r="L14" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="M14" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N14" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="O14" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P14" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q14" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="R14" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="S14" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="T14" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="U14" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="V14"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>20264169</v>
+        <v>20267688</v>
       </c>
       <c r="B15" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C15" t="s">
         <v>23</v>
       </c>
       <c r="D15" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="E15" t="s">
         <v>25</v>
       </c>
       <c r="F15" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="G15" t="s">
-        <v>43</v>
-      </c>
-      <c r="H15"/>
+        <v>27</v>
+      </c>
+      <c r="H15" t="s">
+        <v>60</v>
+      </c>
       <c r="I15" t="s">
-        <v>28</v>
+        <v>185</v>
       </c>
       <c r="J15" t="s">
-        <v>184</v>
-      </c>
-      <c r="K15" t="s">
-        <v>30</v>
-      </c>
+        <v>186</v>
+      </c>
+      <c r="K15"/>
       <c r="L15" t="s">
-        <v>185</v>
-      </c>
-      <c r="M15"/>
+        <v>187</v>
+      </c>
+      <c r="M15" t="s">
+        <v>188</v>
+      </c>
       <c r="N15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O15" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="P15" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="Q15" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="R15" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="S15" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="T15" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="U15" t="s">
         <v>183</v>
@@ -6888,594 +6890,590 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>20263628</v>
+        <v>20264169</v>
       </c>
       <c r="B16" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="C16" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D16" t="s">
-        <v>121</v>
+        <v>24</v>
       </c>
       <c r="E16" t="s">
-        <v>122</v>
+        <v>25</v>
       </c>
       <c r="F16" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="G16" t="s">
         <v>27</v>
       </c>
-      <c r="H16" t="s">
-        <v>193</v>
-      </c>
+      <c r="H16"/>
       <c r="I16" t="s">
-        <v>194</v>
+        <v>46</v>
       </c>
       <c r="J16" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K16" t="s">
-        <v>196</v>
+        <v>48</v>
       </c>
       <c r="L16" t="s">
         <v>197</v>
       </c>
-      <c r="M16" t="s">
+      <c r="M16"/>
+      <c r="N16" t="s">
+        <v>50</v>
+      </c>
+      <c r="O16" t="s">
         <v>198</v>
       </c>
-      <c r="N16" t="s">
+      <c r="P16" t="s">
         <v>199</v>
       </c>
-      <c r="O16" t="s">
+      <c r="Q16" t="s">
+        <v>36</v>
+      </c>
+      <c r="R16" t="s">
         <v>200</v>
       </c>
-      <c r="P16" t="s">
+      <c r="S16" t="s">
         <v>201</v>
       </c>
-      <c r="Q16" t="s">
-        <v>53</v>
-      </c>
-      <c r="R16" t="s">
+      <c r="T16" t="s">
         <v>202</v>
       </c>
-      <c r="S16" t="s">
-        <v>203</v>
-      </c>
-      <c r="T16" t="s">
-        <v>204</v>
-      </c>
       <c r="U16" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="V16"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>20263131</v>
+        <v>20263628</v>
       </c>
       <c r="B17" t="s">
+        <v>203</v>
+      </c>
+      <c r="C17" t="s">
+        <v>42</v>
+      </c>
+      <c r="D17" t="s">
+        <v>133</v>
+      </c>
+      <c r="E17" t="s">
+        <v>134</v>
+      </c>
+      <c r="F17" t="s">
+        <v>204</v>
+      </c>
+      <c r="G17" t="s">
+        <v>45</v>
+      </c>
+      <c r="H17" t="s">
         <v>205</v>
       </c>
-      <c r="C17" t="s">
-        <v>23</v>
-      </c>
-      <c r="D17" t="s">
+      <c r="I17" t="s">
         <v>206</v>
       </c>
-      <c r="E17"/>
-      <c r="F17" t="s">
+      <c r="J17" t="s">
         <v>207</v>
       </c>
-      <c r="G17" t="s">
-        <v>43</v>
-      </c>
-      <c r="H17" t="s">
-        <v>72</v>
-      </c>
-      <c r="I17" t="s">
+      <c r="K17" t="s">
         <v>208</v>
       </c>
-      <c r="J17" t="s">
+      <c r="L17" t="s">
         <v>209</v>
       </c>
-      <c r="K17" t="s">
-        <v>75</v>
-      </c>
-      <c r="L17" t="s">
+      <c r="M17" t="s">
         <v>210</v>
       </c>
-      <c r="M17" t="s">
-        <v>77</v>
-      </c>
       <c r="N17" t="s">
-        <v>50</v>
+        <v>211</v>
       </c>
       <c r="O17" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P17" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q17" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="R17" t="s">
-        <v>80</v>
+        <v>214</v>
       </c>
       <c r="S17" t="s">
-        <v>81</v>
+        <v>215</v>
       </c>
       <c r="T17" t="s">
-        <v>82</v>
+        <v>216</v>
       </c>
       <c r="U17" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="V17"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>20264146</v>
+        <v>20263131</v>
       </c>
       <c r="B18" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="C18" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D18" t="s">
-        <v>214</v>
-      </c>
-      <c r="E18" t="s">
-        <v>71</v>
-      </c>
+        <v>218</v>
+      </c>
+      <c r="E18"/>
       <c r="F18" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="G18" t="s">
-        <v>43</v>
-      </c>
-      <c r="H18"/>
+        <v>27</v>
+      </c>
+      <c r="H18" t="s">
+        <v>28</v>
+      </c>
       <c r="I18" t="s">
-        <v>28</v>
+        <v>220</v>
       </c>
       <c r="J18" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="K18" t="s">
-        <v>30</v>
+        <v>88</v>
       </c>
       <c r="L18" t="s">
-        <v>217</v>
-      </c>
-      <c r="M18"/>
+        <v>222</v>
+      </c>
+      <c r="M18" t="s">
+        <v>90</v>
+      </c>
       <c r="N18" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O18" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="P18" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="Q18" t="s">
         <v>53</v>
       </c>
       <c r="R18" t="s">
-        <v>220</v>
+        <v>93</v>
       </c>
       <c r="S18" t="s">
-        <v>221</v>
+        <v>94</v>
       </c>
       <c r="T18" t="s">
-        <v>222</v>
+        <v>95</v>
       </c>
       <c r="U18" t="s">
-        <v>215</v>
+        <v>195</v>
       </c>
       <c r="V18"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>20267829</v>
+        <v>20264146</v>
       </c>
       <c r="B19" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C19" t="s">
-        <v>107</v>
+        <v>58</v>
       </c>
       <c r="D19" t="s">
-        <v>41</v>
+        <v>226</v>
       </c>
       <c r="E19" t="s">
-        <v>25</v>
+        <v>85</v>
       </c>
       <c r="F19" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="G19" t="s">
-        <v>43</v>
-      </c>
-      <c r="H19" t="s">
-        <v>44</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="H19"/>
       <c r="I19" t="s">
-        <v>224</v>
+        <v>46</v>
       </c>
       <c r="J19" t="s">
-        <v>225</v>
-      </c>
-      <c r="K19"/>
+        <v>228</v>
+      </c>
+      <c r="K19" t="s">
+        <v>48</v>
+      </c>
       <c r="L19" t="s">
-        <v>226</v>
-      </c>
-      <c r="M19" t="s">
-        <v>227</v>
-      </c>
+        <v>229</v>
+      </c>
+      <c r="M19"/>
       <c r="N19" t="s">
         <v>50</v>
       </c>
       <c r="O19" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="P19" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q19" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="R19" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="S19" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="T19" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="U19" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="V19"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>20264127</v>
+        <v>20267829</v>
       </c>
       <c r="B20" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C20" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="D20" t="s">
-        <v>234</v>
+        <v>24</v>
       </c>
       <c r="E20" t="s">
         <v>25</v>
       </c>
       <c r="F20" t="s">
-        <v>161</v>
+        <v>227</v>
       </c>
       <c r="G20" t="s">
-        <v>43</v>
-      </c>
-      <c r="H20"/>
+        <v>27</v>
+      </c>
+      <c r="H20" t="s">
+        <v>60</v>
+      </c>
       <c r="I20" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="J20" t="s">
-        <v>236</v>
-      </c>
-      <c r="K20" t="s">
         <v>237</v>
       </c>
-      <c r="L20"/>
+      <c r="K20"/>
+      <c r="L20" t="s">
+        <v>238</v>
+      </c>
       <c r="M20" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="N20" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O20" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="P20" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q20" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="R20" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="S20" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="T20" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="U20" t="s">
-        <v>161</v>
+        <v>227</v>
       </c>
       <c r="V20"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>20260312</v>
+        <v>20264127</v>
       </c>
       <c r="B21" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C21" t="s">
-        <v>245</v>
+        <v>58</v>
       </c>
       <c r="D21" t="s">
         <v>246</v>
       </c>
-      <c r="E21"/>
+      <c r="E21" t="s">
+        <v>25</v>
+      </c>
       <c r="F21" t="s">
+        <v>173</v>
+      </c>
+      <c r="G21" t="s">
+        <v>27</v>
+      </c>
+      <c r="H21"/>
+      <c r="I21" t="s">
         <v>247</v>
       </c>
-      <c r="G21"/>
-      <c r="H21" t="s">
+      <c r="J21" t="s">
         <v>248</v>
       </c>
-      <c r="I21" t="s">
+      <c r="K21" t="s">
         <v>249</v>
       </c>
-      <c r="J21" t="s">
+      <c r="L21"/>
+      <c r="M21" t="s">
         <v>250</v>
       </c>
-      <c r="K21" t="s">
+      <c r="N21" t="s">
+        <v>50</v>
+      </c>
+      <c r="O21" t="s">
         <v>251</v>
       </c>
-      <c r="L21" t="s">
+      <c r="P21" t="s">
         <v>252</v>
       </c>
-      <c r="M21" t="s">
+      <c r="Q21" t="s">
+        <v>53</v>
+      </c>
+      <c r="R21" t="s">
         <v>253</v>
       </c>
-      <c r="N21" t="s">
+      <c r="S21" t="s">
         <v>254</v>
       </c>
-      <c r="O21" t="s">
+      <c r="T21" t="s">
         <v>255</v>
       </c>
-      <c r="P21" t="s">
-        <v>256</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>35</v>
-      </c>
-      <c r="R21"/>
-      <c r="S21"/>
-      <c r="T21"/>
       <c r="U21" t="s">
-        <v>257</v>
+        <v>173</v>
       </c>
       <c r="V21"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>20263916</v>
+        <v>20260312</v>
       </c>
       <c r="B22" t="s">
+        <v>256</v>
+      </c>
+      <c r="C22" t="s">
+        <v>257</v>
+      </c>
+      <c r="D22" t="s">
         <v>258</v>
       </c>
-      <c r="C22" t="s">
-        <v>40</v>
-      </c>
-      <c r="D22" t="s">
-        <v>24</v>
-      </c>
-      <c r="E22" t="s">
-        <v>25</v>
-      </c>
+      <c r="E22"/>
       <c r="F22" t="s">
-        <v>132</v>
-      </c>
-      <c r="G22" t="s">
-        <v>27</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="G22"/>
       <c r="H22" t="s">
-        <v>44</v>
+        <v>260</v>
       </c>
       <c r="I22" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="J22" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="K22" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="L22" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="M22" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="N22" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="O22" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="P22" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q22" t="s">
         <v>53</v>
       </c>
-      <c r="R22" t="s">
-        <v>267</v>
-      </c>
-      <c r="S22" t="s">
-        <v>268</v>
-      </c>
-      <c r="T22" t="s">
+      <c r="R22"/>
+      <c r="S22"/>
+      <c r="T22"/>
+      <c r="U22" t="s">
         <v>269</v>
-      </c>
-      <c r="U22" t="s">
-        <v>270</v>
       </c>
       <c r="V22"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>20263968</v>
+        <v>20263916</v>
       </c>
       <c r="B23" t="s">
+        <v>270</v>
+      </c>
+      <c r="C23" t="s">
+        <v>58</v>
+      </c>
+      <c r="D23" t="s">
+        <v>43</v>
+      </c>
+      <c r="E23" t="s">
+        <v>25</v>
+      </c>
+      <c r="F23" t="s">
+        <v>144</v>
+      </c>
+      <c r="G23" t="s">
+        <v>45</v>
+      </c>
+      <c r="H23" t="s">
+        <v>60</v>
+      </c>
+      <c r="I23" t="s">
         <v>271</v>
       </c>
-      <c r="C23" t="s">
-        <v>40</v>
-      </c>
-      <c r="D23" t="s">
+      <c r="J23" t="s">
         <v>272</v>
       </c>
-      <c r="E23" t="s">
+      <c r="K23" t="s">
         <v>273</v>
       </c>
-      <c r="F23" t="s">
-        <v>132</v>
-      </c>
-      <c r="G23" t="s">
-        <v>43</v>
-      </c>
-      <c r="H23" t="s">
-        <v>44</v>
-      </c>
-      <c r="I23" t="s">
+      <c r="L23" t="s">
         <v>274</v>
       </c>
-      <c r="J23" t="s">
+      <c r="M23" t="s">
         <v>275</v>
       </c>
-      <c r="K23" t="s">
+      <c r="N23" t="s">
         <v>276</v>
       </c>
-      <c r="L23" t="s">
+      <c r="O23" t="s">
         <v>277</v>
       </c>
-      <c r="M23" t="s">
+      <c r="P23" t="s">
         <v>278</v>
       </c>
-      <c r="N23" t="s">
+      <c r="Q23" t="s">
+        <v>36</v>
+      </c>
+      <c r="R23" t="s">
         <v>279</v>
       </c>
-      <c r="O23" t="s">
+      <c r="S23" t="s">
         <v>280</v>
       </c>
-      <c r="P23" t="s">
+      <c r="T23" t="s">
         <v>281</v>
       </c>
-      <c r="Q23" t="s">
-        <v>156</v>
-      </c>
-      <c r="R23" t="s">
-        <v>230</v>
-      </c>
-      <c r="S23" t="s">
-        <v>231</v>
-      </c>
-      <c r="T23" t="s">
-        <v>232</v>
-      </c>
       <c r="U23" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="V23"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>20263997</v>
+        <v>20263968</v>
       </c>
       <c r="B24" t="s">
+        <v>283</v>
+      </c>
+      <c r="C24" t="s">
+        <v>58</v>
+      </c>
+      <c r="D24" t="s">
+        <v>284</v>
+      </c>
+      <c r="E24" t="s">
+        <v>285</v>
+      </c>
+      <c r="F24" t="s">
+        <v>144</v>
+      </c>
+      <c r="G24" t="s">
+        <v>27</v>
+      </c>
+      <c r="H24" t="s">
+        <v>60</v>
+      </c>
+      <c r="I24" t="s">
+        <v>286</v>
+      </c>
+      <c r="J24" t="s">
+        <v>287</v>
+      </c>
+      <c r="K24" t="s">
+        <v>288</v>
+      </c>
+      <c r="L24" t="s">
+        <v>289</v>
+      </c>
+      <c r="M24" t="s">
+        <v>290</v>
+      </c>
+      <c r="N24" t="s">
+        <v>291</v>
+      </c>
+      <c r="O24" t="s">
+        <v>292</v>
+      </c>
+      <c r="P24" t="s">
+        <v>293</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>168</v>
+      </c>
+      <c r="R24" t="s">
+        <v>242</v>
+      </c>
+      <c r="S24" t="s">
+        <v>243</v>
+      </c>
+      <c r="T24" t="s">
+        <v>244</v>
+      </c>
+      <c r="U24" t="s">
         <v>282</v>
-      </c>
-      <c r="C24" t="s">
-        <v>40</v>
-      </c>
-      <c r="D24" t="s">
-        <v>283</v>
-      </c>
-      <c r="E24" t="s">
-        <v>284</v>
-      </c>
-      <c r="F24" t="s">
-        <v>132</v>
-      </c>
-      <c r="G24" t="s">
-        <v>43</v>
-      </c>
-      <c r="H24" t="s">
-        <v>58</v>
-      </c>
-      <c r="I24" t="s">
-        <v>285</v>
-      </c>
-      <c r="J24" t="s">
-        <v>286</v>
-      </c>
-      <c r="K24" t="s">
-        <v>287</v>
-      </c>
-      <c r="L24" t="s">
-        <v>288</v>
-      </c>
-      <c r="M24" t="s">
-        <v>289</v>
-      </c>
-      <c r="N24" t="s">
-        <v>279</v>
-      </c>
-      <c r="O24" t="s">
-        <v>290</v>
-      </c>
-      <c r="P24" t="s">
-        <v>291</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>156</v>
-      </c>
-      <c r="R24" t="s">
-        <v>292</v>
-      </c>
-      <c r="S24" t="s">
-        <v>293</v>
-      </c>
-      <c r="T24" t="s">
-        <v>294</v>
-      </c>
-      <c r="U24" t="s">
-        <v>270</v>
       </c>
       <c r="V24"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>20263597</v>
+        <v>20263997</v>
       </c>
       <c r="B25" t="s">
+        <v>294</v>
+      </c>
+      <c r="C25" t="s">
+        <v>58</v>
+      </c>
+      <c r="D25" t="s">
         <v>295</v>
       </c>
-      <c r="C25" t="s">
+      <c r="E25" t="s">
         <v>296</v>
       </c>
-      <c r="D25" t="s">
-        <v>121</v>
-      </c>
-      <c r="E25" t="s">
-        <v>122</v>
-      </c>
       <c r="F25" t="s">
-        <v>297</v>
+        <v>144</v>
       </c>
       <c r="G25" t="s">
         <v>27</v>
@@ -7484,482 +7482,484 @@
         <v>72</v>
       </c>
       <c r="I25" t="s">
+        <v>297</v>
+      </c>
+      <c r="J25" t="s">
         <v>298</v>
       </c>
-      <c r="J25" t="s">
+      <c r="K25" t="s">
         <v>299</v>
       </c>
-      <c r="K25" t="s">
+      <c r="L25" t="s">
         <v>300</v>
       </c>
-      <c r="L25" t="s">
+      <c r="M25" t="s">
         <v>301</v>
       </c>
-      <c r="M25" t="s">
+      <c r="N25" t="s">
+        <v>291</v>
+      </c>
+      <c r="O25" t="s">
         <v>302</v>
       </c>
-      <c r="N25" t="s">
-        <v>50</v>
-      </c>
-      <c r="O25" t="s">
+      <c r="P25" t="s">
         <v>303</v>
       </c>
-      <c r="P25" t="s">
+      <c r="Q25" t="s">
+        <v>168</v>
+      </c>
+      <c r="R25" t="s">
         <v>304</v>
       </c>
-      <c r="Q25" t="s">
-        <v>53</v>
-      </c>
-      <c r="R25" t="s">
+      <c r="S25" t="s">
         <v>305</v>
       </c>
-      <c r="S25" t="s">
+      <c r="T25" t="s">
         <v>306</v>
       </c>
-      <c r="T25" t="s">
-        <v>307</v>
-      </c>
       <c r="U25" t="s">
-        <v>308</v>
+        <v>282</v>
       </c>
       <c r="V25"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>20263936</v>
+        <v>20263597</v>
       </c>
       <c r="B26" t="s">
+        <v>307</v>
+      </c>
+      <c r="C26" t="s">
+        <v>308</v>
+      </c>
+      <c r="D26" t="s">
+        <v>133</v>
+      </c>
+      <c r="E26" t="s">
+        <v>134</v>
+      </c>
+      <c r="F26" t="s">
         <v>309</v>
       </c>
-      <c r="C26" t="s">
-        <v>40</v>
-      </c>
-      <c r="D26" t="s">
+      <c r="G26" t="s">
+        <v>45</v>
+      </c>
+      <c r="H26" t="s">
+        <v>28</v>
+      </c>
+      <c r="I26" t="s">
         <v>310</v>
       </c>
-      <c r="E26" t="s">
-        <v>273</v>
-      </c>
-      <c r="F26" t="s">
-        <v>132</v>
-      </c>
-      <c r="G26" t="s">
-        <v>43</v>
-      </c>
-      <c r="H26" t="s">
-        <v>109</v>
-      </c>
-      <c r="I26" t="s">
+      <c r="J26" t="s">
         <v>311</v>
       </c>
-      <c r="J26" t="s">
+      <c r="K26" t="s">
         <v>312</v>
       </c>
-      <c r="K26" t="s">
+      <c r="L26" t="s">
         <v>313</v>
       </c>
-      <c r="L26" t="s">
+      <c r="M26" t="s">
         <v>314</v>
       </c>
-      <c r="M26" t="s">
+      <c r="N26" t="s">
+        <v>33</v>
+      </c>
+      <c r="O26" t="s">
         <v>315</v>
       </c>
-      <c r="N26" t="s">
-        <v>279</v>
-      </c>
-      <c r="O26" t="s">
+      <c r="P26" t="s">
         <v>316</v>
       </c>
-      <c r="P26" t="s">
+      <c r="Q26" t="s">
+        <v>36</v>
+      </c>
+      <c r="R26" t="s">
         <v>317</v>
       </c>
-      <c r="Q26" t="s">
+      <c r="S26" t="s">
         <v>318</v>
       </c>
-      <c r="R26" t="s">
+      <c r="T26" t="s">
         <v>319</v>
       </c>
-      <c r="S26" t="s">
+      <c r="U26" t="s">
         <v>320</v>
-      </c>
-      <c r="T26" t="s">
-        <v>321</v>
-      </c>
-      <c r="U26" t="s">
-        <v>322</v>
       </c>
       <c r="V26"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>20263949</v>
+        <v>20263936</v>
       </c>
       <c r="B27" t="s">
+        <v>321</v>
+      </c>
+      <c r="C27" t="s">
+        <v>58</v>
+      </c>
+      <c r="D27" t="s">
+        <v>322</v>
+      </c>
+      <c r="E27" t="s">
+        <v>285</v>
+      </c>
+      <c r="F27" t="s">
+        <v>144</v>
+      </c>
+      <c r="G27" t="s">
+        <v>27</v>
+      </c>
+      <c r="H27" t="s">
+        <v>121</v>
+      </c>
+      <c r="I27" t="s">
         <v>323</v>
       </c>
-      <c r="C27" t="s">
-        <v>40</v>
-      </c>
-      <c r="D27" t="s">
-        <v>310</v>
-      </c>
-      <c r="E27" t="s">
-        <v>273</v>
-      </c>
-      <c r="F27" t="s">
-        <v>132</v>
-      </c>
-      <c r="G27" t="s">
-        <v>43</v>
-      </c>
-      <c r="H27" t="s">
-        <v>109</v>
-      </c>
-      <c r="I27" t="s">
+      <c r="J27" t="s">
         <v>324</v>
       </c>
-      <c r="J27" t="s">
+      <c r="K27" t="s">
         <v>325</v>
       </c>
-      <c r="K27" t="s">
+      <c r="L27" t="s">
         <v>326</v>
       </c>
-      <c r="L27" t="s">
+      <c r="M27" t="s">
         <v>327</v>
       </c>
-      <c r="M27" t="s">
+      <c r="N27" t="s">
+        <v>291</v>
+      </c>
+      <c r="O27" t="s">
         <v>328</v>
       </c>
-      <c r="N27" t="s">
-        <v>279</v>
-      </c>
-      <c r="O27" t="s">
+      <c r="P27" t="s">
         <v>329</v>
       </c>
-      <c r="P27" t="s">
+      <c r="Q27" t="s">
         <v>330</v>
       </c>
-      <c r="Q27" t="s">
-        <v>318</v>
-      </c>
       <c r="R27" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
       <c r="S27" t="s">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="T27" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="U27" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="V27"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>20263601</v>
+        <v>20263949</v>
       </c>
       <c r="B28" t="s">
+        <v>335</v>
+      </c>
+      <c r="C28" t="s">
+        <v>58</v>
+      </c>
+      <c r="D28" t="s">
+        <v>322</v>
+      </c>
+      <c r="E28" t="s">
+        <v>285</v>
+      </c>
+      <c r="F28" t="s">
+        <v>144</v>
+      </c>
+      <c r="G28" t="s">
+        <v>27</v>
+      </c>
+      <c r="H28" t="s">
+        <v>121</v>
+      </c>
+      <c r="I28" t="s">
+        <v>336</v>
+      </c>
+      <c r="J28" t="s">
+        <v>337</v>
+      </c>
+      <c r="K28" t="s">
+        <v>338</v>
+      </c>
+      <c r="L28" t="s">
+        <v>339</v>
+      </c>
+      <c r="M28" t="s">
+        <v>340</v>
+      </c>
+      <c r="N28" t="s">
+        <v>291</v>
+      </c>
+      <c r="O28" t="s">
+        <v>341</v>
+      </c>
+      <c r="P28" t="s">
+        <v>342</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>330</v>
+      </c>
+      <c r="R28" t="s">
         <v>331</v>
       </c>
-      <c r="C28" t="s">
-        <v>40</v>
-      </c>
-      <c r="D28" t="s">
+      <c r="S28" t="s">
         <v>332</v>
       </c>
-      <c r="E28" t="s">
-        <v>273</v>
-      </c>
-      <c r="F28" t="s">
+      <c r="T28" t="s">
         <v>333</v>
       </c>
-      <c r="G28" t="s">
-        <v>43</v>
-      </c>
-      <c r="H28" t="s">
-        <v>44</v>
-      </c>
-      <c r="I28" t="s">
+      <c r="U28" t="s">
         <v>334</v>
-      </c>
-      <c r="J28" t="s">
-        <v>335</v>
-      </c>
-      <c r="K28" t="s">
-        <v>336</v>
-      </c>
-      <c r="L28" t="s">
-        <v>337</v>
-      </c>
-      <c r="M28" t="s">
-        <v>338</v>
-      </c>
-      <c r="N28" t="s">
-        <v>279</v>
-      </c>
-      <c r="O28" t="s">
-        <v>339</v>
-      </c>
-      <c r="P28" t="s">
-        <v>340</v>
-      </c>
-      <c r="Q28" t="s">
-        <v>156</v>
-      </c>
-      <c r="R28" t="s">
-        <v>341</v>
-      </c>
-      <c r="S28" t="s">
-        <v>342</v>
-      </c>
-      <c r="T28" t="s">
-        <v>343</v>
-      </c>
-      <c r="U28" t="s">
-        <v>344</v>
       </c>
       <c r="V28"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>20263411</v>
+        <v>20263601</v>
       </c>
       <c r="B29" t="s">
+        <v>343</v>
+      </c>
+      <c r="C29" t="s">
+        <v>58</v>
+      </c>
+      <c r="D29" t="s">
+        <v>344</v>
+      </c>
+      <c r="E29" t="s">
+        <v>285</v>
+      </c>
+      <c r="F29" t="s">
         <v>345</v>
-      </c>
-      <c r="C29" t="s">
-        <v>23</v>
-      </c>
-      <c r="D29" t="s">
-        <v>24</v>
-      </c>
-      <c r="E29" t="s">
-        <v>25</v>
-      </c>
-      <c r="F29" t="s">
-        <v>346</v>
       </c>
       <c r="G29" t="s">
         <v>27</v>
       </c>
       <c r="H29" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="I29" t="s">
+        <v>346</v>
+      </c>
+      <c r="J29" t="s">
         <v>347</v>
       </c>
-      <c r="J29" t="s">
+      <c r="K29" t="s">
         <v>348</v>
       </c>
-      <c r="K29" t="s">
+      <c r="L29" t="s">
         <v>349</v>
       </c>
-      <c r="L29" t="s">
+      <c r="M29" t="s">
         <v>350</v>
       </c>
-      <c r="M29" t="s">
+      <c r="N29" t="s">
+        <v>291</v>
+      </c>
+      <c r="O29" t="s">
         <v>351</v>
       </c>
-      <c r="N29" t="s">
-        <v>254</v>
-      </c>
-      <c r="O29" t="s">
+      <c r="P29" t="s">
         <v>352</v>
       </c>
-      <c r="P29" t="s">
+      <c r="Q29" t="s">
+        <v>168</v>
+      </c>
+      <c r="R29" t="s">
         <v>353</v>
       </c>
-      <c r="Q29" t="s">
-        <v>53</v>
-      </c>
-      <c r="R29" t="s">
+      <c r="S29" t="s">
         <v>354</v>
       </c>
-      <c r="S29" t="s">
+      <c r="T29" t="s">
         <v>355</v>
       </c>
-      <c r="T29" t="s">
+      <c r="U29" t="s">
         <v>356</v>
-      </c>
-      <c r="U29" t="s">
-        <v>357</v>
       </c>
       <c r="V29"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>20263323</v>
+        <v>20263411</v>
       </c>
       <c r="B30" t="s">
+        <v>357</v>
+      </c>
+      <c r="C30" t="s">
+        <v>42</v>
+      </c>
+      <c r="D30" t="s">
+        <v>43</v>
+      </c>
+      <c r="E30" t="s">
+        <v>25</v>
+      </c>
+      <c r="F30" t="s">
         <v>358</v>
       </c>
-      <c r="C30" t="s">
-        <v>40</v>
-      </c>
-      <c r="D30" t="s">
-        <v>310</v>
-      </c>
-      <c r="E30" t="s">
-        <v>273</v>
-      </c>
-      <c r="F30" t="s">
+      <c r="G30" t="s">
+        <v>45</v>
+      </c>
+      <c r="H30" t="s">
+        <v>72</v>
+      </c>
+      <c r="I30" t="s">
         <v>359</v>
       </c>
-      <c r="G30" t="s">
-        <v>43</v>
-      </c>
-      <c r="H30" t="s">
-        <v>109</v>
-      </c>
-      <c r="I30" t="s">
+      <c r="J30" t="s">
         <v>360</v>
       </c>
-      <c r="J30" t="s">
+      <c r="K30" t="s">
         <v>361</v>
       </c>
-      <c r="K30" t="s">
+      <c r="L30" t="s">
         <v>362</v>
       </c>
-      <c r="L30" t="s">
+      <c r="M30" t="s">
         <v>363</v>
       </c>
-      <c r="M30" t="s">
+      <c r="N30" t="s">
+        <v>266</v>
+      </c>
+      <c r="O30" t="s">
         <v>364</v>
       </c>
-      <c r="N30" t="s">
-        <v>50</v>
-      </c>
-      <c r="O30" t="s">
+      <c r="P30" t="s">
         <v>365</v>
       </c>
-      <c r="P30" t="s">
+      <c r="Q30" t="s">
+        <v>36</v>
+      </c>
+      <c r="R30" t="s">
         <v>366</v>
       </c>
-      <c r="Q30" t="s">
-        <v>318</v>
-      </c>
-      <c r="R30" t="s">
-        <v>319</v>
-      </c>
       <c r="S30" t="s">
-        <v>320</v>
+        <v>367</v>
       </c>
       <c r="T30" t="s">
-        <v>321</v>
+        <v>368</v>
       </c>
       <c r="U30" t="s">
-        <v>132</v>
+        <v>369</v>
       </c>
       <c r="V30"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>20263099</v>
+        <v>20263323</v>
       </c>
       <c r="B31" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="C31" t="s">
-        <v>296</v>
+        <v>58</v>
       </c>
       <c r="D31" t="s">
-        <v>121</v>
+        <v>322</v>
       </c>
       <c r="E31" t="s">
-        <v>122</v>
+        <v>285</v>
       </c>
       <c r="F31" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="G31" t="s">
         <v>27</v>
       </c>
       <c r="H31" t="s">
-        <v>72</v>
+        <v>121</v>
       </c>
       <c r="I31" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="J31" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="K31" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="L31" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="M31" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="N31" t="s">
-        <v>374</v>
+        <v>33</v>
       </c>
       <c r="O31" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="P31" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="Q31" t="s">
-        <v>53</v>
+        <v>330</v>
       </c>
       <c r="R31" t="s">
-        <v>377</v>
+        <v>331</v>
       </c>
       <c r="S31" t="s">
-        <v>378</v>
+        <v>332</v>
       </c>
       <c r="T31" t="s">
-        <v>379</v>
+        <v>333</v>
       </c>
       <c r="U31" t="s">
-        <v>380</v>
+        <v>144</v>
       </c>
       <c r="V31"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>20267473</v>
+        <v>20263099</v>
       </c>
       <c r="B32" t="s">
+        <v>379</v>
+      </c>
+      <c r="C32" t="s">
+        <v>308</v>
+      </c>
+      <c r="D32" t="s">
+        <v>133</v>
+      </c>
+      <c r="E32" t="s">
+        <v>134</v>
+      </c>
+      <c r="F32" t="s">
+        <v>380</v>
+      </c>
+      <c r="G32" t="s">
+        <v>45</v>
+      </c>
+      <c r="H32" t="s">
+        <v>28</v>
+      </c>
+      <c r="I32" t="s">
         <v>381</v>
       </c>
-      <c r="C32" t="s">
-        <v>107</v>
-      </c>
-      <c r="D32" t="s">
-        <v>41</v>
-      </c>
-      <c r="E32" t="s">
-        <v>25</v>
-      </c>
-      <c r="F32" t="s">
+      <c r="J32" t="s">
         <v>382</v>
       </c>
-      <c r="G32" t="s">
-        <v>43</v>
-      </c>
-      <c r="H32" t="s">
-        <v>72</v>
-      </c>
-      <c r="I32" t="s">
+      <c r="K32" t="s">
         <v>383</v>
       </c>
-      <c r="J32" t="s">
+      <c r="L32" t="s">
         <v>384</v>
       </c>
-      <c r="K32"/>
-      <c r="L32" t="s">
+      <c r="M32" t="s">
         <v>385</v>
       </c>
-      <c r="M32" t="s">
+      <c r="N32" t="s">
         <v>386</v>
-      </c>
-      <c r="N32" t="s">
-        <v>50</v>
       </c>
       <c r="O32" t="s">
         <v>387</v>
@@ -7968,7 +7968,7 @@
         <v>388</v>
       </c>
       <c r="Q32" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="R32" t="s">
         <v>389</v>
@@ -7982,9 +7982,7 @@
       <c r="U32" t="s">
         <v>392</v>
       </c>
-      <c r="V32" t="s">
-        <v>392</v>
-      </c>
+      <c r="V32"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -7994,10 +7992,10 @@
         <v>393</v>
       </c>
       <c r="C33" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D33" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="E33" t="s">
         <v>25</v>
@@ -8006,10 +8004,10 @@
         <v>394</v>
       </c>
       <c r="G33" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H33" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="I33" t="s">
         <v>395</v>
@@ -8025,7 +8023,7 @@
         <v>398</v>
       </c>
       <c r="N33" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="O33" t="s">
         <v>399</v>
@@ -8034,7 +8032,7 @@
         <v>400</v>
       </c>
       <c r="Q33" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="R33" t="s">
         <v>401</v>
@@ -8046,7 +8044,7 @@
         <v>403</v>
       </c>
       <c r="U33" t="s">
-        <v>382</v>
+        <v>26</v>
       </c>
       <c r="V33"/>
     </row>
@@ -8058,22 +8056,22 @@
         <v>404</v>
       </c>
       <c r="C34" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D34" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="E34" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="F34" t="s">
         <v>394</v>
       </c>
       <c r="G34" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H34" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="I34" t="s">
         <v>405</v>
@@ -8089,7 +8087,7 @@
         <v>408</v>
       </c>
       <c r="N34" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="O34" t="s">
         <v>409</v>
@@ -8098,7 +8096,7 @@
         <v>410</v>
       </c>
       <c r="Q34" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="R34" t="s">
         <v>411</v>
@@ -8110,7 +8108,7 @@
         <v>413</v>
       </c>
       <c r="U34" t="s">
-        <v>382</v>
+        <v>26</v>
       </c>
       <c r="V34"/>
     </row>
@@ -8122,7 +8120,7 @@
         <v>414</v>
       </c>
       <c r="C35" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="D35" t="s">
         <v>415</v>
@@ -8134,10 +8132,10 @@
         <v>416</v>
       </c>
       <c r="G35" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H35" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="I35" t="s">
         <v>417</v>
@@ -8155,7 +8153,7 @@
         <v>421</v>
       </c>
       <c r="N35" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="O35" t="s">
         <v>422</v>
@@ -8164,7 +8162,7 @@
         <v>423</v>
       </c>
       <c r="Q35" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="R35" t="s">
         <v>424</v>
@@ -8188,22 +8186,22 @@
         <v>428</v>
       </c>
       <c r="C36" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="D36" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="E36" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="F36" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="G36" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="H36" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="I36" t="s">
         <v>429</v>
@@ -8221,7 +8219,7 @@
         <v>433</v>
       </c>
       <c r="N36" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="O36" t="s">
         <v>434</v>
@@ -8230,7 +8228,7 @@
         <v>435</v>
       </c>
       <c r="Q36" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="R36" t="s">
         <v>436</v>
@@ -8254,22 +8252,22 @@
         <v>439</v>
       </c>
       <c r="C37" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D37" t="s">
         <v>440</v>
       </c>
       <c r="E37" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="F37" t="s">
-        <v>346</v>
+        <v>358</v>
       </c>
       <c r="G37" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H37" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="I37" t="s">
         <v>441</v>
@@ -8287,7 +8285,7 @@
         <v>445</v>
       </c>
       <c r="N37" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="O37" t="s">
         <v>446</v>
@@ -8296,7 +8294,7 @@
         <v>447</v>
       </c>
       <c r="Q37" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="R37" t="s">
         <v>448</v>
@@ -8320,7 +8318,7 @@
         <v>452</v>
       </c>
       <c r="C38" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="D38" t="s">
         <v>453</v>
@@ -8329,13 +8327,13 @@
         <v>25</v>
       </c>
       <c r="F38" t="s">
-        <v>359</v>
+        <v>371</v>
       </c>
       <c r="G38" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H38" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="I38" t="s">
         <v>454</v>
@@ -8353,7 +8351,7 @@
         <v>458</v>
       </c>
       <c r="N38" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="O38" t="s">
         <v>459</v>
@@ -8362,7 +8360,7 @@
         <v>460</v>
       </c>
       <c r="Q38" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="R38" t="s">
         <v>436</v>
@@ -8386,20 +8384,20 @@
         <v>461</v>
       </c>
       <c r="C39" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D39" t="s">
         <v>462</v>
       </c>
       <c r="E39"/>
       <c r="F39" t="s">
-        <v>346</v>
+        <v>358</v>
       </c>
       <c r="G39" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H39" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="I39" t="s">
         <v>463</v>
@@ -8417,7 +8415,7 @@
         <v>467</v>
       </c>
       <c r="N39" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="O39" t="s">
         <v>468</v>
@@ -8426,7 +8424,7 @@
         <v>469</v>
       </c>
       <c r="Q39" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="R39" t="s">
         <v>470</v>
@@ -8450,22 +8448,22 @@
         <v>474</v>
       </c>
       <c r="C40" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="D40" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="E40" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="F40" t="s">
-        <v>346</v>
+        <v>358</v>
       </c>
       <c r="G40" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H40" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="I40" t="s">
         <v>475</v>
@@ -8483,7 +8481,7 @@
         <v>479</v>
       </c>
       <c r="N40" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="O40" t="s">
         <v>480</v>
@@ -8492,16 +8490,16 @@
         <v>481</v>
       </c>
       <c r="Q40" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="R40" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="S40" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="T40" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="U40" t="s">
         <v>473</v>
@@ -8516,19 +8514,19 @@
         <v>482</v>
       </c>
       <c r="C41" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="D41" t="s">
         <v>483</v>
       </c>
       <c r="E41" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="F41" t="s">
         <v>484</v>
       </c>
       <c r="G41" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H41" t="s">
         <v>485</v>
@@ -8549,7 +8547,7 @@
         <v>490</v>
       </c>
       <c r="N41" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="O41" t="s">
         <v>491</v>
@@ -8558,7 +8556,7 @@
         <v>492</v>
       </c>
       <c r="Q41" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="R41" t="s">
         <v>493</v>
@@ -8582,22 +8580,22 @@
         <v>496</v>
       </c>
       <c r="C42" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D42" t="s">
         <v>497</v>
       </c>
       <c r="E42" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="F42" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="G42" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H42" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="I42" t="s">
         <v>498</v>
@@ -8615,7 +8613,7 @@
         <v>502</v>
       </c>
       <c r="N42" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="O42" t="s">
         <v>503</v>
@@ -8624,7 +8622,7 @@
         <v>504</v>
       </c>
       <c r="Q42" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="R42" t="s">
         <v>505</v>
@@ -8648,22 +8646,22 @@
         <v>509</v>
       </c>
       <c r="C43" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="D43" t="s">
         <v>510</v>
       </c>
       <c r="E43" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="F43" t="s">
         <v>511</v>
       </c>
       <c r="G43" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H43" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="I43" t="s">
         <v>512</v>
@@ -8681,7 +8679,7 @@
         <v>516</v>
       </c>
       <c r="N43" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="O43" t="s">
         <v>517</v>
@@ -8690,16 +8688,16 @@
         <v>518</v>
       </c>
       <c r="Q43" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="R43" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="S43" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="T43" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="U43" t="s">
         <v>508</v>
@@ -8714,22 +8712,22 @@
         <v>519</v>
       </c>
       <c r="C44" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D44" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="E44" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="F44" t="s">
         <v>520</v>
       </c>
       <c r="G44" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="H44" t="s">
-        <v>72</v>
+        <v>28</v>
       </c>
       <c r="I44" t="s">
         <v>521</v>
@@ -8747,7 +8745,7 @@
         <v>525</v>
       </c>
       <c r="N44" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="O44" t="s">
         <v>526</v>
@@ -8756,16 +8754,16 @@
         <v>527</v>
       </c>
       <c r="Q44" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="R44" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="S44" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="T44" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="U44" t="s">
         <v>528</v>
@@ -8780,7 +8778,7 @@
         <v>529</v>
       </c>
       <c r="C45" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D45" t="s">
         <v>415</v>
@@ -8792,10 +8790,10 @@
         <v>530</v>
       </c>
       <c r="G45" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H45" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="I45" t="s">
         <v>531</v>
@@ -8811,7 +8809,7 @@
         <v>534</v>
       </c>
       <c r="N45" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="O45" t="s">
         <v>535</v>
@@ -8820,7 +8818,7 @@
         <v>536</v>
       </c>
       <c r="Q45" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="R45" t="s">
         <v>537</v>
@@ -8844,7 +8842,7 @@
         <v>541</v>
       </c>
       <c r="C46" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D46" t="s">
         <v>542</v>
@@ -8856,10 +8854,10 @@
         <v>511</v>
       </c>
       <c r="G46" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H46" t="s">
-        <v>72</v>
+        <v>28</v>
       </c>
       <c r="I46" t="s">
         <v>544</v>
@@ -8875,7 +8873,7 @@
         <v>547</v>
       </c>
       <c r="N46" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="O46" t="s">
         <v>548</v>
@@ -8884,7 +8882,7 @@
         <v>549</v>
       </c>
       <c r="Q46" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="R46" t="s">
         <v>550</v>
@@ -8912,14 +8910,14 @@
       </c>
       <c r="D47"/>
       <c r="E47" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="F47" t="s">
         <v>555</v>
       </c>
       <c r="G47"/>
       <c r="H47" t="s">
-        <v>72</v>
+        <v>28</v>
       </c>
       <c r="I47" t="s">
         <v>556</v>
@@ -8933,7 +8931,7 @@
       <c r="L47"/>
       <c r="M47"/>
       <c r="N47" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="O47" t="s">
         <v>559</v>
@@ -8942,7 +8940,7 @@
         <v>560</v>
       </c>
       <c r="Q47" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="R47" t="s">
         <v>493</v>
@@ -8966,22 +8964,22 @@
         <v>561</v>
       </c>
       <c r="C48" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D48" t="s">
         <v>440</v>
       </c>
       <c r="E48" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="F48" t="s">
         <v>562</v>
       </c>
       <c r="G48" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H48" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="I48" t="s">
         <v>563</v>
@@ -8997,7 +8995,7 @@
         <v>566</v>
       </c>
       <c r="N48" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="O48" t="s">
         <v>567</v>
@@ -9006,7 +9004,7 @@
         <v>568</v>
       </c>
       <c r="Q48" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="R48" t="s">
         <v>569</v>
@@ -9030,22 +9028,22 @@
         <v>572</v>
       </c>
       <c r="C49" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D49" t="s">
         <v>573</v>
       </c>
       <c r="E49" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="F49" t="s">
         <v>574</v>
       </c>
       <c r="G49" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H49" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="I49" t="s">
         <v>575</v>
@@ -9063,7 +9061,7 @@
         <v>579</v>
       </c>
       <c r="N49" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="O49" t="s">
         <v>580</v>
@@ -9072,16 +9070,16 @@
         <v>581</v>
       </c>
       <c r="Q49" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="R49" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="S49" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="T49" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="U49" t="s">
         <v>540</v>
@@ -9096,7 +9094,7 @@
         <v>582</v>
       </c>
       <c r="C50" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="D50" t="s">
         <v>583</v>
@@ -9108,10 +9106,10 @@
         <v>520</v>
       </c>
       <c r="G50" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H50" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="I50" t="s">
         <v>585</v>
@@ -9129,7 +9127,7 @@
         <v>589</v>
       </c>
       <c r="N50" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="O50" t="s">
         <v>590</v>
@@ -9138,7 +9136,7 @@
         <v>591</v>
       </c>
       <c r="Q50" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="R50" t="s">
         <v>592</v>
@@ -9162,22 +9160,22 @@
         <v>595</v>
       </c>
       <c r="C51" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="D51" t="s">
         <v>596</v>
       </c>
       <c r="E51" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="F51" t="s">
         <v>520</v>
       </c>
       <c r="G51" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H51" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="I51" t="s">
         <v>597</v>
@@ -9195,7 +9193,7 @@
         <v>601</v>
       </c>
       <c r="N51" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="O51" t="s">
         <v>602</v>
@@ -9204,7 +9202,7 @@
         <v>603</v>
       </c>
       <c r="Q51" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="R51" t="s">
         <v>604</v>
@@ -9228,22 +9226,22 @@
         <v>607</v>
       </c>
       <c r="C52" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D52" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="E52" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="F52" t="s">
         <v>608</v>
       </c>
       <c r="G52" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="H52" t="s">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="I52" t="s">
         <v>609</v>
@@ -9261,7 +9259,7 @@
         <v>613</v>
       </c>
       <c r="N52" t="s">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="O52" t="s">
         <v>614</v>
@@ -9270,7 +9268,7 @@
         <v>615</v>
       </c>
       <c r="Q52" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="R52" t="s">
         <v>616</v>
@@ -9294,22 +9292,22 @@
         <v>619</v>
       </c>
       <c r="C53" t="s">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="D53" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="E53" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="F53" t="s">
         <v>608</v>
       </c>
       <c r="G53" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="H53" t="s">
-        <v>72</v>
+        <v>28</v>
       </c>
       <c r="I53" t="s">
         <v>620</v>
@@ -9327,7 +9325,7 @@
         <v>624</v>
       </c>
       <c r="N53" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="O53" t="s">
         <v>625</v>
@@ -9336,7 +9334,7 @@
         <v>626</v>
       </c>
       <c r="Q53" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="R53" t="s">
         <v>627</v>
@@ -9360,22 +9358,22 @@
         <v>630</v>
       </c>
       <c r="C54" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="D54" t="s">
         <v>631</v>
       </c>
       <c r="E54" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="F54" t="s">
         <v>632</v>
       </c>
       <c r="G54" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="H54" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="I54" t="s">
         <v>633</v>
@@ -9393,7 +9391,7 @@
         <v>637</v>
       </c>
       <c r="N54" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="O54" t="s">
         <v>638</v>
@@ -9402,7 +9400,7 @@
         <v>639</v>
       </c>
       <c r="Q54" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="R54" t="s">
         <v>640</v>
@@ -9426,22 +9424,22 @@
         <v>643</v>
       </c>
       <c r="C55" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D55" t="s">
         <v>497</v>
       </c>
       <c r="E55" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="F55" t="s">
         <v>416</v>
       </c>
       <c r="G55" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H55" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="I55" t="s">
         <v>644</v>
@@ -9459,7 +9457,7 @@
         <v>648</v>
       </c>
       <c r="N55" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="O55" t="s">
         <v>649</v>
@@ -9468,16 +9466,16 @@
         <v>650</v>
       </c>
       <c r="Q55" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="R55" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="S55" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="T55" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="U55" t="s">
         <v>540</v>
@@ -9492,7 +9490,7 @@
         <v>651</v>
       </c>
       <c r="C56" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D56" t="s">
         <v>652</v>
@@ -9504,10 +9502,10 @@
         <v>653</v>
       </c>
       <c r="G56" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H56" t="s">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="I56" t="s">
         <v>654</v>
@@ -9523,7 +9521,7 @@
         <v>657</v>
       </c>
       <c r="N56" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="O56" t="s">
         <v>658</v>
@@ -9532,7 +9530,7 @@
         <v>659</v>
       </c>
       <c r="Q56" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="R56" t="s">
         <v>660</v>
@@ -9556,22 +9554,22 @@
         <v>663</v>
       </c>
       <c r="C57" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D57" t="s">
         <v>483</v>
       </c>
       <c r="E57" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="F57" t="s">
         <v>653</v>
       </c>
       <c r="G57" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H57" t="s">
-        <v>72</v>
+        <v>28</v>
       </c>
       <c r="I57" t="s">
         <v>664</v>
@@ -9587,7 +9585,7 @@
         <v>667</v>
       </c>
       <c r="N57" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="O57" t="s">
         <v>668</v>
@@ -9596,16 +9594,16 @@
         <v>669</v>
       </c>
       <c r="Q57" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="R57" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="S57" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="T57" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="U57" t="s">
         <v>540</v>
@@ -9620,7 +9618,7 @@
         <v>670</v>
       </c>
       <c r="C58" t="s">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="D58" t="s">
         <v>671</v>
@@ -9630,10 +9628,10 @@
         <v>672</v>
       </c>
       <c r="G58" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H58" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="I58" t="s">
         <v>673</v>
@@ -9651,7 +9649,7 @@
         <v>677</v>
       </c>
       <c r="N58" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="O58" t="s">
         <v>678</v>
@@ -9660,7 +9658,7 @@
         <v>679</v>
       </c>
       <c r="Q58" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="R58" t="s">
         <v>680</v>
@@ -9684,22 +9682,22 @@
         <v>683</v>
       </c>
       <c r="C59" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D59" t="s">
         <v>684</v>
       </c>
       <c r="E59" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="F59" t="s">
         <v>685</v>
       </c>
       <c r="G59" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="H59" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="I59" t="s">
         <v>686</v>
@@ -9717,7 +9715,7 @@
         <v>690</v>
       </c>
       <c r="N59" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="O59" t="s">
         <v>691</v>
@@ -9726,7 +9724,7 @@
         <v>692</v>
       </c>
       <c r="Q59" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="R59" t="s">
         <v>693</v>
@@ -9750,22 +9748,22 @@
         <v>696</v>
       </c>
       <c r="C60" t="s">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="D60" t="s">
         <v>697</v>
       </c>
       <c r="E60" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="F60" t="s">
         <v>685</v>
       </c>
       <c r="G60" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H60" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="I60" t="s">
         <v>698</v>
@@ -9783,7 +9781,7 @@
         <v>702</v>
       </c>
       <c r="N60" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="O60" t="s">
         <v>703</v>
@@ -9792,7 +9790,7 @@
         <v>704</v>
       </c>
       <c r="Q60" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="R60" t="s">
         <v>493</v>
@@ -9816,7 +9814,7 @@
         <v>705</v>
       </c>
       <c r="C61" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="D61" t="s">
         <v>453</v>
@@ -9828,10 +9826,10 @@
         <v>685</v>
       </c>
       <c r="G61" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H61" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="I61" t="s">
         <v>706</v>
@@ -9849,7 +9847,7 @@
         <v>710</v>
       </c>
       <c r="N61" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="O61" t="s">
         <v>711</v>
@@ -9858,16 +9856,16 @@
         <v>712</v>
       </c>
       <c r="Q61" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="R61" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="S61" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="T61" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="U61" t="s">
         <v>540</v>
@@ -9882,10 +9880,10 @@
         <v>713</v>
       </c>
       <c r="C62" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D62" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="E62" t="s">
         <v>25</v>
@@ -9894,10 +9892,10 @@
         <v>685</v>
       </c>
       <c r="G62" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="H62" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="I62" t="s">
         <v>714</v>
@@ -9915,7 +9913,7 @@
         <v>718</v>
       </c>
       <c r="N62" t="s">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="O62" t="s">
         <v>719</v>
@@ -9924,7 +9922,7 @@
         <v>720</v>
       </c>
       <c r="Q62" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="R62" t="s">
         <v>721</v>
@@ -9948,22 +9946,22 @@
         <v>724</v>
       </c>
       <c r="C63" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="D63" t="s">
         <v>725</v>
       </c>
       <c r="E63" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="F63" t="s">
         <v>726</v>
       </c>
       <c r="G63" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H63" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="I63" t="s">
         <v>727</v>
@@ -9981,7 +9979,7 @@
         <v>731</v>
       </c>
       <c r="N63" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="O63" t="s">
         <v>732</v>
@@ -9990,7 +9988,7 @@
         <v>733</v>
       </c>
       <c r="Q63" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="R63" t="s">
         <v>592</v>
@@ -10014,22 +10012,22 @@
         <v>734</v>
       </c>
       <c r="C64" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="D64" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="E64" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="F64" t="s">
         <v>735</v>
       </c>
       <c r="G64" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="H64" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="I64" t="s">
         <v>736</v>
@@ -10047,7 +10045,7 @@
         <v>740</v>
       </c>
       <c r="N64" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="O64" t="s">
         <v>741</v>
@@ -10056,7 +10054,7 @@
         <v>742</v>
       </c>
       <c r="Q64" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="R64" t="s">
         <v>743</v>
@@ -10080,22 +10078,22 @@
         <v>746</v>
       </c>
       <c r="C65" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="D65" t="s">
         <v>747</v>
       </c>
       <c r="E65" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="F65" t="s">
         <v>735</v>
       </c>
       <c r="G65" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H65" t="s">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="I65" t="s">
         <v>748</v>
@@ -10113,7 +10111,7 @@
         <v>752</v>
       </c>
       <c r="N65" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="O65" t="s">
         <v>753</v>
@@ -10122,7 +10120,7 @@
         <v>754</v>
       </c>
       <c r="Q65" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="R65" t="s">
         <v>755</v>
@@ -10146,22 +10144,22 @@
         <v>758</v>
       </c>
       <c r="C66" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="D66" t="s">
         <v>759</v>
       </c>
       <c r="E66" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="F66" t="s">
         <v>760</v>
       </c>
       <c r="G66" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="H66" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="I66" t="s">
         <v>761</v>
@@ -10179,7 +10177,7 @@
         <v>765</v>
       </c>
       <c r="N66" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="O66" t="s">
         <v>766</v>
@@ -10188,7 +10186,7 @@
         <v>767</v>
       </c>
       <c r="Q66" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="R66" t="s">
         <v>768</v>
@@ -10215,19 +10213,19 @@
         <v>772</v>
       </c>
       <c r="D67" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="E67" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="F67" t="s">
         <v>773</v>
       </c>
       <c r="G67" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H67" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="I67" t="s">
         <v>774</v>
@@ -10254,7 +10252,7 @@
         <v>781</v>
       </c>
       <c r="Q67" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="R67" t="s">
         <v>782</v>
@@ -10278,7 +10276,7 @@
         <v>785</v>
       </c>
       <c r="C68" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D68" t="s">
         <v>786</v>
@@ -10290,10 +10288,10 @@
         <v>787</v>
       </c>
       <c r="G68" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H68" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="I68" t="s">
         <v>788</v>
@@ -10311,7 +10309,7 @@
         <v>792</v>
       </c>
       <c r="N68" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="O68" t="s">
         <v>793</v>
@@ -10320,16 +10318,16 @@
         <v>794</v>
       </c>
       <c r="Q68" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="R68" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="S68" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="T68" t="s">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="U68" t="s">
         <v>540</v>
@@ -10344,22 +10342,22 @@
         <v>795</v>
       </c>
       <c r="C69" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D69" t="s">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="E69" t="s">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="F69" t="s">
         <v>787</v>
       </c>
       <c r="G69" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H69" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="I69" t="s">
         <v>796</v>
@@ -10375,7 +10373,7 @@
         <v>799</v>
       </c>
       <c r="N69" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="O69" t="s">
         <v>800</v>
@@ -10384,7 +10382,7 @@
         <v>801</v>
       </c>
       <c r="Q69" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="R69" t="s">
         <v>592</v>
@@ -10408,22 +10406,22 @@
         <v>802</v>
       </c>
       <c r="C70" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D70" t="s">
         <v>803</v>
       </c>
       <c r="E70" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="F70" t="s">
         <v>787</v>
       </c>
       <c r="G70" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H70" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="I70" t="s">
         <v>804</v>
@@ -10439,7 +10437,7 @@
         <v>807</v>
       </c>
       <c r="N70" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="O70" t="s">
         <v>808</v>
@@ -10448,7 +10446,7 @@
         <v>809</v>
       </c>
       <c r="Q70" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="R70" t="s">
         <v>810</v>
@@ -10472,22 +10470,22 @@
         <v>813</v>
       </c>
       <c r="C71" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D71" t="s">
         <v>747</v>
       </c>
       <c r="E71" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="F71" t="s">
         <v>814</v>
       </c>
       <c r="G71" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H71" t="s">
-        <v>72</v>
+        <v>28</v>
       </c>
       <c r="I71" t="s">
         <v>815</v>
@@ -10503,7 +10501,7 @@
         <v>818</v>
       </c>
       <c r="N71" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="O71" t="s">
         <v>819</v>
@@ -10512,7 +10510,7 @@
         <v>820</v>
       </c>
       <c r="Q71" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="R71" t="s">
         <v>821</v>
@@ -10536,22 +10534,22 @@
         <v>824</v>
       </c>
       <c r="C72" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="D72" t="s">
         <v>825</v>
       </c>
       <c r="E72" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="F72" t="s">
         <v>826</v>
       </c>
       <c r="G72" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H72" t="s">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="I72" t="s">
         <v>827</v>
@@ -10569,7 +10567,7 @@
         <v>831</v>
       </c>
       <c r="N72" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="O72" t="s">
         <v>832</v>
@@ -10578,7 +10576,7 @@
         <v>833</v>
       </c>
       <c r="Q72" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="R72" t="s">
         <v>834</v>
@@ -10602,22 +10600,22 @@
         <v>837</v>
       </c>
       <c r="C73" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D73" t="s">
         <v>825</v>
       </c>
       <c r="E73" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="F73" t="s">
         <v>826</v>
       </c>
       <c r="G73" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H73" t="s">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="I73" t="s">
         <v>838</v>
@@ -10633,7 +10631,7 @@
         <v>841</v>
       </c>
       <c r="N73" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="O73" t="s">
         <v>842</v>
@@ -10642,7 +10640,7 @@
         <v>843</v>
       </c>
       <c r="Q73" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="R73" t="s">
         <v>844</v>
@@ -10666,7 +10664,7 @@
         <v>847</v>
       </c>
       <c r="C74" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="D74" t="s">
         <v>848</v>
@@ -10677,7 +10675,7 @@
       </c>
       <c r="G74"/>
       <c r="H74" t="s">
-        <v>72</v>
+        <v>28</v>
       </c>
       <c r="I74" t="s">
         <v>850</v>
@@ -10695,7 +10693,7 @@
         <v>854</v>
       </c>
       <c r="N74" t="s">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="O74" t="s">
         <v>855</v>
@@ -10704,7 +10702,7 @@
         <v>856</v>
       </c>
       <c r="Q74" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="R74"/>
       <c r="S74"/>
@@ -10722,7 +10720,7 @@
         <v>857</v>
       </c>
       <c r="C75" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="D75" t="s">
         <v>858</v>
@@ -10734,10 +10732,10 @@
         <v>859</v>
       </c>
       <c r="G75" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H75" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="I75" t="s">
         <v>860</v>
@@ -10755,7 +10753,7 @@
         <v>864</v>
       </c>
       <c r="N75" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="O75" t="s">
         <v>865</v>
@@ -10764,7 +10762,7 @@
         <v>866</v>
       </c>
       <c r="Q75" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="R75" t="s">
         <v>867</v>
@@ -10788,7 +10786,7 @@
         <v>870</v>
       </c>
       <c r="C76" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="D76" t="s">
         <v>871</v>
@@ -10800,10 +10798,10 @@
         <v>859</v>
       </c>
       <c r="G76" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H76" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="I76" t="s">
         <v>872</v>
@@ -10821,7 +10819,7 @@
         <v>876</v>
       </c>
       <c r="N76" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="O76" t="s">
         <v>877</v>
@@ -10830,7 +10828,7 @@
         <v>878</v>
       </c>
       <c r="Q76" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="R76" t="s">
         <v>879</v>
@@ -10854,22 +10852,22 @@
         <v>882</v>
       </c>
       <c r="C77" t="s">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="D77" t="s">
         <v>883</v>
       </c>
       <c r="E77" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="F77" t="s">
         <v>859</v>
       </c>
       <c r="G77" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H77" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="I77" t="s">
         <v>884</v>
@@ -10896,7 +10894,7 @@
         <v>891</v>
       </c>
       <c r="Q77" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="R77" t="s">
         <v>892</v>
@@ -10920,7 +10918,7 @@
         <v>895</v>
       </c>
       <c r="C78" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D78" t="s">
         <v>462</v>
@@ -10930,10 +10928,10 @@
         <v>896</v>
       </c>
       <c r="G78" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H78" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="I78" t="s">
         <v>897</v>
@@ -10951,7 +10949,7 @@
         <v>901</v>
       </c>
       <c r="N78" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="O78" t="s">
         <v>902</v>
@@ -10960,16 +10958,16 @@
         <v>903</v>
       </c>
       <c r="Q78" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="R78" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="S78" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="T78" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="U78" t="s">
         <v>540</v>
@@ -10984,7 +10982,7 @@
         <v>904</v>
       </c>
       <c r="C79" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="D79" t="s">
         <v>905</v>
@@ -10996,10 +10994,10 @@
         <v>896</v>
       </c>
       <c r="G79" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H79" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="I79" t="s">
         <v>906</v>
@@ -11017,7 +11015,7 @@
         <v>910</v>
       </c>
       <c r="N79" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="O79" t="s">
         <v>911</v>
@@ -11026,7 +11024,7 @@
         <v>912</v>
       </c>
       <c r="Q79" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="R79" t="s">
         <v>913</v>
@@ -11050,7 +11048,7 @@
         <v>916</v>
       </c>
       <c r="C80" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="D80" t="s">
         <v>917</v>
@@ -11062,10 +11060,10 @@
         <v>918</v>
       </c>
       <c r="G80" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H80" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="I80" t="s">
         <v>919</v>
@@ -11083,7 +11081,7 @@
         <v>923</v>
       </c>
       <c r="N80" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="O80" t="s">
         <v>924</v>
@@ -11092,16 +11090,16 @@
         <v>925</v>
       </c>
       <c r="Q80" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="R80" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="S80" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="T80" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="U80" t="s">
         <v>540</v>
@@ -11116,7 +11114,7 @@
         <v>926</v>
       </c>
       <c r="C81" t="s">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="D81" t="s">
         <v>927</v>
@@ -11126,10 +11124,10 @@
         <v>918</v>
       </c>
       <c r="G81" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H81" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="I81" t="s">
         <v>928</v>
@@ -11147,7 +11145,7 @@
         <v>932</v>
       </c>
       <c r="N81" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="O81" t="s">
         <v>933</v>
@@ -11156,7 +11154,7 @@
         <v>934</v>
       </c>
       <c r="Q81" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="R81" t="s">
         <v>935</v>
@@ -11180,22 +11178,22 @@
         <v>938</v>
       </c>
       <c r="C82" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="D82" t="s">
         <v>697</v>
       </c>
       <c r="E82" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="F82" t="s">
         <v>918</v>
       </c>
       <c r="G82" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H82" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="I82" t="s">
         <v>939</v>
@@ -11213,7 +11211,7 @@
         <v>943</v>
       </c>
       <c r="N82" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="O82" t="s">
         <v>944</v>
@@ -11222,7 +11220,7 @@
         <v>945</v>
       </c>
       <c r="Q82" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="R82" t="s">
         <v>946</v>
@@ -11246,7 +11244,7 @@
         <v>949</v>
       </c>
       <c r="C83" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="D83" t="s">
         <v>950</v>
@@ -11258,10 +11256,10 @@
         <v>951</v>
       </c>
       <c r="G83" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="H83" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="I83" t="s">
         <v>952</v>
@@ -11279,7 +11277,7 @@
         <v>956</v>
       </c>
       <c r="N83" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="O83" t="s">
         <v>957</v>
@@ -11288,7 +11286,7 @@
         <v>958</v>
       </c>
       <c r="Q83" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="R83" t="s">
         <v>867</v>
@@ -11312,22 +11310,22 @@
         <v>959</v>
       </c>
       <c r="C84" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D84" t="s">
         <v>960</v>
       </c>
       <c r="E84" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="F84" t="s">
         <v>961</v>
       </c>
       <c r="G84" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H84" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="I84" t="s">
         <v>962</v>
@@ -11345,7 +11343,7 @@
         <v>966</v>
       </c>
       <c r="N84" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="O84" t="s">
         <v>967</v>
@@ -11354,7 +11352,7 @@
         <v>968</v>
       </c>
       <c r="Q84" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="R84" t="s">
         <v>436</v>
@@ -11378,7 +11376,7 @@
         <v>969</v>
       </c>
       <c r="C85" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D85" t="s">
         <v>970</v>
@@ -11390,10 +11388,10 @@
         <v>972</v>
       </c>
       <c r="G85" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H85" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="I85" t="s">
         <v>973</v>
@@ -11411,7 +11409,7 @@
         <v>977</v>
       </c>
       <c r="N85" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="O85" t="s">
         <v>978</v>
@@ -11420,7 +11418,7 @@
         <v>979</v>
       </c>
       <c r="Q85" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="R85" t="s">
         <v>980</v>
@@ -11444,22 +11442,22 @@
         <v>983</v>
       </c>
       <c r="C86" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D86" t="s">
         <v>747</v>
       </c>
       <c r="E86" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="F86" t="s">
         <v>972</v>
       </c>
       <c r="G86" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H86" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="I86" t="s">
         <v>984</v>
@@ -11477,7 +11475,7 @@
         <v>988</v>
       </c>
       <c r="N86" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="O86" t="s">
         <v>989</v>
@@ -11486,7 +11484,7 @@
         <v>990</v>
       </c>
       <c r="Q86" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="R86" t="s">
         <v>991</v>
@@ -11510,7 +11508,7 @@
         <v>994</v>
       </c>
       <c r="C87" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D87" t="s">
         <v>995</v>
@@ -11520,10 +11518,10 @@
         <v>996</v>
       </c>
       <c r="G87" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H87" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="I87" t="s">
         <v>997</v>
@@ -11550,7 +11548,7 @@
         <v>1003</v>
       </c>
       <c r="Q87" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="R87" t="s">
         <v>991</v>
@@ -11574,19 +11572,19 @@
         <v>1004</v>
       </c>
       <c r="C88" t="s">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="D88" t="s">
         <v>1005</v>
       </c>
       <c r="E88" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="F88" t="s">
         <v>1006</v>
       </c>
       <c r="G88" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H88" t="s">
         <v>1007</v>
@@ -11607,7 +11605,7 @@
         <v>1012</v>
       </c>
       <c r="N88" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="O88" t="s">
         <v>1013</v>
@@ -11616,7 +11614,7 @@
         <v>1014</v>
       </c>
       <c r="Q88" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="R88" t="s">
         <v>1015</v>
@@ -11640,22 +11638,22 @@
         <v>1018</v>
       </c>
       <c r="C89" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="D89" t="s">
         <v>1019</v>
       </c>
       <c r="E89" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="F89" t="s">
         <v>1006</v>
       </c>
       <c r="G89" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H89" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="I89" t="s">
         <v>1020</v>
@@ -11673,7 +11671,7 @@
         <v>1024</v>
       </c>
       <c r="N89" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="O89" t="s">
         <v>1025</v>
@@ -11682,7 +11680,7 @@
         <v>1026</v>
       </c>
       <c r="Q89" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="R89" t="s">
         <v>1027</v>
@@ -11706,22 +11704,22 @@
         <v>1030</v>
       </c>
       <c r="C90" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="D90" t="s">
         <v>1031</v>
       </c>
       <c r="E90" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="F90" t="s">
         <v>1006</v>
       </c>
       <c r="G90" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H90" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="I90" t="s">
         <v>1032</v>
@@ -11739,7 +11737,7 @@
         <v>1036</v>
       </c>
       <c r="N90" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="O90" t="s">
         <v>1037</v>
@@ -11748,16 +11746,16 @@
         <v>1038</v>
       </c>
       <c r="Q90" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="R90" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="S90" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="T90" t="s">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="U90" t="s">
         <v>540</v>
@@ -11772,22 +11770,22 @@
         <v>1039</v>
       </c>
       <c r="C91" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D91" t="s">
         <v>1040</v>
       </c>
       <c r="E91" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="F91" t="s">
         <v>1041</v>
       </c>
       <c r="G91" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="H91" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="I91" t="s">
         <v>1042</v>
@@ -11805,7 +11803,7 @@
         <v>1046</v>
       </c>
       <c r="N91" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="O91" t="s">
         <v>1047</v>
@@ -11814,7 +11812,7 @@
         <v>1048</v>
       </c>
       <c r="Q91" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="R91" t="s">
         <v>1049</v>
@@ -11838,22 +11836,22 @@
         <v>1052</v>
       </c>
       <c r="C92" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D92" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="E92" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="F92" t="s">
         <v>1041</v>
       </c>
       <c r="G92" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="H92" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="I92" t="s">
         <v>1053</v>
@@ -11871,7 +11869,7 @@
         <v>1057</v>
       </c>
       <c r="N92" t="s">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="O92" t="s">
         <v>1058</v>
@@ -11880,7 +11878,7 @@
         <v>1059</v>
       </c>
       <c r="Q92" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="R92" t="s">
         <v>991</v>
@@ -11904,22 +11902,22 @@
         <v>1060</v>
       </c>
       <c r="C93" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="D93" t="s">
         <v>631</v>
       </c>
       <c r="E93" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="F93" t="s">
         <v>1061</v>
       </c>
       <c r="G93" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="H93" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="I93" t="s">
         <v>1062</v>
@@ -11937,7 +11935,7 @@
         <v>1066</v>
       </c>
       <c r="N93" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="O93" t="s">
         <v>1067</v>
@@ -11946,7 +11944,7 @@
         <v>1068</v>
       </c>
       <c r="Q93" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="R93" t="s">
         <v>1069</v>
@@ -11970,7 +11968,7 @@
         <v>1072</v>
       </c>
       <c r="C94" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="D94" t="s">
         <v>905</v>
@@ -11982,10 +11980,10 @@
         <v>1073</v>
       </c>
       <c r="G94" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H94" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="I94" t="s">
         <v>1074</v>
@@ -12003,7 +12001,7 @@
         <v>1078</v>
       </c>
       <c r="N94" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="O94" t="s">
         <v>1079</v>
@@ -12012,7 +12010,7 @@
         <v>1080</v>
       </c>
       <c r="Q94" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="R94" t="s">
         <v>1081</v>
@@ -12036,7 +12034,7 @@
         <v>1084</v>
       </c>
       <c r="C95" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="D95" t="s">
         <v>1085</v>
@@ -12047,7 +12045,7 @@
       </c>
       <c r="G95"/>
       <c r="H95" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="I95" t="s">
         <v>1087</v>
@@ -12065,7 +12063,7 @@
         <v>1091</v>
       </c>
       <c r="N95" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="O95" t="s">
         <v>1092</v>
@@ -12074,7 +12072,7 @@
         <v>1093</v>
       </c>
       <c r="Q95" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="R95"/>
       <c r="S95"/>
@@ -12092,7 +12090,7 @@
         <v>1094</v>
       </c>
       <c r="C96" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="D96" t="s">
         <v>1095</v>
@@ -12103,7 +12101,7 @@
       </c>
       <c r="G96"/>
       <c r="H96" t="s">
-        <v>72</v>
+        <v>28</v>
       </c>
       <c r="I96" t="s">
         <v>850</v>
@@ -12121,7 +12119,7 @@
         <v>1098</v>
       </c>
       <c r="N96" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="O96" t="s">
         <v>1099</v>
@@ -12130,7 +12128,7 @@
         <v>1100</v>
       </c>
       <c r="Q96" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="R96"/>
       <c r="S96"/>
@@ -12158,10 +12156,10 @@
         <v>1103</v>
       </c>
       <c r="G97" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="H97" t="s">
-        <v>72</v>
+        <v>28</v>
       </c>
       <c r="I97" t="s">
         <v>1104</v>
@@ -12179,7 +12177,7 @@
         <v>1108</v>
       </c>
       <c r="N97" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="O97" t="s">
         <v>1109</v>
@@ -12188,7 +12186,7 @@
         <v>1110</v>
       </c>
       <c r="Q97" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="R97" t="s">
         <v>1111</v>
@@ -12224,10 +12222,10 @@
         <v>1115</v>
       </c>
       <c r="G98" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H98" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="I98" t="s">
         <v>1116</v>
@@ -12245,7 +12243,7 @@
         <v>1120</v>
       </c>
       <c r="N98" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="O98" t="s">
         <v>1121</v>
@@ -12254,7 +12252,7 @@
         <v>1122</v>
       </c>
       <c r="Q98" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="R98" t="s">
         <v>1123</v>
@@ -12278,7 +12276,7 @@
         <v>1126</v>
       </c>
       <c r="C99" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="D99" t="s">
         <v>970</v>
@@ -12290,10 +12288,10 @@
         <v>1115</v>
       </c>
       <c r="G99" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H99" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="I99" t="s">
         <v>1127</v>
@@ -12311,7 +12309,7 @@
         <v>1131</v>
       </c>
       <c r="N99" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="O99" t="s">
         <v>1132</v>
@@ -12320,7 +12318,7 @@
         <v>1133</v>
       </c>
       <c r="Q99" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="R99" t="s">
         <v>1134</v>
@@ -12344,19 +12342,19 @@
         <v>1137</v>
       </c>
       <c r="C100" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="D100" t="s">
         <v>1138</v>
       </c>
       <c r="E100" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="F100" t="s">
         <v>1115</v>
       </c>
       <c r="G100" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H100" t="s">
         <v>485</v>
@@ -12377,7 +12375,7 @@
         <v>1143</v>
       </c>
       <c r="N100" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="O100" t="s">
         <v>1144</v>
@@ -12386,7 +12384,7 @@
         <v>1145</v>
       </c>
       <c r="Q100" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="R100" t="s">
         <v>1146</v>
@@ -12410,22 +12408,22 @@
         <v>1149</v>
       </c>
       <c r="C101" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D101" t="s">
         <v>697</v>
       </c>
       <c r="E101" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="F101" t="s">
         <v>1115</v>
       </c>
       <c r="G101" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H101" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="I101" t="s">
         <v>1150</v>
@@ -12452,7 +12450,7 @@
         <v>1156</v>
       </c>
       <c r="Q101" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="R101" t="s">
         <v>1157</v>
@@ -12476,7 +12474,7 @@
         <v>1160</v>
       </c>
       <c r="C102" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D102" t="s">
         <v>1161</v>
@@ -12488,10 +12486,10 @@
         <v>1115</v>
       </c>
       <c r="G102" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H102" t="s">
-        <v>72</v>
+        <v>28</v>
       </c>
       <c r="I102" t="s">
         <v>1162</v>
@@ -12509,7 +12507,7 @@
         <v>1166</v>
       </c>
       <c r="N102" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="O102" t="s">
         <v>1167</v>
@@ -12518,7 +12516,7 @@
         <v>1168</v>
       </c>
       <c r="Q102" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="R102" t="s">
         <v>1169</v>
@@ -12542,7 +12540,7 @@
         <v>1172</v>
       </c>
       <c r="C103" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="D103" t="s">
         <v>1173</v>
@@ -12554,10 +12552,10 @@
         <v>1115</v>
       </c>
       <c r="G103" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H103" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="I103" t="s">
         <v>1174</v>
@@ -12575,7 +12573,7 @@
         <v>1178</v>
       </c>
       <c r="N103" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="O103" t="s">
         <v>1179</v>
@@ -12584,7 +12582,7 @@
         <v>1180</v>
       </c>
       <c r="Q103" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="R103" t="s">
         <v>1181</v>
@@ -12608,22 +12606,22 @@
         <v>1184</v>
       </c>
       <c r="C104" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D104" t="s">
         <v>803</v>
       </c>
       <c r="E104" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="F104" t="s">
         <v>1185</v>
       </c>
       <c r="G104" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H104" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="I104" t="s">
         <v>1186</v>
@@ -12641,7 +12639,7 @@
         <v>1190</v>
       </c>
       <c r="N104" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="O104" t="s">
         <v>1191</v>
@@ -12650,7 +12648,7 @@
         <v>1192</v>
       </c>
       <c r="Q104" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="R104" t="s">
         <v>1193</v>
@@ -12674,7 +12672,7 @@
         <v>1196</v>
       </c>
       <c r="C105" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="D105" t="s">
         <v>1197</v>
@@ -12686,10 +12684,10 @@
         <v>1185</v>
       </c>
       <c r="G105" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H105" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="I105" t="s">
         <v>1198</v>
@@ -12707,7 +12705,7 @@
         <v>1202</v>
       </c>
       <c r="N105" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="O105" t="s">
         <v>1203</v>
@@ -12716,7 +12714,7 @@
         <v>1204</v>
       </c>
       <c r="Q105" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="R105" t="s">
         <v>1205</v>
@@ -12740,7 +12738,7 @@
         <v>1208</v>
       </c>
       <c r="C106" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="D106" t="s">
         <v>1209</v>
@@ -12751,7 +12749,7 @@
       </c>
       <c r="G106"/>
       <c r="H106" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="I106" t="s">
         <v>1210</v>
@@ -12769,7 +12767,7 @@
         <v>1214</v>
       </c>
       <c r="N106" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="O106" t="s">
         <v>1215</v>
@@ -12778,7 +12776,7 @@
         <v>1216</v>
       </c>
       <c r="Q106" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="R106"/>
       <c r="S106"/>
@@ -12796,22 +12794,22 @@
         <v>1217</v>
       </c>
       <c r="C107" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D107" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="E107" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="F107" t="s">
         <v>1218</v>
       </c>
       <c r="G107" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H107" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="I107" t="s">
         <v>686</v>
@@ -12829,7 +12827,7 @@
         <v>1222</v>
       </c>
       <c r="N107" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="O107" t="s">
         <v>1223</v>
@@ -12838,7 +12836,7 @@
         <v>1224</v>
       </c>
       <c r="Q107" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="R107" t="s">
         <v>693</v>
@@ -12862,22 +12860,22 @@
         <v>1225</v>
       </c>
       <c r="C108" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D108" t="s">
         <v>1226</v>
       </c>
       <c r="E108" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="F108" t="s">
         <v>1227</v>
       </c>
       <c r="G108" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H108" t="s">
-        <v>72</v>
+        <v>28</v>
       </c>
       <c r="I108" t="s">
         <v>1228</v>
@@ -12893,7 +12891,7 @@
         <v>1231</v>
       </c>
       <c r="N108" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="O108" t="s">
         <v>1232</v>
@@ -12902,7 +12900,7 @@
         <v>1233</v>
       </c>
       <c r="Q108" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="R108" t="s">
         <v>1234</v>
@@ -12926,7 +12924,7 @@
         <v>1237</v>
       </c>
       <c r="C109" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D109" t="s">
         <v>1238</v>
@@ -12938,10 +12936,10 @@
         <v>1239</v>
       </c>
       <c r="G109" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H109" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="I109" t="s">
         <v>1240</v>
@@ -12957,7 +12955,7 @@
         <v>1243</v>
       </c>
       <c r="N109" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="O109" t="s">
         <v>1244</v>
@@ -12966,7 +12964,7 @@
         <v>1245</v>
       </c>
       <c r="Q109" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="R109" t="s">
         <v>1123</v>
@@ -12994,14 +12992,14 @@
       </c>
       <c r="D110"/>
       <c r="E110" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="F110" t="s">
         <v>1247</v>
       </c>
       <c r="G110"/>
       <c r="H110" t="s">
-        <v>72</v>
+        <v>28</v>
       </c>
       <c r="I110" t="s">
         <v>1248</v>
@@ -13015,7 +13013,7 @@
       <c r="L110"/>
       <c r="M110"/>
       <c r="N110" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="O110" t="s">
         <v>1251</v>
@@ -13024,7 +13022,7 @@
         <v>1252</v>
       </c>
       <c r="Q110" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="R110" t="s">
         <v>1253</v>
@@ -13048,7 +13046,7 @@
         <v>1256</v>
       </c>
       <c r="C111" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="D111" t="s">
         <v>1209</v>
@@ -13059,7 +13057,7 @@
       </c>
       <c r="G111"/>
       <c r="H111" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="I111" t="s">
         <v>1258</v>
@@ -13077,7 +13075,7 @@
         <v>1262</v>
       </c>
       <c r="N111" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="O111" t="s">
         <v>1263</v>
@@ -13086,7 +13084,7 @@
         <v>1264</v>
       </c>
       <c r="Q111" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="R111" t="s">
         <v>1265</v>
@@ -13110,7 +13108,7 @@
         <v>1268</v>
       </c>
       <c r="C112" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="D112" t="s">
         <v>1209</v>
@@ -13121,7 +13119,7 @@
       </c>
       <c r="G112"/>
       <c r="H112" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="I112" t="s">
         <v>1269</v>
@@ -13148,7 +13146,7 @@
         <v>1276</v>
       </c>
       <c r="Q112" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="R112" t="s">
         <v>1277</v>
@@ -13172,7 +13170,7 @@
         <v>1280</v>
       </c>
       <c r="C113" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D113" t="s">
         <v>970</v>
@@ -13184,10 +13182,10 @@
         <v>1281</v>
       </c>
       <c r="G113" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H113" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="I113" t="s">
         <v>1282</v>
@@ -13205,7 +13203,7 @@
         <v>1286</v>
       </c>
       <c r="N113" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="O113" t="s">
         <v>1287</v>
@@ -13214,7 +13212,7 @@
         <v>1288</v>
       </c>
       <c r="Q113" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="R113" t="s">
         <v>1289</v>
@@ -13238,22 +13236,22 @@
         <v>1292</v>
       </c>
       <c r="C114" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D114" t="s">
         <v>1293</v>
       </c>
       <c r="E114" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="F114" t="s">
         <v>1294</v>
       </c>
       <c r="G114" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H114" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="I114" t="s">
         <v>1295</v>
@@ -13271,7 +13269,7 @@
         <v>1299</v>
       </c>
       <c r="N114" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="O114" t="s">
         <v>1300</v>
@@ -13280,7 +13278,7 @@
         <v>1301</v>
       </c>
       <c r="Q114" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="R114" t="s">
         <v>1302</v>
@@ -13304,22 +13302,22 @@
         <v>1305</v>
       </c>
       <c r="C115" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="D115" t="s">
         <v>1306</v>
       </c>
       <c r="E115" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="F115" t="s">
         <v>1294</v>
       </c>
       <c r="G115" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H115" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="I115" t="s">
         <v>1307</v>
@@ -13337,7 +13335,7 @@
         <v>1311</v>
       </c>
       <c r="N115" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="O115" t="s">
         <v>1312</v>
@@ -13346,7 +13344,7 @@
         <v>1313</v>
       </c>
       <c r="Q115" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="R115" t="s">
         <v>946</v>
@@ -13370,7 +13368,7 @@
         <v>1314</v>
       </c>
       <c r="C116" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D116" t="s">
         <v>1315</v>
@@ -13382,10 +13380,10 @@
         <v>1294</v>
       </c>
       <c r="G116" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H116" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="I116" t="s">
         <v>1316</v>
@@ -13403,7 +13401,7 @@
         <v>1320</v>
       </c>
       <c r="N116" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="O116" t="s">
         <v>1321</v>
@@ -13412,7 +13410,7 @@
         <v>1322</v>
       </c>
       <c r="Q116" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="R116" t="s">
         <v>1323</v>
@@ -13436,22 +13434,22 @@
         <v>1326</v>
       </c>
       <c r="C117" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="D117" t="s">
         <v>1327</v>
       </c>
       <c r="E117" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="F117" t="s">
         <v>1294</v>
       </c>
       <c r="G117" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H117" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="I117" t="s">
         <v>1328</v>
@@ -13469,7 +13467,7 @@
         <v>1332</v>
       </c>
       <c r="N117" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="O117" t="s">
         <v>1333</v>
@@ -13478,7 +13476,7 @@
         <v>1334</v>
       </c>
       <c r="Q117" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="R117" t="s">
         <v>867</v>
@@ -13502,22 +13500,22 @@
         <v>1335</v>
       </c>
       <c r="C118" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D118" t="s">
         <v>1336</v>
       </c>
       <c r="E118" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="F118" t="s">
         <v>1337</v>
       </c>
       <c r="G118" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H118" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="I118" t="s">
         <v>1338</v>
@@ -13535,7 +13533,7 @@
         <v>1342</v>
       </c>
       <c r="N118" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="O118" t="s">
         <v>1343</v>
@@ -13544,7 +13542,7 @@
         <v>1344</v>
       </c>
       <c r="Q118" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="R118" t="s">
         <v>660</v>
@@ -13568,22 +13566,22 @@
         <v>1345</v>
       </c>
       <c r="C119" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D119" t="s">
         <v>747</v>
       </c>
       <c r="E119" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="F119" t="s">
         <v>1346</v>
       </c>
       <c r="G119" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H119" t="s">
-        <v>72</v>
+        <v>28</v>
       </c>
       <c r="I119" t="s">
         <v>1347</v>
@@ -13599,7 +13597,7 @@
         <v>1350</v>
       </c>
       <c r="N119" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="O119" t="s">
         <v>1351</v>
@@ -13608,7 +13606,7 @@
         <v>1352</v>
       </c>
       <c r="Q119" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="R119" t="s">
         <v>493</v>
@@ -13632,22 +13630,22 @@
         <v>1353</v>
       </c>
       <c r="C120" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="D120" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="E120" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="F120" t="s">
         <v>1354</v>
       </c>
       <c r="G120" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H120" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="I120" t="s">
         <v>1355</v>
@@ -13665,7 +13663,7 @@
         <v>1359</v>
       </c>
       <c r="N120" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="O120" t="s">
         <v>1360</v>
@@ -13674,16 +13672,16 @@
         <v>1361</v>
       </c>
       <c r="Q120" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="R120" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="S120" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="T120" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="U120" t="s">
         <v>540</v>
@@ -13698,22 +13696,22 @@
         <v>1362</v>
       </c>
       <c r="C121" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D121" t="s">
         <v>1327</v>
       </c>
       <c r="E121" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="F121" t="s">
         <v>1363</v>
       </c>
       <c r="G121" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H121" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="I121" t="s">
         <v>1364</v>
@@ -13729,7 +13727,7 @@
         <v>1367</v>
       </c>
       <c r="N121" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="O121" t="s">
         <v>1368</v>
@@ -13738,16 +13736,16 @@
         <v>1369</v>
       </c>
       <c r="Q121" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="R121" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="S121" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="T121" t="s">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="U121" t="s">
         <v>540</v>
@@ -13762,22 +13760,22 @@
         <v>1370</v>
       </c>
       <c r="C122" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D122" t="s">
         <v>747</v>
       </c>
       <c r="E122" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="F122" t="s">
         <v>1363</v>
       </c>
       <c r="G122" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H122" t="s">
-        <v>72</v>
+        <v>28</v>
       </c>
       <c r="I122" t="s">
         <v>1371</v>
@@ -13793,7 +13791,7 @@
         <v>1374</v>
       </c>
       <c r="N122" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="O122" t="s">
         <v>1375</v>
@@ -13802,7 +13800,7 @@
         <v>1376</v>
       </c>
       <c r="Q122" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="R122" t="s">
         <v>493</v>
@@ -13826,22 +13824,22 @@
         <v>1377</v>
       </c>
       <c r="C123" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D123" t="s">
         <v>747</v>
       </c>
       <c r="E123" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="F123" t="s">
         <v>1363</v>
       </c>
       <c r="G123" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H123" t="s">
-        <v>72</v>
+        <v>28</v>
       </c>
       <c r="I123" t="s">
         <v>1371</v>
@@ -13857,7 +13855,7 @@
         <v>1379</v>
       </c>
       <c r="N123" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="O123" t="s">
         <v>1380</v>
@@ -13866,7 +13864,7 @@
         <v>1381</v>
       </c>
       <c r="Q123" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="R123" t="s">
         <v>493</v>
@@ -13890,22 +13888,22 @@
         <v>1382</v>
       </c>
       <c r="C124" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D124" t="s">
         <v>747</v>
       </c>
       <c r="E124" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="F124" t="s">
         <v>1363</v>
       </c>
       <c r="G124" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H124" t="s">
-        <v>72</v>
+        <v>28</v>
       </c>
       <c r="I124" t="s">
         <v>1371</v>
@@ -13921,7 +13919,7 @@
         <v>1384</v>
       </c>
       <c r="N124" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="O124" t="s">
         <v>1385</v>
@@ -13930,7 +13928,7 @@
         <v>1386</v>
       </c>
       <c r="Q124" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="R124" t="s">
         <v>493</v>
@@ -13954,22 +13952,22 @@
         <v>1387</v>
       </c>
       <c r="C125" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="D125" t="s">
         <v>825</v>
       </c>
       <c r="E125" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="F125" t="s">
         <v>1388</v>
       </c>
       <c r="G125" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H125" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="I125" t="s">
         <v>1389</v>
@@ -13987,7 +13985,7 @@
         <v>1393</v>
       </c>
       <c r="N125" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="O125" t="s">
         <v>1394</v>
@@ -13996,7 +13994,7 @@
         <v>1395</v>
       </c>
       <c r="Q125" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="R125" t="s">
         <v>1396</v>
@@ -14020,22 +14018,22 @@
         <v>1399</v>
       </c>
       <c r="C126" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="D126" t="s">
         <v>883</v>
       </c>
       <c r="E126" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="F126" t="s">
         <v>1400</v>
       </c>
       <c r="G126" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H126" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="I126" t="s">
         <v>1401</v>
@@ -14053,7 +14051,7 @@
         <v>1405</v>
       </c>
       <c r="N126" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="O126" t="s">
         <v>1406</v>
@@ -14062,7 +14060,7 @@
         <v>1407</v>
       </c>
       <c r="Q126" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="R126" t="s">
         <v>470</v>
@@ -14086,22 +14084,22 @@
         <v>1408</v>
       </c>
       <c r="C127" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="D127" t="s">
         <v>1409</v>
       </c>
       <c r="E127" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="F127" t="s">
         <v>1400</v>
       </c>
       <c r="G127" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H127" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="I127" t="s">
         <v>1410</v>
@@ -14119,7 +14117,7 @@
         <v>1414</v>
       </c>
       <c r="N127" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="O127" t="s">
         <v>1415</v>
@@ -14128,7 +14126,7 @@
         <v>1416</v>
       </c>
       <c r="Q127" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="R127" t="s">
         <v>1417</v>
@@ -14152,22 +14150,22 @@
         <v>1420</v>
       </c>
       <c r="C128" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="D128" t="s">
         <v>1421</v>
       </c>
       <c r="E128" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="F128" t="s">
         <v>1400</v>
       </c>
       <c r="G128" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H128" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="I128" t="s">
         <v>1422</v>
@@ -14185,7 +14183,7 @@
         <v>1426</v>
       </c>
       <c r="N128" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="O128" t="s">
         <v>1427</v>
@@ -14194,7 +14192,7 @@
         <v>1428</v>
       </c>
       <c r="Q128" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="R128" t="s">
         <v>1429</v>
@@ -14218,7 +14216,7 @@
         <v>1432</v>
       </c>
       <c r="C129" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="D129" t="s">
         <v>1209</v>
@@ -14229,7 +14227,7 @@
       </c>
       <c r="G129"/>
       <c r="H129" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="I129" t="s">
         <v>1434</v>
@@ -14247,7 +14245,7 @@
         <v>1438</v>
       </c>
       <c r="N129" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="O129" t="s">
         <v>1439</v>
@@ -14256,16 +14254,16 @@
         <v>1440</v>
       </c>
       <c r="Q129" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="R129" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="S129" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="T129" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="U129" t="s">
         <v>540</v>
@@ -14280,22 +14278,22 @@
         <v>1441</v>
       </c>
       <c r="C130" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D130" t="s">
         <v>725</v>
       </c>
       <c r="E130" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="F130" t="s">
         <v>1433</v>
       </c>
       <c r="G130" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H130" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="I130" t="s">
         <v>1442</v>
@@ -14313,7 +14311,7 @@
         <v>1446</v>
       </c>
       <c r="N130" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="O130" t="s">
         <v>1447</v>
@@ -14322,7 +14320,7 @@
         <v>1448</v>
       </c>
       <c r="Q130" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="R130" t="s">
         <v>1449</v>
@@ -14346,22 +14344,22 @@
         <v>1452</v>
       </c>
       <c r="C131" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D131" t="s">
         <v>1453</v>
       </c>
       <c r="E131" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="F131" t="s">
         <v>1433</v>
       </c>
       <c r="G131" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H131" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="I131" t="s">
         <v>1454</v>
@@ -14379,7 +14377,7 @@
         <v>1458</v>
       </c>
       <c r="N131" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="O131" t="s">
         <v>1459</v>
@@ -14388,7 +14386,7 @@
         <v>1460</v>
       </c>
       <c r="Q131" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="R131" t="s">
         <v>1461</v>
@@ -14412,7 +14410,7 @@
         <v>1464</v>
       </c>
       <c r="C132" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="D132" t="s">
         <v>1465</v>
@@ -14424,10 +14422,10 @@
         <v>1433</v>
       </c>
       <c r="G132" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H132" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="I132" t="s">
         <v>1466</v>
@@ -14445,7 +14443,7 @@
         <v>1470</v>
       </c>
       <c r="N132" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="O132" t="s">
         <v>1471</v>
@@ -14454,7 +14452,7 @@
         <v>1472</v>
       </c>
       <c r="Q132" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="R132" t="s">
         <v>1134</v>
@@ -14478,7 +14476,7 @@
         <v>1473</v>
       </c>
       <c r="C133" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D133" t="s">
         <v>871</v>
@@ -14490,10 +14488,10 @@
         <v>1433</v>
       </c>
       <c r="G133" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H133" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="I133" t="s">
         <v>1474</v>
@@ -14511,7 +14509,7 @@
         <v>1478</v>
       </c>
       <c r="N133" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="O133" t="s">
         <v>1479</v>
@@ -14520,7 +14518,7 @@
         <v>1480</v>
       </c>
       <c r="Q133" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="R133" t="s">
         <v>1481</v>
@@ -14544,22 +14542,22 @@
         <v>1484</v>
       </c>
       <c r="C134" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D134" t="s">
         <v>825</v>
       </c>
       <c r="E134" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="F134" t="s">
         <v>1433</v>
       </c>
       <c r="G134" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H134" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="I134" t="s">
         <v>1485</v>
@@ -14586,7 +14584,7 @@
         <v>1492</v>
       </c>
       <c r="Q134" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="R134" t="s">
         <v>1493</v>
@@ -14610,22 +14608,22 @@
         <v>1496</v>
       </c>
       <c r="C135" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="D135" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="E135" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="F135" t="s">
         <v>1497</v>
       </c>
       <c r="G135" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H135" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="I135" t="s">
         <v>1498</v>
@@ -14643,7 +14641,7 @@
         <v>1502</v>
       </c>
       <c r="N135" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="O135" t="s">
         <v>1503</v>
@@ -14652,16 +14650,16 @@
         <v>1504</v>
       </c>
       <c r="Q135" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="R135" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="S135" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="T135" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="U135" t="s">
         <v>540</v>
@@ -14676,22 +14674,22 @@
         <v>1505</v>
       </c>
       <c r="C136" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D136" t="s">
         <v>697</v>
       </c>
       <c r="E136" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="F136" t="s">
         <v>1506</v>
       </c>
       <c r="G136" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H136" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="I136" t="s">
         <v>1507</v>
@@ -14709,7 +14707,7 @@
         <v>1511</v>
       </c>
       <c r="N136" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="O136" t="s">
         <v>1512</v>
@@ -14718,7 +14716,7 @@
         <v>1513</v>
       </c>
       <c r="Q136" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="R136" t="s">
         <v>991</v>
@@ -14742,22 +14740,22 @@
         <v>1514</v>
       </c>
       <c r="C137" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D137" t="s">
         <v>1515</v>
       </c>
       <c r="E137" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="F137" t="s">
         <v>1516</v>
       </c>
       <c r="G137" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H137" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="I137" t="s">
         <v>1517</v>
@@ -14773,7 +14771,7 @@
         <v>1520</v>
       </c>
       <c r="N137" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="O137" t="s">
         <v>1521</v>
@@ -14782,7 +14780,7 @@
         <v>1522</v>
       </c>
       <c r="Q137" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="R137" t="s">
         <v>991</v>
@@ -14806,7 +14804,7 @@
         <v>1523</v>
       </c>
       <c r="C138" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D138" t="s">
         <v>1524</v>
@@ -14818,10 +14816,10 @@
         <v>1516</v>
       </c>
       <c r="G138" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H138" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="I138" t="s">
         <v>1525</v>
@@ -14837,7 +14835,7 @@
         <v>1528</v>
       </c>
       <c r="N138" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="O138" t="s">
         <v>1529</v>
@@ -14846,16 +14844,16 @@
         <v>1530</v>
       </c>
       <c r="Q138" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="R138" t="s">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="S138" t="s">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="T138" t="s">
-        <v>232</v>
+        <v>244</v>
       </c>
       <c r="U138" t="s">
         <v>540</v>
@@ -14870,7 +14868,7 @@
         <v>1531</v>
       </c>
       <c r="C139" t="s">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="D139" t="s">
         <v>453</v>
@@ -14882,10 +14880,10 @@
         <v>1532</v>
       </c>
       <c r="G139" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H139" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="I139" t="s">
         <v>1533</v>
@@ -14903,7 +14901,7 @@
         <v>1537</v>
       </c>
       <c r="N139" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="O139" t="s">
         <v>1538</v>
@@ -14912,7 +14910,7 @@
         <v>1539</v>
       </c>
       <c r="Q139" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="R139" t="s">
         <v>1069</v>
@@ -14940,14 +14938,14 @@
       </c>
       <c r="D140"/>
       <c r="E140" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="F140" t="s">
         <v>1541</v>
       </c>
       <c r="G140"/>
       <c r="H140" t="s">
-        <v>72</v>
+        <v>28</v>
       </c>
       <c r="I140" t="s">
         <v>1542</v>
@@ -14961,7 +14959,7 @@
       <c r="L140"/>
       <c r="M140"/>
       <c r="N140" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="O140" t="s">
         <v>1545</v>
@@ -14970,7 +14968,7 @@
         <v>1546</v>
       </c>
       <c r="Q140" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="R140" t="s">
         <v>1547</v>
@@ -14994,7 +14992,7 @@
         <v>1550</v>
       </c>
       <c r="C141" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="D141" t="s">
         <v>1209</v>
@@ -15005,7 +15003,7 @@
       </c>
       <c r="G141"/>
       <c r="H141" t="s">
-        <v>72</v>
+        <v>28</v>
       </c>
       <c r="I141" t="s">
         <v>1552</v>
@@ -15032,7 +15030,7 @@
         <v>1558</v>
       </c>
       <c r="Q141" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="R141" t="s">
         <v>1559</v>
@@ -15056,7 +15054,7 @@
         <v>1562</v>
       </c>
       <c r="C142" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="D142" t="s">
         <v>1563</v>
@@ -15068,10 +15066,10 @@
         <v>1564</v>
       </c>
       <c r="G142" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H142" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="I142" t="s">
         <v>1565</v>
@@ -15089,7 +15087,7 @@
         <v>1569</v>
       </c>
       <c r="N142" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="O142" t="s">
         <v>1570</v>
@@ -15098,7 +15096,7 @@
         <v>1571</v>
       </c>
       <c r="Q142" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="R142" t="s">
         <v>1572</v>
@@ -15122,7 +15120,7 @@
         <v>1575</v>
       </c>
       <c r="C143" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="D143" t="s">
         <v>1576</v>
@@ -15134,10 +15132,10 @@
         <v>1577</v>
       </c>
       <c r="G143" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H143" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="I143" t="s">
         <v>1578</v>
@@ -15155,7 +15153,7 @@
         <v>1582</v>
       </c>
       <c r="N143" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="O143" t="s">
         <v>1583</v>
@@ -15164,7 +15162,7 @@
         <v>1584</v>
       </c>
       <c r="Q143" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="R143" t="s">
         <v>1585</v>
@@ -15188,10 +15186,10 @@
         <v>1588</v>
       </c>
       <c r="C144" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="D144" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="E144" t="s">
         <v>25</v>
@@ -15200,10 +15198,10 @@
         <v>1577</v>
       </c>
       <c r="G144" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="H144" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="I144" t="s">
         <v>1589</v>
@@ -15221,7 +15219,7 @@
         <v>1593</v>
       </c>
       <c r="N144" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="O144" t="s">
         <v>1594</v>
@@ -15230,7 +15228,7 @@
         <v>1595</v>
       </c>
       <c r="Q144" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="R144" t="s">
         <v>946</v>
@@ -15254,22 +15252,22 @@
         <v>1596</v>
       </c>
       <c r="C145" t="s">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="D145" t="s">
         <v>631</v>
       </c>
       <c r="E145" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="F145" t="s">
         <v>1597</v>
       </c>
       <c r="G145" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="H145" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="I145" t="s">
         <v>1598</v>
@@ -15287,7 +15285,7 @@
         <v>1602</v>
       </c>
       <c r="N145" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="O145" t="s">
         <v>1603</v>
@@ -15296,16 +15294,16 @@
         <v>1604</v>
       </c>
       <c r="Q145" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="R145" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="S145" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="T145" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="U145" t="s">
         <v>540</v>
@@ -15320,22 +15318,22 @@
         <v>1605</v>
       </c>
       <c r="C146" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D146" t="s">
         <v>1606</v>
       </c>
       <c r="E146" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="F146" t="s">
         <v>1597</v>
       </c>
       <c r="G146" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H146" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="I146" t="s">
         <v>1607</v>
@@ -15353,7 +15351,7 @@
         <v>1611</v>
       </c>
       <c r="N146" t="s">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="O146" t="s">
         <v>1612</v>
@@ -15362,7 +15360,7 @@
         <v>1613</v>
       </c>
       <c r="Q146" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="R146" t="s">
         <v>1614</v>
@@ -15386,7 +15384,7 @@
         <v>1617</v>
       </c>
       <c r="C147" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D147" t="s">
         <v>1618</v>
@@ -15398,10 +15396,10 @@
         <v>1597</v>
       </c>
       <c r="G147" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H147" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="I147" t="s">
         <v>1620</v>
@@ -15419,7 +15417,7 @@
         <v>1624</v>
       </c>
       <c r="N147" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="O147" t="s">
         <v>1625</v>
@@ -15428,7 +15426,7 @@
         <v>1626</v>
       </c>
       <c r="Q147" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="R147" t="s">
         <v>1627</v>
@@ -15452,22 +15450,22 @@
         <v>1630</v>
       </c>
       <c r="C148" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="D148" t="s">
         <v>596</v>
       </c>
       <c r="E148" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="F148" t="s">
         <v>1597</v>
       </c>
       <c r="G148" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H148" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="I148" t="s">
         <v>1631</v>
@@ -15485,7 +15483,7 @@
         <v>1635</v>
       </c>
       <c r="N148" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="O148" t="s">
         <v>1636</v>
@@ -15494,7 +15492,7 @@
         <v>1637</v>
       </c>
       <c r="Q148" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="R148" t="s">
         <v>1638</v>
@@ -15518,22 +15516,22 @@
         <v>1641</v>
       </c>
       <c r="C149" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="D149" t="s">
         <v>1606</v>
       </c>
       <c r="E149" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="F149" t="s">
         <v>1597</v>
       </c>
       <c r="G149" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H149" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="I149" t="s">
         <v>1642</v>
@@ -15551,7 +15549,7 @@
         <v>1646</v>
       </c>
       <c r="N149" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="O149" t="s">
         <v>1647</v>
@@ -15560,7 +15558,7 @@
         <v>1648</v>
       </c>
       <c r="Q149" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="R149" t="s">
         <v>1649</v>
@@ -15584,7 +15582,7 @@
         <v>1652</v>
       </c>
       <c r="C150" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="D150" t="s">
         <v>1315</v>
@@ -15596,10 +15594,10 @@
         <v>1597</v>
       </c>
       <c r="G150" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H150" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="I150" t="s">
         <v>1653</v>
@@ -15617,7 +15615,7 @@
         <v>1657</v>
       </c>
       <c r="N150" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="O150" t="s">
         <v>1658</v>
@@ -15626,7 +15624,7 @@
         <v>1659</v>
       </c>
       <c r="Q150" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="R150" t="s">
         <v>1660</v>
@@ -15650,22 +15648,22 @@
         <v>1663</v>
       </c>
       <c r="C151" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="D151" t="s">
         <v>1664</v>
       </c>
       <c r="E151" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="F151" t="s">
         <v>1665</v>
       </c>
       <c r="G151" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H151" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="I151" t="s">
         <v>1666</v>
@@ -15683,7 +15681,7 @@
         <v>1670</v>
       </c>
       <c r="N151" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="O151" t="s">
         <v>1671</v>
@@ -15692,7 +15690,7 @@
         <v>1672</v>
       </c>
       <c r="Q151" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="R151" t="s">
         <v>991</v>
@@ -15716,22 +15714,22 @@
         <v>1673</v>
       </c>
       <c r="C152" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="D152" t="s">
         <v>497</v>
       </c>
       <c r="E152" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="F152" t="s">
         <v>1674</v>
       </c>
       <c r="G152" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H152" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="I152" t="s">
         <v>1675</v>
@@ -15749,7 +15747,7 @@
         <v>1679</v>
       </c>
       <c r="N152" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="O152" t="s">
         <v>1680</v>
@@ -15758,7 +15756,7 @@
         <v>1681</v>
       </c>
       <c r="Q152" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="R152" t="s">
         <v>592</v>
@@ -15782,7 +15780,7 @@
         <v>1682</v>
       </c>
       <c r="C153" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="D153" t="s">
         <v>1683</v>
@@ -15794,10 +15792,10 @@
         <v>1684</v>
       </c>
       <c r="G153" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="H153" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="I153" t="s">
         <v>1685</v>
@@ -15815,7 +15813,7 @@
         <v>1689</v>
       </c>
       <c r="N153" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="O153" t="s">
         <v>1690</v>
@@ -15824,7 +15822,7 @@
         <v>1691</v>
       </c>
       <c r="Q153" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="R153" t="s">
         <v>913</v>
@@ -15848,7 +15846,7 @@
         <v>1692</v>
       </c>
       <c r="C154" t="s">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="D154" t="s">
         <v>1693</v>
@@ -15860,10 +15858,10 @@
         <v>1694</v>
       </c>
       <c r="G154" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="H154" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="I154" t="s">
         <v>1695</v>
@@ -15881,7 +15879,7 @@
         <v>1699</v>
       </c>
       <c r="N154" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="O154" t="s">
         <v>1700</v>
@@ -15890,7 +15888,7 @@
         <v>1701</v>
       </c>
       <c r="Q154" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="R154" t="s">
         <v>1461</v>
@@ -15914,22 +15912,22 @@
         <v>1702</v>
       </c>
       <c r="C155" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D155" t="s">
         <v>825</v>
       </c>
       <c r="E155" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="F155" t="s">
         <v>1694</v>
       </c>
       <c r="G155" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H155" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="I155" t="s">
         <v>1703</v>
@@ -15945,7 +15943,7 @@
         <v>1706</v>
       </c>
       <c r="N155" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="O155" t="s">
         <v>1707</v>
@@ -15954,16 +15952,16 @@
         <v>1708</v>
       </c>
       <c r="Q155" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="R155" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="S155" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="T155" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="U155" t="s">
         <v>540</v>
@@ -15978,7 +15976,7 @@
         <v>1709</v>
       </c>
       <c r="C156" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D156" t="s">
         <v>453</v>
@@ -15990,10 +15988,10 @@
         <v>1710</v>
       </c>
       <c r="G156" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H156" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="I156" t="s">
         <v>1711</v>
@@ -16009,7 +16007,7 @@
         <v>1714</v>
       </c>
       <c r="N156" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="O156" t="s">
         <v>1715</v>
@@ -16018,16 +16016,16 @@
         <v>1716</v>
       </c>
       <c r="Q156" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="R156" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="S156" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="T156" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="U156" t="s">
         <v>540</v>
@@ -16042,7 +16040,7 @@
         <v>1717</v>
       </c>
       <c r="C157" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D157" t="s">
         <v>1718</v>
@@ -16052,10 +16050,10 @@
         <v>1719</v>
       </c>
       <c r="G157" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H157" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="I157" t="s">
         <v>1720</v>
@@ -16073,7 +16071,7 @@
         <v>1724</v>
       </c>
       <c r="N157" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="O157" t="s">
         <v>1725</v>
@@ -16082,7 +16080,7 @@
         <v>1726</v>
       </c>
       <c r="Q157" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="R157" t="s">
         <v>1727</v>
@@ -16106,22 +16104,22 @@
         <v>1730</v>
       </c>
       <c r="C158" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="D158" t="s">
         <v>1031</v>
       </c>
       <c r="E158" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="F158" t="s">
         <v>1731</v>
       </c>
       <c r="G158" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H158" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="I158" t="s">
         <v>1732</v>
@@ -16139,7 +16137,7 @@
         <v>1736</v>
       </c>
       <c r="N158" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="O158" t="s">
         <v>1737</v>
@@ -16148,7 +16146,7 @@
         <v>1738</v>
       </c>
       <c r="Q158" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="R158" t="s">
         <v>1739</v>
@@ -16172,7 +16170,7 @@
         <v>1742</v>
       </c>
       <c r="C159" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D159" t="s">
         <v>858</v>
@@ -16184,10 +16182,10 @@
         <v>1731</v>
       </c>
       <c r="G159" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H159" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="I159" t="s">
         <v>1743</v>
@@ -16205,7 +16203,7 @@
         <v>1747</v>
       </c>
       <c r="N159" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="O159" t="s">
         <v>1748</v>
@@ -16214,7 +16212,7 @@
         <v>1749</v>
       </c>
       <c r="Q159" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="R159" t="s">
         <v>1750</v>
@@ -16238,7 +16236,7 @@
         <v>1753</v>
       </c>
       <c r="C160" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D160" t="s">
         <v>1754</v>
@@ -16250,7 +16248,7 @@
         <v>1755</v>
       </c>
       <c r="G160" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="H160" t="s">
         <v>1007</v>
@@ -16271,7 +16269,7 @@
         <v>1760</v>
       </c>
       <c r="N160" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="O160" t="s">
         <v>1761</v>
@@ -16280,7 +16278,7 @@
         <v>1762</v>
       </c>
       <c r="Q160" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="R160" t="s">
         <v>1763</v>
@@ -16304,7 +16302,7 @@
         <v>1766</v>
       </c>
       <c r="C161" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D161" t="s">
         <v>1161</v>
@@ -16316,7 +16314,7 @@
         <v>1755</v>
       </c>
       <c r="G161" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H161" t="s">
         <v>1007</v>
@@ -16337,7 +16335,7 @@
         <v>1760</v>
       </c>
       <c r="N161" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="O161" t="s">
         <v>1767</v>
@@ -16346,7 +16344,7 @@
         <v>1768</v>
       </c>
       <c r="Q161" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="R161" t="s">
         <v>1769</v>
@@ -16370,7 +16368,7 @@
         <v>1772</v>
       </c>
       <c r="C162" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="D162" t="s">
         <v>1773</v>
@@ -16382,10 +16380,10 @@
         <v>1774</v>
       </c>
       <c r="G162" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H162" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="I162" t="s">
         <v>1775</v>
@@ -16403,7 +16401,7 @@
         <v>1779</v>
       </c>
       <c r="N162" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="O162" t="s">
         <v>1780</v>
@@ -16412,16 +16410,16 @@
         <v>1781</v>
       </c>
       <c r="Q162" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="R162" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="S162" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="T162" t="s">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="U162" t="s">
         <v>540</v>
@@ -16436,22 +16434,22 @@
         <v>1782</v>
       </c>
       <c r="C163" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="D163" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="E163" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="F163" t="s">
         <v>1783</v>
       </c>
       <c r="G163" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="H163" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="I163" t="s">
         <v>1784</v>
@@ -16469,7 +16467,7 @@
         <v>1788</v>
       </c>
       <c r="N163" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="O163" t="s">
         <v>1789</v>
@@ -16478,7 +16476,7 @@
         <v>1790</v>
       </c>
       <c r="Q163" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="R163" t="s">
         <v>1791</v>
@@ -16502,22 +16500,22 @@
         <v>1794</v>
       </c>
       <c r="C164" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="D164" t="s">
         <v>825</v>
       </c>
       <c r="E164" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="F164" t="s">
         <v>1795</v>
       </c>
       <c r="G164" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H164" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="I164" t="s">
         <v>1796</v>
@@ -16535,7 +16533,7 @@
         <v>1800</v>
       </c>
       <c r="N164" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="O164" t="s">
         <v>1801</v>
@@ -16544,7 +16542,7 @@
         <v>1802</v>
       </c>
       <c r="Q164" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="R164" t="s">
         <v>1803</v>
@@ -16568,22 +16566,22 @@
         <v>1806</v>
       </c>
       <c r="C165" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D165" t="s">
         <v>1807</v>
       </c>
       <c r="E165" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="F165" t="s">
         <v>1795</v>
       </c>
       <c r="G165" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H165" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="I165" t="s">
         <v>1808</v>
@@ -16599,7 +16597,7 @@
         <v>1811</v>
       </c>
       <c r="N165" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="O165" t="s">
         <v>1812</v>
@@ -16608,7 +16606,7 @@
         <v>1813</v>
       </c>
       <c r="Q165" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="R165" t="s">
         <v>1803</v>
@@ -16632,22 +16630,22 @@
         <v>1814</v>
       </c>
       <c r="C166" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D166" t="s">
         <v>1807</v>
       </c>
       <c r="E166" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="F166" t="s">
         <v>1795</v>
       </c>
       <c r="G166" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H166" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="I166" t="s">
         <v>1815</v>
@@ -16663,7 +16661,7 @@
         <v>1818</v>
       </c>
       <c r="N166" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="O166" t="s">
         <v>1819</v>
@@ -16672,7 +16670,7 @@
         <v>1820</v>
       </c>
       <c r="Q166" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="R166" t="s">
         <v>1803</v>
@@ -16696,7 +16694,7 @@
         <v>1821</v>
       </c>
       <c r="C167" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D167" t="s">
         <v>1822</v>
@@ -16708,10 +16706,10 @@
         <v>1823</v>
       </c>
       <c r="G167" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H167" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="I167" t="s">
         <v>1824</v>
@@ -16727,7 +16725,7 @@
         <v>1827</v>
       </c>
       <c r="N167" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="O167" t="s">
         <v>1828</v>
@@ -16736,16 +16734,16 @@
         <v>1829</v>
       </c>
       <c r="Q167" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="R167" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="S167" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="T167" t="s">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="U167" t="s">
         <v>540</v>
@@ -16760,22 +16758,22 @@
         <v>1830</v>
       </c>
       <c r="C168" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D168" t="s">
         <v>1606</v>
       </c>
       <c r="E168" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="F168" t="s">
         <v>1831</v>
       </c>
       <c r="G168" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H168" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="I168" t="s">
         <v>1832</v>
@@ -16791,7 +16789,7 @@
         <v>1835</v>
       </c>
       <c r="N168" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="O168" t="s">
         <v>1836</v>
@@ -16800,7 +16798,7 @@
         <v>1837</v>
       </c>
       <c r="Q168" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="R168" t="s">
         <v>1838</v>
@@ -16824,7 +16822,7 @@
         <v>1841</v>
       </c>
       <c r="C169" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="D169" t="s">
         <v>1209</v>
@@ -16835,7 +16833,7 @@
       </c>
       <c r="G169"/>
       <c r="H169" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="I169" t="s">
         <v>1843</v>
@@ -16853,7 +16851,7 @@
         <v>1847</v>
       </c>
       <c r="N169" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="O169" t="s">
         <v>1848</v>
@@ -16862,7 +16860,7 @@
         <v>1849</v>
       </c>
       <c r="Q169" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="R169" t="s">
         <v>1850</v>

--- a/Objets_parlementaires_Jura.xlsx
+++ b/Objets_parlementaires_Jura.xlsx
@@ -320,6 +320,15 @@
     <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20264418</t>
   </si>
   <si>
+    <t xml:space="preserve">Staatspolitik|Sozialer Schutz|Gesundheit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politique d'Etat|Protection sociale|Santé</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politica nazionale|Protezione sociale|Salute</t>
+  </si>
+  <si>
     <t xml:space="preserve">26.4338</t>
   </si>
   <si>
@@ -432,15 +441,6 @@
   </si>
   <si>
     <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20264261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staatspolitik|Sozialer Schutz|Gesundheit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politique d'Etat|Protection sociale|Santé</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politica nazionale|Protezione sociale|Salute</t>
   </si>
   <si>
     <t xml:space="preserve">26.3891</t>
@@ -6370,9 +6370,15 @@
       <c r="Q7" t="s">
         <v>53</v>
       </c>
-      <c r="R7"/>
-      <c r="S7"/>
-      <c r="T7"/>
+      <c r="R7" t="s">
+        <v>102</v>
+      </c>
+      <c r="S7" t="s">
+        <v>103</v>
+      </c>
+      <c r="T7" t="s">
+        <v>104</v>
+      </c>
       <c r="U7" t="s">
         <v>97</v>
       </c>
@@ -6383,7 +6389,7 @@
         <v>20264338</v>
       </c>
       <c r="B8" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C8" t="s">
         <v>42</v>
@@ -6395,7 +6401,7 @@
         <v>25</v>
       </c>
       <c r="F8" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G8" t="s">
         <v>27</v>
@@ -6405,38 +6411,38 @@
         <v>46</v>
       </c>
       <c r="J8" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="K8" t="s">
         <v>48</v>
       </c>
       <c r="L8" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M8"/>
       <c r="N8" t="s">
         <v>50</v>
       </c>
       <c r="O8" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="P8" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="Q8" t="s">
         <v>36</v>
       </c>
       <c r="R8" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="S8" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="T8" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="U8" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="V8"/>
     </row>
@@ -6445,7 +6451,7 @@
         <v>20264339</v>
       </c>
       <c r="B9" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C9" t="s">
         <v>58</v>
@@ -6457,7 +6463,7 @@
         <v>25</v>
       </c>
       <c r="F9" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G9" t="s">
         <v>27</v>
@@ -6467,38 +6473,38 @@
         <v>46</v>
       </c>
       <c r="J9" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="K9" t="s">
         <v>48</v>
       </c>
       <c r="L9" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M9"/>
       <c r="N9" t="s">
         <v>50</v>
       </c>
       <c r="O9" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="P9" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="Q9" t="s">
         <v>36</v>
       </c>
       <c r="R9" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="S9" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="T9" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="U9" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="V9"/>
     </row>
@@ -6507,7 +6513,7 @@
         <v>20267901</v>
       </c>
       <c r="B10" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C10" t="s">
         <v>23</v>
@@ -6519,50 +6525,50 @@
         <v>25</v>
       </c>
       <c r="F10" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="G10" t="s">
         <v>27</v>
       </c>
       <c r="H10" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="I10" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="J10" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="K10"/>
       <c r="L10" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="M10" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="N10" t="s">
         <v>33</v>
       </c>
       <c r="O10" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="P10" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="Q10" t="s">
         <v>36</v>
       </c>
       <c r="R10" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="S10" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="T10" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="U10" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="V10"/>
     </row>
@@ -6571,19 +6577,19 @@
         <v>20264261</v>
       </c>
       <c r="B11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C11" t="s">
         <v>58</v>
       </c>
       <c r="D11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E11" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F11" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="G11" t="s">
         <v>45</v>
@@ -6593,38 +6599,38 @@
         <v>46</v>
       </c>
       <c r="J11" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="K11" t="s">
         <v>48</v>
       </c>
       <c r="L11" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="M11"/>
       <c r="N11" t="s">
         <v>50</v>
       </c>
       <c r="O11" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="P11" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="Q11" t="s">
         <v>36</v>
       </c>
       <c r="R11" t="s">
-        <v>140</v>
+        <v>102</v>
       </c>
       <c r="S11" t="s">
-        <v>141</v>
+        <v>103</v>
       </c>
       <c r="T11" t="s">
-        <v>142</v>
+        <v>104</v>
       </c>
       <c r="U11" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="V11"/>
     </row>
@@ -6639,10 +6645,10 @@
         <v>58</v>
       </c>
       <c r="D12" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E12" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F12" t="s">
         <v>144</v>
@@ -6961,10 +6967,10 @@
         <v>42</v>
       </c>
       <c r="D17" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E17" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F17" t="s">
         <v>204</v>
@@ -7533,10 +7539,10 @@
         <v>308</v>
       </c>
       <c r="D26" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E26" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F26" t="s">
         <v>309</v>
@@ -7611,7 +7617,7 @@
         <v>27</v>
       </c>
       <c r="H27" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="I27" t="s">
         <v>323</v>
@@ -7677,7 +7683,7 @@
         <v>27</v>
       </c>
       <c r="H28" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="I28" t="s">
         <v>336</v>
@@ -7875,7 +7881,7 @@
         <v>27</v>
       </c>
       <c r="H31" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="I31" t="s">
         <v>372</v>
@@ -7929,10 +7935,10 @@
         <v>308</v>
       </c>
       <c r="D32" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E32" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F32" t="s">
         <v>380</v>
@@ -8007,7 +8013,7 @@
         <v>27</v>
       </c>
       <c r="H33" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="I33" t="s">
         <v>395</v>
@@ -8071,7 +8077,7 @@
         <v>27</v>
       </c>
       <c r="H34" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="I34" t="s">
         <v>405</v>
@@ -8189,10 +8195,10 @@
         <v>58</v>
       </c>
       <c r="D36" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E36" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F36" t="s">
         <v>219</v>
@@ -8267,7 +8273,7 @@
         <v>27</v>
       </c>
       <c r="H37" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="I37" t="s">
         <v>441</v>
@@ -8715,10 +8721,10 @@
         <v>42</v>
       </c>
       <c r="D44" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E44" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F44" t="s">
         <v>520</v>
@@ -8793,7 +8799,7 @@
         <v>27</v>
       </c>
       <c r="H45" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="I45" t="s">
         <v>531</v>
@@ -9229,10 +9235,10 @@
         <v>42</v>
       </c>
       <c r="D52" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E52" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F52" t="s">
         <v>608</v>
@@ -9295,10 +9301,10 @@
         <v>308</v>
       </c>
       <c r="D53" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E53" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F53" t="s">
         <v>608</v>
@@ -9364,7 +9370,7 @@
         <v>631</v>
       </c>
       <c r="E54" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F54" t="s">
         <v>632</v>
@@ -9952,7 +9958,7 @@
         <v>725</v>
       </c>
       <c r="E63" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F63" t="s">
         <v>726</v>
@@ -10015,10 +10021,10 @@
         <v>58</v>
       </c>
       <c r="D64" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E64" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F64" t="s">
         <v>735</v>
@@ -10027,7 +10033,7 @@
         <v>45</v>
       </c>
       <c r="H64" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="I64" t="s">
         <v>736</v>
@@ -10150,7 +10156,7 @@
         <v>759</v>
       </c>
       <c r="E66" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F66" t="s">
         <v>760</v>
@@ -10412,7 +10418,7 @@
         <v>803</v>
       </c>
       <c r="E70" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F70" t="s">
         <v>787</v>
@@ -10421,7 +10427,7 @@
         <v>27</v>
       </c>
       <c r="H70" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="I70" t="s">
         <v>804</v>
@@ -10858,7 +10864,7 @@
         <v>883</v>
       </c>
       <c r="E77" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F77" t="s">
         <v>859</v>
@@ -11578,7 +11584,7 @@
         <v>1005</v>
       </c>
       <c r="E88" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F88" t="s">
         <v>1006</v>
@@ -11644,7 +11650,7 @@
         <v>1019</v>
       </c>
       <c r="E89" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F89" t="s">
         <v>1006</v>
@@ -11776,7 +11782,7 @@
         <v>1040</v>
       </c>
       <c r="E91" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F91" t="s">
         <v>1041</v>
@@ -11839,10 +11845,10 @@
         <v>42</v>
       </c>
       <c r="D92" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E92" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F92" t="s">
         <v>1041</v>
@@ -11908,7 +11914,7 @@
         <v>631</v>
       </c>
       <c r="E93" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F93" t="s">
         <v>1061</v>
@@ -12348,7 +12354,7 @@
         <v>1138</v>
       </c>
       <c r="E100" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F100" t="s">
         <v>1115</v>
@@ -12612,7 +12618,7 @@
         <v>803</v>
       </c>
       <c r="E104" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F104" t="s">
         <v>1185</v>
@@ -13242,7 +13248,7 @@
         <v>1293</v>
       </c>
       <c r="E114" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F114" t="s">
         <v>1294</v>
@@ -13251,7 +13257,7 @@
         <v>27</v>
       </c>
       <c r="H114" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="I114" t="s">
         <v>1295</v>
@@ -13440,7 +13446,7 @@
         <v>1327</v>
       </c>
       <c r="E117" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F117" t="s">
         <v>1294</v>
@@ -13449,7 +13455,7 @@
         <v>27</v>
       </c>
       <c r="H117" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="I117" t="s">
         <v>1328</v>
@@ -13515,7 +13521,7 @@
         <v>27</v>
       </c>
       <c r="H118" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="I118" t="s">
         <v>1338</v>
@@ -13702,7 +13708,7 @@
         <v>1327</v>
       </c>
       <c r="E121" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F121" t="s">
         <v>1363</v>
@@ -14024,7 +14030,7 @@
         <v>883</v>
       </c>
       <c r="E126" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F126" t="s">
         <v>1400</v>
@@ -14284,7 +14290,7 @@
         <v>725</v>
       </c>
       <c r="E130" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F130" t="s">
         <v>1433</v>
@@ -14293,7 +14299,7 @@
         <v>27</v>
       </c>
       <c r="H130" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="I130" t="s">
         <v>1442</v>
@@ -15258,7 +15264,7 @@
         <v>631</v>
       </c>
       <c r="E145" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F145" t="s">
         <v>1597</v>
@@ -15324,7 +15330,7 @@
         <v>1606</v>
       </c>
       <c r="E146" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F146" t="s">
         <v>1597</v>
@@ -15399,7 +15405,7 @@
         <v>27</v>
       </c>
       <c r="H147" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="I147" t="s">
         <v>1620</v>
@@ -15522,7 +15528,7 @@
         <v>1606</v>
       </c>
       <c r="E149" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F149" t="s">
         <v>1597</v>
@@ -15654,7 +15660,7 @@
         <v>1664</v>
       </c>
       <c r="E151" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F151" t="s">
         <v>1665</v>
@@ -16383,7 +16389,7 @@
         <v>27</v>
       </c>
       <c r="H162" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="I162" t="s">
         <v>1775</v>
@@ -16437,10 +16443,10 @@
         <v>58</v>
       </c>
       <c r="D163" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E163" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F163" t="s">
         <v>1783</v>
@@ -16764,7 +16770,7 @@
         <v>1606</v>
       </c>
       <c r="E168" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F168" t="s">
         <v>1831</v>
@@ -16833,7 +16839,7 @@
       </c>
       <c r="G169"/>
       <c r="H169" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="I169" t="s">
         <v>1843</v>

--- a/Objets_parlementaires_Jura.xlsx
+++ b/Objets_parlementaires_Jura.xlsx
@@ -455,7 +455,7 @@
     <t xml:space="preserve">Für eine neue Finanzierungsquelle für grosse öffentliche Ausgabenposten. Eine befristete Solidaritätsabgabe auf den Zahlungsverkehr</t>
   </si>
   <si>
-    <t xml:space="preserve">Pour une nouvelle source de financement des grands dossiers en charge des collectivités publiques. Une contribution de solidarité temporaire prélevée sur les mouvements financiers</t>
+    <t xml:space="preserve">Pour une nouvelle source de financement des grands dossiers dont les collectivités publiques ont la charge. Une contribution de solidarité temporaire prélevée sur les mouvements financiers</t>
   </si>
   <si>
     <t xml:space="preserve">Una nuova fonte di finanziamento per i grandi progetti a carico delle collettività pubbliche. Un contributo di solidarietà temporaneo prelevato sui movimenti finanziari</t>

--- a/Objets_parlementaires_Jura.xlsx
+++ b/Objets_parlementaires_Jura.xlsx
@@ -881,7 +881,7 @@
     <t xml:space="preserve">Der "Roi du Doubs" muss gerettet werden, bevor es zu spät ist</t>
   </si>
   <si>
-    <t xml:space="preserve">Il faut sauver le Roi du Doubs avant qu'il ne soit trop tard</t>
+    <t xml:space="preserve">Il faut sauver le "Roi du Doubs" avant qu'il ne soit trop tard</t>
   </si>
   <si>
     <t xml:space="preserve">Bisogna salvare il re del Doubs prima che sia troppo tardi</t>

--- a/Objets_parlementaires_Jura.xlsx
+++ b/Objets_parlementaires_Jura.xlsx
@@ -152,6 +152,9 @@
     <t xml:space="preserve">SR</t>
   </si>
   <si>
+    <t xml:space="preserve">UVEK</t>
+  </si>
+  <si>
     <t xml:space="preserve">Titel folgt</t>
   </si>
   <si>
@@ -194,9 +197,6 @@
     <t xml:space="preserve">2026-06-04</t>
   </si>
   <si>
-    <t xml:space="preserve">UVEK</t>
-  </si>
-  <si>
     <t xml:space="preserve">Wie sieht bei der Post die geografische Verteilung der Arbeitsplätze aus?</t>
   </si>
   <si>
@@ -371,6 +371,9 @@
     <t xml:space="preserve">26.4339</t>
   </si>
   <si>
+    <t xml:space="preserve">WBF</t>
+  </si>
+  <si>
     <t xml:space="preserve">Chômage des seniors : la Confédération se désengage-t-elle au pire moment ?</t>
   </si>
   <si>
@@ -396,9 +399,6 @@
   </si>
   <si>
     <t xml:space="preserve">2026-09-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WBF</t>
   </si>
   <si>
     <t xml:space="preserve">Mercosur: Wie sollen die 517 Millionen für die Landwirtschaft finanziert werden?</t>
@@ -6096,40 +6096,42 @@
       <c r="G3" t="s">
         <v>45</v>
       </c>
-      <c r="H3"/>
+      <c r="H3" t="s">
+        <v>46</v>
+      </c>
       <c r="I3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M3"/>
       <c r="N3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="P3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="S3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="T3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="U3" t="s">
         <v>44</v>
@@ -6141,10 +6143,10 @@
         <v>20263563</v>
       </c>
       <c r="B4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D4" t="s">
         <v>24</v>
@@ -6153,13 +6155,13 @@
         <v>25</v>
       </c>
       <c r="F4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G4" t="s">
         <v>27</v>
       </c>
       <c r="H4" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="I4" t="s">
         <v>61</v>
@@ -6210,7 +6212,7 @@
         <v>71</v>
       </c>
       <c r="C5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D5" t="s">
         <v>24</v>
@@ -6219,7 +6221,7 @@
         <v>25</v>
       </c>
       <c r="F5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G5" t="s">
         <v>27</v>
@@ -6285,7 +6287,7 @@
         <v>85</v>
       </c>
       <c r="F6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G6" t="s">
         <v>45</v>
@@ -6318,7 +6320,7 @@
         <v>92</v>
       </c>
       <c r="Q6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R6" t="s">
         <v>93</v>
@@ -6342,7 +6344,7 @@
         <v>96</v>
       </c>
       <c r="C7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D7" t="s">
         <v>24</v>
@@ -6356,7 +6358,9 @@
       <c r="G7" t="s">
         <v>27</v>
       </c>
-      <c r="H7"/>
+      <c r="H7" t="s">
+        <v>72</v>
+      </c>
       <c r="I7" t="s">
         <v>98</v>
       </c>
@@ -6364,7 +6368,7 @@
         <v>99</v>
       </c>
       <c r="K7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L7" t="s">
         <v>100</v>
@@ -6373,7 +6377,7 @@
         <v>101</v>
       </c>
       <c r="N7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O7" t="s">
         <v>102</v>
@@ -6382,7 +6386,7 @@
         <v>103</v>
       </c>
       <c r="Q7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R7" t="s">
         <v>104</v>
@@ -6420,7 +6424,9 @@
       <c r="G8" t="s">
         <v>27</v>
       </c>
-      <c r="H8"/>
+      <c r="H8" t="s">
+        <v>72</v>
+      </c>
       <c r="I8" t="s">
         <v>109</v>
       </c>
@@ -6428,7 +6434,7 @@
         <v>110</v>
       </c>
       <c r="K8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L8" t="s">
         <v>111</v>
@@ -6437,7 +6443,7 @@
         <v>112</v>
       </c>
       <c r="N8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O8" t="s">
         <v>113</v>
@@ -6470,7 +6476,7 @@
         <v>118</v>
       </c>
       <c r="C9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D9" t="s">
         <v>24</v>
@@ -6484,40 +6490,42 @@
       <c r="G9" t="s">
         <v>27</v>
       </c>
-      <c r="H9"/>
+      <c r="H9" t="s">
+        <v>119</v>
+      </c>
       <c r="I9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M9"/>
       <c r="N9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="P9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Q9" t="s">
         <v>36</v>
       </c>
       <c r="R9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="S9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="T9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="U9" t="s">
         <v>108</v>
@@ -6529,7 +6537,7 @@
         <v>20267901</v>
       </c>
       <c r="B10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C10" t="s">
         <v>23</v>
@@ -6541,13 +6549,13 @@
         <v>25</v>
       </c>
       <c r="F10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G10" t="s">
         <v>27</v>
       </c>
       <c r="H10" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="I10" t="s">
         <v>129</v>
@@ -6596,7 +6604,7 @@
         <v>139</v>
       </c>
       <c r="C11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D11" t="s">
         <v>140</v>
@@ -6610,22 +6618,24 @@
       <c r="G11" t="s">
         <v>45</v>
       </c>
-      <c r="H11"/>
+      <c r="H11" t="s">
+        <v>72</v>
+      </c>
       <c r="I11" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J11" t="s">
         <v>143</v>
       </c>
       <c r="K11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L11" t="s">
         <v>144</v>
       </c>
       <c r="M11"/>
       <c r="N11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O11" t="s">
         <v>145</v>
@@ -6658,7 +6668,7 @@
         <v>147</v>
       </c>
       <c r="C12" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D12" t="s">
         <v>140</v>
@@ -6869,7 +6879,7 @@
         <v>27</v>
       </c>
       <c r="H15" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="I15" t="s">
         <v>189</v>
@@ -6932,22 +6942,24 @@
       <c r="G16" t="s">
         <v>27</v>
       </c>
-      <c r="H16"/>
+      <c r="H16" t="s">
+        <v>72</v>
+      </c>
       <c r="I16" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J16" t="s">
         <v>200</v>
       </c>
       <c r="K16" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L16" t="s">
         <v>201</v>
       </c>
       <c r="M16"/>
       <c r="N16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O16" t="s">
         <v>202</v>
@@ -7086,7 +7098,7 @@
         <v>228</v>
       </c>
       <c r="Q18" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R18" t="s">
         <v>93</v>
@@ -7110,7 +7122,7 @@
         <v>229</v>
       </c>
       <c r="C19" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D19" t="s">
         <v>230</v>
@@ -7124,22 +7136,24 @@
       <c r="G19" t="s">
         <v>27</v>
       </c>
-      <c r="H19"/>
+      <c r="H19" t="s">
+        <v>46</v>
+      </c>
       <c r="I19" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J19" t="s">
         <v>232</v>
       </c>
       <c r="K19" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L19" t="s">
         <v>233</v>
       </c>
       <c r="M19"/>
       <c r="N19" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O19" t="s">
         <v>234</v>
@@ -7187,7 +7201,7 @@
         <v>27</v>
       </c>
       <c r="H20" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="I20" t="s">
         <v>240</v>
@@ -7236,7 +7250,7 @@
         <v>249</v>
       </c>
       <c r="C21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D21" t="s">
         <v>250</v>
@@ -7250,7 +7264,9 @@
       <c r="G21" t="s">
         <v>27</v>
       </c>
-      <c r="H21"/>
+      <c r="H21" t="s">
+        <v>28</v>
+      </c>
       <c r="I21" t="s">
         <v>251</v>
       </c>
@@ -7265,7 +7281,7 @@
         <v>254</v>
       </c>
       <c r="N21" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O21" t="s">
         <v>255</v>
@@ -7274,7 +7290,7 @@
         <v>256</v>
       </c>
       <c r="Q21" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R21" t="s">
         <v>257</v>
@@ -7336,7 +7352,7 @@
         <v>272</v>
       </c>
       <c r="Q22" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R22"/>
       <c r="S22"/>
@@ -7354,7 +7370,7 @@
         <v>274</v>
       </c>
       <c r="C23" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D23" t="s">
         <v>43</v>
@@ -7369,7 +7385,7 @@
         <v>45</v>
       </c>
       <c r="H23" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="I23" t="s">
         <v>275</v>
@@ -7420,7 +7436,7 @@
         <v>287</v>
       </c>
       <c r="C24" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D24" t="s">
         <v>288</v>
@@ -7435,7 +7451,7 @@
         <v>27</v>
       </c>
       <c r="H24" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="I24" t="s">
         <v>290</v>
@@ -7486,7 +7502,7 @@
         <v>298</v>
       </c>
       <c r="C25" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D25" t="s">
         <v>299</v>
@@ -7618,7 +7634,7 @@
         <v>325</v>
       </c>
       <c r="C27" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D27" t="s">
         <v>326</v>
@@ -7633,7 +7649,7 @@
         <v>27</v>
       </c>
       <c r="H27" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="I27" t="s">
         <v>327</v>
@@ -7684,7 +7700,7 @@
         <v>339</v>
       </c>
       <c r="C28" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D28" t="s">
         <v>326</v>
@@ -7699,7 +7715,7 @@
         <v>27</v>
       </c>
       <c r="H28" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="I28" t="s">
         <v>340</v>
@@ -7750,7 +7766,7 @@
         <v>347</v>
       </c>
       <c r="C29" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D29" t="s">
         <v>348</v>
@@ -7765,7 +7781,7 @@
         <v>27</v>
       </c>
       <c r="H29" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="I29" t="s">
         <v>350</v>
@@ -7882,7 +7898,7 @@
         <v>374</v>
       </c>
       <c r="C31" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D31" t="s">
         <v>326</v>
@@ -7897,7 +7913,7 @@
         <v>27</v>
       </c>
       <c r="H31" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="I31" t="s">
         <v>376</v>
@@ -8029,7 +8045,7 @@
         <v>27</v>
       </c>
       <c r="H33" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="I33" t="s">
         <v>399</v>
@@ -8093,7 +8109,7 @@
         <v>27</v>
       </c>
       <c r="H34" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="I34" t="s">
         <v>409</v>
@@ -8142,7 +8158,7 @@
         <v>418</v>
       </c>
       <c r="C35" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D35" t="s">
         <v>419</v>
@@ -8208,7 +8224,7 @@
         <v>432</v>
       </c>
       <c r="C36" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D36" t="s">
         <v>140</v>
@@ -8223,7 +8239,7 @@
         <v>45</v>
       </c>
       <c r="H36" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="I36" t="s">
         <v>433</v>
@@ -8289,7 +8305,7 @@
         <v>27</v>
       </c>
       <c r="H37" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="I37" t="s">
         <v>445</v>
@@ -8340,7 +8356,7 @@
         <v>456</v>
       </c>
       <c r="C38" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D38" t="s">
         <v>457</v>
@@ -8355,7 +8371,7 @@
         <v>27</v>
       </c>
       <c r="H38" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="I38" t="s">
         <v>458</v>
@@ -8470,7 +8486,7 @@
         <v>478</v>
       </c>
       <c r="C40" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D40" t="s">
         <v>230</v>
@@ -8485,7 +8501,7 @@
         <v>27</v>
       </c>
       <c r="H40" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="I40" t="s">
         <v>479</v>
@@ -8536,7 +8552,7 @@
         <v>486</v>
       </c>
       <c r="C41" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D41" t="s">
         <v>487</v>
@@ -8644,7 +8660,7 @@
         <v>508</v>
       </c>
       <c r="Q42" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R42" t="s">
         <v>509</v>
@@ -8668,7 +8684,7 @@
         <v>513</v>
       </c>
       <c r="C43" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D43" t="s">
         <v>514</v>
@@ -8683,7 +8699,7 @@
         <v>27</v>
       </c>
       <c r="H43" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="I43" t="s">
         <v>516</v>
@@ -8815,7 +8831,7 @@
         <v>27</v>
       </c>
       <c r="H45" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="I45" t="s">
         <v>535</v>
@@ -9026,7 +9042,7 @@
         <v>572</v>
       </c>
       <c r="Q48" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R48" t="s">
         <v>573</v>
@@ -9092,7 +9108,7 @@
         <v>585</v>
       </c>
       <c r="Q49" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R49" t="s">
         <v>157</v>
@@ -9116,7 +9132,7 @@
         <v>586</v>
       </c>
       <c r="C50" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D50" t="s">
         <v>587</v>
@@ -9182,7 +9198,7 @@
         <v>599</v>
       </c>
       <c r="C51" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D51" t="s">
         <v>600</v>
@@ -9197,7 +9213,7 @@
         <v>27</v>
       </c>
       <c r="H51" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="I51" t="s">
         <v>601</v>
@@ -9380,7 +9396,7 @@
         <v>634</v>
       </c>
       <c r="C54" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D54" t="s">
         <v>635</v>
@@ -9552,7 +9568,7 @@
         <v>663</v>
       </c>
       <c r="Q56" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R56" t="s">
         <v>664</v>
@@ -9616,7 +9632,7 @@
         <v>673</v>
       </c>
       <c r="Q57" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R57" t="s">
         <v>93</v>
@@ -9680,7 +9696,7 @@
         <v>683</v>
       </c>
       <c r="Q58" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R58" t="s">
         <v>684</v>
@@ -9746,7 +9762,7 @@
         <v>696</v>
       </c>
       <c r="Q59" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R59" t="s">
         <v>697</v>
@@ -9812,7 +9828,7 @@
         <v>708</v>
       </c>
       <c r="Q60" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R60" t="s">
         <v>497</v>
@@ -9836,7 +9852,7 @@
         <v>709</v>
       </c>
       <c r="C61" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D61" t="s">
         <v>457</v>
@@ -9851,7 +9867,7 @@
         <v>27</v>
       </c>
       <c r="H61" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="I61" t="s">
         <v>710</v>
@@ -9968,7 +9984,7 @@
         <v>728</v>
       </c>
       <c r="C63" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D63" t="s">
         <v>729</v>
@@ -10034,7 +10050,7 @@
         <v>738</v>
       </c>
       <c r="C64" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D64" t="s">
         <v>140</v>
@@ -10049,7 +10065,7 @@
         <v>45</v>
       </c>
       <c r="H64" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="I64" t="s">
         <v>740</v>
@@ -10100,7 +10116,7 @@
         <v>750</v>
       </c>
       <c r="C65" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D65" t="s">
         <v>751</v>
@@ -10166,7 +10182,7 @@
         <v>762</v>
       </c>
       <c r="C66" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D66" t="s">
         <v>763</v>
@@ -10313,7 +10329,7 @@
         <v>27</v>
       </c>
       <c r="H68" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="I68" t="s">
         <v>792</v>
@@ -10340,7 +10356,7 @@
         <v>798</v>
       </c>
       <c r="Q68" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R68" t="s">
         <v>236</v>
@@ -10443,7 +10459,7 @@
         <v>27</v>
       </c>
       <c r="H70" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="I70" t="s">
         <v>808</v>
@@ -10556,7 +10572,7 @@
         <v>828</v>
       </c>
       <c r="C72" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D72" t="s">
         <v>829</v>
@@ -10598,7 +10614,7 @@
         <v>837</v>
       </c>
       <c r="Q72" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R72" t="s">
         <v>838</v>
@@ -10662,7 +10678,7 @@
         <v>847</v>
       </c>
       <c r="Q73" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R73" t="s">
         <v>848</v>
@@ -10724,7 +10740,7 @@
         <v>860</v>
       </c>
       <c r="Q74" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R74"/>
       <c r="S74"/>
@@ -10742,7 +10758,7 @@
         <v>861</v>
       </c>
       <c r="C75" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D75" t="s">
         <v>862</v>
@@ -10757,7 +10773,7 @@
         <v>27</v>
       </c>
       <c r="H75" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="I75" t="s">
         <v>864</v>
@@ -10808,7 +10824,7 @@
         <v>874</v>
       </c>
       <c r="C76" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D76" t="s">
         <v>875</v>
@@ -10823,7 +10839,7 @@
         <v>27</v>
       </c>
       <c r="H76" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="I76" t="s">
         <v>876</v>
@@ -10850,7 +10866,7 @@
         <v>882</v>
       </c>
       <c r="Q76" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R76" t="s">
         <v>883</v>
@@ -10916,7 +10932,7 @@
         <v>895</v>
       </c>
       <c r="Q77" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R77" t="s">
         <v>896</v>
@@ -10983,13 +10999,13 @@
         <v>334</v>
       </c>
       <c r="R78" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="S78" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="T78" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="U78" t="s">
         <v>544</v>
@@ -11004,7 +11020,7 @@
         <v>908</v>
       </c>
       <c r="C79" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D79" t="s">
         <v>909</v>
@@ -11070,7 +11086,7 @@
         <v>920</v>
       </c>
       <c r="C80" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D80" t="s">
         <v>921</v>
@@ -11085,7 +11101,7 @@
         <v>27</v>
       </c>
       <c r="H80" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="I80" t="s">
         <v>923</v>
@@ -11149,7 +11165,7 @@
         <v>27</v>
       </c>
       <c r="H81" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="I81" t="s">
         <v>932</v>
@@ -11176,7 +11192,7 @@
         <v>938</v>
       </c>
       <c r="Q81" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R81" t="s">
         <v>939</v>
@@ -11200,7 +11216,7 @@
         <v>942</v>
       </c>
       <c r="C82" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D82" t="s">
         <v>701</v>
@@ -11215,7 +11231,7 @@
         <v>27</v>
       </c>
       <c r="H82" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="I82" t="s">
         <v>943</v>
@@ -11266,7 +11282,7 @@
         <v>953</v>
       </c>
       <c r="C83" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D83" t="s">
         <v>954</v>
@@ -11281,7 +11297,7 @@
         <v>45</v>
       </c>
       <c r="H83" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="I83" t="s">
         <v>956</v>
@@ -11308,7 +11324,7 @@
         <v>962</v>
       </c>
       <c r="Q83" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R83" t="s">
         <v>871</v>
@@ -11347,7 +11363,7 @@
         <v>27</v>
       </c>
       <c r="H84" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="I84" t="s">
         <v>966</v>
@@ -11374,7 +11390,7 @@
         <v>972</v>
       </c>
       <c r="Q84" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R84" t="s">
         <v>440</v>
@@ -11636,7 +11652,7 @@
         <v>1018</v>
       </c>
       <c r="Q88" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R88" t="s">
         <v>1019</v>
@@ -11660,7 +11676,7 @@
         <v>1022</v>
       </c>
       <c r="C89" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D89" t="s">
         <v>1023</v>
@@ -11702,7 +11718,7 @@
         <v>1030</v>
       </c>
       <c r="Q89" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R89" t="s">
         <v>1031</v>
@@ -11726,7 +11742,7 @@
         <v>1034</v>
       </c>
       <c r="C90" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D90" t="s">
         <v>1035</v>
@@ -11741,7 +11757,7 @@
         <v>27</v>
       </c>
       <c r="H90" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="I90" t="s">
         <v>1036</v>
@@ -11924,7 +11940,7 @@
         <v>1064</v>
       </c>
       <c r="C93" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D93" t="s">
         <v>635</v>
@@ -11939,7 +11955,7 @@
         <v>45</v>
       </c>
       <c r="H93" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="I93" t="s">
         <v>1066</v>
@@ -11990,7 +12006,7 @@
         <v>1076</v>
       </c>
       <c r="C94" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D94" t="s">
         <v>909</v>
@@ -12032,7 +12048,7 @@
         <v>1084</v>
       </c>
       <c r="Q94" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R94" t="s">
         <v>1085</v>
@@ -12067,7 +12083,7 @@
       </c>
       <c r="G95"/>
       <c r="H95" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="I95" t="s">
         <v>1091</v>
@@ -12094,7 +12110,7 @@
         <v>1097</v>
       </c>
       <c r="Q95" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R95"/>
       <c r="S95"/>
@@ -12150,7 +12166,7 @@
         <v>1104</v>
       </c>
       <c r="Q96" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R96"/>
       <c r="S96"/>
@@ -12208,7 +12224,7 @@
         <v>1114</v>
       </c>
       <c r="Q97" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R97" t="s">
         <v>1115</v>
@@ -12247,7 +12263,7 @@
         <v>27</v>
       </c>
       <c r="H98" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="I98" t="s">
         <v>1120</v>
@@ -12274,7 +12290,7 @@
         <v>1126</v>
       </c>
       <c r="Q98" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R98" t="s">
         <v>1127</v>
@@ -12298,7 +12314,7 @@
         <v>1130</v>
       </c>
       <c r="C99" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D99" t="s">
         <v>974</v>
@@ -12364,7 +12380,7 @@
         <v>1141</v>
       </c>
       <c r="C100" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D100" t="s">
         <v>1142</v>
@@ -12562,7 +12578,7 @@
         <v>1176</v>
       </c>
       <c r="C103" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D103" t="s">
         <v>1177</v>
@@ -12643,7 +12659,7 @@
         <v>27</v>
       </c>
       <c r="H104" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="I104" t="s">
         <v>1190</v>
@@ -12670,7 +12686,7 @@
         <v>1196</v>
       </c>
       <c r="Q104" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R104" t="s">
         <v>1197</v>
@@ -12694,7 +12710,7 @@
         <v>1200</v>
       </c>
       <c r="C105" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D105" t="s">
         <v>1201</v>
@@ -12709,7 +12725,7 @@
         <v>27</v>
       </c>
       <c r="H105" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="I105" t="s">
         <v>1202</v>
@@ -12771,7 +12787,7 @@
       </c>
       <c r="G106"/>
       <c r="H106" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="I106" t="s">
         <v>1214</v>
@@ -12798,7 +12814,7 @@
         <v>1220</v>
       </c>
       <c r="Q106" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R106"/>
       <c r="S106"/>
@@ -12858,7 +12874,7 @@
         <v>1228</v>
       </c>
       <c r="Q107" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R107" t="s">
         <v>697</v>
@@ -12922,7 +12938,7 @@
         <v>1237</v>
       </c>
       <c r="Q108" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R108" t="s">
         <v>1238</v>
@@ -12961,7 +12977,7 @@
         <v>27</v>
       </c>
       <c r="H109" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="I109" t="s">
         <v>1244</v>
@@ -12986,7 +13002,7 @@
         <v>1249</v>
       </c>
       <c r="Q109" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R109" t="s">
         <v>1127</v>
@@ -13106,7 +13122,7 @@
         <v>1268</v>
       </c>
       <c r="Q111" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R111" t="s">
         <v>1269</v>
@@ -13141,7 +13157,7 @@
       </c>
       <c r="G112"/>
       <c r="H112" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="I112" t="s">
         <v>1273</v>
@@ -13168,7 +13184,7 @@
         <v>1280</v>
       </c>
       <c r="Q112" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R112" t="s">
         <v>1281</v>
@@ -13273,7 +13289,7 @@
         <v>27</v>
       </c>
       <c r="H114" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="I114" t="s">
         <v>1299</v>
@@ -13324,7 +13340,7 @@
         <v>1309</v>
       </c>
       <c r="C115" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D115" t="s">
         <v>1310</v>
@@ -13339,7 +13355,7 @@
         <v>27</v>
       </c>
       <c r="H115" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="I115" t="s">
         <v>1311</v>
@@ -13366,7 +13382,7 @@
         <v>1317</v>
       </c>
       <c r="Q115" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R115" t="s">
         <v>950</v>
@@ -13456,7 +13472,7 @@
         <v>1330</v>
       </c>
       <c r="C117" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D117" t="s">
         <v>1331</v>
@@ -13471,7 +13487,7 @@
         <v>27</v>
       </c>
       <c r="H117" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="I117" t="s">
         <v>1332</v>
@@ -13537,7 +13553,7 @@
         <v>27</v>
       </c>
       <c r="H118" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="I118" t="s">
         <v>1342</v>
@@ -13652,7 +13668,7 @@
         <v>1357</v>
       </c>
       <c r="C120" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D120" t="s">
         <v>326</v>
@@ -13667,7 +13683,7 @@
         <v>27</v>
       </c>
       <c r="H120" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="I120" t="s">
         <v>1359</v>
@@ -13733,7 +13749,7 @@
         <v>27</v>
       </c>
       <c r="H121" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="I121" t="s">
         <v>1368</v>
@@ -13758,7 +13774,7 @@
         <v>1373</v>
       </c>
       <c r="Q121" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R121" t="s">
         <v>236</v>
@@ -13974,7 +13990,7 @@
         <v>1391</v>
       </c>
       <c r="C125" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D125" t="s">
         <v>829</v>
@@ -14016,7 +14032,7 @@
         <v>1399</v>
       </c>
       <c r="Q125" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R125" t="s">
         <v>1400</v>
@@ -14040,7 +14056,7 @@
         <v>1403</v>
       </c>
       <c r="C126" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D126" t="s">
         <v>887</v>
@@ -14082,7 +14098,7 @@
         <v>1411</v>
       </c>
       <c r="Q126" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R126" t="s">
         <v>474</v>
@@ -14106,7 +14122,7 @@
         <v>1412</v>
       </c>
       <c r="C127" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D127" t="s">
         <v>1413</v>
@@ -14121,7 +14137,7 @@
         <v>27</v>
       </c>
       <c r="H127" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="I127" t="s">
         <v>1414</v>
@@ -14148,7 +14164,7 @@
         <v>1420</v>
       </c>
       <c r="Q127" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R127" t="s">
         <v>1421</v>
@@ -14172,7 +14188,7 @@
         <v>1424</v>
       </c>
       <c r="C128" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D128" t="s">
         <v>1425</v>
@@ -14276,7 +14292,7 @@
         <v>1444</v>
       </c>
       <c r="Q129" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R129" t="s">
         <v>204</v>
@@ -14315,7 +14331,7 @@
         <v>27</v>
       </c>
       <c r="H130" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="I130" t="s">
         <v>1446</v>
@@ -14432,7 +14448,7 @@
         <v>1468</v>
       </c>
       <c r="C132" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D132" t="s">
         <v>1469</v>
@@ -14513,7 +14529,7 @@
         <v>27</v>
       </c>
       <c r="H133" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="I133" t="s">
         <v>1478</v>
@@ -14606,7 +14622,7 @@
         <v>1496</v>
       </c>
       <c r="Q134" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R134" t="s">
         <v>1497</v>
@@ -14630,7 +14646,7 @@
         <v>1500</v>
       </c>
       <c r="C135" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D135" t="s">
         <v>230</v>
@@ -14645,7 +14661,7 @@
         <v>27</v>
       </c>
       <c r="H135" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="I135" t="s">
         <v>1502</v>
@@ -14672,7 +14688,7 @@
         <v>1508</v>
       </c>
       <c r="Q135" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R135" t="s">
         <v>195</v>
@@ -14802,7 +14818,7 @@
         <v>1526</v>
       </c>
       <c r="Q137" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R137" t="s">
         <v>995</v>
@@ -14841,7 +14857,7 @@
         <v>27</v>
       </c>
       <c r="H138" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="I138" t="s">
         <v>1529</v>
@@ -14866,7 +14882,7 @@
         <v>1534</v>
       </c>
       <c r="Q138" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R138" t="s">
         <v>246</v>
@@ -14905,7 +14921,7 @@
         <v>27</v>
       </c>
       <c r="H139" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="I139" t="s">
         <v>1537</v>
@@ -15052,7 +15068,7 @@
         <v>1562</v>
       </c>
       <c r="Q141" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R141" t="s">
         <v>1563</v>
@@ -15076,7 +15092,7 @@
         <v>1566</v>
       </c>
       <c r="C142" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D142" t="s">
         <v>1567</v>
@@ -15091,7 +15107,7 @@
         <v>27</v>
       </c>
       <c r="H142" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="I142" t="s">
         <v>1569</v>
@@ -15142,7 +15158,7 @@
         <v>1579</v>
       </c>
       <c r="C143" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D143" t="s">
         <v>1580</v>
@@ -15208,7 +15224,7 @@
         <v>1592</v>
       </c>
       <c r="C144" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D144" t="s">
         <v>43</v>
@@ -15223,7 +15239,7 @@
         <v>45</v>
       </c>
       <c r="H144" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="I144" t="s">
         <v>1593</v>
@@ -15250,7 +15266,7 @@
         <v>1599</v>
       </c>
       <c r="Q144" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R144" t="s">
         <v>950</v>
@@ -15355,7 +15371,7 @@
         <v>27</v>
       </c>
       <c r="H146" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="I146" t="s">
         <v>1611</v>
@@ -15421,7 +15437,7 @@
         <v>27</v>
       </c>
       <c r="H147" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="I147" t="s">
         <v>1624</v>
@@ -15472,7 +15488,7 @@
         <v>1634</v>
       </c>
       <c r="C148" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D148" t="s">
         <v>600</v>
@@ -15487,7 +15503,7 @@
         <v>27</v>
       </c>
       <c r="H148" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="I148" t="s">
         <v>1635</v>
@@ -15514,7 +15530,7 @@
         <v>1641</v>
       </c>
       <c r="Q148" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R148" t="s">
         <v>1642</v>
@@ -15538,7 +15554,7 @@
         <v>1645</v>
       </c>
       <c r="C149" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D149" t="s">
         <v>1610</v>
@@ -15580,7 +15596,7 @@
         <v>1652</v>
       </c>
       <c r="Q149" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R149" t="s">
         <v>1653</v>
@@ -15604,7 +15620,7 @@
         <v>1656</v>
       </c>
       <c r="C150" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D150" t="s">
         <v>1319</v>
@@ -15670,7 +15686,7 @@
         <v>1667</v>
       </c>
       <c r="C151" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D151" t="s">
         <v>1668</v>
@@ -15736,7 +15752,7 @@
         <v>1677</v>
       </c>
       <c r="C152" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D152" t="s">
         <v>501</v>
@@ -15778,7 +15794,7 @@
         <v>1685</v>
       </c>
       <c r="Q152" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R152" t="s">
         <v>596</v>
@@ -15802,7 +15818,7 @@
         <v>1686</v>
       </c>
       <c r="C153" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D153" t="s">
         <v>1687</v>
@@ -15844,7 +15860,7 @@
         <v>1695</v>
       </c>
       <c r="Q153" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R153" t="s">
         <v>917</v>
@@ -15910,7 +15926,7 @@
         <v>1705</v>
       </c>
       <c r="Q154" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R154" t="s">
         <v>1465</v>
@@ -15949,7 +15965,7 @@
         <v>27</v>
       </c>
       <c r="H155" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="I155" t="s">
         <v>1707</v>
@@ -16013,7 +16029,7 @@
         <v>27</v>
       </c>
       <c r="H156" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="I156" t="s">
         <v>1715</v>
@@ -16038,7 +16054,7 @@
         <v>1720</v>
       </c>
       <c r="Q156" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R156" t="s">
         <v>195</v>
@@ -16126,7 +16142,7 @@
         <v>1734</v>
       </c>
       <c r="C158" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D158" t="s">
         <v>1035</v>
@@ -16141,7 +16157,7 @@
         <v>27</v>
       </c>
       <c r="H158" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="I158" t="s">
         <v>1736</v>
@@ -16390,7 +16406,7 @@
         <v>1776</v>
       </c>
       <c r="C162" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D162" t="s">
         <v>1777</v>
@@ -16405,7 +16421,7 @@
         <v>27</v>
       </c>
       <c r="H162" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="I162" t="s">
         <v>1779</v>
@@ -16456,7 +16472,7 @@
         <v>1786</v>
       </c>
       <c r="C163" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D163" t="s">
         <v>140</v>
@@ -16471,7 +16487,7 @@
         <v>45</v>
       </c>
       <c r="H163" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="I163" t="s">
         <v>1788</v>
@@ -16498,7 +16514,7 @@
         <v>1794</v>
       </c>
       <c r="Q163" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R163" t="s">
         <v>1795</v>
@@ -16522,7 +16538,7 @@
         <v>1798</v>
       </c>
       <c r="C164" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D164" t="s">
         <v>829</v>
@@ -16537,7 +16553,7 @@
         <v>27</v>
       </c>
       <c r="H164" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="I164" t="s">
         <v>1800</v>
@@ -16564,7 +16580,7 @@
         <v>1806</v>
       </c>
       <c r="Q164" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R164" t="s">
         <v>1807</v>
@@ -16603,7 +16619,7 @@
         <v>27</v>
       </c>
       <c r="H165" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="I165" t="s">
         <v>1812</v>
@@ -16667,7 +16683,7 @@
         <v>27</v>
       </c>
       <c r="H166" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="I166" t="s">
         <v>1819</v>
@@ -16731,7 +16747,7 @@
         <v>27</v>
       </c>
       <c r="H167" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="I167" t="s">
         <v>1828</v>
@@ -16855,7 +16871,7 @@
       </c>
       <c r="G169"/>
       <c r="H169" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="I169" t="s">
         <v>1847</v>
@@ -16882,7 +16898,7 @@
         <v>1853</v>
       </c>
       <c r="Q169" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R169" t="s">
         <v>1854</v>

--- a/Objets_parlementaires_Jura.xlsx
+++ b/Objets_parlementaires_Jura.xlsx
@@ -8993,9 +8993,7 @@
         <v>570</v>
       </c>
       <c r="D47"/>
-      <c r="E47" t="s">
-        <v>168</v>
-      </c>
+      <c r="E47"/>
       <c r="F47" t="s">
         <v>571</v>
       </c>
@@ -13075,9 +13073,7 @@
         <v>570</v>
       </c>
       <c r="D110"/>
-      <c r="E110" t="s">
-        <v>168</v>
-      </c>
+      <c r="E110"/>
       <c r="F110" t="s">
         <v>1263</v>
       </c>
@@ -15021,9 +15017,7 @@
         <v>570</v>
       </c>
       <c r="D140"/>
-      <c r="E140" t="s">
-        <v>168</v>
-      </c>
+      <c r="E140"/>
       <c r="F140" t="s">
         <v>1557</v>
       </c>
